--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="135">
   <si>
     <t>CUMA</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>S.ARAS.</t>
+  </si>
+  <si>
+    <t>İLETİŞİM BAŞKANLIĞI</t>
+  </si>
+  <si>
+    <t>S.CÜREBAL.</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1563,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2161,12 +2167,6 @@
     <xf numFmtId="49" fontId="8" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="6" borderId="41" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="6" borderId="42" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="37" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2196,6 +2196,33 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="41" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="42" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="43" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="32" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="33" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="34" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="38" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="39" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="40" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -3153,11 +3180,11 @@
       <c r="AE9" s="129"/>
       <c r="AF9" s="130"/>
       <c r="AG9" s="38"/>
-      <c r="AH9" s="136" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI9" s="137"/>
-      <c r="AJ9" s="138"/>
+      <c r="AH9" s="167" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="168"/>
+      <c r="AJ9" s="169"/>
       <c r="AK9" s="38"/>
       <c r="AL9" s="136" t="s">
         <v>15</v>
@@ -3206,9 +3233,11 @@
       <c r="AE10" s="174"/>
       <c r="AF10" s="175"/>
       <c r="AG10" s="39"/>
-      <c r="AH10" s="170"/>
-      <c r="AI10" s="171"/>
-      <c r="AJ10" s="172"/>
+      <c r="AH10" s="221" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI10" s="222"/>
+      <c r="AJ10" s="223"/>
       <c r="AK10" s="39"/>
       <c r="AL10" s="170"/>
       <c r="AM10" s="171"/>
@@ -3267,7 +3296,7 @@
       </c>
       <c r="AQ11" s="22">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" s="27"/>
     </row>
@@ -4046,10 +4075,10 @@
         <v>34</v>
       </c>
       <c r="AG24" s="38"/>
-      <c r="AH24" s="101" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI24" s="102"/>
+      <c r="AH24" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI24" s="104"/>
       <c r="AJ24" s="56" t="s">
         <v>34</v>
       </c>
@@ -4066,7 +4095,7 @@
       </c>
       <c r="AQ24" s="22">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR24" s="27"/>
     </row>
@@ -4232,7 +4261,7 @@
       </c>
       <c r="AQ26" s="22">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR26" s="27"/>
     </row>
@@ -6213,11 +6242,11 @@
       <c r="AA64" s="129"/>
       <c r="AB64" s="130"/>
       <c r="AC64" s="39"/>
-      <c r="AD64" s="220" t="s">
+      <c r="AD64" s="218" t="s">
         <v>120</v>
       </c>
-      <c r="AE64" s="221"/>
-      <c r="AF64" s="222"/>
+      <c r="AE64" s="219"/>
+      <c r="AF64" s="220"/>
       <c r="AG64" s="39"/>
       <c r="AH64" s="78"/>
       <c r="AI64" s="79"/>
@@ -6421,9 +6450,11 @@
       <c r="AE68" s="132"/>
       <c r="AF68" s="59"/>
       <c r="AG68" s="33"/>
-      <c r="AH68" s="91"/>
-      <c r="AI68" s="92"/>
-      <c r="AJ68" s="31"/>
+      <c r="AH68" s="139" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI68" s="140"/>
+      <c r="AJ68" s="68"/>
       <c r="AK68" s="29"/>
       <c r="AL68" s="139" t="s">
         <v>116</v>
@@ -6557,9 +6588,11 @@
       <c r="AE70" s="89"/>
       <c r="AF70" s="90"/>
       <c r="AG70" s="28"/>
-      <c r="AH70" s="98"/>
-      <c r="AI70" s="99"/>
-      <c r="AJ70" s="100"/>
+      <c r="AH70" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI70" s="89"/>
+      <c r="AJ70" s="90"/>
       <c r="AK70" s="29"/>
       <c r="AL70" s="208" t="s">
         <v>118</v>
@@ -6627,7 +6660,9 @@
       <c r="AE71" s="115"/>
       <c r="AF71" s="116"/>
       <c r="AG71" s="29"/>
-      <c r="AH71" s="75"/>
+      <c r="AH71" s="75" t="s">
+        <v>19</v>
+      </c>
       <c r="AI71" s="76"/>
       <c r="AJ71" s="77"/>
       <c r="AK71" s="29"/>
@@ -6685,7 +6720,9 @@
       <c r="AE72" s="106"/>
       <c r="AF72" s="107"/>
       <c r="AG72" s="33"/>
-      <c r="AH72" s="78"/>
+      <c r="AH72" s="78" t="s">
+        <v>15</v>
+      </c>
       <c r="AI72" s="79"/>
       <c r="AJ72" s="80"/>
       <c r="AK72" s="29"/>
@@ -6965,11 +7002,11 @@
       <c r="S77" s="76"/>
       <c r="T77" s="77"/>
       <c r="U77" s="28"/>
-      <c r="V77" s="216" t="s">
+      <c r="V77" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="W77" s="217"/>
-      <c r="X77" s="218"/>
+      <c r="W77" s="215"/>
+      <c r="X77" s="216"/>
       <c r="Y77" s="29"/>
       <c r="Z77" s="75" t="s">
         <v>28</v>
@@ -7235,7 +7272,7 @@
         <v>52</v>
       </c>
       <c r="W82" s="82"/>
-      <c r="X82" s="219"/>
+      <c r="X82" s="217"/>
       <c r="Y82" s="29"/>
       <c r="Z82" s="98" t="s">
         <v>52</v>
@@ -7289,17 +7326,17 @@
       <c r="S83" s="76"/>
       <c r="T83" s="77"/>
       <c r="U83" s="29"/>
-      <c r="V83" s="213" t="s">
+      <c r="V83" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="W83" s="214"/>
-      <c r="X83" s="215"/>
+      <c r="W83" s="212"/>
+      <c r="X83" s="213"/>
       <c r="Y83" s="29"/>
-      <c r="Z83" s="216" t="s">
+      <c r="Z83" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="217"/>
-      <c r="AB83" s="218"/>
+      <c r="AA83" s="215"/>
+      <c r="AB83" s="216"/>
       <c r="AC83" s="29"/>
       <c r="AD83" s="75" t="s">
         <v>15</v>
@@ -7747,11 +7784,11 @@
       <c r="AE92" s="159"/>
       <c r="AF92" s="69"/>
       <c r="AG92" s="29"/>
-      <c r="AH92" s="144" t="s">
+      <c r="AH92" s="224" t="s">
         <v>58</v>
       </c>
-      <c r="AI92" s="145"/>
-      <c r="AJ92" s="62"/>
+      <c r="AI92" s="225"/>
+      <c r="AJ92" s="226"/>
       <c r="AK92" s="29"/>
       <c r="AL92" s="91"/>
       <c r="AM92" s="92"/>
@@ -7799,11 +7836,11 @@
       <c r="AE93" s="82"/>
       <c r="AF93" s="70"/>
       <c r="AG93" s="29"/>
-      <c r="AH93" s="83" t="s">
+      <c r="AH93" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="AI93" s="84"/>
-      <c r="AJ93" s="64"/>
+      <c r="AI93" s="228"/>
+      <c r="AJ93" s="229"/>
       <c r="AK93" s="32"/>
       <c r="AL93" s="95"/>
       <c r="AM93" s="96"/>
@@ -7855,11 +7892,11 @@
         <v>32</v>
       </c>
       <c r="AG94" s="29"/>
-      <c r="AH94" s="110" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI94" s="111"/>
-      <c r="AJ94" s="55" t="s">
+      <c r="AH94" s="154" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI94" s="155"/>
+      <c r="AJ94" s="71" t="s">
         <v>32</v>
       </c>
       <c r="AK94" s="28"/>
@@ -7913,11 +7950,11 @@
         <v>33</v>
       </c>
       <c r="AG95" s="29"/>
-      <c r="AH95" s="112" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI95" s="113"/>
-      <c r="AJ95" s="56" t="s">
+      <c r="AH95" s="156" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI95" s="157"/>
+      <c r="AJ95" s="72" t="s">
         <v>33</v>
       </c>
       <c r="AK95" s="28"/>
@@ -7971,11 +8008,11 @@
         <v>34</v>
       </c>
       <c r="AG96" s="28"/>
-      <c r="AH96" s="101" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI96" s="102"/>
-      <c r="AJ96" s="56" t="s">
+      <c r="AH96" s="156" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI96" s="157"/>
+      <c r="AJ96" s="72" t="s">
         <v>34</v>
       </c>
       <c r="AK96" s="29"/>
@@ -8029,11 +8066,11 @@
         <v>35</v>
       </c>
       <c r="AG97" s="28"/>
-      <c r="AH97" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI97" s="104"/>
-      <c r="AJ97" s="56" t="s">
+      <c r="AH97" s="156" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI97" s="157"/>
+      <c r="AJ97" s="72" t="s">
         <v>35</v>
       </c>
       <c r="AK97" s="29"/>
@@ -8093,11 +8130,11 @@
         <v>35</v>
       </c>
       <c r="AG98" s="33"/>
-      <c r="AH98" s="211" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI98" s="212"/>
-      <c r="AJ98" s="57" t="s">
+      <c r="AH98" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI98" s="161"/>
+      <c r="AJ98" s="73" t="s">
         <v>35</v>
       </c>
       <c r="AK98" s="29"/>
@@ -9654,7 +9691,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AF22:AF27 AB22:AB27 P22:P27 AB94:AB98 X22:X27 T22:T27 P36:P37 D58 H59 AJ22:AJ27 AF94:AF98 AN22:AN27 AJ94:AJ98 D22:D27 D70:D75 H70:H75 H22:H27 L22:L27 L59">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 J132:L133 J114:L115 B126:D127 F108:H109 B114:D115 J126:L127 J120:L121 B108:D109 R22:S27 AH8:AJ10 AH63:AJ64 AL56:AN58 Z102:AB102 N56:P58 AH71:AJ72 V83:X84 AD22:AE27 R83:T84 N83:P84 N49:P51 V42:X44 AL77:AN78 V49:X51 V63:X64 N77:P78 R8:T10 AD89:AF90 V8:X10 AH42:AJ44 R63:T64 AL89:AN90 N22:O27 N101:P102 AD83:AF84 V101:X102 Z14:AB16 Z42:AB44 R14:T16 Z34:AB37 AH14:AJ16 B95:D96 AD34:AF37 V22:W27 R95:T96 B101:D102 N63:P64 R55:T58 AD8:AF10 R89:T90 J57:L58 AL14:AN16 N8:P10 V14:X16 R34:T37 V95:X96 AH83:AJ84 Z56:AB58 Z63:AB65 V56:X58 AL101:AN102 AL49:AN51 AL8:AN10 N42:P44 R77:T78 R42:T44 AL83:AN84 AD71:AF72 Z71:AB72 Z83:AB84 AH34:AJ37 AD63:AF65 AH77:AJ78 J59:K59 N14:P16 AL95:AN96 AH102:AJ102 V34:X37 N89:P90 AD94:AE98 N34:P35 AD42:AF44 Z89:AB90 Z94:AA98 AH22:AI27 V89:X90 R71:T72 Z49:AB51 V71:X72 Z22:AA27 AL22:AM27 AH49:AJ51 Z77:AB78 AL71:AN72 N71:P72 Z8:AB10 AD77:AF78 AD14:AF16 R101:T102 R49:T50 N95:P96 AL63:AN64 V77:X78 AL42:AN44 AH56:AJ58 AH94:AI98 AD49:AF51 B58:C58 N36:O37 F101:H102 B22:C27 F95:H96 B14:D16 F22:G27 B83:D84 F14:H16 F63:H64 F89:H90 B42:D44 B70:C75 B89:D90 B49:D51 F59:G59 AD102:AF102 B63:D64 F51:H52 B8:D10 F42:H46 F83:H84 B34:D37 F8:H10 F34:H37 AH89:AJ90 F70:G75 F57:H58 B56:D57 J95:L96 J101:L102 J77:L78 J8:L10 J22:K27 J63:L64 J34:L37 J83:L84 J42:L46 J14:L16 J89:L90 J71:L72 J51:L52 AL34:AN37 AD56:AF58">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 J132:L133 J114:L115 B126:D127 F108:H109 B114:D115 J126:L127 J120:L121 B108:D109 R22:S27 AH8:AJ10 AH63:AJ64 AL56:AN58 Z102:AB102 N56:P58 AD56:AF58 V83:X84 AD22:AE27 R83:T84 N83:P84 N49:P51 V42:X44 AL77:AN78 V49:X51 V63:X64 N77:P78 R8:T10 AD89:AF90 V8:X10 AH42:AJ44 R63:T64 AL89:AN90 N22:O27 N101:P102 AD83:AF84 V101:X102 Z14:AB16 Z42:AB44 R14:T16 Z34:AB37 AH14:AJ16 B95:D96 AD34:AF37 V22:W27 R95:T96 B101:D102 N63:P64 R55:T58 AD8:AF10 R89:T90 J57:L58 AL14:AN16 N8:P10 V14:X16 R34:T37 V95:X96 AH83:AJ84 Z56:AB58 Z63:AB65 V56:X58 AL101:AN102 AL49:AN51 AL8:AN10 N42:P44 R77:T78 R42:T44 AL83:AN84 AD71:AF72 Z71:AB72 Z83:AB84 AH34:AJ37 AD63:AF65 AH77:AJ78 J59:K59 N14:P16 AL95:AN96 AH102:AJ102 V34:X37 N89:P90 AD94:AE98 N34:P35 AD42:AF44 Z89:AB90 Z94:AA98 AH71:AJ72 V89:X90 R71:T72 Z49:AB51 V71:X72 Z22:AA27 AL22:AM27 AH49:AJ51 Z77:AB78 AL71:AN72 N71:P72 Z8:AB10 AD77:AF78 AD14:AF16 R101:T102 R49:T50 N95:P96 AL63:AN64 V77:X78 AL42:AN44 AH56:AJ58 AH94:AI98 AD49:AF51 B58:C58 N36:O37 F101:H102 B22:C27 F95:H96 B14:D16 F22:G27 B83:D84 F14:H16 F63:H64 F89:H90 B42:D44 B70:C75 B89:D90 B49:D51 F59:G59 AD102:AF102 B63:D64 F51:H52 B8:D10 F42:H46 F83:H84 B34:D37 F8:H10 F34:H37 AH89:AJ90 F70:G75 F57:H58 B56:D57 J95:L96 J101:L102 J77:L78 J8:L10 J22:K27 J63:L64 J34:L37 J83:L84 J42:L46 J14:L16 J89:L90 J71:L72 J51:L52 AL34:AN37 AH22:AI27">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="138">
   <si>
     <t>CUMA</t>
   </si>
@@ -428,7 +428,16 @@
     <t>İLETİŞİM BAŞKANLIĞI</t>
   </si>
   <si>
-    <t>S.CÜREBAL.</t>
+    <t>CUMHURBAŞKANLIĞI</t>
+  </si>
+  <si>
+    <t>Sultanahmet</t>
+  </si>
+  <si>
+    <t>06.00</t>
+  </si>
+  <si>
+    <t>Dolmabahçe</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1572,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1759,6 +1768,12 @@
     <xf numFmtId="49" fontId="38" fillId="6" borderId="34" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="34" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="40" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1783,10 +1798,10 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="8" borderId="38" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="8" borderId="39" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="38" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="39" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1933,6 +1948,15 @@
     <xf numFmtId="49" fontId="38" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1942,28 +1966,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="38" fillId="8" borderId="32" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2044,6 +2050,15 @@
     <xf numFmtId="49" fontId="39" fillId="6" borderId="37" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="39" fillId="37" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2051,15 +2066,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="39" fillId="37" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="38" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2077,6 +2083,12 @@
     <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="38" fillId="8" borderId="38" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="8" borderId="39" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="37" fillId="9" borderId="35" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2149,6 +2161,15 @@
     <xf numFmtId="49" fontId="37" fillId="9" borderId="42" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2167,6 +2188,12 @@
     <xf numFmtId="49" fontId="8" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="32" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="9" borderId="33" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="37" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2196,33 +2223,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="41" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="42" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="43" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="32" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="33" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="34" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="38" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="39" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="40" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2596,7 +2596,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="200" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2622,197 +2622,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="23" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="23" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="23" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="23" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="23" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="23" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" style="23" customWidth="1"/>
-    <col min="10" max="10" width="2.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="23" customWidth="1"/>
-    <col min="14" max="14" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
-    <col min="17" max="17" width="1.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="1.7109375" customWidth="1"/>
-    <col min="26" max="26" width="2.7109375" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" customWidth="1"/>
-    <col min="29" max="29" width="1.7109375" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" customWidth="1"/>
-    <col min="31" max="31" width="20.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="33" width="1.7109375" customWidth="1"/>
-    <col min="34" max="34" width="2.7109375" customWidth="1"/>
-    <col min="35" max="35" width="20.7109375" customWidth="1"/>
-    <col min="36" max="36" width="6.7109375" customWidth="1"/>
-    <col min="37" max="37" width="1.7109375" customWidth="1"/>
-    <col min="38" max="38" width="2.7109375" customWidth="1"/>
-    <col min="39" max="39" width="20.7109375" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" customWidth="1"/>
-    <col min="41" max="41" width="2.7109375" customWidth="1"/>
-    <col min="42" max="42" width="16.7109375" customWidth="1"/>
-    <col min="43" max="43" width="3.7109375" customWidth="1"/>
-    <col min="44" max="44" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="2.6640625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="23" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="23" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="23" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" style="23" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="23" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="1.6640625" style="23" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" customWidth="1"/>
+    <col min="17" max="17" width="1.6640625" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="1.6640625" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="1.6640625" customWidth="1"/>
+    <col min="26" max="26" width="2.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="1.6640625" customWidth="1"/>
+    <col min="30" max="30" width="2.6640625" customWidth="1"/>
+    <col min="31" max="31" width="20.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="33" width="1.6640625" customWidth="1"/>
+    <col min="34" max="34" width="2.6640625" customWidth="1"/>
+    <col min="35" max="35" width="20.6640625" customWidth="1"/>
+    <col min="36" max="36" width="6.6640625" customWidth="1"/>
+    <col min="37" max="37" width="1.6640625" customWidth="1"/>
+    <col min="38" max="38" width="2.6640625" customWidth="1"/>
+    <col min="39" max="39" width="20.6640625" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" customWidth="1"/>
+    <col min="41" max="41" width="2.6640625" customWidth="1"/>
+    <col min="42" max="42" width="16.6640625" customWidth="1"/>
+    <col min="43" max="43" width="3.6640625" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="193" t="s">
+      <c r="B1" s="194" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="194" t="s">
+      <c r="F1" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="194" t="s">
+      <c r="J1" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="194"/>
-      <c r="L1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="196"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="198" t="s">
+      <c r="N1" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="185"/>
-      <c r="P1" s="185"/>
+      <c r="O1" s="186"/>
+      <c r="P1" s="186"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="185" t="s">
+      <c r="R1" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="185"/>
-      <c r="T1" s="185"/>
+      <c r="S1" s="186"/>
+      <c r="T1" s="186"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="185" t="s">
+      <c r="V1" s="186" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="185"/>
-      <c r="X1" s="185"/>
+      <c r="W1" s="186"/>
+      <c r="X1" s="186"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="185" t="s">
+      <c r="Z1" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="185"/>
-      <c r="AB1" s="185"/>
+      <c r="AA1" s="186"/>
+      <c r="AB1" s="186"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="185" t="s">
+      <c r="AD1" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="185"/>
-      <c r="AF1" s="185"/>
+      <c r="AE1" s="186"/>
+      <c r="AF1" s="186"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="185" t="s">
+      <c r="AH1" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="185"/>
-      <c r="AJ1" s="185"/>
+      <c r="AI1" s="186"/>
+      <c r="AJ1" s="186"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="185" t="s">
+      <c r="AL1" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="185"/>
-      <c r="AN1" s="189"/>
+      <c r="AM1" s="186"/>
+      <c r="AN1" s="190"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="196">
+      <c r="B2" s="197">
         <f>N2-3</f>
         <v>46178</v>
       </c>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="197">
+      <c r="F2" s="198">
         <f>N2-2</f>
         <v>46179</v>
       </c>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="197">
+      <c r="J2" s="198">
         <f>N2-1</f>
         <v>46180</v>
       </c>
-      <c r="K2" s="197"/>
-      <c r="L2" s="200"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="201"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="199">
+      <c r="N2" s="200">
         <v>46181</v>
       </c>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
+      <c r="O2" s="191"/>
+      <c r="P2" s="191"/>
       <c r="Q2" s="47"/>
-      <c r="R2" s="190">
+      <c r="R2" s="191">
         <f>N2+1</f>
         <v>46182</v>
       </c>
-      <c r="S2" s="190"/>
-      <c r="T2" s="190"/>
+      <c r="S2" s="191"/>
+      <c r="T2" s="191"/>
       <c r="U2" s="47"/>
-      <c r="V2" s="190">
+      <c r="V2" s="191">
         <f>N2+2</f>
         <v>46183</v>
       </c>
-      <c r="W2" s="190"/>
-      <c r="X2" s="190"/>
+      <c r="W2" s="191"/>
+      <c r="X2" s="191"/>
       <c r="Y2" s="47"/>
-      <c r="Z2" s="190">
+      <c r="Z2" s="191">
         <f>N2+3</f>
         <v>46184</v>
       </c>
-      <c r="AA2" s="190"/>
-      <c r="AB2" s="190"/>
+      <c r="AA2" s="191"/>
+      <c r="AB2" s="191"/>
       <c r="AC2" s="47"/>
-      <c r="AD2" s="190">
+      <c r="AD2" s="191">
         <f>N2+4</f>
         <v>46185</v>
       </c>
-      <c r="AE2" s="190"/>
-      <c r="AF2" s="190"/>
+      <c r="AE2" s="191"/>
+      <c r="AF2" s="191"/>
       <c r="AG2" s="47"/>
-      <c r="AH2" s="190">
+      <c r="AH2" s="191">
         <f>N2+5</f>
         <v>46186</v>
       </c>
-      <c r="AI2" s="190"/>
-      <c r="AJ2" s="190"/>
+      <c r="AI2" s="191"/>
+      <c r="AJ2" s="191"/>
       <c r="AK2" s="47"/>
-      <c r="AL2" s="190">
+      <c r="AL2" s="191">
         <f>N2+6</f>
         <v>46187</v>
       </c>
-      <c r="AM2" s="190"/>
-      <c r="AN2" s="191"/>
+      <c r="AM2" s="191"/>
+      <c r="AN2" s="192"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2858,165 +2858,165 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="192"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
+      <c r="L4" s="193"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="180" t="s">
+      <c r="N4" s="179" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="180"/>
-      <c r="P4" s="180"/>
-      <c r="Q4" s="180"/>
-      <c r="R4" s="180"/>
-      <c r="S4" s="180"/>
-      <c r="T4" s="180"/>
-      <c r="U4" s="180"/>
-      <c r="V4" s="180"/>
-      <c r="W4" s="180"/>
-      <c r="X4" s="180"/>
-      <c r="Y4" s="180"/>
-      <c r="Z4" s="180"/>
-      <c r="AA4" s="180"/>
-      <c r="AB4" s="180"/>
+      <c r="O4" s="179"/>
+      <c r="P4" s="179"/>
+      <c r="Q4" s="179"/>
+      <c r="R4" s="179"/>
+      <c r="S4" s="179"/>
+      <c r="T4" s="179"/>
+      <c r="U4" s="179"/>
+      <c r="V4" s="179"/>
+      <c r="W4" s="179"/>
+      <c r="X4" s="179"/>
+      <c r="Y4" s="179"/>
+      <c r="Z4" s="179"/>
+      <c r="AA4" s="179"/>
+      <c r="AB4" s="179"/>
       <c r="AC4" s="30"/>
-      <c r="AD4" s="192"/>
-      <c r="AE4" s="192"/>
-      <c r="AF4" s="192"/>
-      <c r="AG4" s="192"/>
-      <c r="AH4" s="192"/>
-      <c r="AI4" s="192"/>
-      <c r="AJ4" s="192"/>
-      <c r="AK4" s="192"/>
-      <c r="AL4" s="192"/>
-      <c r="AM4" s="192"/>
-      <c r="AN4" s="192"/>
+      <c r="AD4" s="193"/>
+      <c r="AE4" s="193"/>
+      <c r="AF4" s="193"/>
+      <c r="AG4" s="193"/>
+      <c r="AH4" s="193"/>
+      <c r="AI4" s="193"/>
+      <c r="AJ4" s="193"/>
+      <c r="AK4" s="193"/>
+      <c r="AL4" s="193"/>
+      <c r="AM4" s="193"/>
+      <c r="AN4" s="193"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="192"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="193"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="193"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="193"/>
+      <c r="K5" s="193"/>
+      <c r="L5" s="193"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="180"/>
-      <c r="U5" s="180"/>
-      <c r="V5" s="180"/>
-      <c r="W5" s="180"/>
-      <c r="X5" s="180"/>
-      <c r="Y5" s="180"/>
-      <c r="Z5" s="180"/>
-      <c r="AA5" s="180"/>
-      <c r="AB5" s="180"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="179"/>
+      <c r="R5" s="179"/>
+      <c r="S5" s="179"/>
+      <c r="T5" s="179"/>
+      <c r="U5" s="179"/>
+      <c r="V5" s="179"/>
+      <c r="W5" s="179"/>
+      <c r="X5" s="179"/>
+      <c r="Y5" s="179"/>
+      <c r="Z5" s="179"/>
+      <c r="AA5" s="179"/>
+      <c r="AB5" s="179"/>
       <c r="AC5" s="30"/>
-      <c r="AD5" s="192"/>
-      <c r="AE5" s="192"/>
-      <c r="AF5" s="192"/>
-      <c r="AG5" s="192"/>
-      <c r="AH5" s="192"/>
-      <c r="AI5" s="192"/>
-      <c r="AJ5" s="192"/>
-      <c r="AK5" s="192"/>
-      <c r="AL5" s="192"/>
-      <c r="AM5" s="192"/>
-      <c r="AN5" s="192"/>
+      <c r="AD5" s="193"/>
+      <c r="AE5" s="193"/>
+      <c r="AF5" s="193"/>
+      <c r="AG5" s="193"/>
+      <c r="AH5" s="193"/>
+      <c r="AI5" s="193"/>
+      <c r="AJ5" s="193"/>
+      <c r="AK5" s="193"/>
+      <c r="AL5" s="193"/>
+      <c r="AM5" s="193"/>
+      <c r="AN5" s="193"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="122"/>
-      <c r="C6" s="123"/>
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="124"/>
+      <c r="C6" s="125"/>
       <c r="D6" s="52"/>
       <c r="E6" s="36"/>
-      <c r="F6" s="122" t="s">
+      <c r="F6" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="123"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="52" t="s">
         <v>44</v>
       </c>
       <c r="I6" s="33"/>
-      <c r="J6" s="122" t="s">
+      <c r="J6" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="123"/>
+      <c r="K6" s="125"/>
       <c r="L6" s="52" t="s">
         <v>44</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="91" t="s">
+      <c r="N6" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="O6" s="92"/>
+      <c r="O6" s="94"/>
       <c r="P6" s="31" t="s">
         <v>88</v>
       </c>
       <c r="Q6" s="36"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="92"/>
+      <c r="R6" s="93"/>
+      <c r="S6" s="94"/>
       <c r="T6" s="31"/>
       <c r="U6" s="33"/>
-      <c r="V6" s="91" t="s">
+      <c r="V6" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="W6" s="92"/>
+      <c r="W6" s="94"/>
       <c r="X6" s="31" t="s">
         <v>66</v>
       </c>
       <c r="Y6" s="65"/>
-      <c r="Z6" s="91" t="s">
+      <c r="Z6" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="AA6" s="92"/>
+      <c r="AA6" s="94"/>
       <c r="AB6" s="31" t="s">
         <v>66</v>
       </c>
       <c r="AC6" s="33"/>
-      <c r="AD6" s="91"/>
-      <c r="AE6" s="92"/>
+      <c r="AD6" s="93"/>
+      <c r="AE6" s="94"/>
       <c r="AF6" s="31"/>
       <c r="AG6" s="36"/>
-      <c r="AH6" s="131" t="s">
+      <c r="AH6" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="AI6" s="132"/>
+      <c r="AI6" s="134"/>
       <c r="AJ6" s="59" t="s">
         <v>44</v>
       </c>
       <c r="AK6" s="33"/>
-      <c r="AL6" s="131" t="s">
+      <c r="AL6" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="AM6" s="132"/>
+      <c r="AM6" s="134"/>
       <c r="AN6" s="59" t="s">
         <v>44</v>
       </c>
@@ -3029,109 +3029,109 @@
       </c>
       <c r="AR6" s="27"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="117"/>
-      <c r="C7" s="118"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="119"/>
+      <c r="C7" s="120"/>
       <c r="D7" s="54"/>
       <c r="E7" s="35"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="118"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="120"/>
       <c r="H7" s="54"/>
       <c r="I7" s="33"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="118"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="54"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="99"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="101"/>
       <c r="P7" s="66"/>
       <c r="Q7" s="33"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="99"/>
+      <c r="R7" s="100"/>
+      <c r="S7" s="101"/>
       <c r="T7" s="66"/>
       <c r="U7" s="33"/>
-      <c r="V7" s="98"/>
-      <c r="W7" s="99"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="101"/>
       <c r="X7" s="66"/>
       <c r="Y7" s="33"/>
-      <c r="Z7" s="98"/>
-      <c r="AA7" s="99"/>
+      <c r="Z7" s="100"/>
+      <c r="AA7" s="101"/>
       <c r="AB7" s="66"/>
       <c r="AC7" s="33"/>
-      <c r="AD7" s="98"/>
-      <c r="AE7" s="99"/>
+      <c r="AD7" s="100"/>
+      <c r="AE7" s="101"/>
       <c r="AF7" s="66"/>
       <c r="AG7" s="35"/>
-      <c r="AH7" s="88"/>
-      <c r="AI7" s="89"/>
+      <c r="AH7" s="90"/>
+      <c r="AI7" s="91"/>
       <c r="AJ7" s="60"/>
       <c r="AK7" s="33"/>
-      <c r="AL7" s="88"/>
-      <c r="AM7" s="89"/>
+      <c r="AL7" s="90"/>
+      <c r="AM7" s="91"/>
       <c r="AN7" s="60"/>
       <c r="AP7" s="40" t="s">
         <v>9</v>
       </c>
       <c r="AQ7" s="22">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR7" s="27"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="114"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="116"/>
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="116"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="118"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="114" t="s">
+      <c r="F8" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="115"/>
-      <c r="H8" s="116"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="118"/>
       <c r="I8" s="32"/>
-      <c r="J8" s="114" t="s">
+      <c r="J8" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="115"/>
-      <c r="L8" s="116"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="118"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="186" t="s">
+      <c r="N8" s="187" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="187"/>
-      <c r="P8" s="188"/>
+      <c r="O8" s="188"/>
+      <c r="P8" s="189"/>
       <c r="Q8" s="32"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="76"/>
-      <c r="T8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="78"/>
+      <c r="T8" s="79"/>
       <c r="U8" s="34"/>
-      <c r="V8" s="75" t="s">
+      <c r="V8" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="W8" s="76"/>
-      <c r="X8" s="77"/>
+      <c r="W8" s="78"/>
+      <c r="X8" s="79"/>
       <c r="Y8" s="32"/>
-      <c r="Z8" s="75" t="s">
+      <c r="Z8" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="AA8" s="76"/>
-      <c r="AB8" s="77"/>
+      <c r="AA8" s="78"/>
+      <c r="AB8" s="79"/>
       <c r="AC8" s="32"/>
-      <c r="AD8" s="75"/>
-      <c r="AE8" s="76"/>
-      <c r="AF8" s="77"/>
+      <c r="AD8" s="77"/>
+      <c r="AE8" s="78"/>
+      <c r="AF8" s="79"/>
       <c r="AG8" s="32"/>
-      <c r="AH8" s="114" t="s">
+      <c r="AH8" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="AI8" s="115"/>
-      <c r="AJ8" s="116"/>
+      <c r="AI8" s="117"/>
+      <c r="AJ8" s="118"/>
       <c r="AK8" s="32"/>
-      <c r="AL8" s="114" t="s">
+      <c r="AL8" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="115"/>
-      <c r="AN8" s="116"/>
+      <c r="AM8" s="117"/>
+      <c r="AN8" s="118"/>
       <c r="AP8" s="50" t="s">
         <v>16</v>
       </c>
@@ -3143,54 +3143,54 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="136"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="138"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
       <c r="E9" s="38"/>
-      <c r="F9" s="136" t="s">
+      <c r="F9" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="138"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="137"/>
       <c r="I9" s="38"/>
-      <c r="J9" s="136" t="s">
+      <c r="J9" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="137"/>
-      <c r="L9" s="138"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="137"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="132"/>
       <c r="Q9" s="38"/>
-      <c r="R9" s="128"/>
-      <c r="S9" s="129"/>
-      <c r="T9" s="130"/>
+      <c r="R9" s="130"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="132"/>
       <c r="U9" s="39"/>
-      <c r="V9" s="128"/>
-      <c r="W9" s="129"/>
-      <c r="X9" s="130"/>
+      <c r="V9" s="130"/>
+      <c r="W9" s="131"/>
+      <c r="X9" s="132"/>
       <c r="Y9" s="38"/>
-      <c r="Z9" s="128"/>
-      <c r="AA9" s="129"/>
-      <c r="AB9" s="130"/>
+      <c r="Z9" s="130"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="132"/>
       <c r="AC9" s="38"/>
-      <c r="AD9" s="128"/>
-      <c r="AE9" s="129"/>
-      <c r="AF9" s="130"/>
+      <c r="AD9" s="130"/>
+      <c r="AE9" s="131"/>
+      <c r="AF9" s="132"/>
       <c r="AG9" s="38"/>
-      <c r="AH9" s="167" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI9" s="168"/>
-      <c r="AJ9" s="169"/>
+      <c r="AH9" s="135" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI9" s="136"/>
+      <c r="AJ9" s="137"/>
       <c r="AK9" s="38"/>
-      <c r="AL9" s="136" t="s">
+      <c r="AL9" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="137"/>
-      <c r="AN9" s="138"/>
+      <c r="AM9" s="136"/>
+      <c r="AN9" s="137"/>
       <c r="AP9" s="40" t="s">
         <v>11</v>
       </c>
@@ -3200,48 +3200,46 @@
       </c>
       <c r="AR9" s="27"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="170"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="172"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="172"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="174"/>
       <c r="E10" s="39"/>
-      <c r="F10" s="170"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="172"/>
+      <c r="F10" s="172"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="174"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="170"/>
-      <c r="K10" s="171"/>
-      <c r="L10" s="172"/>
+      <c r="J10" s="172"/>
+      <c r="K10" s="173"/>
+      <c r="L10" s="174"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="173"/>
-      <c r="O10" s="174"/>
-      <c r="P10" s="175"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="170"/>
+      <c r="P10" s="171"/>
       <c r="Q10" s="39"/>
-      <c r="R10" s="173"/>
-      <c r="S10" s="174"/>
-      <c r="T10" s="175"/>
+      <c r="R10" s="169"/>
+      <c r="S10" s="170"/>
+      <c r="T10" s="171"/>
       <c r="U10" s="39"/>
-      <c r="V10" s="173"/>
-      <c r="W10" s="174"/>
-      <c r="X10" s="175"/>
+      <c r="V10" s="169"/>
+      <c r="W10" s="170"/>
+      <c r="X10" s="171"/>
       <c r="Y10" s="39"/>
-      <c r="Z10" s="173"/>
-      <c r="AA10" s="174"/>
-      <c r="AB10" s="175"/>
+      <c r="Z10" s="169"/>
+      <c r="AA10" s="170"/>
+      <c r="AB10" s="171"/>
       <c r="AC10" s="39"/>
-      <c r="AD10" s="173"/>
-      <c r="AE10" s="174"/>
-      <c r="AF10" s="175"/>
+      <c r="AD10" s="169"/>
+      <c r="AE10" s="170"/>
+      <c r="AF10" s="171"/>
       <c r="AG10" s="39"/>
-      <c r="AH10" s="221" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI10" s="222"/>
-      <c r="AJ10" s="223"/>
+      <c r="AH10" s="172"/>
+      <c r="AI10" s="173"/>
+      <c r="AJ10" s="174"/>
       <c r="AK10" s="39"/>
-      <c r="AL10" s="170"/>
-      <c r="AM10" s="171"/>
-      <c r="AN10" s="172"/>
+      <c r="AL10" s="172"/>
+      <c r="AM10" s="173"/>
+      <c r="AN10" s="174"/>
       <c r="AP10" s="40" t="s">
         <v>8</v>
       </c>
@@ -3251,7 +3249,7 @@
       </c>
       <c r="AR10" s="27"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>
@@ -3300,98 +3298,98 @@
       </c>
       <c r="AR11" s="27"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="122"/>
-      <c r="C12" s="123"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="124"/>
+      <c r="C12" s="125"/>
       <c r="D12" s="52"/>
       <c r="E12" s="36"/>
-      <c r="F12" s="144" t="s">
+      <c r="F12" s="143" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="145"/>
+      <c r="G12" s="144"/>
       <c r="H12" s="62" t="s">
         <v>86</v>
       </c>
       <c r="I12" s="33"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="123"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="125"/>
       <c r="L12" s="52"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="92"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="94"/>
       <c r="P12" s="31"/>
       <c r="Q12" s="65"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="92"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="94"/>
       <c r="T12" s="31"/>
       <c r="U12" s="33"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="92"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="94"/>
       <c r="X12" s="31"/>
       <c r="Y12" s="65"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="92"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="94"/>
       <c r="AB12" s="31"/>
       <c r="AC12" s="33"/>
-      <c r="AD12" s="91"/>
-      <c r="AE12" s="92"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="94"/>
       <c r="AF12" s="31"/>
       <c r="AG12" s="36"/>
-      <c r="AH12" s="91"/>
-      <c r="AI12" s="92"/>
+      <c r="AH12" s="93"/>
+      <c r="AI12" s="94"/>
       <c r="AJ12" s="31"/>
       <c r="AK12" s="33"/>
-      <c r="AL12" s="91"/>
-      <c r="AM12" s="92"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="94"/>
       <c r="AN12" s="31"/>
       <c r="AP12" s="51" t="s">
         <v>19</v>
       </c>
       <c r="AQ12" s="22">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR12" s="27"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="117"/>
-      <c r="C13" s="118"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="119"/>
+      <c r="C13" s="120"/>
       <c r="D13" s="54"/>
       <c r="E13" s="35"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="84"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="181"/>
       <c r="H13" s="64"/>
       <c r="I13" s="33"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="118"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="120"/>
       <c r="L13" s="54"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="95"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="99"/>
       <c r="Q13" s="33"/>
-      <c r="R13" s="95"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="97"/>
+      <c r="R13" s="97"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="99"/>
       <c r="U13" s="33"/>
-      <c r="V13" s="95"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="97"/>
+      <c r="V13" s="97"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="99"/>
       <c r="Y13" s="33"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="99"/>
+      <c r="Z13" s="100"/>
+      <c r="AA13" s="101"/>
       <c r="AB13" s="66"/>
       <c r="AC13" s="33"/>
-      <c r="AD13" s="98"/>
-      <c r="AE13" s="99"/>
+      <c r="AD13" s="100"/>
+      <c r="AE13" s="101"/>
       <c r="AF13" s="66"/>
       <c r="AG13" s="35"/>
-      <c r="AH13" s="98"/>
-      <c r="AI13" s="99"/>
+      <c r="AH13" s="100"/>
+      <c r="AI13" s="101"/>
       <c r="AJ13" s="66"/>
       <c r="AK13" s="33"/>
-      <c r="AL13" s="98"/>
-      <c r="AM13" s="99"/>
+      <c r="AL13" s="100"/>
+      <c r="AM13" s="101"/>
       <c r="AN13" s="66"/>
       <c r="AP13" s="51" t="s">
         <v>22</v>
@@ -3402,48 +3400,48 @@
       </c>
       <c r="AR13" s="27"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="114"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="116"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="116"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
       <c r="E14" s="34"/>
-      <c r="F14" s="114" t="s">
+      <c r="F14" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="116"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="118"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="118"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="76"/>
-      <c r="P14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="79"/>
       <c r="Q14" s="32"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="76"/>
-      <c r="T14" s="77"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
       <c r="U14" s="34"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="76"/>
-      <c r="X14" s="77"/>
+      <c r="V14" s="77"/>
+      <c r="W14" s="78"/>
+      <c r="X14" s="79"/>
       <c r="Y14" s="32"/>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="76"/>
-      <c r="AB14" s="77"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="78"/>
+      <c r="AB14" s="79"/>
       <c r="AC14" s="34"/>
-      <c r="AD14" s="75"/>
-      <c r="AE14" s="76"/>
-      <c r="AF14" s="77"/>
+      <c r="AD14" s="77"/>
+      <c r="AE14" s="78"/>
+      <c r="AF14" s="79"/>
       <c r="AG14" s="34"/>
-      <c r="AH14" s="75"/>
-      <c r="AI14" s="76"/>
-      <c r="AJ14" s="77"/>
+      <c r="AH14" s="77"/>
+      <c r="AI14" s="78"/>
+      <c r="AJ14" s="79"/>
       <c r="AK14" s="34"/>
-      <c r="AL14" s="75"/>
-      <c r="AM14" s="76"/>
-      <c r="AN14" s="77"/>
+      <c r="AL14" s="77"/>
+      <c r="AM14" s="78"/>
+      <c r="AN14" s="79"/>
       <c r="AP14" s="51" t="s">
         <v>23</v>
       </c>
@@ -3453,48 +3451,48 @@
       </c>
       <c r="AR14" s="27"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="136"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="138"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="135"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="137"/>
       <c r="E15" s="39"/>
-      <c r="F15" s="167" t="s">
+      <c r="F15" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="168"/>
-      <c r="H15" s="169"/>
+      <c r="G15" s="167"/>
+      <c r="H15" s="168"/>
       <c r="I15" s="38"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="138"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="137"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="128"/>
-      <c r="O15" s="129"/>
-      <c r="P15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="132"/>
       <c r="Q15" s="38"/>
-      <c r="R15" s="128"/>
-      <c r="S15" s="129"/>
-      <c r="T15" s="130"/>
+      <c r="R15" s="130"/>
+      <c r="S15" s="131"/>
+      <c r="T15" s="132"/>
       <c r="U15" s="39"/>
-      <c r="V15" s="128"/>
-      <c r="W15" s="129"/>
-      <c r="X15" s="130"/>
+      <c r="V15" s="130"/>
+      <c r="W15" s="131"/>
+      <c r="X15" s="132"/>
       <c r="Y15" s="38"/>
-      <c r="Z15" s="128"/>
-      <c r="AA15" s="129"/>
-      <c r="AB15" s="130"/>
+      <c r="Z15" s="130"/>
+      <c r="AA15" s="131"/>
+      <c r="AB15" s="132"/>
       <c r="AC15" s="38"/>
-      <c r="AD15" s="128"/>
-      <c r="AE15" s="129"/>
-      <c r="AF15" s="130"/>
+      <c r="AD15" s="130"/>
+      <c r="AE15" s="131"/>
+      <c r="AF15" s="132"/>
       <c r="AG15" s="39"/>
-      <c r="AH15" s="128"/>
-      <c r="AI15" s="129"/>
-      <c r="AJ15" s="130"/>
+      <c r="AH15" s="130"/>
+      <c r="AI15" s="131"/>
+      <c r="AJ15" s="132"/>
       <c r="AK15" s="38"/>
-      <c r="AL15" s="128"/>
-      <c r="AM15" s="129"/>
-      <c r="AN15" s="130"/>
+      <c r="AL15" s="130"/>
+      <c r="AM15" s="131"/>
+      <c r="AN15" s="132"/>
       <c r="AP15" s="40" t="s">
         <v>18</v>
       </c>
@@ -3504,46 +3502,46 @@
       </c>
       <c r="AR15" s="27"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="170"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="172"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="172"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="174"/>
       <c r="E16" s="39"/>
-      <c r="F16" s="170"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="172"/>
+      <c r="F16" s="172"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="174"/>
       <c r="I16" s="39"/>
-      <c r="J16" s="170"/>
-      <c r="K16" s="171"/>
-      <c r="L16" s="172"/>
+      <c r="J16" s="172"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="174"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="173"/>
-      <c r="O16" s="174"/>
-      <c r="P16" s="175"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="170"/>
+      <c r="P16" s="171"/>
       <c r="Q16" s="39"/>
-      <c r="R16" s="173"/>
-      <c r="S16" s="174"/>
-      <c r="T16" s="175"/>
+      <c r="R16" s="169"/>
+      <c r="S16" s="170"/>
+      <c r="T16" s="171"/>
       <c r="U16" s="39"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="174"/>
-      <c r="X16" s="175"/>
+      <c r="V16" s="169"/>
+      <c r="W16" s="170"/>
+      <c r="X16" s="171"/>
       <c r="Y16" s="39"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="174"/>
-      <c r="AB16" s="175"/>
+      <c r="Z16" s="169"/>
+      <c r="AA16" s="170"/>
+      <c r="AB16" s="171"/>
       <c r="AC16" s="39"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="174"/>
-      <c r="AF16" s="175"/>
+      <c r="AD16" s="169"/>
+      <c r="AE16" s="170"/>
+      <c r="AF16" s="171"/>
       <c r="AG16" s="39"/>
-      <c r="AH16" s="173"/>
-      <c r="AI16" s="174"/>
-      <c r="AJ16" s="175"/>
+      <c r="AH16" s="169"/>
+      <c r="AI16" s="170"/>
+      <c r="AJ16" s="171"/>
       <c r="AK16" s="39"/>
-      <c r="AL16" s="173"/>
-      <c r="AM16" s="174"/>
-      <c r="AN16" s="175"/>
+      <c r="AL16" s="169"/>
+      <c r="AM16" s="170"/>
+      <c r="AN16" s="171"/>
       <c r="AP16" s="51" t="s">
         <v>24</v>
       </c>
@@ -3553,7 +3551,7 @@
       </c>
       <c r="AR16" s="27"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
       <c r="D17" s="58"/>
@@ -3602,7 +3600,7 @@
       </c>
       <c r="AR17" s="27"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
       <c r="D18" s="58"/>
@@ -3615,23 +3613,23 @@
       <c r="K18" s="58"/>
       <c r="L18" s="58"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="180" t="s">
+      <c r="N18" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="180"/>
-      <c r="P18" s="180"/>
-      <c r="Q18" s="180"/>
-      <c r="R18" s="180"/>
-      <c r="S18" s="180"/>
-      <c r="T18" s="180"/>
-      <c r="U18" s="180"/>
-      <c r="V18" s="180"/>
-      <c r="W18" s="180"/>
-      <c r="X18" s="180"/>
-      <c r="Y18" s="180"/>
-      <c r="Z18" s="180"/>
-      <c r="AA18" s="180"/>
-      <c r="AB18" s="180"/>
+      <c r="O18" s="179"/>
+      <c r="P18" s="179"/>
+      <c r="Q18" s="179"/>
+      <c r="R18" s="179"/>
+      <c r="S18" s="179"/>
+      <c r="T18" s="179"/>
+      <c r="U18" s="179"/>
+      <c r="V18" s="179"/>
+      <c r="W18" s="179"/>
+      <c r="X18" s="179"/>
+      <c r="Y18" s="179"/>
+      <c r="Z18" s="179"/>
+      <c r="AA18" s="179"/>
+      <c r="AB18" s="179"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="30"/>
       <c r="AE18" s="30"/>
@@ -3653,7 +3651,7 @@
       </c>
       <c r="AR18" s="27"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
       <c r="D19" s="58"/>
@@ -3666,21 +3664,21 @@
       <c r="K19" s="58"/>
       <c r="L19" s="58"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="180"/>
-      <c r="O19" s="180"/>
-      <c r="P19" s="180"/>
-      <c r="Q19" s="180"/>
-      <c r="R19" s="180"/>
-      <c r="S19" s="180"/>
-      <c r="T19" s="180"/>
-      <c r="U19" s="180"/>
-      <c r="V19" s="180"/>
-      <c r="W19" s="180"/>
-      <c r="X19" s="180"/>
-      <c r="Y19" s="180"/>
-      <c r="Z19" s="180"/>
-      <c r="AA19" s="180"/>
-      <c r="AB19" s="180"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="179"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="179"/>
+      <c r="T19" s="179"/>
+      <c r="U19" s="179"/>
+      <c r="V19" s="179"/>
+      <c r="W19" s="179"/>
+      <c r="X19" s="179"/>
+      <c r="Y19" s="179"/>
+      <c r="Z19" s="179"/>
+      <c r="AA19" s="179"/>
+      <c r="AB19" s="179"/>
       <c r="AC19" s="30"/>
       <c r="AD19" s="30"/>
       <c r="AE19" s="30"/>
@@ -3702,79 +3700,79 @@
       </c>
       <c r="AR19" s="27"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="122" t="s">
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="123"/>
+      <c r="C20" s="125"/>
       <c r="D20" s="52" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="33"/>
-      <c r="F20" s="122" t="s">
+      <c r="F20" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="123"/>
+      <c r="G20" s="125"/>
       <c r="H20" s="52" t="s">
         <v>46</v>
       </c>
       <c r="I20" s="33"/>
-      <c r="J20" s="122" t="s">
+      <c r="J20" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="123"/>
+      <c r="K20" s="125"/>
       <c r="L20" s="52" t="s">
         <v>40</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="132"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="134"/>
       <c r="P20" s="59"/>
       <c r="Q20" s="33"/>
-      <c r="R20" s="131" t="s">
+      <c r="R20" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="S20" s="132"/>
+      <c r="S20" s="134"/>
       <c r="T20" s="59" t="s">
         <v>56</v>
       </c>
       <c r="U20" s="33"/>
-      <c r="V20" s="131" t="s">
+      <c r="V20" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="W20" s="132"/>
+      <c r="W20" s="134"/>
       <c r="X20" s="59" t="s">
         <v>56</v>
       </c>
       <c r="Y20" s="33"/>
-      <c r="Z20" s="91" t="s">
+      <c r="Z20" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="AA20" s="92"/>
+      <c r="AA20" s="94"/>
       <c r="AB20" s="31" t="s">
         <v>43</v>
       </c>
       <c r="AC20" s="33"/>
-      <c r="AD20" s="91" t="s">
+      <c r="AD20" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="AE20" s="92"/>
+      <c r="AE20" s="94"/>
       <c r="AF20" s="31" t="s">
         <v>43</v>
       </c>
       <c r="AG20" s="33"/>
-      <c r="AH20" s="131" t="s">
+      <c r="AH20" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="AI20" s="132"/>
+      <c r="AI20" s="134"/>
       <c r="AJ20" s="74" t="s">
         <v>44</v>
       </c>
       <c r="AK20" s="33"/>
-      <c r="AL20" s="91" t="s">
+      <c r="AL20" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="AM20" s="92"/>
+      <c r="AM20" s="94"/>
       <c r="AN20" s="31" t="s">
         <v>40</v>
       </c>
@@ -3787,53 +3785,53 @@
       </c>
       <c r="AR20" s="27"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="117" t="s">
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="118"/>
+      <c r="C21" s="120"/>
       <c r="D21" s="54"/>
       <c r="E21" s="35"/>
-      <c r="F21" s="117" t="s">
+      <c r="F21" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="118"/>
+      <c r="G21" s="120"/>
       <c r="H21" s="54"/>
       <c r="I21" s="33"/>
-      <c r="J21" s="176" t="s">
+      <c r="J21" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="K21" s="177"/>
+      <c r="K21" s="176"/>
       <c r="L21" s="54"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="88"/>
-      <c r="O21" s="89"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="91"/>
       <c r="P21" s="60"/>
       <c r="Q21" s="35"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="89"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="91"/>
       <c r="T21" s="60"/>
       <c r="U21" s="35"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="89"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="91"/>
       <c r="X21" s="60"/>
       <c r="Y21" s="33"/>
-      <c r="Z21" s="98"/>
-      <c r="AA21" s="99"/>
+      <c r="Z21" s="100"/>
+      <c r="AA21" s="101"/>
       <c r="AB21" s="66"/>
       <c r="AC21" s="33"/>
-      <c r="AD21" s="98"/>
-      <c r="AE21" s="99"/>
+      <c r="AD21" s="100"/>
+      <c r="AE21" s="101"/>
       <c r="AF21" s="66"/>
       <c r="AG21" s="35"/>
-      <c r="AH21" s="88" t="s">
+      <c r="AH21" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="AI21" s="89"/>
+      <c r="AI21" s="91"/>
       <c r="AJ21" s="60"/>
       <c r="AK21" s="33"/>
-      <c r="AL21" s="98"/>
-      <c r="AM21" s="99"/>
+      <c r="AL21" s="100"/>
+      <c r="AM21" s="101"/>
       <c r="AN21" s="66"/>
       <c r="AP21" s="40" t="s">
         <v>12</v>
@@ -3844,79 +3842,79 @@
       </c>
       <c r="AR21" s="27"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="110" t="s">
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="111"/>
+      <c r="C22" s="113"/>
       <c r="D22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="34"/>
-      <c r="F22" s="110" t="s">
+      <c r="F22" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="111"/>
+      <c r="G22" s="113"/>
       <c r="H22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="32"/>
-      <c r="J22" s="178" t="s">
+      <c r="J22" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="K22" s="179"/>
+      <c r="K22" s="178"/>
       <c r="L22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="111"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="113"/>
       <c r="P22" s="55"/>
       <c r="Q22" s="32"/>
-      <c r="R22" s="110" t="s">
+      <c r="R22" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="S22" s="111"/>
+      <c r="S22" s="113"/>
       <c r="T22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="34"/>
-      <c r="V22" s="110" t="s">
+      <c r="V22" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="W22" s="111"/>
+      <c r="W22" s="113"/>
       <c r="X22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="32"/>
-      <c r="Z22" s="110" t="s">
+      <c r="Z22" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="AA22" s="111"/>
+      <c r="AA22" s="113"/>
       <c r="AB22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="AC22" s="32"/>
-      <c r="AD22" s="110" t="s">
+      <c r="AD22" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="AE22" s="111"/>
+      <c r="AE22" s="113"/>
       <c r="AF22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="AG22" s="34"/>
-      <c r="AH22" s="110" t="s">
+      <c r="AH22" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="AI22" s="111"/>
+      <c r="AI22" s="113"/>
       <c r="AJ22" s="55" t="s">
         <v>32</v>
       </c>
       <c r="AK22" s="32"/>
-      <c r="AL22" s="110" t="s">
+      <c r="AL22" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="AM22" s="111"/>
+      <c r="AM22" s="113"/>
       <c r="AN22" s="55" t="s">
         <v>32</v>
       </c>
@@ -3929,79 +3927,79 @@
       </c>
       <c r="AR22" s="27"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="112" t="s">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="113"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="38"/>
-      <c r="F23" s="112" t="s">
+      <c r="F23" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="113"/>
+      <c r="G23" s="115"/>
       <c r="H23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="38"/>
-      <c r="J23" s="181" t="s">
+      <c r="J23" s="182" t="s">
         <v>76</v>
       </c>
-      <c r="K23" s="182"/>
+      <c r="K23" s="183"/>
       <c r="L23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="113"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="115"/>
       <c r="P23" s="56"/>
       <c r="Q23" s="38"/>
-      <c r="R23" s="112" t="s">
+      <c r="R23" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="113"/>
+      <c r="S23" s="115"/>
       <c r="T23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="U23" s="38"/>
-      <c r="V23" s="112" t="s">
+      <c r="V23" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="W23" s="113"/>
+      <c r="W23" s="115"/>
       <c r="X23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="Y23" s="38"/>
-      <c r="Z23" s="112" t="s">
+      <c r="Z23" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="AA23" s="113"/>
+      <c r="AA23" s="115"/>
       <c r="AB23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="AC23" s="38"/>
-      <c r="AD23" s="112" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE23" s="113"/>
+      <c r="AD23" s="105" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE23" s="106"/>
       <c r="AF23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="AG23" s="38"/>
-      <c r="AH23" s="112" t="s">
+      <c r="AH23" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="AI23" s="113"/>
+      <c r="AI23" s="115"/>
       <c r="AJ23" s="56" t="s">
         <v>33</v>
       </c>
       <c r="AK23" s="38"/>
-      <c r="AL23" s="112" t="s">
+      <c r="AL23" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="AM23" s="113"/>
+      <c r="AM23" s="115"/>
       <c r="AN23" s="56" t="s">
         <v>33</v>
       </c>
@@ -4014,79 +4012,79 @@
       </c>
       <c r="AR23" s="27"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="101" t="s">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="102"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="38"/>
-      <c r="F24" s="101" t="s">
+      <c r="F24" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="102"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="I24" s="39"/>
-      <c r="J24" s="183" t="s">
+      <c r="J24" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="K24" s="184"/>
+      <c r="K24" s="185"/>
       <c r="L24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="101"/>
-      <c r="O24" s="102"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="104"/>
       <c r="P24" s="56"/>
       <c r="Q24" s="38"/>
-      <c r="R24" s="101" t="s">
+      <c r="R24" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="S24" s="102"/>
+      <c r="S24" s="104"/>
       <c r="T24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="39"/>
-      <c r="V24" s="101" t="s">
+      <c r="V24" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="W24" s="102"/>
+      <c r="W24" s="104"/>
       <c r="X24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="38"/>
-      <c r="Z24" s="103" t="s">
+      <c r="Z24" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="AA24" s="104"/>
+      <c r="AA24" s="106"/>
       <c r="AB24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="38"/>
-      <c r="AD24" s="101" t="s">
+      <c r="AD24" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AE24" s="102"/>
+      <c r="AE24" s="104"/>
       <c r="AF24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="AG24" s="38"/>
-      <c r="AH24" s="103" t="s">
+      <c r="AH24" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="AI24" s="104"/>
+      <c r="AI24" s="106"/>
       <c r="AJ24" s="56" t="s">
         <v>34</v>
       </c>
       <c r="AK24" s="39"/>
-      <c r="AL24" s="101" t="s">
+      <c r="AL24" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="AM24" s="102"/>
+      <c r="AM24" s="104"/>
       <c r="AN24" s="56" t="s">
         <v>34</v>
       </c>
@@ -4099,79 +4097,79 @@
       </c>
       <c r="AR24" s="27"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="101" t="s">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="102"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="39"/>
-      <c r="F25" s="101" t="s">
+      <c r="F25" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="102"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="39"/>
-      <c r="J25" s="183" t="s">
+      <c r="J25" s="184" t="s">
         <v>78</v>
       </c>
-      <c r="K25" s="184"/>
+      <c r="K25" s="185"/>
       <c r="L25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="101"/>
-      <c r="O25" s="102"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="104"/>
       <c r="P25" s="56"/>
       <c r="Q25" s="39"/>
-      <c r="R25" s="101" t="s">
+      <c r="R25" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="S25" s="102"/>
+      <c r="S25" s="104"/>
       <c r="T25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="39"/>
-      <c r="V25" s="103" t="s">
+      <c r="V25" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="W25" s="104"/>
+      <c r="W25" s="106"/>
       <c r="X25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="39"/>
-      <c r="Z25" s="103" t="s">
+      <c r="Z25" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="AA25" s="104"/>
+      <c r="AA25" s="106"/>
       <c r="AB25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="39"/>
-      <c r="AD25" s="101" t="s">
+      <c r="AD25" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="AE25" s="102"/>
+      <c r="AE25" s="104"/>
       <c r="AF25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AG25" s="39"/>
-      <c r="AH25" s="103" t="s">
+      <c r="AH25" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="AI25" s="104"/>
+      <c r="AI25" s="106"/>
       <c r="AJ25" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AK25" s="39"/>
-      <c r="AL25" s="103" t="s">
+      <c r="AL25" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="AM25" s="104"/>
+      <c r="AM25" s="106"/>
       <c r="AN25" s="56" t="s">
         <v>35</v>
       </c>
@@ -4184,75 +4182,75 @@
       </c>
       <c r="AR25" s="27"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="101" t="s">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="102"/>
+      <c r="C26" s="104"/>
       <c r="D26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="39"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="102"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="56"/>
       <c r="I26" s="39"/>
-      <c r="J26" s="183" t="s">
+      <c r="J26" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="K26" s="184"/>
+      <c r="K26" s="185"/>
       <c r="L26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="101"/>
-      <c r="O26" s="102"/>
+      <c r="N26" s="103"/>
+      <c r="O26" s="104"/>
       <c r="P26" s="56"/>
       <c r="Q26" s="39"/>
-      <c r="R26" s="101" t="s">
+      <c r="R26" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="S26" s="102"/>
+      <c r="S26" s="104"/>
       <c r="T26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="39"/>
-      <c r="V26" s="101" t="s">
+      <c r="V26" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="102"/>
+      <c r="W26" s="104"/>
       <c r="X26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="39"/>
-      <c r="Z26" s="101" t="s">
+      <c r="Z26" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AA26" s="102"/>
+      <c r="AA26" s="104"/>
       <c r="AB26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="39"/>
-      <c r="AD26" s="101" t="s">
+      <c r="AD26" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="AE26" s="102"/>
+      <c r="AE26" s="104"/>
       <c r="AF26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AG26" s="39"/>
-      <c r="AH26" s="101" t="s">
+      <c r="AH26" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AI26" s="102"/>
+      <c r="AI26" s="104"/>
       <c r="AJ26" s="56" t="s">
         <v>35</v>
       </c>
       <c r="AK26" s="39"/>
-      <c r="AL26" s="201" t="s">
+      <c r="AL26" s="202" t="s">
         <v>21</v>
       </c>
-      <c r="AM26" s="202"/>
+      <c r="AM26" s="203"/>
       <c r="AN26" s="56" t="s">
         <v>35</v>
       </c>
@@ -4265,51 +4263,51 @@
       </c>
       <c r="AR26" s="27"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="108"/>
-      <c r="C27" s="109"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="110"/>
+      <c r="C27" s="111"/>
       <c r="D27" s="57"/>
       <c r="E27" s="39"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="109"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="111"/>
       <c r="H27" s="57"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="109"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="111"/>
       <c r="L27" s="57"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="109"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="111"/>
       <c r="P27" s="57"/>
       <c r="Q27" s="39"/>
-      <c r="R27" s="108"/>
-      <c r="S27" s="109"/>
+      <c r="R27" s="110"/>
+      <c r="S27" s="111"/>
       <c r="T27" s="57"/>
       <c r="U27" s="39"/>
-      <c r="V27" s="203" t="s">
+      <c r="V27" s="204" t="s">
         <v>78</v>
       </c>
-      <c r="W27" s="204"/>
+      <c r="W27" s="205"/>
       <c r="X27" s="57"/>
       <c r="Y27" s="39"/>
-      <c r="Z27" s="203" t="s">
+      <c r="Z27" s="204" t="s">
         <v>112</v>
       </c>
-      <c r="AA27" s="204"/>
+      <c r="AA27" s="205"/>
       <c r="AB27" s="57"/>
       <c r="AC27" s="39"/>
-      <c r="AD27" s="108"/>
-      <c r="AE27" s="109"/>
+      <c r="AD27" s="110"/>
+      <c r="AE27" s="111"/>
       <c r="AF27" s="57"/>
       <c r="AG27" s="39"/>
-      <c r="AH27" s="108"/>
-      <c r="AI27" s="109"/>
+      <c r="AH27" s="110"/>
+      <c r="AI27" s="111"/>
       <c r="AJ27" s="57"/>
       <c r="AK27" s="39"/>
-      <c r="AL27" s="203" t="s">
+      <c r="AL27" s="204" t="s">
         <v>78</v>
       </c>
-      <c r="AM27" s="204"/>
+      <c r="AM27" s="205"/>
       <c r="AN27" s="57"/>
       <c r="AP27" s="50" t="s">
         <v>13</v>
@@ -4322,7 +4320,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
@@ -4371,7 +4369,7 @@
       </c>
       <c r="AR28" s="27"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
@@ -4384,23 +4382,23 @@
       <c r="K29" s="58"/>
       <c r="L29" s="58"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="180" t="s">
+      <c r="N29" s="179" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="180"/>
-      <c r="P29" s="180"/>
-      <c r="Q29" s="180"/>
-      <c r="R29" s="180"/>
-      <c r="S29" s="180"/>
-      <c r="T29" s="180"/>
-      <c r="U29" s="180"/>
-      <c r="V29" s="180"/>
-      <c r="W29" s="180"/>
-      <c r="X29" s="180"/>
-      <c r="Y29" s="180"/>
-      <c r="Z29" s="180"/>
-      <c r="AA29" s="180"/>
-      <c r="AB29" s="180"/>
+      <c r="O29" s="179"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="179"/>
+      <c r="R29" s="179"/>
+      <c r="S29" s="179"/>
+      <c r="T29" s="179"/>
+      <c r="U29" s="179"/>
+      <c r="V29" s="179"/>
+      <c r="W29" s="179"/>
+      <c r="X29" s="179"/>
+      <c r="Y29" s="179"/>
+      <c r="Z29" s="179"/>
+      <c r="AA29" s="179"/>
+      <c r="AB29" s="179"/>
       <c r="AC29" s="30"/>
       <c r="AD29" s="30"/>
       <c r="AE29" s="30"/>
@@ -4422,7 +4420,7 @@
       </c>
       <c r="AR29" s="27"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B30" s="58"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -4435,21 +4433,21 @@
       <c r="K30" s="58"/>
       <c r="L30" s="58"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="180"/>
-      <c r="Q30" s="180"/>
-      <c r="R30" s="180"/>
-      <c r="S30" s="180"/>
-      <c r="T30" s="180"/>
-      <c r="U30" s="180"/>
-      <c r="V30" s="180"/>
-      <c r="W30" s="180"/>
-      <c r="X30" s="180"/>
-      <c r="Y30" s="180"/>
-      <c r="Z30" s="180"/>
-      <c r="AA30" s="180"/>
-      <c r="AB30" s="180"/>
+      <c r="N30" s="179"/>
+      <c r="O30" s="179"/>
+      <c r="P30" s="179"/>
+      <c r="Q30" s="179"/>
+      <c r="R30" s="179"/>
+      <c r="S30" s="179"/>
+      <c r="T30" s="179"/>
+      <c r="U30" s="179"/>
+      <c r="V30" s="179"/>
+      <c r="W30" s="179"/>
+      <c r="X30" s="179"/>
+      <c r="Y30" s="179"/>
+      <c r="Z30" s="179"/>
+      <c r="AA30" s="179"/>
+      <c r="AB30" s="179"/>
       <c r="AC30" s="30"/>
       <c r="AD30" s="30"/>
       <c r="AE30" s="30"/>
@@ -4471,434 +4469,434 @@
       </c>
       <c r="AR30" s="27"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="122" t="s">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="123"/>
+      <c r="C31" s="125"/>
       <c r="D31" s="52"/>
       <c r="E31" s="29"/>
-      <c r="F31" s="122" t="s">
+      <c r="F31" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="G31" s="123"/>
+      <c r="G31" s="125"/>
       <c r="H31" s="52"/>
       <c r="I31" s="49"/>
-      <c r="J31" s="122" t="s">
+      <c r="J31" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="K31" s="123"/>
+      <c r="K31" s="125"/>
       <c r="L31" s="52"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="91" t="s">
+      <c r="N31" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="O31" s="92"/>
+      <c r="O31" s="94"/>
       <c r="P31" s="31" t="s">
         <v>72</v>
       </c>
       <c r="Q31" s="33"/>
-      <c r="R31" s="91"/>
-      <c r="S31" s="92"/>
+      <c r="R31" s="93"/>
+      <c r="S31" s="94"/>
       <c r="T31" s="31"/>
       <c r="U31" s="33"/>
-      <c r="V31" s="139" t="s">
+      <c r="V31" s="141" t="s">
         <v>126</v>
       </c>
-      <c r="W31" s="140"/>
+      <c r="W31" s="142"/>
       <c r="X31" s="68" t="s">
         <v>46</v>
       </c>
       <c r="Y31" s="33"/>
-      <c r="Z31" s="91" t="s">
+      <c r="Z31" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="AA31" s="92"/>
+      <c r="AA31" s="94"/>
       <c r="AB31" s="31"/>
       <c r="AC31" s="33"/>
-      <c r="AD31" s="91" t="s">
+      <c r="AD31" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="AE31" s="92"/>
+      <c r="AE31" s="94"/>
       <c r="AF31" s="31"/>
       <c r="AG31" s="29"/>
-      <c r="AH31" s="91" t="s">
+      <c r="AH31" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="AI31" s="92"/>
+      <c r="AI31" s="94"/>
       <c r="AJ31" s="31"/>
       <c r="AK31" s="49"/>
-      <c r="AL31" s="91" t="s">
+      <c r="AL31" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="AM31" s="92"/>
+      <c r="AM31" s="94"/>
       <c r="AN31" s="31"/>
       <c r="AP31" s="42"/>
       <c r="AQ31" s="43"/>
       <c r="AR31" s="27"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="124" t="s">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="125"/>
-      <c r="D32" s="126"/>
+      <c r="C32" s="127"/>
+      <c r="D32" s="128"/>
       <c r="E32" s="29"/>
-      <c r="F32" s="124" t="s">
+      <c r="F32" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="125"/>
-      <c r="H32" s="126"/>
+      <c r="G32" s="127"/>
+      <c r="H32" s="128"/>
       <c r="I32" s="32"/>
-      <c r="J32" s="124" t="s">
+      <c r="J32" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="K32" s="125"/>
-      <c r="L32" s="126"/>
+      <c r="K32" s="127"/>
+      <c r="L32" s="128"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="95" t="s">
+      <c r="N32" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="O32" s="96"/>
-      <c r="P32" s="97"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="99"/>
       <c r="Q32" s="34"/>
-      <c r="R32" s="95"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="97"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="99"/>
       <c r="U32" s="33"/>
-      <c r="V32" s="95" t="s">
+      <c r="V32" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="W32" s="96"/>
-      <c r="X32" s="97"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="99"/>
       <c r="Y32" s="34"/>
-      <c r="Z32" s="95" t="s">
+      <c r="Z32" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AA32" s="96"/>
-      <c r="AB32" s="97"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="99"/>
       <c r="AC32" s="38"/>
-      <c r="AD32" s="95" t="s">
+      <c r="AD32" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AE32" s="96"/>
-      <c r="AF32" s="97"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="99"/>
       <c r="AG32" s="29"/>
-      <c r="AH32" s="95" t="s">
+      <c r="AH32" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AI32" s="96"/>
-      <c r="AJ32" s="97"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="99"/>
       <c r="AK32" s="32"/>
-      <c r="AL32" s="95" t="s">
+      <c r="AL32" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AM32" s="96"/>
-      <c r="AN32" s="97"/>
+      <c r="AM32" s="98"/>
+      <c r="AN32" s="99"/>
       <c r="AP32" s="45"/>
       <c r="AQ32" s="46"/>
       <c r="AR32" s="27"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="117" t="s">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="118"/>
-      <c r="D33" s="127"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="129"/>
       <c r="E33" s="38"/>
-      <c r="F33" s="117" t="s">
+      <c r="F33" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="118"/>
-      <c r="H33" s="127"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="129"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="117" t="s">
+      <c r="J33" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="118"/>
-      <c r="L33" s="127"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="129"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="98"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="100"/>
+      <c r="N33" s="100"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="102"/>
       <c r="Q33" s="33"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="99"/>
-      <c r="T33" s="100"/>
+      <c r="R33" s="100"/>
+      <c r="S33" s="101"/>
+      <c r="T33" s="102"/>
       <c r="U33" s="32"/>
-      <c r="V33" s="98" t="s">
+      <c r="V33" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="W33" s="99"/>
-      <c r="X33" s="100"/>
+      <c r="W33" s="101"/>
+      <c r="X33" s="102"/>
       <c r="Y33" s="33"/>
-      <c r="Z33" s="98" t="s">
+      <c r="Z33" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="AA33" s="99"/>
-      <c r="AB33" s="100"/>
+      <c r="AA33" s="101"/>
+      <c r="AB33" s="102"/>
       <c r="AC33" s="34"/>
-      <c r="AD33" s="98"/>
-      <c r="AE33" s="99"/>
-      <c r="AF33" s="100"/>
+      <c r="AD33" s="100"/>
+      <c r="AE33" s="101"/>
+      <c r="AF33" s="102"/>
       <c r="AG33" s="38"/>
-      <c r="AH33" s="98"/>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="100"/>
+      <c r="AH33" s="100"/>
+      <c r="AI33" s="101"/>
+      <c r="AJ33" s="102"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="98"/>
-      <c r="AM33" s="99"/>
-      <c r="AN33" s="100"/>
+      <c r="AL33" s="100"/>
+      <c r="AM33" s="101"/>
+      <c r="AN33" s="102"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="116"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="118"/>
       <c r="E34" s="34"/>
-      <c r="F34" s="114" t="s">
+      <c r="F34" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="115"/>
-      <c r="H34" s="116"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="118"/>
       <c r="I34" s="32"/>
-      <c r="J34" s="114" t="s">
+      <c r="J34" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="K34" s="115"/>
-      <c r="L34" s="116"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="118"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="75" t="s">
+      <c r="N34" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="O34" s="76"/>
-      <c r="P34" s="77"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="79"/>
       <c r="Q34" s="29"/>
-      <c r="R34" s="75"/>
-      <c r="S34" s="76"/>
-      <c r="T34" s="77"/>
+      <c r="R34" s="77"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="79"/>
       <c r="U34" s="28"/>
-      <c r="V34" s="75" t="s">
+      <c r="V34" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="W34" s="76"/>
-      <c r="X34" s="77"/>
+      <c r="W34" s="78"/>
+      <c r="X34" s="79"/>
       <c r="Y34" s="29"/>
-      <c r="Z34" s="75" t="s">
+      <c r="Z34" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AA34" s="76"/>
-      <c r="AB34" s="77"/>
+      <c r="AA34" s="78"/>
+      <c r="AB34" s="79"/>
       <c r="AC34" s="39"/>
-      <c r="AD34" s="75" t="s">
+      <c r="AD34" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="77"/>
+      <c r="AE34" s="78"/>
+      <c r="AF34" s="79"/>
       <c r="AG34" s="34"/>
-      <c r="AH34" s="75" t="s">
+      <c r="AH34" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AI34" s="76"/>
-      <c r="AJ34" s="77"/>
+      <c r="AI34" s="78"/>
+      <c r="AJ34" s="79"/>
       <c r="AK34" s="32"/>
-      <c r="AL34" s="75" t="s">
+      <c r="AL34" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AM34" s="76"/>
-      <c r="AN34" s="77"/>
+      <c r="AM34" s="78"/>
+      <c r="AN34" s="79"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="136" t="s">
+      <c r="B35" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="137"/>
-      <c r="D35" s="138"/>
+      <c r="C35" s="136"/>
+      <c r="D35" s="137"/>
       <c r="E35" s="39"/>
-      <c r="F35" s="136" t="s">
+      <c r="F35" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="137"/>
-      <c r="H35" s="138"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="137"/>
       <c r="I35" s="37"/>
-      <c r="J35" s="136" t="s">
+      <c r="J35" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="137"/>
-      <c r="L35" s="138"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="137"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="128" t="s">
+      <c r="N35" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="129"/>
-      <c r="P35" s="130"/>
+      <c r="O35" s="131"/>
+      <c r="P35" s="132"/>
       <c r="Q35" s="29"/>
-      <c r="R35" s="128"/>
-      <c r="S35" s="129"/>
-      <c r="T35" s="130"/>
+      <c r="R35" s="130"/>
+      <c r="S35" s="131"/>
+      <c r="T35" s="132"/>
       <c r="U35" s="29"/>
-      <c r="V35" s="128"/>
-      <c r="W35" s="129"/>
-      <c r="X35" s="130"/>
+      <c r="V35" s="130"/>
+      <c r="W35" s="131"/>
+      <c r="X35" s="132"/>
       <c r="Y35" s="29"/>
-      <c r="Z35" s="128" t="s">
+      <c r="Z35" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="130"/>
+      <c r="AA35" s="131"/>
+      <c r="AB35" s="132"/>
       <c r="AC35" s="39"/>
-      <c r="AD35" s="128" t="s">
+      <c r="AD35" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="AE35" s="129"/>
-      <c r="AF35" s="130"/>
+      <c r="AE35" s="131"/>
+      <c r="AF35" s="132"/>
       <c r="AG35" s="39"/>
-      <c r="AH35" s="128" t="s">
+      <c r="AH35" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="AI35" s="129"/>
-      <c r="AJ35" s="130"/>
+      <c r="AI35" s="131"/>
+      <c r="AJ35" s="132"/>
       <c r="AK35" s="37"/>
-      <c r="AL35" s="128" t="s">
+      <c r="AL35" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="AM35" s="129"/>
-      <c r="AN35" s="130"/>
+      <c r="AM35" s="131"/>
+      <c r="AN35" s="132"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="136" t="s">
+      <c r="B36" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="137"/>
-      <c r="D36" s="138"/>
+      <c r="C36" s="136"/>
+      <c r="D36" s="137"/>
       <c r="E36" s="39"/>
-      <c r="F36" s="136" t="s">
+      <c r="F36" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="137"/>
-      <c r="H36" s="138"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="137"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="136" t="s">
+      <c r="J36" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="K36" s="137"/>
-      <c r="L36" s="138"/>
+      <c r="K36" s="136"/>
+      <c r="L36" s="137"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="101" t="s">
+      <c r="N36" s="103" t="s">
         <v>95</v>
       </c>
-      <c r="O36" s="102"/>
+      <c r="O36" s="104"/>
       <c r="P36" s="63" t="s">
         <v>83</v>
       </c>
       <c r="Q36" s="29"/>
-      <c r="R36" s="128"/>
-      <c r="S36" s="129"/>
-      <c r="T36" s="130"/>
+      <c r="R36" s="130"/>
+      <c r="S36" s="131"/>
+      <c r="T36" s="132"/>
       <c r="U36" s="32"/>
-      <c r="V36" s="128"/>
-      <c r="W36" s="129"/>
-      <c r="X36" s="130"/>
+      <c r="V36" s="130"/>
+      <c r="W36" s="131"/>
+      <c r="X36" s="132"/>
       <c r="Y36" s="29"/>
-      <c r="Z36" s="141" t="s">
+      <c r="Z36" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="AA36" s="142"/>
-      <c r="AB36" s="143"/>
+      <c r="AA36" s="207"/>
+      <c r="AB36" s="208"/>
       <c r="AC36" s="39"/>
-      <c r="AD36" s="141" t="s">
+      <c r="AD36" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="AE36" s="142"/>
-      <c r="AF36" s="143"/>
+      <c r="AE36" s="207"/>
+      <c r="AF36" s="208"/>
       <c r="AG36" s="39"/>
-      <c r="AH36" s="141" t="s">
+      <c r="AH36" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="AI36" s="142"/>
-      <c r="AJ36" s="143"/>
+      <c r="AI36" s="207"/>
+      <c r="AJ36" s="208"/>
       <c r="AK36" s="44"/>
-      <c r="AL36" s="141" t="s">
+      <c r="AL36" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="AM36" s="142"/>
-      <c r="AN36" s="143"/>
+      <c r="AM36" s="207"/>
+      <c r="AN36" s="208"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="20"/>
       <c r="AQ36" s="28"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
-      <c r="B37" s="105"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="107"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="109"/>
       <c r="E37" s="44"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="107"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="109"/>
       <c r="I37" s="44"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
+      <c r="J37" s="107"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="109"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="108" t="s">
+      <c r="N37" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="O37" s="109"/>
+      <c r="O37" s="111"/>
       <c r="P37" s="63" t="s">
         <v>83</v>
       </c>
       <c r="Q37" s="44"/>
-      <c r="R37" s="78"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="81"/>
+      <c r="T37" s="82"/>
       <c r="U37" s="44"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="79"/>
-      <c r="X37" s="80"/>
+      <c r="V37" s="80"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="82"/>
       <c r="Y37" s="44"/>
-      <c r="Z37" s="85" t="s">
+      <c r="Z37" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="AA37" s="86"/>
-      <c r="AB37" s="87"/>
+      <c r="AA37" s="88"/>
+      <c r="AB37" s="89"/>
       <c r="AC37" s="44"/>
-      <c r="AD37" s="85" t="s">
+      <c r="AD37" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="AE37" s="86"/>
-      <c r="AF37" s="87"/>
+      <c r="AE37" s="88"/>
+      <c r="AF37" s="89"/>
       <c r="AG37" s="44"/>
-      <c r="AH37" s="85" t="s">
+      <c r="AH37" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="AI37" s="86"/>
-      <c r="AJ37" s="87"/>
+      <c r="AI37" s="88"/>
+      <c r="AJ37" s="89"/>
       <c r="AK37" s="44"/>
-      <c r="AL37" s="85" t="s">
+      <c r="AL37" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="AM37" s="86"/>
-      <c r="AN37" s="87"/>
+      <c r="AM37" s="88"/>
+      <c r="AN37" s="89"/>
       <c r="AO37" s="28"/>
       <c r="AP37" s="20"/>
       <c r="AQ37" s="28"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="53"/>
       <c r="C38" s="53"/>
@@ -4944,58 +4942,58 @@
       <c r="AQ38" s="28"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="122" t="s">
+      <c r="B39" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="123"/>
+      <c r="C39" s="125"/>
       <c r="D39" s="52"/>
       <c r="E39" s="29"/>
-      <c r="F39" s="122" t="s">
+      <c r="F39" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="G39" s="123"/>
+      <c r="G39" s="125"/>
       <c r="H39" s="52"/>
       <c r="I39" s="49"/>
-      <c r="J39" s="122" t="s">
+      <c r="J39" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="K39" s="123"/>
+      <c r="K39" s="125"/>
       <c r="L39" s="52"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="91"/>
-      <c r="O39" s="92"/>
+      <c r="N39" s="93"/>
+      <c r="O39" s="94"/>
       <c r="P39" s="31"/>
       <c r="Q39" s="33"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="92"/>
+      <c r="R39" s="93"/>
+      <c r="S39" s="94"/>
       <c r="T39" s="31"/>
       <c r="U39" s="29"/>
-      <c r="V39" s="91"/>
-      <c r="W39" s="92"/>
+      <c r="V39" s="93"/>
+      <c r="W39" s="94"/>
       <c r="X39" s="31"/>
       <c r="Y39" s="49"/>
-      <c r="Z39" s="91" t="s">
+      <c r="Z39" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="AA39" s="92"/>
+      <c r="AA39" s="94"/>
       <c r="AB39" s="31"/>
       <c r="AC39" s="33"/>
-      <c r="AD39" s="91" t="s">
+      <c r="AD39" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="AE39" s="92"/>
+      <c r="AE39" s="94"/>
       <c r="AF39" s="31"/>
       <c r="AG39" s="29"/>
-      <c r="AH39" s="91"/>
-      <c r="AI39" s="92"/>
+      <c r="AH39" s="93"/>
+      <c r="AI39" s="94"/>
       <c r="AJ39" s="31"/>
       <c r="AK39" s="49"/>
-      <c r="AL39" s="91" t="s">
+      <c r="AL39" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="AM39" s="92"/>
+      <c r="AM39" s="94"/>
       <c r="AN39" s="31" t="s">
         <v>99</v>
       </c>
@@ -5004,297 +5002,297 @@
       <c r="AQ39" s="28"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="124" t="s">
+      <c r="B40" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="125"/>
-      <c r="D40" s="126"/>
+      <c r="C40" s="127"/>
+      <c r="D40" s="128"/>
       <c r="E40" s="29"/>
-      <c r="F40" s="124" t="s">
+      <c r="F40" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="G40" s="125"/>
-      <c r="H40" s="126"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="128"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="124" t="s">
+      <c r="J40" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="K40" s="125"/>
-      <c r="L40" s="126"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="128"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="95"/>
-      <c r="O40" s="96"/>
-      <c r="P40" s="97"/>
+      <c r="N40" s="97"/>
+      <c r="O40" s="98"/>
+      <c r="P40" s="99"/>
       <c r="Q40" s="38"/>
-      <c r="R40" s="95"/>
-      <c r="S40" s="96"/>
-      <c r="T40" s="97"/>
+      <c r="R40" s="97"/>
+      <c r="S40" s="98"/>
+      <c r="T40" s="99"/>
       <c r="U40" s="29"/>
-      <c r="V40" s="95"/>
-      <c r="W40" s="96"/>
-      <c r="X40" s="97"/>
+      <c r="V40" s="97"/>
+      <c r="W40" s="98"/>
+      <c r="X40" s="99"/>
       <c r="Y40" s="32"/>
-      <c r="Z40" s="95" t="s">
+      <c r="Z40" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="AA40" s="96"/>
-      <c r="AB40" s="97"/>
+      <c r="AA40" s="98"/>
+      <c r="AB40" s="99"/>
       <c r="AC40" s="38"/>
-      <c r="AD40" s="95" t="s">
+      <c r="AD40" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="AE40" s="96"/>
-      <c r="AF40" s="97"/>
+      <c r="AE40" s="98"/>
+      <c r="AF40" s="99"/>
       <c r="AG40" s="29"/>
-      <c r="AH40" s="95"/>
-      <c r="AI40" s="96"/>
-      <c r="AJ40" s="97"/>
+      <c r="AH40" s="97"/>
+      <c r="AI40" s="98"/>
+      <c r="AJ40" s="99"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="95"/>
-      <c r="AM40" s="96"/>
-      <c r="AN40" s="97"/>
+      <c r="AL40" s="97"/>
+      <c r="AM40" s="98"/>
+      <c r="AN40" s="99"/>
       <c r="AO40" s="28"/>
       <c r="AP40" s="28"/>
       <c r="AQ40" s="28"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="117" t="s">
+      <c r="B41" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="118"/>
-      <c r="D41" s="127"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="129"/>
       <c r="E41" s="38"/>
-      <c r="F41" s="117" t="s">
+      <c r="F41" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="G41" s="118"/>
-      <c r="H41" s="127"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="129"/>
       <c r="I41" s="32"/>
-      <c r="J41" s="117"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="127"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="129"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="98"/>
-      <c r="O41" s="99"/>
-      <c r="P41" s="100"/>
+      <c r="N41" s="100"/>
+      <c r="O41" s="101"/>
+      <c r="P41" s="102"/>
       <c r="Q41" s="34"/>
-      <c r="R41" s="98"/>
-      <c r="S41" s="99"/>
-      <c r="T41" s="100"/>
+      <c r="R41" s="100"/>
+      <c r="S41" s="101"/>
+      <c r="T41" s="102"/>
       <c r="U41" s="34"/>
-      <c r="V41" s="98"/>
-      <c r="W41" s="99"/>
-      <c r="X41" s="100"/>
+      <c r="V41" s="100"/>
+      <c r="W41" s="101"/>
+      <c r="X41" s="102"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="98"/>
-      <c r="AA41" s="99"/>
-      <c r="AB41" s="100"/>
+      <c r="Z41" s="100"/>
+      <c r="AA41" s="101"/>
+      <c r="AB41" s="102"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="98"/>
-      <c r="AE41" s="99"/>
-      <c r="AF41" s="100"/>
+      <c r="AD41" s="100"/>
+      <c r="AE41" s="101"/>
+      <c r="AF41" s="102"/>
       <c r="AG41" s="38"/>
-      <c r="AH41" s="98"/>
-      <c r="AI41" s="99"/>
-      <c r="AJ41" s="100"/>
+      <c r="AH41" s="100"/>
+      <c r="AI41" s="101"/>
+      <c r="AJ41" s="102"/>
       <c r="AK41" s="32"/>
-      <c r="AL41" s="98" t="s">
+      <c r="AL41" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="AM41" s="99"/>
-      <c r="AN41" s="100"/>
+      <c r="AM41" s="101"/>
+      <c r="AN41" s="102"/>
       <c r="AO41" s="28"/>
       <c r="AP41" s="28"/>
       <c r="AQ41" s="28"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="114" t="s">
+      <c r="B42" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="115"/>
-      <c r="D42" s="116"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="118"/>
       <c r="E42" s="34"/>
-      <c r="F42" s="114" t="s">
+      <c r="F42" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="115"/>
-      <c r="H42" s="116"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="118"/>
       <c r="I42" s="32"/>
-      <c r="J42" s="114" t="s">
+      <c r="J42" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="K42" s="115"/>
-      <c r="L42" s="116"/>
+      <c r="K42" s="117"/>
+      <c r="L42" s="118"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="128"/>
-      <c r="O42" s="129"/>
-      <c r="P42" s="130"/>
+      <c r="N42" s="130"/>
+      <c r="O42" s="131"/>
+      <c r="P42" s="132"/>
       <c r="Q42" s="39"/>
-      <c r="R42" s="128"/>
-      <c r="S42" s="129"/>
-      <c r="T42" s="130"/>
+      <c r="R42" s="130"/>
+      <c r="S42" s="131"/>
+      <c r="T42" s="132"/>
       <c r="U42" s="39"/>
-      <c r="V42" s="128"/>
-      <c r="W42" s="129"/>
-      <c r="X42" s="130"/>
+      <c r="V42" s="130"/>
+      <c r="W42" s="131"/>
+      <c r="X42" s="132"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="75" t="s">
+      <c r="Z42" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="AA42" s="76"/>
-      <c r="AB42" s="77"/>
+      <c r="AA42" s="78"/>
+      <c r="AB42" s="79"/>
       <c r="AC42" s="44"/>
-      <c r="AD42" s="75" t="s">
+      <c r="AD42" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="AE42" s="76"/>
-      <c r="AF42" s="77"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="79"/>
       <c r="AG42" s="34"/>
-      <c r="AH42" s="75"/>
-      <c r="AI42" s="76"/>
-      <c r="AJ42" s="77"/>
+      <c r="AH42" s="77"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="79"/>
       <c r="AK42" s="32"/>
-      <c r="AL42" s="75" t="s">
+      <c r="AL42" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="AM42" s="76"/>
-      <c r="AN42" s="77"/>
+      <c r="AM42" s="78"/>
+      <c r="AN42" s="79"/>
       <c r="AO42" s="28"/>
       <c r="AP42" s="28"/>
       <c r="AQ42" s="28"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="136" t="s">
+      <c r="B43" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="137"/>
-      <c r="D43" s="138"/>
+      <c r="C43" s="136"/>
+      <c r="D43" s="137"/>
       <c r="E43" s="39"/>
-      <c r="F43" s="136" t="s">
+      <c r="F43" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="137"/>
-      <c r="H43" s="138"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="137"/>
       <c r="I43" s="37"/>
-      <c r="J43" s="136" t="s">
+      <c r="J43" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="137"/>
-      <c r="L43" s="138"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="137"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="128"/>
-      <c r="O43" s="129"/>
-      <c r="P43" s="130"/>
+      <c r="N43" s="130"/>
+      <c r="O43" s="131"/>
+      <c r="P43" s="132"/>
       <c r="Q43" s="39"/>
-      <c r="R43" s="128"/>
-      <c r="S43" s="129"/>
-      <c r="T43" s="130"/>
+      <c r="R43" s="130"/>
+      <c r="S43" s="131"/>
+      <c r="T43" s="132"/>
       <c r="U43" s="39"/>
-      <c r="V43" s="128"/>
-      <c r="W43" s="129"/>
-      <c r="X43" s="130"/>
+      <c r="V43" s="130"/>
+      <c r="W43" s="131"/>
+      <c r="X43" s="132"/>
       <c r="Y43" s="44"/>
-      <c r="Z43" s="128" t="s">
+      <c r="Z43" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="AA43" s="129"/>
-      <c r="AB43" s="130"/>
+      <c r="AA43" s="131"/>
+      <c r="AB43" s="132"/>
       <c r="AC43" s="37"/>
-      <c r="AD43" s="128" t="s">
+      <c r="AD43" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="AE43" s="129"/>
-      <c r="AF43" s="130"/>
+      <c r="AE43" s="131"/>
+      <c r="AF43" s="132"/>
       <c r="AG43" s="39"/>
-      <c r="AH43" s="128"/>
-      <c r="AI43" s="129"/>
-      <c r="AJ43" s="130"/>
+      <c r="AH43" s="130"/>
+      <c r="AI43" s="131"/>
+      <c r="AJ43" s="132"/>
       <c r="AK43" s="37"/>
-      <c r="AL43" s="128" t="s">
+      <c r="AL43" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="AM43" s="129"/>
-      <c r="AN43" s="130"/>
+      <c r="AM43" s="131"/>
+      <c r="AN43" s="132"/>
       <c r="AO43" s="28"/>
       <c r="AP43" s="28"/>
       <c r="AQ43" s="28"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
-      <c r="B44" s="105"/>
-      <c r="C44" s="106"/>
-      <c r="D44" s="107"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="109"/>
       <c r="E44" s="39"/>
-      <c r="F44" s="136" t="s">
+      <c r="F44" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="G44" s="137"/>
-      <c r="H44" s="138"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="137"/>
       <c r="I44" s="44"/>
-      <c r="J44" s="136" t="s">
+      <c r="J44" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="137"/>
-      <c r="L44" s="138"/>
+      <c r="K44" s="136"/>
+      <c r="L44" s="137"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="78"/>
-      <c r="O44" s="79"/>
-      <c r="P44" s="80"/>
+      <c r="N44" s="80"/>
+      <c r="O44" s="81"/>
+      <c r="P44" s="82"/>
       <c r="Q44" s="44"/>
-      <c r="R44" s="78"/>
-      <c r="S44" s="79"/>
-      <c r="T44" s="80"/>
+      <c r="R44" s="80"/>
+      <c r="S44" s="81"/>
+      <c r="T44" s="82"/>
       <c r="U44" s="44"/>
-      <c r="V44" s="78"/>
-      <c r="W44" s="79"/>
-      <c r="X44" s="80"/>
+      <c r="V44" s="80"/>
+      <c r="W44" s="81"/>
+      <c r="X44" s="82"/>
       <c r="Y44" s="44"/>
-      <c r="Z44" s="78"/>
-      <c r="AA44" s="79"/>
-      <c r="AB44" s="80"/>
+      <c r="Z44" s="80"/>
+      <c r="AA44" s="81"/>
+      <c r="AB44" s="82"/>
       <c r="AC44" s="44"/>
-      <c r="AD44" s="78"/>
-      <c r="AE44" s="79"/>
-      <c r="AF44" s="80"/>
+      <c r="AD44" s="80"/>
+      <c r="AE44" s="81"/>
+      <c r="AF44" s="82"/>
       <c r="AG44" s="39"/>
-      <c r="AH44" s="78"/>
-      <c r="AI44" s="79"/>
-      <c r="AJ44" s="80"/>
+      <c r="AH44" s="80"/>
+      <c r="AI44" s="81"/>
+      <c r="AJ44" s="82"/>
       <c r="AK44" s="44"/>
-      <c r="AL44" s="78"/>
-      <c r="AM44" s="79"/>
-      <c r="AN44" s="80"/>
+      <c r="AL44" s="80"/>
+      <c r="AM44" s="81"/>
+      <c r="AN44" s="82"/>
       <c r="AO44" s="28"/>
       <c r="AP44" s="28"/>
       <c r="AQ44" s="28"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="53"/>
       <c r="C45" s="53"/>
       <c r="D45" s="53"/>
       <c r="E45" s="44"/>
-      <c r="F45" s="136" t="s">
+      <c r="F45" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="137"/>
-      <c r="H45" s="138"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="137"/>
       <c r="I45" s="44"/>
-      <c r="J45" s="136" t="s">
+      <c r="J45" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="K45" s="137"/>
-      <c r="L45" s="138"/>
+      <c r="K45" s="136"/>
+      <c r="L45" s="137"/>
       <c r="M45" s="14"/>
       <c r="N45" s="32"/>
       <c r="O45" s="32"/>
@@ -5328,69 +5326,69 @@
       <c r="AQ45" s="28"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12"/>
-      <c r="B46" s="144" t="s">
+      <c r="B46" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="145"/>
+      <c r="C46" s="144"/>
       <c r="D46" s="62" t="s">
         <v>40</v>
       </c>
       <c r="E46" s="29"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="107"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="109"/>
       <c r="I46" s="49"/>
-      <c r="J46" s="105" t="s">
+      <c r="J46" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="K46" s="106"/>
-      <c r="L46" s="107"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="109"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="91"/>
-      <c r="O46" s="92"/>
+      <c r="N46" s="93"/>
+      <c r="O46" s="94"/>
       <c r="P46" s="31"/>
       <c r="Q46" s="33"/>
-      <c r="R46" s="139" t="s">
+      <c r="R46" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="S46" s="140"/>
+      <c r="S46" s="142"/>
       <c r="T46" s="68"/>
       <c r="U46" s="29"/>
-      <c r="V46" s="91"/>
-      <c r="W46" s="92"/>
+      <c r="V46" s="93"/>
+      <c r="W46" s="94"/>
       <c r="X46" s="31"/>
       <c r="Y46" s="49"/>
-      <c r="Z46" s="91"/>
-      <c r="AA46" s="92"/>
+      <c r="Z46" s="93"/>
+      <c r="AA46" s="94"/>
       <c r="AB46" s="31"/>
       <c r="AC46" s="33"/>
-      <c r="AD46" s="139" t="s">
+      <c r="AD46" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="AE46" s="140"/>
+      <c r="AE46" s="142"/>
       <c r="AF46" s="68"/>
       <c r="AG46" s="29"/>
-      <c r="AH46" s="91"/>
-      <c r="AI46" s="92"/>
+      <c r="AH46" s="93"/>
+      <c r="AI46" s="94"/>
       <c r="AJ46" s="31"/>
       <c r="AK46" s="49"/>
-      <c r="AL46" s="91"/>
-      <c r="AM46" s="92"/>
+      <c r="AL46" s="93"/>
+      <c r="AM46" s="94"/>
       <c r="AN46" s="31"/>
       <c r="AO46" s="28"/>
       <c r="AP46" s="28"/>
       <c r="AQ46" s="28"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
-      <c r="B47" s="124" t="s">
+      <c r="B47" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="125"/>
-      <c r="D47" s="126"/>
+      <c r="C47" s="127"/>
+      <c r="D47" s="128"/>
       <c r="E47" s="29"/>
       <c r="F47" s="53"/>
       <c r="G47" s="53"/>
@@ -5400,264 +5398,264 @@
       <c r="K47" s="53"/>
       <c r="L47" s="53"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="95"/>
-      <c r="O47" s="96"/>
-      <c r="P47" s="97"/>
+      <c r="N47" s="97"/>
+      <c r="O47" s="98"/>
+      <c r="P47" s="99"/>
       <c r="Q47" s="38"/>
-      <c r="R47" s="95" t="s">
+      <c r="R47" s="97" t="s">
         <v>123</v>
       </c>
-      <c r="S47" s="96"/>
-      <c r="T47" s="97"/>
+      <c r="S47" s="98"/>
+      <c r="T47" s="99"/>
       <c r="U47" s="29"/>
-      <c r="V47" s="95"/>
-      <c r="W47" s="96"/>
-      <c r="X47" s="97"/>
+      <c r="V47" s="97"/>
+      <c r="W47" s="98"/>
+      <c r="X47" s="99"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="95"/>
-      <c r="AA47" s="96"/>
-      <c r="AB47" s="97"/>
+      <c r="Z47" s="97"/>
+      <c r="AA47" s="98"/>
+      <c r="AB47" s="99"/>
       <c r="AC47" s="38"/>
-      <c r="AD47" s="95" t="s">
+      <c r="AD47" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="AE47" s="96"/>
-      <c r="AF47" s="97"/>
+      <c r="AE47" s="98"/>
+      <c r="AF47" s="99"/>
       <c r="AG47" s="29"/>
-      <c r="AH47" s="95"/>
-      <c r="AI47" s="96"/>
-      <c r="AJ47" s="97"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="98"/>
+      <c r="AJ47" s="99"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="95"/>
-      <c r="AM47" s="96"/>
-      <c r="AN47" s="97"/>
+      <c r="AL47" s="97"/>
+      <c r="AM47" s="98"/>
+      <c r="AN47" s="99"/>
       <c r="AO47" s="28"/>
       <c r="AP47" s="28"/>
       <c r="AQ47" s="28"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="117"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="127"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="120"/>
+      <c r="D48" s="129"/>
       <c r="E48" s="38"/>
-      <c r="F48" s="122"/>
-      <c r="G48" s="123"/>
+      <c r="F48" s="124"/>
+      <c r="G48" s="125"/>
       <c r="H48" s="52"/>
       <c r="I48" s="32"/>
-      <c r="J48" s="122" t="s">
+      <c r="J48" s="124" t="s">
         <v>64</v>
       </c>
-      <c r="K48" s="123"/>
+      <c r="K48" s="125"/>
       <c r="L48" s="52" t="s">
         <v>44</v>
       </c>
       <c r="M48" s="5"/>
-      <c r="N48" s="98"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="100"/>
+      <c r="N48" s="100"/>
+      <c r="O48" s="101"/>
+      <c r="P48" s="102"/>
       <c r="Q48" s="34"/>
-      <c r="R48" s="98"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="100"/>
+      <c r="R48" s="100"/>
+      <c r="S48" s="101"/>
+      <c r="T48" s="102"/>
       <c r="U48" s="34"/>
-      <c r="V48" s="98"/>
-      <c r="W48" s="99"/>
-      <c r="X48" s="100"/>
+      <c r="V48" s="100"/>
+      <c r="W48" s="101"/>
+      <c r="X48" s="102"/>
       <c r="Y48" s="32"/>
-      <c r="Z48" s="98"/>
-      <c r="AA48" s="99"/>
-      <c r="AB48" s="100"/>
+      <c r="Z48" s="100"/>
+      <c r="AA48" s="101"/>
+      <c r="AB48" s="102"/>
       <c r="AC48" s="32"/>
-      <c r="AD48" s="98"/>
-      <c r="AE48" s="99"/>
-      <c r="AF48" s="100"/>
+      <c r="AD48" s="100"/>
+      <c r="AE48" s="101"/>
+      <c r="AF48" s="102"/>
       <c r="AG48" s="38"/>
-      <c r="AH48" s="98"/>
-      <c r="AI48" s="99"/>
-      <c r="AJ48" s="100"/>
+      <c r="AH48" s="100"/>
+      <c r="AI48" s="101"/>
+      <c r="AJ48" s="102"/>
       <c r="AK48" s="32"/>
-      <c r="AL48" s="98"/>
-      <c r="AM48" s="99"/>
-      <c r="AN48" s="100"/>
+      <c r="AL48" s="100"/>
+      <c r="AM48" s="101"/>
+      <c r="AN48" s="102"/>
       <c r="AO48" s="28"/>
       <c r="AP48" s="28"/>
       <c r="AQ48" s="28"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="162" t="s">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="161" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="163"/>
-      <c r="D49" s="164"/>
+      <c r="C49" s="162"/>
+      <c r="D49" s="163"/>
       <c r="E49" s="34"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="126"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="127"/>
+      <c r="H49" s="128"/>
       <c r="I49" s="32"/>
-      <c r="J49" s="124" t="s">
+      <c r="J49" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K49" s="125"/>
-      <c r="L49" s="126"/>
+      <c r="K49" s="127"/>
+      <c r="L49" s="128"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="75"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="77"/>
+      <c r="N49" s="77"/>
+      <c r="O49" s="78"/>
+      <c r="P49" s="79"/>
       <c r="Q49" s="39"/>
-      <c r="R49" s="75" t="s">
+      <c r="R49" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="S49" s="76"/>
-      <c r="T49" s="77"/>
+      <c r="S49" s="78"/>
+      <c r="T49" s="79"/>
       <c r="U49" s="39"/>
-      <c r="V49" s="75"/>
-      <c r="W49" s="76"/>
-      <c r="X49" s="77"/>
+      <c r="V49" s="77"/>
+      <c r="W49" s="78"/>
+      <c r="X49" s="79"/>
       <c r="Y49" s="37"/>
-      <c r="Z49" s="75"/>
-      <c r="AA49" s="76"/>
-      <c r="AB49" s="77"/>
+      <c r="Z49" s="77"/>
+      <c r="AA49" s="78"/>
+      <c r="AB49" s="79"/>
       <c r="AC49" s="38"/>
-      <c r="AD49" s="75" t="s">
+      <c r="AD49" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AE49" s="76"/>
-      <c r="AF49" s="77"/>
+      <c r="AE49" s="78"/>
+      <c r="AF49" s="79"/>
       <c r="AG49" s="34"/>
-      <c r="AH49" s="75"/>
-      <c r="AI49" s="76"/>
-      <c r="AJ49" s="77"/>
+      <c r="AH49" s="77"/>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="79"/>
       <c r="AK49" s="32"/>
-      <c r="AL49" s="75"/>
-      <c r="AM49" s="76"/>
-      <c r="AN49" s="77"/>
+      <c r="AL49" s="77"/>
+      <c r="AM49" s="78"/>
+      <c r="AN49" s="79"/>
       <c r="AO49" s="28"/>
       <c r="AP49" s="28"/>
       <c r="AQ49" s="28"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="167" t="s">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="168"/>
-      <c r="D50" s="169"/>
+      <c r="C50" s="167"/>
+      <c r="D50" s="168"/>
       <c r="E50" s="39"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="118"/>
-      <c r="H50" s="127"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="120"/>
+      <c r="H50" s="129"/>
       <c r="I50" s="37"/>
-      <c r="J50" s="117"/>
-      <c r="K50" s="118"/>
-      <c r="L50" s="127"/>
+      <c r="J50" s="119"/>
+      <c r="K50" s="120"/>
+      <c r="L50" s="129"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="128"/>
-      <c r="O50" s="129"/>
-      <c r="P50" s="130"/>
+      <c r="N50" s="130"/>
+      <c r="O50" s="131"/>
+      <c r="P50" s="132"/>
       <c r="Q50" s="39"/>
-      <c r="R50" s="78"/>
-      <c r="S50" s="79"/>
-      <c r="T50" s="80"/>
+      <c r="R50" s="80"/>
+      <c r="S50" s="81"/>
+      <c r="T50" s="82"/>
       <c r="U50" s="39"/>
-      <c r="V50" s="128"/>
-      <c r="W50" s="129"/>
-      <c r="X50" s="130"/>
+      <c r="V50" s="130"/>
+      <c r="W50" s="131"/>
+      <c r="X50" s="132"/>
       <c r="Y50" s="44"/>
-      <c r="Z50" s="128"/>
-      <c r="AA50" s="129"/>
-      <c r="AB50" s="130"/>
+      <c r="Z50" s="130"/>
+      <c r="AA50" s="131"/>
+      <c r="AB50" s="132"/>
       <c r="AC50" s="39"/>
-      <c r="AD50" s="128" t="s">
+      <c r="AD50" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="AE50" s="129"/>
-      <c r="AF50" s="130"/>
+      <c r="AE50" s="131"/>
+      <c r="AF50" s="132"/>
       <c r="AG50" s="39"/>
-      <c r="AH50" s="128"/>
-      <c r="AI50" s="129"/>
-      <c r="AJ50" s="130"/>
+      <c r="AH50" s="130"/>
+      <c r="AI50" s="131"/>
+      <c r="AJ50" s="132"/>
       <c r="AK50" s="37"/>
-      <c r="AL50" s="128"/>
-      <c r="AM50" s="129"/>
-      <c r="AN50" s="130"/>
+      <c r="AL50" s="130"/>
+      <c r="AM50" s="131"/>
+      <c r="AN50" s="132"/>
       <c r="AO50" s="28"/>
       <c r="AP50" s="28"/>
       <c r="AQ50" s="28"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="105"/>
-      <c r="C51" s="106"/>
-      <c r="D51" s="107"/>
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="107"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="109"/>
       <c r="E51" s="39"/>
-      <c r="F51" s="136"/>
-      <c r="G51" s="137"/>
-      <c r="H51" s="138"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="136"/>
+      <c r="H51" s="137"/>
       <c r="I51" s="44"/>
-      <c r="J51" s="136" t="s">
+      <c r="J51" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="137"/>
-      <c r="L51" s="138"/>
+      <c r="K51" s="136"/>
+      <c r="L51" s="137"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="78"/>
-      <c r="O51" s="79"/>
-      <c r="P51" s="80"/>
+      <c r="N51" s="80"/>
+      <c r="O51" s="81"/>
+      <c r="P51" s="82"/>
       <c r="Q51" s="44"/>
       <c r="R51" s="32"/>
       <c r="S51" s="32"/>
       <c r="T51" s="32"/>
       <c r="U51" s="44"/>
-      <c r="V51" s="78"/>
-      <c r="W51" s="79"/>
-      <c r="X51" s="80"/>
+      <c r="V51" s="80"/>
+      <c r="W51" s="81"/>
+      <c r="X51" s="82"/>
       <c r="Y51" s="44"/>
-      <c r="Z51" s="78"/>
-      <c r="AA51" s="79"/>
-      <c r="AB51" s="80"/>
+      <c r="Z51" s="80"/>
+      <c r="AA51" s="81"/>
+      <c r="AB51" s="82"/>
       <c r="AC51" s="44"/>
-      <c r="AD51" s="78"/>
-      <c r="AE51" s="79"/>
-      <c r="AF51" s="80"/>
+      <c r="AD51" s="80"/>
+      <c r="AE51" s="81"/>
+      <c r="AF51" s="82"/>
       <c r="AG51" s="39"/>
-      <c r="AH51" s="78"/>
-      <c r="AI51" s="79"/>
-      <c r="AJ51" s="80"/>
+      <c r="AH51" s="80"/>
+      <c r="AI51" s="81"/>
+      <c r="AJ51" s="82"/>
       <c r="AK51" s="44"/>
-      <c r="AL51" s="133"/>
-      <c r="AM51" s="134"/>
-      <c r="AN51" s="135"/>
+      <c r="AL51" s="138"/>
+      <c r="AM51" s="139"/>
+      <c r="AN51" s="140"/>
       <c r="AO51" s="28"/>
       <c r="AP51" s="28"/>
       <c r="AQ51" s="28"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="53"/>
       <c r="C52" s="53"/>
       <c r="D52" s="53"/>
       <c r="E52" s="44"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="106"/>
-      <c r="H52" s="107"/>
+      <c r="F52" s="107"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="109"/>
       <c r="I52" s="44"/>
-      <c r="J52" s="105" t="s">
+      <c r="J52" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="K52" s="106"/>
-      <c r="L52" s="107"/>
+      <c r="K52" s="108"/>
+      <c r="L52" s="109"/>
       <c r="M52" s="14"/>
       <c r="N52" s="32"/>
       <c r="O52" s="32"/>
       <c r="P52" s="32"/>
       <c r="Q52" s="28"/>
-      <c r="R52" s="139" t="s">
+      <c r="R52" s="141" t="s">
         <v>114</v>
       </c>
-      <c r="S52" s="140"/>
+      <c r="S52" s="142"/>
       <c r="T52" s="68"/>
       <c r="U52" s="44"/>
       <c r="V52" s="32"/>
@@ -5681,11 +5679,11 @@
       <c r="AN52" s="32"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="144" t="s">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="145"/>
+      <c r="C53" s="144"/>
       <c r="D53" s="62" t="s">
         <v>43</v>
       </c>
@@ -5698,310 +5696,310 @@
       <c r="K53" s="53"/>
       <c r="L53" s="53"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="91"/>
-      <c r="O53" s="92"/>
+      <c r="N53" s="93"/>
+      <c r="O53" s="94"/>
       <c r="P53" s="31"/>
       <c r="Q53" s="33"/>
-      <c r="R53" s="95" t="s">
+      <c r="R53" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="S53" s="96"/>
-      <c r="T53" s="97"/>
+      <c r="S53" s="98"/>
+      <c r="T53" s="99"/>
       <c r="U53" s="29"/>
-      <c r="V53" s="91"/>
-      <c r="W53" s="92"/>
+      <c r="V53" s="93"/>
+      <c r="W53" s="94"/>
       <c r="X53" s="31"/>
       <c r="Y53" s="49"/>
-      <c r="Z53" s="91"/>
-      <c r="AA53" s="92"/>
+      <c r="Z53" s="93"/>
+      <c r="AA53" s="94"/>
       <c r="AB53" s="31"/>
       <c r="AC53" s="49"/>
-      <c r="AD53" s="139" t="s">
+      <c r="AD53" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="AE53" s="140"/>
+      <c r="AE53" s="142"/>
       <c r="AF53" s="68"/>
       <c r="AG53" s="29"/>
-      <c r="AH53" s="91"/>
-      <c r="AI53" s="92"/>
+      <c r="AH53" s="93"/>
+      <c r="AI53" s="94"/>
       <c r="AJ53" s="31"/>
       <c r="AK53" s="49"/>
-      <c r="AL53" s="91"/>
-      <c r="AM53" s="92"/>
+      <c r="AL53" s="93"/>
+      <c r="AM53" s="94"/>
       <c r="AN53" s="31"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="124" t="s">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="125"/>
-      <c r="D54" s="126"/>
+      <c r="C54" s="127"/>
+      <c r="D54" s="128"/>
       <c r="E54" s="29"/>
-      <c r="F54" s="144" t="s">
+      <c r="F54" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="G54" s="145"/>
+      <c r="G54" s="144"/>
       <c r="H54" s="62" t="s">
         <v>43</v>
       </c>
       <c r="I54" s="32"/>
-      <c r="J54" s="144" t="s">
+      <c r="J54" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="K54" s="145"/>
+      <c r="K54" s="144"/>
       <c r="L54" s="62" t="s">
         <v>43</v>
       </c>
       <c r="M54" s="4"/>
-      <c r="N54" s="95"/>
-      <c r="O54" s="96"/>
-      <c r="P54" s="97"/>
+      <c r="N54" s="97"/>
+      <c r="O54" s="98"/>
+      <c r="P54" s="99"/>
       <c r="Q54" s="38"/>
-      <c r="R54" s="98"/>
-      <c r="S54" s="99"/>
-      <c r="T54" s="100"/>
+      <c r="R54" s="100"/>
+      <c r="S54" s="101"/>
+      <c r="T54" s="102"/>
       <c r="U54" s="29"/>
-      <c r="V54" s="95"/>
-      <c r="W54" s="96"/>
-      <c r="X54" s="97"/>
+      <c r="V54" s="97"/>
+      <c r="W54" s="98"/>
+      <c r="X54" s="99"/>
       <c r="Y54" s="32"/>
-      <c r="Z54" s="95"/>
-      <c r="AA54" s="96"/>
-      <c r="AB54" s="97"/>
+      <c r="Z54" s="97"/>
+      <c r="AA54" s="98"/>
+      <c r="AB54" s="99"/>
       <c r="AC54" s="32"/>
-      <c r="AD54" s="95" t="s">
+      <c r="AD54" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="AE54" s="96"/>
-      <c r="AF54" s="97"/>
+      <c r="AE54" s="98"/>
+      <c r="AF54" s="99"/>
       <c r="AG54" s="29"/>
-      <c r="AH54" s="95"/>
-      <c r="AI54" s="96"/>
-      <c r="AJ54" s="97"/>
+      <c r="AH54" s="97"/>
+      <c r="AI54" s="98"/>
+      <c r="AJ54" s="99"/>
       <c r="AK54" s="32"/>
-      <c r="AL54" s="95"/>
-      <c r="AM54" s="96"/>
-      <c r="AN54" s="97"/>
+      <c r="AL54" s="97"/>
+      <c r="AM54" s="98"/>
+      <c r="AN54" s="99"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="117"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="127"/>
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="119"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="129"/>
       <c r="E55" s="38"/>
-      <c r="F55" s="124" t="s">
+      <c r="F55" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="G55" s="125"/>
-      <c r="H55" s="126"/>
+      <c r="G55" s="127"/>
+      <c r="H55" s="128"/>
       <c r="I55" s="32"/>
-      <c r="J55" s="124" t="s">
+      <c r="J55" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="K55" s="125"/>
-      <c r="L55" s="126"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="98"/>
-      <c r="O55" s="99"/>
-      <c r="P55" s="100"/>
+      <c r="N55" s="100"/>
+      <c r="O55" s="101"/>
+      <c r="P55" s="102"/>
       <c r="Q55" s="34"/>
-      <c r="R55" s="75" t="s">
+      <c r="R55" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="S55" s="76"/>
-      <c r="T55" s="77"/>
+      <c r="S55" s="78"/>
+      <c r="T55" s="79"/>
       <c r="U55" s="49"/>
-      <c r="V55" s="98"/>
-      <c r="W55" s="99"/>
-      <c r="X55" s="100"/>
+      <c r="V55" s="100"/>
+      <c r="W55" s="101"/>
+      <c r="X55" s="102"/>
       <c r="Y55" s="32"/>
-      <c r="Z55" s="98"/>
-      <c r="AA55" s="99"/>
-      <c r="AB55" s="100"/>
+      <c r="Z55" s="100"/>
+      <c r="AA55" s="101"/>
+      <c r="AB55" s="102"/>
       <c r="AC55" s="32"/>
-      <c r="AD55" s="98"/>
-      <c r="AE55" s="99"/>
-      <c r="AF55" s="100"/>
+      <c r="AD55" s="100"/>
+      <c r="AE55" s="101"/>
+      <c r="AF55" s="102"/>
       <c r="AG55" s="38"/>
-      <c r="AH55" s="98"/>
-      <c r="AI55" s="99"/>
-      <c r="AJ55" s="100"/>
+      <c r="AH55" s="100"/>
+      <c r="AI55" s="101"/>
+      <c r="AJ55" s="102"/>
       <c r="AK55" s="32"/>
-      <c r="AL55" s="98"/>
-      <c r="AM55" s="99"/>
-      <c r="AN55" s="100"/>
+      <c r="AL55" s="100"/>
+      <c r="AM55" s="101"/>
+      <c r="AN55" s="102"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="162" t="s">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="163"/>
-      <c r="D56" s="164"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="163"/>
       <c r="E56" s="34"/>
-      <c r="F56" s="117"/>
-      <c r="G56" s="118"/>
-      <c r="H56" s="127"/>
+      <c r="F56" s="119"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="129"/>
       <c r="I56" s="32"/>
-      <c r="J56" s="117"/>
-      <c r="K56" s="118"/>
-      <c r="L56" s="127"/>
+      <c r="J56" s="119"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="75"/>
-      <c r="O56" s="76"/>
-      <c r="P56" s="77"/>
+      <c r="N56" s="77"/>
+      <c r="O56" s="78"/>
+      <c r="P56" s="79"/>
       <c r="Q56" s="39"/>
-      <c r="R56" s="128" t="s">
+      <c r="R56" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="S56" s="129"/>
-      <c r="T56" s="130"/>
+      <c r="S56" s="131"/>
+      <c r="T56" s="132"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="75"/>
-      <c r="W56" s="76"/>
-      <c r="X56" s="77"/>
+      <c r="V56" s="77"/>
+      <c r="W56" s="78"/>
+      <c r="X56" s="79"/>
       <c r="Y56" s="37"/>
-      <c r="Z56" s="75"/>
-      <c r="AA56" s="76"/>
-      <c r="AB56" s="77"/>
+      <c r="Z56" s="77"/>
+      <c r="AA56" s="78"/>
+      <c r="AB56" s="79"/>
       <c r="AC56" s="32"/>
-      <c r="AD56" s="128" t="s">
+      <c r="AD56" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="AE56" s="129"/>
-      <c r="AF56" s="130"/>
+      <c r="AE56" s="131"/>
+      <c r="AF56" s="132"/>
       <c r="AG56" s="34"/>
-      <c r="AH56" s="75"/>
-      <c r="AI56" s="76"/>
-      <c r="AJ56" s="77"/>
+      <c r="AH56" s="77"/>
+      <c r="AI56" s="78"/>
+      <c r="AJ56" s="79"/>
       <c r="AK56" s="32"/>
-      <c r="AL56" s="128"/>
-      <c r="AM56" s="129"/>
-      <c r="AN56" s="130"/>
+      <c r="AL56" s="130"/>
+      <c r="AM56" s="131"/>
+      <c r="AN56" s="132"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="167" t="s">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="C57" s="168"/>
-      <c r="D57" s="169"/>
+      <c r="C57" s="167"/>
+      <c r="D57" s="168"/>
       <c r="E57" s="39"/>
-      <c r="F57" s="162" t="s">
+      <c r="F57" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="G57" s="163"/>
-      <c r="H57" s="164"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="163"/>
       <c r="I57" s="37"/>
-      <c r="J57" s="162" t="s">
+      <c r="J57" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="K57" s="163"/>
-      <c r="L57" s="164"/>
+      <c r="K57" s="162"/>
+      <c r="L57" s="163"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="128"/>
-      <c r="O57" s="129"/>
-      <c r="P57" s="130"/>
+      <c r="N57" s="130"/>
+      <c r="O57" s="131"/>
+      <c r="P57" s="132"/>
       <c r="Q57" s="39"/>
-      <c r="R57" s="128" t="s">
+      <c r="R57" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="S57" s="129"/>
-      <c r="T57" s="130"/>
+      <c r="S57" s="131"/>
+      <c r="T57" s="132"/>
       <c r="U57" s="39"/>
-      <c r="V57" s="128"/>
-      <c r="W57" s="129"/>
-      <c r="X57" s="130"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="131"/>
+      <c r="X57" s="132"/>
       <c r="Y57" s="44"/>
-      <c r="Z57" s="128"/>
-      <c r="AA57" s="129"/>
-      <c r="AB57" s="130"/>
+      <c r="Z57" s="130"/>
+      <c r="AA57" s="131"/>
+      <c r="AB57" s="132"/>
       <c r="AC57" s="37"/>
-      <c r="AD57" s="141" t="s">
+      <c r="AD57" s="206" t="s">
         <v>131</v>
       </c>
-      <c r="AE57" s="142"/>
-      <c r="AF57" s="143"/>
+      <c r="AE57" s="207"/>
+      <c r="AF57" s="208"/>
       <c r="AG57" s="39"/>
-      <c r="AH57" s="128"/>
-      <c r="AI57" s="129"/>
-      <c r="AJ57" s="130"/>
+      <c r="AH57" s="130"/>
+      <c r="AI57" s="131"/>
+      <c r="AJ57" s="132"/>
       <c r="AK57" s="37"/>
-      <c r="AL57" s="128"/>
-      <c r="AM57" s="129"/>
-      <c r="AN57" s="130"/>
+      <c r="AL57" s="130"/>
+      <c r="AM57" s="131"/>
+      <c r="AN57" s="132"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="165" t="s">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="166"/>
+      <c r="C58" s="165"/>
       <c r="D58" s="63" t="s">
         <v>83</v>
       </c>
       <c r="E58" s="39"/>
-      <c r="F58" s="167" t="s">
+      <c r="F58" s="166" t="s">
         <v>37</v>
       </c>
-      <c r="G58" s="168"/>
-      <c r="H58" s="169"/>
+      <c r="G58" s="167"/>
+      <c r="H58" s="168"/>
       <c r="I58" s="44"/>
-      <c r="J58" s="167" t="s">
+      <c r="J58" s="166" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="168"/>
-      <c r="L58" s="169"/>
+      <c r="K58" s="167"/>
+      <c r="L58" s="168"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="78"/>
-      <c r="O58" s="79"/>
-      <c r="P58" s="80"/>
+      <c r="N58" s="80"/>
+      <c r="O58" s="81"/>
+      <c r="P58" s="82"/>
       <c r="Q58" s="44"/>
-      <c r="R58" s="78" t="s">
+      <c r="R58" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="S58" s="79"/>
-      <c r="T58" s="80"/>
+      <c r="S58" s="81"/>
+      <c r="T58" s="82"/>
       <c r="U58" s="44"/>
-      <c r="V58" s="78"/>
-      <c r="W58" s="79"/>
-      <c r="X58" s="80"/>
+      <c r="V58" s="80"/>
+      <c r="W58" s="81"/>
+      <c r="X58" s="82"/>
       <c r="Y58" s="44"/>
-      <c r="Z58" s="78"/>
-      <c r="AA58" s="79"/>
-      <c r="AB58" s="80"/>
+      <c r="Z58" s="80"/>
+      <c r="AA58" s="81"/>
+      <c r="AB58" s="82"/>
       <c r="AC58" s="44"/>
-      <c r="AD58" s="78"/>
-      <c r="AE58" s="79"/>
-      <c r="AF58" s="80"/>
+      <c r="AD58" s="80"/>
+      <c r="AE58" s="81"/>
+      <c r="AF58" s="82"/>
       <c r="AG58" s="39"/>
-      <c r="AH58" s="78"/>
-      <c r="AI58" s="79"/>
-      <c r="AJ58" s="80"/>
+      <c r="AH58" s="80"/>
+      <c r="AI58" s="81"/>
+      <c r="AJ58" s="82"/>
       <c r="AK58" s="44"/>
-      <c r="AL58" s="78"/>
-      <c r="AM58" s="79"/>
-      <c r="AN58" s="80"/>
+      <c r="AL58" s="80"/>
+      <c r="AM58" s="81"/>
+      <c r="AN58" s="82"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="53"/>
       <c r="C59" s="53"/>
       <c r="D59" s="53"/>
       <c r="E59" s="44"/>
-      <c r="F59" s="165" t="s">
+      <c r="F59" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="G59" s="166"/>
+      <c r="G59" s="165"/>
       <c r="H59" s="63" t="s">
         <v>83</v>
       </c>
       <c r="I59" s="44"/>
-      <c r="J59" s="165" t="s">
+      <c r="J59" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="K59" s="166"/>
+      <c r="K59" s="165"/>
       <c r="L59" s="63" t="s">
         <v>83</v>
       </c>
@@ -6035,229 +6033,229 @@
       <c r="AN59" s="32"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="122"/>
-      <c r="C60" s="123"/>
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="124"/>
+      <c r="C60" s="125"/>
       <c r="D60" s="52"/>
       <c r="E60" s="29"/>
-      <c r="F60" s="122"/>
-      <c r="G60" s="123"/>
+      <c r="F60" s="124"/>
+      <c r="G60" s="125"/>
       <c r="H60" s="52"/>
       <c r="I60" s="49"/>
-      <c r="J60" s="122"/>
-      <c r="K60" s="123"/>
+      <c r="J60" s="124"/>
+      <c r="K60" s="125"/>
       <c r="L60" s="52"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="91"/>
-      <c r="O60" s="92"/>
+      <c r="N60" s="93"/>
+      <c r="O60" s="94"/>
       <c r="P60" s="31"/>
       <c r="Q60" s="33"/>
-      <c r="R60" s="91"/>
-      <c r="S60" s="92"/>
+      <c r="R60" s="93"/>
+      <c r="S60" s="94"/>
       <c r="T60" s="31"/>
       <c r="U60" s="29"/>
-      <c r="V60" s="91"/>
-      <c r="W60" s="92"/>
+      <c r="V60" s="93"/>
+      <c r="W60" s="94"/>
       <c r="X60" s="31"/>
       <c r="Y60" s="49"/>
-      <c r="Z60" s="139" t="s">
+      <c r="Z60" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="AA60" s="140"/>
+      <c r="AA60" s="142"/>
       <c r="AB60" s="68"/>
       <c r="AC60" s="33"/>
-      <c r="AD60" s="139" t="s">
+      <c r="AD60" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="AE60" s="140"/>
+      <c r="AE60" s="142"/>
       <c r="AF60" s="68"/>
       <c r="AG60" s="29"/>
-      <c r="AH60" s="91"/>
-      <c r="AI60" s="92"/>
+      <c r="AH60" s="93"/>
+      <c r="AI60" s="94"/>
       <c r="AJ60" s="31"/>
       <c r="AK60" s="49"/>
-      <c r="AL60" s="91"/>
-      <c r="AM60" s="92"/>
+      <c r="AL60" s="93"/>
+      <c r="AM60" s="94"/>
       <c r="AN60" s="31"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="124"/>
-      <c r="C61" s="125"/>
-      <c r="D61" s="126"/>
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="126"/>
+      <c r="C61" s="127"/>
+      <c r="D61" s="128"/>
       <c r="E61" s="29"/>
-      <c r="F61" s="124"/>
-      <c r="G61" s="125"/>
-      <c r="H61" s="126"/>
+      <c r="F61" s="126"/>
+      <c r="G61" s="127"/>
+      <c r="H61" s="128"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="124"/>
-      <c r="K61" s="125"/>
-      <c r="L61" s="126"/>
+      <c r="J61" s="126"/>
+      <c r="K61" s="127"/>
+      <c r="L61" s="128"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="95"/>
-      <c r="O61" s="96"/>
-      <c r="P61" s="97"/>
+      <c r="N61" s="97"/>
+      <c r="O61" s="98"/>
+      <c r="P61" s="99"/>
       <c r="Q61" s="38"/>
-      <c r="R61" s="95"/>
-      <c r="S61" s="96"/>
-      <c r="T61" s="97"/>
+      <c r="R61" s="97"/>
+      <c r="S61" s="98"/>
+      <c r="T61" s="99"/>
       <c r="U61" s="29"/>
-      <c r="V61" s="95"/>
-      <c r="W61" s="96"/>
-      <c r="X61" s="97"/>
+      <c r="V61" s="97"/>
+      <c r="W61" s="98"/>
+      <c r="X61" s="99"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="95"/>
-      <c r="AA61" s="96"/>
-      <c r="AB61" s="97"/>
+      <c r="Z61" s="97"/>
+      <c r="AA61" s="98"/>
+      <c r="AB61" s="99"/>
       <c r="AC61" s="38"/>
-      <c r="AD61" s="95"/>
-      <c r="AE61" s="96"/>
-      <c r="AF61" s="97"/>
+      <c r="AD61" s="97"/>
+      <c r="AE61" s="98"/>
+      <c r="AF61" s="99"/>
       <c r="AG61" s="29"/>
-      <c r="AH61" s="95"/>
-      <c r="AI61" s="96"/>
-      <c r="AJ61" s="97"/>
+      <c r="AH61" s="97"/>
+      <c r="AI61" s="98"/>
+      <c r="AJ61" s="99"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="95"/>
-      <c r="AM61" s="96"/>
-      <c r="AN61" s="97"/>
+      <c r="AL61" s="97"/>
+      <c r="AM61" s="98"/>
+      <c r="AN61" s="99"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="117"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="127"/>
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="119"/>
+      <c r="C62" s="120"/>
+      <c r="D62" s="129"/>
       <c r="E62" s="38"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="118"/>
-      <c r="H62" s="127"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="120"/>
+      <c r="H62" s="129"/>
       <c r="I62" s="32"/>
-      <c r="J62" s="117"/>
-      <c r="K62" s="118"/>
-      <c r="L62" s="127"/>
+      <c r="J62" s="119"/>
+      <c r="K62" s="120"/>
+      <c r="L62" s="129"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="98"/>
-      <c r="O62" s="99"/>
-      <c r="P62" s="100"/>
+      <c r="N62" s="100"/>
+      <c r="O62" s="101"/>
+      <c r="P62" s="102"/>
       <c r="Q62" s="34"/>
-      <c r="R62" s="98"/>
-      <c r="S62" s="99"/>
-      <c r="T62" s="100"/>
+      <c r="R62" s="100"/>
+      <c r="S62" s="101"/>
+      <c r="T62" s="102"/>
       <c r="U62" s="34"/>
-      <c r="V62" s="98"/>
-      <c r="W62" s="99"/>
-      <c r="X62" s="100"/>
+      <c r="V62" s="100"/>
+      <c r="W62" s="101"/>
+      <c r="X62" s="102"/>
       <c r="Y62" s="32"/>
-      <c r="Z62" s="98"/>
-      <c r="AA62" s="99"/>
-      <c r="AB62" s="100"/>
+      <c r="Z62" s="100"/>
+      <c r="AA62" s="101"/>
+      <c r="AB62" s="102"/>
       <c r="AC62" s="32"/>
-      <c r="AD62" s="98"/>
-      <c r="AE62" s="99"/>
-      <c r="AF62" s="100"/>
+      <c r="AD62" s="100"/>
+      <c r="AE62" s="101"/>
+      <c r="AF62" s="102"/>
       <c r="AG62" s="38"/>
-      <c r="AH62" s="98"/>
-      <c r="AI62" s="99"/>
-      <c r="AJ62" s="100"/>
+      <c r="AH62" s="100"/>
+      <c r="AI62" s="101"/>
+      <c r="AJ62" s="102"/>
       <c r="AK62" s="32"/>
-      <c r="AL62" s="98"/>
-      <c r="AM62" s="99"/>
-      <c r="AN62" s="100"/>
+      <c r="AL62" s="100"/>
+      <c r="AM62" s="101"/>
+      <c r="AN62" s="102"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="114"/>
-      <c r="C63" s="115"/>
-      <c r="D63" s="116"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="116"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="118"/>
       <c r="E63" s="34"/>
-      <c r="F63" s="114"/>
-      <c r="G63" s="115"/>
-      <c r="H63" s="116"/>
+      <c r="F63" s="116"/>
+      <c r="G63" s="117"/>
+      <c r="H63" s="118"/>
       <c r="I63" s="32"/>
-      <c r="J63" s="136"/>
-      <c r="K63" s="137"/>
-      <c r="L63" s="138"/>
+      <c r="J63" s="135"/>
+      <c r="K63" s="136"/>
+      <c r="L63" s="137"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="75"/>
-      <c r="O63" s="76"/>
-      <c r="P63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="78"/>
+      <c r="P63" s="79"/>
       <c r="Q63" s="39"/>
-      <c r="R63" s="75"/>
-      <c r="S63" s="76"/>
-      <c r="T63" s="77"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="78"/>
+      <c r="T63" s="79"/>
       <c r="U63" s="39"/>
-      <c r="V63" s="75"/>
-      <c r="W63" s="76"/>
-      <c r="X63" s="77"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="78"/>
+      <c r="X63" s="79"/>
       <c r="Y63" s="37"/>
-      <c r="Z63" s="75" t="s">
+      <c r="Z63" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="AA63" s="76"/>
-      <c r="AB63" s="77"/>
+      <c r="AA63" s="78"/>
+      <c r="AB63" s="79"/>
       <c r="AC63" s="38"/>
-      <c r="AD63" s="75" t="s">
+      <c r="AD63" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="AE63" s="76"/>
-      <c r="AF63" s="77"/>
+      <c r="AE63" s="78"/>
+      <c r="AF63" s="79"/>
       <c r="AG63" s="34"/>
-      <c r="AH63" s="75"/>
-      <c r="AI63" s="76"/>
-      <c r="AJ63" s="77"/>
+      <c r="AH63" s="77"/>
+      <c r="AI63" s="78"/>
+      <c r="AJ63" s="79"/>
       <c r="AK63" s="32"/>
-      <c r="AL63" s="128"/>
-      <c r="AM63" s="129"/>
-      <c r="AN63" s="130"/>
+      <c r="AL63" s="130"/>
+      <c r="AM63" s="131"/>
+      <c r="AN63" s="132"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="105"/>
-      <c r="C64" s="106"/>
-      <c r="D64" s="107"/>
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="107"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="109"/>
       <c r="E64" s="39"/>
-      <c r="F64" s="105"/>
-      <c r="G64" s="106"/>
-      <c r="H64" s="107"/>
+      <c r="F64" s="107"/>
+      <c r="G64" s="108"/>
+      <c r="H64" s="109"/>
       <c r="I64" s="39"/>
-      <c r="J64" s="105"/>
-      <c r="K64" s="106"/>
-      <c r="L64" s="107"/>
+      <c r="J64" s="107"/>
+      <c r="K64" s="108"/>
+      <c r="L64" s="109"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="78"/>
-      <c r="O64" s="79"/>
-      <c r="P64" s="80"/>
+      <c r="N64" s="80"/>
+      <c r="O64" s="81"/>
+      <c r="P64" s="82"/>
       <c r="Q64" s="44"/>
-      <c r="R64" s="78"/>
-      <c r="S64" s="79"/>
-      <c r="T64" s="80"/>
+      <c r="R64" s="80"/>
+      <c r="S64" s="81"/>
+      <c r="T64" s="82"/>
       <c r="U64" s="44"/>
-      <c r="V64" s="78"/>
-      <c r="W64" s="79"/>
-      <c r="X64" s="80"/>
+      <c r="V64" s="80"/>
+      <c r="W64" s="81"/>
+      <c r="X64" s="82"/>
       <c r="Y64" s="44"/>
-      <c r="Z64" s="128" t="s">
+      <c r="Z64" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="AA64" s="129"/>
-      <c r="AB64" s="130"/>
+      <c r="AA64" s="131"/>
+      <c r="AB64" s="132"/>
       <c r="AC64" s="39"/>
-      <c r="AD64" s="218" t="s">
+      <c r="AD64" s="224" t="s">
         <v>120</v>
       </c>
-      <c r="AE64" s="219"/>
-      <c r="AF64" s="220"/>
+      <c r="AE64" s="225"/>
+      <c r="AF64" s="226"/>
       <c r="AG64" s="39"/>
-      <c r="AH64" s="78"/>
-      <c r="AI64" s="79"/>
-      <c r="AJ64" s="80"/>
+      <c r="AH64" s="80"/>
+      <c r="AI64" s="81"/>
+      <c r="AJ64" s="82"/>
       <c r="AK64" s="39"/>
-      <c r="AL64" s="78"/>
-      <c r="AM64" s="79"/>
-      <c r="AN64" s="80"/>
+      <c r="AL64" s="80"/>
+      <c r="AM64" s="81"/>
+      <c r="AN64" s="82"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="12"/>
       <c r="B65" s="58"/>
       <c r="C65" s="58"/>
@@ -6283,13 +6281,13 @@
       <c r="W65" s="32"/>
       <c r="X65" s="32"/>
       <c r="Y65" s="67"/>
-      <c r="Z65" s="78"/>
-      <c r="AA65" s="79"/>
-      <c r="AB65" s="80"/>
+      <c r="Z65" s="80"/>
+      <c r="AA65" s="81"/>
+      <c r="AB65" s="82"/>
       <c r="AC65" s="44"/>
-      <c r="AD65" s="78"/>
-      <c r="AE65" s="79"/>
-      <c r="AF65" s="80"/>
+      <c r="AD65" s="80"/>
+      <c r="AE65" s="81"/>
+      <c r="AF65" s="82"/>
       <c r="AG65" s="30"/>
       <c r="AH65" s="30"/>
       <c r="AI65" s="30"/>
@@ -6303,7 +6301,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="61"/>
       <c r="C66" s="58"/>
@@ -6317,23 +6315,23 @@
       <c r="K66" s="58"/>
       <c r="L66" s="58"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="180" t="s">
+      <c r="N66" s="179" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="180"/>
-      <c r="P66" s="180"/>
-      <c r="Q66" s="180"/>
-      <c r="R66" s="180"/>
-      <c r="S66" s="180"/>
-      <c r="T66" s="180"/>
-      <c r="U66" s="180"/>
-      <c r="V66" s="180"/>
-      <c r="W66" s="180"/>
-      <c r="X66" s="180"/>
-      <c r="Y66" s="180"/>
-      <c r="Z66" s="180"/>
-      <c r="AA66" s="180"/>
-      <c r="AB66" s="180"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
+      <c r="R66" s="179"/>
+      <c r="S66" s="179"/>
+      <c r="T66" s="179"/>
+      <c r="U66" s="179"/>
+      <c r="V66" s="179"/>
+      <c r="W66" s="179"/>
+      <c r="X66" s="179"/>
+      <c r="Y66" s="179"/>
+      <c r="Z66" s="179"/>
+      <c r="AA66" s="179"/>
+      <c r="AB66" s="179"/>
       <c r="AD66" s="37"/>
       <c r="AE66" s="30"/>
       <c r="AF66" s="30"/>
@@ -6350,7 +6348,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
       <c r="B67" s="58"/>
       <c r="C67" s="58"/>
@@ -6364,21 +6362,21 @@
       <c r="K67" s="58"/>
       <c r="L67" s="58"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="180"/>
-      <c r="O67" s="180"/>
-      <c r="P67" s="180"/>
-      <c r="Q67" s="180"/>
-      <c r="R67" s="180"/>
-      <c r="S67" s="180"/>
-      <c r="T67" s="180"/>
-      <c r="U67" s="180"/>
-      <c r="V67" s="180"/>
-      <c r="W67" s="180"/>
-      <c r="X67" s="180"/>
-      <c r="Y67" s="180"/>
-      <c r="Z67" s="180"/>
-      <c r="AA67" s="180"/>
-      <c r="AB67" s="180"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
+      <c r="R67" s="179"/>
+      <c r="S67" s="179"/>
+      <c r="T67" s="179"/>
+      <c r="U67" s="179"/>
+      <c r="V67" s="179"/>
+      <c r="W67" s="179"/>
+      <c r="X67" s="179"/>
+      <c r="Y67" s="179"/>
+      <c r="Z67" s="179"/>
+      <c r="AA67" s="179"/>
+      <c r="AB67" s="179"/>
       <c r="AC67" s="67"/>
       <c r="AD67" s="30"/>
       <c r="AE67" s="30"/>
@@ -6396,70 +6394,72 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="122" t="s">
+      <c r="B68" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="123"/>
+      <c r="C68" s="125"/>
       <c r="D68" s="52" t="s">
         <v>66</v>
       </c>
       <c r="E68" s="33"/>
-      <c r="F68" s="122" t="s">
+      <c r="F68" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="G68" s="123"/>
+      <c r="G68" s="125"/>
       <c r="H68" s="52" t="s">
         <v>66</v>
       </c>
       <c r="I68" s="29"/>
-      <c r="J68" s="122" t="s">
+      <c r="J68" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="K68" s="123"/>
+      <c r="K68" s="125"/>
       <c r="L68" s="52"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="131" t="s">
+      <c r="N68" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="O68" s="132"/>
+      <c r="O68" s="134"/>
       <c r="P68" s="59"/>
       <c r="Q68" s="29"/>
-      <c r="R68" s="131" t="s">
+      <c r="R68" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="S68" s="132"/>
+      <c r="S68" s="134"/>
       <c r="T68" s="59"/>
       <c r="U68" s="33"/>
-      <c r="V68" s="131" t="s">
+      <c r="V68" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="W68" s="132"/>
+      <c r="W68" s="134"/>
       <c r="X68" s="59"/>
       <c r="Y68" s="29"/>
-      <c r="Z68" s="131" t="s">
+      <c r="Z68" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="AA68" s="132"/>
+      <c r="AA68" s="134"/>
       <c r="AB68" s="59"/>
       <c r="AC68" s="29"/>
-      <c r="AD68" s="131" t="s">
+      <c r="AD68" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="AE68" s="132"/>
+      <c r="AE68" s="134"/>
       <c r="AF68" s="59"/>
       <c r="AG68" s="33"/>
-      <c r="AH68" s="139" t="s">
+      <c r="AH68" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="AI68" s="140"/>
-      <c r="AJ68" s="68"/>
+      <c r="AI68" s="142"/>
+      <c r="AJ68" s="68" t="s">
+        <v>136</v>
+      </c>
       <c r="AK68" s="29"/>
-      <c r="AL68" s="139" t="s">
+      <c r="AL68" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="AM68" s="140"/>
+      <c r="AM68" s="142"/>
       <c r="AN68" s="68"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="24" t="s">
@@ -6468,65 +6468,67 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="117" t="s">
+      <c r="B69" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="118"/>
+      <c r="C69" s="120"/>
       <c r="D69" s="54"/>
       <c r="E69" s="29"/>
-      <c r="F69" s="117" t="s">
+      <c r="F69" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="G69" s="118"/>
+      <c r="G69" s="120"/>
       <c r="H69" s="54"/>
       <c r="I69" s="29"/>
-      <c r="J69" s="124" t="s">
+      <c r="J69" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="K69" s="125"/>
-      <c r="L69" s="126"/>
+      <c r="K69" s="127"/>
+      <c r="L69" s="128"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="119" t="s">
+      <c r="N69" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="O69" s="120"/>
-      <c r="P69" s="121"/>
+      <c r="O69" s="122"/>
+      <c r="P69" s="123"/>
       <c r="Q69" s="29"/>
-      <c r="R69" s="119" t="s">
+      <c r="R69" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="S69" s="120"/>
-      <c r="T69" s="121"/>
+      <c r="S69" s="122"/>
+      <c r="T69" s="123"/>
       <c r="U69" s="29"/>
-      <c r="V69" s="119" t="s">
+      <c r="V69" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="W69" s="120"/>
-      <c r="X69" s="121"/>
+      <c r="W69" s="122"/>
+      <c r="X69" s="123"/>
       <c r="Y69" s="29"/>
-      <c r="Z69" s="119" t="s">
+      <c r="Z69" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="AA69" s="120"/>
-      <c r="AB69" s="121"/>
+      <c r="AA69" s="122"/>
+      <c r="AB69" s="123"/>
       <c r="AC69" s="29"/>
-      <c r="AD69" s="119" t="s">
+      <c r="AD69" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="AE69" s="120"/>
-      <c r="AF69" s="121"/>
+      <c r="AE69" s="122"/>
+      <c r="AF69" s="123"/>
       <c r="AG69" s="29"/>
-      <c r="AH69" s="95"/>
-      <c r="AI69" s="96"/>
-      <c r="AJ69" s="97"/>
+      <c r="AH69" s="121" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI69" s="122"/>
+      <c r="AJ69" s="123"/>
       <c r="AK69" s="29"/>
-      <c r="AL69" s="205" t="s">
+      <c r="AL69" s="209" t="s">
         <v>117</v>
       </c>
-      <c r="AM69" s="206"/>
-      <c r="AN69" s="207"/>
+      <c r="AM69" s="210"/>
+      <c r="AN69" s="211"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="24" t="s">
         <v>33</v>
@@ -6534,71 +6536,71 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
-      <c r="B70" s="110" t="s">
+      <c r="B70" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="111"/>
+      <c r="C70" s="113"/>
       <c r="D70" s="55" t="s">
         <v>32</v>
       </c>
       <c r="E70" s="28"/>
-      <c r="F70" s="110" t="s">
+      <c r="F70" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="111"/>
+      <c r="G70" s="113"/>
       <c r="H70" s="55" t="s">
         <v>32</v>
       </c>
       <c r="I70" s="29"/>
-      <c r="J70" s="117" t="s">
+      <c r="J70" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="K70" s="118"/>
-      <c r="L70" s="127"/>
+      <c r="K70" s="120"/>
+      <c r="L70" s="129"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="88" t="s">
+      <c r="N70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="O70" s="89"/>
-      <c r="P70" s="90"/>
+      <c r="O70" s="91"/>
+      <c r="P70" s="92"/>
       <c r="Q70" s="29"/>
-      <c r="R70" s="88" t="s">
+      <c r="R70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="S70" s="89"/>
-      <c r="T70" s="90"/>
+      <c r="S70" s="91"/>
+      <c r="T70" s="92"/>
       <c r="U70" s="28"/>
-      <c r="V70" s="88" t="s">
+      <c r="V70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="W70" s="89"/>
-      <c r="X70" s="90"/>
+      <c r="W70" s="91"/>
+      <c r="X70" s="92"/>
       <c r="Y70" s="29"/>
-      <c r="Z70" s="88" t="s">
+      <c r="Z70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="AA70" s="89"/>
-      <c r="AB70" s="90"/>
+      <c r="AA70" s="91"/>
+      <c r="AB70" s="92"/>
       <c r="AC70" s="29"/>
-      <c r="AD70" s="88" t="s">
+      <c r="AD70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="AE70" s="89"/>
-      <c r="AF70" s="90"/>
+      <c r="AE70" s="91"/>
+      <c r="AF70" s="92"/>
       <c r="AG70" s="28"/>
-      <c r="AH70" s="88" t="s">
+      <c r="AH70" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="AI70" s="89"/>
-      <c r="AJ70" s="90"/>
+      <c r="AI70" s="91"/>
+      <c r="AJ70" s="92"/>
       <c r="AK70" s="29"/>
-      <c r="AL70" s="208" t="s">
+      <c r="AL70" s="212" t="s">
         <v>118</v>
       </c>
-      <c r="AM70" s="209"/>
-      <c r="AN70" s="210"/>
+      <c r="AM70" s="213"/>
+      <c r="AN70" s="214"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="24" t="s">
         <v>34</v>
@@ -6606,71 +6608,71 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="112" t="s">
+      <c r="B71" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="113"/>
+      <c r="C71" s="115"/>
       <c r="D71" s="56" t="s">
         <v>33</v>
       </c>
       <c r="E71" s="29"/>
-      <c r="F71" s="112" t="s">
+      <c r="F71" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="113"/>
+      <c r="G71" s="115"/>
       <c r="H71" s="56" t="s">
         <v>33</v>
       </c>
       <c r="I71" s="29"/>
-      <c r="J71" s="114" t="s">
+      <c r="J71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="K71" s="115"/>
-      <c r="L71" s="116"/>
+      <c r="K71" s="117"/>
+      <c r="L71" s="118"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="114" t="s">
+      <c r="N71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="O71" s="115"/>
-      <c r="P71" s="116"/>
+      <c r="O71" s="117"/>
+      <c r="P71" s="118"/>
       <c r="Q71" s="29"/>
-      <c r="R71" s="114" t="s">
+      <c r="R71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="S71" s="115"/>
-      <c r="T71" s="116"/>
+      <c r="S71" s="117"/>
+      <c r="T71" s="118"/>
       <c r="U71" s="29"/>
-      <c r="V71" s="114" t="s">
+      <c r="V71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="W71" s="115"/>
-      <c r="X71" s="116"/>
+      <c r="W71" s="117"/>
+      <c r="X71" s="118"/>
       <c r="Y71" s="29"/>
-      <c r="Z71" s="114" t="s">
+      <c r="Z71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="AA71" s="115"/>
-      <c r="AB71" s="116"/>
+      <c r="AA71" s="117"/>
+      <c r="AB71" s="118"/>
       <c r="AC71" s="29"/>
-      <c r="AD71" s="114" t="s">
+      <c r="AD71" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="AE71" s="115"/>
-      <c r="AF71" s="116"/>
+      <c r="AE71" s="117"/>
+      <c r="AF71" s="118"/>
       <c r="AG71" s="29"/>
-      <c r="AH71" s="75" t="s">
+      <c r="AH71" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AI71" s="76"/>
-      <c r="AJ71" s="77"/>
+      <c r="AI71" s="78"/>
+      <c r="AJ71" s="79"/>
       <c r="AK71" s="29"/>
-      <c r="AL71" s="75" t="s">
+      <c r="AL71" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="AM71" s="76"/>
-      <c r="AN71" s="77"/>
+      <c r="AM71" s="78"/>
+      <c r="AN71" s="79"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="24" t="s">
         <v>35</v>
@@ -6678,76 +6680,74 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12"/>
-      <c r="B72" s="101" t="s">
+      <c r="B72" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="102"/>
+      <c r="C72" s="104"/>
       <c r="D72" s="56" t="s">
         <v>34</v>
       </c>
       <c r="E72" s="33"/>
-      <c r="F72" s="103" t="s">
+      <c r="F72" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="104"/>
+      <c r="G72" s="106"/>
       <c r="H72" s="56" t="s">
         <v>34</v>
       </c>
       <c r="I72" s="29"/>
-      <c r="J72" s="105"/>
-      <c r="K72" s="106"/>
-      <c r="L72" s="107"/>
+      <c r="J72" s="107"/>
+      <c r="K72" s="108"/>
+      <c r="L72" s="109"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="105"/>
-      <c r="O72" s="106"/>
-      <c r="P72" s="107"/>
+      <c r="N72" s="107"/>
+      <c r="O72" s="108"/>
+      <c r="P72" s="109"/>
       <c r="Q72" s="29"/>
-      <c r="R72" s="105"/>
-      <c r="S72" s="106"/>
-      <c r="T72" s="107"/>
+      <c r="R72" s="107"/>
+      <c r="S72" s="108"/>
+      <c r="T72" s="109"/>
       <c r="U72" s="33"/>
-      <c r="V72" s="105"/>
-      <c r="W72" s="106"/>
-      <c r="X72" s="107"/>
+      <c r="V72" s="107"/>
+      <c r="W72" s="108"/>
+      <c r="X72" s="109"/>
       <c r="Y72" s="29"/>
-      <c r="Z72" s="105"/>
-      <c r="AA72" s="106"/>
-      <c r="AB72" s="107"/>
+      <c r="Z72" s="107"/>
+      <c r="AA72" s="108"/>
+      <c r="AB72" s="109"/>
       <c r="AC72" s="29"/>
-      <c r="AD72" s="105"/>
-      <c r="AE72" s="106"/>
-      <c r="AF72" s="107"/>
+      <c r="AD72" s="107"/>
+      <c r="AE72" s="108"/>
+      <c r="AF72" s="109"/>
       <c r="AG72" s="33"/>
-      <c r="AH72" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI72" s="79"/>
-      <c r="AJ72" s="80"/>
+      <c r="AH72" s="80"/>
+      <c r="AI72" s="81"/>
+      <c r="AJ72" s="82"/>
       <c r="AK72" s="29"/>
-      <c r="AL72" s="78"/>
-      <c r="AM72" s="79"/>
-      <c r="AN72" s="80"/>
+      <c r="AL72" s="80"/>
+      <c r="AM72" s="81"/>
+      <c r="AN72" s="82"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="25"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
-      <c r="B73" s="101" t="s">
+      <c r="B73" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="C73" s="102"/>
+      <c r="C73" s="104"/>
       <c r="D73" s="56" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="28"/>
-      <c r="F73" s="101" t="s">
+      <c r="F73" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="G73" s="102"/>
+      <c r="G73" s="104"/>
       <c r="H73" s="56" t="s">
         <v>35</v>
       </c>
@@ -6788,131 +6788,131 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
-      <c r="B74" s="101" t="s">
+      <c r="B74" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="C74" s="102"/>
+      <c r="C74" s="104"/>
       <c r="D74" s="56" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="29"/>
-      <c r="F74" s="101" t="s">
+      <c r="F74" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="G74" s="102"/>
+      <c r="G74" s="104"/>
       <c r="H74" s="56" t="s">
         <v>35</v>
       </c>
       <c r="I74" s="29"/>
-      <c r="J74" s="122" t="s">
+      <c r="J74" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="K74" s="123"/>
+      <c r="K74" s="125"/>
       <c r="L74" s="52"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="91" t="s">
+      <c r="N74" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="O74" s="92"/>
+      <c r="O74" s="94"/>
       <c r="P74" s="31"/>
       <c r="Q74" s="29"/>
-      <c r="R74" s="91" t="s">
+      <c r="R74" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="S74" s="92"/>
+      <c r="S74" s="94"/>
       <c r="T74" s="31"/>
       <c r="U74" s="29"/>
-      <c r="V74" s="91" t="s">
+      <c r="V74" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="W74" s="92"/>
+      <c r="W74" s="94"/>
       <c r="X74" s="31"/>
       <c r="Y74" s="29"/>
-      <c r="Z74" s="91" t="s">
+      <c r="Z74" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="AA74" s="92"/>
+      <c r="AA74" s="94"/>
       <c r="AB74" s="31"/>
       <c r="AC74" s="29"/>
-      <c r="AD74" s="91" t="s">
+      <c r="AD74" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="AE74" s="92"/>
+      <c r="AE74" s="94"/>
       <c r="AF74" s="31"/>
       <c r="AG74" s="29"/>
-      <c r="AH74" s="91" t="s">
+      <c r="AH74" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="AI74" s="92"/>
+      <c r="AI74" s="94"/>
       <c r="AJ74" s="31"/>
       <c r="AK74" s="29"/>
-      <c r="AL74" s="91" t="s">
+      <c r="AL74" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="AM74" s="92"/>
+      <c r="AM74" s="94"/>
       <c r="AN74" s="31"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="25"/>
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
-      <c r="B75" s="108"/>
-      <c r="C75" s="109"/>
+      <c r="B75" s="110"/>
+      <c r="C75" s="111"/>
       <c r="D75" s="57"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="108"/>
-      <c r="G75" s="109"/>
+      <c r="F75" s="110"/>
+      <c r="G75" s="111"/>
       <c r="H75" s="57"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="124"/>
-      <c r="K75" s="125"/>
-      <c r="L75" s="126"/>
+      <c r="J75" s="126"/>
+      <c r="K75" s="127"/>
+      <c r="L75" s="128"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="95"/>
-      <c r="O75" s="96"/>
-      <c r="P75" s="97"/>
+      <c r="N75" s="97"/>
+      <c r="O75" s="98"/>
+      <c r="P75" s="99"/>
       <c r="Q75" s="29"/>
-      <c r="R75" s="95"/>
-      <c r="S75" s="96"/>
-      <c r="T75" s="97"/>
+      <c r="R75" s="97"/>
+      <c r="S75" s="98"/>
+      <c r="T75" s="99"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="95"/>
-      <c r="W75" s="96"/>
-      <c r="X75" s="97"/>
+      <c r="V75" s="97"/>
+      <c r="W75" s="98"/>
+      <c r="X75" s="99"/>
       <c r="Y75" s="29"/>
-      <c r="Z75" s="95" t="s">
+      <c r="Z75" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="AA75" s="96"/>
-      <c r="AB75" s="97"/>
+      <c r="AA75" s="98"/>
+      <c r="AB75" s="99"/>
       <c r="AC75" s="29"/>
-      <c r="AD75" s="95" t="s">
+      <c r="AD75" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="AE75" s="96"/>
-      <c r="AF75" s="97"/>
+      <c r="AE75" s="98"/>
+      <c r="AF75" s="99"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="95" t="s">
+      <c r="AH75" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="AI75" s="96"/>
-      <c r="AJ75" s="97"/>
+      <c r="AI75" s="98"/>
+      <c r="AJ75" s="99"/>
       <c r="AK75" s="29"/>
-      <c r="AL75" s="95" t="s">
+      <c r="AL75" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="AM75" s="96"/>
-      <c r="AN75" s="97"/>
+      <c r="AM75" s="98"/>
+      <c r="AN75" s="99"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="26"/>
       <c r="AQ75" s="23"/>
       <c r="AR75" s="21"/>
     </row>
-    <row r="76" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="12"/>
       <c r="B76" s="58"/>
       <c r="C76" s="58"/>
@@ -6922,59 +6922,59 @@
       <c r="G76" s="58"/>
       <c r="H76" s="58"/>
       <c r="I76" s="28"/>
-      <c r="J76" s="117" t="s">
+      <c r="J76" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="K76" s="118"/>
-      <c r="L76" s="127"/>
+      <c r="K76" s="120"/>
+      <c r="L76" s="129"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="98" t="s">
+      <c r="N76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="O76" s="99"/>
-      <c r="P76" s="100"/>
+      <c r="O76" s="101"/>
+      <c r="P76" s="102"/>
       <c r="Q76" s="29"/>
-      <c r="R76" s="98" t="s">
+      <c r="R76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="S76" s="99"/>
-      <c r="T76" s="100"/>
+      <c r="S76" s="101"/>
+      <c r="T76" s="102"/>
       <c r="U76" s="28"/>
-      <c r="V76" s="98" t="s">
+      <c r="V76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="W76" s="99"/>
-      <c r="X76" s="100"/>
+      <c r="W76" s="101"/>
+      <c r="X76" s="102"/>
       <c r="Y76" s="29"/>
-      <c r="Z76" s="98" t="s">
+      <c r="Z76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AA76" s="99"/>
-      <c r="AB76" s="100"/>
+      <c r="AA76" s="101"/>
+      <c r="AB76" s="102"/>
       <c r="AC76" s="29"/>
-      <c r="AD76" s="98" t="s">
+      <c r="AD76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AE76" s="99"/>
-      <c r="AF76" s="100"/>
+      <c r="AE76" s="101"/>
+      <c r="AF76" s="102"/>
       <c r="AG76" s="28"/>
-      <c r="AH76" s="98" t="s">
+      <c r="AH76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AI76" s="99"/>
-      <c r="AJ76" s="100"/>
+      <c r="AI76" s="101"/>
+      <c r="AJ76" s="102"/>
       <c r="AK76" s="29"/>
-      <c r="AL76" s="98" t="s">
+      <c r="AL76" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AM76" s="99"/>
-      <c r="AN76" s="100"/>
+      <c r="AM76" s="101"/>
+      <c r="AN76" s="102"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="26"/>
       <c r="AQ76" s="23"/>
       <c r="AR76" s="21"/>
     </row>
-    <row r="77" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="16"/>
       <c r="B77" s="58"/>
       <c r="C77" s="58"/>
@@ -6984,59 +6984,59 @@
       <c r="G77" s="58"/>
       <c r="H77" s="58"/>
       <c r="I77" s="28"/>
-      <c r="J77" s="162" t="s">
+      <c r="J77" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="K77" s="163"/>
-      <c r="L77" s="164"/>
+      <c r="K77" s="162"/>
+      <c r="L77" s="163"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="75" t="s">
+      <c r="N77" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="O77" s="76"/>
-      <c r="P77" s="77"/>
+      <c r="O77" s="78"/>
+      <c r="P77" s="79"/>
       <c r="Q77" s="29"/>
-      <c r="R77" s="75" t="s">
+      <c r="R77" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="S77" s="76"/>
-      <c r="T77" s="77"/>
+      <c r="S77" s="78"/>
+      <c r="T77" s="79"/>
       <c r="U77" s="28"/>
-      <c r="V77" s="214" t="s">
+      <c r="V77" s="220" t="s">
         <v>18</v>
       </c>
-      <c r="W77" s="215"/>
-      <c r="X77" s="216"/>
+      <c r="W77" s="221"/>
+      <c r="X77" s="222"/>
       <c r="Y77" s="29"/>
-      <c r="Z77" s="75" t="s">
+      <c r="Z77" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AA77" s="76"/>
-      <c r="AB77" s="77"/>
+      <c r="AA77" s="78"/>
+      <c r="AB77" s="79"/>
       <c r="AC77" s="29"/>
-      <c r="AD77" s="75" t="s">
+      <c r="AD77" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="77"/>
+      <c r="AE77" s="78"/>
+      <c r="AF77" s="79"/>
       <c r="AG77" s="28"/>
-      <c r="AH77" s="75" t="s">
+      <c r="AH77" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AI77" s="76"/>
-      <c r="AJ77" s="77"/>
+      <c r="AI77" s="78"/>
+      <c r="AJ77" s="79"/>
       <c r="AK77" s="29"/>
-      <c r="AL77" s="75" t="s">
+      <c r="AL77" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AM77" s="76"/>
-      <c r="AN77" s="77"/>
+      <c r="AM77" s="78"/>
+      <c r="AN77" s="79"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="26"/>
       <c r="AQ77" s="23"/>
       <c r="AR77" s="21"/>
     </row>
-    <row r="78" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A78" s="16"/>
       <c r="B78" s="58"/>
       <c r="C78" s="58"/>
@@ -7046,47 +7046,47 @@
       <c r="G78" s="58"/>
       <c r="H78" s="58"/>
       <c r="I78" s="29"/>
-      <c r="J78" s="105"/>
-      <c r="K78" s="106"/>
-      <c r="L78" s="107"/>
+      <c r="J78" s="107"/>
+      <c r="K78" s="108"/>
+      <c r="L78" s="109"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="78" t="s">
+      <c r="N78" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="O78" s="79"/>
-      <c r="P78" s="80"/>
+      <c r="O78" s="81"/>
+      <c r="P78" s="82"/>
       <c r="Q78" s="28"/>
-      <c r="R78" s="78"/>
-      <c r="S78" s="79"/>
-      <c r="T78" s="80"/>
+      <c r="R78" s="80"/>
+      <c r="S78" s="81"/>
+      <c r="T78" s="82"/>
       <c r="U78" s="29"/>
-      <c r="V78" s="85" t="s">
+      <c r="V78" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="W78" s="86"/>
-      <c r="X78" s="87"/>
+      <c r="W78" s="88"/>
+      <c r="X78" s="89"/>
       <c r="Y78" s="28"/>
-      <c r="Z78" s="78"/>
-      <c r="AA78" s="79"/>
-      <c r="AB78" s="80"/>
+      <c r="Z78" s="80"/>
+      <c r="AA78" s="81"/>
+      <c r="AB78" s="82"/>
       <c r="AC78" s="28"/>
-      <c r="AD78" s="78"/>
-      <c r="AE78" s="79"/>
-      <c r="AF78" s="80"/>
+      <c r="AD78" s="80"/>
+      <c r="AE78" s="81"/>
+      <c r="AF78" s="82"/>
       <c r="AG78" s="29"/>
-      <c r="AH78" s="78"/>
-      <c r="AI78" s="79"/>
-      <c r="AJ78" s="80"/>
+      <c r="AH78" s="80"/>
+      <c r="AI78" s="81"/>
+      <c r="AJ78" s="82"/>
       <c r="AK78" s="29"/>
-      <c r="AL78" s="78"/>
-      <c r="AM78" s="79"/>
-      <c r="AN78" s="80"/>
+      <c r="AL78" s="80"/>
+      <c r="AM78" s="81"/>
+      <c r="AN78" s="82"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="26"/>
       <c r="AQ78" s="23"/>
       <c r="AR78" s="21"/>
     </row>
-    <row r="79" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="53"/>
       <c r="C79" s="53"/>
@@ -7132,279 +7132,289 @@
       <c r="AQ79" s="23"/>
       <c r="AR79" s="21"/>
     </row>
-    <row r="80" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
-      <c r="B80" s="122"/>
-      <c r="C80" s="123"/>
+      <c r="B80" s="124"/>
+      <c r="C80" s="125"/>
       <c r="D80" s="52"/>
       <c r="E80" s="29"/>
-      <c r="F80" s="144" t="s">
+      <c r="F80" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="G80" s="145"/>
+      <c r="G80" s="144"/>
       <c r="H80" s="62"/>
       <c r="I80" s="29"/>
-      <c r="J80" s="122" t="s">
+      <c r="J80" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="K80" s="123"/>
+      <c r="K80" s="125"/>
       <c r="L80" s="52"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="131" t="s">
+      <c r="N80" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="O80" s="132"/>
+      <c r="O80" s="134"/>
       <c r="P80" s="59"/>
       <c r="Q80" s="29"/>
-      <c r="R80" s="91"/>
-      <c r="S80" s="92"/>
+      <c r="R80" s="93"/>
+      <c r="S80" s="94"/>
       <c r="T80" s="31"/>
       <c r="U80" s="29"/>
-      <c r="V80" s="158" t="s">
+      <c r="V80" s="157" t="s">
         <v>69</v>
       </c>
-      <c r="W80" s="159"/>
+      <c r="W80" s="158"/>
       <c r="X80" s="69"/>
       <c r="Y80" s="29"/>
-      <c r="Z80" s="91" t="s">
+      <c r="Z80" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="AA80" s="92"/>
+      <c r="AA80" s="94"/>
       <c r="AB80" s="31"/>
       <c r="AC80" s="29"/>
-      <c r="AD80" s="91" t="s">
+      <c r="AD80" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="AE80" s="92"/>
+      <c r="AE80" s="94"/>
       <c r="AF80" s="31"/>
       <c r="AG80" s="29"/>
-      <c r="AH80" s="91"/>
-      <c r="AI80" s="92"/>
-      <c r="AJ80" s="31"/>
+      <c r="AH80" s="141" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI80" s="142"/>
+      <c r="AJ80" s="68" t="s">
+        <v>46</v>
+      </c>
       <c r="AK80" s="29"/>
-      <c r="AL80" s="91"/>
-      <c r="AM80" s="92"/>
+      <c r="AL80" s="93"/>
+      <c r="AM80" s="94"/>
       <c r="AN80" s="31"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="26"/>
       <c r="AQ80" s="23"/>
       <c r="AR80" s="21"/>
     </row>
-    <row r="81" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
-      <c r="B81" s="124"/>
-      <c r="C81" s="125"/>
-      <c r="D81" s="126"/>
+      <c r="B81" s="126"/>
+      <c r="C81" s="127"/>
+      <c r="D81" s="128"/>
       <c r="E81" s="29"/>
-      <c r="F81" s="124" t="s">
+      <c r="F81" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="G81" s="125"/>
-      <c r="H81" s="126"/>
+      <c r="G81" s="127"/>
+      <c r="H81" s="128"/>
       <c r="I81" s="29"/>
-      <c r="J81" s="124" t="s">
+      <c r="J81" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="K81" s="125"/>
-      <c r="L81" s="126"/>
+      <c r="K81" s="127"/>
+      <c r="L81" s="128"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="119"/>
-      <c r="O81" s="120"/>
-      <c r="P81" s="121"/>
+      <c r="N81" s="121"/>
+      <c r="O81" s="122"/>
+      <c r="P81" s="123"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="95"/>
-      <c r="S81" s="96"/>
-      <c r="T81" s="97"/>
+      <c r="R81" s="97"/>
+      <c r="S81" s="98"/>
+      <c r="T81" s="99"/>
       <c r="U81" s="29"/>
-      <c r="V81" s="205"/>
-      <c r="W81" s="206"/>
-      <c r="X81" s="207"/>
+      <c r="V81" s="209"/>
+      <c r="W81" s="210"/>
+      <c r="X81" s="211"/>
       <c r="Y81" s="29"/>
-      <c r="Z81" s="95"/>
-      <c r="AA81" s="96"/>
-      <c r="AB81" s="97"/>
+      <c r="Z81" s="97"/>
+      <c r="AA81" s="98"/>
+      <c r="AB81" s="99"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="95"/>
-      <c r="AE81" s="96"/>
-      <c r="AF81" s="97"/>
+      <c r="AD81" s="97"/>
+      <c r="AE81" s="98"/>
+      <c r="AF81" s="99"/>
       <c r="AG81" s="29"/>
-      <c r="AH81" s="95"/>
-      <c r="AI81" s="96"/>
-      <c r="AJ81" s="97"/>
+      <c r="AH81" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI81" s="98"/>
+      <c r="AJ81" s="99"/>
       <c r="AK81" s="29"/>
-      <c r="AL81" s="95"/>
-      <c r="AM81" s="96"/>
-      <c r="AN81" s="97"/>
+      <c r="AL81" s="97"/>
+      <c r="AM81" s="98"/>
+      <c r="AN81" s="99"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="26"/>
       <c r="AQ81" s="23"/>
       <c r="AR81" s="21"/>
     </row>
-    <row r="82" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
-      <c r="B82" s="117"/>
-      <c r="C82" s="118"/>
-      <c r="D82" s="127"/>
+      <c r="B82" s="119"/>
+      <c r="C82" s="120"/>
+      <c r="D82" s="129"/>
       <c r="E82" s="29"/>
-      <c r="F82" s="117" t="s">
+      <c r="F82" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="G82" s="118"/>
-      <c r="H82" s="127"/>
+      <c r="G82" s="120"/>
+      <c r="H82" s="129"/>
       <c r="I82" s="29"/>
-      <c r="J82" s="117" t="s">
+      <c r="J82" s="119" t="s">
         <v>71</v>
       </c>
-      <c r="K82" s="118"/>
-      <c r="L82" s="127"/>
+      <c r="K82" s="120"/>
+      <c r="L82" s="129"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="88" t="s">
+      <c r="N82" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="O82" s="89"/>
-      <c r="P82" s="90"/>
+      <c r="O82" s="91"/>
+      <c r="P82" s="92"/>
       <c r="Q82" s="28"/>
-      <c r="R82" s="98"/>
-      <c r="S82" s="99"/>
-      <c r="T82" s="100"/>
+      <c r="R82" s="100"/>
+      <c r="S82" s="101"/>
+      <c r="T82" s="102"/>
       <c r="U82" s="29"/>
-      <c r="V82" s="81" t="s">
+      <c r="V82" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="W82" s="82"/>
-      <c r="X82" s="217"/>
+      <c r="W82" s="84"/>
+      <c r="X82" s="223"/>
       <c r="Y82" s="29"/>
-      <c r="Z82" s="98" t="s">
+      <c r="Z82" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AA82" s="99"/>
-      <c r="AB82" s="100"/>
+      <c r="AA82" s="101"/>
+      <c r="AB82" s="102"/>
       <c r="AC82" s="28"/>
-      <c r="AD82" s="98" t="s">
+      <c r="AD82" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AE82" s="99"/>
-      <c r="AF82" s="100"/>
+      <c r="AE82" s="101"/>
+      <c r="AF82" s="102"/>
       <c r="AG82" s="29"/>
-      <c r="AH82" s="98"/>
-      <c r="AI82" s="99"/>
-      <c r="AJ82" s="100"/>
+      <c r="AH82" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI82" s="91"/>
+      <c r="AJ82" s="92"/>
       <c r="AK82" s="29"/>
-      <c r="AL82" s="98"/>
-      <c r="AM82" s="99"/>
-      <c r="AN82" s="100"/>
+      <c r="AL82" s="100"/>
+      <c r="AM82" s="101"/>
+      <c r="AN82" s="102"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="26"/>
       <c r="AQ82" s="23"/>
       <c r="AR82" s="21"/>
     </row>
-    <row r="83" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
-      <c r="B83" s="114"/>
-      <c r="C83" s="115"/>
-      <c r="D83" s="116"/>
+      <c r="B83" s="116"/>
+      <c r="C83" s="117"/>
+      <c r="D83" s="118"/>
       <c r="E83" s="29"/>
-      <c r="F83" s="162" t="s">
+      <c r="F83" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="G83" s="163"/>
-      <c r="H83" s="164"/>
+      <c r="G83" s="162"/>
+      <c r="H83" s="163"/>
       <c r="I83" s="29"/>
-      <c r="J83" s="114" t="s">
+      <c r="J83" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="K83" s="115"/>
-      <c r="L83" s="116"/>
+      <c r="K83" s="117"/>
+      <c r="L83" s="118"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="75" t="s">
+      <c r="N83" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="O83" s="76"/>
-      <c r="P83" s="77"/>
+      <c r="O83" s="78"/>
+      <c r="P83" s="79"/>
       <c r="Q83" s="28"/>
-      <c r="R83" s="75"/>
-      <c r="S83" s="76"/>
-      <c r="T83" s="77"/>
+      <c r="R83" s="77"/>
+      <c r="S83" s="78"/>
+      <c r="T83" s="79"/>
       <c r="U83" s="29"/>
-      <c r="V83" s="211" t="s">
+      <c r="V83" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="W83" s="212"/>
-      <c r="X83" s="213"/>
+      <c r="W83" s="218"/>
+      <c r="X83" s="219"/>
       <c r="Y83" s="29"/>
-      <c r="Z83" s="214" t="s">
+      <c r="Z83" s="220" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="215"/>
-      <c r="AB83" s="216"/>
+      <c r="AA83" s="221"/>
+      <c r="AB83" s="222"/>
       <c r="AC83" s="29"/>
-      <c r="AD83" s="75" t="s">
+      <c r="AD83" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="AE83" s="76"/>
-      <c r="AF83" s="77"/>
+      <c r="AE83" s="78"/>
+      <c r="AF83" s="79"/>
       <c r="AG83" s="29"/>
-      <c r="AH83" s="75"/>
-      <c r="AI83" s="76"/>
-      <c r="AJ83" s="77"/>
+      <c r="AH83" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI83" s="78"/>
+      <c r="AJ83" s="79"/>
       <c r="AK83" s="29"/>
-      <c r="AL83" s="75"/>
-      <c r="AM83" s="76"/>
-      <c r="AN83" s="77"/>
+      <c r="AL83" s="77"/>
+      <c r="AM83" s="78"/>
+      <c r="AN83" s="79"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="26"/>
       <c r="AQ83" s="23"/>
       <c r="AR83" s="21"/>
     </row>
-    <row r="84" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12"/>
-      <c r="B84" s="105"/>
-      <c r="C84" s="106"/>
-      <c r="D84" s="107"/>
+      <c r="B84" s="107"/>
+      <c r="C84" s="108"/>
+      <c r="D84" s="109"/>
       <c r="E84" s="28"/>
-      <c r="F84" s="105"/>
-      <c r="G84" s="106"/>
-      <c r="H84" s="107"/>
+      <c r="F84" s="107"/>
+      <c r="G84" s="108"/>
+      <c r="H84" s="109"/>
       <c r="I84" s="29"/>
-      <c r="J84" s="105"/>
-      <c r="K84" s="106"/>
-      <c r="L84" s="107"/>
+      <c r="J84" s="107"/>
+      <c r="K84" s="108"/>
+      <c r="L84" s="109"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="105"/>
-      <c r="O84" s="106"/>
-      <c r="P84" s="107"/>
+      <c r="N84" s="107"/>
+      <c r="O84" s="108"/>
+      <c r="P84" s="109"/>
       <c r="Q84" s="28"/>
-      <c r="R84" s="78"/>
-      <c r="S84" s="79"/>
-      <c r="T84" s="80"/>
+      <c r="R84" s="80"/>
+      <c r="S84" s="81"/>
+      <c r="T84" s="82"/>
       <c r="U84" s="28"/>
-      <c r="V84" s="85"/>
-      <c r="W84" s="86"/>
-      <c r="X84" s="87"/>
+      <c r="V84" s="87"/>
+      <c r="W84" s="88"/>
+      <c r="X84" s="89"/>
       <c r="Y84" s="28"/>
-      <c r="Z84" s="85" t="s">
+      <c r="Z84" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="AA84" s="86"/>
-      <c r="AB84" s="87"/>
+      <c r="AA84" s="88"/>
+      <c r="AB84" s="89"/>
       <c r="AC84" s="29"/>
-      <c r="AD84" s="78"/>
-      <c r="AE84" s="79"/>
-      <c r="AF84" s="80"/>
+      <c r="AD84" s="80"/>
+      <c r="AE84" s="81"/>
+      <c r="AF84" s="82"/>
       <c r="AG84" s="28"/>
-      <c r="AH84" s="78"/>
-      <c r="AI84" s="79"/>
-      <c r="AJ84" s="80"/>
+      <c r="AH84" s="80"/>
+      <c r="AI84" s="81"/>
+      <c r="AJ84" s="82"/>
       <c r="AK84" s="29"/>
-      <c r="AL84" s="78"/>
-      <c r="AM84" s="79"/>
-      <c r="AN84" s="80"/>
+      <c r="AL84" s="80"/>
+      <c r="AM84" s="81"/>
+      <c r="AN84" s="82"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="26"/>
       <c r="AQ84" s="23"/>
       <c r="AR84" s="21"/>
     </row>
-    <row r="85" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="53"/>
       <c r="C85" s="53"/>
@@ -7450,257 +7460,259 @@
       <c r="AQ85" s="23"/>
       <c r="AR85" s="21"/>
     </row>
-    <row r="86" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
-      <c r="B86" s="122"/>
-      <c r="C86" s="123"/>
+      <c r="B86" s="124"/>
+      <c r="C86" s="125"/>
       <c r="D86" s="52"/>
       <c r="E86" s="29"/>
-      <c r="F86" s="122"/>
-      <c r="G86" s="123"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="125"/>
       <c r="H86" s="52"/>
       <c r="I86" s="33"/>
-      <c r="J86" s="122"/>
-      <c r="K86" s="123"/>
+      <c r="J86" s="124"/>
+      <c r="K86" s="125"/>
       <c r="L86" s="52"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="139" t="s">
+      <c r="N86" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="O86" s="140"/>
+      <c r="O86" s="142"/>
       <c r="P86" s="68"/>
       <c r="Q86" s="33"/>
-      <c r="R86" s="139" t="s">
+      <c r="R86" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="S86" s="140"/>
+      <c r="S86" s="142"/>
       <c r="T86" s="68"/>
       <c r="U86" s="33"/>
-      <c r="V86" s="91"/>
-      <c r="W86" s="92"/>
+      <c r="V86" s="93"/>
+      <c r="W86" s="94"/>
       <c r="X86" s="31"/>
       <c r="Y86" s="29"/>
-      <c r="Z86" s="91"/>
-      <c r="AA86" s="92"/>
+      <c r="Z86" s="93"/>
+      <c r="AA86" s="94"/>
       <c r="AB86" s="31"/>
       <c r="AC86" s="33"/>
-      <c r="AD86" s="93" t="s">
+      <c r="AD86" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="AE86" s="94"/>
+      <c r="AE86" s="96"/>
       <c r="AF86" s="74"/>
       <c r="AG86" s="29"/>
-      <c r="AH86" s="91"/>
-      <c r="AI86" s="92"/>
+      <c r="AH86" s="93"/>
+      <c r="AI86" s="94"/>
       <c r="AJ86" s="31"/>
       <c r="AK86" s="33"/>
-      <c r="AL86" s="91"/>
-      <c r="AM86" s="92"/>
+      <c r="AL86" s="93"/>
+      <c r="AM86" s="94"/>
       <c r="AN86" s="31"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="26"/>
       <c r="AQ86" s="23"/>
       <c r="AR86" s="21"/>
     </row>
-    <row r="87" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
-      <c r="B87" s="124"/>
-      <c r="C87" s="125"/>
-      <c r="D87" s="126"/>
+      <c r="B87" s="126"/>
+      <c r="C87" s="127"/>
+      <c r="D87" s="128"/>
       <c r="E87" s="29"/>
-      <c r="F87" s="124"/>
-      <c r="G87" s="125"/>
-      <c r="H87" s="126"/>
+      <c r="F87" s="126"/>
+      <c r="G87" s="127"/>
+      <c r="H87" s="128"/>
       <c r="I87" s="33"/>
-      <c r="J87" s="124"/>
-      <c r="K87" s="125"/>
-      <c r="L87" s="126"/>
+      <c r="J87" s="126"/>
+      <c r="K87" s="127"/>
+      <c r="L87" s="128"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="95" t="s">
+      <c r="N87" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="O87" s="96"/>
-      <c r="P87" s="97"/>
+      <c r="O87" s="98"/>
+      <c r="P87" s="99"/>
       <c r="Q87" s="33"/>
-      <c r="R87" s="95" t="s">
+      <c r="R87" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="S87" s="96"/>
-      <c r="T87" s="97"/>
+      <c r="S87" s="98"/>
+      <c r="T87" s="99"/>
       <c r="U87" s="29"/>
-      <c r="V87" s="95"/>
-      <c r="W87" s="96"/>
-      <c r="X87" s="97"/>
+      <c r="V87" s="97"/>
+      <c r="W87" s="98"/>
+      <c r="X87" s="99"/>
       <c r="Y87" s="29"/>
-      <c r="Z87" s="95"/>
-      <c r="AA87" s="96"/>
-      <c r="AB87" s="97"/>
+      <c r="Z87" s="97"/>
+      <c r="AA87" s="98"/>
+      <c r="AB87" s="99"/>
       <c r="AC87" s="33"/>
-      <c r="AD87" s="119"/>
-      <c r="AE87" s="120"/>
-      <c r="AF87" s="121"/>
+      <c r="AD87" s="121"/>
+      <c r="AE87" s="122"/>
+      <c r="AF87" s="123"/>
       <c r="AG87" s="29"/>
-      <c r="AH87" s="95"/>
-      <c r="AI87" s="96"/>
-      <c r="AJ87" s="97"/>
+      <c r="AH87" s="97"/>
+      <c r="AI87" s="98"/>
+      <c r="AJ87" s="99"/>
       <c r="AK87" s="33"/>
-      <c r="AL87" s="95"/>
-      <c r="AM87" s="96"/>
-      <c r="AN87" s="97"/>
+      <c r="AL87" s="97"/>
+      <c r="AM87" s="98"/>
+      <c r="AN87" s="99"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="26"/>
       <c r="AQ87" s="23"/>
       <c r="AR87" s="21"/>
     </row>
-    <row r="88" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
-      <c r="B88" s="117"/>
-      <c r="C88" s="118"/>
-      <c r="D88" s="127"/>
+      <c r="B88" s="119"/>
+      <c r="C88" s="120"/>
+      <c r="D88" s="129"/>
       <c r="E88" s="29"/>
-      <c r="F88" s="117"/>
-      <c r="G88" s="118"/>
-      <c r="H88" s="127"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="120"/>
+      <c r="H88" s="129"/>
       <c r="I88" s="33"/>
-      <c r="J88" s="117"/>
-      <c r="K88" s="118"/>
-      <c r="L88" s="127"/>
+      <c r="J88" s="119"/>
+      <c r="K88" s="120"/>
+      <c r="L88" s="129"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="98"/>
-      <c r="O88" s="99"/>
-      <c r="P88" s="100"/>
+      <c r="N88" s="100"/>
+      <c r="O88" s="101"/>
+      <c r="P88" s="102"/>
       <c r="Q88" s="33"/>
-      <c r="R88" s="98"/>
-      <c r="S88" s="99"/>
-      <c r="T88" s="100"/>
+      <c r="R88" s="100"/>
+      <c r="S88" s="101"/>
+      <c r="T88" s="102"/>
       <c r="U88" s="28"/>
-      <c r="V88" s="98"/>
-      <c r="W88" s="99"/>
-      <c r="X88" s="100"/>
+      <c r="V88" s="100"/>
+      <c r="W88" s="101"/>
+      <c r="X88" s="102"/>
       <c r="Y88" s="29"/>
-      <c r="Z88" s="98"/>
-      <c r="AA88" s="99"/>
-      <c r="AB88" s="100"/>
+      <c r="Z88" s="100"/>
+      <c r="AA88" s="101"/>
+      <c r="AB88" s="102"/>
       <c r="AC88" s="33"/>
-      <c r="AD88" s="88" t="s">
+      <c r="AD88" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="AE88" s="89"/>
-      <c r="AF88" s="90"/>
+      <c r="AE88" s="91"/>
+      <c r="AF88" s="92"/>
       <c r="AG88" s="29"/>
-      <c r="AH88" s="98"/>
-      <c r="AI88" s="99"/>
-      <c r="AJ88" s="100"/>
+      <c r="AH88" s="100"/>
+      <c r="AI88" s="101"/>
+      <c r="AJ88" s="102"/>
       <c r="AK88" s="33"/>
-      <c r="AL88" s="98"/>
-      <c r="AM88" s="99"/>
-      <c r="AN88" s="100"/>
+      <c r="AL88" s="100"/>
+      <c r="AM88" s="101"/>
+      <c r="AN88" s="102"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="26"/>
       <c r="AQ88" s="23"/>
       <c r="AR88" s="21"/>
     </row>
-    <row r="89" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
-      <c r="B89" s="114"/>
-      <c r="C89" s="115"/>
-      <c r="D89" s="116"/>
+      <c r="B89" s="116"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="118"/>
       <c r="E89" s="29"/>
-      <c r="F89" s="114"/>
-      <c r="G89" s="115"/>
-      <c r="H89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="118"/>
       <c r="I89" s="28"/>
-      <c r="J89" s="114"/>
-      <c r="K89" s="115"/>
-      <c r="L89" s="116"/>
+      <c r="J89" s="116"/>
+      <c r="K89" s="117"/>
+      <c r="L89" s="118"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="75" t="s">
+      <c r="N89" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="O89" s="76"/>
-      <c r="P89" s="77"/>
+      <c r="O89" s="78"/>
+      <c r="P89" s="79"/>
       <c r="Q89" s="28"/>
-      <c r="R89" s="75" t="s">
+      <c r="R89" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="S89" s="76"/>
-      <c r="T89" s="77"/>
+      <c r="S89" s="78"/>
+      <c r="T89" s="79"/>
       <c r="U89" s="29"/>
-      <c r="V89" s="75"/>
-      <c r="W89" s="76"/>
-      <c r="X89" s="77"/>
+      <c r="V89" s="77"/>
+      <c r="W89" s="78"/>
+      <c r="X89" s="79"/>
       <c r="Y89" s="28"/>
-      <c r="Z89" s="75"/>
-      <c r="AA89" s="76"/>
-      <c r="AB89" s="77"/>
+      <c r="Z89" s="77"/>
+      <c r="AA89" s="78"/>
+      <c r="AB89" s="79"/>
       <c r="AC89" s="28"/>
-      <c r="AD89" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE89" s="76"/>
-      <c r="AF89" s="77"/>
+      <c r="AD89" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE89" s="78"/>
+      <c r="AF89" s="79"/>
       <c r="AG89" s="29"/>
-      <c r="AH89" s="75"/>
-      <c r="AI89" s="76"/>
-      <c r="AJ89" s="77"/>
+      <c r="AH89" s="77"/>
+      <c r="AI89" s="78"/>
+      <c r="AJ89" s="79"/>
       <c r="AK89" s="28"/>
-      <c r="AL89" s="75"/>
-      <c r="AM89" s="76"/>
-      <c r="AN89" s="77"/>
+      <c r="AL89" s="77"/>
+      <c r="AM89" s="78"/>
+      <c r="AN89" s="79"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="26"/>
       <c r="AQ89" s="23"/>
       <c r="AR89" s="21"/>
     </row>
-    <row r="90" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12"/>
-      <c r="B90" s="105"/>
-      <c r="C90" s="106"/>
-      <c r="D90" s="107"/>
+      <c r="B90" s="107"/>
+      <c r="C90" s="108"/>
+      <c r="D90" s="109"/>
       <c r="E90" s="28"/>
-      <c r="F90" s="105"/>
-      <c r="G90" s="106"/>
-      <c r="H90" s="107"/>
+      <c r="F90" s="107"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="109"/>
       <c r="I90" s="29"/>
-      <c r="J90" s="105"/>
-      <c r="K90" s="106"/>
-      <c r="L90" s="107"/>
+      <c r="J90" s="107"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="109"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="78" t="s">
+      <c r="N90" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="O90" s="79"/>
-      <c r="P90" s="80"/>
+      <c r="O90" s="81"/>
+      <c r="P90" s="82"/>
       <c r="Q90" s="29"/>
-      <c r="R90" s="78"/>
-      <c r="S90" s="79"/>
-      <c r="T90" s="80"/>
+      <c r="R90" s="80"/>
+      <c r="S90" s="81"/>
+      <c r="T90" s="82"/>
       <c r="U90" s="29"/>
-      <c r="V90" s="78"/>
-      <c r="W90" s="79"/>
-      <c r="X90" s="80"/>
+      <c r="V90" s="80"/>
+      <c r="W90" s="81"/>
+      <c r="X90" s="82"/>
       <c r="Y90" s="29"/>
-      <c r="Z90" s="78"/>
-      <c r="AA90" s="79"/>
-      <c r="AB90" s="80"/>
+      <c r="Z90" s="80"/>
+      <c r="AA90" s="81"/>
+      <c r="AB90" s="82"/>
       <c r="AC90" s="29"/>
-      <c r="AD90" s="78"/>
-      <c r="AE90" s="79"/>
-      <c r="AF90" s="80"/>
+      <c r="AD90" s="87" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE90" s="88"/>
+      <c r="AF90" s="89"/>
       <c r="AG90" s="28"/>
-      <c r="AH90" s="78"/>
-      <c r="AI90" s="79"/>
-      <c r="AJ90" s="80"/>
+      <c r="AH90" s="80"/>
+      <c r="AI90" s="81"/>
+      <c r="AJ90" s="82"/>
       <c r="AK90" s="29"/>
-      <c r="AL90" s="78"/>
-      <c r="AM90" s="79"/>
-      <c r="AN90" s="80"/>
+      <c r="AL90" s="80"/>
+      <c r="AM90" s="81"/>
+      <c r="AN90" s="82"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="26"/>
       <c r="AQ90" s="23"/>
       <c r="AR90" s="21"/>
     </row>
-    <row r="91" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="32"/>
       <c r="C91" s="32"/>
@@ -7746,285 +7758,285 @@
       <c r="AQ91" s="23"/>
       <c r="AR91" s="21"/>
     </row>
-    <row r="92" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
-      <c r="B92" s="146"/>
-      <c r="C92" s="147"/>
+      <c r="B92" s="145"/>
+      <c r="C92" s="146"/>
       <c r="D92" s="48"/>
       <c r="E92" s="29"/>
-      <c r="F92" s="146"/>
-      <c r="G92" s="147"/>
+      <c r="F92" s="145"/>
+      <c r="G92" s="146"/>
       <c r="H92" s="48"/>
       <c r="I92" s="29"/>
-      <c r="J92" s="146"/>
-      <c r="K92" s="147"/>
+      <c r="J92" s="145"/>
+      <c r="K92" s="146"/>
       <c r="L92" s="48"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="91"/>
-      <c r="O92" s="92"/>
+      <c r="N92" s="93"/>
+      <c r="O92" s="94"/>
       <c r="P92" s="31"/>
       <c r="Q92" s="29"/>
-      <c r="R92" s="91"/>
-      <c r="S92" s="92"/>
+      <c r="R92" s="93"/>
+      <c r="S92" s="94"/>
       <c r="T92" s="31"/>
       <c r="U92" s="29"/>
-      <c r="V92" s="91"/>
-      <c r="W92" s="92"/>
+      <c r="V92" s="93"/>
+      <c r="W92" s="94"/>
       <c r="X92" s="31"/>
       <c r="Y92" s="29"/>
-      <c r="Z92" s="158" t="s">
+      <c r="Z92" s="157" t="s">
         <v>90</v>
       </c>
-      <c r="AA92" s="159"/>
+      <c r="AA92" s="158"/>
       <c r="AB92" s="69"/>
       <c r="AC92" s="29"/>
-      <c r="AD92" s="158" t="s">
+      <c r="AD92" s="157" t="s">
         <v>90</v>
       </c>
-      <c r="AE92" s="159"/>
+      <c r="AE92" s="158"/>
       <c r="AF92" s="69"/>
       <c r="AG92" s="29"/>
-      <c r="AH92" s="224" t="s">
+      <c r="AH92" s="215" t="s">
         <v>58</v>
       </c>
-      <c r="AI92" s="225"/>
-      <c r="AJ92" s="226"/>
+      <c r="AI92" s="216"/>
+      <c r="AJ92" s="75"/>
       <c r="AK92" s="29"/>
-      <c r="AL92" s="91"/>
-      <c r="AM92" s="92"/>
+      <c r="AL92" s="93"/>
+      <c r="AM92" s="94"/>
       <c r="AN92" s="31"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="26"/>
       <c r="AQ92" s="23"/>
       <c r="AR92" s="21"/>
     </row>
-    <row r="93" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
-      <c r="B93" s="148"/>
-      <c r="C93" s="149"/>
-      <c r="D93" s="150"/>
+      <c r="B93" s="147"/>
+      <c r="C93" s="148"/>
+      <c r="D93" s="149"/>
       <c r="E93" s="29"/>
-      <c r="F93" s="148"/>
-      <c r="G93" s="149"/>
-      <c r="H93" s="150"/>
+      <c r="F93" s="147"/>
+      <c r="G93" s="148"/>
+      <c r="H93" s="149"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="148"/>
-      <c r="K93" s="149"/>
-      <c r="L93" s="150"/>
+      <c r="J93" s="147"/>
+      <c r="K93" s="148"/>
+      <c r="L93" s="149"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="95"/>
-      <c r="O93" s="96"/>
-      <c r="P93" s="97"/>
+      <c r="N93" s="97"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="99"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
-      <c r="T93" s="97"/>
+      <c r="R93" s="97"/>
+      <c r="S93" s="98"/>
+      <c r="T93" s="99"/>
       <c r="U93" s="29"/>
-      <c r="V93" s="95"/>
-      <c r="W93" s="96"/>
-      <c r="X93" s="97"/>
+      <c r="V93" s="97"/>
+      <c r="W93" s="98"/>
+      <c r="X93" s="99"/>
       <c r="Y93" s="29"/>
-      <c r="Z93" s="81" t="s">
+      <c r="Z93" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="AA93" s="82"/>
+      <c r="AA93" s="84"/>
       <c r="AB93" s="70"/>
       <c r="AC93" s="32"/>
-      <c r="AD93" s="81" t="s">
+      <c r="AD93" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="AE93" s="82"/>
+      <c r="AE93" s="84"/>
       <c r="AF93" s="70"/>
       <c r="AG93" s="29"/>
-      <c r="AH93" s="227" t="s">
+      <c r="AH93" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="AI93" s="228"/>
-      <c r="AJ93" s="229"/>
+      <c r="AI93" s="86"/>
+      <c r="AJ93" s="76"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="95"/>
-      <c r="AM93" s="96"/>
-      <c r="AN93" s="97"/>
+      <c r="AL93" s="97"/>
+      <c r="AM93" s="98"/>
+      <c r="AN93" s="99"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="26"/>
       <c r="AQ93" s="23"/>
       <c r="AR93" s="21"/>
     </row>
-    <row r="94" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
-      <c r="B94" s="151"/>
-      <c r="C94" s="152"/>
-      <c r="D94" s="153"/>
+      <c r="B94" s="150"/>
+      <c r="C94" s="151"/>
+      <c r="D94" s="152"/>
       <c r="E94" s="29"/>
-      <c r="F94" s="151"/>
-      <c r="G94" s="152"/>
-      <c r="H94" s="153"/>
+      <c r="F94" s="150"/>
+      <c r="G94" s="151"/>
+      <c r="H94" s="152"/>
       <c r="I94" s="28"/>
-      <c r="J94" s="151"/>
-      <c r="K94" s="152"/>
-      <c r="L94" s="153"/>
+      <c r="J94" s="150"/>
+      <c r="K94" s="151"/>
+      <c r="L94" s="152"/>
       <c r="M94" s="23"/>
-      <c r="N94" s="98"/>
-      <c r="O94" s="99"/>
-      <c r="P94" s="100"/>
+      <c r="N94" s="100"/>
+      <c r="O94" s="101"/>
+      <c r="P94" s="102"/>
       <c r="Q94" s="28"/>
-      <c r="R94" s="98"/>
-      <c r="S94" s="99"/>
-      <c r="T94" s="100"/>
+      <c r="R94" s="100"/>
+      <c r="S94" s="101"/>
+      <c r="T94" s="102"/>
       <c r="U94" s="29"/>
-      <c r="V94" s="98"/>
-      <c r="W94" s="99"/>
-      <c r="X94" s="100"/>
+      <c r="V94" s="100"/>
+      <c r="W94" s="101"/>
+      <c r="X94" s="102"/>
       <c r="Y94" s="29"/>
-      <c r="Z94" s="154" t="s">
+      <c r="Z94" s="153" t="s">
         <v>111</v>
       </c>
-      <c r="AA94" s="155"/>
+      <c r="AA94" s="154"/>
       <c r="AB94" s="71" t="s">
         <v>32</v>
       </c>
       <c r="AC94" s="28"/>
-      <c r="AD94" s="154" t="s">
+      <c r="AD94" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="AE94" s="155"/>
+      <c r="AE94" s="154"/>
       <c r="AF94" s="71" t="s">
         <v>32</v>
       </c>
       <c r="AG94" s="29"/>
-      <c r="AH94" s="154" t="s">
+      <c r="AH94" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="AI94" s="155"/>
+      <c r="AI94" s="154"/>
       <c r="AJ94" s="71" t="s">
         <v>32</v>
       </c>
       <c r="AK94" s="28"/>
-      <c r="AL94" s="98"/>
-      <c r="AM94" s="99"/>
-      <c r="AN94" s="100"/>
+      <c r="AL94" s="100"/>
+      <c r="AM94" s="101"/>
+      <c r="AN94" s="102"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="26"/>
       <c r="AQ94" s="23"/>
       <c r="AR94" s="21"/>
     </row>
-    <row r="95" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
-      <c r="B95" s="75"/>
-      <c r="C95" s="76"/>
-      <c r="D95" s="77"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="79"/>
       <c r="E95" s="29"/>
-      <c r="F95" s="75"/>
-      <c r="G95" s="76"/>
-      <c r="H95" s="77"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="78"/>
+      <c r="H95" s="79"/>
       <c r="I95" s="28"/>
-      <c r="J95" s="75"/>
-      <c r="K95" s="76"/>
-      <c r="L95" s="77"/>
+      <c r="J95" s="77"/>
+      <c r="K95" s="78"/>
+      <c r="L95" s="79"/>
       <c r="M95" s="23"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="77"/>
+      <c r="N95" s="77"/>
+      <c r="O95" s="78"/>
+      <c r="P95" s="79"/>
       <c r="Q95" s="28"/>
-      <c r="R95" s="75"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="77"/>
+      <c r="R95" s="77"/>
+      <c r="S95" s="78"/>
+      <c r="T95" s="79"/>
       <c r="U95" s="29"/>
-      <c r="V95" s="75"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="77"/>
+      <c r="V95" s="77"/>
+      <c r="W95" s="78"/>
+      <c r="X95" s="79"/>
       <c r="Y95" s="29"/>
-      <c r="Z95" s="156" t="s">
+      <c r="Z95" s="155" t="s">
         <v>76</v>
       </c>
-      <c r="AA95" s="157"/>
+      <c r="AA95" s="156"/>
       <c r="AB95" s="72" t="s">
         <v>33</v>
       </c>
       <c r="AC95" s="28"/>
-      <c r="AD95" s="156" t="s">
+      <c r="AD95" s="155" t="s">
         <v>76</v>
       </c>
-      <c r="AE95" s="157"/>
+      <c r="AE95" s="156"/>
       <c r="AF95" s="72" t="s">
         <v>33</v>
       </c>
       <c r="AG95" s="29"/>
-      <c r="AH95" s="156" t="s">
+      <c r="AH95" s="155" t="s">
         <v>76</v>
       </c>
-      <c r="AI95" s="157"/>
+      <c r="AI95" s="156"/>
       <c r="AJ95" s="72" t="s">
         <v>33</v>
       </c>
       <c r="AK95" s="28"/>
-      <c r="AL95" s="75"/>
-      <c r="AM95" s="76"/>
-      <c r="AN95" s="77"/>
+      <c r="AL95" s="77"/>
+      <c r="AM95" s="78"/>
+      <c r="AN95" s="79"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="26"/>
       <c r="AQ95" s="23"/>
       <c r="AR95" s="21"/>
     </row>
-    <row r="96" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
-      <c r="B96" s="78"/>
-      <c r="C96" s="79"/>
-      <c r="D96" s="80"/>
+      <c r="B96" s="80"/>
+      <c r="C96" s="81"/>
+      <c r="D96" s="82"/>
       <c r="E96" s="28"/>
-      <c r="F96" s="78"/>
-      <c r="G96" s="79"/>
-      <c r="H96" s="80"/>
+      <c r="F96" s="80"/>
+      <c r="G96" s="81"/>
+      <c r="H96" s="82"/>
       <c r="I96" s="29"/>
-      <c r="J96" s="78"/>
-      <c r="K96" s="79"/>
-      <c r="L96" s="80"/>
+      <c r="J96" s="80"/>
+      <c r="K96" s="81"/>
+      <c r="L96" s="82"/>
       <c r="M96" s="23"/>
-      <c r="N96" s="78"/>
-      <c r="O96" s="79"/>
-      <c r="P96" s="80"/>
+      <c r="N96" s="80"/>
+      <c r="O96" s="81"/>
+      <c r="P96" s="82"/>
       <c r="Q96" s="28"/>
-      <c r="R96" s="78"/>
-      <c r="S96" s="79"/>
-      <c r="T96" s="80"/>
+      <c r="R96" s="80"/>
+      <c r="S96" s="81"/>
+      <c r="T96" s="82"/>
       <c r="U96" s="28"/>
-      <c r="V96" s="78"/>
-      <c r="W96" s="79"/>
-      <c r="X96" s="80"/>
+      <c r="V96" s="80"/>
+      <c r="W96" s="81"/>
+      <c r="X96" s="82"/>
       <c r="Y96" s="28"/>
-      <c r="Z96" s="156" t="s">
+      <c r="Z96" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="AA96" s="157"/>
+      <c r="AA96" s="156"/>
       <c r="AB96" s="72" t="s">
         <v>34</v>
       </c>
       <c r="AC96" s="28"/>
-      <c r="AD96" s="156" t="s">
+      <c r="AD96" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="AE96" s="157"/>
+      <c r="AE96" s="156"/>
       <c r="AF96" s="72" t="s">
         <v>34</v>
       </c>
       <c r="AG96" s="28"/>
-      <c r="AH96" s="156" t="s">
+      <c r="AH96" s="155" t="s">
         <v>96</v>
       </c>
-      <c r="AI96" s="157"/>
+      <c r="AI96" s="156"/>
       <c r="AJ96" s="72" t="s">
         <v>34</v>
       </c>
       <c r="AK96" s="29"/>
-      <c r="AL96" s="78"/>
-      <c r="AM96" s="79"/>
-      <c r="AN96" s="80"/>
+      <c r="AL96" s="80"/>
+      <c r="AM96" s="81"/>
+      <c r="AN96" s="82"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="26"/>
       <c r="AQ96" s="23"/>
       <c r="AR96" s="21"/>
     </row>
-    <row r="97" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="32"/>
       <c r="C97" s="32"/>
@@ -8050,26 +8062,26 @@
       <c r="W97" s="32"/>
       <c r="X97" s="32"/>
       <c r="Y97" s="32"/>
-      <c r="Z97" s="156" t="s">
+      <c r="Z97" s="155" t="s">
         <v>112</v>
       </c>
-      <c r="AA97" s="157"/>
+      <c r="AA97" s="156"/>
       <c r="AB97" s="72" t="s">
         <v>35</v>
       </c>
       <c r="AC97" s="29"/>
-      <c r="AD97" s="156" t="s">
+      <c r="AD97" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="AE97" s="157"/>
+      <c r="AE97" s="156"/>
       <c r="AF97" s="72" t="s">
         <v>35</v>
       </c>
       <c r="AG97" s="28"/>
-      <c r="AH97" s="156" t="s">
+      <c r="AH97" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="AI97" s="157"/>
+      <c r="AI97" s="156"/>
       <c r="AJ97" s="72" t="s">
         <v>35</v>
       </c>
@@ -8082,101 +8094,101 @@
       <c r="AQ97" s="23"/>
       <c r="AR97" s="21"/>
     </row>
-    <row r="98" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12"/>
-      <c r="B98" s="146"/>
-      <c r="C98" s="147"/>
+      <c r="B98" s="145"/>
+      <c r="C98" s="146"/>
       <c r="D98" s="48"/>
       <c r="E98" s="33"/>
-      <c r="F98" s="146"/>
-      <c r="G98" s="147"/>
+      <c r="F98" s="145"/>
+      <c r="G98" s="146"/>
       <c r="H98" s="48"/>
       <c r="I98" s="29"/>
-      <c r="J98" s="146"/>
-      <c r="K98" s="147"/>
+      <c r="J98" s="145"/>
+      <c r="K98" s="146"/>
       <c r="L98" s="48"/>
       <c r="M98" s="23"/>
-      <c r="N98" s="91" t="s">
+      <c r="N98" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="O98" s="92"/>
+      <c r="O98" s="94"/>
       <c r="P98" s="31"/>
       <c r="Q98" s="33"/>
-      <c r="R98" s="91" t="s">
+      <c r="R98" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="S98" s="92"/>
+      <c r="S98" s="94"/>
       <c r="T98" s="31"/>
       <c r="U98" s="29"/>
-      <c r="V98" s="91" t="s">
+      <c r="V98" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="W98" s="92"/>
+      <c r="W98" s="94"/>
       <c r="X98" s="31"/>
       <c r="Y98" s="29"/>
-      <c r="Z98" s="160" t="s">
+      <c r="Z98" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="AA98" s="161"/>
+      <c r="AA98" s="160"/>
       <c r="AB98" s="73" t="s">
         <v>35</v>
       </c>
       <c r="AC98" s="29"/>
-      <c r="AD98" s="160" t="s">
+      <c r="AD98" s="159" t="s">
         <v>113</v>
       </c>
-      <c r="AE98" s="161"/>
+      <c r="AE98" s="160"/>
       <c r="AF98" s="73" t="s">
         <v>35</v>
       </c>
       <c r="AG98" s="33"/>
-      <c r="AH98" s="160" t="s">
+      <c r="AH98" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="AI98" s="161"/>
+      <c r="AI98" s="160"/>
       <c r="AJ98" s="73" t="s">
         <v>35</v>
       </c>
       <c r="AK98" s="29"/>
-      <c r="AL98" s="91"/>
-      <c r="AM98" s="92"/>
+      <c r="AL98" s="93"/>
+      <c r="AM98" s="94"/>
       <c r="AN98" s="31"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="26"/>
       <c r="AQ98" s="23"/>
       <c r="AR98" s="21"/>
     </row>
-    <row r="99" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
-      <c r="B99" s="148"/>
-      <c r="C99" s="149"/>
-      <c r="D99" s="150"/>
+      <c r="B99" s="147"/>
+      <c r="C99" s="148"/>
+      <c r="D99" s="149"/>
       <c r="E99" s="29"/>
-      <c r="F99" s="148"/>
-      <c r="G99" s="149"/>
-      <c r="H99" s="150"/>
+      <c r="F99" s="147"/>
+      <c r="G99" s="148"/>
+      <c r="H99" s="149"/>
       <c r="I99" s="32"/>
-      <c r="J99" s="148"/>
-      <c r="K99" s="149"/>
-      <c r="L99" s="150"/>
+      <c r="J99" s="147"/>
+      <c r="K99" s="148"/>
+      <c r="L99" s="149"/>
       <c r="M99" s="23"/>
-      <c r="N99" s="95" t="s">
+      <c r="N99" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="O99" s="96"/>
-      <c r="P99" s="97"/>
+      <c r="O99" s="98"/>
+      <c r="P99" s="99"/>
       <c r="Q99" s="38"/>
-      <c r="R99" s="95" t="s">
+      <c r="R99" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="S99" s="96"/>
-      <c r="T99" s="97"/>
+      <c r="S99" s="98"/>
+      <c r="T99" s="99"/>
       <c r="U99" s="29"/>
-      <c r="V99" s="95" t="s">
+      <c r="V99" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="W99" s="96"/>
-      <c r="X99" s="97"/>
+      <c r="W99" s="98"/>
+      <c r="X99" s="99"/>
       <c r="Y99" s="29"/>
       <c r="Z99" s="32"/>
       <c r="AA99" s="32"/>
@@ -8190,177 +8202,177 @@
       <c r="AI99" s="32"/>
       <c r="AJ99" s="32"/>
       <c r="AK99" s="32"/>
-      <c r="AL99" s="95"/>
-      <c r="AM99" s="96"/>
-      <c r="AN99" s="97"/>
+      <c r="AL99" s="97"/>
+      <c r="AM99" s="98"/>
+      <c r="AN99" s="99"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="26"/>
       <c r="AQ99" s="23"/>
       <c r="AR99" s="21"/>
     </row>
-    <row r="100" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
-      <c r="B100" s="151"/>
-      <c r="C100" s="152"/>
-      <c r="D100" s="153"/>
+      <c r="B100" s="150"/>
+      <c r="C100" s="151"/>
+      <c r="D100" s="152"/>
       <c r="E100" s="28"/>
-      <c r="F100" s="151"/>
-      <c r="G100" s="152"/>
-      <c r="H100" s="153"/>
+      <c r="F100" s="150"/>
+      <c r="G100" s="151"/>
+      <c r="H100" s="152"/>
       <c r="I100" s="28"/>
-      <c r="J100" s="151"/>
-      <c r="K100" s="152"/>
-      <c r="L100" s="153"/>
+      <c r="J100" s="150"/>
+      <c r="K100" s="151"/>
+      <c r="L100" s="152"/>
       <c r="M100" s="23"/>
-      <c r="N100" s="98" t="s">
+      <c r="N100" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="O100" s="99"/>
-      <c r="P100" s="100"/>
+      <c r="O100" s="101"/>
+      <c r="P100" s="102"/>
       <c r="Q100" s="34"/>
-      <c r="R100" s="98" t="s">
+      <c r="R100" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="S100" s="99"/>
-      <c r="T100" s="100"/>
+      <c r="S100" s="101"/>
+      <c r="T100" s="102"/>
       <c r="U100" s="34"/>
-      <c r="V100" s="98" t="s">
+      <c r="V100" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="W100" s="99"/>
-      <c r="X100" s="100"/>
+      <c r="W100" s="101"/>
+      <c r="X100" s="102"/>
       <c r="Y100" s="29"/>
-      <c r="Z100" s="91" t="s">
+      <c r="Z100" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="AA100" s="92"/>
+      <c r="AA100" s="94"/>
       <c r="AB100" s="31"/>
       <c r="AC100" s="29"/>
-      <c r="AD100" s="91" t="s">
+      <c r="AD100" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="AE100" s="92"/>
+      <c r="AE100" s="94"/>
       <c r="AF100" s="31"/>
       <c r="AG100" s="28"/>
-      <c r="AH100" s="91"/>
-      <c r="AI100" s="92"/>
+      <c r="AH100" s="93"/>
+      <c r="AI100" s="94"/>
       <c r="AJ100" s="31"/>
       <c r="AK100" s="28"/>
-      <c r="AL100" s="98"/>
-      <c r="AM100" s="99"/>
-      <c r="AN100" s="100"/>
+      <c r="AL100" s="100"/>
+      <c r="AM100" s="101"/>
+      <c r="AN100" s="102"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="26"/>
       <c r="AQ100" s="23"/>
       <c r="AR100" s="21"/>
     </row>
-    <row r="101" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
-      <c r="B101" s="75"/>
-      <c r="C101" s="76"/>
-      <c r="D101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="78"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="29"/>
-      <c r="F101" s="75"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="77"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="78"/>
+      <c r="H101" s="79"/>
       <c r="I101" s="28"/>
-      <c r="J101" s="75"/>
-      <c r="K101" s="76"/>
-      <c r="L101" s="77"/>
+      <c r="J101" s="77"/>
+      <c r="K101" s="78"/>
+      <c r="L101" s="79"/>
       <c r="M101" s="23"/>
-      <c r="N101" s="75" t="s">
+      <c r="N101" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="O101" s="76"/>
-      <c r="P101" s="77"/>
+      <c r="O101" s="78"/>
+      <c r="P101" s="79"/>
       <c r="Q101" s="39"/>
-      <c r="R101" s="75" t="s">
+      <c r="R101" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="S101" s="76"/>
-      <c r="T101" s="77"/>
+      <c r="S101" s="78"/>
+      <c r="T101" s="79"/>
       <c r="U101" s="39"/>
-      <c r="V101" s="75" t="s">
+      <c r="V101" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="W101" s="76"/>
-      <c r="X101" s="77"/>
+      <c r="W101" s="78"/>
+      <c r="X101" s="79"/>
       <c r="Y101" s="29"/>
-      <c r="Z101" s="98" t="s">
+      <c r="Z101" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="AA101" s="99"/>
-      <c r="AB101" s="100"/>
+      <c r="AA101" s="101"/>
+      <c r="AB101" s="102"/>
       <c r="AC101" s="28"/>
-      <c r="AD101" s="98" t="s">
+      <c r="AD101" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="AE101" s="99"/>
-      <c r="AF101" s="100"/>
+      <c r="AE101" s="101"/>
+      <c r="AF101" s="102"/>
       <c r="AG101" s="29"/>
-      <c r="AH101" s="98"/>
-      <c r="AI101" s="99"/>
-      <c r="AJ101" s="100"/>
+      <c r="AH101" s="100"/>
+      <c r="AI101" s="101"/>
+      <c r="AJ101" s="102"/>
       <c r="AK101" s="28"/>
-      <c r="AL101" s="75"/>
-      <c r="AM101" s="76"/>
-      <c r="AN101" s="77"/>
+      <c r="AL101" s="77"/>
+      <c r="AM101" s="78"/>
+      <c r="AN101" s="79"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="26"/>
       <c r="AQ101" s="23"/>
       <c r="AR101" s="21"/>
     </row>
-    <row r="102" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
-      <c r="B102" s="78"/>
-      <c r="C102" s="79"/>
-      <c r="D102" s="80"/>
+      <c r="B102" s="80"/>
+      <c r="C102" s="81"/>
+      <c r="D102" s="82"/>
       <c r="E102" s="29"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="79"/>
-      <c r="H102" s="80"/>
+      <c r="F102" s="80"/>
+      <c r="G102" s="81"/>
+      <c r="H102" s="82"/>
       <c r="I102" s="29"/>
-      <c r="J102" s="78"/>
-      <c r="K102" s="79"/>
-      <c r="L102" s="80"/>
+      <c r="J102" s="80"/>
+      <c r="K102" s="81"/>
+      <c r="L102" s="82"/>
       <c r="M102" s="23"/>
-      <c r="N102" s="78"/>
-      <c r="O102" s="79"/>
-      <c r="P102" s="80"/>
+      <c r="N102" s="80"/>
+      <c r="O102" s="81"/>
+      <c r="P102" s="82"/>
       <c r="Q102" s="28"/>
-      <c r="R102" s="78"/>
-      <c r="S102" s="79"/>
-      <c r="T102" s="80"/>
+      <c r="R102" s="80"/>
+      <c r="S102" s="81"/>
+      <c r="T102" s="82"/>
       <c r="U102" s="29"/>
-      <c r="V102" s="78"/>
-      <c r="W102" s="79"/>
-      <c r="X102" s="80"/>
+      <c r="V102" s="80"/>
+      <c r="W102" s="81"/>
+      <c r="X102" s="82"/>
       <c r="Y102" s="29"/>
-      <c r="Z102" s="78" t="s">
+      <c r="Z102" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="AA102" s="79"/>
-      <c r="AB102" s="80"/>
+      <c r="AA102" s="81"/>
+      <c r="AB102" s="82"/>
       <c r="AC102" s="28"/>
-      <c r="AD102" s="78" t="s">
+      <c r="AD102" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="AE102" s="79"/>
-      <c r="AF102" s="80"/>
+      <c r="AE102" s="81"/>
+      <c r="AF102" s="82"/>
       <c r="AG102" s="29"/>
-      <c r="AH102" s="78"/>
-      <c r="AI102" s="79"/>
-      <c r="AJ102" s="80"/>
+      <c r="AH102" s="80"/>
+      <c r="AI102" s="81"/>
+      <c r="AJ102" s="82"/>
       <c r="AK102" s="29"/>
-      <c r="AL102" s="78"/>
-      <c r="AM102" s="79"/>
-      <c r="AN102" s="80"/>
+      <c r="AL102" s="80"/>
+      <c r="AM102" s="81"/>
+      <c r="AN102" s="82"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="26"/>
       <c r="AQ102" s="23"/>
       <c r="AR102" s="21"/>
     </row>
-    <row r="103" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:44" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="12"/>
       <c r="B103" s="37"/>
       <c r="C103" s="30"/>
@@ -8406,7 +8418,7 @@
       <c r="AQ103" s="23"/>
       <c r="AR103" s="23"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B104" s="30"/>
       <c r="C104" s="30"/>
       <c r="D104" s="30"/>
@@ -8423,73 +8435,73 @@
       <c r="AQ104" s="23"/>
       <c r="AR104" s="23"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="91"/>
-      <c r="C105" s="92"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="93"/>
+      <c r="C105" s="94"/>
       <c r="D105" s="31"/>
       <c r="E105" s="29"/>
-      <c r="F105" s="91"/>
-      <c r="G105" s="92"/>
+      <c r="F105" s="93"/>
+      <c r="G105" s="94"/>
       <c r="H105" s="31"/>
       <c r="I105" s="29"/>
-      <c r="J105" s="91"/>
-      <c r="K105" s="92"/>
+      <c r="J105" s="93"/>
+      <c r="K105" s="94"/>
       <c r="L105" s="31"/>
       <c r="AO105" s="23"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="95"/>
-      <c r="C106" s="96"/>
-      <c r="D106" s="97"/>
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="97"/>
+      <c r="C106" s="98"/>
+      <c r="D106" s="99"/>
       <c r="E106" s="29"/>
-      <c r="F106" s="95"/>
-      <c r="G106" s="96"/>
-      <c r="H106" s="97"/>
+      <c r="F106" s="97"/>
+      <c r="G106" s="98"/>
+      <c r="H106" s="99"/>
       <c r="I106" s="29"/>
-      <c r="J106" s="95"/>
-      <c r="K106" s="96"/>
-      <c r="L106" s="97"/>
-    </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="98"/>
-      <c r="C107" s="99"/>
-      <c r="D107" s="100"/>
+      <c r="J106" s="97"/>
+      <c r="K106" s="98"/>
+      <c r="L106" s="99"/>
+    </row>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="100"/>
+      <c r="C107" s="101"/>
+      <c r="D107" s="102"/>
       <c r="E107" s="29"/>
-      <c r="F107" s="98"/>
-      <c r="G107" s="99"/>
-      <c r="H107" s="100"/>
+      <c r="F107" s="100"/>
+      <c r="G107" s="101"/>
+      <c r="H107" s="102"/>
       <c r="I107" s="29"/>
-      <c r="J107" s="98"/>
-      <c r="K107" s="99"/>
-      <c r="L107" s="100"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="75"/>
-      <c r="C108" s="76"/>
-      <c r="D108" s="77"/>
+      <c r="J107" s="100"/>
+      <c r="K107" s="101"/>
+      <c r="L107" s="102"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="77"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="79"/>
       <c r="E108" s="29"/>
-      <c r="F108" s="75"/>
-      <c r="G108" s="76"/>
-      <c r="H108" s="77"/>
+      <c r="F108" s="77"/>
+      <c r="G108" s="78"/>
+      <c r="H108" s="79"/>
       <c r="I108" s="28"/>
-      <c r="J108" s="75"/>
-      <c r="K108" s="76"/>
-      <c r="L108" s="77"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="78"/>
-      <c r="C109" s="79"/>
-      <c r="D109" s="80"/>
+      <c r="J108" s="77"/>
+      <c r="K108" s="78"/>
+      <c r="L108" s="79"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="80"/>
+      <c r="C109" s="81"/>
+      <c r="D109" s="82"/>
       <c r="E109" s="28"/>
-      <c r="F109" s="78"/>
-      <c r="G109" s="79"/>
-      <c r="H109" s="80"/>
+      <c r="F109" s="80"/>
+      <c r="G109" s="81"/>
+      <c r="H109" s="82"/>
       <c r="I109" s="28"/>
-      <c r="J109" s="78"/>
-      <c r="K109" s="79"/>
-      <c r="L109" s="80"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J109" s="80"/>
+      <c r="K109" s="81"/>
+      <c r="L109" s="82"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="32"/>
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
@@ -8502,72 +8514,72 @@
       <c r="K110" s="32"/>
       <c r="L110" s="32"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="91"/>
-      <c r="C111" s="92"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="93"/>
+      <c r="C111" s="94"/>
       <c r="D111" s="31"/>
       <c r="E111" s="28"/>
-      <c r="F111" s="91"/>
-      <c r="G111" s="92"/>
+      <c r="F111" s="93"/>
+      <c r="G111" s="94"/>
       <c r="H111" s="31"/>
       <c r="I111" s="28"/>
-      <c r="J111" s="91"/>
-      <c r="K111" s="92"/>
+      <c r="J111" s="93"/>
+      <c r="K111" s="94"/>
       <c r="L111" s="31"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="95"/>
-      <c r="C112" s="96"/>
-      <c r="D112" s="97"/>
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="97"/>
+      <c r="C112" s="98"/>
+      <c r="D112" s="99"/>
       <c r="E112" s="29"/>
-      <c r="F112" s="95"/>
-      <c r="G112" s="96"/>
-      <c r="H112" s="97"/>
+      <c r="F112" s="97"/>
+      <c r="G112" s="98"/>
+      <c r="H112" s="99"/>
       <c r="I112" s="29"/>
-      <c r="J112" s="95"/>
-      <c r="K112" s="96"/>
-      <c r="L112" s="97"/>
-    </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="98"/>
-      <c r="C113" s="99"/>
-      <c r="D113" s="100"/>
+      <c r="J112" s="97"/>
+      <c r="K112" s="98"/>
+      <c r="L112" s="99"/>
+    </row>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="100"/>
+      <c r="C113" s="101"/>
+      <c r="D113" s="102"/>
       <c r="E113" s="32"/>
-      <c r="F113" s="98"/>
-      <c r="G113" s="99"/>
-      <c r="H113" s="100"/>
+      <c r="F113" s="100"/>
+      <c r="G113" s="101"/>
+      <c r="H113" s="102"/>
       <c r="I113" s="32"/>
-      <c r="J113" s="98"/>
-      <c r="K113" s="99"/>
-      <c r="L113" s="100"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="75"/>
-      <c r="C114" s="76"/>
-      <c r="D114" s="77"/>
+      <c r="J113" s="100"/>
+      <c r="K113" s="101"/>
+      <c r="L113" s="102"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="77"/>
+      <c r="C114" s="78"/>
+      <c r="D114" s="79"/>
       <c r="E114" s="29"/>
-      <c r="F114" s="75"/>
-      <c r="G114" s="76"/>
-      <c r="H114" s="77"/>
+      <c r="F114" s="77"/>
+      <c r="G114" s="78"/>
+      <c r="H114" s="79"/>
       <c r="I114" s="29"/>
-      <c r="J114" s="75"/>
-      <c r="K114" s="76"/>
-      <c r="L114" s="77"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="78"/>
-      <c r="C115" s="79"/>
-      <c r="D115" s="80"/>
+      <c r="J114" s="77"/>
+      <c r="K114" s="78"/>
+      <c r="L114" s="79"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="80"/>
+      <c r="C115" s="81"/>
+      <c r="D115" s="82"/>
       <c r="E115" s="28"/>
-      <c r="F115" s="78"/>
-      <c r="G115" s="79"/>
-      <c r="H115" s="80"/>
+      <c r="F115" s="80"/>
+      <c r="G115" s="81"/>
+      <c r="H115" s="82"/>
       <c r="I115" s="28"/>
-      <c r="J115" s="78"/>
-      <c r="K115" s="79"/>
-      <c r="L115" s="80"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J115" s="80"/>
+      <c r="K115" s="81"/>
+      <c r="L115" s="82"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="32"/>
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
@@ -8580,72 +8592,72 @@
       <c r="K116" s="32"/>
       <c r="L116" s="32"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="91"/>
-      <c r="C117" s="92"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="93"/>
+      <c r="C117" s="94"/>
       <c r="D117" s="31"/>
       <c r="E117" s="29"/>
-      <c r="F117" s="91"/>
-      <c r="G117" s="92"/>
+      <c r="F117" s="93"/>
+      <c r="G117" s="94"/>
       <c r="H117" s="31"/>
       <c r="I117" s="29"/>
-      <c r="J117" s="91"/>
-      <c r="K117" s="92"/>
+      <c r="J117" s="93"/>
+      <c r="K117" s="94"/>
       <c r="L117" s="31"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="95"/>
-      <c r="C118" s="96"/>
-      <c r="D118" s="97"/>
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="97"/>
+      <c r="C118" s="98"/>
+      <c r="D118" s="99"/>
       <c r="E118" s="29"/>
-      <c r="F118" s="95"/>
-      <c r="G118" s="96"/>
-      <c r="H118" s="97"/>
+      <c r="F118" s="97"/>
+      <c r="G118" s="98"/>
+      <c r="H118" s="99"/>
       <c r="I118" s="29"/>
-      <c r="J118" s="95"/>
-      <c r="K118" s="96"/>
-      <c r="L118" s="97"/>
-    </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="98"/>
-      <c r="C119" s="99"/>
-      <c r="D119" s="100"/>
+      <c r="J118" s="97"/>
+      <c r="K118" s="98"/>
+      <c r="L118" s="99"/>
+    </row>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="100"/>
+      <c r="C119" s="101"/>
+      <c r="D119" s="102"/>
       <c r="E119" s="29"/>
-      <c r="F119" s="98"/>
-      <c r="G119" s="99"/>
-      <c r="H119" s="100"/>
+      <c r="F119" s="100"/>
+      <c r="G119" s="101"/>
+      <c r="H119" s="102"/>
       <c r="I119" s="29"/>
-      <c r="J119" s="98"/>
-      <c r="K119" s="99"/>
-      <c r="L119" s="100"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="75"/>
-      <c r="C120" s="76"/>
-      <c r="D120" s="77"/>
+      <c r="J119" s="100"/>
+      <c r="K119" s="101"/>
+      <c r="L119" s="102"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="77"/>
+      <c r="C120" s="78"/>
+      <c r="D120" s="79"/>
       <c r="E120" s="29"/>
-      <c r="F120" s="75"/>
-      <c r="G120" s="76"/>
-      <c r="H120" s="77"/>
+      <c r="F120" s="77"/>
+      <c r="G120" s="78"/>
+      <c r="H120" s="79"/>
       <c r="I120" s="29"/>
-      <c r="J120" s="75"/>
-      <c r="K120" s="76"/>
-      <c r="L120" s="77"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="78"/>
-      <c r="C121" s="79"/>
-      <c r="D121" s="80"/>
+      <c r="J120" s="77"/>
+      <c r="K120" s="78"/>
+      <c r="L120" s="79"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="80"/>
+      <c r="C121" s="81"/>
+      <c r="D121" s="82"/>
       <c r="E121" s="28"/>
-      <c r="F121" s="78"/>
-      <c r="G121" s="79"/>
-      <c r="H121" s="80"/>
+      <c r="F121" s="80"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="82"/>
       <c r="I121" s="28"/>
-      <c r="J121" s="78"/>
-      <c r="K121" s="79"/>
-      <c r="L121" s="80"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J121" s="80"/>
+      <c r="K121" s="81"/>
+      <c r="L121" s="82"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="32"/>
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
@@ -8658,72 +8670,72 @@
       <c r="K122" s="32"/>
       <c r="L122" s="32"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="91"/>
-      <c r="C123" s="92"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="93"/>
+      <c r="C123" s="94"/>
       <c r="D123" s="31"/>
       <c r="E123" s="29"/>
-      <c r="F123" s="91"/>
-      <c r="G123" s="92"/>
+      <c r="F123" s="93"/>
+      <c r="G123" s="94"/>
       <c r="H123" s="31"/>
       <c r="I123" s="29"/>
-      <c r="J123" s="91"/>
-      <c r="K123" s="92"/>
+      <c r="J123" s="93"/>
+      <c r="K123" s="94"/>
       <c r="L123" s="31"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="95"/>
-      <c r="C124" s="96"/>
-      <c r="D124" s="97"/>
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="97"/>
+      <c r="C124" s="98"/>
+      <c r="D124" s="99"/>
       <c r="E124" s="29"/>
-      <c r="F124" s="95"/>
-      <c r="G124" s="96"/>
-      <c r="H124" s="97"/>
+      <c r="F124" s="97"/>
+      <c r="G124" s="98"/>
+      <c r="H124" s="99"/>
       <c r="I124" s="29"/>
-      <c r="J124" s="95"/>
-      <c r="K124" s="96"/>
-      <c r="L124" s="97"/>
-    </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="98"/>
-      <c r="C125" s="99"/>
-      <c r="D125" s="100"/>
+      <c r="J124" s="97"/>
+      <c r="K124" s="98"/>
+      <c r="L124" s="99"/>
+    </row>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="100"/>
+      <c r="C125" s="101"/>
+      <c r="D125" s="102"/>
       <c r="E125" s="29"/>
-      <c r="F125" s="98"/>
-      <c r="G125" s="99"/>
-      <c r="H125" s="100"/>
+      <c r="F125" s="100"/>
+      <c r="G125" s="101"/>
+      <c r="H125" s="102"/>
       <c r="I125" s="29"/>
-      <c r="J125" s="98"/>
-      <c r="K125" s="99"/>
-      <c r="L125" s="100"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="75"/>
-      <c r="C126" s="76"/>
-      <c r="D126" s="77"/>
+      <c r="J125" s="100"/>
+      <c r="K125" s="101"/>
+      <c r="L125" s="102"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="77"/>
+      <c r="C126" s="78"/>
+      <c r="D126" s="79"/>
       <c r="E126" s="29"/>
-      <c r="F126" s="75"/>
-      <c r="G126" s="76"/>
-      <c r="H126" s="77"/>
+      <c r="F126" s="77"/>
+      <c r="G126" s="78"/>
+      <c r="H126" s="79"/>
       <c r="I126" s="28"/>
-      <c r="J126" s="75"/>
-      <c r="K126" s="76"/>
-      <c r="L126" s="77"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="78"/>
-      <c r="C127" s="79"/>
-      <c r="D127" s="80"/>
+      <c r="J126" s="77"/>
+      <c r="K126" s="78"/>
+      <c r="L126" s="79"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="80"/>
+      <c r="C127" s="81"/>
+      <c r="D127" s="82"/>
       <c r="E127" s="28"/>
-      <c r="F127" s="78"/>
-      <c r="G127" s="79"/>
-      <c r="H127" s="80"/>
+      <c r="F127" s="80"/>
+      <c r="G127" s="81"/>
+      <c r="H127" s="82"/>
       <c r="I127" s="28"/>
-      <c r="J127" s="78"/>
-      <c r="K127" s="79"/>
-      <c r="L127" s="80"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J127" s="80"/>
+      <c r="K127" s="81"/>
+      <c r="L127" s="82"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="32"/>
       <c r="C128" s="32"/>
       <c r="D128" s="32"/>
@@ -8736,70 +8748,70 @@
       <c r="K128" s="32"/>
       <c r="L128" s="32"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="91"/>
-      <c r="C129" s="92"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="93"/>
+      <c r="C129" s="94"/>
       <c r="D129" s="31"/>
       <c r="E129" s="28"/>
-      <c r="F129" s="91"/>
-      <c r="G129" s="92"/>
+      <c r="F129" s="93"/>
+      <c r="G129" s="94"/>
       <c r="H129" s="31"/>
       <c r="I129" s="29"/>
-      <c r="J129" s="91"/>
-      <c r="K129" s="92"/>
+      <c r="J129" s="93"/>
+      <c r="K129" s="94"/>
       <c r="L129" s="31"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="95"/>
-      <c r="C130" s="96"/>
-      <c r="D130" s="97"/>
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="97"/>
+      <c r="C130" s="98"/>
+      <c r="D130" s="99"/>
       <c r="E130" s="29"/>
-      <c r="F130" s="95"/>
-      <c r="G130" s="96"/>
-      <c r="H130" s="97"/>
+      <c r="F130" s="97"/>
+      <c r="G130" s="98"/>
+      <c r="H130" s="99"/>
       <c r="I130" s="29"/>
-      <c r="J130" s="95"/>
-      <c r="K130" s="96"/>
-      <c r="L130" s="97"/>
-    </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="98"/>
-      <c r="C131" s="99"/>
-      <c r="D131" s="100"/>
+      <c r="J130" s="97"/>
+      <c r="K130" s="98"/>
+      <c r="L130" s="99"/>
+    </row>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="100"/>
+      <c r="C131" s="101"/>
+      <c r="D131" s="102"/>
       <c r="E131" s="32"/>
-      <c r="F131" s="98"/>
-      <c r="G131" s="99"/>
-      <c r="H131" s="100"/>
+      <c r="F131" s="100"/>
+      <c r="G131" s="101"/>
+      <c r="H131" s="102"/>
       <c r="I131" s="29"/>
-      <c r="J131" s="98"/>
-      <c r="K131" s="99"/>
-      <c r="L131" s="100"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="75"/>
-      <c r="C132" s="76"/>
-      <c r="D132" s="77"/>
+      <c r="J131" s="100"/>
+      <c r="K131" s="101"/>
+      <c r="L131" s="102"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="77"/>
+      <c r="C132" s="78"/>
+      <c r="D132" s="79"/>
       <c r="E132" s="32"/>
-      <c r="F132" s="75"/>
-      <c r="G132" s="76"/>
-      <c r="H132" s="77"/>
+      <c r="F132" s="77"/>
+      <c r="G132" s="78"/>
+      <c r="H132" s="79"/>
       <c r="I132" s="28"/>
-      <c r="J132" s="75"/>
-      <c r="K132" s="76"/>
-      <c r="L132" s="77"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="78"/>
-      <c r="C133" s="79"/>
-      <c r="D133" s="80"/>
+      <c r="J132" s="77"/>
+      <c r="K132" s="78"/>
+      <c r="L132" s="79"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="80"/>
+      <c r="C133" s="81"/>
+      <c r="D133" s="82"/>
       <c r="E133" s="28"/>
-      <c r="F133" s="78"/>
-      <c r="G133" s="79"/>
-      <c r="H133" s="80"/>
+      <c r="F133" s="80"/>
+      <c r="G133" s="81"/>
+      <c r="H133" s="82"/>
       <c r="I133" s="28"/>
-      <c r="J133" s="78"/>
-      <c r="K133" s="79"/>
-      <c r="L133" s="80"/>
+      <c r="J133" s="80"/>
+      <c r="K133" s="81"/>
+      <c r="L133" s="82"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
@@ -8820,6 +8832,9 @@
     <mergeCell ref="AH63:AJ63"/>
     <mergeCell ref="AH62:AJ62"/>
     <mergeCell ref="AD58:AF58"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="N57:P57"/>
     <mergeCell ref="AL58:AN58"/>
     <mergeCell ref="AL63:AN63"/>
     <mergeCell ref="AL64:AN64"/>
@@ -9564,8 +9579,6 @@
     <mergeCell ref="R92:S92"/>
     <mergeCell ref="N93:P93"/>
     <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="AH57:AJ57"/>
     <mergeCell ref="V55:X55"/>
     <mergeCell ref="V54:X54"/>
     <mergeCell ref="F45:H45"/>
@@ -9584,7 +9597,10 @@
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="R54:T54"/>
-    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="AD53:AE53"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="R57:T57"/>
     <mergeCell ref="F43:H43"/>
@@ -9609,10 +9625,6 @@
     <mergeCell ref="AH51:AJ51"/>
     <mergeCell ref="AL51:AN51"/>
     <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="AD53:AE53"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="F69:G69"/>
     <mergeCell ref="Z69:AB69"/>
@@ -9691,7 +9703,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AF22:AF27 AB22:AB27 P22:P27 AB94:AB98 X22:X27 T22:T27 P36:P37 D58 H59 AJ22:AJ27 AF94:AF98 AN22:AN27 AJ94:AJ98 D22:D27 D70:D75 H70:H75 H22:H27 L22:L27 L59">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 J132:L133 J114:L115 B126:D127 F108:H109 B114:D115 J126:L127 J120:L121 B108:D109 R22:S27 AH8:AJ10 AH63:AJ64 AL56:AN58 Z102:AB102 N56:P58 AD56:AF58 V83:X84 AD22:AE27 R83:T84 N83:P84 N49:P51 V42:X44 AL77:AN78 V49:X51 V63:X64 N77:P78 R8:T10 AD89:AF90 V8:X10 AH42:AJ44 R63:T64 AL89:AN90 N22:O27 N101:P102 AD83:AF84 V101:X102 Z14:AB16 Z42:AB44 R14:T16 Z34:AB37 AH14:AJ16 B95:D96 AD34:AF37 V22:W27 R95:T96 B101:D102 N63:P64 R55:T58 AD8:AF10 R89:T90 J57:L58 AL14:AN16 N8:P10 V14:X16 R34:T37 V95:X96 AH83:AJ84 Z56:AB58 Z63:AB65 V56:X58 AL101:AN102 AL49:AN51 AL8:AN10 N42:P44 R77:T78 R42:T44 AL83:AN84 AD71:AF72 Z71:AB72 Z83:AB84 AH34:AJ37 AD63:AF65 AH77:AJ78 J59:K59 N14:P16 AL95:AN96 AH102:AJ102 V34:X37 N89:P90 AD94:AE98 N34:P35 AD42:AF44 Z89:AB90 Z94:AA98 AH71:AJ72 V89:X90 R71:T72 Z49:AB51 V71:X72 Z22:AA27 AL22:AM27 AH49:AJ51 Z77:AB78 AL71:AN72 N71:P72 Z8:AB10 AD77:AF78 AD14:AF16 R101:T102 R49:T50 N95:P96 AL63:AN64 V77:X78 AL42:AN44 AH56:AJ58 AH94:AI98 AD49:AF51 B58:C58 N36:O37 F101:H102 B22:C27 F95:H96 B14:D16 F22:G27 B83:D84 F14:H16 F63:H64 F89:H90 B42:D44 B70:C75 B89:D90 B49:D51 F59:G59 AD102:AF102 B63:D64 F51:H52 B8:D10 F42:H46 F83:H84 B34:D37 F8:H10 F34:H37 AH89:AJ90 F70:G75 F57:H58 B56:D57 J95:L96 J101:L102 J77:L78 J8:L10 J22:K27 J63:L64 J34:L37 J83:L84 J42:L46 J14:L16 J89:L90 J71:L72 J51:L52 AL34:AN37 AH22:AI27">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 J132:L133 J114:L115 B126:D127 F108:H109 B114:D115 J126:L127 J120:L121 B108:D109 R22:S27 AH83:AJ84 AH63:AJ64 AL56:AN58 Z102:AB102 N56:P58 AD56:AF58 V83:X84 AD22:AE27 R83:T84 N83:P84 N49:P51 V42:X44 AL77:AN78 V49:X51 V63:X64 N77:P78 R8:T10 AD89:AF90 V8:X10 AH42:AJ44 R63:T64 AL89:AN90 N22:O27 N101:P102 AD83:AF84 V101:X102 Z14:AB16 Z42:AB44 R14:T16 Z34:AB37 AH14:AJ16 B95:D96 AD34:AF37 V22:W27 R95:T96 B101:D102 N63:P64 R55:T58 AD8:AF10 R89:T90 J57:L58 AL14:AN16 N8:P10 V14:X16 R34:T37 V95:X96 AH22:AI27 Z56:AB58 Z63:AB65 V56:X58 AL101:AN102 AL49:AN51 AL8:AN10 N42:P44 R77:T78 R42:T44 AL83:AN84 AD71:AF72 Z71:AB72 Z83:AB84 AH34:AJ37 AD63:AF65 AH77:AJ78 J59:K59 N14:P16 AL95:AN96 AH102:AJ102 V34:X37 N89:P90 AD94:AE98 N34:P35 AD42:AF44 Z89:AB90 Z94:AA98 AH71:AJ72 V89:X90 R71:T72 Z49:AB51 V71:X72 Z22:AA27 AL22:AM27 AH49:AJ51 Z77:AB78 AL71:AN72 N71:P72 Z8:AB10 AD77:AF78 AD14:AF16 R101:T102 R49:T50 N95:P96 AL63:AN64 V77:X78 AL42:AN44 AH56:AJ58 AH94:AI98 AD49:AF51 B58:C58 N36:O37 F101:H102 B22:C27 F95:H96 B14:D16 F22:G27 B83:D84 F14:H16 F63:H64 F89:H90 B42:D44 B70:C75 B89:D90 B49:D51 F59:G59 AD102:AF102 B63:D64 F51:H52 B8:D10 F42:H46 F83:H84 B34:D37 F8:H10 F34:H37 AH89:AJ90 F70:G75 F57:H58 B56:D57 J95:L96 J101:L102 J77:L78 J8:L10 J22:K27 J63:L64 J34:L37 J83:L84 J42:L46 J14:L16 J89:L90 J71:L72 J51:L52 AL34:AN37 AH8:AJ10">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="102">
   <si>
     <t>CUMA</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>T.ERDEN.</t>
+  </si>
+  <si>
+    <t>A.KORUN.</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1409,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1568,6 +1571,45 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1586,213 +1628,183 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1811,14 +1823,20 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2269,65 +2287,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="104" t="s">
+      <c r="F1" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="104" t="s">
+      <c r="J1" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="104"/>
-      <c r="L1" s="105"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="131"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="108" t="s">
+      <c r="N1" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="102" t="s">
+      <c r="R1" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="102" t="s">
+      <c r="V1" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="102" t="s">
+      <c r="Z1" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="102" t="s">
+      <c r="AD1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="102"/>
+      <c r="AE1" s="124"/>
+      <c r="AF1" s="124"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="102" t="s">
+      <c r="AH1" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="102"/>
-      <c r="AJ1" s="102"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="102" t="s">
+      <c r="AL1" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="102"/>
-      <c r="AN1" s="115"/>
+      <c r="AM1" s="124"/>
+      <c r="AN1" s="125"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2335,74 +2353,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="106">
+      <c r="B2" s="132">
         <f>N2-3</f>
         <v>46192</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="107">
+      <c r="F2" s="133">
         <f>N2-2</f>
         <v>46193</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="107">
+      <c r="J2" s="133">
         <f>N2-1</f>
         <v>46194</v>
       </c>
-      <c r="K2" s="107"/>
-      <c r="L2" s="110"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="136"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="109">
+      <c r="N2" s="135">
         <v>46195</v>
       </c>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="101">
+      <c r="R2" s="126">
         <f>N2+1</f>
         <v>46196</v>
       </c>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="101">
+      <c r="V2" s="126">
         <f>N2+2</f>
         <v>46197</v>
       </c>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="101">
+      <c r="Z2" s="126">
         <f>N2+3</f>
         <v>46198</v>
       </c>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
+      <c r="AA2" s="126"/>
+      <c r="AB2" s="126"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="101">
+      <c r="AD2" s="126">
         <f>N2+4</f>
         <v>46199</v>
       </c>
-      <c r="AE2" s="101"/>
-      <c r="AF2" s="101"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="126"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="101">
+      <c r="AH2" s="126">
         <f>N2+5</f>
         <v>46200</v>
       </c>
-      <c r="AI2" s="101"/>
-      <c r="AJ2" s="101"/>
+      <c r="AI2" s="126"/>
+      <c r="AJ2" s="126"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="101">
+      <c r="AL2" s="126">
         <f>N2+6</f>
         <v>46201</v>
       </c>
-      <c r="AM2" s="101"/>
-      <c r="AN2" s="116"/>
+      <c r="AM2" s="126"/>
+      <c r="AN2" s="127"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2456,47 +2474,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="100" t="s">
+      <c r="N4" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="119"/>
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
+      <c r="W4" s="119"/>
+      <c r="X4" s="119"/>
+      <c r="Y4" s="119"/>
+      <c r="Z4" s="119"/>
+      <c r="AA4" s="119"/>
+      <c r="AB4" s="119"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="111"/>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
+      <c r="AD4" s="128"/>
+      <c r="AE4" s="128"/>
+      <c r="AF4" s="128"/>
+      <c r="AG4" s="128"/>
+      <c r="AH4" s="128"/>
+      <c r="AI4" s="128"/>
+      <c r="AJ4" s="128"/>
+      <c r="AK4" s="128"/>
+      <c r="AL4" s="128"/>
+      <c r="AM4" s="128"/>
+      <c r="AN4" s="128"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2504,101 +2522,101 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100"/>
-      <c r="V5" s="100"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="100"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="119"/>
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="119"/>
+      <c r="W5" s="119"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="111"/>
-      <c r="AE5" s="111"/>
-      <c r="AF5" s="111"/>
-      <c r="AG5" s="111"/>
-      <c r="AH5" s="111"/>
-      <c r="AI5" s="111"/>
-      <c r="AJ5" s="111"/>
-      <c r="AK5" s="111"/>
-      <c r="AL5" s="111"/>
-      <c r="AM5" s="111"/>
-      <c r="AN5" s="111"/>
+      <c r="AD5" s="128"/>
+      <c r="AE5" s="128"/>
+      <c r="AF5" s="128"/>
+      <c r="AG5" s="128"/>
+      <c r="AH5" s="128"/>
+      <c r="AI5" s="128"/>
+      <c r="AJ5" s="128"/>
+      <c r="AK5" s="128"/>
+      <c r="AL5" s="128"/>
+      <c r="AM5" s="128"/>
+      <c r="AN5" s="128"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="93"/>
-      <c r="C6" s="94"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="70"/>
       <c r="D6" s="61"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="95" t="s">
+      <c r="F6" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="96"/>
+      <c r="G6" s="75"/>
       <c r="H6" s="55" t="s">
         <v>46</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="94"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="70"/>
       <c r="L6" s="61"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="78"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="83"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="77" t="s">
+      <c r="R6" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="S6" s="78"/>
+      <c r="S6" s="83"/>
       <c r="T6" s="34" t="s">
         <v>46</v>
       </c>
       <c r="U6" s="36"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="78"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="83"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="77"/>
-      <c r="AA6" s="78"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="83"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="77" t="s">
+      <c r="AD6" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="AE6" s="78"/>
+      <c r="AE6" s="83"/>
       <c r="AF6" s="34" t="s">
         <v>73</v>
       </c>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="78"/>
+      <c r="AH6" s="82"/>
+      <c r="AI6" s="83"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="78"/>
+      <c r="AL6" s="82"/>
+      <c r="AM6" s="83"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2610,44 +2628,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="62"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="67"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="80"/>
       <c r="H7" s="62"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="67"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="80"/>
       <c r="L7" s="62"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="70"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="88"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="70"/>
+      <c r="R7" s="87"/>
+      <c r="S7" s="88"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="70"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="88"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="70"/>
+      <c r="Z7" s="87"/>
+      <c r="AA7" s="88"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="70"/>
+      <c r="AD7" s="87"/>
+      <c r="AE7" s="88"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="69"/>
-      <c r="AI7" s="70"/>
+      <c r="AH7" s="87"/>
+      <c r="AI7" s="88"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="69"/>
-      <c r="AM7" s="70"/>
+      <c r="AL7" s="87"/>
+      <c r="AM7" s="88"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2659,51 +2677,51 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="87"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="89"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="87" t="s">
+      <c r="F8" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="88"/>
-      <c r="H8" s="89"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="65"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="89"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="65"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="89"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="65"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="87" t="s">
+      <c r="R8" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="S8" s="88"/>
-      <c r="T8" s="89"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="65"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="89"/>
+      <c r="V8" s="63"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="65"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="89"/>
+      <c r="Z8" s="63"/>
+      <c r="AA8" s="64"/>
+      <c r="AB8" s="65"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="87" t="s">
+      <c r="AD8" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="88"/>
-      <c r="AF8" s="89"/>
+      <c r="AE8" s="64"/>
+      <c r="AF8" s="65"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="88"/>
-      <c r="AJ8" s="89"/>
+      <c r="AH8" s="63"/>
+      <c r="AI8" s="64"/>
+      <c r="AJ8" s="65"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="87"/>
-      <c r="AM8" s="88"/>
-      <c r="AN8" s="89"/>
+      <c r="AL8" s="63"/>
+      <c r="AM8" s="64"/>
+      <c r="AN8" s="65"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2714,45 +2732,45 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="63"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="65"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="78"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="65"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="78"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="65"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="78"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="65"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="78"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="65"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="78"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="65"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="77"/>
+      <c r="X9" s="78"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="65"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="77"/>
+      <c r="AB9" s="78"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="64"/>
-      <c r="AF9" s="65"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="77"/>
+      <c r="AF9" s="78"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="63"/>
-      <c r="AI9" s="64"/>
-      <c r="AJ9" s="65"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="77"/>
+      <c r="AJ9" s="78"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="63"/>
-      <c r="AM9" s="64"/>
-      <c r="AN9" s="65"/>
+      <c r="AL9" s="76"/>
+      <c r="AM9" s="77"/>
+      <c r="AN9" s="78"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2763,45 +2781,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="112"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="114"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="116"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="114"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="116"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="116"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="113"/>
-      <c r="P10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="115"/>
+      <c r="P10" s="116"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="112"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="114"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="115"/>
+      <c r="T10" s="116"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="112"/>
-      <c r="W10" s="113"/>
-      <c r="X10" s="114"/>
+      <c r="V10" s="114"/>
+      <c r="W10" s="115"/>
+      <c r="X10" s="116"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="112"/>
-      <c r="AA10" s="113"/>
-      <c r="AB10" s="114"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="115"/>
+      <c r="AB10" s="116"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="112"/>
-      <c r="AE10" s="113"/>
-      <c r="AF10" s="114"/>
+      <c r="AD10" s="114"/>
+      <c r="AE10" s="115"/>
+      <c r="AF10" s="116"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="112"/>
-      <c r="AI10" s="113"/>
-      <c r="AJ10" s="114"/>
+      <c r="AH10" s="114"/>
+      <c r="AI10" s="115"/>
+      <c r="AJ10" s="116"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="112"/>
-      <c r="AM10" s="113"/>
-      <c r="AN10" s="114"/>
+      <c r="AL10" s="114"/>
+      <c r="AM10" s="115"/>
+      <c r="AN10" s="116"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2861,44 +2879,44 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="93"/>
-      <c r="C12" s="94"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
       <c r="D12" s="61"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="94"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="70"/>
       <c r="H12" s="61"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="94"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="70"/>
       <c r="L12" s="61"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="78"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="83"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="78"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="83"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="78"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="83"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="78"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="83"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="78"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="83"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="77"/>
-      <c r="AI12" s="78"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="83"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="77"/>
-      <c r="AM12" s="78"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="83"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2910,45 +2928,45 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
       <c r="D13" s="62"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="84"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="73"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="84"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="73"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="81"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="86"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="80"/>
-      <c r="T13" s="81"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="86"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="79"/>
-      <c r="W13" s="80"/>
-      <c r="X13" s="81"/>
+      <c r="V13" s="84"/>
+      <c r="W13" s="85"/>
+      <c r="X13" s="86"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="70"/>
+      <c r="Z13" s="87"/>
+      <c r="AA13" s="88"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="69"/>
-      <c r="AE13" s="70"/>
+      <c r="AD13" s="87"/>
+      <c r="AE13" s="88"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="79"/>
-      <c r="AI13" s="80"/>
-      <c r="AJ13" s="81"/>
+      <c r="AH13" s="84"/>
+      <c r="AI13" s="85"/>
+      <c r="AJ13" s="86"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="79"/>
-      <c r="AM13" s="80"/>
-      <c r="AN13" s="81"/>
+      <c r="AL13" s="84"/>
+      <c r="AM13" s="85"/>
+      <c r="AN13" s="86"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2959,45 +2977,45 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="87"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="89"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="89"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="65"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="89"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="65"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="88"/>
-      <c r="P14" s="89"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="65"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="89"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="65"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="89"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="65"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="89"/>
+      <c r="Z14" s="63"/>
+      <c r="AA14" s="64"/>
+      <c r="AB14" s="65"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="89"/>
+      <c r="AD14" s="63"/>
+      <c r="AE14" s="64"/>
+      <c r="AF14" s="65"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="87"/>
-      <c r="AI14" s="88"/>
-      <c r="AJ14" s="89"/>
+      <c r="AH14" s="63"/>
+      <c r="AI14" s="64"/>
+      <c r="AJ14" s="65"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="87"/>
-      <c r="AM14" s="88"/>
-      <c r="AN14" s="89"/>
+      <c r="AL14" s="63"/>
+      <c r="AM14" s="64"/>
+      <c r="AN14" s="65"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -3008,45 +3026,45 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="63"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="65"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="78"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="65"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="78"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="65"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="78"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="63"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="65"/>
+      <c r="R15" s="76"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="78"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="63"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="65"/>
+      <c r="V15" s="76"/>
+      <c r="W15" s="77"/>
+      <c r="X15" s="78"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="64"/>
-      <c r="AB15" s="65"/>
+      <c r="Z15" s="76"/>
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="78"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="63"/>
-      <c r="AE15" s="64"/>
-      <c r="AF15" s="65"/>
+      <c r="AD15" s="76"/>
+      <c r="AE15" s="77"/>
+      <c r="AF15" s="78"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="63"/>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="65"/>
+      <c r="AH15" s="76"/>
+      <c r="AI15" s="77"/>
+      <c r="AJ15" s="78"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="63"/>
-      <c r="AM15" s="64"/>
-      <c r="AN15" s="65"/>
+      <c r="AL15" s="76"/>
+      <c r="AM15" s="77"/>
+      <c r="AN15" s="78"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3057,45 +3075,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="112"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="114"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="116"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="114"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="116"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="116"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="114"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="116"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="115"/>
+      <c r="T16" s="116"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="112"/>
-      <c r="W16" s="113"/>
-      <c r="X16" s="114"/>
+      <c r="V16" s="114"/>
+      <c r="W16" s="115"/>
+      <c r="X16" s="116"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="112"/>
-      <c r="AA16" s="113"/>
-      <c r="AB16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="115"/>
+      <c r="AB16" s="116"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="112"/>
-      <c r="AE16" s="113"/>
-      <c r="AF16" s="114"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="115"/>
+      <c r="AF16" s="116"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="112"/>
-      <c r="AI16" s="113"/>
-      <c r="AJ16" s="114"/>
+      <c r="AH16" s="114"/>
+      <c r="AI16" s="115"/>
+      <c r="AJ16" s="116"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="112"/>
-      <c r="AM16" s="113"/>
-      <c r="AN16" s="114"/>
+      <c r="AL16" s="114"/>
+      <c r="AM16" s="115"/>
+      <c r="AN16" s="116"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3169,23 +3187,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="100" t="s">
+      <c r="N18" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="100"/>
-      <c r="T18" s="100"/>
-      <c r="U18" s="100"/>
-      <c r="V18" s="100"/>
-      <c r="W18" s="100"/>
-      <c r="X18" s="100"/>
-      <c r="Y18" s="100"/>
-      <c r="Z18" s="100"/>
-      <c r="AA18" s="100"/>
-      <c r="AB18" s="100"/>
+      <c r="O18" s="119"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="119"/>
+      <c r="U18" s="119"/>
+      <c r="V18" s="119"/>
+      <c r="W18" s="119"/>
+      <c r="X18" s="119"/>
+      <c r="Y18" s="119"/>
+      <c r="Z18" s="119"/>
+      <c r="AA18" s="119"/>
+      <c r="AB18" s="119"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3220,21 +3238,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="100"/>
-      <c r="W19" s="100"/>
-      <c r="X19" s="100"/>
-      <c r="Y19" s="100"/>
-      <c r="Z19" s="100"/>
-      <c r="AA19" s="100"/>
-      <c r="AB19" s="100"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="119"/>
+      <c r="U19" s="119"/>
+      <c r="V19" s="119"/>
+      <c r="W19" s="119"/>
+      <c r="X19" s="119"/>
+      <c r="Y19" s="119"/>
+      <c r="Z19" s="119"/>
+      <c r="AA19" s="119"/>
+      <c r="AB19" s="119"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3257,78 +3275,78 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="94"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="61" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="36"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="94"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="70"/>
       <c r="H20" s="61"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="95" t="s">
+      <c r="J20" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="96"/>
+      <c r="K20" s="75"/>
       <c r="L20" s="55" t="s">
         <v>81</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="77" t="s">
+      <c r="N20" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="O20" s="78"/>
+      <c r="O20" s="83"/>
       <c r="P20" s="34" t="s">
         <v>50</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="119" t="s">
+      <c r="R20" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="S20" s="120"/>
+      <c r="S20" s="121"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="119" t="s">
+      <c r="V20" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="W20" s="120"/>
+      <c r="W20" s="121"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="77" t="s">
+      <c r="Z20" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AA20" s="78"/>
+      <c r="AA20" s="83"/>
       <c r="AB20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="77" t="s">
+      <c r="AD20" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AE20" s="78"/>
+      <c r="AE20" s="83"/>
       <c r="AF20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="77" t="s">
+      <c r="AH20" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AI20" s="78"/>
+      <c r="AI20" s="83"/>
       <c r="AJ20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="77" t="s">
+      <c r="AL20" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="AM20" s="78"/>
+      <c r="AM20" s="83"/>
       <c r="AN20" s="34" t="s">
         <v>81</v>
       </c>
@@ -3342,44 +3360,44 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="62"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="67"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="80"/>
       <c r="H21" s="62"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="67"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="80"/>
       <c r="L21" s="62"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="70"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="88"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="70"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="88"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="117"/>
-      <c r="W21" s="118"/>
+      <c r="V21" s="122"/>
+      <c r="W21" s="123"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="70"/>
+      <c r="Z21" s="87"/>
+      <c r="AA21" s="88"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="69"/>
-      <c r="AE21" s="70"/>
+      <c r="AD21" s="87"/>
+      <c r="AE21" s="88"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="70"/>
+      <c r="AH21" s="87"/>
+      <c r="AI21" s="88"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="69"/>
-      <c r="AM21" s="70"/>
+      <c r="AL21" s="87"/>
+      <c r="AM21" s="88"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3391,78 +3409,78 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="72"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="37"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="72"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="140"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="71" t="s">
+      <c r="J22" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="72"/>
+      <c r="K22" s="140"/>
       <c r="L22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="91" t="s">
+      <c r="N22" s="137" t="s">
         <v>7</v>
       </c>
-      <c r="O22" s="92"/>
+      <c r="O22" s="138"/>
       <c r="P22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="71" t="s">
+      <c r="R22" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="S22" s="72"/>
+      <c r="S22" s="140"/>
       <c r="T22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="37"/>
-      <c r="V22" s="91" t="s">
+      <c r="V22" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="92"/>
+      <c r="W22" s="138"/>
       <c r="X22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="71" t="s">
+      <c r="Z22" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="AA22" s="72"/>
+      <c r="AA22" s="140"/>
       <c r="AB22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="71" t="s">
+      <c r="AD22" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="AE22" s="72"/>
+      <c r="AE22" s="140"/>
       <c r="AF22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="71" t="s">
+      <c r="AH22" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="AI22" s="72"/>
+      <c r="AI22" s="140"/>
       <c r="AJ22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="71" t="s">
+      <c r="AL22" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="AM22" s="72"/>
+      <c r="AM22" s="140"/>
       <c r="AN22" s="41" t="s">
         <v>32</v>
       </c>
@@ -3478,78 +3496,78 @@
       </c>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="74"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="74"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="118"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="73" t="s">
+      <c r="J23" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="74"/>
+      <c r="K23" s="118"/>
       <c r="L23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="73" t="s">
+      <c r="N23" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="O23" s="74"/>
+      <c r="O23" s="118"/>
       <c r="P23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q23" s="43"/>
-      <c r="R23" s="73" t="s">
+      <c r="R23" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="74"/>
+      <c r="S23" s="118"/>
       <c r="T23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U23" s="43"/>
-      <c r="V23" s="73" t="s">
+      <c r="V23" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="W23" s="74"/>
+      <c r="W23" s="118"/>
       <c r="X23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="73" t="s">
+      <c r="Z23" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="AA23" s="74"/>
+      <c r="AA23" s="118"/>
       <c r="AB23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="73" t="s">
+      <c r="AD23" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="AE23" s="74"/>
+      <c r="AE23" s="118"/>
       <c r="AF23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="73" t="s">
+      <c r="AH23" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="AI23" s="74"/>
+      <c r="AI23" s="118"/>
       <c r="AJ23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="73" t="s">
+      <c r="AL23" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="AM23" s="74"/>
+      <c r="AM23" s="118"/>
       <c r="AN23" s="45" t="s">
         <v>33</v>
       </c>
@@ -3563,78 +3581,78 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="76"/>
+      <c r="C24" s="105"/>
       <c r="D24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="76"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="105"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="75" t="s">
+      <c r="J24" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="76"/>
+      <c r="K24" s="105"/>
       <c r="L24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="75" t="s">
+      <c r="N24" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="76"/>
+      <c r="O24" s="105"/>
       <c r="P24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q24" s="43"/>
-      <c r="R24" s="75" t="s">
+      <c r="R24" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="S24" s="76"/>
+      <c r="S24" s="105"/>
       <c r="T24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="44"/>
-      <c r="V24" s="75" t="s">
+      <c r="V24" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="76"/>
+      <c r="W24" s="105"/>
       <c r="X24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="75" t="s">
+      <c r="Z24" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="AA24" s="76"/>
+      <c r="AA24" s="105"/>
       <c r="AB24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="75" t="s">
+      <c r="AD24" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="AE24" s="76"/>
+      <c r="AE24" s="105"/>
       <c r="AF24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="75" t="s">
+      <c r="AH24" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="AI24" s="76"/>
+      <c r="AI24" s="105"/>
       <c r="AJ24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="75" t="s">
+      <c r="AL24" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="AM24" s="76"/>
+      <c r="AM24" s="105"/>
       <c r="AN24" s="45" t="s">
         <v>34</v>
       </c>
@@ -3648,78 +3666,78 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="76"/>
+      <c r="C25" s="105"/>
       <c r="D25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="76"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="105"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="75" t="s">
+      <c r="J25" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="76"/>
+      <c r="K25" s="105"/>
       <c r="L25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="75" t="s">
+      <c r="N25" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="76"/>
+      <c r="O25" s="105"/>
       <c r="P25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q25" s="44"/>
-      <c r="R25" s="75" t="s">
+      <c r="R25" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="S25" s="76"/>
+      <c r="S25" s="105"/>
       <c r="T25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="44"/>
-      <c r="V25" s="75" t="s">
+      <c r="V25" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="W25" s="76"/>
+      <c r="W25" s="105"/>
       <c r="X25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="75" t="s">
+      <c r="Z25" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="AA25" s="76"/>
+      <c r="AA25" s="105"/>
       <c r="AB25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="75" t="s">
+      <c r="AD25" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="AE25" s="76"/>
+      <c r="AE25" s="105"/>
       <c r="AF25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI25" s="76"/>
+      <c r="AH25" s="150" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI25" s="151"/>
       <c r="AJ25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="75" t="s">
+      <c r="AL25" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="AM25" s="76"/>
+      <c r="AM25" s="105"/>
       <c r="AN25" s="45" t="s">
         <v>35</v>
       </c>
@@ -3733,78 +3751,78 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="76"/>
+      <c r="C26" s="105"/>
       <c r="D26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="76"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="105"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="75" t="s">
+      <c r="J26" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="76"/>
+      <c r="K26" s="105"/>
       <c r="L26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="75" t="s">
+      <c r="N26" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="O26" s="76"/>
+      <c r="O26" s="105"/>
       <c r="P26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q26" s="44"/>
-      <c r="R26" s="75" t="s">
+      <c r="R26" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="S26" s="76"/>
+      <c r="S26" s="105"/>
       <c r="T26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="44"/>
-      <c r="V26" s="75" t="s">
+      <c r="V26" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="W26" s="76"/>
+      <c r="W26" s="105"/>
       <c r="X26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="75" t="s">
+      <c r="Z26" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="AA26" s="76"/>
+      <c r="AA26" s="105"/>
       <c r="AB26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="75" t="s">
+      <c r="AD26" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="AE26" s="76"/>
+      <c r="AE26" s="105"/>
       <c r="AF26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="75" t="s">
+      <c r="AH26" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="AI26" s="76"/>
+      <c r="AI26" s="105"/>
       <c r="AJ26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="75" t="s">
+      <c r="AL26" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="AM26" s="76"/>
+      <c r="AM26" s="105"/>
       <c r="AN26" s="45" t="s">
         <v>35</v>
       </c>
@@ -3818,44 +3836,44 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="86"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="107"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="107"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="86"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="107"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="85"/>
-      <c r="S27" s="86"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="107"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="85"/>
-      <c r="W27" s="86"/>
+      <c r="V27" s="106"/>
+      <c r="W27" s="107"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="86"/>
+      <c r="Z27" s="106"/>
+      <c r="AA27" s="107"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="85"/>
-      <c r="AE27" s="86"/>
+      <c r="AD27" s="106"/>
+      <c r="AE27" s="107"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="85"/>
-      <c r="AI27" s="86"/>
+      <c r="AH27" s="106"/>
+      <c r="AI27" s="107"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="85"/>
-      <c r="AM27" s="86"/>
+      <c r="AL27" s="106"/>
+      <c r="AM27" s="107"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3928,23 +3946,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="100" t="s">
+      <c r="N29" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="100"/>
-      <c r="T29" s="100"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
-      <c r="W29" s="100"/>
-      <c r="X29" s="100"/>
-      <c r="Y29" s="100"/>
-      <c r="Z29" s="100"/>
-      <c r="AA29" s="100"/>
-      <c r="AB29" s="100"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="119"/>
+      <c r="Q29" s="119"/>
+      <c r="R29" s="119"/>
+      <c r="S29" s="119"/>
+      <c r="T29" s="119"/>
+      <c r="U29" s="119"/>
+      <c r="V29" s="119"/>
+      <c r="W29" s="119"/>
+      <c r="X29" s="119"/>
+      <c r="Y29" s="119"/>
+      <c r="Z29" s="119"/>
+      <c r="AA29" s="119"/>
+      <c r="AB29" s="119"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3979,21 +3997,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="100"/>
-      <c r="Q30" s="100"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
-      <c r="T30" s="100"/>
-      <c r="U30" s="100"/>
-      <c r="V30" s="100"/>
-      <c r="W30" s="100"/>
-      <c r="X30" s="100"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="100"/>
-      <c r="AA30" s="100"/>
-      <c r="AB30" s="100"/>
+      <c r="N30" s="119"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="119"/>
+      <c r="Q30" s="119"/>
+      <c r="R30" s="119"/>
+      <c r="S30" s="119"/>
+      <c r="T30" s="119"/>
+      <c r="U30" s="119"/>
+      <c r="V30" s="119"/>
+      <c r="W30" s="119"/>
+      <c r="X30" s="119"/>
+      <c r="Y30" s="119"/>
+      <c r="Z30" s="119"/>
+      <c r="AA30" s="119"/>
+      <c r="AB30" s="119"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -4016,234 +4034,234 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="94"/>
+      <c r="C31" s="70"/>
       <c r="D31" s="61" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="36"/>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="94"/>
+      <c r="G31" s="70"/>
       <c r="H31" s="61" t="s">
         <v>44</v>
       </c>
       <c r="I31" s="36"/>
-      <c r="J31" s="93" t="s">
+      <c r="J31" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="K31" s="94"/>
+      <c r="K31" s="70"/>
       <c r="L31" s="61" t="s">
         <v>48</v>
       </c>
       <c r="M31" s="6"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="78"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="83"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="77" t="s">
+      <c r="R31" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="S31" s="78"/>
+      <c r="S31" s="83"/>
       <c r="T31" s="34" t="s">
         <v>83</v>
       </c>
       <c r="U31" s="36"/>
-      <c r="V31" s="77"/>
-      <c r="W31" s="78"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="83"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="77" t="s">
+      <c r="Z31" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="AA31" s="78"/>
+      <c r="AA31" s="83"/>
       <c r="AB31" s="34" t="s">
         <v>86</v>
       </c>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="77" t="s">
+      <c r="AD31" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="AE31" s="78"/>
+      <c r="AE31" s="83"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="77" t="s">
+      <c r="AH31" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="AI31" s="78"/>
+      <c r="AI31" s="83"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="77" t="s">
+      <c r="AL31" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="AM31" s="78"/>
+      <c r="AM31" s="83"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="82" t="s">
+      <c r="B32" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="83"/>
-      <c r="D32" s="84"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="73"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="82" t="s">
+      <c r="F32" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="84"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="73"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="82" t="s">
+      <c r="J32" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="K32" s="83"/>
-      <c r="L32" s="84"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="81"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="79" t="s">
+      <c r="R32" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="S32" s="80"/>
-      <c r="T32" s="81"/>
+      <c r="S32" s="85"/>
+      <c r="T32" s="86"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="79"/>
-      <c r="W32" s="80"/>
-      <c r="X32" s="81"/>
+      <c r="V32" s="84"/>
+      <c r="W32" s="85"/>
+      <c r="X32" s="86"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="79" t="s">
+      <c r="Z32" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="AA32" s="80"/>
-      <c r="AB32" s="81"/>
+      <c r="AA32" s="85"/>
+      <c r="AB32" s="86"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="79" t="s">
+      <c r="AD32" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="AE32" s="80"/>
-      <c r="AF32" s="81"/>
+      <c r="AE32" s="85"/>
+      <c r="AF32" s="86"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="79" t="s">
+      <c r="AH32" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="AI32" s="80"/>
-      <c r="AJ32" s="81"/>
+      <c r="AI32" s="85"/>
+      <c r="AJ32" s="86"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="79" t="s">
+      <c r="AL32" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="AM32" s="80"/>
-      <c r="AN32" s="81"/>
+      <c r="AM32" s="85"/>
+      <c r="AN32" s="86"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="66"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="68"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="68"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="81"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="68"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="81"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="90"/>
+      <c r="N33" s="87"/>
+      <c r="O33" s="88"/>
+      <c r="P33" s="89"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="70"/>
-      <c r="T33" s="90"/>
+      <c r="R33" s="87"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="89"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="69"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="90"/>
+      <c r="V33" s="87"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="89"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="69"/>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="90"/>
+      <c r="Z33" s="87"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="89"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="69"/>
-      <c r="AE33" s="70"/>
-      <c r="AF33" s="90"/>
+      <c r="AD33" s="87"/>
+      <c r="AE33" s="88"/>
+      <c r="AF33" s="89"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="69"/>
-      <c r="AI33" s="70"/>
-      <c r="AJ33" s="90"/>
+      <c r="AH33" s="87"/>
+      <c r="AI33" s="88"/>
+      <c r="AJ33" s="89"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="69"/>
-      <c r="AM33" s="70"/>
-      <c r="AN33" s="90"/>
+      <c r="AL33" s="87"/>
+      <c r="AM33" s="88"/>
+      <c r="AN33" s="89"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="78"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="63" t="s">
+      <c r="F34" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="64"/>
-      <c r="H34" s="65"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="78"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="63" t="s">
+      <c r="J34" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="64"/>
-      <c r="L34" s="65"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="78"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="87"/>
-      <c r="O34" s="88"/>
-      <c r="P34" s="89"/>
+      <c r="N34" s="63"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="65"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="87" t="s">
+      <c r="R34" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="89"/>
+      <c r="S34" s="64"/>
+      <c r="T34" s="65"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="87"/>
-      <c r="W34" s="88"/>
-      <c r="X34" s="89"/>
+      <c r="V34" s="63"/>
+      <c r="W34" s="64"/>
+      <c r="X34" s="65"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="87" t="s">
+      <c r="Z34" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="AA34" s="88"/>
-      <c r="AB34" s="89"/>
+      <c r="AA34" s="64"/>
+      <c r="AB34" s="65"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="63" t="s">
+      <c r="AD34" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AE34" s="64"/>
-      <c r="AF34" s="65"/>
+      <c r="AE34" s="77"/>
+      <c r="AF34" s="78"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="63" t="s">
+      <c r="AH34" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="65"/>
+      <c r="AI34" s="77"/>
+      <c r="AJ34" s="78"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="63" t="s">
+      <c r="AL34" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AM34" s="64"/>
-      <c r="AN34" s="65"/>
+      <c r="AM34" s="77"/>
+      <c r="AN34" s="78"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -4251,106 +4269,106 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="65"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="78"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="63" t="s">
+      <c r="F35" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="64"/>
-      <c r="H35" s="65"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="78"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="63" t="s">
+      <c r="J35" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="64"/>
-      <c r="L35" s="65"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="78"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="65"/>
+      <c r="N35" s="76"/>
+      <c r="O35" s="77"/>
+      <c r="P35" s="78"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="63" t="s">
+      <c r="R35" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="S35" s="64"/>
-      <c r="T35" s="65"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="78"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="63"/>
-      <c r="W35" s="64"/>
-      <c r="X35" s="65"/>
+      <c r="V35" s="76"/>
+      <c r="W35" s="77"/>
+      <c r="X35" s="78"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="63" t="s">
+      <c r="Z35" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="AA35" s="64"/>
-      <c r="AB35" s="65"/>
+      <c r="AA35" s="77"/>
+      <c r="AB35" s="78"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="63" t="s">
+      <c r="AD35" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="AE35" s="64"/>
-      <c r="AF35" s="65"/>
+      <c r="AE35" s="77"/>
+      <c r="AF35" s="78"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="63" t="s">
+      <c r="AH35" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="AI35" s="64"/>
-      <c r="AJ35" s="65"/>
+      <c r="AI35" s="77"/>
+      <c r="AJ35" s="78"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="63" t="s">
+      <c r="AL35" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="AM35" s="64"/>
-      <c r="AN35" s="65"/>
+      <c r="AM35" s="77"/>
+      <c r="AN35" s="78"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="99"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="68"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="97"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="99"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="68"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="99"/>
+      <c r="J36" s="66"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="68"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="97"/>
-      <c r="O36" s="98"/>
-      <c r="P36" s="99"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="68"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="97"/>
-      <c r="S36" s="98"/>
-      <c r="T36" s="99"/>
+      <c r="R36" s="66"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="68"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="97"/>
-      <c r="W36" s="98"/>
-      <c r="X36" s="99"/>
+      <c r="V36" s="66"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="68"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="97"/>
-      <c r="AA36" s="98"/>
-      <c r="AB36" s="99"/>
+      <c r="Z36" s="66"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="68"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="97"/>
-      <c r="AE36" s="98"/>
-      <c r="AF36" s="99"/>
+      <c r="AD36" s="66"/>
+      <c r="AE36" s="67"/>
+      <c r="AF36" s="68"/>
       <c r="AG36" s="44"/>
-      <c r="AH36" s="97"/>
-      <c r="AI36" s="98"/>
-      <c r="AJ36" s="99"/>
+      <c r="AH36" s="66"/>
+      <c r="AI36" s="67"/>
+      <c r="AJ36" s="68"/>
       <c r="AK36" s="44"/>
-      <c r="AL36" s="97"/>
-      <c r="AM36" s="98"/>
-      <c r="AN36" s="99"/>
+      <c r="AL36" s="66"/>
+      <c r="AM36" s="67"/>
+      <c r="AN36" s="68"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -4404,58 +4422,58 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="93" t="s">
+      <c r="B38" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="94"/>
+      <c r="C38" s="70"/>
       <c r="D38" s="61" t="s">
         <v>61</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="93" t="s">
+      <c r="F38" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G38" s="94"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="61" t="s">
         <v>62</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="95" t="s">
+      <c r="J38" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="K38" s="96"/>
+      <c r="K38" s="75"/>
       <c r="L38" s="55" t="s">
         <v>61</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="78"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="83"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="78"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="83"/>
       <c r="T38" s="34"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="78"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="83"/>
       <c r="X38" s="34"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="77"/>
-      <c r="AA38" s="78"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="83"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="77"/>
-      <c r="AE38" s="78"/>
+      <c r="AD38" s="82"/>
+      <c r="AE38" s="83"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="77"/>
-      <c r="AI38" s="78"/>
+      <c r="AH38" s="82"/>
+      <c r="AI38" s="83"/>
       <c r="AJ38" s="34"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="77" t="s">
+      <c r="AL38" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="AM38" s="78"/>
+      <c r="AM38" s="83"/>
       <c r="AN38" s="34"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
@@ -4464,53 +4482,53 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="82" t="s">
+      <c r="B39" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="83"/>
-      <c r="D39" s="84"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="73"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="82" t="s">
+      <c r="F39" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="83"/>
-      <c r="H39" s="84"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="73"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="82" t="s">
+      <c r="J39" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="K39" s="83"/>
-      <c r="L39" s="84"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="73"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="79"/>
-      <c r="O39" s="80"/>
-      <c r="P39" s="81"/>
+      <c r="N39" s="84"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="86"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="79"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="81"/>
+      <c r="R39" s="84"/>
+      <c r="S39" s="85"/>
+      <c r="T39" s="86"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="79"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="81"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="85"/>
+      <c r="X39" s="86"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="79"/>
-      <c r="AA39" s="80"/>
-      <c r="AB39" s="81"/>
+      <c r="Z39" s="84"/>
+      <c r="AA39" s="85"/>
+      <c r="AB39" s="86"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="79"/>
-      <c r="AE39" s="80"/>
-      <c r="AF39" s="81"/>
+      <c r="AD39" s="84"/>
+      <c r="AE39" s="85"/>
+      <c r="AF39" s="86"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="79"/>
-      <c r="AI39" s="80"/>
-      <c r="AJ39" s="81"/>
+      <c r="AH39" s="84"/>
+      <c r="AI39" s="85"/>
+      <c r="AJ39" s="86"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="79" t="s">
+      <c r="AL39" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="AM39" s="80"/>
-      <c r="AN39" s="81"/>
+      <c r="AM39" s="85"/>
+      <c r="AN39" s="86"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4518,45 +4536,45 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="66"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="68"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="81"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="68"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="81"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="68"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="81"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="90"/>
+      <c r="N40" s="87"/>
+      <c r="O40" s="88"/>
+      <c r="P40" s="89"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="69"/>
-      <c r="S40" s="70"/>
-      <c r="T40" s="90"/>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
+      <c r="T40" s="89"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="69"/>
-      <c r="W40" s="70"/>
-      <c r="X40" s="90"/>
+      <c r="V40" s="87"/>
+      <c r="W40" s="88"/>
+      <c r="X40" s="89"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="69"/>
-      <c r="AA40" s="70"/>
-      <c r="AB40" s="90"/>
+      <c r="Z40" s="87"/>
+      <c r="AA40" s="88"/>
+      <c r="AB40" s="89"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="69"/>
-      <c r="AE40" s="70"/>
-      <c r="AF40" s="90"/>
+      <c r="AD40" s="87"/>
+      <c r="AE40" s="88"/>
+      <c r="AF40" s="89"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="69"/>
-      <c r="AI40" s="70"/>
-      <c r="AJ40" s="90"/>
+      <c r="AH40" s="87"/>
+      <c r="AI40" s="88"/>
+      <c r="AJ40" s="89"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="69"/>
-      <c r="AM40" s="70"/>
-      <c r="AN40" s="90"/>
+      <c r="AL40" s="87"/>
+      <c r="AM40" s="88"/>
+      <c r="AN40" s="89"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4564,53 +4582,53 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="65"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="64"/>
-      <c r="H41" s="65"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="78"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="87" t="s">
+      <c r="J41" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="88"/>
-      <c r="L41" s="89"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="65"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="88"/>
-      <c r="P41" s="89"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="64"/>
+      <c r="P41" s="65"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="87"/>
-      <c r="S41" s="88"/>
-      <c r="T41" s="89"/>
+      <c r="R41" s="63"/>
+      <c r="S41" s="64"/>
+      <c r="T41" s="65"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="87"/>
-      <c r="W41" s="88"/>
-      <c r="X41" s="89"/>
+      <c r="V41" s="63"/>
+      <c r="W41" s="64"/>
+      <c r="X41" s="65"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="87"/>
-      <c r="AA41" s="88"/>
-      <c r="AB41" s="89"/>
+      <c r="Z41" s="63"/>
+      <c r="AA41" s="64"/>
+      <c r="AB41" s="65"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="63"/>
-      <c r="AE41" s="64"/>
-      <c r="AF41" s="65"/>
+      <c r="AD41" s="76"/>
+      <c r="AE41" s="77"/>
+      <c r="AF41" s="78"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="63"/>
-      <c r="AI41" s="64"/>
-      <c r="AJ41" s="65"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
+      <c r="AJ41" s="78"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="87" t="s">
+      <c r="AL41" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="AM41" s="88"/>
-      <c r="AN41" s="89"/>
+      <c r="AM41" s="64"/>
+      <c r="AN41" s="65"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4618,53 +4636,53 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="65"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="78"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="63" t="s">
+      <c r="F42" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="64"/>
-      <c r="H42" s="65"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="78"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="63" t="s">
+      <c r="J42" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="K42" s="64"/>
-      <c r="L42" s="65"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="63"/>
-      <c r="O42" s="64"/>
-      <c r="P42" s="65"/>
+      <c r="N42" s="76"/>
+      <c r="O42" s="77"/>
+      <c r="P42" s="78"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="63"/>
-      <c r="S42" s="64"/>
-      <c r="T42" s="65"/>
+      <c r="R42" s="76"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="78"/>
       <c r="U42" s="44"/>
-      <c r="V42" s="63"/>
-      <c r="W42" s="64"/>
-      <c r="X42" s="65"/>
+      <c r="V42" s="76"/>
+      <c r="W42" s="77"/>
+      <c r="X42" s="78"/>
       <c r="Y42" s="50"/>
-      <c r="Z42" s="63"/>
-      <c r="AA42" s="64"/>
-      <c r="AB42" s="65"/>
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="77"/>
+      <c r="AB42" s="78"/>
       <c r="AC42" s="44"/>
-      <c r="AD42" s="63"/>
-      <c r="AE42" s="64"/>
-      <c r="AF42" s="65"/>
+      <c r="AD42" s="76"/>
+      <c r="AE42" s="77"/>
+      <c r="AF42" s="78"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="63"/>
-      <c r="AI42" s="64"/>
-      <c r="AJ42" s="65"/>
+      <c r="AH42" s="76"/>
+      <c r="AI42" s="77"/>
+      <c r="AJ42" s="78"/>
       <c r="AK42" s="44"/>
-      <c r="AL42" s="63" t="s">
+      <c r="AL42" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="AM42" s="64"/>
-      <c r="AN42" s="65"/>
+      <c r="AM42" s="77"/>
+      <c r="AN42" s="78"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4672,45 +4690,45 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="97"/>
-      <c r="C43" s="98"/>
-      <c r="D43" s="99"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="67"/>
+      <c r="D43" s="68"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="98"/>
-      <c r="H43" s="99"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="68"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="97"/>
-      <c r="K43" s="98"/>
-      <c r="L43" s="99"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="68"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="97"/>
-      <c r="O43" s="98"/>
-      <c r="P43" s="99"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="67"/>
+      <c r="P43" s="68"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="97"/>
-      <c r="S43" s="98"/>
-      <c r="T43" s="99"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="68"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="97"/>
-      <c r="W43" s="98"/>
-      <c r="X43" s="99"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="67"/>
+      <c r="X43" s="68"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="97"/>
-      <c r="AA43" s="98"/>
-      <c r="AB43" s="99"/>
+      <c r="Z43" s="66"/>
+      <c r="AA43" s="67"/>
+      <c r="AB43" s="68"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="97"/>
-      <c r="AE43" s="98"/>
-      <c r="AF43" s="99"/>
+      <c r="AD43" s="66"/>
+      <c r="AE43" s="67"/>
+      <c r="AF43" s="68"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="97"/>
-      <c r="AI43" s="98"/>
-      <c r="AJ43" s="99"/>
+      <c r="AH43" s="66"/>
+      <c r="AI43" s="67"/>
+      <c r="AJ43" s="68"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="97"/>
-      <c r="AM43" s="98"/>
-      <c r="AN43" s="99"/>
+      <c r="AL43" s="66"/>
+      <c r="AM43" s="67"/>
+      <c r="AN43" s="68"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4764,52 +4782,52 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="95" t="s">
+      <c r="B45" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="96"/>
+      <c r="C45" s="75"/>
       <c r="D45" s="55"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="93" t="s">
+      <c r="F45" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G45" s="94"/>
+      <c r="G45" s="70"/>
       <c r="H45" s="61" t="s">
         <v>44</v>
       </c>
       <c r="I45" s="50"/>
-      <c r="J45" s="95" t="s">
+      <c r="J45" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="96"/>
+      <c r="K45" s="75"/>
       <c r="L45" s="55"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="77"/>
-      <c r="O45" s="78"/>
+      <c r="N45" s="82"/>
+      <c r="O45" s="83"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="77"/>
-      <c r="S45" s="78"/>
+      <c r="R45" s="82"/>
+      <c r="S45" s="83"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="77"/>
-      <c r="W45" s="78"/>
+      <c r="V45" s="82"/>
+      <c r="W45" s="83"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="77"/>
-      <c r="AA45" s="78"/>
+      <c r="Z45" s="82"/>
+      <c r="AA45" s="83"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="77"/>
-      <c r="AE45" s="78"/>
+      <c r="AD45" s="82"/>
+      <c r="AE45" s="83"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="77"/>
-      <c r="AI45" s="78"/>
+      <c r="AH45" s="82"/>
+      <c r="AI45" s="83"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="77"/>
-      <c r="AM45" s="78"/>
+      <c r="AL45" s="82"/>
+      <c r="AM45" s="83"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
@@ -4818,51 +4836,51 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="82" t="s">
+      <c r="B46" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="83"/>
-      <c r="D46" s="84"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="73"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="82" t="s">
+      <c r="F46" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G46" s="83"/>
-      <c r="H46" s="84"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="73"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="82" t="s">
+      <c r="J46" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="K46" s="83"/>
-      <c r="L46" s="84"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="73"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="79"/>
-      <c r="O46" s="80"/>
-      <c r="P46" s="81"/>
+      <c r="N46" s="84"/>
+      <c r="O46" s="85"/>
+      <c r="P46" s="86"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="79"/>
-      <c r="S46" s="80"/>
-      <c r="T46" s="81"/>
+      <c r="R46" s="84"/>
+      <c r="S46" s="85"/>
+      <c r="T46" s="86"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="79"/>
-      <c r="W46" s="80"/>
-      <c r="X46" s="81"/>
+      <c r="V46" s="84"/>
+      <c r="W46" s="85"/>
+      <c r="X46" s="86"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="79"/>
-      <c r="AA46" s="80"/>
-      <c r="AB46" s="81"/>
+      <c r="Z46" s="84"/>
+      <c r="AA46" s="85"/>
+      <c r="AB46" s="86"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="79"/>
-      <c r="AE46" s="80"/>
-      <c r="AF46" s="81"/>
+      <c r="AD46" s="84"/>
+      <c r="AE46" s="85"/>
+      <c r="AF46" s="86"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="79"/>
-      <c r="AI46" s="80"/>
-      <c r="AJ46" s="81"/>
+      <c r="AH46" s="84"/>
+      <c r="AI46" s="85"/>
+      <c r="AJ46" s="86"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="79"/>
-      <c r="AM46" s="80"/>
-      <c r="AN46" s="81"/>
+      <c r="AL46" s="84"/>
+      <c r="AM46" s="85"/>
+      <c r="AN46" s="86"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4870,47 +4888,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="66" t="s">
+      <c r="B47" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="67"/>
-      <c r="D47" s="68"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="81"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="68"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="81"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="68"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="81"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="90"/>
+      <c r="N47" s="87"/>
+      <c r="O47" s="88"/>
+      <c r="P47" s="89"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="69"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="90"/>
+      <c r="R47" s="87"/>
+      <c r="S47" s="88"/>
+      <c r="T47" s="89"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="70"/>
-      <c r="X47" s="90"/>
+      <c r="V47" s="87"/>
+      <c r="W47" s="88"/>
+      <c r="X47" s="89"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="70"/>
-      <c r="AB47" s="90"/>
+      <c r="Z47" s="87"/>
+      <c r="AA47" s="88"/>
+      <c r="AB47" s="89"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="69"/>
-      <c r="AE47" s="70"/>
-      <c r="AF47" s="90"/>
+      <c r="AD47" s="87"/>
+      <c r="AE47" s="88"/>
+      <c r="AF47" s="89"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="69"/>
-      <c r="AI47" s="70"/>
-      <c r="AJ47" s="90"/>
+      <c r="AH47" s="87"/>
+      <c r="AI47" s="88"/>
+      <c r="AJ47" s="89"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="69"/>
-      <c r="AM47" s="70"/>
-      <c r="AN47" s="90"/>
+      <c r="AL47" s="87"/>
+      <c r="AM47" s="88"/>
+      <c r="AN47" s="89"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4918,145 +4936,145 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="87" t="s">
+      <c r="B48" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="89"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="63" t="s">
+      <c r="F48" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="64"/>
-      <c r="H48" s="65"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="78"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="87" t="s">
+      <c r="J48" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="88"/>
-      <c r="L48" s="89"/>
+      <c r="K48" s="64"/>
+      <c r="L48" s="65"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="63"/>
-      <c r="O48" s="64"/>
-      <c r="P48" s="65"/>
+      <c r="N48" s="76"/>
+      <c r="O48" s="77"/>
+      <c r="P48" s="78"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="63"/>
-      <c r="S48" s="64"/>
-      <c r="T48" s="65"/>
+      <c r="R48" s="76"/>
+      <c r="S48" s="77"/>
+      <c r="T48" s="78"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="63"/>
-      <c r="W48" s="64"/>
-      <c r="X48" s="65"/>
+      <c r="V48" s="76"/>
+      <c r="W48" s="77"/>
+      <c r="X48" s="78"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="87"/>
-      <c r="AA48" s="88"/>
-      <c r="AB48" s="89"/>
+      <c r="Z48" s="63"/>
+      <c r="AA48" s="64"/>
+      <c r="AB48" s="65"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="87"/>
-      <c r="AE48" s="88"/>
-      <c r="AF48" s="89"/>
+      <c r="AD48" s="63"/>
+      <c r="AE48" s="64"/>
+      <c r="AF48" s="65"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="63"/>
-      <c r="AI48" s="64"/>
-      <c r="AJ48" s="65"/>
+      <c r="AH48" s="76"/>
+      <c r="AI48" s="77"/>
+      <c r="AJ48" s="78"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="63"/>
-      <c r="AM48" s="64"/>
-      <c r="AN48" s="65"/>
+      <c r="AL48" s="76"/>
+      <c r="AM48" s="77"/>
+      <c r="AN48" s="78"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="63"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="65"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="78"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="63" t="s">
+      <c r="F49" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="64"/>
-      <c r="H49" s="65"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="78"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="63" t="s">
+      <c r="J49" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="64"/>
-      <c r="L49" s="65"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="78"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="63"/>
-      <c r="O49" s="64"/>
-      <c r="P49" s="65"/>
+      <c r="N49" s="76"/>
+      <c r="O49" s="77"/>
+      <c r="P49" s="78"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="63"/>
-      <c r="S49" s="64"/>
-      <c r="T49" s="65"/>
+      <c r="R49" s="76"/>
+      <c r="S49" s="77"/>
+      <c r="T49" s="78"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="63"/>
-      <c r="W49" s="64"/>
-      <c r="X49" s="65"/>
+      <c r="V49" s="76"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="78"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="63"/>
-      <c r="AA49" s="64"/>
-      <c r="AB49" s="65"/>
+      <c r="Z49" s="76"/>
+      <c r="AA49" s="77"/>
+      <c r="AB49" s="78"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="63"/>
-      <c r="AE49" s="64"/>
-      <c r="AF49" s="65"/>
+      <c r="AD49" s="76"/>
+      <c r="AE49" s="77"/>
+      <c r="AF49" s="78"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="63"/>
-      <c r="AI49" s="64"/>
-      <c r="AJ49" s="65"/>
+      <c r="AH49" s="76"/>
+      <c r="AI49" s="77"/>
+      <c r="AJ49" s="78"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="63"/>
-      <c r="AM49" s="64"/>
-      <c r="AN49" s="65"/>
+      <c r="AL49" s="76"/>
+      <c r="AM49" s="77"/>
+      <c r="AN49" s="78"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="97"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="99"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="68"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="97"/>
-      <c r="G50" s="98"/>
-      <c r="H50" s="99"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="68"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="97"/>
-      <c r="K50" s="98"/>
-      <c r="L50" s="99"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="67"/>
+      <c r="L50" s="68"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="97"/>
-      <c r="O50" s="98"/>
-      <c r="P50" s="99"/>
+      <c r="N50" s="66"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="68"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="97"/>
-      <c r="S50" s="98"/>
-      <c r="T50" s="99"/>
+      <c r="R50" s="66"/>
+      <c r="S50" s="67"/>
+      <c r="T50" s="68"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="97"/>
-      <c r="W50" s="98"/>
-      <c r="X50" s="99"/>
+      <c r="V50" s="66"/>
+      <c r="W50" s="67"/>
+      <c r="X50" s="68"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="97"/>
-      <c r="AA50" s="98"/>
-      <c r="AB50" s="99"/>
+      <c r="Z50" s="66"/>
+      <c r="AA50" s="67"/>
+      <c r="AB50" s="68"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="97"/>
-      <c r="AE50" s="98"/>
-      <c r="AF50" s="99"/>
+      <c r="AD50" s="66"/>
+      <c r="AE50" s="67"/>
+      <c r="AF50" s="68"/>
       <c r="AG50" s="44"/>
-      <c r="AH50" s="97"/>
-      <c r="AI50" s="98"/>
-      <c r="AJ50" s="99"/>
+      <c r="AH50" s="66"/>
+      <c r="AI50" s="67"/>
+      <c r="AJ50" s="68"/>
       <c r="AK50" s="44"/>
-      <c r="AL50" s="97"/>
-      <c r="AM50" s="98"/>
-      <c r="AN50" s="99"/>
+      <c r="AL50" s="66"/>
+      <c r="AM50" s="67"/>
+      <c r="AN50" s="68"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5108,255 +5126,255 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="93"/>
-      <c r="C52" s="94"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="70"/>
       <c r="D52" s="61"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="94"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="70"/>
       <c r="H52" s="61"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="93"/>
-      <c r="K52" s="94"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="70"/>
       <c r="L52" s="61"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="77"/>
-      <c r="O52" s="78"/>
+      <c r="N52" s="82"/>
+      <c r="O52" s="83"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="78"/>
+      <c r="R52" s="82"/>
+      <c r="S52" s="83"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="77"/>
-      <c r="W52" s="78"/>
+      <c r="V52" s="82"/>
+      <c r="W52" s="83"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="77"/>
-      <c r="AA52" s="78"/>
+      <c r="Z52" s="82"/>
+      <c r="AA52" s="83"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="77"/>
-      <c r="AE52" s="78"/>
+      <c r="AD52" s="82"/>
+      <c r="AE52" s="83"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="77"/>
-      <c r="AI52" s="78"/>
+      <c r="AH52" s="82"/>
+      <c r="AI52" s="83"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="77"/>
-      <c r="AM52" s="78"/>
+      <c r="AL52" s="82"/>
+      <c r="AM52" s="83"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="82"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="84"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="73"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="84"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="73"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="82"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="84"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="73"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="80"/>
-      <c r="P53" s="81"/>
+      <c r="N53" s="84"/>
+      <c r="O53" s="85"/>
+      <c r="P53" s="86"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="79"/>
-      <c r="S53" s="80"/>
-      <c r="T53" s="81"/>
+      <c r="R53" s="84"/>
+      <c r="S53" s="85"/>
+      <c r="T53" s="86"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="79"/>
-      <c r="W53" s="80"/>
-      <c r="X53" s="81"/>
+      <c r="V53" s="84"/>
+      <c r="W53" s="85"/>
+      <c r="X53" s="86"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="79"/>
-      <c r="AA53" s="80"/>
-      <c r="AB53" s="81"/>
+      <c r="Z53" s="84"/>
+      <c r="AA53" s="85"/>
+      <c r="AB53" s="86"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="79"/>
-      <c r="AE53" s="80"/>
-      <c r="AF53" s="81"/>
+      <c r="AD53" s="84"/>
+      <c r="AE53" s="85"/>
+      <c r="AF53" s="86"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="79"/>
-      <c r="AI53" s="80"/>
-      <c r="AJ53" s="81"/>
+      <c r="AH53" s="84"/>
+      <c r="AI53" s="85"/>
+      <c r="AJ53" s="86"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="79"/>
-      <c r="AM53" s="80"/>
-      <c r="AN53" s="81"/>
+      <c r="AL53" s="84"/>
+      <c r="AM53" s="85"/>
+      <c r="AN53" s="86"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="66"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="68"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="81"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="66"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="68"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="81"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="66"/>
-      <c r="K54" s="67"/>
-      <c r="L54" s="68"/>
+      <c r="J54" s="79"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="81"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="69"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="90"/>
+      <c r="N54" s="87"/>
+      <c r="O54" s="88"/>
+      <c r="P54" s="89"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="69"/>
-      <c r="S54" s="70"/>
-      <c r="T54" s="90"/>
+      <c r="R54" s="87"/>
+      <c r="S54" s="88"/>
+      <c r="T54" s="89"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="69"/>
-      <c r="W54" s="70"/>
-      <c r="X54" s="90"/>
+      <c r="V54" s="87"/>
+      <c r="W54" s="88"/>
+      <c r="X54" s="89"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="69"/>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="90"/>
+      <c r="Z54" s="87"/>
+      <c r="AA54" s="88"/>
+      <c r="AB54" s="89"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="69"/>
-      <c r="AE54" s="70"/>
-      <c r="AF54" s="90"/>
+      <c r="AD54" s="87"/>
+      <c r="AE54" s="88"/>
+      <c r="AF54" s="89"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="69"/>
-      <c r="AI54" s="70"/>
-      <c r="AJ54" s="90"/>
+      <c r="AH54" s="87"/>
+      <c r="AI54" s="88"/>
+      <c r="AJ54" s="89"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="69"/>
-      <c r="AM54" s="70"/>
-      <c r="AN54" s="90"/>
+      <c r="AL54" s="87"/>
+      <c r="AM54" s="88"/>
+      <c r="AN54" s="89"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="87"/>
-      <c r="C55" s="88"/>
-      <c r="D55" s="89"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="65"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="87"/>
-      <c r="G55" s="88"/>
-      <c r="H55" s="89"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="65"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="87"/>
-      <c r="K55" s="88"/>
-      <c r="L55" s="89"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="65"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="87"/>
-      <c r="O55" s="88"/>
-      <c r="P55" s="89"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="64"/>
+      <c r="P55" s="65"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="87"/>
-      <c r="S55" s="88"/>
-      <c r="T55" s="89"/>
+      <c r="R55" s="63"/>
+      <c r="S55" s="64"/>
+      <c r="T55" s="65"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="87"/>
-      <c r="W55" s="88"/>
-      <c r="X55" s="89"/>
+      <c r="V55" s="63"/>
+      <c r="W55" s="64"/>
+      <c r="X55" s="65"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="87"/>
-      <c r="AA55" s="88"/>
-      <c r="AB55" s="89"/>
+      <c r="Z55" s="63"/>
+      <c r="AA55" s="64"/>
+      <c r="AB55" s="65"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="87"/>
-      <c r="AE55" s="88"/>
-      <c r="AF55" s="89"/>
+      <c r="AD55" s="63"/>
+      <c r="AE55" s="64"/>
+      <c r="AF55" s="65"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="87"/>
-      <c r="AI55" s="88"/>
-      <c r="AJ55" s="89"/>
+      <c r="AH55" s="63"/>
+      <c r="AI55" s="64"/>
+      <c r="AJ55" s="65"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="87"/>
-      <c r="AM55" s="88"/>
-      <c r="AN55" s="89"/>
+      <c r="AL55" s="63"/>
+      <c r="AM55" s="64"/>
+      <c r="AN55" s="65"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="63"/>
-      <c r="C56" s="64"/>
-      <c r="D56" s="65"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="78"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="65"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="78"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="63"/>
-      <c r="K56" s="64"/>
-      <c r="L56" s="65"/>
+      <c r="J56" s="76"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="78"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="63"/>
-      <c r="O56" s="64"/>
-      <c r="P56" s="65"/>
+      <c r="N56" s="76"/>
+      <c r="O56" s="77"/>
+      <c r="P56" s="78"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="63"/>
-      <c r="S56" s="64"/>
-      <c r="T56" s="65"/>
+      <c r="R56" s="76"/>
+      <c r="S56" s="77"/>
+      <c r="T56" s="78"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="63"/>
-      <c r="W56" s="64"/>
-      <c r="X56" s="65"/>
+      <c r="V56" s="76"/>
+      <c r="W56" s="77"/>
+      <c r="X56" s="78"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="63"/>
-      <c r="AA56" s="64"/>
-      <c r="AB56" s="65"/>
+      <c r="Z56" s="76"/>
+      <c r="AA56" s="77"/>
+      <c r="AB56" s="78"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="63"/>
-      <c r="AE56" s="64"/>
-      <c r="AF56" s="65"/>
+      <c r="AD56" s="76"/>
+      <c r="AE56" s="77"/>
+      <c r="AF56" s="78"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="63"/>
-      <c r="AI56" s="64"/>
-      <c r="AJ56" s="65"/>
+      <c r="AH56" s="76"/>
+      <c r="AI56" s="77"/>
+      <c r="AJ56" s="78"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="63"/>
-      <c r="AM56" s="64"/>
-      <c r="AN56" s="65"/>
+      <c r="AL56" s="76"/>
+      <c r="AM56" s="77"/>
+      <c r="AN56" s="78"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="97"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="99"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="68"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="97"/>
-      <c r="G57" s="98"/>
-      <c r="H57" s="99"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="68"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="97"/>
-      <c r="K57" s="98"/>
-      <c r="L57" s="99"/>
+      <c r="J57" s="66"/>
+      <c r="K57" s="67"/>
+      <c r="L57" s="68"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="97"/>
-      <c r="O57" s="98"/>
-      <c r="P57" s="99"/>
+      <c r="N57" s="66"/>
+      <c r="O57" s="67"/>
+      <c r="P57" s="68"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="97"/>
-      <c r="S57" s="98"/>
-      <c r="T57" s="99"/>
+      <c r="R57" s="66"/>
+      <c r="S57" s="67"/>
+      <c r="T57" s="68"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="97"/>
-      <c r="W57" s="98"/>
-      <c r="X57" s="99"/>
+      <c r="V57" s="66"/>
+      <c r="W57" s="67"/>
+      <c r="X57" s="68"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="97"/>
-      <c r="AA57" s="98"/>
-      <c r="AB57" s="99"/>
+      <c r="Z57" s="66"/>
+      <c r="AA57" s="67"/>
+      <c r="AB57" s="68"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="97"/>
-      <c r="AE57" s="98"/>
-      <c r="AF57" s="99"/>
+      <c r="AD57" s="66"/>
+      <c r="AE57" s="67"/>
+      <c r="AF57" s="68"/>
       <c r="AG57" s="44"/>
-      <c r="AH57" s="97"/>
-      <c r="AI57" s="98"/>
-      <c r="AJ57" s="99"/>
+      <c r="AH57" s="66"/>
+      <c r="AI57" s="67"/>
+      <c r="AJ57" s="68"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="97"/>
-      <c r="AM57" s="98"/>
-      <c r="AN57" s="99"/>
+      <c r="AL57" s="66"/>
+      <c r="AM57" s="67"/>
+      <c r="AN57" s="68"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5402,261 +5420,261 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="124" t="s">
+      <c r="B59" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="125"/>
+      <c r="C59" s="97"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="94"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="70"/>
       <c r="H59" s="61"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="93"/>
-      <c r="K59" s="94"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="70"/>
       <c r="L59" s="61"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="77"/>
-      <c r="O59" s="78"/>
+      <c r="N59" s="82"/>
+      <c r="O59" s="83"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="77"/>
-      <c r="S59" s="78"/>
+      <c r="R59" s="82"/>
+      <c r="S59" s="83"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="77"/>
-      <c r="W59" s="78"/>
+      <c r="V59" s="82"/>
+      <c r="W59" s="83"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="77"/>
-      <c r="AA59" s="78"/>
+      <c r="Z59" s="82"/>
+      <c r="AA59" s="83"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="77"/>
-      <c r="AE59" s="78"/>
+      <c r="AD59" s="82"/>
+      <c r="AE59" s="83"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="77"/>
-      <c r="AI59" s="78"/>
+      <c r="AH59" s="82"/>
+      <c r="AI59" s="83"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="77"/>
-      <c r="AM59" s="78"/>
+      <c r="AL59" s="82"/>
+      <c r="AM59" s="83"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="135" t="s">
+      <c r="B60" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="136"/>
-      <c r="D60" s="137"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="95"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="83"/>
-      <c r="H60" s="84"/>
+      <c r="F60" s="71"/>
+      <c r="G60" s="72"/>
+      <c r="H60" s="73"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="83"/>
-      <c r="L60" s="84"/>
+      <c r="J60" s="71"/>
+      <c r="K60" s="72"/>
+      <c r="L60" s="73"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="79"/>
-      <c r="O60" s="80"/>
-      <c r="P60" s="81"/>
+      <c r="N60" s="84"/>
+      <c r="O60" s="85"/>
+      <c r="P60" s="86"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="79"/>
-      <c r="S60" s="80"/>
-      <c r="T60" s="81"/>
+      <c r="R60" s="84"/>
+      <c r="S60" s="85"/>
+      <c r="T60" s="86"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="79"/>
-      <c r="W60" s="80"/>
-      <c r="X60" s="81"/>
+      <c r="V60" s="84"/>
+      <c r="W60" s="85"/>
+      <c r="X60" s="86"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="79"/>
-      <c r="AA60" s="80"/>
-      <c r="AB60" s="81"/>
+      <c r="Z60" s="84"/>
+      <c r="AA60" s="85"/>
+      <c r="AB60" s="86"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="79"/>
-      <c r="AE60" s="80"/>
-      <c r="AF60" s="81"/>
+      <c r="AD60" s="84"/>
+      <c r="AE60" s="85"/>
+      <c r="AF60" s="86"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="79"/>
-      <c r="AI60" s="80"/>
-      <c r="AJ60" s="81"/>
+      <c r="AH60" s="84"/>
+      <c r="AI60" s="85"/>
+      <c r="AJ60" s="86"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="79"/>
-      <c r="AM60" s="80"/>
-      <c r="AN60" s="81"/>
+      <c r="AL60" s="84"/>
+      <c r="AM60" s="85"/>
+      <c r="AN60" s="86"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="121"/>
-      <c r="C61" s="122"/>
-      <c r="D61" s="123"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="92"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="68"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="80"/>
+      <c r="H61" s="81"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="66"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="68"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="80"/>
+      <c r="L61" s="81"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="69"/>
-      <c r="O61" s="70"/>
-      <c r="P61" s="90"/>
+      <c r="N61" s="87"/>
+      <c r="O61" s="88"/>
+      <c r="P61" s="89"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="69"/>
-      <c r="S61" s="70"/>
-      <c r="T61" s="90"/>
+      <c r="R61" s="87"/>
+      <c r="S61" s="88"/>
+      <c r="T61" s="89"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="69"/>
-      <c r="W61" s="70"/>
-      <c r="X61" s="90"/>
+      <c r="V61" s="87"/>
+      <c r="W61" s="88"/>
+      <c r="X61" s="89"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="69"/>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="90"/>
+      <c r="Z61" s="87"/>
+      <c r="AA61" s="88"/>
+      <c r="AB61" s="89"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="69"/>
-      <c r="AE61" s="70"/>
-      <c r="AF61" s="90"/>
+      <c r="AD61" s="87"/>
+      <c r="AE61" s="88"/>
+      <c r="AF61" s="89"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="69"/>
-      <c r="AI61" s="70"/>
-      <c r="AJ61" s="90"/>
+      <c r="AH61" s="87"/>
+      <c r="AI61" s="88"/>
+      <c r="AJ61" s="89"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="69"/>
-      <c r="AM61" s="70"/>
-      <c r="AN61" s="90"/>
+      <c r="AL61" s="87"/>
+      <c r="AM61" s="88"/>
+      <c r="AN61" s="89"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="132" t="s">
+      <c r="B62" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="133"/>
-      <c r="D62" s="134"/>
+      <c r="C62" s="102"/>
+      <c r="D62" s="103"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="88"/>
-      <c r="H62" s="89"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="65"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="87"/>
-      <c r="K62" s="88"/>
-      <c r="L62" s="89"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="64"/>
+      <c r="L62" s="65"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="63"/>
-      <c r="O62" s="64"/>
-      <c r="P62" s="65"/>
+      <c r="N62" s="76"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="78"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="63"/>
-      <c r="S62" s="64"/>
-      <c r="T62" s="65"/>
+      <c r="R62" s="76"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="78"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="87"/>
-      <c r="W62" s="88"/>
-      <c r="X62" s="89"/>
+      <c r="V62" s="63"/>
+      <c r="W62" s="64"/>
+      <c r="X62" s="65"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="87"/>
-      <c r="AA62" s="88"/>
-      <c r="AB62" s="89"/>
+      <c r="Z62" s="63"/>
+      <c r="AA62" s="64"/>
+      <c r="AB62" s="65"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="87"/>
-      <c r="AE62" s="88"/>
-      <c r="AF62" s="89"/>
+      <c r="AD62" s="63"/>
+      <c r="AE62" s="64"/>
+      <c r="AF62" s="65"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="87"/>
-      <c r="AI62" s="88"/>
-      <c r="AJ62" s="89"/>
+      <c r="AH62" s="63"/>
+      <c r="AI62" s="64"/>
+      <c r="AJ62" s="65"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="87"/>
-      <c r="AM62" s="88"/>
-      <c r="AN62" s="89"/>
+      <c r="AL62" s="63"/>
+      <c r="AM62" s="64"/>
+      <c r="AN62" s="65"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="129"/>
-      <c r="C63" s="130"/>
-      <c r="D63" s="131"/>
+      <c r="B63" s="98"/>
+      <c r="C63" s="99"/>
+      <c r="D63" s="100"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="65"/>
+      <c r="F63" s="76"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="78"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="64"/>
-      <c r="L63" s="65"/>
+      <c r="J63" s="76"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="78"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="63"/>
-      <c r="O63" s="64"/>
-      <c r="P63" s="65"/>
+      <c r="N63" s="76"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="78"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="63"/>
-      <c r="S63" s="64"/>
-      <c r="T63" s="65"/>
+      <c r="R63" s="76"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="78"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="63"/>
-      <c r="W63" s="64"/>
-      <c r="X63" s="65"/>
+      <c r="V63" s="76"/>
+      <c r="W63" s="77"/>
+      <c r="X63" s="78"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="63"/>
-      <c r="AA63" s="64"/>
-      <c r="AB63" s="65"/>
+      <c r="Z63" s="76"/>
+      <c r="AA63" s="77"/>
+      <c r="AB63" s="78"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="63"/>
-      <c r="AE63" s="64"/>
-      <c r="AF63" s="65"/>
+      <c r="AD63" s="76"/>
+      <c r="AE63" s="77"/>
+      <c r="AF63" s="78"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="63"/>
-      <c r="AI63" s="64"/>
-      <c r="AJ63" s="65"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
+      <c r="AJ63" s="78"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="63"/>
-      <c r="AM63" s="64"/>
-      <c r="AN63" s="65"/>
+      <c r="AL63" s="76"/>
+      <c r="AM63" s="77"/>
+      <c r="AN63" s="78"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="126"/>
-      <c r="C64" s="127"/>
-      <c r="D64" s="128"/>
+      <c r="B64" s="108"/>
+      <c r="C64" s="109"/>
+      <c r="D64" s="110"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="97"/>
-      <c r="G64" s="98"/>
-      <c r="H64" s="99"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="68"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="97"/>
-      <c r="K64" s="98"/>
-      <c r="L64" s="99"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="67"/>
+      <c r="L64" s="68"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="97"/>
-      <c r="O64" s="98"/>
-      <c r="P64" s="99"/>
+      <c r="N64" s="66"/>
+      <c r="O64" s="67"/>
+      <c r="P64" s="68"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="97"/>
-      <c r="S64" s="98"/>
-      <c r="T64" s="99"/>
+      <c r="R64" s="66"/>
+      <c r="S64" s="67"/>
+      <c r="T64" s="68"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="97"/>
-      <c r="W64" s="98"/>
-      <c r="X64" s="99"/>
+      <c r="V64" s="66"/>
+      <c r="W64" s="67"/>
+      <c r="X64" s="68"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="97"/>
-      <c r="AA64" s="98"/>
-      <c r="AB64" s="99"/>
+      <c r="Z64" s="66"/>
+      <c r="AA64" s="67"/>
+      <c r="AB64" s="68"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="97"/>
-      <c r="AE64" s="98"/>
-      <c r="AF64" s="99"/>
+      <c r="AD64" s="66"/>
+      <c r="AE64" s="67"/>
+      <c r="AF64" s="68"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="97"/>
-      <c r="AI64" s="98"/>
-      <c r="AJ64" s="99"/>
+      <c r="AH64" s="66"/>
+      <c r="AI64" s="67"/>
+      <c r="AJ64" s="68"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="97"/>
-      <c r="AM64" s="98"/>
-      <c r="AN64" s="99"/>
+      <c r="AL64" s="66"/>
+      <c r="AM64" s="67"/>
+      <c r="AN64" s="68"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5719,23 +5737,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="100" t="s">
+      <c r="N66" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="100"/>
-      <c r="P66" s="100"/>
-      <c r="Q66" s="100"/>
-      <c r="R66" s="100"/>
-      <c r="S66" s="100"/>
-      <c r="T66" s="100"/>
-      <c r="U66" s="100"/>
-      <c r="V66" s="100"/>
-      <c r="W66" s="100"/>
-      <c r="X66" s="100"/>
-      <c r="Y66" s="100"/>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="100"/>
-      <c r="AB66" s="100"/>
+      <c r="O66" s="119"/>
+      <c r="P66" s="119"/>
+      <c r="Q66" s="119"/>
+      <c r="R66" s="119"/>
+      <c r="S66" s="119"/>
+      <c r="T66" s="119"/>
+      <c r="U66" s="119"/>
+      <c r="V66" s="119"/>
+      <c r="W66" s="119"/>
+      <c r="X66" s="119"/>
+      <c r="Y66" s="119"/>
+      <c r="Z66" s="119"/>
+      <c r="AA66" s="119"/>
+      <c r="AB66" s="119"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5766,21 +5784,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="100"/>
-      <c r="O67" s="100"/>
-      <c r="P67" s="100"/>
-      <c r="Q67" s="100"/>
-      <c r="R67" s="100"/>
-      <c r="S67" s="100"/>
-      <c r="T67" s="100"/>
-      <c r="U67" s="100"/>
-      <c r="V67" s="100"/>
-      <c r="W67" s="100"/>
-      <c r="X67" s="100"/>
-      <c r="Y67" s="100"/>
-      <c r="Z67" s="100"/>
-      <c r="AA67" s="100"/>
-      <c r="AB67" s="100"/>
+      <c r="N67" s="119"/>
+      <c r="O67" s="119"/>
+      <c r="P67" s="119"/>
+      <c r="Q67" s="119"/>
+      <c r="R67" s="119"/>
+      <c r="S67" s="119"/>
+      <c r="T67" s="119"/>
+      <c r="U67" s="119"/>
+      <c r="V67" s="119"/>
+      <c r="W67" s="119"/>
+      <c r="X67" s="119"/>
+      <c r="Y67" s="119"/>
+      <c r="Z67" s="119"/>
+      <c r="AA67" s="119"/>
+      <c r="AB67" s="119"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5800,58 +5818,58 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="93" t="s">
+      <c r="B68" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="94"/>
+      <c r="C68" s="70"/>
       <c r="D68" s="61"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="93"/>
-      <c r="G68" s="94"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="70"/>
       <c r="H68" s="61"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="93"/>
-      <c r="K68" s="94"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="70"/>
       <c r="L68" s="61"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="77" t="s">
+      <c r="N68" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="O68" s="78"/>
+      <c r="O68" s="83"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="77"/>
-      <c r="S68" s="78"/>
+      <c r="R68" s="82"/>
+      <c r="S68" s="83"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="77" t="s">
+      <c r="V68" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="W68" s="78"/>
+      <c r="W68" s="83"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="77" t="s">
+      <c r="Z68" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="AA68" s="78"/>
+      <c r="AA68" s="83"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="77" t="s">
+      <c r="AD68" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="AE68" s="78"/>
+      <c r="AE68" s="83"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="77" t="s">
+      <c r="AH68" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="AI68" s="78"/>
+      <c r="AI68" s="83"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="77" t="s">
+      <c r="AL68" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="AM68" s="78"/>
+      <c r="AM68" s="83"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5862,55 +5880,55 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="82"/>
-      <c r="C69" s="83"/>
-      <c r="D69" s="84"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="73"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="83"/>
-      <c r="H69" s="84"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="72"/>
+      <c r="H69" s="73"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="82"/>
-      <c r="K69" s="83"/>
-      <c r="L69" s="84"/>
+      <c r="J69" s="71"/>
+      <c r="K69" s="72"/>
+      <c r="L69" s="73"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="79" t="s">
+      <c r="N69" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="O69" s="80"/>
-      <c r="P69" s="81"/>
+      <c r="O69" s="85"/>
+      <c r="P69" s="86"/>
       <c r="Q69" s="32"/>
-      <c r="R69" s="79"/>
-      <c r="S69" s="80"/>
-      <c r="T69" s="81"/>
+      <c r="R69" s="84"/>
+      <c r="S69" s="85"/>
+      <c r="T69" s="86"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="79"/>
-      <c r="W69" s="80"/>
-      <c r="X69" s="81"/>
+      <c r="V69" s="84"/>
+      <c r="W69" s="85"/>
+      <c r="X69" s="86"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="79" t="s">
+      <c r="Z69" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="AA69" s="80"/>
-      <c r="AB69" s="81"/>
+      <c r="AA69" s="85"/>
+      <c r="AB69" s="86"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="79" t="s">
+      <c r="AD69" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="AE69" s="80"/>
-      <c r="AF69" s="81"/>
+      <c r="AE69" s="85"/>
+      <c r="AF69" s="86"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="79" t="s">
+      <c r="AH69" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="AI69" s="80"/>
-      <c r="AJ69" s="81"/>
+      <c r="AI69" s="85"/>
+      <c r="AJ69" s="86"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="79" t="s">
+      <c r="AL69" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="AM69" s="80"/>
-      <c r="AN69" s="81"/>
+      <c r="AM69" s="85"/>
+      <c r="AN69" s="86"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5920,59 +5938,59 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="66" t="s">
+      <c r="B70" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="67"/>
-      <c r="D70" s="68"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="81"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="68"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="81"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="66"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="68"/>
+      <c r="J70" s="79"/>
+      <c r="K70" s="80"/>
+      <c r="L70" s="81"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="69" t="s">
+      <c r="N70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="70"/>
-      <c r="P70" s="90"/>
+      <c r="O70" s="88"/>
+      <c r="P70" s="89"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="69"/>
-      <c r="S70" s="70"/>
-      <c r="T70" s="90"/>
+      <c r="R70" s="87"/>
+      <c r="S70" s="88"/>
+      <c r="T70" s="89"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="69" t="s">
+      <c r="V70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="W70" s="70"/>
-      <c r="X70" s="90"/>
+      <c r="W70" s="88"/>
+      <c r="X70" s="89"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="69" t="s">
+      <c r="Z70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AA70" s="70"/>
-      <c r="AB70" s="90"/>
+      <c r="AA70" s="88"/>
+      <c r="AB70" s="89"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="69" t="s">
+      <c r="AD70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AE70" s="70"/>
-      <c r="AF70" s="90"/>
+      <c r="AE70" s="88"/>
+      <c r="AF70" s="89"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="69" t="s">
+      <c r="AH70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AI70" s="70"/>
-      <c r="AJ70" s="90"/>
+      <c r="AI70" s="88"/>
+      <c r="AJ70" s="89"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="69" t="s">
+      <c r="AL70" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AM70" s="70"/>
-      <c r="AN70" s="90"/>
+      <c r="AM70" s="88"/>
+      <c r="AN70" s="89"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5982,59 +6000,59 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="87" t="s">
+      <c r="B71" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="88"/>
-      <c r="D71" s="89"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="65"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="87"/>
-      <c r="G71" s="88"/>
-      <c r="H71" s="89"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="65"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="87"/>
-      <c r="K71" s="88"/>
-      <c r="L71" s="89"/>
+      <c r="J71" s="63"/>
+      <c r="K71" s="64"/>
+      <c r="L71" s="65"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="87" t="s">
+      <c r="N71" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="O71" s="88"/>
-      <c r="P71" s="89"/>
+      <c r="O71" s="64"/>
+      <c r="P71" s="65"/>
       <c r="Q71" s="31"/>
-      <c r="R71" s="87"/>
-      <c r="S71" s="88"/>
-      <c r="T71" s="89"/>
+      <c r="R71" s="63"/>
+      <c r="S71" s="64"/>
+      <c r="T71" s="65"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="87" t="s">
+      <c r="V71" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="W71" s="88"/>
-      <c r="X71" s="89"/>
+      <c r="W71" s="64"/>
+      <c r="X71" s="65"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="87" t="s">
+      <c r="Z71" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="88"/>
-      <c r="AB71" s="89"/>
+      <c r="AA71" s="64"/>
+      <c r="AB71" s="65"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="87" t="s">
+      <c r="AD71" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="88"/>
-      <c r="AF71" s="89"/>
+      <c r="AE71" s="64"/>
+      <c r="AF71" s="65"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="87" t="s">
+      <c r="AH71" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="88"/>
-      <c r="AJ71" s="89"/>
+      <c r="AI71" s="64"/>
+      <c r="AJ71" s="65"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="87" t="s">
+      <c r="AL71" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="AM71" s="88"/>
-      <c r="AN71" s="89"/>
+      <c r="AM71" s="64"/>
+      <c r="AN71" s="65"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6044,47 +6062,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="97"/>
-      <c r="C72" s="98"/>
-      <c r="D72" s="99"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="67"/>
+      <c r="D72" s="68"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="97"/>
-      <c r="G72" s="98"/>
-      <c r="H72" s="99"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="67"/>
+      <c r="H72" s="68"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="97"/>
-      <c r="K72" s="98"/>
-      <c r="L72" s="99"/>
+      <c r="J72" s="66"/>
+      <c r="K72" s="67"/>
+      <c r="L72" s="68"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="97"/>
-      <c r="O72" s="98"/>
-      <c r="P72" s="99"/>
+      <c r="N72" s="66"/>
+      <c r="O72" s="67"/>
+      <c r="P72" s="68"/>
       <c r="Q72" s="44"/>
-      <c r="R72" s="97"/>
-      <c r="S72" s="98"/>
-      <c r="T72" s="99"/>
+      <c r="R72" s="66"/>
+      <c r="S72" s="67"/>
+      <c r="T72" s="68"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="138" t="s">
-        <v>100</v>
-      </c>
-      <c r="W72" s="139"/>
-      <c r="X72" s="140"/>
+      <c r="V72" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="W72" s="67"/>
+      <c r="X72" s="68"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="97"/>
-      <c r="AA72" s="98"/>
-      <c r="AB72" s="99"/>
+      <c r="Z72" s="66"/>
+      <c r="AA72" s="67"/>
+      <c r="AB72" s="68"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="97"/>
-      <c r="AE72" s="98"/>
-      <c r="AF72" s="99"/>
+      <c r="AD72" s="66"/>
+      <c r="AE72" s="67"/>
+      <c r="AF72" s="68"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="97"/>
-      <c r="AI72" s="98"/>
-      <c r="AJ72" s="99"/>
+      <c r="AH72" s="66"/>
+      <c r="AI72" s="67"/>
+      <c r="AJ72" s="68"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="97"/>
-      <c r="AM72" s="98"/>
-      <c r="AN72" s="99"/>
+      <c r="AL72" s="66"/>
+      <c r="AM72" s="67"/>
+      <c r="AN72" s="68"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6138,58 +6156,58 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="93" t="s">
+      <c r="B74" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="94"/>
+      <c r="C74" s="70"/>
       <c r="D74" s="61"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="93"/>
-      <c r="G74" s="94"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
       <c r="H74" s="61"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="93"/>
-      <c r="K74" s="94"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="70"/>
       <c r="L74" s="61"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="77" t="s">
+      <c r="N74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="O74" s="78"/>
+      <c r="O74" s="83"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="32"/>
-      <c r="R74" s="77" t="s">
+      <c r="R74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="S74" s="78"/>
+      <c r="S74" s="83"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="77" t="s">
+      <c r="V74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="W74" s="78"/>
+      <c r="W74" s="83"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="77" t="s">
+      <c r="Z74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="AA74" s="78"/>
+      <c r="AA74" s="83"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="77" t="s">
+      <c r="AD74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="AE74" s="78"/>
+      <c r="AE74" s="83"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="77" t="s">
+      <c r="AH74" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="AI74" s="78"/>
+      <c r="AI74" s="83"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="77"/>
-      <c r="AM74" s="78"/>
+      <c r="AL74" s="82"/>
+      <c r="AM74" s="83"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6198,57 +6216,57 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="84"/>
+      <c r="B75" s="71"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="73"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="82"/>
-      <c r="G75" s="83"/>
-      <c r="H75" s="84"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="73"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="82"/>
-      <c r="K75" s="83"/>
-      <c r="L75" s="84"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="72"/>
+      <c r="L75" s="73"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="79" t="s">
+      <c r="N75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="O75" s="80"/>
-      <c r="P75" s="81"/>
+      <c r="O75" s="85"/>
+      <c r="P75" s="86"/>
       <c r="Q75" s="32"/>
-      <c r="R75" s="79" t="s">
+      <c r="R75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="S75" s="80"/>
-      <c r="T75" s="81"/>
+      <c r="S75" s="85"/>
+      <c r="T75" s="86"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="79" t="s">
+      <c r="V75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="W75" s="80"/>
-      <c r="X75" s="81"/>
+      <c r="W75" s="85"/>
+      <c r="X75" s="86"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="79" t="s">
+      <c r="Z75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="AA75" s="80"/>
-      <c r="AB75" s="81"/>
+      <c r="AA75" s="85"/>
+      <c r="AB75" s="86"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="79" t="s">
+      <c r="AD75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="AE75" s="80"/>
-      <c r="AF75" s="81"/>
+      <c r="AE75" s="85"/>
+      <c r="AF75" s="86"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="79" t="s">
+      <c r="AH75" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="AI75" s="80"/>
-      <c r="AJ75" s="81"/>
+      <c r="AI75" s="85"/>
+      <c r="AJ75" s="86"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="79"/>
-      <c r="AM75" s="80"/>
-      <c r="AN75" s="81"/>
+      <c r="AL75" s="84"/>
+      <c r="AM75" s="85"/>
+      <c r="AN75" s="86"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6256,59 +6274,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="66" t="s">
+      <c r="B76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="67"/>
-      <c r="D76" s="68"/>
+      <c r="C76" s="80"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="68"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="80"/>
+      <c r="H76" s="81"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="66"/>
-      <c r="K76" s="67"/>
-      <c r="L76" s="68"/>
+      <c r="J76" s="79"/>
+      <c r="K76" s="80"/>
+      <c r="L76" s="81"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="69" t="s">
+      <c r="N76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="70"/>
-      <c r="P76" s="90"/>
+      <c r="O76" s="88"/>
+      <c r="P76" s="89"/>
       <c r="Q76" s="32"/>
-      <c r="R76" s="69" t="s">
+      <c r="R76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="70"/>
-      <c r="T76" s="90"/>
+      <c r="S76" s="88"/>
+      <c r="T76" s="89"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="69" t="s">
+      <c r="V76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="W76" s="70"/>
-      <c r="X76" s="90"/>
+      <c r="W76" s="88"/>
+      <c r="X76" s="89"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="69" t="s">
+      <c r="Z76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="70"/>
-      <c r="AB76" s="90"/>
+      <c r="AA76" s="88"/>
+      <c r="AB76" s="89"/>
       <c r="AC76" s="36"/>
-      <c r="AD76" s="69" t="s">
+      <c r="AD76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AE76" s="70"/>
-      <c r="AF76" s="90"/>
+      <c r="AE76" s="88"/>
+      <c r="AF76" s="89"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="69" t="s">
+      <c r="AH76" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AI76" s="70"/>
-      <c r="AJ76" s="90"/>
+      <c r="AI76" s="88"/>
+      <c r="AJ76" s="89"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="69"/>
-      <c r="AM76" s="70"/>
-      <c r="AN76" s="90"/>
+      <c r="AL76" s="87"/>
+      <c r="AM76" s="88"/>
+      <c r="AN76" s="89"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6316,59 +6334,59 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="87" t="s">
+      <c r="B77" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="88"/>
-      <c r="D77" s="89"/>
+      <c r="C77" s="64"/>
+      <c r="D77" s="65"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="87"/>
-      <c r="G77" s="88"/>
-      <c r="H77" s="89"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="64"/>
+      <c r="H77" s="65"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="87"/>
-      <c r="K77" s="88"/>
-      <c r="L77" s="89"/>
+      <c r="J77" s="63"/>
+      <c r="K77" s="64"/>
+      <c r="L77" s="65"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="87" t="s">
+      <c r="N77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="O77" s="88"/>
-      <c r="P77" s="89"/>
+      <c r="O77" s="64"/>
+      <c r="P77" s="65"/>
       <c r="Q77" s="32"/>
-      <c r="R77" s="87" t="s">
+      <c r="R77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="88"/>
-      <c r="T77" s="89"/>
+      <c r="S77" s="64"/>
+      <c r="T77" s="65"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="87" t="s">
+      <c r="V77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="W77" s="88"/>
-      <c r="X77" s="89"/>
+      <c r="W77" s="64"/>
+      <c r="X77" s="65"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="87" t="s">
+      <c r="Z77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="88"/>
-      <c r="AB77" s="89"/>
+      <c r="AA77" s="64"/>
+      <c r="AB77" s="65"/>
       <c r="AC77" s="32"/>
-      <c r="AD77" s="87" t="s">
+      <c r="AD77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="88"/>
-      <c r="AF77" s="89"/>
+      <c r="AE77" s="64"/>
+      <c r="AF77" s="65"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="87" t="s">
+      <c r="AH77" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="88"/>
-      <c r="AJ77" s="89"/>
+      <c r="AI77" s="64"/>
+      <c r="AJ77" s="65"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="87"/>
-      <c r="AM77" s="88"/>
-      <c r="AN77" s="89"/>
+      <c r="AL77" s="63"/>
+      <c r="AM77" s="64"/>
+      <c r="AN77" s="65"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6376,45 +6394,45 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="97"/>
-      <c r="C78" s="98"/>
-      <c r="D78" s="99"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="68"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="97"/>
-      <c r="G78" s="98"/>
-      <c r="H78" s="99"/>
+      <c r="F78" s="66"/>
+      <c r="G78" s="67"/>
+      <c r="H78" s="68"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="97"/>
-      <c r="K78" s="98"/>
-      <c r="L78" s="99"/>
+      <c r="J78" s="66"/>
+      <c r="K78" s="67"/>
+      <c r="L78" s="68"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="97"/>
-      <c r="O78" s="98"/>
-      <c r="P78" s="99"/>
+      <c r="N78" s="66"/>
+      <c r="O78" s="67"/>
+      <c r="P78" s="68"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="97"/>
-      <c r="S78" s="98"/>
-      <c r="T78" s="99"/>
+      <c r="R78" s="66"/>
+      <c r="S78" s="67"/>
+      <c r="T78" s="68"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="97"/>
-      <c r="W78" s="98"/>
-      <c r="X78" s="99"/>
+      <c r="V78" s="66"/>
+      <c r="W78" s="67"/>
+      <c r="X78" s="68"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="97"/>
-      <c r="AA78" s="98"/>
-      <c r="AB78" s="99"/>
+      <c r="Z78" s="66"/>
+      <c r="AA78" s="67"/>
+      <c r="AB78" s="68"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="97"/>
-      <c r="AE78" s="98"/>
-      <c r="AF78" s="99"/>
+      <c r="AD78" s="66"/>
+      <c r="AE78" s="67"/>
+      <c r="AF78" s="68"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="97"/>
-      <c r="AI78" s="98"/>
-      <c r="AJ78" s="99"/>
+      <c r="AH78" s="66"/>
+      <c r="AI78" s="67"/>
+      <c r="AJ78" s="68"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="97"/>
-      <c r="AM78" s="98"/>
-      <c r="AN78" s="99"/>
+      <c r="AL78" s="66"/>
+      <c r="AM78" s="67"/>
+      <c r="AN78" s="68"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6468,60 +6486,60 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="93" t="s">
+      <c r="B80" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="C80" s="94"/>
+      <c r="C80" s="70"/>
       <c r="D80" s="61"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="93" t="s">
+      <c r="F80" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="G80" s="94"/>
+      <c r="G80" s="70"/>
       <c r="H80" s="61"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="K80" s="94"/>
+      <c r="K80" s="70"/>
       <c r="L80" s="61"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="124" t="s">
+      <c r="N80" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="O80" s="125"/>
+      <c r="O80" s="97"/>
       <c r="P80" s="60"/>
       <c r="Q80" s="36"/>
-      <c r="R80" s="77" t="s">
+      <c r="R80" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="S80" s="78"/>
+      <c r="S80" s="83"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="77"/>
-      <c r="W80" s="78"/>
+      <c r="V80" s="82"/>
+      <c r="W80" s="83"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="95" t="s">
+      <c r="Z80" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="AA80" s="96"/>
+      <c r="AA80" s="75"/>
       <c r="AB80" s="55"/>
       <c r="AC80" s="32"/>
-      <c r="AD80" s="77"/>
-      <c r="AE80" s="78"/>
+      <c r="AD80" s="82"/>
+      <c r="AE80" s="83"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="124" t="s">
+      <c r="AH80" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="AI80" s="125"/>
-      <c r="AJ80" s="60"/>
+      <c r="AI80" s="83"/>
+      <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="77" t="s">
+      <c r="AL80" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="AM80" s="78"/>
+      <c r="AM80" s="83"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6530,57 +6548,57 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="82" t="s">
+      <c r="B81" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="C81" s="83"/>
-      <c r="D81" s="84"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="73"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="82" t="s">
+      <c r="F81" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="83"/>
-      <c r="H81" s="84"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="73"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="82" t="s">
+      <c r="J81" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="K81" s="83"/>
-      <c r="L81" s="84"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="73"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="135" t="s">
+      <c r="N81" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="O81" s="136"/>
-      <c r="P81" s="137"/>
+      <c r="O81" s="94"/>
+      <c r="P81" s="95"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="79" t="s">
+      <c r="R81" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="S81" s="80"/>
-      <c r="T81" s="81"/>
+      <c r="S81" s="85"/>
+      <c r="T81" s="86"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="79"/>
-      <c r="W81" s="80"/>
-      <c r="X81" s="81"/>
+      <c r="V81" s="84"/>
+      <c r="W81" s="85"/>
+      <c r="X81" s="86"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="79" t="s">
+      <c r="Z81" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="AA81" s="80"/>
-      <c r="AB81" s="81"/>
+      <c r="AA81" s="85"/>
+      <c r="AB81" s="86"/>
       <c r="AC81" s="35"/>
-      <c r="AD81" s="79"/>
-      <c r="AE81" s="80"/>
-      <c r="AF81" s="81"/>
+      <c r="AD81" s="84"/>
+      <c r="AE81" s="85"/>
+      <c r="AF81" s="86"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="135"/>
-      <c r="AI81" s="136"/>
-      <c r="AJ81" s="137"/>
+      <c r="AH81" s="84"/>
+      <c r="AI81" s="85"/>
+      <c r="AJ81" s="86"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="79"/>
-      <c r="AM81" s="80"/>
-      <c r="AN81" s="81"/>
+      <c r="AL81" s="84"/>
+      <c r="AM81" s="85"/>
+      <c r="AN81" s="86"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6588,51 +6606,51 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="66"/>
-      <c r="C82" s="67"/>
-      <c r="D82" s="68"/>
+      <c r="B82" s="79"/>
+      <c r="C82" s="80"/>
+      <c r="D82" s="81"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="68"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="80"/>
+      <c r="H82" s="81"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="66"/>
-      <c r="K82" s="67"/>
-      <c r="L82" s="68"/>
+      <c r="J82" s="79"/>
+      <c r="K82" s="80"/>
+      <c r="L82" s="81"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="121"/>
-      <c r="O82" s="122"/>
-      <c r="P82" s="123"/>
+      <c r="N82" s="90"/>
+      <c r="O82" s="91"/>
+      <c r="P82" s="92"/>
       <c r="Q82" s="31"/>
-      <c r="R82" s="69"/>
-      <c r="S82" s="70"/>
-      <c r="T82" s="90"/>
+      <c r="R82" s="87"/>
+      <c r="S82" s="88"/>
+      <c r="T82" s="89"/>
       <c r="U82" s="36"/>
-      <c r="V82" s="69"/>
-      <c r="W82" s="70"/>
-      <c r="X82" s="90"/>
+      <c r="V82" s="87"/>
+      <c r="W82" s="88"/>
+      <c r="X82" s="89"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="69" t="s">
+      <c r="Z82" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AA82" s="70"/>
-      <c r="AB82" s="90"/>
+      <c r="AA82" s="88"/>
+      <c r="AB82" s="89"/>
       <c r="AC82" s="31"/>
-      <c r="AD82" s="69"/>
-      <c r="AE82" s="70"/>
-      <c r="AF82" s="90"/>
+      <c r="AD82" s="87"/>
+      <c r="AE82" s="88"/>
+      <c r="AF82" s="89"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="121" t="s">
+      <c r="AH82" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AI82" s="122"/>
-      <c r="AJ82" s="123"/>
+      <c r="AI82" s="88"/>
+      <c r="AJ82" s="89"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="69" t="s">
+      <c r="AL82" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="AM82" s="70"/>
-      <c r="AN82" s="90"/>
+      <c r="AM82" s="88"/>
+      <c r="AN82" s="89"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6640,61 +6658,61 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="87" t="s">
+      <c r="B83" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="C83" s="88"/>
-      <c r="D83" s="89"/>
+      <c r="C83" s="64"/>
+      <c r="D83" s="65"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="87" t="s">
+      <c r="F83" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="G83" s="88"/>
-      <c r="H83" s="89"/>
+      <c r="G83" s="64"/>
+      <c r="H83" s="65"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="87" t="s">
+      <c r="J83" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="K83" s="88"/>
-      <c r="L83" s="89"/>
+      <c r="K83" s="64"/>
+      <c r="L83" s="65"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="141" t="s">
+      <c r="N83" s="144" t="s">
         <v>96</v>
       </c>
-      <c r="O83" s="142"/>
-      <c r="P83" s="143"/>
+      <c r="O83" s="145"/>
+      <c r="P83" s="146"/>
       <c r="Q83" s="37"/>
-      <c r="R83" s="87" t="s">
+      <c r="R83" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="S83" s="88"/>
-      <c r="T83" s="89"/>
+      <c r="S83" s="64"/>
+      <c r="T83" s="65"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="87"/>
-      <c r="W83" s="88"/>
-      <c r="X83" s="89"/>
+      <c r="V83" s="63"/>
+      <c r="W83" s="64"/>
+      <c r="X83" s="65"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="87" t="s">
+      <c r="Z83" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="88"/>
-      <c r="AB83" s="89"/>
+      <c r="AA83" s="64"/>
+      <c r="AB83" s="65"/>
       <c r="AC83" s="31"/>
-      <c r="AD83" s="87"/>
-      <c r="AE83" s="88"/>
-      <c r="AF83" s="89"/>
+      <c r="AD83" s="63"/>
+      <c r="AE83" s="64"/>
+      <c r="AF83" s="65"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="87" t="s">
+      <c r="AH83" s="147" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI83" s="148"/>
+      <c r="AJ83" s="149"/>
+      <c r="AK83" s="31"/>
+      <c r="AL83" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="AI83" s="88"/>
-      <c r="AJ83" s="89"/>
-      <c r="AK83" s="31"/>
-      <c r="AL83" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM83" s="88"/>
-      <c r="AN83" s="89"/>
+      <c r="AM83" s="64"/>
+      <c r="AN83" s="65"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6702,53 +6720,53 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="97"/>
-      <c r="C84" s="98"/>
-      <c r="D84" s="99"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="68"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="97"/>
-      <c r="G84" s="98"/>
-      <c r="H84" s="99"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="67"/>
+      <c r="H84" s="68"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="97"/>
-      <c r="K84" s="98"/>
-      <c r="L84" s="99"/>
+      <c r="J84" s="66"/>
+      <c r="K84" s="67"/>
+      <c r="L84" s="68"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="144" t="s">
+      <c r="N84" s="111" t="s">
         <v>97</v>
       </c>
-      <c r="O84" s="145"/>
-      <c r="P84" s="146"/>
+      <c r="O84" s="112"/>
+      <c r="P84" s="113"/>
       <c r="Q84" s="44"/>
-      <c r="R84" s="63" t="s">
+      <c r="R84" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="S84" s="64"/>
-      <c r="T84" s="65"/>
+      <c r="S84" s="77"/>
+      <c r="T84" s="78"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="97"/>
-      <c r="W84" s="98"/>
-      <c r="X84" s="99"/>
+      <c r="V84" s="66"/>
+      <c r="W84" s="67"/>
+      <c r="X84" s="68"/>
       <c r="Y84" s="31"/>
-      <c r="Z84" s="97"/>
-      <c r="AA84" s="98"/>
-      <c r="AB84" s="99"/>
+      <c r="Z84" s="66"/>
+      <c r="AA84" s="67"/>
+      <c r="AB84" s="68"/>
       <c r="AC84" s="31"/>
-      <c r="AD84" s="97"/>
-      <c r="AE84" s="98"/>
-      <c r="AF84" s="99"/>
+      <c r="AD84" s="66"/>
+      <c r="AE84" s="67"/>
+      <c r="AF84" s="68"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="138" t="s">
+      <c r="AH84" s="141" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI84" s="142"/>
+      <c r="AJ84" s="143"/>
+      <c r="AK84" s="32"/>
+      <c r="AL84" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="AI84" s="139"/>
-      <c r="AJ84" s="140"/>
-      <c r="AK84" s="32"/>
-      <c r="AL84" s="138" t="s">
-        <v>95</v>
-      </c>
-      <c r="AM84" s="139"/>
-      <c r="AN84" s="140"/>
+      <c r="AM84" s="142"/>
+      <c r="AN84" s="143"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6768,17 +6786,17 @@
       <c r="K85" s="35"/>
       <c r="L85" s="35"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="144" t="s">
+      <c r="N85" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="O85" s="145"/>
-      <c r="P85" s="146"/>
+      <c r="O85" s="112"/>
+      <c r="P85" s="113"/>
       <c r="Q85" s="44"/>
-      <c r="R85" s="63" t="s">
+      <c r="R85" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="S85" s="64"/>
-      <c r="T85" s="65"/>
+      <c r="S85" s="77"/>
+      <c r="T85" s="78"/>
       <c r="U85" s="31"/>
       <c r="V85" s="35"/>
       <c r="W85" s="35"/>
@@ -6806,62 +6824,62 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="93" t="s">
+      <c r="B86" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="C86" s="94"/>
+      <c r="C86" s="70"/>
       <c r="D86" s="61"/>
       <c r="E86" s="32"/>
-      <c r="F86" s="93"/>
-      <c r="G86" s="94"/>
+      <c r="F86" s="69"/>
+      <c r="G86" s="70"/>
       <c r="H86" s="61"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="93"/>
-      <c r="K86" s="94"/>
+      <c r="J86" s="69"/>
+      <c r="K86" s="70"/>
       <c r="L86" s="61"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="144" t="s">
+      <c r="N86" s="111" t="s">
         <v>99</v>
       </c>
-      <c r="O86" s="145"/>
-      <c r="P86" s="146"/>
+      <c r="O86" s="112"/>
+      <c r="P86" s="113"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="63" t="s">
+      <c r="R86" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="S86" s="64"/>
-      <c r="T86" s="65"/>
+      <c r="S86" s="77"/>
+      <c r="T86" s="78"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="77"/>
-      <c r="W86" s="78"/>
+      <c r="V86" s="82"/>
+      <c r="W86" s="83"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="77" t="s">
+      <c r="Z86" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AA86" s="78"/>
+      <c r="AA86" s="83"/>
       <c r="AB86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="77" t="s">
+      <c r="AD86" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AE86" s="78"/>
+      <c r="AE86" s="83"/>
       <c r="AF86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="77" t="s">
+      <c r="AH86" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AI86" s="78"/>
+      <c r="AI86" s="83"/>
       <c r="AJ86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="77"/>
-      <c r="AM86" s="78"/>
+      <c r="AL86" s="82"/>
+      <c r="AM86" s="83"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6870,45 +6888,45 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="82"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="84"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="73"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="83"/>
-      <c r="H87" s="84"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="73"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="83"/>
-      <c r="L87" s="84"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="73"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="129"/>
-      <c r="O87" s="130"/>
-      <c r="P87" s="131"/>
+      <c r="N87" s="98"/>
+      <c r="O87" s="99"/>
+      <c r="P87" s="100"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="63"/>
-      <c r="S87" s="64"/>
-      <c r="T87" s="65"/>
+      <c r="R87" s="76"/>
+      <c r="S87" s="77"/>
+      <c r="T87" s="78"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="79"/>
-      <c r="W87" s="80"/>
-      <c r="X87" s="81"/>
+      <c r="V87" s="84"/>
+      <c r="W87" s="85"/>
+      <c r="X87" s="86"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="69"/>
-      <c r="AA87" s="70"/>
+      <c r="Z87" s="87"/>
+      <c r="AA87" s="88"/>
       <c r="AB87" s="18"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="69"/>
-      <c r="AE87" s="70"/>
+      <c r="AD87" s="87"/>
+      <c r="AE87" s="88"/>
       <c r="AF87" s="18"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="69"/>
-      <c r="AI87" s="70"/>
+      <c r="AH87" s="87"/>
+      <c r="AI87" s="88"/>
       <c r="AJ87" s="18"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="79"/>
-      <c r="AM87" s="80"/>
-      <c r="AN87" s="81"/>
+      <c r="AL87" s="84"/>
+      <c r="AM87" s="85"/>
+      <c r="AN87" s="86"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6916,59 +6934,59 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="66" t="s">
+      <c r="B88" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C88" s="67"/>
-      <c r="D88" s="68"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="81"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="66"/>
-      <c r="G88" s="67"/>
-      <c r="H88" s="68"/>
+      <c r="F88" s="79"/>
+      <c r="G88" s="80"/>
+      <c r="H88" s="81"/>
       <c r="I88" s="31"/>
-      <c r="J88" s="66"/>
-      <c r="K88" s="67"/>
-      <c r="L88" s="68"/>
+      <c r="J88" s="79"/>
+      <c r="K88" s="80"/>
+      <c r="L88" s="81"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="129"/>
-      <c r="O88" s="130"/>
-      <c r="P88" s="131"/>
+      <c r="N88" s="98"/>
+      <c r="O88" s="99"/>
+      <c r="P88" s="100"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="64"/>
-      <c r="T88" s="65"/>
+      <c r="R88" s="76"/>
+      <c r="S88" s="77"/>
+      <c r="T88" s="78"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="69"/>
-      <c r="W88" s="70"/>
-      <c r="X88" s="90"/>
+      <c r="V88" s="87"/>
+      <c r="W88" s="88"/>
+      <c r="X88" s="89"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="71" t="s">
+      <c r="Z88" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="AA88" s="72"/>
+      <c r="AA88" s="140"/>
       <c r="AB88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="71" t="s">
+      <c r="AD88" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="AE88" s="72"/>
+      <c r="AE88" s="140"/>
       <c r="AF88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="71" t="s">
+      <c r="AH88" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="AI88" s="72"/>
+      <c r="AI88" s="140"/>
       <c r="AJ88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="69"/>
-      <c r="AM88" s="70"/>
-      <c r="AN88" s="90"/>
+      <c r="AL88" s="87"/>
+      <c r="AM88" s="88"/>
+      <c r="AN88" s="89"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6976,59 +6994,59 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="87" t="s">
+      <c r="B89" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C89" s="88"/>
-      <c r="D89" s="89"/>
+      <c r="C89" s="64"/>
+      <c r="D89" s="65"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="87"/>
-      <c r="G89" s="88"/>
-      <c r="H89" s="89"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="64"/>
+      <c r="H89" s="65"/>
       <c r="I89" s="31"/>
-      <c r="J89" s="87"/>
-      <c r="K89" s="88"/>
-      <c r="L89" s="89"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="64"/>
+      <c r="L89" s="65"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="129"/>
-      <c r="O89" s="130"/>
-      <c r="P89" s="131"/>
+      <c r="N89" s="98"/>
+      <c r="O89" s="99"/>
+      <c r="P89" s="100"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="63"/>
-      <c r="S89" s="64"/>
-      <c r="T89" s="65"/>
+      <c r="R89" s="76"/>
+      <c r="S89" s="77"/>
+      <c r="T89" s="78"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="87"/>
-      <c r="W89" s="88"/>
-      <c r="X89" s="89"/>
+      <c r="V89" s="63"/>
+      <c r="W89" s="64"/>
+      <c r="X89" s="65"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="73" t="s">
+      <c r="Z89" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="AA89" s="74"/>
+      <c r="AA89" s="118"/>
       <c r="AB89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="73" t="s">
+      <c r="AD89" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="AE89" s="74"/>
+      <c r="AE89" s="118"/>
       <c r="AF89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="73" t="s">
+      <c r="AH89" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="AI89" s="74"/>
+      <c r="AI89" s="118"/>
       <c r="AJ89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="87"/>
-      <c r="AM89" s="88"/>
-      <c r="AN89" s="89"/>
+      <c r="AL89" s="63"/>
+      <c r="AM89" s="64"/>
+      <c r="AN89" s="65"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7036,57 +7054,57 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="97"/>
-      <c r="C90" s="98"/>
-      <c r="D90" s="99"/>
+      <c r="B90" s="66"/>
+      <c r="C90" s="67"/>
+      <c r="D90" s="68"/>
       <c r="E90" s="31"/>
-      <c r="F90" s="97"/>
-      <c r="G90" s="98"/>
-      <c r="H90" s="99"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="67"/>
+      <c r="H90" s="68"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="97"/>
-      <c r="K90" s="98"/>
-      <c r="L90" s="99"/>
+      <c r="J90" s="66"/>
+      <c r="K90" s="67"/>
+      <c r="L90" s="68"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="126"/>
-      <c r="O90" s="127"/>
-      <c r="P90" s="128"/>
+      <c r="N90" s="108"/>
+      <c r="O90" s="109"/>
+      <c r="P90" s="110"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="97"/>
-      <c r="S90" s="98"/>
-      <c r="T90" s="99"/>
+      <c r="R90" s="66"/>
+      <c r="S90" s="67"/>
+      <c r="T90" s="68"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="97"/>
-      <c r="W90" s="98"/>
-      <c r="X90" s="99"/>
+      <c r="V90" s="66"/>
+      <c r="W90" s="67"/>
+      <c r="X90" s="68"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="75" t="s">
+      <c r="Z90" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="AA90" s="76"/>
+      <c r="AA90" s="105"/>
       <c r="AB90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="75" t="s">
+      <c r="AD90" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="AE90" s="76"/>
+      <c r="AE90" s="105"/>
       <c r="AF90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="75" t="s">
+      <c r="AH90" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="AI90" s="76"/>
+      <c r="AI90" s="105"/>
       <c r="AJ90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="97"/>
-      <c r="AM90" s="98"/>
-      <c r="AN90" s="99"/>
+      <c r="AL90" s="66"/>
+      <c r="AM90" s="67"/>
+      <c r="AN90" s="68"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7118,26 +7136,26 @@
       <c r="W91" s="35"/>
       <c r="X91" s="35"/>
       <c r="Y91" s="35"/>
-      <c r="Z91" s="75" t="s">
+      <c r="Z91" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="AA91" s="76"/>
+      <c r="AA91" s="105"/>
       <c r="AB91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC91" s="44"/>
-      <c r="AD91" s="75" t="s">
+      <c r="AD91" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="AE91" s="76"/>
+      <c r="AE91" s="105"/>
       <c r="AF91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG91" s="44"/>
-      <c r="AH91" s="75" t="s">
+      <c r="AH91" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="AI91" s="76"/>
+      <c r="AI91" s="105"/>
       <c r="AJ91" s="45" t="s">
         <v>35</v>
       </c>
@@ -7152,58 +7170,58 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="93" t="s">
+      <c r="B92" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C92" s="94"/>
+      <c r="C92" s="70"/>
       <c r="D92" s="61"/>
       <c r="E92" s="32"/>
-      <c r="F92" s="93"/>
-      <c r="G92" s="94"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
       <c r="H92" s="61"/>
       <c r="I92" s="31"/>
-      <c r="J92" s="93"/>
-      <c r="K92" s="94"/>
+      <c r="J92" s="69"/>
+      <c r="K92" s="70"/>
       <c r="L92" s="61"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="77"/>
-      <c r="O92" s="78"/>
+      <c r="N92" s="82"/>
+      <c r="O92" s="83"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="36"/>
-      <c r="R92" s="77"/>
-      <c r="S92" s="78"/>
+      <c r="R92" s="82"/>
+      <c r="S92" s="83"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="77"/>
-      <c r="W92" s="78"/>
+      <c r="V92" s="82"/>
+      <c r="W92" s="83"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="75" t="s">
+      <c r="Z92" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="AA92" s="76"/>
+      <c r="AA92" s="105"/>
       <c r="AB92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="75" t="s">
+      <c r="AD92" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="AE92" s="76"/>
+      <c r="AE92" s="105"/>
       <c r="AF92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="75" t="s">
+      <c r="AH92" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="AI92" s="76"/>
+      <c r="AI92" s="105"/>
       <c r="AJ92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="77"/>
-      <c r="AM92" s="78"/>
+      <c r="AL92" s="82"/>
+      <c r="AM92" s="83"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -7212,47 +7230,47 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="82" t="s">
+      <c r="B93" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="83"/>
-      <c r="D93" s="84"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="73"/>
       <c r="E93" s="32"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="84"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="73"/>
       <c r="I93" s="31"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="83"/>
-      <c r="L93" s="84"/>
+      <c r="J93" s="71"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="73"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="79"/>
-      <c r="O93" s="80"/>
-      <c r="P93" s="81"/>
+      <c r="N93" s="84"/>
+      <c r="O93" s="85"/>
+      <c r="P93" s="86"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="79"/>
-      <c r="S93" s="80"/>
-      <c r="T93" s="81"/>
+      <c r="R93" s="84"/>
+      <c r="S93" s="85"/>
+      <c r="T93" s="86"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="79"/>
-      <c r="W93" s="80"/>
-      <c r="X93" s="81"/>
+      <c r="V93" s="84"/>
+      <c r="W93" s="85"/>
+      <c r="X93" s="86"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="75"/>
-      <c r="AA93" s="76"/>
+      <c r="Z93" s="104"/>
+      <c r="AA93" s="105"/>
       <c r="AB93" s="45"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="75"/>
-      <c r="AE93" s="76"/>
+      <c r="AD93" s="104"/>
+      <c r="AE93" s="105"/>
       <c r="AF93" s="45"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="75"/>
-      <c r="AI93" s="76"/>
+      <c r="AH93" s="104"/>
+      <c r="AI93" s="105"/>
       <c r="AJ93" s="45"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="79"/>
-      <c r="AM93" s="80"/>
-      <c r="AN93" s="81"/>
+      <c r="AL93" s="84"/>
+      <c r="AM93" s="85"/>
+      <c r="AN93" s="86"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -7260,45 +7278,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="66"/>
-      <c r="C94" s="67"/>
-      <c r="D94" s="68"/>
+      <c r="B94" s="79"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="81"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="67"/>
-      <c r="H94" s="68"/>
+      <c r="F94" s="79"/>
+      <c r="G94" s="80"/>
+      <c r="H94" s="81"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="66"/>
-      <c r="K94" s="67"/>
-      <c r="L94" s="68"/>
+      <c r="J94" s="79"/>
+      <c r="K94" s="80"/>
+      <c r="L94" s="81"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="69"/>
-      <c r="O94" s="70"/>
-      <c r="P94" s="90"/>
+      <c r="N94" s="87"/>
+      <c r="O94" s="88"/>
+      <c r="P94" s="89"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="69"/>
-      <c r="S94" s="70"/>
-      <c r="T94" s="90"/>
+      <c r="R94" s="87"/>
+      <c r="S94" s="88"/>
+      <c r="T94" s="89"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="69"/>
-      <c r="W94" s="70"/>
-      <c r="X94" s="90"/>
+      <c r="V94" s="87"/>
+      <c r="W94" s="88"/>
+      <c r="X94" s="89"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="75"/>
-      <c r="AA94" s="76"/>
+      <c r="Z94" s="104"/>
+      <c r="AA94" s="105"/>
       <c r="AB94" s="45"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="75"/>
-      <c r="AE94" s="76"/>
+      <c r="AD94" s="104"/>
+      <c r="AE94" s="105"/>
       <c r="AF94" s="45"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="75"/>
-      <c r="AI94" s="76"/>
+      <c r="AH94" s="104"/>
+      <c r="AI94" s="105"/>
       <c r="AJ94" s="45"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="69"/>
-      <c r="AM94" s="70"/>
-      <c r="AN94" s="90"/>
+      <c r="AL94" s="87"/>
+      <c r="AM94" s="88"/>
+      <c r="AN94" s="89"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7306,47 +7324,47 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="87" t="s">
+      <c r="B95" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="88"/>
-      <c r="D95" s="89"/>
+      <c r="C95" s="64"/>
+      <c r="D95" s="65"/>
       <c r="E95" s="32"/>
-      <c r="F95" s="87"/>
-      <c r="G95" s="88"/>
-      <c r="H95" s="89"/>
+      <c r="F95" s="63"/>
+      <c r="G95" s="64"/>
+      <c r="H95" s="65"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="87"/>
-      <c r="K95" s="88"/>
-      <c r="L95" s="89"/>
+      <c r="J95" s="63"/>
+      <c r="K95" s="64"/>
+      <c r="L95" s="65"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="87"/>
-      <c r="O95" s="88"/>
-      <c r="P95" s="89"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="64"/>
+      <c r="P95" s="65"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="87"/>
-      <c r="S95" s="88"/>
-      <c r="T95" s="89"/>
+      <c r="R95" s="63"/>
+      <c r="S95" s="64"/>
+      <c r="T95" s="65"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="87"/>
-      <c r="W95" s="88"/>
-      <c r="X95" s="89"/>
+      <c r="V95" s="63"/>
+      <c r="W95" s="64"/>
+      <c r="X95" s="65"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="75"/>
-      <c r="AA95" s="76"/>
+      <c r="Z95" s="104"/>
+      <c r="AA95" s="105"/>
       <c r="AB95" s="45"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="75"/>
-      <c r="AE95" s="76"/>
+      <c r="AD95" s="104"/>
+      <c r="AE95" s="105"/>
       <c r="AF95" s="45"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="75"/>
-      <c r="AI95" s="76"/>
+      <c r="AH95" s="104"/>
+      <c r="AI95" s="105"/>
       <c r="AJ95" s="45"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="87"/>
-      <c r="AM95" s="88"/>
-      <c r="AN95" s="89"/>
+      <c r="AL95" s="63"/>
+      <c r="AM95" s="64"/>
+      <c r="AN95" s="65"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7354,45 +7372,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="63"/>
-      <c r="C96" s="64"/>
-      <c r="D96" s="65"/>
+      <c r="B96" s="76"/>
+      <c r="C96" s="77"/>
+      <c r="D96" s="78"/>
       <c r="E96" s="31"/>
-      <c r="F96" s="97"/>
-      <c r="G96" s="98"/>
-      <c r="H96" s="99"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="67"/>
+      <c r="H96" s="68"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="97"/>
-      <c r="K96" s="98"/>
-      <c r="L96" s="99"/>
+      <c r="J96" s="66"/>
+      <c r="K96" s="67"/>
+      <c r="L96" s="68"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="97"/>
-      <c r="O96" s="98"/>
-      <c r="P96" s="99"/>
+      <c r="N96" s="66"/>
+      <c r="O96" s="67"/>
+      <c r="P96" s="68"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="97"/>
-      <c r="S96" s="98"/>
-      <c r="T96" s="99"/>
+      <c r="R96" s="66"/>
+      <c r="S96" s="67"/>
+      <c r="T96" s="68"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="97"/>
-      <c r="W96" s="98"/>
-      <c r="X96" s="99"/>
+      <c r="V96" s="66"/>
+      <c r="W96" s="67"/>
+      <c r="X96" s="68"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="85"/>
-      <c r="AA96" s="86"/>
+      <c r="Z96" s="106"/>
+      <c r="AA96" s="107"/>
       <c r="AB96" s="42"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="85"/>
-      <c r="AE96" s="86"/>
+      <c r="AD96" s="106"/>
+      <c r="AE96" s="107"/>
       <c r="AF96" s="42"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="85"/>
-      <c r="AI96" s="86"/>
+      <c r="AH96" s="106"/>
+      <c r="AI96" s="107"/>
       <c r="AJ96" s="42"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="97"/>
-      <c r="AM96" s="98"/>
-      <c r="AN96" s="99"/>
+      <c r="AL96" s="66"/>
+      <c r="AM96" s="67"/>
+      <c r="AN96" s="68"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7400,11 +7418,11 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
-      <c r="B97" s="63" t="s">
+      <c r="B97" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="64"/>
-      <c r="D97" s="65"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="78"/>
       <c r="E97" s="35"/>
       <c r="F97" s="35"/>
       <c r="G97" s="35"/>
@@ -7448,56 +7466,56 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="63" t="s">
+      <c r="B98" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="C98" s="64"/>
-      <c r="D98" s="65"/>
+      <c r="C98" s="77"/>
+      <c r="D98" s="78"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="93"/>
-      <c r="G98" s="94"/>
+      <c r="F98" s="69"/>
+      <c r="G98" s="70"/>
       <c r="H98" s="61"/>
       <c r="I98" s="31"/>
-      <c r="J98" s="93"/>
-      <c r="K98" s="94"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="70"/>
       <c r="L98" s="61"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="77" t="s">
+      <c r="N98" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="O98" s="78"/>
+      <c r="O98" s="83"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="77" t="s">
+      <c r="R98" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="S98" s="78"/>
+      <c r="S98" s="83"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="77" t="s">
+      <c r="V98" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="W98" s="78"/>
+      <c r="W98" s="83"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="77" t="s">
+      <c r="Z98" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="AA98" s="78"/>
+      <c r="AA98" s="83"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="77" t="s">
+      <c r="AD98" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="AE98" s="78"/>
+      <c r="AE98" s="83"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="77"/>
-      <c r="AI98" s="78"/>
+      <c r="AH98" s="82"/>
+      <c r="AI98" s="83"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="77"/>
-      <c r="AM98" s="78"/>
+      <c r="AL98" s="82"/>
+      <c r="AM98" s="83"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7506,57 +7524,57 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="63" t="s">
+      <c r="B99" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="64"/>
-      <c r="D99" s="65"/>
+      <c r="C99" s="77"/>
+      <c r="D99" s="78"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="82"/>
-      <c r="G99" s="83"/>
-      <c r="H99" s="84"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="73"/>
       <c r="I99" s="31"/>
-      <c r="J99" s="82"/>
-      <c r="K99" s="83"/>
-      <c r="L99" s="84"/>
+      <c r="J99" s="71"/>
+      <c r="K99" s="72"/>
+      <c r="L99" s="73"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="79" t="s">
+      <c r="N99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="O99" s="80"/>
-      <c r="P99" s="81"/>
+      <c r="O99" s="85"/>
+      <c r="P99" s="86"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="79" t="s">
+      <c r="R99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="S99" s="80"/>
-      <c r="T99" s="81"/>
+      <c r="S99" s="85"/>
+      <c r="T99" s="86"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="79" t="s">
+      <c r="V99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="W99" s="80"/>
-      <c r="X99" s="81"/>
+      <c r="W99" s="85"/>
+      <c r="X99" s="86"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="79" t="s">
+      <c r="Z99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="AA99" s="80"/>
-      <c r="AB99" s="81"/>
+      <c r="AA99" s="85"/>
+      <c r="AB99" s="86"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="79" t="s">
+      <c r="AD99" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="AE99" s="80"/>
-      <c r="AF99" s="81"/>
+      <c r="AE99" s="85"/>
+      <c r="AF99" s="86"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="79"/>
-      <c r="AI99" s="80"/>
-      <c r="AJ99" s="81"/>
+      <c r="AH99" s="84"/>
+      <c r="AI99" s="85"/>
+      <c r="AJ99" s="86"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="79"/>
-      <c r="AM99" s="80"/>
-      <c r="AN99" s="81"/>
+      <c r="AL99" s="84"/>
+      <c r="AM99" s="85"/>
+      <c r="AN99" s="86"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7564,47 +7582,47 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="63" t="s">
+      <c r="B100" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C100" s="64"/>
-      <c r="D100" s="65"/>
+      <c r="C100" s="77"/>
+      <c r="D100" s="78"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="66"/>
-      <c r="G100" s="67"/>
-      <c r="H100" s="68"/>
+      <c r="F100" s="79"/>
+      <c r="G100" s="80"/>
+      <c r="H100" s="81"/>
       <c r="I100" s="32"/>
-      <c r="J100" s="66"/>
-      <c r="K100" s="67"/>
-      <c r="L100" s="68"/>
+      <c r="J100" s="79"/>
+      <c r="K100" s="80"/>
+      <c r="L100" s="81"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="69"/>
-      <c r="O100" s="70"/>
-      <c r="P100" s="90"/>
+      <c r="N100" s="87"/>
+      <c r="O100" s="88"/>
+      <c r="P100" s="89"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="69"/>
-      <c r="S100" s="70"/>
-      <c r="T100" s="90"/>
+      <c r="R100" s="87"/>
+      <c r="S100" s="88"/>
+      <c r="T100" s="89"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="69"/>
-      <c r="W100" s="70"/>
-      <c r="X100" s="90"/>
+      <c r="V100" s="87"/>
+      <c r="W100" s="88"/>
+      <c r="X100" s="89"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="69"/>
-      <c r="AA100" s="70"/>
-      <c r="AB100" s="90"/>
+      <c r="Z100" s="87"/>
+      <c r="AA100" s="88"/>
+      <c r="AB100" s="89"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="69"/>
-      <c r="AE100" s="70"/>
-      <c r="AF100" s="90"/>
+      <c r="AD100" s="87"/>
+      <c r="AE100" s="88"/>
+      <c r="AF100" s="89"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="69"/>
-      <c r="AI100" s="70"/>
-      <c r="AJ100" s="90"/>
+      <c r="AH100" s="87"/>
+      <c r="AI100" s="88"/>
+      <c r="AJ100" s="89"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="69"/>
-      <c r="AM100" s="70"/>
-      <c r="AN100" s="90"/>
+      <c r="AL100" s="87"/>
+      <c r="AM100" s="88"/>
+      <c r="AN100" s="89"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7612,57 +7630,57 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="63" t="s">
+      <c r="B101" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="64"/>
-      <c r="D101" s="65"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="78"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="87"/>
-      <c r="G101" s="88"/>
-      <c r="H101" s="89"/>
+      <c r="F101" s="63"/>
+      <c r="G101" s="64"/>
+      <c r="H101" s="65"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="87"/>
-      <c r="K101" s="88"/>
-      <c r="L101" s="89"/>
+      <c r="J101" s="63"/>
+      <c r="K101" s="64"/>
+      <c r="L101" s="65"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="87" t="s">
+      <c r="N101" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="O101" s="88"/>
-      <c r="P101" s="89"/>
+      <c r="O101" s="64"/>
+      <c r="P101" s="65"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="87" t="s">
+      <c r="R101" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="S101" s="88"/>
-      <c r="T101" s="89"/>
+      <c r="S101" s="64"/>
+      <c r="T101" s="65"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="87" t="s">
+      <c r="V101" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="W101" s="88"/>
-      <c r="X101" s="89"/>
+      <c r="W101" s="64"/>
+      <c r="X101" s="65"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="87" t="s">
+      <c r="Z101" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="AA101" s="88"/>
-      <c r="AB101" s="89"/>
+      <c r="AA101" s="64"/>
+      <c r="AB101" s="65"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="87" t="s">
+      <c r="AD101" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="AE101" s="88"/>
-      <c r="AF101" s="89"/>
+      <c r="AE101" s="64"/>
+      <c r="AF101" s="65"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="87"/>
-      <c r="AI101" s="88"/>
-      <c r="AJ101" s="89"/>
+      <c r="AH101" s="63"/>
+      <c r="AI101" s="64"/>
+      <c r="AJ101" s="65"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="87"/>
-      <c r="AM101" s="88"/>
-      <c r="AN101" s="89"/>
+      <c r="AL101" s="63"/>
+      <c r="AM101" s="64"/>
+      <c r="AN101" s="65"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7670,45 +7688,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="97"/>
-      <c r="C102" s="98"/>
-      <c r="D102" s="99"/>
+      <c r="B102" s="66"/>
+      <c r="C102" s="67"/>
+      <c r="D102" s="68"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="97"/>
-      <c r="G102" s="98"/>
-      <c r="H102" s="99"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="67"/>
+      <c r="H102" s="68"/>
       <c r="I102" s="31"/>
-      <c r="J102" s="97"/>
-      <c r="K102" s="98"/>
-      <c r="L102" s="99"/>
+      <c r="J102" s="66"/>
+      <c r="K102" s="67"/>
+      <c r="L102" s="68"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="97"/>
-      <c r="O102" s="98"/>
-      <c r="P102" s="99"/>
+      <c r="N102" s="66"/>
+      <c r="O102" s="67"/>
+      <c r="P102" s="68"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="97"/>
-      <c r="S102" s="98"/>
-      <c r="T102" s="99"/>
+      <c r="R102" s="66"/>
+      <c r="S102" s="67"/>
+      <c r="T102" s="68"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="97"/>
-      <c r="W102" s="98"/>
-      <c r="X102" s="99"/>
+      <c r="V102" s="66"/>
+      <c r="W102" s="67"/>
+      <c r="X102" s="68"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="97"/>
-      <c r="AA102" s="98"/>
-      <c r="AB102" s="99"/>
+      <c r="Z102" s="66"/>
+      <c r="AA102" s="67"/>
+      <c r="AB102" s="68"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="97"/>
-      <c r="AE102" s="98"/>
-      <c r="AF102" s="99"/>
+      <c r="AD102" s="66"/>
+      <c r="AE102" s="67"/>
+      <c r="AF102" s="68"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="97"/>
-      <c r="AI102" s="98"/>
-      <c r="AJ102" s="99"/>
+      <c r="AH102" s="66"/>
+      <c r="AI102" s="67"/>
+      <c r="AJ102" s="68"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="97"/>
-      <c r="AM102" s="98"/>
-      <c r="AN102" s="99"/>
+      <c r="AL102" s="66"/>
+      <c r="AM102" s="67"/>
+      <c r="AN102" s="68"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7778,70 +7796,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="77"/>
-      <c r="C105" s="78"/>
+      <c r="B105" s="82"/>
+      <c r="C105" s="83"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="77"/>
-      <c r="G105" s="78"/>
+      <c r="F105" s="82"/>
+      <c r="G105" s="83"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="77"/>
-      <c r="K105" s="78"/>
+      <c r="J105" s="82"/>
+      <c r="K105" s="83"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="79"/>
-      <c r="C106" s="80"/>
-      <c r="D106" s="81"/>
+      <c r="B106" s="84"/>
+      <c r="C106" s="85"/>
+      <c r="D106" s="86"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="79"/>
-      <c r="G106" s="80"/>
-      <c r="H106" s="81"/>
+      <c r="F106" s="84"/>
+      <c r="G106" s="85"/>
+      <c r="H106" s="86"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="79"/>
-      <c r="K106" s="80"/>
-      <c r="L106" s="81"/>
+      <c r="J106" s="84"/>
+      <c r="K106" s="85"/>
+      <c r="L106" s="86"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="69"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="90"/>
+      <c r="B107" s="87"/>
+      <c r="C107" s="88"/>
+      <c r="D107" s="89"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="70"/>
-      <c r="H107" s="90"/>
+      <c r="F107" s="87"/>
+      <c r="G107" s="88"/>
+      <c r="H107" s="89"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="69"/>
-      <c r="K107" s="70"/>
-      <c r="L107" s="90"/>
+      <c r="J107" s="87"/>
+      <c r="K107" s="88"/>
+      <c r="L107" s="89"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="87"/>
-      <c r="C108" s="88"/>
-      <c r="D108" s="89"/>
+      <c r="B108" s="63"/>
+      <c r="C108" s="64"/>
+      <c r="D108" s="65"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="87"/>
-      <c r="G108" s="88"/>
-      <c r="H108" s="89"/>
+      <c r="F108" s="63"/>
+      <c r="G108" s="64"/>
+      <c r="H108" s="65"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="87"/>
-      <c r="K108" s="88"/>
-      <c r="L108" s="89"/>
+      <c r="J108" s="63"/>
+      <c r="K108" s="64"/>
+      <c r="L108" s="65"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="97"/>
-      <c r="C109" s="98"/>
-      <c r="D109" s="99"/>
+      <c r="B109" s="66"/>
+      <c r="C109" s="67"/>
+      <c r="D109" s="68"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="97"/>
-      <c r="G109" s="98"/>
-      <c r="H109" s="99"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="67"/>
+      <c r="H109" s="68"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="97"/>
-      <c r="K109" s="98"/>
-      <c r="L109" s="99"/>
+      <c r="J109" s="66"/>
+      <c r="K109" s="67"/>
+      <c r="L109" s="68"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7857,69 +7875,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="77"/>
-      <c r="C111" s="78"/>
+      <c r="B111" s="82"/>
+      <c r="C111" s="83"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="77"/>
-      <c r="G111" s="78"/>
+      <c r="F111" s="82"/>
+      <c r="G111" s="83"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="77"/>
-      <c r="K111" s="78"/>
+      <c r="J111" s="82"/>
+      <c r="K111" s="83"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="79"/>
-      <c r="C112" s="80"/>
-      <c r="D112" s="81"/>
+      <c r="B112" s="84"/>
+      <c r="C112" s="85"/>
+      <c r="D112" s="86"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="79"/>
-      <c r="G112" s="80"/>
-      <c r="H112" s="81"/>
+      <c r="F112" s="84"/>
+      <c r="G112" s="85"/>
+      <c r="H112" s="86"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="79"/>
-      <c r="K112" s="80"/>
-      <c r="L112" s="81"/>
+      <c r="J112" s="84"/>
+      <c r="K112" s="85"/>
+      <c r="L112" s="86"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="69"/>
-      <c r="C113" s="70"/>
-      <c r="D113" s="90"/>
+      <c r="B113" s="87"/>
+      <c r="C113" s="88"/>
+      <c r="D113" s="89"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="69"/>
-      <c r="G113" s="70"/>
-      <c r="H113" s="90"/>
+      <c r="F113" s="87"/>
+      <c r="G113" s="88"/>
+      <c r="H113" s="89"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="69"/>
-      <c r="K113" s="70"/>
-      <c r="L113" s="90"/>
+      <c r="J113" s="87"/>
+      <c r="K113" s="88"/>
+      <c r="L113" s="89"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="87"/>
-      <c r="C114" s="88"/>
-      <c r="D114" s="89"/>
+      <c r="B114" s="63"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="65"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="87"/>
-      <c r="G114" s="88"/>
-      <c r="H114" s="89"/>
+      <c r="F114" s="63"/>
+      <c r="G114" s="64"/>
+      <c r="H114" s="65"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="87"/>
-      <c r="K114" s="88"/>
-      <c r="L114" s="89"/>
+      <c r="J114" s="63"/>
+      <c r="K114" s="64"/>
+      <c r="L114" s="65"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="97"/>
-      <c r="C115" s="98"/>
-      <c r="D115" s="99"/>
+      <c r="B115" s="66"/>
+      <c r="C115" s="67"/>
+      <c r="D115" s="68"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="97"/>
-      <c r="G115" s="98"/>
-      <c r="H115" s="99"/>
+      <c r="F115" s="66"/>
+      <c r="G115" s="67"/>
+      <c r="H115" s="68"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="97"/>
-      <c r="K115" s="98"/>
-      <c r="L115" s="99"/>
+      <c r="J115" s="66"/>
+      <c r="K115" s="67"/>
+      <c r="L115" s="68"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7935,69 +7953,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="77"/>
-      <c r="C117" s="78"/>
+      <c r="B117" s="82"/>
+      <c r="C117" s="83"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="77"/>
-      <c r="G117" s="78"/>
+      <c r="F117" s="82"/>
+      <c r="G117" s="83"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="77"/>
-      <c r="K117" s="78"/>
+      <c r="J117" s="82"/>
+      <c r="K117" s="83"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="79"/>
-      <c r="C118" s="80"/>
-      <c r="D118" s="81"/>
+      <c r="B118" s="84"/>
+      <c r="C118" s="85"/>
+      <c r="D118" s="86"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="79"/>
-      <c r="G118" s="80"/>
-      <c r="H118" s="81"/>
+      <c r="F118" s="84"/>
+      <c r="G118" s="85"/>
+      <c r="H118" s="86"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="79"/>
-      <c r="K118" s="80"/>
-      <c r="L118" s="81"/>
+      <c r="J118" s="84"/>
+      <c r="K118" s="85"/>
+      <c r="L118" s="86"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="69"/>
-      <c r="C119" s="70"/>
-      <c r="D119" s="90"/>
+      <c r="B119" s="87"/>
+      <c r="C119" s="88"/>
+      <c r="D119" s="89"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="69"/>
-      <c r="G119" s="70"/>
-      <c r="H119" s="90"/>
+      <c r="F119" s="87"/>
+      <c r="G119" s="88"/>
+      <c r="H119" s="89"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="69"/>
-      <c r="K119" s="70"/>
-      <c r="L119" s="90"/>
+      <c r="J119" s="87"/>
+      <c r="K119" s="88"/>
+      <c r="L119" s="89"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="87"/>
-      <c r="C120" s="88"/>
-      <c r="D120" s="89"/>
+      <c r="B120" s="63"/>
+      <c r="C120" s="64"/>
+      <c r="D120" s="65"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="87"/>
-      <c r="G120" s="88"/>
-      <c r="H120" s="89"/>
+      <c r="F120" s="63"/>
+      <c r="G120" s="64"/>
+      <c r="H120" s="65"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="87"/>
-      <c r="K120" s="88"/>
-      <c r="L120" s="89"/>
+      <c r="J120" s="63"/>
+      <c r="K120" s="64"/>
+      <c r="L120" s="65"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="97"/>
-      <c r="C121" s="98"/>
-      <c r="D121" s="99"/>
+      <c r="B121" s="66"/>
+      <c r="C121" s="67"/>
+      <c r="D121" s="68"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="97"/>
-      <c r="G121" s="98"/>
-      <c r="H121" s="99"/>
+      <c r="F121" s="66"/>
+      <c r="G121" s="67"/>
+      <c r="H121" s="68"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="97"/>
-      <c r="K121" s="98"/>
-      <c r="L121" s="99"/>
+      <c r="J121" s="66"/>
+      <c r="K121" s="67"/>
+      <c r="L121" s="68"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -8013,69 +8031,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="77"/>
-      <c r="C123" s="78"/>
+      <c r="B123" s="82"/>
+      <c r="C123" s="83"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="77"/>
-      <c r="G123" s="78"/>
+      <c r="F123" s="82"/>
+      <c r="G123" s="83"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="77"/>
-      <c r="K123" s="78"/>
+      <c r="J123" s="82"/>
+      <c r="K123" s="83"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="79"/>
-      <c r="C124" s="80"/>
-      <c r="D124" s="81"/>
+      <c r="B124" s="84"/>
+      <c r="C124" s="85"/>
+      <c r="D124" s="86"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="79"/>
-      <c r="G124" s="80"/>
-      <c r="H124" s="81"/>
+      <c r="F124" s="84"/>
+      <c r="G124" s="85"/>
+      <c r="H124" s="86"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="79"/>
-      <c r="K124" s="80"/>
-      <c r="L124" s="81"/>
+      <c r="J124" s="84"/>
+      <c r="K124" s="85"/>
+      <c r="L124" s="86"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="69"/>
-      <c r="C125" s="70"/>
-      <c r="D125" s="90"/>
+      <c r="B125" s="87"/>
+      <c r="C125" s="88"/>
+      <c r="D125" s="89"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="69"/>
-      <c r="G125" s="70"/>
-      <c r="H125" s="90"/>
+      <c r="F125" s="87"/>
+      <c r="G125" s="88"/>
+      <c r="H125" s="89"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="69"/>
-      <c r="K125" s="70"/>
-      <c r="L125" s="90"/>
+      <c r="J125" s="87"/>
+      <c r="K125" s="88"/>
+      <c r="L125" s="89"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="87"/>
-      <c r="C126" s="88"/>
-      <c r="D126" s="89"/>
+      <c r="B126" s="63"/>
+      <c r="C126" s="64"/>
+      <c r="D126" s="65"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="87"/>
-      <c r="G126" s="88"/>
-      <c r="H126" s="89"/>
+      <c r="F126" s="63"/>
+      <c r="G126" s="64"/>
+      <c r="H126" s="65"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="87"/>
-      <c r="K126" s="88"/>
-      <c r="L126" s="89"/>
+      <c r="J126" s="63"/>
+      <c r="K126" s="64"/>
+      <c r="L126" s="65"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="97"/>
-      <c r="C127" s="98"/>
-      <c r="D127" s="99"/>
+      <c r="B127" s="66"/>
+      <c r="C127" s="67"/>
+      <c r="D127" s="68"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="97"/>
-      <c r="G127" s="98"/>
-      <c r="H127" s="99"/>
+      <c r="F127" s="66"/>
+      <c r="G127" s="67"/>
+      <c r="H127" s="68"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="97"/>
-      <c r="K127" s="98"/>
-      <c r="L127" s="99"/>
+      <c r="J127" s="66"/>
+      <c r="K127" s="67"/>
+      <c r="L127" s="68"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8091,98 +8109,913 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="77"/>
-      <c r="C129" s="78"/>
+      <c r="B129" s="82"/>
+      <c r="C129" s="83"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="77"/>
-      <c r="G129" s="78"/>
+      <c r="F129" s="82"/>
+      <c r="G129" s="83"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="77"/>
-      <c r="K129" s="78"/>
+      <c r="J129" s="82"/>
+      <c r="K129" s="83"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="79"/>
-      <c r="C130" s="80"/>
-      <c r="D130" s="81"/>
+      <c r="B130" s="84"/>
+      <c r="C130" s="85"/>
+      <c r="D130" s="86"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="79"/>
-      <c r="G130" s="80"/>
-      <c r="H130" s="81"/>
+      <c r="F130" s="84"/>
+      <c r="G130" s="85"/>
+      <c r="H130" s="86"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="79"/>
-      <c r="K130" s="80"/>
-      <c r="L130" s="81"/>
+      <c r="J130" s="84"/>
+      <c r="K130" s="85"/>
+      <c r="L130" s="86"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="69"/>
-      <c r="C131" s="70"/>
-      <c r="D131" s="90"/>
+      <c r="B131" s="87"/>
+      <c r="C131" s="88"/>
+      <c r="D131" s="89"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="69"/>
-      <c r="G131" s="70"/>
-      <c r="H131" s="90"/>
+      <c r="F131" s="87"/>
+      <c r="G131" s="88"/>
+      <c r="H131" s="89"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="69"/>
-      <c r="K131" s="70"/>
-      <c r="L131" s="90"/>
+      <c r="J131" s="87"/>
+      <c r="K131" s="88"/>
+      <c r="L131" s="89"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="87"/>
-      <c r="C132" s="88"/>
-      <c r="D132" s="89"/>
+      <c r="B132" s="63"/>
+      <c r="C132" s="64"/>
+      <c r="D132" s="65"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="87"/>
-      <c r="G132" s="88"/>
-      <c r="H132" s="89"/>
+      <c r="F132" s="63"/>
+      <c r="G132" s="64"/>
+      <c r="H132" s="65"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="87"/>
-      <c r="K132" s="88"/>
-      <c r="L132" s="89"/>
+      <c r="J132" s="63"/>
+      <c r="K132" s="64"/>
+      <c r="L132" s="65"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="97"/>
-      <c r="C133" s="98"/>
-      <c r="D133" s="99"/>
+      <c r="B133" s="66"/>
+      <c r="C133" s="67"/>
+      <c r="D133" s="68"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="97"/>
-      <c r="G133" s="98"/>
-      <c r="H133" s="99"/>
+      <c r="F133" s="66"/>
+      <c r="G133" s="67"/>
+      <c r="H133" s="68"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="97"/>
-      <c r="K133" s="98"/>
-      <c r="L133" s="99"/>
+      <c r="J133" s="66"/>
+      <c r="K133" s="67"/>
+      <c r="L133" s="68"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="887">
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="Z88:AA88"/>
+    <mergeCell ref="AD88:AE88"/>
+    <mergeCell ref="AH88:AI88"/>
+    <mergeCell ref="Z89:AA89"/>
+    <mergeCell ref="AD89:AE89"/>
+    <mergeCell ref="AH89:AI89"/>
+    <mergeCell ref="Z90:AA90"/>
+    <mergeCell ref="AD90:AE90"/>
+    <mergeCell ref="AH90:AI90"/>
+    <mergeCell ref="Z91:AA91"/>
+    <mergeCell ref="AD91:AE91"/>
+    <mergeCell ref="AH91:AI91"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="N86:P86"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="R86:T86"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD95:AE95"/>
+    <mergeCell ref="AH95:AI95"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AD94:AE94"/>
+    <mergeCell ref="AH94:AI94"/>
+    <mergeCell ref="AH96:AI96"/>
+    <mergeCell ref="AD96:AE96"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="Z95:AA95"/>
+    <mergeCell ref="Z94:AA94"/>
+    <mergeCell ref="Z96:AA96"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="J78:L78"/>
     <mergeCell ref="B92:C92"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F90:H90"/>
@@ -8207,845 +9040,30 @@
     <mergeCell ref="Z68:AA68"/>
     <mergeCell ref="AH54:AJ54"/>
     <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="Z95:AA95"/>
-    <mergeCell ref="Z94:AA94"/>
-    <mergeCell ref="Z96:AA96"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD95:AE95"/>
-    <mergeCell ref="AH95:AI95"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AD94:AE94"/>
-    <mergeCell ref="AH94:AI94"/>
-    <mergeCell ref="AH96:AI96"/>
-    <mergeCell ref="AD96:AE96"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="R86:T86"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="N86:P86"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="Z88:AA88"/>
-    <mergeCell ref="AD88:AE88"/>
-    <mergeCell ref="AH88:AI88"/>
-    <mergeCell ref="Z89:AA89"/>
-    <mergeCell ref="AD89:AE89"/>
-    <mergeCell ref="AH89:AI89"/>
-    <mergeCell ref="Z90:AA90"/>
-    <mergeCell ref="AD90:AE90"/>
-    <mergeCell ref="AH90:AI90"/>
-    <mergeCell ref="Z91:AA91"/>
-    <mergeCell ref="AD91:AE91"/>
-    <mergeCell ref="AH91:AI91"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AJ88:AJ96 AJ22:AJ27 AF22:AF27 AB22:AB27 T22:T27 AF88:AF96 AB88:AB96 AN22:AN27 H22:H27 D22:D27 L22:L27">

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="102">
   <si>
     <t>CUMA</t>
   </si>
@@ -1571,6 +1571,78 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1580,6 +1652,27 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1589,67 +1682,142 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1661,30 +1829,6 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1693,150 +1837,6 @@
     </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2287,65 +2287,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="130" t="s">
+      <c r="F1" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="130" t="s">
+      <c r="J1" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="130"/>
-      <c r="L1" s="131"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="128"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="134" t="s">
+      <c r="N1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="124" t="s">
+      <c r="R1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="124" t="s">
+      <c r="V1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="124" t="s">
+      <c r="Z1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="124" t="s">
+      <c r="AD1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="124"/>
-      <c r="AF1" s="124"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="124" t="s">
+      <c r="AH1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="124"/>
-      <c r="AJ1" s="124"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="124" t="s">
+      <c r="AL1" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="124"/>
-      <c r="AN1" s="125"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="138"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2353,74 +2353,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="132">
+      <c r="B2" s="129">
         <f>N2-3</f>
         <v>46192</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="133">
+      <c r="F2" s="130">
         <f>N2-2</f>
         <v>46193</v>
       </c>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="133">
+      <c r="J2" s="130">
         <f>N2-1</f>
         <v>46194</v>
       </c>
-      <c r="K2" s="133"/>
-      <c r="L2" s="136"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="133"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="135">
+      <c r="N2" s="132">
         <v>46195</v>
       </c>
-      <c r="O2" s="126"/>
-      <c r="P2" s="126"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="126">
+      <c r="R2" s="122">
         <f>N2+1</f>
         <v>46196</v>
       </c>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="126">
+      <c r="V2" s="122">
         <f>N2+2</f>
         <v>46197</v>
       </c>
-      <c r="W2" s="126"/>
-      <c r="X2" s="126"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="126">
+      <c r="Z2" s="122">
         <f>N2+3</f>
         <v>46198</v>
       </c>
-      <c r="AA2" s="126"/>
-      <c r="AB2" s="126"/>
+      <c r="AA2" s="122"/>
+      <c r="AB2" s="122"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="126">
+      <c r="AD2" s="122">
         <f>N2+4</f>
         <v>46199</v>
       </c>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="126"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="126">
+      <c r="AH2" s="122">
         <f>N2+5</f>
         <v>46200</v>
       </c>
-      <c r="AI2" s="126"/>
-      <c r="AJ2" s="126"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="126">
+      <c r="AL2" s="122">
         <f>N2+6</f>
         <v>46201</v>
       </c>
-      <c r="AM2" s="126"/>
-      <c r="AN2" s="127"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="139"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2474,47 +2474,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="119" t="s">
+      <c r="N4" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119"/>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119"/>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="119"/>
-      <c r="Z4" s="119"/>
-      <c r="AA4" s="119"/>
-      <c r="AB4" s="119"/>
+      <c r="O4" s="100"/>
+      <c r="P4" s="100"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="100"/>
+      <c r="W4" s="100"/>
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="128"/>
-      <c r="AE4" s="128"/>
-      <c r="AF4" s="128"/>
-      <c r="AG4" s="128"/>
-      <c r="AH4" s="128"/>
-      <c r="AI4" s="128"/>
-      <c r="AJ4" s="128"/>
-      <c r="AK4" s="128"/>
-      <c r="AL4" s="128"/>
-      <c r="AM4" s="128"/>
-      <c r="AN4" s="128"/>
+      <c r="AD4" s="134"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="134"/>
+      <c r="AH4" s="134"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="134"/>
+      <c r="AL4" s="134"/>
+      <c r="AM4" s="134"/>
+      <c r="AN4" s="134"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2522,101 +2522,101 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="119"/>
-      <c r="O5" s="119"/>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="119"/>
-      <c r="W5" s="119"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="100"/>
+      <c r="U5" s="100"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="100"/>
+      <c r="X5" s="100"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="128"/>
-      <c r="AE5" s="128"/>
-      <c r="AF5" s="128"/>
-      <c r="AG5" s="128"/>
-      <c r="AH5" s="128"/>
-      <c r="AI5" s="128"/>
-      <c r="AJ5" s="128"/>
-      <c r="AK5" s="128"/>
-      <c r="AL5" s="128"/>
-      <c r="AM5" s="128"/>
-      <c r="AN5" s="128"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="134"/>
+      <c r="AG5" s="134"/>
+      <c r="AH5" s="134"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="134"/>
+      <c r="AL5" s="134"/>
+      <c r="AM5" s="134"/>
+      <c r="AN5" s="134"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="69"/>
-      <c r="C6" s="70"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="94"/>
       <c r="D6" s="61"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="75"/>
+      <c r="G6" s="96"/>
       <c r="H6" s="55" t="s">
         <v>46</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="94"/>
       <c r="L6" s="61"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="83"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="78"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="82" t="s">
+      <c r="R6" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="S6" s="83"/>
+      <c r="S6" s="78"/>
       <c r="T6" s="34" t="s">
         <v>46</v>
       </c>
       <c r="U6" s="36"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="83"/>
+      <c r="V6" s="77"/>
+      <c r="W6" s="78"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="83"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="78"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="82" t="s">
+      <c r="AD6" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="AE6" s="83"/>
+      <c r="AE6" s="78"/>
       <c r="AF6" s="34" t="s">
         <v>73</v>
       </c>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="83"/>
+      <c r="AH6" s="77"/>
+      <c r="AI6" s="78"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="83"/>
+      <c r="AL6" s="77"/>
+      <c r="AM6" s="78"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2628,44 +2628,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="62"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="80"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="67"/>
       <c r="H7" s="62"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="80"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
       <c r="L7" s="62"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="88"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="87"/>
-      <c r="S7" s="88"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="70"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="88"/>
+      <c r="V7" s="69"/>
+      <c r="W7" s="70"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="87"/>
-      <c r="AA7" s="88"/>
+      <c r="Z7" s="69"/>
+      <c r="AA7" s="70"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="87"/>
-      <c r="AE7" s="88"/>
+      <c r="AD7" s="69"/>
+      <c r="AE7" s="70"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="87"/>
-      <c r="AI7" s="88"/>
+      <c r="AH7" s="69"/>
+      <c r="AI7" s="70"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="87"/>
-      <c r="AM7" s="88"/>
+      <c r="AL7" s="69"/>
+      <c r="AM7" s="70"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2677,51 +2677,51 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="63"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="89"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="64"/>
-      <c r="H8" s="65"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="65"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="89"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="65"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="89"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="63" t="s">
+      <c r="R8" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="S8" s="64"/>
-      <c r="T8" s="65"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="89"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="65"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="89"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="63"/>
-      <c r="AA8" s="64"/>
-      <c r="AB8" s="65"/>
+      <c r="Z8" s="87"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="89"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="63" t="s">
+      <c r="AD8" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="64"/>
-      <c r="AF8" s="65"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="89"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="64"/>
-      <c r="AJ8" s="65"/>
+      <c r="AH8" s="87"/>
+      <c r="AI8" s="88"/>
+      <c r="AJ8" s="89"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="63"/>
-      <c r="AM8" s="64"/>
-      <c r="AN8" s="65"/>
+      <c r="AL8" s="87"/>
+      <c r="AM8" s="88"/>
+      <c r="AN8" s="89"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2732,45 +2732,45 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="76"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="78"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="78"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="65"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="78"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="65"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="76"/>
-      <c r="O9" s="77"/>
-      <c r="P9" s="78"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="65"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="78"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="65"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="76"/>
-      <c r="W9" s="77"/>
-      <c r="X9" s="78"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="65"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="77"/>
-      <c r="AB9" s="78"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="65"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="77"/>
-      <c r="AF9" s="78"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="64"/>
+      <c r="AF9" s="65"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="76"/>
-      <c r="AI9" s="77"/>
-      <c r="AJ9" s="78"/>
+      <c r="AH9" s="63"/>
+      <c r="AI9" s="64"/>
+      <c r="AJ9" s="65"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="76"/>
-      <c r="AM9" s="77"/>
-      <c r="AN9" s="78"/>
+      <c r="AL9" s="63"/>
+      <c r="AM9" s="64"/>
+      <c r="AN9" s="65"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2781,45 +2781,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="114"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="116"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="137"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="116"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="136"/>
+      <c r="H10" s="137"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="116"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="137"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="115"/>
-      <c r="P10" s="116"/>
+      <c r="N10" s="135"/>
+      <c r="O10" s="136"/>
+      <c r="P10" s="137"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="114"/>
-      <c r="S10" s="115"/>
-      <c r="T10" s="116"/>
+      <c r="R10" s="135"/>
+      <c r="S10" s="136"/>
+      <c r="T10" s="137"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="114"/>
-      <c r="W10" s="115"/>
-      <c r="X10" s="116"/>
+      <c r="V10" s="135"/>
+      <c r="W10" s="136"/>
+      <c r="X10" s="137"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="114"/>
-      <c r="AA10" s="115"/>
-      <c r="AB10" s="116"/>
+      <c r="Z10" s="135"/>
+      <c r="AA10" s="136"/>
+      <c r="AB10" s="137"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="114"/>
-      <c r="AE10" s="115"/>
-      <c r="AF10" s="116"/>
+      <c r="AD10" s="135"/>
+      <c r="AE10" s="136"/>
+      <c r="AF10" s="137"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="114"/>
-      <c r="AI10" s="115"/>
-      <c r="AJ10" s="116"/>
+      <c r="AH10" s="135"/>
+      <c r="AI10" s="136"/>
+      <c r="AJ10" s="137"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="114"/>
-      <c r="AM10" s="115"/>
-      <c r="AN10" s="116"/>
+      <c r="AL10" s="135"/>
+      <c r="AM10" s="136"/>
+      <c r="AN10" s="137"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2879,44 +2879,44 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="69"/>
-      <c r="C12" s="70"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="61"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="70"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="94"/>
       <c r="H12" s="61"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="70"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="94"/>
       <c r="L12" s="61"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="83"/>
+      <c r="N12" s="77"/>
+      <c r="O12" s="78"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="83"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="78"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="82"/>
-      <c r="W12" s="83"/>
+      <c r="V12" s="77"/>
+      <c r="W12" s="78"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="82"/>
-      <c r="AA12" s="83"/>
+      <c r="Z12" s="77"/>
+      <c r="AA12" s="78"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="82"/>
-      <c r="AE12" s="83"/>
+      <c r="AD12" s="77"/>
+      <c r="AE12" s="78"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="82"/>
-      <c r="AI12" s="83"/>
+      <c r="AH12" s="77"/>
+      <c r="AI12" s="78"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="82"/>
-      <c r="AM12" s="83"/>
+      <c r="AL12" s="77"/>
+      <c r="AM12" s="78"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2928,45 +2928,45 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="62"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="73"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="84"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="73"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="84"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="85"/>
-      <c r="P13" s="86"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="81"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="84"/>
-      <c r="S13" s="85"/>
-      <c r="T13" s="86"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="81"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="85"/>
-      <c r="X13" s="86"/>
+      <c r="V13" s="79"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="81"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="88"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="70"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="88"/>
+      <c r="AD13" s="69"/>
+      <c r="AE13" s="70"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="84"/>
-      <c r="AI13" s="85"/>
-      <c r="AJ13" s="86"/>
+      <c r="AH13" s="79"/>
+      <c r="AI13" s="80"/>
+      <c r="AJ13" s="81"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="84"/>
-      <c r="AM13" s="85"/>
-      <c r="AN13" s="86"/>
+      <c r="AL13" s="79"/>
+      <c r="AM13" s="80"/>
+      <c r="AN13" s="81"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2977,94 +2977,94 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="63"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="65"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="89"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="65"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="89"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="65"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="89"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="64"/>
-      <c r="T14" s="65"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="65"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="89"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="63"/>
-      <c r="AA14" s="64"/>
-      <c r="AB14" s="65"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="89"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="63"/>
-      <c r="AE14" s="64"/>
-      <c r="AF14" s="65"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="89"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="63"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="65"/>
+      <c r="AH14" s="87"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="89"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="63"/>
-      <c r="AM14" s="64"/>
-      <c r="AN14" s="65"/>
+      <c r="AL14" s="87"/>
+      <c r="AM14" s="88"/>
+      <c r="AN14" s="89"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
       <c r="AQ14" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="76"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="65"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="78"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="65"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="78"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="65"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="76"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="78"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="65"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="76"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="78"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="65"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="76"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="78"/>
+      <c r="Z15" s="63"/>
+      <c r="AA15" s="64"/>
+      <c r="AB15" s="65"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="76"/>
-      <c r="AE15" s="77"/>
-      <c r="AF15" s="78"/>
+      <c r="AD15" s="63"/>
+      <c r="AE15" s="64"/>
+      <c r="AF15" s="65"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="76"/>
-      <c r="AI15" s="77"/>
-      <c r="AJ15" s="78"/>
+      <c r="AH15" s="63"/>
+      <c r="AI15" s="64"/>
+      <c r="AJ15" s="65"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="76"/>
-      <c r="AM15" s="77"/>
-      <c r="AN15" s="78"/>
+      <c r="AL15" s="63"/>
+      <c r="AM15" s="64"/>
+      <c r="AN15" s="65"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3075,51 +3075,51 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="114"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="116"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="137"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="116"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="137"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="116"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="137"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="115"/>
-      <c r="P16" s="116"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="137"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="115"/>
-      <c r="T16" s="116"/>
+      <c r="R16" s="135"/>
+      <c r="S16" s="136"/>
+      <c r="T16" s="137"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="114"/>
-      <c r="W16" s="115"/>
-      <c r="X16" s="116"/>
+      <c r="V16" s="135"/>
+      <c r="W16" s="136"/>
+      <c r="X16" s="137"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="115"/>
-      <c r="AB16" s="116"/>
+      <c r="Z16" s="135"/>
+      <c r="AA16" s="136"/>
+      <c r="AB16" s="137"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="115"/>
-      <c r="AF16" s="116"/>
+      <c r="AD16" s="135"/>
+      <c r="AE16" s="136"/>
+      <c r="AF16" s="137"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="114"/>
-      <c r="AI16" s="115"/>
-      <c r="AJ16" s="116"/>
+      <c r="AH16" s="135"/>
+      <c r="AI16" s="136"/>
+      <c r="AJ16" s="137"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="114"/>
-      <c r="AM16" s="115"/>
-      <c r="AN16" s="116"/>
+      <c r="AL16" s="135"/>
+      <c r="AM16" s="136"/>
+      <c r="AN16" s="137"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
       <c r="AQ16" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR16" s="30"/>
     </row>
@@ -3187,23 +3187,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="119" t="s">
+      <c r="N18" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="119"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
-      <c r="U18" s="119"/>
-      <c r="V18" s="119"/>
-      <c r="W18" s="119"/>
-      <c r="X18" s="119"/>
-      <c r="Y18" s="119"/>
-      <c r="Z18" s="119"/>
-      <c r="AA18" s="119"/>
-      <c r="AB18" s="119"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3238,21 +3238,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="119"/>
-      <c r="R19" s="119"/>
-      <c r="S19" s="119"/>
-      <c r="T19" s="119"/>
-      <c r="U19" s="119"/>
-      <c r="V19" s="119"/>
-      <c r="W19" s="119"/>
-      <c r="X19" s="119"/>
-      <c r="Y19" s="119"/>
-      <c r="Z19" s="119"/>
-      <c r="AA19" s="119"/>
-      <c r="AB19" s="119"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3270,83 +3270,83 @@
       </c>
       <c r="AQ19" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="70"/>
+      <c r="C20" s="94"/>
       <c r="D20" s="61" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="36"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="70"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="94"/>
       <c r="H20" s="61"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="74" t="s">
+      <c r="J20" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="75"/>
+      <c r="K20" s="96"/>
       <c r="L20" s="55" t="s">
         <v>81</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="82" t="s">
+      <c r="N20" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="O20" s="83"/>
+      <c r="O20" s="78"/>
       <c r="P20" s="34" t="s">
         <v>50</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="120" t="s">
+      <c r="R20" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="S20" s="121"/>
+      <c r="S20" s="143"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="120" t="s">
+      <c r="V20" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="W20" s="121"/>
+      <c r="W20" s="143"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="82" t="s">
+      <c r="Z20" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AA20" s="83"/>
+      <c r="AA20" s="78"/>
       <c r="AB20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="82" t="s">
+      <c r="AD20" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AE20" s="83"/>
+      <c r="AE20" s="78"/>
       <c r="AF20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="82" t="s">
+      <c r="AH20" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AI20" s="83"/>
+      <c r="AI20" s="78"/>
       <c r="AJ20" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="82" t="s">
+      <c r="AL20" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="AM20" s="83"/>
+      <c r="AM20" s="78"/>
       <c r="AN20" s="34" t="s">
         <v>81</v>
       </c>
@@ -3355,49 +3355,49 @@
       </c>
       <c r="AQ20" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="62"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="80"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="67"/>
       <c r="H21" s="62"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="80"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="67"/>
       <c r="L21" s="62"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="88"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="88"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="70"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="122"/>
-      <c r="W21" s="123"/>
+      <c r="V21" s="140"/>
+      <c r="W21" s="141"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="87"/>
-      <c r="AA21" s="88"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="70"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="87"/>
-      <c r="AE21" s="88"/>
+      <c r="AD21" s="69"/>
+      <c r="AE21" s="70"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="87"/>
-      <c r="AI21" s="88"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="70"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="87"/>
-      <c r="AM21" s="88"/>
+      <c r="AL21" s="69"/>
+      <c r="AM21" s="70"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3409,78 +3409,78 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="139" t="s">
+      <c r="B22" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="140"/>
+      <c r="C22" s="72"/>
       <c r="D22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="37"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="140"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="72"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="139" t="s">
+      <c r="J22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="140"/>
+      <c r="K22" s="72"/>
       <c r="L22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="137" t="s">
+      <c r="N22" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="O22" s="138"/>
+      <c r="O22" s="92"/>
       <c r="P22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="139" t="s">
+      <c r="R22" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="S22" s="140"/>
+      <c r="S22" s="72"/>
       <c r="T22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="37"/>
-      <c r="V22" s="137" t="s">
+      <c r="V22" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="138"/>
+      <c r="W22" s="92"/>
       <c r="X22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="139" t="s">
+      <c r="Z22" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="AA22" s="140"/>
+      <c r="AA22" s="72"/>
       <c r="AB22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="139" t="s">
+      <c r="AD22" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="AE22" s="140"/>
+      <c r="AE22" s="72"/>
       <c r="AF22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="139" t="s">
+      <c r="AH22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="AI22" s="140"/>
+      <c r="AI22" s="72"/>
       <c r="AJ22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="139" t="s">
+      <c r="AL22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="AM22" s="140"/>
+      <c r="AM22" s="72"/>
       <c r="AN22" s="41" t="s">
         <v>32</v>
       </c>
@@ -3496,78 +3496,78 @@
       </c>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="118"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="118"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="74"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="117" t="s">
+      <c r="J23" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="118"/>
+      <c r="K23" s="74"/>
       <c r="L23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="117" t="s">
+      <c r="N23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="O23" s="118"/>
+      <c r="O23" s="74"/>
       <c r="P23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q23" s="43"/>
-      <c r="R23" s="117" t="s">
+      <c r="R23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="118"/>
+      <c r="S23" s="74"/>
       <c r="T23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U23" s="43"/>
-      <c r="V23" s="117" t="s">
+      <c r="V23" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="W23" s="118"/>
+      <c r="W23" s="74"/>
       <c r="X23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="117" t="s">
+      <c r="Z23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AA23" s="118"/>
+      <c r="AA23" s="74"/>
       <c r="AB23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="117" t="s">
+      <c r="AD23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AE23" s="118"/>
+      <c r="AE23" s="74"/>
       <c r="AF23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="117" t="s">
+      <c r="AH23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AI23" s="118"/>
+      <c r="AI23" s="74"/>
       <c r="AJ23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="117" t="s">
+      <c r="AL23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AM23" s="118"/>
+      <c r="AM23" s="74"/>
       <c r="AN23" s="45" t="s">
         <v>33</v>
       </c>
@@ -3581,78 +3581,78 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="105"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="105"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="76"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="104" t="s">
+      <c r="J24" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="105"/>
+      <c r="K24" s="76"/>
       <c r="L24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="104" t="s">
+      <c r="N24" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="105"/>
+      <c r="O24" s="76"/>
       <c r="P24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q24" s="43"/>
-      <c r="R24" s="104" t="s">
+      <c r="R24" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="S24" s="105"/>
+      <c r="S24" s="76"/>
       <c r="T24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="44"/>
-      <c r="V24" s="104" t="s">
+      <c r="V24" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="105"/>
+      <c r="W24" s="76"/>
       <c r="X24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="104" t="s">
+      <c r="Z24" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="AA24" s="105"/>
+      <c r="AA24" s="76"/>
       <c r="AB24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="104" t="s">
+      <c r="AD24" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="AE24" s="105"/>
+      <c r="AE24" s="76"/>
       <c r="AF24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="104" t="s">
+      <c r="AH24" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="AI24" s="105"/>
+      <c r="AI24" s="76"/>
       <c r="AJ24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="104" t="s">
+      <c r="AL24" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="AM24" s="105"/>
+      <c r="AM24" s="76"/>
       <c r="AN24" s="45" t="s">
         <v>34</v>
       </c>
@@ -3666,78 +3666,78 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="105"/>
+      <c r="C25" s="76"/>
       <c r="D25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="105"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="76"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="104" t="s">
+      <c r="J25" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="105"/>
+      <c r="K25" s="76"/>
       <c r="L25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="104" t="s">
+      <c r="N25" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="105"/>
+      <c r="O25" s="76"/>
       <c r="P25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q25" s="44"/>
-      <c r="R25" s="104" t="s">
+      <c r="R25" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="S25" s="105"/>
+      <c r="S25" s="76"/>
       <c r="T25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="44"/>
-      <c r="V25" s="104" t="s">
+      <c r="V25" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W25" s="105"/>
+      <c r="W25" s="76"/>
       <c r="X25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="104" t="s">
+      <c r="Z25" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="AA25" s="105"/>
+      <c r="AA25" s="76"/>
       <c r="AB25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="104" t="s">
+      <c r="AD25" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="AE25" s="105"/>
+      <c r="AE25" s="76"/>
       <c r="AF25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="150" t="s">
+      <c r="AH25" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="AI25" s="151"/>
+      <c r="AI25" s="124"/>
       <c r="AJ25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="104" t="s">
+      <c r="AL25" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="AM25" s="105"/>
+      <c r="AM25" s="76"/>
       <c r="AN25" s="45" t="s">
         <v>35</v>
       </c>
@@ -3751,78 +3751,78 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="104" t="s">
+      <c r="B26" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="105"/>
+      <c r="C26" s="76"/>
       <c r="D26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="105"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="76"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="104" t="s">
+      <c r="J26" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="105"/>
+      <c r="K26" s="76"/>
       <c r="L26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="104" t="s">
+      <c r="N26" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="O26" s="105"/>
+      <c r="O26" s="76"/>
       <c r="P26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q26" s="44"/>
-      <c r="R26" s="104" t="s">
+      <c r="R26" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="S26" s="105"/>
+      <c r="S26" s="76"/>
       <c r="T26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="44"/>
-      <c r="V26" s="104" t="s">
+      <c r="V26" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="W26" s="105"/>
+      <c r="W26" s="76"/>
       <c r="X26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="104" t="s">
+      <c r="Z26" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="AA26" s="105"/>
+      <c r="AA26" s="76"/>
       <c r="AB26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="104" t="s">
+      <c r="AD26" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="AE26" s="105"/>
+      <c r="AE26" s="76"/>
       <c r="AF26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="104" t="s">
+      <c r="AH26" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="AI26" s="105"/>
+      <c r="AI26" s="76"/>
       <c r="AJ26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="104" t="s">
+      <c r="AL26" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="AM26" s="105"/>
+      <c r="AM26" s="76"/>
       <c r="AN26" s="45" t="s">
         <v>35</v>
       </c>
@@ -3836,44 +3836,44 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="86"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="107"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="86"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="107"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="86"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="106"/>
-      <c r="O27" s="107"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="86"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="106"/>
-      <c r="S27" s="107"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="86"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="106"/>
-      <c r="W27" s="107"/>
+      <c r="V27" s="85"/>
+      <c r="W27" s="86"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="106"/>
-      <c r="AA27" s="107"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="86"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="106"/>
-      <c r="AE27" s="107"/>
+      <c r="AD27" s="85"/>
+      <c r="AE27" s="86"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="106"/>
-      <c r="AI27" s="107"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="86"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="106"/>
-      <c r="AM27" s="107"/>
+      <c r="AL27" s="85"/>
+      <c r="AM27" s="86"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3946,23 +3946,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="119" t="s">
+      <c r="N29" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="119"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="119"/>
-      <c r="R29" s="119"/>
-      <c r="S29" s="119"/>
-      <c r="T29" s="119"/>
-      <c r="U29" s="119"/>
-      <c r="V29" s="119"/>
-      <c r="W29" s="119"/>
-      <c r="X29" s="119"/>
-      <c r="Y29" s="119"/>
-      <c r="Z29" s="119"/>
-      <c r="AA29" s="119"/>
-      <c r="AB29" s="119"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="100"/>
+      <c r="Q29" s="100"/>
+      <c r="R29" s="100"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="100"/>
+      <c r="U29" s="100"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="100"/>
+      <c r="X29" s="100"/>
+      <c r="Y29" s="100"/>
+      <c r="Z29" s="100"/>
+      <c r="AA29" s="100"/>
+      <c r="AB29" s="100"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3997,21 +3997,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="119"/>
-      <c r="O30" s="119"/>
-      <c r="P30" s="119"/>
-      <c r="Q30" s="119"/>
-      <c r="R30" s="119"/>
-      <c r="S30" s="119"/>
-      <c r="T30" s="119"/>
-      <c r="U30" s="119"/>
-      <c r="V30" s="119"/>
-      <c r="W30" s="119"/>
-      <c r="X30" s="119"/>
-      <c r="Y30" s="119"/>
-      <c r="Z30" s="119"/>
-      <c r="AA30" s="119"/>
-      <c r="AB30" s="119"/>
+      <c r="N30" s="100"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="100"/>
+      <c r="Q30" s="100"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="100"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="100"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -4034,234 +4034,234 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="94"/>
       <c r="D31" s="61" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="36"/>
-      <c r="F31" s="69" t="s">
+      <c r="F31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="70"/>
+      <c r="G31" s="94"/>
       <c r="H31" s="61" t="s">
         <v>44</v>
       </c>
       <c r="I31" s="36"/>
-      <c r="J31" s="69" t="s">
+      <c r="J31" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="K31" s="70"/>
+      <c r="K31" s="94"/>
       <c r="L31" s="61" t="s">
         <v>48</v>
       </c>
       <c r="M31" s="6"/>
-      <c r="N31" s="82"/>
-      <c r="O31" s="83"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="78"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="82" t="s">
+      <c r="R31" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="S31" s="83"/>
+      <c r="S31" s="78"/>
       <c r="T31" s="34" t="s">
         <v>83</v>
       </c>
       <c r="U31" s="36"/>
-      <c r="V31" s="82"/>
-      <c r="W31" s="83"/>
+      <c r="V31" s="77"/>
+      <c r="W31" s="78"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="82" t="s">
+      <c r="Z31" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="AA31" s="83"/>
+      <c r="AA31" s="78"/>
       <c r="AB31" s="34" t="s">
         <v>86</v>
       </c>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="82" t="s">
+      <c r="AD31" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="AE31" s="83"/>
+      <c r="AE31" s="78"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="82" t="s">
+      <c r="AH31" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="AI31" s="83"/>
+      <c r="AI31" s="78"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="82" t="s">
+      <c r="AL31" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="AM31" s="83"/>
+      <c r="AM31" s="78"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="73"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="84"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="71" t="s">
+      <c r="F32" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="72"/>
-      <c r="H32" s="73"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="84"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="71" t="s">
+      <c r="J32" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="K32" s="72"/>
-      <c r="L32" s="73"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="84"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="84"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="86"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="81"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="84" t="s">
+      <c r="R32" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="S32" s="85"/>
-      <c r="T32" s="86"/>
+      <c r="S32" s="80"/>
+      <c r="T32" s="81"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="84"/>
-      <c r="W32" s="85"/>
-      <c r="X32" s="86"/>
+      <c r="V32" s="79"/>
+      <c r="W32" s="80"/>
+      <c r="X32" s="81"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="84" t="s">
+      <c r="Z32" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="AA32" s="85"/>
-      <c r="AB32" s="86"/>
+      <c r="AA32" s="80"/>
+      <c r="AB32" s="81"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="84" t="s">
+      <c r="AD32" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="AE32" s="85"/>
-      <c r="AF32" s="86"/>
+      <c r="AE32" s="80"/>
+      <c r="AF32" s="81"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="84" t="s">
+      <c r="AH32" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="AI32" s="85"/>
-      <c r="AJ32" s="86"/>
+      <c r="AI32" s="80"/>
+      <c r="AJ32" s="81"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="84" t="s">
+      <c r="AL32" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="AM32" s="85"/>
-      <c r="AN32" s="86"/>
+      <c r="AM32" s="80"/>
+      <c r="AN32" s="81"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="79"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="81"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="68"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="81"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="68"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="81"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="68"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="87"/>
-      <c r="O33" s="88"/>
-      <c r="P33" s="89"/>
+      <c r="N33" s="69"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="90"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="89"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="70"/>
+      <c r="T33" s="90"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="89"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="70"/>
+      <c r="X33" s="90"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="87"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="89"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="70"/>
+      <c r="AB33" s="90"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="87"/>
-      <c r="AE33" s="88"/>
-      <c r="AF33" s="89"/>
+      <c r="AD33" s="69"/>
+      <c r="AE33" s="70"/>
+      <c r="AF33" s="90"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="87"/>
-      <c r="AI33" s="88"/>
-      <c r="AJ33" s="89"/>
+      <c r="AH33" s="69"/>
+      <c r="AI33" s="70"/>
+      <c r="AJ33" s="90"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="87"/>
-      <c r="AM33" s="88"/>
-      <c r="AN33" s="89"/>
+      <c r="AL33" s="69"/>
+      <c r="AM33" s="70"/>
+      <c r="AN33" s="90"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="76" t="s">
+      <c r="B34" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="78"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="76" t="s">
+      <c r="F34" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="77"/>
-      <c r="H34" s="78"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="65"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="76" t="s">
+      <c r="J34" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="77"/>
-      <c r="L34" s="78"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="65"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="63"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="65"/>
+      <c r="N34" s="87"/>
+      <c r="O34" s="88"/>
+      <c r="P34" s="89"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="63" t="s">
+      <c r="R34" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="S34" s="64"/>
-      <c r="T34" s="65"/>
+      <c r="S34" s="88"/>
+      <c r="T34" s="89"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="63"/>
-      <c r="W34" s="64"/>
-      <c r="X34" s="65"/>
+      <c r="V34" s="87"/>
+      <c r="W34" s="88"/>
+      <c r="X34" s="89"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="63" t="s">
+      <c r="Z34" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AA34" s="64"/>
-      <c r="AB34" s="65"/>
+      <c r="AA34" s="88"/>
+      <c r="AB34" s="89"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="76" t="s">
+      <c r="AD34" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AE34" s="77"/>
-      <c r="AF34" s="78"/>
+      <c r="AE34" s="64"/>
+      <c r="AF34" s="65"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="76" t="s">
+      <c r="AH34" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AI34" s="77"/>
-      <c r="AJ34" s="78"/>
+      <c r="AI34" s="64"/>
+      <c r="AJ34" s="65"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="76" t="s">
+      <c r="AL34" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AM34" s="77"/>
-      <c r="AN34" s="78"/>
+      <c r="AM34" s="64"/>
+      <c r="AN34" s="65"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -4269,106 +4269,106 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="78"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="65"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="76" t="s">
+      <c r="F35" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="77"/>
-      <c r="H35" s="78"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="65"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="76" t="s">
+      <c r="J35" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="77"/>
-      <c r="L35" s="78"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="65"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="77"/>
-      <c r="P35" s="78"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="65"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="76" t="s">
+      <c r="R35" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="S35" s="77"/>
-      <c r="T35" s="78"/>
+      <c r="S35" s="64"/>
+      <c r="T35" s="65"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="76"/>
-      <c r="W35" s="77"/>
-      <c r="X35" s="78"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="65"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="76" t="s">
+      <c r="Z35" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AA35" s="77"/>
-      <c r="AB35" s="78"/>
+      <c r="AA35" s="64"/>
+      <c r="AB35" s="65"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="76" t="s">
+      <c r="AD35" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="AE35" s="77"/>
-      <c r="AF35" s="78"/>
+      <c r="AE35" s="64"/>
+      <c r="AF35" s="65"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="76" t="s">
+      <c r="AH35" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="AI35" s="77"/>
-      <c r="AJ35" s="78"/>
+      <c r="AI35" s="64"/>
+      <c r="AJ35" s="65"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="76" t="s">
+      <c r="AL35" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="AM35" s="77"/>
-      <c r="AN35" s="78"/>
+      <c r="AM35" s="64"/>
+      <c r="AN35" s="65"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="68"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="99"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="68"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="98"/>
+      <c r="H36" s="99"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="68"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="99"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="68"/>
+      <c r="N36" s="97"/>
+      <c r="O36" s="98"/>
+      <c r="P36" s="99"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="66"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="68"/>
+      <c r="R36" s="97"/>
+      <c r="S36" s="98"/>
+      <c r="T36" s="99"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="67"/>
-      <c r="X36" s="68"/>
+      <c r="V36" s="97"/>
+      <c r="W36" s="98"/>
+      <c r="X36" s="99"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="66"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="68"/>
+      <c r="Z36" s="97"/>
+      <c r="AA36" s="98"/>
+      <c r="AB36" s="99"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="66"/>
-      <c r="AE36" s="67"/>
-      <c r="AF36" s="68"/>
+      <c r="AD36" s="97"/>
+      <c r="AE36" s="98"/>
+      <c r="AF36" s="99"/>
       <c r="AG36" s="44"/>
-      <c r="AH36" s="66"/>
-      <c r="AI36" s="67"/>
-      <c r="AJ36" s="68"/>
+      <c r="AH36" s="97"/>
+      <c r="AI36" s="98"/>
+      <c r="AJ36" s="99"/>
       <c r="AK36" s="44"/>
-      <c r="AL36" s="66"/>
-      <c r="AM36" s="67"/>
-      <c r="AN36" s="68"/>
+      <c r="AL36" s="97"/>
+      <c r="AM36" s="98"/>
+      <c r="AN36" s="99"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -4422,58 +4422,58 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="70"/>
+      <c r="C38" s="94"/>
       <c r="D38" s="61" t="s">
         <v>61</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="69" t="s">
+      <c r="F38" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="G38" s="70"/>
+      <c r="G38" s="94"/>
       <c r="H38" s="61" t="s">
         <v>62</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="74" t="s">
+      <c r="J38" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="K38" s="75"/>
+      <c r="K38" s="96"/>
       <c r="L38" s="55" t="s">
         <v>61</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="83"/>
+      <c r="N38" s="77"/>
+      <c r="O38" s="78"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="82"/>
-      <c r="S38" s="83"/>
+      <c r="R38" s="77"/>
+      <c r="S38" s="78"/>
       <c r="T38" s="34"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="82"/>
-      <c r="W38" s="83"/>
+      <c r="V38" s="77"/>
+      <c r="W38" s="78"/>
       <c r="X38" s="34"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="82"/>
-      <c r="AA38" s="83"/>
+      <c r="Z38" s="77"/>
+      <c r="AA38" s="78"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="82"/>
-      <c r="AE38" s="83"/>
+      <c r="AD38" s="77"/>
+      <c r="AE38" s="78"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="82"/>
-      <c r="AI38" s="83"/>
+      <c r="AH38" s="77"/>
+      <c r="AI38" s="78"/>
       <c r="AJ38" s="34"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="82" t="s">
+      <c r="AL38" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="AM38" s="83"/>
+      <c r="AM38" s="78"/>
       <c r="AN38" s="34"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
@@ -4482,53 +4482,53 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="72"/>
-      <c r="D39" s="73"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="84"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="72"/>
-      <c r="H39" s="73"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="84"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="71" t="s">
+      <c r="J39" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="K39" s="72"/>
-      <c r="L39" s="73"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="84"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="84"/>
-      <c r="O39" s="85"/>
-      <c r="P39" s="86"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="81"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="84"/>
-      <c r="S39" s="85"/>
-      <c r="T39" s="86"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="81"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="84"/>
-      <c r="W39" s="85"/>
-      <c r="X39" s="86"/>
+      <c r="V39" s="79"/>
+      <c r="W39" s="80"/>
+      <c r="X39" s="81"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="84"/>
-      <c r="AA39" s="85"/>
-      <c r="AB39" s="86"/>
+      <c r="Z39" s="79"/>
+      <c r="AA39" s="80"/>
+      <c r="AB39" s="81"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="84"/>
-      <c r="AE39" s="85"/>
-      <c r="AF39" s="86"/>
+      <c r="AD39" s="79"/>
+      <c r="AE39" s="80"/>
+      <c r="AF39" s="81"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="84"/>
-      <c r="AI39" s="85"/>
-      <c r="AJ39" s="86"/>
+      <c r="AH39" s="79"/>
+      <c r="AI39" s="80"/>
+      <c r="AJ39" s="81"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="84" t="s">
+      <c r="AL39" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="AM39" s="85"/>
-      <c r="AN39" s="86"/>
+      <c r="AM39" s="80"/>
+      <c r="AN39" s="81"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4536,45 +4536,45 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="79"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="81"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="68"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="81"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="68"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="81"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="68"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="87"/>
-      <c r="O40" s="88"/>
-      <c r="P40" s="89"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="90"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
-      <c r="T40" s="89"/>
+      <c r="R40" s="69"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="90"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="87"/>
-      <c r="W40" s="88"/>
-      <c r="X40" s="89"/>
+      <c r="V40" s="69"/>
+      <c r="W40" s="70"/>
+      <c r="X40" s="90"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="87"/>
-      <c r="AA40" s="88"/>
-      <c r="AB40" s="89"/>
+      <c r="Z40" s="69"/>
+      <c r="AA40" s="70"/>
+      <c r="AB40" s="90"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="87"/>
-      <c r="AE40" s="88"/>
-      <c r="AF40" s="89"/>
+      <c r="AD40" s="69"/>
+      <c r="AE40" s="70"/>
+      <c r="AF40" s="90"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="87"/>
-      <c r="AI40" s="88"/>
-      <c r="AJ40" s="89"/>
+      <c r="AH40" s="69"/>
+      <c r="AI40" s="70"/>
+      <c r="AJ40" s="90"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="87"/>
-      <c r="AM40" s="88"/>
-      <c r="AN40" s="89"/>
+      <c r="AL40" s="69"/>
+      <c r="AM40" s="70"/>
+      <c r="AN40" s="90"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4582,53 +4582,53 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="76" t="s">
+      <c r="B41" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="77"/>
-      <c r="D41" s="78"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="65"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="76" t="s">
+      <c r="F41" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="77"/>
-      <c r="H41" s="78"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="65"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="63" t="s">
+      <c r="J41" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="64"/>
-      <c r="L41" s="65"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="89"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="63"/>
-      <c r="O41" s="64"/>
-      <c r="P41" s="65"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="88"/>
+      <c r="P41" s="89"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="63"/>
-      <c r="S41" s="64"/>
-      <c r="T41" s="65"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="89"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="63"/>
-      <c r="W41" s="64"/>
-      <c r="X41" s="65"/>
+      <c r="V41" s="87"/>
+      <c r="W41" s="88"/>
+      <c r="X41" s="89"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="63"/>
-      <c r="AA41" s="64"/>
-      <c r="AB41" s="65"/>
+      <c r="Z41" s="87"/>
+      <c r="AA41" s="88"/>
+      <c r="AB41" s="89"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="76"/>
-      <c r="AE41" s="77"/>
-      <c r="AF41" s="78"/>
+      <c r="AD41" s="63"/>
+      <c r="AE41" s="64"/>
+      <c r="AF41" s="65"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="76"/>
-      <c r="AI41" s="77"/>
-      <c r="AJ41" s="78"/>
+      <c r="AH41" s="63"/>
+      <c r="AI41" s="64"/>
+      <c r="AJ41" s="65"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="63" t="s">
+      <c r="AL41" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AM41" s="64"/>
-      <c r="AN41" s="65"/>
+      <c r="AM41" s="88"/>
+      <c r="AN41" s="89"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4636,53 +4636,53 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="76" t="s">
+      <c r="B42" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="77"/>
-      <c r="D42" s="78"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="65"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="76" t="s">
+      <c r="F42" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="77"/>
-      <c r="H42" s="78"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="65"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="76" t="s">
+      <c r="J42" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="K42" s="64"/>
+      <c r="L42" s="65"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="76"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="78"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="64"/>
+      <c r="P42" s="65"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="76"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="78"/>
+      <c r="R42" s="63"/>
+      <c r="S42" s="64"/>
+      <c r="T42" s="65"/>
       <c r="U42" s="44"/>
-      <c r="V42" s="76"/>
-      <c r="W42" s="77"/>
-      <c r="X42" s="78"/>
+      <c r="V42" s="63"/>
+      <c r="W42" s="64"/>
+      <c r="X42" s="65"/>
       <c r="Y42" s="50"/>
-      <c r="Z42" s="76"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="78"/>
+      <c r="Z42" s="63"/>
+      <c r="AA42" s="64"/>
+      <c r="AB42" s="65"/>
       <c r="AC42" s="44"/>
-      <c r="AD42" s="76"/>
-      <c r="AE42" s="77"/>
-      <c r="AF42" s="78"/>
+      <c r="AD42" s="63"/>
+      <c r="AE42" s="64"/>
+      <c r="AF42" s="65"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="76"/>
-      <c r="AI42" s="77"/>
-      <c r="AJ42" s="78"/>
+      <c r="AH42" s="63"/>
+      <c r="AI42" s="64"/>
+      <c r="AJ42" s="65"/>
       <c r="AK42" s="44"/>
-      <c r="AL42" s="76" t="s">
+      <c r="AL42" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="AM42" s="77"/>
-      <c r="AN42" s="78"/>
+      <c r="AM42" s="64"/>
+      <c r="AN42" s="65"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4690,45 +4690,45 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="66"/>
-      <c r="C43" s="67"/>
-      <c r="D43" s="68"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="98"/>
+      <c r="D43" s="99"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="68"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="98"/>
+      <c r="H43" s="99"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="67"/>
-      <c r="L43" s="68"/>
+      <c r="J43" s="97"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="99"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="66"/>
-      <c r="O43" s="67"/>
-      <c r="P43" s="68"/>
+      <c r="N43" s="97"/>
+      <c r="O43" s="98"/>
+      <c r="P43" s="99"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="66"/>
-      <c r="S43" s="67"/>
-      <c r="T43" s="68"/>
+      <c r="R43" s="97"/>
+      <c r="S43" s="98"/>
+      <c r="T43" s="99"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="66"/>
-      <c r="W43" s="67"/>
-      <c r="X43" s="68"/>
+      <c r="V43" s="97"/>
+      <c r="W43" s="98"/>
+      <c r="X43" s="99"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="66"/>
-      <c r="AA43" s="67"/>
-      <c r="AB43" s="68"/>
+      <c r="Z43" s="97"/>
+      <c r="AA43" s="98"/>
+      <c r="AB43" s="99"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="66"/>
-      <c r="AE43" s="67"/>
-      <c r="AF43" s="68"/>
+      <c r="AD43" s="97"/>
+      <c r="AE43" s="98"/>
+      <c r="AF43" s="99"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="66"/>
-      <c r="AI43" s="67"/>
-      <c r="AJ43" s="68"/>
+      <c r="AH43" s="97"/>
+      <c r="AI43" s="98"/>
+      <c r="AJ43" s="99"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="66"/>
-      <c r="AM43" s="67"/>
-      <c r="AN43" s="68"/>
+      <c r="AL43" s="97"/>
+      <c r="AM43" s="98"/>
+      <c r="AN43" s="99"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4782,52 +4782,52 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="74" t="s">
+      <c r="B45" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="75"/>
+      <c r="C45" s="96"/>
       <c r="D45" s="55"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="69" t="s">
+      <c r="F45" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="G45" s="70"/>
+      <c r="G45" s="94"/>
       <c r="H45" s="61" t="s">
         <v>44</v>
       </c>
       <c r="I45" s="50"/>
-      <c r="J45" s="74" t="s">
+      <c r="J45" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="75"/>
+      <c r="K45" s="96"/>
       <c r="L45" s="55"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="82"/>
-      <c r="O45" s="83"/>
+      <c r="N45" s="77"/>
+      <c r="O45" s="78"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="82"/>
-      <c r="S45" s="83"/>
+      <c r="R45" s="77"/>
+      <c r="S45" s="78"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="82"/>
-      <c r="W45" s="83"/>
+      <c r="V45" s="77"/>
+      <c r="W45" s="78"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="82"/>
-      <c r="AA45" s="83"/>
+      <c r="Z45" s="77"/>
+      <c r="AA45" s="78"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="82"/>
-      <c r="AE45" s="83"/>
+      <c r="AD45" s="77"/>
+      <c r="AE45" s="78"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="82"/>
-      <c r="AI45" s="83"/>
+      <c r="AH45" s="77"/>
+      <c r="AI45" s="78"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="82"/>
-      <c r="AM45" s="83"/>
+      <c r="AL45" s="77"/>
+      <c r="AM45" s="78"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
@@ -4836,51 +4836,51 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="71" t="s">
+      <c r="B46" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="72"/>
-      <c r="D46" s="73"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="84"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="71" t="s">
+      <c r="F46" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="G46" s="72"/>
-      <c r="H46" s="73"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="84"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="71" t="s">
+      <c r="J46" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="K46" s="72"/>
-      <c r="L46" s="73"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="84"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="85"/>
-      <c r="P46" s="86"/>
+      <c r="N46" s="79"/>
+      <c r="O46" s="80"/>
+      <c r="P46" s="81"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="84"/>
-      <c r="S46" s="85"/>
-      <c r="T46" s="86"/>
+      <c r="R46" s="79"/>
+      <c r="S46" s="80"/>
+      <c r="T46" s="81"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="84"/>
-      <c r="W46" s="85"/>
-      <c r="X46" s="86"/>
+      <c r="V46" s="79"/>
+      <c r="W46" s="80"/>
+      <c r="X46" s="81"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="84"/>
-      <c r="AA46" s="85"/>
-      <c r="AB46" s="86"/>
+      <c r="Z46" s="79"/>
+      <c r="AA46" s="80"/>
+      <c r="AB46" s="81"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="84"/>
-      <c r="AE46" s="85"/>
-      <c r="AF46" s="86"/>
+      <c r="AD46" s="79"/>
+      <c r="AE46" s="80"/>
+      <c r="AF46" s="81"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="84"/>
-      <c r="AI46" s="85"/>
-      <c r="AJ46" s="86"/>
+      <c r="AH46" s="79"/>
+      <c r="AI46" s="80"/>
+      <c r="AJ46" s="81"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="84"/>
-      <c r="AM46" s="85"/>
-      <c r="AN46" s="86"/>
+      <c r="AL46" s="79"/>
+      <c r="AM46" s="80"/>
+      <c r="AN46" s="81"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4888,47 +4888,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="79" t="s">
+      <c r="B47" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="80"/>
-      <c r="D47" s="81"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="68"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="81"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="68"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="81"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="68"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="87"/>
-      <c r="O47" s="88"/>
-      <c r="P47" s="89"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="90"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="87"/>
-      <c r="S47" s="88"/>
-      <c r="T47" s="89"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="90"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="87"/>
-      <c r="W47" s="88"/>
-      <c r="X47" s="89"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="90"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="87"/>
-      <c r="AA47" s="88"/>
-      <c r="AB47" s="89"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="90"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="87"/>
-      <c r="AE47" s="88"/>
-      <c r="AF47" s="89"/>
+      <c r="AD47" s="69"/>
+      <c r="AE47" s="70"/>
+      <c r="AF47" s="90"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="87"/>
-      <c r="AI47" s="88"/>
-      <c r="AJ47" s="89"/>
+      <c r="AH47" s="69"/>
+      <c r="AI47" s="70"/>
+      <c r="AJ47" s="90"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="87"/>
-      <c r="AM47" s="88"/>
-      <c r="AN47" s="89"/>
+      <c r="AL47" s="69"/>
+      <c r="AM47" s="70"/>
+      <c r="AN47" s="90"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4936,145 +4936,145 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="89"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="76" t="s">
+      <c r="F48" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="77"/>
-      <c r="H48" s="78"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="65"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="63" t="s">
+      <c r="J48" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="64"/>
-      <c r="L48" s="65"/>
+      <c r="K48" s="88"/>
+      <c r="L48" s="89"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="76"/>
-      <c r="O48" s="77"/>
-      <c r="P48" s="78"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="64"/>
+      <c r="P48" s="65"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="77"/>
-      <c r="T48" s="78"/>
+      <c r="R48" s="63"/>
+      <c r="S48" s="64"/>
+      <c r="T48" s="65"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="76"/>
-      <c r="W48" s="77"/>
-      <c r="X48" s="78"/>
+      <c r="V48" s="63"/>
+      <c r="W48" s="64"/>
+      <c r="X48" s="65"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="63"/>
-      <c r="AA48" s="64"/>
-      <c r="AB48" s="65"/>
+      <c r="Z48" s="87"/>
+      <c r="AA48" s="88"/>
+      <c r="AB48" s="89"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="63"/>
-      <c r="AE48" s="64"/>
-      <c r="AF48" s="65"/>
+      <c r="AD48" s="87"/>
+      <c r="AE48" s="88"/>
+      <c r="AF48" s="89"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="76"/>
-      <c r="AI48" s="77"/>
-      <c r="AJ48" s="78"/>
+      <c r="AH48" s="63"/>
+      <c r="AI48" s="64"/>
+      <c r="AJ48" s="65"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="76"/>
-      <c r="AM48" s="77"/>
-      <c r="AN48" s="78"/>
+      <c r="AL48" s="63"/>
+      <c r="AM48" s="64"/>
+      <c r="AN48" s="65"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="76"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="78"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="65"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="76" t="s">
+      <c r="F49" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="77"/>
-      <c r="H49" s="78"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="65"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="76" t="s">
+      <c r="J49" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="77"/>
-      <c r="L49" s="78"/>
+      <c r="K49" s="64"/>
+      <c r="L49" s="65"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="76"/>
-      <c r="O49" s="77"/>
-      <c r="P49" s="78"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="64"/>
+      <c r="P49" s="65"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="76"/>
-      <c r="S49" s="77"/>
-      <c r="T49" s="78"/>
+      <c r="R49" s="63"/>
+      <c r="S49" s="64"/>
+      <c r="T49" s="65"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="76"/>
-      <c r="W49" s="77"/>
-      <c r="X49" s="78"/>
+      <c r="V49" s="63"/>
+      <c r="W49" s="64"/>
+      <c r="X49" s="65"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="76"/>
-      <c r="AA49" s="77"/>
-      <c r="AB49" s="78"/>
+      <c r="Z49" s="63"/>
+      <c r="AA49" s="64"/>
+      <c r="AB49" s="65"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="76"/>
-      <c r="AE49" s="77"/>
-      <c r="AF49" s="78"/>
+      <c r="AD49" s="63"/>
+      <c r="AE49" s="64"/>
+      <c r="AF49" s="65"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="76"/>
-      <c r="AI49" s="77"/>
-      <c r="AJ49" s="78"/>
+      <c r="AH49" s="63"/>
+      <c r="AI49" s="64"/>
+      <c r="AJ49" s="65"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="76"/>
-      <c r="AM49" s="77"/>
-      <c r="AN49" s="78"/>
+      <c r="AL49" s="63"/>
+      <c r="AM49" s="64"/>
+      <c r="AN49" s="65"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="66"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="68"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="99"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="67"/>
-      <c r="H50" s="68"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="98"/>
+      <c r="H50" s="99"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="66"/>
-      <c r="K50" s="67"/>
-      <c r="L50" s="68"/>
+      <c r="J50" s="97"/>
+      <c r="K50" s="98"/>
+      <c r="L50" s="99"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="66"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="68"/>
+      <c r="N50" s="97"/>
+      <c r="O50" s="98"/>
+      <c r="P50" s="99"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="66"/>
-      <c r="S50" s="67"/>
-      <c r="T50" s="68"/>
+      <c r="R50" s="97"/>
+      <c r="S50" s="98"/>
+      <c r="T50" s="99"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="66"/>
-      <c r="W50" s="67"/>
-      <c r="X50" s="68"/>
+      <c r="V50" s="97"/>
+      <c r="W50" s="98"/>
+      <c r="X50" s="99"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="66"/>
-      <c r="AA50" s="67"/>
-      <c r="AB50" s="68"/>
+      <c r="Z50" s="97"/>
+      <c r="AA50" s="98"/>
+      <c r="AB50" s="99"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="66"/>
-      <c r="AE50" s="67"/>
-      <c r="AF50" s="68"/>
+      <c r="AD50" s="97"/>
+      <c r="AE50" s="98"/>
+      <c r="AF50" s="99"/>
       <c r="AG50" s="44"/>
-      <c r="AH50" s="66"/>
-      <c r="AI50" s="67"/>
-      <c r="AJ50" s="68"/>
+      <c r="AH50" s="97"/>
+      <c r="AI50" s="98"/>
+      <c r="AJ50" s="99"/>
       <c r="AK50" s="44"/>
-      <c r="AL50" s="66"/>
-      <c r="AM50" s="67"/>
-      <c r="AN50" s="68"/>
+      <c r="AL50" s="97"/>
+      <c r="AM50" s="98"/>
+      <c r="AN50" s="99"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5126,255 +5126,255 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="69"/>
-      <c r="C52" s="70"/>
+      <c r="B52" s="93"/>
+      <c r="C52" s="94"/>
       <c r="D52" s="61"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="70"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="94"/>
       <c r="H52" s="61"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="70"/>
+      <c r="J52" s="93"/>
+      <c r="K52" s="94"/>
       <c r="L52" s="61"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="82"/>
-      <c r="O52" s="83"/>
+      <c r="N52" s="77"/>
+      <c r="O52" s="78"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="82"/>
-      <c r="S52" s="83"/>
+      <c r="R52" s="77"/>
+      <c r="S52" s="78"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="82"/>
-      <c r="W52" s="83"/>
+      <c r="V52" s="77"/>
+      <c r="W52" s="78"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="82"/>
-      <c r="AA52" s="83"/>
+      <c r="Z52" s="77"/>
+      <c r="AA52" s="78"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="82"/>
-      <c r="AE52" s="83"/>
+      <c r="AD52" s="77"/>
+      <c r="AE52" s="78"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="82"/>
-      <c r="AI52" s="83"/>
+      <c r="AH52" s="77"/>
+      <c r="AI52" s="78"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="82"/>
-      <c r="AM52" s="83"/>
+      <c r="AL52" s="77"/>
+      <c r="AM52" s="78"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="71"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="73"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="84"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="73"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="84"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="73"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="84"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="84"/>
-      <c r="O53" s="85"/>
-      <c r="P53" s="86"/>
+      <c r="N53" s="79"/>
+      <c r="O53" s="80"/>
+      <c r="P53" s="81"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="84"/>
-      <c r="S53" s="85"/>
-      <c r="T53" s="86"/>
+      <c r="R53" s="79"/>
+      <c r="S53" s="80"/>
+      <c r="T53" s="81"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="84"/>
-      <c r="W53" s="85"/>
-      <c r="X53" s="86"/>
+      <c r="V53" s="79"/>
+      <c r="W53" s="80"/>
+      <c r="X53" s="81"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="84"/>
-      <c r="AA53" s="85"/>
-      <c r="AB53" s="86"/>
+      <c r="Z53" s="79"/>
+      <c r="AA53" s="80"/>
+      <c r="AB53" s="81"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="84"/>
-      <c r="AE53" s="85"/>
-      <c r="AF53" s="86"/>
+      <c r="AD53" s="79"/>
+      <c r="AE53" s="80"/>
+      <c r="AF53" s="81"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="84"/>
-      <c r="AI53" s="85"/>
-      <c r="AJ53" s="86"/>
+      <c r="AH53" s="79"/>
+      <c r="AI53" s="80"/>
+      <c r="AJ53" s="81"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="84"/>
-      <c r="AM53" s="85"/>
-      <c r="AN53" s="86"/>
+      <c r="AL53" s="79"/>
+      <c r="AM53" s="80"/>
+      <c r="AN53" s="81"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="79"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="81"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="67"/>
+      <c r="D54" s="68"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="81"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="68"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="79"/>
-      <c r="K54" s="80"/>
-      <c r="L54" s="81"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="67"/>
+      <c r="L54" s="68"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="87"/>
-      <c r="O54" s="88"/>
-      <c r="P54" s="89"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="90"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="87"/>
-      <c r="S54" s="88"/>
-      <c r="T54" s="89"/>
+      <c r="R54" s="69"/>
+      <c r="S54" s="70"/>
+      <c r="T54" s="90"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="87"/>
-      <c r="W54" s="88"/>
-      <c r="X54" s="89"/>
+      <c r="V54" s="69"/>
+      <c r="W54" s="70"/>
+      <c r="X54" s="90"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="87"/>
-      <c r="AA54" s="88"/>
-      <c r="AB54" s="89"/>
+      <c r="Z54" s="69"/>
+      <c r="AA54" s="70"/>
+      <c r="AB54" s="90"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="87"/>
-      <c r="AE54" s="88"/>
-      <c r="AF54" s="89"/>
+      <c r="AD54" s="69"/>
+      <c r="AE54" s="70"/>
+      <c r="AF54" s="90"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="87"/>
-      <c r="AI54" s="88"/>
-      <c r="AJ54" s="89"/>
+      <c r="AH54" s="69"/>
+      <c r="AI54" s="70"/>
+      <c r="AJ54" s="90"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="87"/>
-      <c r="AM54" s="88"/>
-      <c r="AN54" s="89"/>
+      <c r="AL54" s="69"/>
+      <c r="AM54" s="70"/>
+      <c r="AN54" s="90"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="63"/>
-      <c r="C55" s="64"/>
-      <c r="D55" s="65"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="89"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="65"/>
+      <c r="F55" s="87"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="89"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="63"/>
-      <c r="K55" s="64"/>
-      <c r="L55" s="65"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="88"/>
+      <c r="L55" s="89"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="63"/>
-      <c r="O55" s="64"/>
-      <c r="P55" s="65"/>
+      <c r="N55" s="87"/>
+      <c r="O55" s="88"/>
+      <c r="P55" s="89"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="63"/>
-      <c r="S55" s="64"/>
-      <c r="T55" s="65"/>
+      <c r="R55" s="87"/>
+      <c r="S55" s="88"/>
+      <c r="T55" s="89"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="63"/>
-      <c r="W55" s="64"/>
-      <c r="X55" s="65"/>
+      <c r="V55" s="87"/>
+      <c r="W55" s="88"/>
+      <c r="X55" s="89"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="63"/>
-      <c r="AA55" s="64"/>
-      <c r="AB55" s="65"/>
+      <c r="Z55" s="87"/>
+      <c r="AA55" s="88"/>
+      <c r="AB55" s="89"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="63"/>
-      <c r="AE55" s="64"/>
-      <c r="AF55" s="65"/>
+      <c r="AD55" s="87"/>
+      <c r="AE55" s="88"/>
+      <c r="AF55" s="89"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="63"/>
-      <c r="AI55" s="64"/>
-      <c r="AJ55" s="65"/>
+      <c r="AH55" s="87"/>
+      <c r="AI55" s="88"/>
+      <c r="AJ55" s="89"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="63"/>
-      <c r="AM55" s="64"/>
-      <c r="AN55" s="65"/>
+      <c r="AL55" s="87"/>
+      <c r="AM55" s="88"/>
+      <c r="AN55" s="89"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="76"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="78"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="65"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="77"/>
-      <c r="H56" s="78"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="65"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="76"/>
-      <c r="K56" s="77"/>
-      <c r="L56" s="78"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="64"/>
+      <c r="L56" s="65"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="76"/>
-      <c r="O56" s="77"/>
-      <c r="P56" s="78"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="64"/>
+      <c r="P56" s="65"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="76"/>
-      <c r="S56" s="77"/>
-      <c r="T56" s="78"/>
+      <c r="R56" s="63"/>
+      <c r="S56" s="64"/>
+      <c r="T56" s="65"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="76"/>
-      <c r="W56" s="77"/>
-      <c r="X56" s="78"/>
+      <c r="V56" s="63"/>
+      <c r="W56" s="64"/>
+      <c r="X56" s="65"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="76"/>
-      <c r="AA56" s="77"/>
-      <c r="AB56" s="78"/>
+      <c r="Z56" s="63"/>
+      <c r="AA56" s="64"/>
+      <c r="AB56" s="65"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="76"/>
-      <c r="AE56" s="77"/>
-      <c r="AF56" s="78"/>
+      <c r="AD56" s="63"/>
+      <c r="AE56" s="64"/>
+      <c r="AF56" s="65"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="76"/>
-      <c r="AI56" s="77"/>
-      <c r="AJ56" s="78"/>
+      <c r="AH56" s="63"/>
+      <c r="AI56" s="64"/>
+      <c r="AJ56" s="65"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="76"/>
-      <c r="AM56" s="77"/>
-      <c r="AN56" s="78"/>
+      <c r="AL56" s="63"/>
+      <c r="AM56" s="64"/>
+      <c r="AN56" s="65"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="66"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="68"/>
+      <c r="B57" s="97"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="99"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="68"/>
+      <c r="F57" s="97"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="99"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="68"/>
+      <c r="J57" s="97"/>
+      <c r="K57" s="98"/>
+      <c r="L57" s="99"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="66"/>
-      <c r="O57" s="67"/>
-      <c r="P57" s="68"/>
+      <c r="N57" s="97"/>
+      <c r="O57" s="98"/>
+      <c r="P57" s="99"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="66"/>
-      <c r="S57" s="67"/>
-      <c r="T57" s="68"/>
+      <c r="R57" s="97"/>
+      <c r="S57" s="98"/>
+      <c r="T57" s="99"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="66"/>
-      <c r="W57" s="67"/>
-      <c r="X57" s="68"/>
+      <c r="V57" s="97"/>
+      <c r="W57" s="98"/>
+      <c r="X57" s="99"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="66"/>
-      <c r="AA57" s="67"/>
-      <c r="AB57" s="68"/>
+      <c r="Z57" s="97"/>
+      <c r="AA57" s="98"/>
+      <c r="AB57" s="99"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="66"/>
-      <c r="AE57" s="67"/>
-      <c r="AF57" s="68"/>
+      <c r="AD57" s="97"/>
+      <c r="AE57" s="98"/>
+      <c r="AF57" s="99"/>
       <c r="AG57" s="44"/>
-      <c r="AH57" s="66"/>
-      <c r="AI57" s="67"/>
-      <c r="AJ57" s="68"/>
+      <c r="AH57" s="97"/>
+      <c r="AI57" s="98"/>
+      <c r="AJ57" s="99"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="66"/>
-      <c r="AM57" s="67"/>
-      <c r="AN57" s="68"/>
+      <c r="AL57" s="97"/>
+      <c r="AM57" s="98"/>
+      <c r="AN57" s="99"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5420,261 +5420,261 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="96" t="s">
+      <c r="B59" s="144" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="97"/>
+      <c r="C59" s="145"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="70"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="94"/>
       <c r="H59" s="61"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="70"/>
+      <c r="J59" s="93"/>
+      <c r="K59" s="94"/>
       <c r="L59" s="61"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="82"/>
-      <c r="O59" s="83"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="78"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="82"/>
-      <c r="S59" s="83"/>
+      <c r="R59" s="77"/>
+      <c r="S59" s="78"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="82"/>
-      <c r="W59" s="83"/>
+      <c r="V59" s="77"/>
+      <c r="W59" s="78"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="82"/>
-      <c r="AA59" s="83"/>
+      <c r="Z59" s="77"/>
+      <c r="AA59" s="78"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="82"/>
-      <c r="AE59" s="83"/>
+      <c r="AD59" s="77"/>
+      <c r="AE59" s="78"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="82"/>
-      <c r="AI59" s="83"/>
+      <c r="AH59" s="77"/>
+      <c r="AI59" s="78"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="82"/>
-      <c r="AM59" s="83"/>
+      <c r="AL59" s="77"/>
+      <c r="AM59" s="78"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="94"/>
-      <c r="D60" s="95"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="103"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="71"/>
-      <c r="G60" s="72"/>
-      <c r="H60" s="73"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="83"/>
+      <c r="H60" s="84"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="71"/>
-      <c r="K60" s="72"/>
-      <c r="L60" s="73"/>
+      <c r="J60" s="82"/>
+      <c r="K60" s="83"/>
+      <c r="L60" s="84"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="84"/>
-      <c r="O60" s="85"/>
-      <c r="P60" s="86"/>
+      <c r="N60" s="79"/>
+      <c r="O60" s="80"/>
+      <c r="P60" s="81"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="84"/>
-      <c r="S60" s="85"/>
-      <c r="T60" s="86"/>
+      <c r="R60" s="79"/>
+      <c r="S60" s="80"/>
+      <c r="T60" s="81"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="84"/>
-      <c r="W60" s="85"/>
-      <c r="X60" s="86"/>
+      <c r="V60" s="79"/>
+      <c r="W60" s="80"/>
+      <c r="X60" s="81"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="84"/>
-      <c r="AA60" s="85"/>
-      <c r="AB60" s="86"/>
+      <c r="Z60" s="79"/>
+      <c r="AA60" s="80"/>
+      <c r="AB60" s="81"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="84"/>
-      <c r="AE60" s="85"/>
-      <c r="AF60" s="86"/>
+      <c r="AD60" s="79"/>
+      <c r="AE60" s="80"/>
+      <c r="AF60" s="81"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="84"/>
-      <c r="AI60" s="85"/>
-      <c r="AJ60" s="86"/>
+      <c r="AH60" s="79"/>
+      <c r="AI60" s="80"/>
+      <c r="AJ60" s="81"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="84"/>
-      <c r="AM60" s="85"/>
-      <c r="AN60" s="86"/>
+      <c r="AL60" s="79"/>
+      <c r="AM60" s="80"/>
+      <c r="AN60" s="81"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="90"/>
-      <c r="C61" s="91"/>
-      <c r="D61" s="92"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="147"/>
+      <c r="D61" s="148"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="81"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="68"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="80"/>
-      <c r="L61" s="81"/>
+      <c r="J61" s="66"/>
+      <c r="K61" s="67"/>
+      <c r="L61" s="68"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="87"/>
-      <c r="O61" s="88"/>
-      <c r="P61" s="89"/>
+      <c r="N61" s="69"/>
+      <c r="O61" s="70"/>
+      <c r="P61" s="90"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="87"/>
-      <c r="S61" s="88"/>
-      <c r="T61" s="89"/>
+      <c r="R61" s="69"/>
+      <c r="S61" s="70"/>
+      <c r="T61" s="90"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="87"/>
-      <c r="W61" s="88"/>
-      <c r="X61" s="89"/>
+      <c r="V61" s="69"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="90"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="87"/>
-      <c r="AA61" s="88"/>
-      <c r="AB61" s="89"/>
+      <c r="Z61" s="69"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="90"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="87"/>
-      <c r="AE61" s="88"/>
-      <c r="AF61" s="89"/>
+      <c r="AD61" s="69"/>
+      <c r="AE61" s="70"/>
+      <c r="AF61" s="90"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="87"/>
-      <c r="AI61" s="88"/>
-      <c r="AJ61" s="89"/>
+      <c r="AH61" s="69"/>
+      <c r="AI61" s="70"/>
+      <c r="AJ61" s="90"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="87"/>
-      <c r="AM61" s="88"/>
-      <c r="AN61" s="89"/>
+      <c r="AL61" s="69"/>
+      <c r="AM61" s="70"/>
+      <c r="AN61" s="90"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="101" t="s">
+      <c r="B62" s="149" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="102"/>
-      <c r="D62" s="103"/>
+      <c r="C62" s="150"/>
+      <c r="D62" s="151"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="65"/>
+      <c r="F62" s="87"/>
+      <c r="G62" s="88"/>
+      <c r="H62" s="89"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="64"/>
-      <c r="L62" s="65"/>
+      <c r="J62" s="87"/>
+      <c r="K62" s="88"/>
+      <c r="L62" s="89"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="76"/>
-      <c r="O62" s="77"/>
-      <c r="P62" s="78"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="64"/>
+      <c r="P62" s="65"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="76"/>
-      <c r="S62" s="77"/>
-      <c r="T62" s="78"/>
+      <c r="R62" s="63"/>
+      <c r="S62" s="64"/>
+      <c r="T62" s="65"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="63"/>
-      <c r="W62" s="64"/>
-      <c r="X62" s="65"/>
+      <c r="V62" s="87"/>
+      <c r="W62" s="88"/>
+      <c r="X62" s="89"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="63"/>
-      <c r="AA62" s="64"/>
-      <c r="AB62" s="65"/>
+      <c r="Z62" s="87"/>
+      <c r="AA62" s="88"/>
+      <c r="AB62" s="89"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="63"/>
-      <c r="AE62" s="64"/>
-      <c r="AF62" s="65"/>
+      <c r="AD62" s="87"/>
+      <c r="AE62" s="88"/>
+      <c r="AF62" s="89"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="63"/>
-      <c r="AI62" s="64"/>
-      <c r="AJ62" s="65"/>
+      <c r="AH62" s="87"/>
+      <c r="AI62" s="88"/>
+      <c r="AJ62" s="89"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="63"/>
-      <c r="AM62" s="64"/>
-      <c r="AN62" s="65"/>
+      <c r="AL62" s="87"/>
+      <c r="AM62" s="88"/>
+      <c r="AN62" s="89"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="98"/>
-      <c r="C63" s="99"/>
-      <c r="D63" s="100"/>
+      <c r="B63" s="107"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="109"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="76"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="78"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="65"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="76"/>
-      <c r="K63" s="77"/>
-      <c r="L63" s="78"/>
+      <c r="J63" s="63"/>
+      <c r="K63" s="64"/>
+      <c r="L63" s="65"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="76"/>
-      <c r="O63" s="77"/>
-      <c r="P63" s="78"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="64"/>
+      <c r="P63" s="65"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="76"/>
-      <c r="S63" s="77"/>
-      <c r="T63" s="78"/>
+      <c r="R63" s="63"/>
+      <c r="S63" s="64"/>
+      <c r="T63" s="65"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="76"/>
-      <c r="W63" s="77"/>
-      <c r="X63" s="78"/>
+      <c r="V63" s="63"/>
+      <c r="W63" s="64"/>
+      <c r="X63" s="65"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="76"/>
-      <c r="AA63" s="77"/>
-      <c r="AB63" s="78"/>
+      <c r="Z63" s="63"/>
+      <c r="AA63" s="64"/>
+      <c r="AB63" s="65"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="76"/>
-      <c r="AE63" s="77"/>
-      <c r="AF63" s="78"/>
+      <c r="AD63" s="63"/>
+      <c r="AE63" s="64"/>
+      <c r="AF63" s="65"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="76"/>
-      <c r="AI63" s="77"/>
-      <c r="AJ63" s="78"/>
+      <c r="AH63" s="63"/>
+      <c r="AI63" s="64"/>
+      <c r="AJ63" s="65"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="76"/>
-      <c r="AM63" s="77"/>
-      <c r="AN63" s="78"/>
+      <c r="AL63" s="63"/>
+      <c r="AM63" s="64"/>
+      <c r="AN63" s="65"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="108"/>
-      <c r="C64" s="109"/>
-      <c r="D64" s="110"/>
+      <c r="B64" s="110"/>
+      <c r="C64" s="111"/>
+      <c r="D64" s="112"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="68"/>
+      <c r="F64" s="97"/>
+      <c r="G64" s="98"/>
+      <c r="H64" s="99"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="66"/>
-      <c r="K64" s="67"/>
-      <c r="L64" s="68"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="98"/>
+      <c r="L64" s="99"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="66"/>
-      <c r="O64" s="67"/>
-      <c r="P64" s="68"/>
+      <c r="N64" s="97"/>
+      <c r="O64" s="98"/>
+      <c r="P64" s="99"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="66"/>
-      <c r="S64" s="67"/>
-      <c r="T64" s="68"/>
+      <c r="R64" s="97"/>
+      <c r="S64" s="98"/>
+      <c r="T64" s="99"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="66"/>
-      <c r="W64" s="67"/>
-      <c r="X64" s="68"/>
+      <c r="V64" s="97"/>
+      <c r="W64" s="98"/>
+      <c r="X64" s="99"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="66"/>
-      <c r="AA64" s="67"/>
-      <c r="AB64" s="68"/>
+      <c r="Z64" s="97"/>
+      <c r="AA64" s="98"/>
+      <c r="AB64" s="99"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="66"/>
-      <c r="AE64" s="67"/>
-      <c r="AF64" s="68"/>
+      <c r="AD64" s="97"/>
+      <c r="AE64" s="98"/>
+      <c r="AF64" s="99"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="66"/>
-      <c r="AI64" s="67"/>
-      <c r="AJ64" s="68"/>
+      <c r="AH64" s="97"/>
+      <c r="AI64" s="98"/>
+      <c r="AJ64" s="99"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="66"/>
-      <c r="AM64" s="67"/>
-      <c r="AN64" s="68"/>
+      <c r="AL64" s="97"/>
+      <c r="AM64" s="98"/>
+      <c r="AN64" s="99"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5737,23 +5737,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="119" t="s">
+      <c r="N66" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="119"/>
-      <c r="P66" s="119"/>
-      <c r="Q66" s="119"/>
-      <c r="R66" s="119"/>
-      <c r="S66" s="119"/>
-      <c r="T66" s="119"/>
-      <c r="U66" s="119"/>
-      <c r="V66" s="119"/>
-      <c r="W66" s="119"/>
-      <c r="X66" s="119"/>
-      <c r="Y66" s="119"/>
-      <c r="Z66" s="119"/>
-      <c r="AA66" s="119"/>
-      <c r="AB66" s="119"/>
+      <c r="O66" s="100"/>
+      <c r="P66" s="100"/>
+      <c r="Q66" s="100"/>
+      <c r="R66" s="100"/>
+      <c r="S66" s="100"/>
+      <c r="T66" s="100"/>
+      <c r="U66" s="100"/>
+      <c r="V66" s="100"/>
+      <c r="W66" s="100"/>
+      <c r="X66" s="100"/>
+      <c r="Y66" s="100"/>
+      <c r="Z66" s="100"/>
+      <c r="AA66" s="100"/>
+      <c r="AB66" s="100"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5784,21 +5784,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="119"/>
-      <c r="O67" s="119"/>
-      <c r="P67" s="119"/>
-      <c r="Q67" s="119"/>
-      <c r="R67" s="119"/>
-      <c r="S67" s="119"/>
-      <c r="T67" s="119"/>
-      <c r="U67" s="119"/>
-      <c r="V67" s="119"/>
-      <c r="W67" s="119"/>
-      <c r="X67" s="119"/>
-      <c r="Y67" s="119"/>
-      <c r="Z67" s="119"/>
-      <c r="AA67" s="119"/>
-      <c r="AB67" s="119"/>
+      <c r="N67" s="100"/>
+      <c r="O67" s="100"/>
+      <c r="P67" s="100"/>
+      <c r="Q67" s="100"/>
+      <c r="R67" s="100"/>
+      <c r="S67" s="100"/>
+      <c r="T67" s="100"/>
+      <c r="U67" s="100"/>
+      <c r="V67" s="100"/>
+      <c r="W67" s="100"/>
+      <c r="X67" s="100"/>
+      <c r="Y67" s="100"/>
+      <c r="Z67" s="100"/>
+      <c r="AA67" s="100"/>
+      <c r="AB67" s="100"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5818,58 +5818,58 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="69" t="s">
+      <c r="B68" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="70"/>
+      <c r="C68" s="94"/>
       <c r="D68" s="61"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="70"/>
+      <c r="F68" s="93"/>
+      <c r="G68" s="94"/>
       <c r="H68" s="61"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="69"/>
-      <c r="K68" s="70"/>
+      <c r="J68" s="93"/>
+      <c r="K68" s="94"/>
       <c r="L68" s="61"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="82" t="s">
+      <c r="N68" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="O68" s="83"/>
+      <c r="O68" s="78"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="82"/>
-      <c r="S68" s="83"/>
+      <c r="R68" s="77"/>
+      <c r="S68" s="78"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="82" t="s">
+      <c r="V68" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="W68" s="83"/>
+      <c r="W68" s="78"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="82" t="s">
+      <c r="Z68" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="AA68" s="83"/>
+      <c r="AA68" s="78"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="82" t="s">
+      <c r="AD68" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="AE68" s="83"/>
+      <c r="AE68" s="78"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="82" t="s">
+      <c r="AH68" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="AI68" s="83"/>
+      <c r="AI68" s="78"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="82" t="s">
+      <c r="AL68" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="AM68" s="83"/>
+      <c r="AM68" s="78"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5880,55 +5880,55 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="71"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="73"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="83"/>
+      <c r="D69" s="84"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="73"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="83"/>
+      <c r="H69" s="84"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="71"/>
-      <c r="K69" s="72"/>
-      <c r="L69" s="73"/>
+      <c r="J69" s="82"/>
+      <c r="K69" s="83"/>
+      <c r="L69" s="84"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="84" t="s">
+      <c r="N69" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="O69" s="85"/>
-      <c r="P69" s="86"/>
+      <c r="O69" s="80"/>
+      <c r="P69" s="81"/>
       <c r="Q69" s="32"/>
-      <c r="R69" s="84"/>
-      <c r="S69" s="85"/>
-      <c r="T69" s="86"/>
+      <c r="R69" s="79"/>
+      <c r="S69" s="80"/>
+      <c r="T69" s="81"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="84"/>
-      <c r="W69" s="85"/>
-      <c r="X69" s="86"/>
+      <c r="V69" s="79"/>
+      <c r="W69" s="80"/>
+      <c r="X69" s="81"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="84" t="s">
+      <c r="Z69" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AA69" s="85"/>
-      <c r="AB69" s="86"/>
+      <c r="AA69" s="80"/>
+      <c r="AB69" s="81"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="84" t="s">
+      <c r="AD69" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AE69" s="85"/>
-      <c r="AF69" s="86"/>
+      <c r="AE69" s="80"/>
+      <c r="AF69" s="81"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="84" t="s">
+      <c r="AH69" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AI69" s="85"/>
-      <c r="AJ69" s="86"/>
+      <c r="AI69" s="80"/>
+      <c r="AJ69" s="81"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="84" t="s">
+      <c r="AL69" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AM69" s="85"/>
-      <c r="AN69" s="86"/>
+      <c r="AM69" s="80"/>
+      <c r="AN69" s="81"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5938,59 +5938,59 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="79" t="s">
+      <c r="B70" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="80"/>
-      <c r="D70" s="81"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="68"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="81"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="67"/>
+      <c r="H70" s="68"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="79"/>
-      <c r="K70" s="80"/>
-      <c r="L70" s="81"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="67"/>
+      <c r="L70" s="68"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="87" t="s">
+      <c r="N70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="88"/>
-      <c r="P70" s="89"/>
+      <c r="O70" s="70"/>
+      <c r="P70" s="90"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="87"/>
-      <c r="S70" s="88"/>
-      <c r="T70" s="89"/>
+      <c r="R70" s="69"/>
+      <c r="S70" s="70"/>
+      <c r="T70" s="90"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="87" t="s">
+      <c r="V70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="W70" s="88"/>
-      <c r="X70" s="89"/>
+      <c r="W70" s="70"/>
+      <c r="X70" s="90"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="87" t="s">
+      <c r="Z70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AA70" s="88"/>
-      <c r="AB70" s="89"/>
+      <c r="AA70" s="70"/>
+      <c r="AB70" s="90"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="87" t="s">
+      <c r="AD70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AE70" s="88"/>
-      <c r="AF70" s="89"/>
+      <c r="AE70" s="70"/>
+      <c r="AF70" s="90"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="87" t="s">
+      <c r="AH70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AI70" s="88"/>
-      <c r="AJ70" s="89"/>
+      <c r="AI70" s="70"/>
+      <c r="AJ70" s="90"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="87" t="s">
+      <c r="AL70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AM70" s="88"/>
-      <c r="AN70" s="89"/>
+      <c r="AM70" s="70"/>
+      <c r="AN70" s="90"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6000,59 +6000,59 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="64"/>
-      <c r="D71" s="65"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="89"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="63"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="65"/>
+      <c r="F71" s="87"/>
+      <c r="G71" s="88"/>
+      <c r="H71" s="89"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="63"/>
-      <c r="K71" s="64"/>
-      <c r="L71" s="65"/>
+      <c r="J71" s="87"/>
+      <c r="K71" s="88"/>
+      <c r="L71" s="89"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="63" t="s">
+      <c r="N71" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="O71" s="64"/>
-      <c r="P71" s="65"/>
+      <c r="O71" s="88"/>
+      <c r="P71" s="89"/>
       <c r="Q71" s="31"/>
-      <c r="R71" s="63"/>
-      <c r="S71" s="64"/>
-      <c r="T71" s="65"/>
+      <c r="R71" s="87"/>
+      <c r="S71" s="88"/>
+      <c r="T71" s="89"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="63" t="s">
+      <c r="V71" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="W71" s="64"/>
-      <c r="X71" s="65"/>
+      <c r="W71" s="88"/>
+      <c r="X71" s="89"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="63" t="s">
+      <c r="Z71" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="64"/>
-      <c r="AB71" s="65"/>
+      <c r="AA71" s="88"/>
+      <c r="AB71" s="89"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="63" t="s">
+      <c r="AD71" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="64"/>
-      <c r="AF71" s="65"/>
+      <c r="AE71" s="88"/>
+      <c r="AF71" s="89"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="63" t="s">
+      <c r="AH71" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="64"/>
-      <c r="AJ71" s="65"/>
+      <c r="AI71" s="88"/>
+      <c r="AJ71" s="89"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="63" t="s">
+      <c r="AL71" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AM71" s="64"/>
-      <c r="AN71" s="65"/>
+      <c r="AM71" s="88"/>
+      <c r="AN71" s="89"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6062,47 +6062,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="68"/>
+      <c r="B72" s="97"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="99"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="68"/>
+      <c r="F72" s="97"/>
+      <c r="G72" s="98"/>
+      <c r="H72" s="99"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="66"/>
-      <c r="K72" s="67"/>
-      <c r="L72" s="68"/>
+      <c r="J72" s="97"/>
+      <c r="K72" s="98"/>
+      <c r="L72" s="99"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="66"/>
-      <c r="O72" s="67"/>
-      <c r="P72" s="68"/>
+      <c r="N72" s="97"/>
+      <c r="O72" s="98"/>
+      <c r="P72" s="99"/>
       <c r="Q72" s="44"/>
-      <c r="R72" s="66"/>
-      <c r="S72" s="67"/>
-      <c r="T72" s="68"/>
+      <c r="R72" s="97"/>
+      <c r="S72" s="98"/>
+      <c r="T72" s="99"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="66" t="s">
+      <c r="V72" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="W72" s="67"/>
-      <c r="X72" s="68"/>
+      <c r="W72" s="98"/>
+      <c r="X72" s="99"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="66"/>
-      <c r="AA72" s="67"/>
-      <c r="AB72" s="68"/>
+      <c r="Z72" s="97"/>
+      <c r="AA72" s="98"/>
+      <c r="AB72" s="99"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="66"/>
-      <c r="AE72" s="67"/>
-      <c r="AF72" s="68"/>
+      <c r="AD72" s="97"/>
+      <c r="AE72" s="98"/>
+      <c r="AF72" s="99"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="66"/>
-      <c r="AI72" s="67"/>
-      <c r="AJ72" s="68"/>
+      <c r="AH72" s="97"/>
+      <c r="AI72" s="98"/>
+      <c r="AJ72" s="99"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="66"/>
-      <c r="AM72" s="67"/>
-      <c r="AN72" s="68"/>
+      <c r="AL72" s="97"/>
+      <c r="AM72" s="98"/>
+      <c r="AN72" s="99"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6156,58 +6156,58 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="69" t="s">
+      <c r="B74" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="70"/>
+      <c r="C74" s="94"/>
       <c r="D74" s="61"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="F74" s="93"/>
+      <c r="G74" s="94"/>
       <c r="H74" s="61"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="70"/>
+      <c r="J74" s="93"/>
+      <c r="K74" s="94"/>
       <c r="L74" s="61"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="82" t="s">
+      <c r="N74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="O74" s="83"/>
+      <c r="O74" s="78"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="32"/>
-      <c r="R74" s="82" t="s">
+      <c r="R74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="S74" s="83"/>
+      <c r="S74" s="78"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="82" t="s">
+      <c r="V74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="W74" s="83"/>
+      <c r="W74" s="78"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="82" t="s">
+      <c r="Z74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="AA74" s="83"/>
+      <c r="AA74" s="78"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="82" t="s">
+      <c r="AD74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="AE74" s="83"/>
+      <c r="AE74" s="78"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="82" t="s">
+      <c r="AH74" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="AI74" s="83"/>
+      <c r="AI74" s="78"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="82"/>
-      <c r="AM74" s="83"/>
+      <c r="AL74" s="77"/>
+      <c r="AM74" s="78"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6216,57 +6216,57 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="71"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="73"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="83"/>
+      <c r="D75" s="84"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="72"/>
-      <c r="H75" s="73"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="83"/>
+      <c r="H75" s="84"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="71"/>
-      <c r="K75" s="72"/>
-      <c r="L75" s="73"/>
+      <c r="J75" s="82"/>
+      <c r="K75" s="83"/>
+      <c r="L75" s="84"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="84" t="s">
+      <c r="N75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="O75" s="85"/>
-      <c r="P75" s="86"/>
+      <c r="O75" s="80"/>
+      <c r="P75" s="81"/>
       <c r="Q75" s="32"/>
-      <c r="R75" s="84" t="s">
+      <c r="R75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="S75" s="85"/>
-      <c r="T75" s="86"/>
+      <c r="S75" s="80"/>
+      <c r="T75" s="81"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="84" t="s">
+      <c r="V75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="W75" s="85"/>
-      <c r="X75" s="86"/>
+      <c r="W75" s="80"/>
+      <c r="X75" s="81"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="84" t="s">
+      <c r="Z75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AA75" s="85"/>
-      <c r="AB75" s="86"/>
+      <c r="AA75" s="80"/>
+      <c r="AB75" s="81"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="84" t="s">
+      <c r="AD75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AE75" s="85"/>
-      <c r="AF75" s="86"/>
+      <c r="AE75" s="80"/>
+      <c r="AF75" s="81"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="84" t="s">
+      <c r="AH75" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AI75" s="85"/>
-      <c r="AJ75" s="86"/>
+      <c r="AI75" s="80"/>
+      <c r="AJ75" s="81"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="84"/>
-      <c r="AM75" s="85"/>
-      <c r="AN75" s="86"/>
+      <c r="AL75" s="79"/>
+      <c r="AM75" s="80"/>
+      <c r="AN75" s="81"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6274,59 +6274,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="79" t="s">
+      <c r="B76" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="80"/>
-      <c r="D76" s="81"/>
+      <c r="C76" s="67"/>
+      <c r="D76" s="68"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="79"/>
-      <c r="G76" s="80"/>
-      <c r="H76" s="81"/>
+      <c r="F76" s="66"/>
+      <c r="G76" s="67"/>
+      <c r="H76" s="68"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="79"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="81"/>
+      <c r="J76" s="66"/>
+      <c r="K76" s="67"/>
+      <c r="L76" s="68"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="87" t="s">
+      <c r="N76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="88"/>
-      <c r="P76" s="89"/>
+      <c r="O76" s="70"/>
+      <c r="P76" s="90"/>
       <c r="Q76" s="32"/>
-      <c r="R76" s="87" t="s">
+      <c r="R76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="88"/>
-      <c r="T76" s="89"/>
+      <c r="S76" s="70"/>
+      <c r="T76" s="90"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="87" t="s">
+      <c r="V76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="W76" s="88"/>
-      <c r="X76" s="89"/>
+      <c r="W76" s="70"/>
+      <c r="X76" s="90"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="87" t="s">
+      <c r="Z76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="88"/>
-      <c r="AB76" s="89"/>
+      <c r="AA76" s="70"/>
+      <c r="AB76" s="90"/>
       <c r="AC76" s="36"/>
-      <c r="AD76" s="87" t="s">
+      <c r="AD76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AE76" s="88"/>
-      <c r="AF76" s="89"/>
+      <c r="AE76" s="70"/>
+      <c r="AF76" s="90"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="87" t="s">
+      <c r="AH76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AI76" s="88"/>
-      <c r="AJ76" s="89"/>
+      <c r="AI76" s="70"/>
+      <c r="AJ76" s="90"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="87"/>
-      <c r="AM76" s="88"/>
-      <c r="AN76" s="89"/>
+      <c r="AL76" s="69"/>
+      <c r="AM76" s="70"/>
+      <c r="AN76" s="90"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6334,59 +6334,59 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="64"/>
-      <c r="D77" s="65"/>
+      <c r="C77" s="88"/>
+      <c r="D77" s="89"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="64"/>
-      <c r="H77" s="65"/>
+      <c r="F77" s="87"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="89"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="63"/>
-      <c r="K77" s="64"/>
-      <c r="L77" s="65"/>
+      <c r="J77" s="87"/>
+      <c r="K77" s="88"/>
+      <c r="L77" s="89"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="63" t="s">
+      <c r="N77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="O77" s="64"/>
-      <c r="P77" s="65"/>
+      <c r="O77" s="88"/>
+      <c r="P77" s="89"/>
       <c r="Q77" s="32"/>
-      <c r="R77" s="63" t="s">
+      <c r="R77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="64"/>
-      <c r="T77" s="65"/>
+      <c r="S77" s="88"/>
+      <c r="T77" s="89"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="63" t="s">
+      <c r="V77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="W77" s="64"/>
-      <c r="X77" s="65"/>
+      <c r="W77" s="88"/>
+      <c r="X77" s="89"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="63" t="s">
+      <c r="Z77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="64"/>
-      <c r="AB77" s="65"/>
+      <c r="AA77" s="88"/>
+      <c r="AB77" s="89"/>
       <c r="AC77" s="32"/>
-      <c r="AD77" s="63" t="s">
+      <c r="AD77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="64"/>
-      <c r="AF77" s="65"/>
+      <c r="AE77" s="88"/>
+      <c r="AF77" s="89"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="63" t="s">
+      <c r="AH77" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="64"/>
-      <c r="AJ77" s="65"/>
+      <c r="AI77" s="88"/>
+      <c r="AJ77" s="89"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="63"/>
-      <c r="AM77" s="64"/>
-      <c r="AN77" s="65"/>
+      <c r="AL77" s="87"/>
+      <c r="AM77" s="88"/>
+      <c r="AN77" s="89"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6394,45 +6394,45 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="67"/>
-      <c r="D78" s="68"/>
+      <c r="B78" s="97"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="99"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="66"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="68"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="98"/>
+      <c r="H78" s="99"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="66"/>
-      <c r="K78" s="67"/>
-      <c r="L78" s="68"/>
+      <c r="J78" s="97"/>
+      <c r="K78" s="98"/>
+      <c r="L78" s="99"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="66"/>
-      <c r="O78" s="67"/>
-      <c r="P78" s="68"/>
+      <c r="N78" s="97"/>
+      <c r="O78" s="98"/>
+      <c r="P78" s="99"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="66"/>
-      <c r="S78" s="67"/>
-      <c r="T78" s="68"/>
+      <c r="R78" s="97"/>
+      <c r="S78" s="98"/>
+      <c r="T78" s="99"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="66"/>
-      <c r="W78" s="67"/>
-      <c r="X78" s="68"/>
+      <c r="V78" s="97"/>
+      <c r="W78" s="98"/>
+      <c r="X78" s="99"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="66"/>
-      <c r="AA78" s="67"/>
-      <c r="AB78" s="68"/>
+      <c r="Z78" s="97"/>
+      <c r="AA78" s="98"/>
+      <c r="AB78" s="99"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="66"/>
-      <c r="AE78" s="67"/>
-      <c r="AF78" s="68"/>
+      <c r="AD78" s="97"/>
+      <c r="AE78" s="98"/>
+      <c r="AF78" s="99"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="66"/>
-      <c r="AI78" s="67"/>
-      <c r="AJ78" s="68"/>
+      <c r="AH78" s="97"/>
+      <c r="AI78" s="98"/>
+      <c r="AJ78" s="99"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="66"/>
-      <c r="AM78" s="67"/>
-      <c r="AN78" s="68"/>
+      <c r="AL78" s="97"/>
+      <c r="AM78" s="98"/>
+      <c r="AN78" s="99"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6486,60 +6486,62 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="69" t="s">
+      <c r="B80" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="C80" s="70"/>
+      <c r="C80" s="94"/>
       <c r="D80" s="61"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="69" t="s">
+      <c r="F80" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="G80" s="70"/>
+      <c r="G80" s="94"/>
       <c r="H80" s="61"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="69" t="s">
+      <c r="J80" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="K80" s="70"/>
+      <c r="K80" s="94"/>
       <c r="L80" s="61"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="96" t="s">
+      <c r="N80" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="O80" s="97"/>
+      <c r="O80" s="145"/>
       <c r="P80" s="60"/>
       <c r="Q80" s="36"/>
-      <c r="R80" s="82" t="s">
+      <c r="R80" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="S80" s="83"/>
+      <c r="S80" s="78"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="82"/>
-      <c r="W80" s="83"/>
+      <c r="V80" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="W80" s="78"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="74" t="s">
+      <c r="Z80" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="AA80" s="75"/>
+      <c r="AA80" s="96"/>
       <c r="AB80" s="55"/>
       <c r="AC80" s="32"/>
-      <c r="AD80" s="82"/>
-      <c r="AE80" s="83"/>
+      <c r="AD80" s="77"/>
+      <c r="AE80" s="78"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="82" t="s">
+      <c r="AH80" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="AI80" s="83"/>
+      <c r="AI80" s="78"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="82" t="s">
+      <c r="AL80" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="AM80" s="83"/>
+      <c r="AM80" s="78"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6548,57 +6550,59 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="71" t="s">
+      <c r="B81" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="C81" s="72"/>
-      <c r="D81" s="73"/>
+      <c r="C81" s="83"/>
+      <c r="D81" s="84"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="71" t="s">
+      <c r="F81" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="72"/>
-      <c r="H81" s="73"/>
+      <c r="G81" s="83"/>
+      <c r="H81" s="84"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="71" t="s">
+      <c r="J81" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="K81" s="72"/>
-      <c r="L81" s="73"/>
+      <c r="K81" s="83"/>
+      <c r="L81" s="84"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="93" t="s">
+      <c r="N81" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="O81" s="94"/>
-      <c r="P81" s="95"/>
+      <c r="O81" s="102"/>
+      <c r="P81" s="103"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="84" t="s">
+      <c r="R81" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="S81" s="85"/>
-      <c r="T81" s="86"/>
+      <c r="S81" s="80"/>
+      <c r="T81" s="81"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="84"/>
-      <c r="W81" s="85"/>
-      <c r="X81" s="86"/>
+      <c r="V81" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" s="80"/>
+      <c r="X81" s="81"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="84" t="s">
+      <c r="Z81" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="AA81" s="85"/>
-      <c r="AB81" s="86"/>
+      <c r="AA81" s="80"/>
+      <c r="AB81" s="81"/>
       <c r="AC81" s="35"/>
-      <c r="AD81" s="84"/>
-      <c r="AE81" s="85"/>
-      <c r="AF81" s="86"/>
+      <c r="AD81" s="79"/>
+      <c r="AE81" s="80"/>
+      <c r="AF81" s="81"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="84"/>
-      <c r="AI81" s="85"/>
-      <c r="AJ81" s="86"/>
+      <c r="AH81" s="79"/>
+      <c r="AI81" s="80"/>
+      <c r="AJ81" s="81"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="84"/>
-      <c r="AM81" s="85"/>
-      <c r="AN81" s="86"/>
+      <c r="AL81" s="79"/>
+      <c r="AM81" s="80"/>
+      <c r="AN81" s="81"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6606,51 +6610,51 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="79"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="81"/>
+      <c r="B82" s="66"/>
+      <c r="C82" s="67"/>
+      <c r="D82" s="68"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="79"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="81"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="67"/>
+      <c r="H82" s="68"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="79"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="81"/>
+      <c r="J82" s="66"/>
+      <c r="K82" s="67"/>
+      <c r="L82" s="68"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="90"/>
-      <c r="O82" s="91"/>
-      <c r="P82" s="92"/>
+      <c r="N82" s="146"/>
+      <c r="O82" s="147"/>
+      <c r="P82" s="148"/>
       <c r="Q82" s="31"/>
-      <c r="R82" s="87"/>
-      <c r="S82" s="88"/>
-      <c r="T82" s="89"/>
+      <c r="R82" s="69"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="90"/>
       <c r="U82" s="36"/>
-      <c r="V82" s="87"/>
-      <c r="W82" s="88"/>
-      <c r="X82" s="89"/>
+      <c r="V82" s="69"/>
+      <c r="W82" s="70"/>
+      <c r="X82" s="90"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="87" t="s">
+      <c r="Z82" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AA82" s="88"/>
-      <c r="AB82" s="89"/>
+      <c r="AA82" s="70"/>
+      <c r="AB82" s="90"/>
       <c r="AC82" s="31"/>
-      <c r="AD82" s="87"/>
-      <c r="AE82" s="88"/>
-      <c r="AF82" s="89"/>
+      <c r="AD82" s="69"/>
+      <c r="AE82" s="70"/>
+      <c r="AF82" s="90"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="87" t="s">
+      <c r="AH82" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AI82" s="88"/>
-      <c r="AJ82" s="89"/>
+      <c r="AI82" s="70"/>
+      <c r="AJ82" s="90"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="87" t="s">
+      <c r="AL82" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="AM82" s="88"/>
-      <c r="AN82" s="89"/>
+      <c r="AM82" s="70"/>
+      <c r="AN82" s="90"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6658,61 +6662,63 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="63" t="s">
+      <c r="B83" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="C83" s="64"/>
-      <c r="D83" s="65"/>
+      <c r="C83" s="88"/>
+      <c r="D83" s="89"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="63" t="s">
+      <c r="F83" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="G83" s="64"/>
-      <c r="H83" s="65"/>
+      <c r="G83" s="88"/>
+      <c r="H83" s="89"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="63" t="s">
+      <c r="J83" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="K83" s="64"/>
-      <c r="L83" s="65"/>
+      <c r="K83" s="88"/>
+      <c r="L83" s="89"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="144" t="s">
+      <c r="N83" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="O83" s="145"/>
-      <c r="P83" s="146"/>
+      <c r="O83" s="105"/>
+      <c r="P83" s="106"/>
       <c r="Q83" s="37"/>
-      <c r="R83" s="63" t="s">
+      <c r="R83" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="S83" s="64"/>
-      <c r="T83" s="65"/>
+      <c r="S83" s="88"/>
+      <c r="T83" s="89"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="63"/>
-      <c r="W83" s="64"/>
-      <c r="X83" s="65"/>
+      <c r="V83" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="W83" s="88"/>
+      <c r="X83" s="89"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="63" t="s">
+      <c r="Z83" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="64"/>
-      <c r="AB83" s="65"/>
+      <c r="AA83" s="88"/>
+      <c r="AB83" s="89"/>
       <c r="AC83" s="31"/>
-      <c r="AD83" s="63"/>
-      <c r="AE83" s="64"/>
-      <c r="AF83" s="65"/>
+      <c r="AD83" s="87"/>
+      <c r="AE83" s="88"/>
+      <c r="AF83" s="89"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="147" t="s">
+      <c r="AH83" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="AI83" s="148"/>
-      <c r="AJ83" s="149"/>
+      <c r="AI83" s="117"/>
+      <c r="AJ83" s="118"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="63" t="s">
+      <c r="AL83" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="AM83" s="64"/>
-      <c r="AN83" s="65"/>
+      <c r="AM83" s="88"/>
+      <c r="AN83" s="89"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6720,53 +6726,55 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="66"/>
-      <c r="C84" s="67"/>
-      <c r="D84" s="68"/>
+      <c r="B84" s="97"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="99"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="66"/>
-      <c r="G84" s="67"/>
-      <c r="H84" s="68"/>
+      <c r="F84" s="97"/>
+      <c r="G84" s="98"/>
+      <c r="H84" s="99"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="66"/>
-      <c r="K84" s="67"/>
-      <c r="L84" s="68"/>
+      <c r="J84" s="97"/>
+      <c r="K84" s="98"/>
+      <c r="L84" s="99"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="111" t="s">
+      <c r="N84" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="O84" s="112"/>
-      <c r="P84" s="113"/>
+      <c r="O84" s="114"/>
+      <c r="P84" s="115"/>
       <c r="Q84" s="44"/>
-      <c r="R84" s="76" t="s">
+      <c r="R84" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="S84" s="77"/>
-      <c r="T84" s="78"/>
+      <c r="S84" s="64"/>
+      <c r="T84" s="65"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="66"/>
-      <c r="W84" s="67"/>
-      <c r="X84" s="68"/>
+      <c r="V84" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="W84" s="64"/>
+      <c r="X84" s="65"/>
       <c r="Y84" s="31"/>
-      <c r="Z84" s="66"/>
-      <c r="AA84" s="67"/>
-      <c r="AB84" s="68"/>
+      <c r="Z84" s="97"/>
+      <c r="AA84" s="98"/>
+      <c r="AB84" s="99"/>
       <c r="AC84" s="31"/>
-      <c r="AD84" s="66"/>
-      <c r="AE84" s="67"/>
-      <c r="AF84" s="68"/>
+      <c r="AD84" s="97"/>
+      <c r="AE84" s="98"/>
+      <c r="AF84" s="99"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="141" t="s">
+      <c r="AH84" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="AI84" s="142"/>
-      <c r="AJ84" s="143"/>
+      <c r="AI84" s="120"/>
+      <c r="AJ84" s="121"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="141" t="s">
+      <c r="AL84" s="119" t="s">
         <v>95</v>
       </c>
-      <c r="AM84" s="142"/>
-      <c r="AN84" s="143"/>
+      <c r="AM84" s="120"/>
+      <c r="AN84" s="121"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6786,21 +6794,23 @@
       <c r="K85" s="35"/>
       <c r="L85" s="35"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="111" t="s">
+      <c r="N85" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="O85" s="112"/>
-      <c r="P85" s="113"/>
+      <c r="O85" s="114"/>
+      <c r="P85" s="115"/>
       <c r="Q85" s="44"/>
-      <c r="R85" s="76" t="s">
+      <c r="R85" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="S85" s="77"/>
-      <c r="T85" s="78"/>
+      <c r="S85" s="64"/>
+      <c r="T85" s="65"/>
       <c r="U85" s="31"/>
-      <c r="V85" s="35"/>
-      <c r="W85" s="35"/>
-      <c r="X85" s="35"/>
+      <c r="V85" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="W85" s="64"/>
+      <c r="X85" s="65"/>
       <c r="Y85" s="35"/>
       <c r="Z85" s="35"/>
       <c r="AA85" s="35"/>
@@ -6824,62 +6834,64 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="69" t="s">
+      <c r="B86" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C86" s="70"/>
+      <c r="C86" s="94"/>
       <c r="D86" s="61"/>
       <c r="E86" s="32"/>
-      <c r="F86" s="69"/>
-      <c r="G86" s="70"/>
+      <c r="F86" s="93"/>
+      <c r="G86" s="94"/>
       <c r="H86" s="61"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="69"/>
-      <c r="K86" s="70"/>
+      <c r="J86" s="93"/>
+      <c r="K86" s="94"/>
       <c r="L86" s="61"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="111" t="s">
+      <c r="N86" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="O86" s="112"/>
-      <c r="P86" s="113"/>
+      <c r="O86" s="114"/>
+      <c r="P86" s="115"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="76" t="s">
+      <c r="R86" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="S86" s="77"/>
-      <c r="T86" s="78"/>
+      <c r="S86" s="64"/>
+      <c r="T86" s="65"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="82"/>
-      <c r="W86" s="83"/>
-      <c r="X86" s="34"/>
+      <c r="V86" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="W86" s="64"/>
+      <c r="X86" s="65"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="82" t="s">
+      <c r="Z86" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AA86" s="83"/>
+      <c r="AA86" s="78"/>
       <c r="AB86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="82" t="s">
+      <c r="AD86" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AE86" s="83"/>
+      <c r="AE86" s="78"/>
       <c r="AF86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="82" t="s">
+      <c r="AH86" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AI86" s="83"/>
+      <c r="AI86" s="78"/>
       <c r="AJ86" s="34" t="s">
         <v>62</v>
       </c>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="82"/>
-      <c r="AM86" s="83"/>
+      <c r="AL86" s="77"/>
+      <c r="AM86" s="78"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6888,45 +6900,45 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="71"/>
-      <c r="C87" s="72"/>
-      <c r="D87" s="73"/>
+      <c r="B87" s="82"/>
+      <c r="C87" s="83"/>
+      <c r="D87" s="84"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="73"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="83"/>
+      <c r="H87" s="84"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="73"/>
+      <c r="J87" s="82"/>
+      <c r="K87" s="83"/>
+      <c r="L87" s="84"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="98"/>
-      <c r="O87" s="99"/>
-      <c r="P87" s="100"/>
+      <c r="N87" s="107"/>
+      <c r="O87" s="108"/>
+      <c r="P87" s="109"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="76"/>
-      <c r="S87" s="77"/>
-      <c r="T87" s="78"/>
+      <c r="R87" s="63"/>
+      <c r="S87" s="64"/>
+      <c r="T87" s="65"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="84"/>
-      <c r="W87" s="85"/>
-      <c r="X87" s="86"/>
+      <c r="V87" s="63"/>
+      <c r="W87" s="64"/>
+      <c r="X87" s="65"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="87"/>
-      <c r="AA87" s="88"/>
+      <c r="Z87" s="69"/>
+      <c r="AA87" s="70"/>
       <c r="AB87" s="18"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="87"/>
-      <c r="AE87" s="88"/>
+      <c r="AD87" s="69"/>
+      <c r="AE87" s="70"/>
       <c r="AF87" s="18"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="87"/>
-      <c r="AI87" s="88"/>
+      <c r="AH87" s="69"/>
+      <c r="AI87" s="70"/>
       <c r="AJ87" s="18"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="84"/>
-      <c r="AM87" s="85"/>
-      <c r="AN87" s="86"/>
+      <c r="AL87" s="79"/>
+      <c r="AM87" s="80"/>
+      <c r="AN87" s="81"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6934,59 +6946,59 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="79" t="s">
+      <c r="B88" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C88" s="80"/>
-      <c r="D88" s="81"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="68"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="79"/>
-      <c r="G88" s="80"/>
-      <c r="H88" s="81"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="67"/>
+      <c r="H88" s="68"/>
       <c r="I88" s="31"/>
-      <c r="J88" s="79"/>
-      <c r="K88" s="80"/>
-      <c r="L88" s="81"/>
+      <c r="J88" s="66"/>
+      <c r="K88" s="67"/>
+      <c r="L88" s="68"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="98"/>
-      <c r="O88" s="99"/>
-      <c r="P88" s="100"/>
+      <c r="N88" s="107"/>
+      <c r="O88" s="108"/>
+      <c r="P88" s="109"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="76"/>
-      <c r="S88" s="77"/>
-      <c r="T88" s="78"/>
+      <c r="R88" s="63"/>
+      <c r="S88" s="64"/>
+      <c r="T88" s="65"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="87"/>
-      <c r="W88" s="88"/>
-      <c r="X88" s="89"/>
+      <c r="V88" s="63"/>
+      <c r="W88" s="64"/>
+      <c r="X88" s="65"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="139" t="s">
+      <c r="Z88" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="AA88" s="140"/>
+      <c r="AA88" s="72"/>
       <c r="AB88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="139" t="s">
+      <c r="AD88" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="AE88" s="140"/>
+      <c r="AE88" s="72"/>
       <c r="AF88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="139" t="s">
+      <c r="AH88" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="AI88" s="140"/>
+      <c r="AI88" s="72"/>
       <c r="AJ88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="87"/>
-      <c r="AM88" s="88"/>
-      <c r="AN88" s="89"/>
+      <c r="AL88" s="69"/>
+      <c r="AM88" s="70"/>
+      <c r="AN88" s="90"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6994,59 +7006,59 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="63" t="s">
+      <c r="B89" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="C89" s="64"/>
-      <c r="D89" s="65"/>
+      <c r="C89" s="88"/>
+      <c r="D89" s="89"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="63"/>
-      <c r="G89" s="64"/>
-      <c r="H89" s="65"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="88"/>
+      <c r="H89" s="89"/>
       <c r="I89" s="31"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="65"/>
+      <c r="J89" s="87"/>
+      <c r="K89" s="88"/>
+      <c r="L89" s="89"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="98"/>
-      <c r="O89" s="99"/>
-      <c r="P89" s="100"/>
+      <c r="N89" s="107"/>
+      <c r="O89" s="108"/>
+      <c r="P89" s="109"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="77"/>
-      <c r="T89" s="78"/>
+      <c r="R89" s="63"/>
+      <c r="S89" s="64"/>
+      <c r="T89" s="65"/>
       <c r="U89" s="32"/>
       <c r="V89" s="63"/>
       <c r="W89" s="64"/>
       <c r="X89" s="65"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="117" t="s">
+      <c r="Z89" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="AA89" s="118"/>
+      <c r="AA89" s="74"/>
       <c r="AB89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="117" t="s">
+      <c r="AD89" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AE89" s="118"/>
+      <c r="AE89" s="74"/>
       <c r="AF89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="117" t="s">
+      <c r="AH89" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AI89" s="118"/>
+      <c r="AI89" s="74"/>
       <c r="AJ89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="63"/>
-      <c r="AM89" s="64"/>
-      <c r="AN89" s="65"/>
+      <c r="AL89" s="87"/>
+      <c r="AM89" s="88"/>
+      <c r="AN89" s="89"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7054,57 +7066,57 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="66"/>
-      <c r="C90" s="67"/>
-      <c r="D90" s="68"/>
+      <c r="B90" s="97"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="99"/>
       <c r="E90" s="31"/>
-      <c r="F90" s="66"/>
-      <c r="G90" s="67"/>
-      <c r="H90" s="68"/>
+      <c r="F90" s="97"/>
+      <c r="G90" s="98"/>
+      <c r="H90" s="99"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="66"/>
-      <c r="K90" s="67"/>
-      <c r="L90" s="68"/>
+      <c r="J90" s="97"/>
+      <c r="K90" s="98"/>
+      <c r="L90" s="99"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="108"/>
-      <c r="O90" s="109"/>
-      <c r="P90" s="110"/>
+      <c r="N90" s="110"/>
+      <c r="O90" s="111"/>
+      <c r="P90" s="112"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="66"/>
-      <c r="S90" s="67"/>
-      <c r="T90" s="68"/>
+      <c r="R90" s="97"/>
+      <c r="S90" s="98"/>
+      <c r="T90" s="99"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="66"/>
-      <c r="W90" s="67"/>
-      <c r="X90" s="68"/>
+      <c r="V90" s="97"/>
+      <c r="W90" s="98"/>
+      <c r="X90" s="99"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="104" t="s">
+      <c r="Z90" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="AA90" s="105"/>
+      <c r="AA90" s="76"/>
       <c r="AB90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="104" t="s">
+      <c r="AD90" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="AE90" s="105"/>
+      <c r="AE90" s="76"/>
       <c r="AF90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="104" t="s">
+      <c r="AH90" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="AI90" s="105"/>
+      <c r="AI90" s="76"/>
       <c r="AJ90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="66"/>
-      <c r="AM90" s="67"/>
-      <c r="AN90" s="68"/>
+      <c r="AL90" s="97"/>
+      <c r="AM90" s="98"/>
+      <c r="AN90" s="99"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7136,26 +7148,26 @@
       <c r="W91" s="35"/>
       <c r="X91" s="35"/>
       <c r="Y91" s="35"/>
-      <c r="Z91" s="104" t="s">
+      <c r="Z91" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="AA91" s="105"/>
+      <c r="AA91" s="76"/>
       <c r="AB91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC91" s="44"/>
-      <c r="AD91" s="104" t="s">
+      <c r="AD91" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="AE91" s="105"/>
+      <c r="AE91" s="76"/>
       <c r="AF91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG91" s="44"/>
-      <c r="AH91" s="104" t="s">
+      <c r="AH91" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="AI91" s="105"/>
+      <c r="AI91" s="76"/>
       <c r="AJ91" s="45" t="s">
         <v>35</v>
       </c>
@@ -7170,58 +7182,58 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="69" t="s">
+      <c r="B92" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C92" s="70"/>
+      <c r="C92" s="94"/>
       <c r="D92" s="61"/>
       <c r="E92" s="32"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="F92" s="93"/>
+      <c r="G92" s="94"/>
       <c r="H92" s="61"/>
       <c r="I92" s="31"/>
-      <c r="J92" s="69"/>
-      <c r="K92" s="70"/>
+      <c r="J92" s="93"/>
+      <c r="K92" s="94"/>
       <c r="L92" s="61"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="82"/>
-      <c r="O92" s="83"/>
+      <c r="N92" s="77"/>
+      <c r="O92" s="78"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="36"/>
-      <c r="R92" s="82"/>
-      <c r="S92" s="83"/>
+      <c r="R92" s="77"/>
+      <c r="S92" s="78"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="82"/>
-      <c r="W92" s="83"/>
+      <c r="V92" s="77"/>
+      <c r="W92" s="78"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="104" t="s">
+      <c r="Z92" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="AA92" s="105"/>
+      <c r="AA92" s="76"/>
       <c r="AB92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="104" t="s">
+      <c r="AD92" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="AE92" s="105"/>
+      <c r="AE92" s="76"/>
       <c r="AF92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="104" t="s">
+      <c r="AH92" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="AI92" s="105"/>
+      <c r="AI92" s="76"/>
       <c r="AJ92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="82"/>
-      <c r="AM92" s="83"/>
+      <c r="AL92" s="77"/>
+      <c r="AM92" s="78"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -7230,47 +7242,47 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="71" t="s">
+      <c r="B93" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="72"/>
-      <c r="D93" s="73"/>
+      <c r="C93" s="83"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="32"/>
-      <c r="F93" s="71"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="73"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="83"/>
+      <c r="H93" s="84"/>
       <c r="I93" s="31"/>
-      <c r="J93" s="71"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="73"/>
+      <c r="J93" s="82"/>
+      <c r="K93" s="83"/>
+      <c r="L93" s="84"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="84"/>
-      <c r="O93" s="85"/>
-      <c r="P93" s="86"/>
+      <c r="N93" s="79"/>
+      <c r="O93" s="80"/>
+      <c r="P93" s="81"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="84"/>
-      <c r="S93" s="85"/>
-      <c r="T93" s="86"/>
+      <c r="R93" s="79"/>
+      <c r="S93" s="80"/>
+      <c r="T93" s="81"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="84"/>
-      <c r="W93" s="85"/>
-      <c r="X93" s="86"/>
+      <c r="V93" s="79"/>
+      <c r="W93" s="80"/>
+      <c r="X93" s="81"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="104"/>
-      <c r="AA93" s="105"/>
+      <c r="Z93" s="75"/>
+      <c r="AA93" s="76"/>
       <c r="AB93" s="45"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="104"/>
-      <c r="AE93" s="105"/>
+      <c r="AD93" s="75"/>
+      <c r="AE93" s="76"/>
       <c r="AF93" s="45"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="104"/>
-      <c r="AI93" s="105"/>
+      <c r="AH93" s="75"/>
+      <c r="AI93" s="76"/>
       <c r="AJ93" s="45"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="84"/>
-      <c r="AM93" s="85"/>
-      <c r="AN93" s="86"/>
+      <c r="AL93" s="79"/>
+      <c r="AM93" s="80"/>
+      <c r="AN93" s="81"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -7278,45 +7290,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="79"/>
-      <c r="C94" s="80"/>
-      <c r="D94" s="81"/>
+      <c r="B94" s="66"/>
+      <c r="C94" s="67"/>
+      <c r="D94" s="68"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="79"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="81"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="67"/>
+      <c r="H94" s="68"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="79"/>
-      <c r="K94" s="80"/>
-      <c r="L94" s="81"/>
+      <c r="J94" s="66"/>
+      <c r="K94" s="67"/>
+      <c r="L94" s="68"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="87"/>
-      <c r="O94" s="88"/>
-      <c r="P94" s="89"/>
+      <c r="N94" s="69"/>
+      <c r="O94" s="70"/>
+      <c r="P94" s="90"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="87"/>
-      <c r="S94" s="88"/>
-      <c r="T94" s="89"/>
+      <c r="R94" s="69"/>
+      <c r="S94" s="70"/>
+      <c r="T94" s="90"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="87"/>
-      <c r="W94" s="88"/>
-      <c r="X94" s="89"/>
+      <c r="V94" s="69"/>
+      <c r="W94" s="70"/>
+      <c r="X94" s="90"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="104"/>
-      <c r="AA94" s="105"/>
+      <c r="Z94" s="75"/>
+      <c r="AA94" s="76"/>
       <c r="AB94" s="45"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="104"/>
-      <c r="AE94" s="105"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
       <c r="AF94" s="45"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="104"/>
-      <c r="AI94" s="105"/>
+      <c r="AH94" s="75"/>
+      <c r="AI94" s="76"/>
       <c r="AJ94" s="45"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="87"/>
-      <c r="AM94" s="88"/>
-      <c r="AN94" s="89"/>
+      <c r="AL94" s="69"/>
+      <c r="AM94" s="70"/>
+      <c r="AN94" s="90"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7324,47 +7336,47 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="63" t="s">
+      <c r="B95" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="64"/>
-      <c r="D95" s="65"/>
+      <c r="C95" s="88"/>
+      <c r="D95" s="89"/>
       <c r="E95" s="32"/>
-      <c r="F95" s="63"/>
-      <c r="G95" s="64"/>
-      <c r="H95" s="65"/>
+      <c r="F95" s="87"/>
+      <c r="G95" s="88"/>
+      <c r="H95" s="89"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="63"/>
-      <c r="K95" s="64"/>
-      <c r="L95" s="65"/>
+      <c r="J95" s="87"/>
+      <c r="K95" s="88"/>
+      <c r="L95" s="89"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="63"/>
-      <c r="O95" s="64"/>
-      <c r="P95" s="65"/>
+      <c r="N95" s="87"/>
+      <c r="O95" s="88"/>
+      <c r="P95" s="89"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="63"/>
-      <c r="S95" s="64"/>
-      <c r="T95" s="65"/>
+      <c r="R95" s="87"/>
+      <c r="S95" s="88"/>
+      <c r="T95" s="89"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="63"/>
-      <c r="W95" s="64"/>
-      <c r="X95" s="65"/>
+      <c r="V95" s="87"/>
+      <c r="W95" s="88"/>
+      <c r="X95" s="89"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="104"/>
-      <c r="AA95" s="105"/>
+      <c r="Z95" s="75"/>
+      <c r="AA95" s="76"/>
       <c r="AB95" s="45"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="104"/>
-      <c r="AE95" s="105"/>
+      <c r="AD95" s="75"/>
+      <c r="AE95" s="76"/>
       <c r="AF95" s="45"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="104"/>
-      <c r="AI95" s="105"/>
+      <c r="AH95" s="75"/>
+      <c r="AI95" s="76"/>
       <c r="AJ95" s="45"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="63"/>
-      <c r="AM95" s="64"/>
-      <c r="AN95" s="65"/>
+      <c r="AL95" s="87"/>
+      <c r="AM95" s="88"/>
+      <c r="AN95" s="89"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7372,45 +7384,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="76"/>
-      <c r="C96" s="77"/>
-      <c r="D96" s="78"/>
+      <c r="B96" s="63"/>
+      <c r="C96" s="64"/>
+      <c r="D96" s="65"/>
       <c r="E96" s="31"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="67"/>
-      <c r="H96" s="68"/>
+      <c r="F96" s="97"/>
+      <c r="G96" s="98"/>
+      <c r="H96" s="99"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="66"/>
-      <c r="K96" s="67"/>
-      <c r="L96" s="68"/>
+      <c r="J96" s="97"/>
+      <c r="K96" s="98"/>
+      <c r="L96" s="99"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="66"/>
-      <c r="O96" s="67"/>
-      <c r="P96" s="68"/>
+      <c r="N96" s="97"/>
+      <c r="O96" s="98"/>
+      <c r="P96" s="99"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="66"/>
-      <c r="S96" s="67"/>
-      <c r="T96" s="68"/>
+      <c r="R96" s="97"/>
+      <c r="S96" s="98"/>
+      <c r="T96" s="99"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="66"/>
-      <c r="W96" s="67"/>
-      <c r="X96" s="68"/>
+      <c r="V96" s="97"/>
+      <c r="W96" s="98"/>
+      <c r="X96" s="99"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="106"/>
-      <c r="AA96" s="107"/>
+      <c r="Z96" s="85"/>
+      <c r="AA96" s="86"/>
       <c r="AB96" s="42"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="106"/>
-      <c r="AE96" s="107"/>
+      <c r="AD96" s="85"/>
+      <c r="AE96" s="86"/>
       <c r="AF96" s="42"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="106"/>
-      <c r="AI96" s="107"/>
+      <c r="AH96" s="85"/>
+      <c r="AI96" s="86"/>
       <c r="AJ96" s="42"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="66"/>
-      <c r="AM96" s="67"/>
-      <c r="AN96" s="68"/>
+      <c r="AL96" s="97"/>
+      <c r="AM96" s="98"/>
+      <c r="AN96" s="99"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7418,11 +7430,11 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
-      <c r="B97" s="76" t="s">
+      <c r="B97" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="77"/>
-      <c r="D97" s="78"/>
+      <c r="C97" s="64"/>
+      <c r="D97" s="65"/>
       <c r="E97" s="35"/>
       <c r="F97" s="35"/>
       <c r="G97" s="35"/>
@@ -7466,56 +7478,56 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="76" t="s">
+      <c r="B98" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="C98" s="77"/>
-      <c r="D98" s="78"/>
+      <c r="C98" s="64"/>
+      <c r="D98" s="65"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="69"/>
-      <c r="G98" s="70"/>
+      <c r="F98" s="93"/>
+      <c r="G98" s="94"/>
       <c r="H98" s="61"/>
       <c r="I98" s="31"/>
-      <c r="J98" s="69"/>
-      <c r="K98" s="70"/>
+      <c r="J98" s="93"/>
+      <c r="K98" s="94"/>
       <c r="L98" s="61"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="82" t="s">
+      <c r="N98" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="O98" s="83"/>
+      <c r="O98" s="78"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="82" t="s">
+      <c r="R98" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="S98" s="83"/>
+      <c r="S98" s="78"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="82" t="s">
+      <c r="V98" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="W98" s="83"/>
+      <c r="W98" s="78"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="82" t="s">
+      <c r="Z98" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="AA98" s="83"/>
+      <c r="AA98" s="78"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="82" t="s">
+      <c r="AD98" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="AE98" s="83"/>
+      <c r="AE98" s="78"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="82"/>
-      <c r="AI98" s="83"/>
+      <c r="AH98" s="77"/>
+      <c r="AI98" s="78"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="82"/>
-      <c r="AM98" s="83"/>
+      <c r="AL98" s="77"/>
+      <c r="AM98" s="78"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7524,57 +7536,57 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="76" t="s">
+      <c r="B99" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="77"/>
-      <c r="D99" s="78"/>
+      <c r="C99" s="64"/>
+      <c r="D99" s="65"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="73"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="83"/>
+      <c r="H99" s="84"/>
       <c r="I99" s="31"/>
-      <c r="J99" s="71"/>
-      <c r="K99" s="72"/>
-      <c r="L99" s="73"/>
+      <c r="J99" s="82"/>
+      <c r="K99" s="83"/>
+      <c r="L99" s="84"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="84" t="s">
+      <c r="N99" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="O99" s="85"/>
-      <c r="P99" s="86"/>
+      <c r="O99" s="80"/>
+      <c r="P99" s="81"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="84" t="s">
+      <c r="R99" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="S99" s="85"/>
-      <c r="T99" s="86"/>
+      <c r="S99" s="80"/>
+      <c r="T99" s="81"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="84" t="s">
+      <c r="V99" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="W99" s="85"/>
-      <c r="X99" s="86"/>
+      <c r="W99" s="80"/>
+      <c r="X99" s="81"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="84" t="s">
+      <c r="Z99" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AA99" s="85"/>
-      <c r="AB99" s="86"/>
+      <c r="AA99" s="80"/>
+      <c r="AB99" s="81"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="84" t="s">
+      <c r="AD99" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AE99" s="85"/>
-      <c r="AF99" s="86"/>
+      <c r="AE99" s="80"/>
+      <c r="AF99" s="81"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="84"/>
-      <c r="AI99" s="85"/>
-      <c r="AJ99" s="86"/>
+      <c r="AH99" s="79"/>
+      <c r="AI99" s="80"/>
+      <c r="AJ99" s="81"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="84"/>
-      <c r="AM99" s="85"/>
-      <c r="AN99" s="86"/>
+      <c r="AL99" s="79"/>
+      <c r="AM99" s="80"/>
+      <c r="AN99" s="81"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7582,47 +7594,47 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="76" t="s">
+      <c r="B100" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="C100" s="77"/>
-      <c r="D100" s="78"/>
+      <c r="C100" s="64"/>
+      <c r="D100" s="65"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="79"/>
-      <c r="G100" s="80"/>
-      <c r="H100" s="81"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="67"/>
+      <c r="H100" s="68"/>
       <c r="I100" s="32"/>
-      <c r="J100" s="79"/>
-      <c r="K100" s="80"/>
-      <c r="L100" s="81"/>
+      <c r="J100" s="66"/>
+      <c r="K100" s="67"/>
+      <c r="L100" s="68"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="87"/>
-      <c r="O100" s="88"/>
-      <c r="P100" s="89"/>
+      <c r="N100" s="69"/>
+      <c r="O100" s="70"/>
+      <c r="P100" s="90"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="87"/>
-      <c r="S100" s="88"/>
-      <c r="T100" s="89"/>
+      <c r="R100" s="69"/>
+      <c r="S100" s="70"/>
+      <c r="T100" s="90"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="87"/>
-      <c r="W100" s="88"/>
-      <c r="X100" s="89"/>
+      <c r="V100" s="69"/>
+      <c r="W100" s="70"/>
+      <c r="X100" s="90"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="87"/>
-      <c r="AA100" s="88"/>
-      <c r="AB100" s="89"/>
+      <c r="Z100" s="69"/>
+      <c r="AA100" s="70"/>
+      <c r="AB100" s="90"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="87"/>
-      <c r="AE100" s="88"/>
-      <c r="AF100" s="89"/>
+      <c r="AD100" s="69"/>
+      <c r="AE100" s="70"/>
+      <c r="AF100" s="90"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="87"/>
-      <c r="AI100" s="88"/>
-      <c r="AJ100" s="89"/>
+      <c r="AH100" s="69"/>
+      <c r="AI100" s="70"/>
+      <c r="AJ100" s="90"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="87"/>
-      <c r="AM100" s="88"/>
-      <c r="AN100" s="89"/>
+      <c r="AL100" s="69"/>
+      <c r="AM100" s="70"/>
+      <c r="AN100" s="90"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7630,57 +7642,57 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="76" t="s">
+      <c r="B101" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="77"/>
-      <c r="D101" s="78"/>
+      <c r="C101" s="64"/>
+      <c r="D101" s="65"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="63"/>
-      <c r="G101" s="64"/>
-      <c r="H101" s="65"/>
+      <c r="F101" s="87"/>
+      <c r="G101" s="88"/>
+      <c r="H101" s="89"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="63"/>
-      <c r="K101" s="64"/>
-      <c r="L101" s="65"/>
+      <c r="J101" s="87"/>
+      <c r="K101" s="88"/>
+      <c r="L101" s="89"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="63" t="s">
+      <c r="N101" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="O101" s="64"/>
-      <c r="P101" s="65"/>
+      <c r="O101" s="88"/>
+      <c r="P101" s="89"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="63" t="s">
+      <c r="R101" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="S101" s="64"/>
-      <c r="T101" s="65"/>
+      <c r="S101" s="88"/>
+      <c r="T101" s="89"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="63" t="s">
+      <c r="V101" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="W101" s="64"/>
-      <c r="X101" s="65"/>
+      <c r="W101" s="88"/>
+      <c r="X101" s="89"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="63" t="s">
+      <c r="Z101" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AA101" s="64"/>
-      <c r="AB101" s="65"/>
+      <c r="AA101" s="88"/>
+      <c r="AB101" s="89"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="63" t="s">
+      <c r="AD101" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AE101" s="64"/>
-      <c r="AF101" s="65"/>
+      <c r="AE101" s="88"/>
+      <c r="AF101" s="89"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="63"/>
-      <c r="AI101" s="64"/>
-      <c r="AJ101" s="65"/>
+      <c r="AH101" s="87"/>
+      <c r="AI101" s="88"/>
+      <c r="AJ101" s="89"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="63"/>
-      <c r="AM101" s="64"/>
-      <c r="AN101" s="65"/>
+      <c r="AL101" s="87"/>
+      <c r="AM101" s="88"/>
+      <c r="AN101" s="89"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7688,45 +7700,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="66"/>
-      <c r="C102" s="67"/>
-      <c r="D102" s="68"/>
+      <c r="B102" s="97"/>
+      <c r="C102" s="98"/>
+      <c r="D102" s="99"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="66"/>
-      <c r="G102" s="67"/>
-      <c r="H102" s="68"/>
+      <c r="F102" s="97"/>
+      <c r="G102" s="98"/>
+      <c r="H102" s="99"/>
       <c r="I102" s="31"/>
-      <c r="J102" s="66"/>
-      <c r="K102" s="67"/>
-      <c r="L102" s="68"/>
+      <c r="J102" s="97"/>
+      <c r="K102" s="98"/>
+      <c r="L102" s="99"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="66"/>
-      <c r="O102" s="67"/>
-      <c r="P102" s="68"/>
+      <c r="N102" s="97"/>
+      <c r="O102" s="98"/>
+      <c r="P102" s="99"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="66"/>
-      <c r="S102" s="67"/>
-      <c r="T102" s="68"/>
+      <c r="R102" s="97"/>
+      <c r="S102" s="98"/>
+      <c r="T102" s="99"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="66"/>
-      <c r="W102" s="67"/>
-      <c r="X102" s="68"/>
+      <c r="V102" s="97"/>
+      <c r="W102" s="98"/>
+      <c r="X102" s="99"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="66"/>
-      <c r="AA102" s="67"/>
-      <c r="AB102" s="68"/>
+      <c r="Z102" s="97"/>
+      <c r="AA102" s="98"/>
+      <c r="AB102" s="99"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="66"/>
-      <c r="AE102" s="67"/>
-      <c r="AF102" s="68"/>
+      <c r="AD102" s="97"/>
+      <c r="AE102" s="98"/>
+      <c r="AF102" s="99"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="66"/>
-      <c r="AI102" s="67"/>
-      <c r="AJ102" s="68"/>
+      <c r="AH102" s="97"/>
+      <c r="AI102" s="98"/>
+      <c r="AJ102" s="99"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="66"/>
-      <c r="AM102" s="67"/>
-      <c r="AN102" s="68"/>
+      <c r="AL102" s="97"/>
+      <c r="AM102" s="98"/>
+      <c r="AN102" s="99"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7796,70 +7808,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="82"/>
-      <c r="C105" s="83"/>
+      <c r="B105" s="77"/>
+      <c r="C105" s="78"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="82"/>
-      <c r="G105" s="83"/>
+      <c r="F105" s="77"/>
+      <c r="G105" s="78"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="82"/>
-      <c r="K105" s="83"/>
+      <c r="J105" s="77"/>
+      <c r="K105" s="78"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="84"/>
-      <c r="C106" s="85"/>
-      <c r="D106" s="86"/>
+      <c r="B106" s="79"/>
+      <c r="C106" s="80"/>
+      <c r="D106" s="81"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="84"/>
-      <c r="G106" s="85"/>
-      <c r="H106" s="86"/>
+      <c r="F106" s="79"/>
+      <c r="G106" s="80"/>
+      <c r="H106" s="81"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="84"/>
-      <c r="K106" s="85"/>
-      <c r="L106" s="86"/>
+      <c r="J106" s="79"/>
+      <c r="K106" s="80"/>
+      <c r="L106" s="81"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="87"/>
-      <c r="C107" s="88"/>
-      <c r="D107" s="89"/>
+      <c r="B107" s="69"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="90"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="87"/>
-      <c r="G107" s="88"/>
-      <c r="H107" s="89"/>
+      <c r="F107" s="69"/>
+      <c r="G107" s="70"/>
+      <c r="H107" s="90"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="87"/>
-      <c r="K107" s="88"/>
-      <c r="L107" s="89"/>
+      <c r="J107" s="69"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="90"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="63"/>
-      <c r="C108" s="64"/>
-      <c r="D108" s="65"/>
+      <c r="B108" s="87"/>
+      <c r="C108" s="88"/>
+      <c r="D108" s="89"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="63"/>
-      <c r="G108" s="64"/>
-      <c r="H108" s="65"/>
+      <c r="F108" s="87"/>
+      <c r="G108" s="88"/>
+      <c r="H108" s="89"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="63"/>
-      <c r="K108" s="64"/>
-      <c r="L108" s="65"/>
+      <c r="J108" s="87"/>
+      <c r="K108" s="88"/>
+      <c r="L108" s="89"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="66"/>
-      <c r="C109" s="67"/>
-      <c r="D109" s="68"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="99"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="66"/>
-      <c r="G109" s="67"/>
-      <c r="H109" s="68"/>
+      <c r="F109" s="97"/>
+      <c r="G109" s="98"/>
+      <c r="H109" s="99"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="66"/>
-      <c r="K109" s="67"/>
-      <c r="L109" s="68"/>
+      <c r="J109" s="97"/>
+      <c r="K109" s="98"/>
+      <c r="L109" s="99"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7875,69 +7887,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="82"/>
-      <c r="C111" s="83"/>
+      <c r="B111" s="77"/>
+      <c r="C111" s="78"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="82"/>
-      <c r="G111" s="83"/>
+      <c r="F111" s="77"/>
+      <c r="G111" s="78"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="82"/>
-      <c r="K111" s="83"/>
+      <c r="J111" s="77"/>
+      <c r="K111" s="78"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="84"/>
-      <c r="C112" s="85"/>
-      <c r="D112" s="86"/>
+      <c r="B112" s="79"/>
+      <c r="C112" s="80"/>
+      <c r="D112" s="81"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="84"/>
-      <c r="G112" s="85"/>
-      <c r="H112" s="86"/>
+      <c r="F112" s="79"/>
+      <c r="G112" s="80"/>
+      <c r="H112" s="81"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="84"/>
-      <c r="K112" s="85"/>
-      <c r="L112" s="86"/>
+      <c r="J112" s="79"/>
+      <c r="K112" s="80"/>
+      <c r="L112" s="81"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="87"/>
-      <c r="C113" s="88"/>
-      <c r="D113" s="89"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="90"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="87"/>
-      <c r="G113" s="88"/>
-      <c r="H113" s="89"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="70"/>
+      <c r="H113" s="90"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="87"/>
-      <c r="K113" s="88"/>
-      <c r="L113" s="89"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="70"/>
+      <c r="L113" s="90"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="63"/>
-      <c r="C114" s="64"/>
-      <c r="D114" s="65"/>
+      <c r="B114" s="87"/>
+      <c r="C114" s="88"/>
+      <c r="D114" s="89"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="63"/>
-      <c r="G114" s="64"/>
-      <c r="H114" s="65"/>
+      <c r="F114" s="87"/>
+      <c r="G114" s="88"/>
+      <c r="H114" s="89"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="63"/>
-      <c r="K114" s="64"/>
-      <c r="L114" s="65"/>
+      <c r="J114" s="87"/>
+      <c r="K114" s="88"/>
+      <c r="L114" s="89"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="66"/>
-      <c r="C115" s="67"/>
-      <c r="D115" s="68"/>
+      <c r="B115" s="97"/>
+      <c r="C115" s="98"/>
+      <c r="D115" s="99"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="66"/>
-      <c r="G115" s="67"/>
-      <c r="H115" s="68"/>
+      <c r="F115" s="97"/>
+      <c r="G115" s="98"/>
+      <c r="H115" s="99"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="66"/>
-      <c r="K115" s="67"/>
-      <c r="L115" s="68"/>
+      <c r="J115" s="97"/>
+      <c r="K115" s="98"/>
+      <c r="L115" s="99"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7953,69 +7965,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="82"/>
-      <c r="C117" s="83"/>
+      <c r="B117" s="77"/>
+      <c r="C117" s="78"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="82"/>
-      <c r="G117" s="83"/>
+      <c r="F117" s="77"/>
+      <c r="G117" s="78"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="82"/>
-      <c r="K117" s="83"/>
+      <c r="J117" s="77"/>
+      <c r="K117" s="78"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="84"/>
-      <c r="C118" s="85"/>
-      <c r="D118" s="86"/>
+      <c r="B118" s="79"/>
+      <c r="C118" s="80"/>
+      <c r="D118" s="81"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="84"/>
-      <c r="G118" s="85"/>
-      <c r="H118" s="86"/>
+      <c r="F118" s="79"/>
+      <c r="G118" s="80"/>
+      <c r="H118" s="81"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="84"/>
-      <c r="K118" s="85"/>
-      <c r="L118" s="86"/>
+      <c r="J118" s="79"/>
+      <c r="K118" s="80"/>
+      <c r="L118" s="81"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="87"/>
-      <c r="C119" s="88"/>
-      <c r="D119" s="89"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="70"/>
+      <c r="D119" s="90"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="87"/>
-      <c r="G119" s="88"/>
-      <c r="H119" s="89"/>
+      <c r="F119" s="69"/>
+      <c r="G119" s="70"/>
+      <c r="H119" s="90"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="87"/>
-      <c r="K119" s="88"/>
-      <c r="L119" s="89"/>
+      <c r="J119" s="69"/>
+      <c r="K119" s="70"/>
+      <c r="L119" s="90"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="63"/>
-      <c r="C120" s="64"/>
-      <c r="D120" s="65"/>
+      <c r="B120" s="87"/>
+      <c r="C120" s="88"/>
+      <c r="D120" s="89"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="63"/>
-      <c r="G120" s="64"/>
-      <c r="H120" s="65"/>
+      <c r="F120" s="87"/>
+      <c r="G120" s="88"/>
+      <c r="H120" s="89"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="63"/>
-      <c r="K120" s="64"/>
-      <c r="L120" s="65"/>
+      <c r="J120" s="87"/>
+      <c r="K120" s="88"/>
+      <c r="L120" s="89"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="66"/>
-      <c r="C121" s="67"/>
-      <c r="D121" s="68"/>
+      <c r="B121" s="97"/>
+      <c r="C121" s="98"/>
+      <c r="D121" s="99"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="66"/>
-      <c r="G121" s="67"/>
-      <c r="H121" s="68"/>
+      <c r="F121" s="97"/>
+      <c r="G121" s="98"/>
+      <c r="H121" s="99"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="66"/>
-      <c r="K121" s="67"/>
-      <c r="L121" s="68"/>
+      <c r="J121" s="97"/>
+      <c r="K121" s="98"/>
+      <c r="L121" s="99"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -8031,69 +8043,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="82"/>
-      <c r="C123" s="83"/>
+      <c r="B123" s="77"/>
+      <c r="C123" s="78"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="82"/>
-      <c r="G123" s="83"/>
+      <c r="F123" s="77"/>
+      <c r="G123" s="78"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="82"/>
-      <c r="K123" s="83"/>
+      <c r="J123" s="77"/>
+      <c r="K123" s="78"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="84"/>
-      <c r="C124" s="85"/>
-      <c r="D124" s="86"/>
+      <c r="B124" s="79"/>
+      <c r="C124" s="80"/>
+      <c r="D124" s="81"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="84"/>
-      <c r="G124" s="85"/>
-      <c r="H124" s="86"/>
+      <c r="F124" s="79"/>
+      <c r="G124" s="80"/>
+      <c r="H124" s="81"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="84"/>
-      <c r="K124" s="85"/>
-      <c r="L124" s="86"/>
+      <c r="J124" s="79"/>
+      <c r="K124" s="80"/>
+      <c r="L124" s="81"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="87"/>
-      <c r="C125" s="88"/>
-      <c r="D125" s="89"/>
+      <c r="B125" s="69"/>
+      <c r="C125" s="70"/>
+      <c r="D125" s="90"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="87"/>
-      <c r="G125" s="88"/>
-      <c r="H125" s="89"/>
+      <c r="F125" s="69"/>
+      <c r="G125" s="70"/>
+      <c r="H125" s="90"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="87"/>
-      <c r="K125" s="88"/>
-      <c r="L125" s="89"/>
+      <c r="J125" s="69"/>
+      <c r="K125" s="70"/>
+      <c r="L125" s="90"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="63"/>
-      <c r="C126" s="64"/>
-      <c r="D126" s="65"/>
+      <c r="B126" s="87"/>
+      <c r="C126" s="88"/>
+      <c r="D126" s="89"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="63"/>
-      <c r="G126" s="64"/>
-      <c r="H126" s="65"/>
+      <c r="F126" s="87"/>
+      <c r="G126" s="88"/>
+      <c r="H126" s="89"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="63"/>
-      <c r="K126" s="64"/>
-      <c r="L126" s="65"/>
+      <c r="J126" s="87"/>
+      <c r="K126" s="88"/>
+      <c r="L126" s="89"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="66"/>
-      <c r="C127" s="67"/>
-      <c r="D127" s="68"/>
+      <c r="B127" s="97"/>
+      <c r="C127" s="98"/>
+      <c r="D127" s="99"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="67"/>
-      <c r="H127" s="68"/>
+      <c r="F127" s="97"/>
+      <c r="G127" s="98"/>
+      <c r="H127" s="99"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="66"/>
-      <c r="K127" s="67"/>
-      <c r="L127" s="68"/>
+      <c r="J127" s="97"/>
+      <c r="K127" s="98"/>
+      <c r="L127" s="99"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8109,74 +8121,938 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="82"/>
-      <c r="C129" s="83"/>
+      <c r="B129" s="77"/>
+      <c r="C129" s="78"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="82"/>
-      <c r="G129" s="83"/>
+      <c r="F129" s="77"/>
+      <c r="G129" s="78"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="82"/>
-      <c r="K129" s="83"/>
+      <c r="J129" s="77"/>
+      <c r="K129" s="78"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="84"/>
-      <c r="C130" s="85"/>
-      <c r="D130" s="86"/>
+      <c r="B130" s="79"/>
+      <c r="C130" s="80"/>
+      <c r="D130" s="81"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="84"/>
-      <c r="G130" s="85"/>
-      <c r="H130" s="86"/>
+      <c r="F130" s="79"/>
+      <c r="G130" s="80"/>
+      <c r="H130" s="81"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="84"/>
-      <c r="K130" s="85"/>
-      <c r="L130" s="86"/>
+      <c r="J130" s="79"/>
+      <c r="K130" s="80"/>
+      <c r="L130" s="81"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="87"/>
-      <c r="C131" s="88"/>
-      <c r="D131" s="89"/>
+      <c r="B131" s="69"/>
+      <c r="C131" s="70"/>
+      <c r="D131" s="90"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="87"/>
-      <c r="G131" s="88"/>
-      <c r="H131" s="89"/>
+      <c r="F131" s="69"/>
+      <c r="G131" s="70"/>
+      <c r="H131" s="90"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="87"/>
-      <c r="K131" s="88"/>
-      <c r="L131" s="89"/>
+      <c r="J131" s="69"/>
+      <c r="K131" s="70"/>
+      <c r="L131" s="90"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="63"/>
-      <c r="C132" s="64"/>
-      <c r="D132" s="65"/>
+      <c r="B132" s="87"/>
+      <c r="C132" s="88"/>
+      <c r="D132" s="89"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="63"/>
-      <c r="G132" s="64"/>
-      <c r="H132" s="65"/>
+      <c r="F132" s="87"/>
+      <c r="G132" s="88"/>
+      <c r="H132" s="89"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="63"/>
-      <c r="K132" s="64"/>
-      <c r="L132" s="65"/>
+      <c r="J132" s="87"/>
+      <c r="K132" s="88"/>
+      <c r="L132" s="89"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="66"/>
-      <c r="C133" s="67"/>
-      <c r="D133" s="68"/>
+      <c r="B133" s="97"/>
+      <c r="C133" s="98"/>
+      <c r="D133" s="99"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="66"/>
-      <c r="G133" s="67"/>
-      <c r="H133" s="68"/>
+      <c r="F133" s="97"/>
+      <c r="G133" s="98"/>
+      <c r="H133" s="99"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="66"/>
-      <c r="K133" s="67"/>
-      <c r="L133" s="68"/>
+      <c r="J133" s="97"/>
+      <c r="K133" s="98"/>
+      <c r="L133" s="99"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
-  <mergeCells count="887">
+  <mergeCells count="888">
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="Z95:AA95"/>
+    <mergeCell ref="Z94:AA94"/>
+    <mergeCell ref="Z96:AA96"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD95:AE95"/>
+    <mergeCell ref="AH95:AI95"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AD94:AE94"/>
+    <mergeCell ref="AH94:AI94"/>
+    <mergeCell ref="AH96:AI96"/>
+    <mergeCell ref="AD96:AE96"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="R86:T86"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="V86:X86"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="N86:P86"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J24:K24"/>
     <mergeCell ref="B100:D100"/>
     <mergeCell ref="F100:H100"/>
     <mergeCell ref="Z87:AA87"/>
@@ -8201,875 +9077,12 @@
     <mergeCell ref="AD98:AE98"/>
     <mergeCell ref="V93:X93"/>
     <mergeCell ref="J93:L93"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="N86:P86"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="R86:T86"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD95:AE95"/>
-    <mergeCell ref="AH95:AI95"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AD94:AE94"/>
-    <mergeCell ref="AH94:AI94"/>
-    <mergeCell ref="AH96:AI96"/>
-    <mergeCell ref="AD96:AE96"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="Z95:AA95"/>
-    <mergeCell ref="Z94:AA94"/>
-    <mergeCell ref="Z96:AA96"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AJ88:AJ96 AJ22:AJ27 AF22:AF27 AB22:AB27 T22:T27 AF88:AF96 AB88:AB96 AN22:AN27 H22:H27 D22:D27 L22:L27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="Z55:AB57 AH14:AJ16 AH83:AJ84 V95:X96 J41:L43 AL22:AM27 AD88:AE96 J132:L133 Z83:AB84 N22:O27 V83:X84 AL62:AN64 AL83:AN84 AH77:AJ78 AD71:AF72 AD41:AF43 V48:X50 AH41:AJ43 AL101:AN102 V77:X78 V8:X10 Z62:AB64 AL48:AN50 J114:L115 AD8:AF10 AL89:AN90 AD83:AF84 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 AH48:AJ50 R14:T16 AH55:AJ57 AL14:AN16 N71:P72 Z77:AB78 V41:X43 AH34:AJ36 V62:X64 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X36 Z101:AB102 V55:X57 Z41:AB43 R77:T78 AD22:AE27 V14:X16 AH88:AI96 F108:H109 N77:P78 R22:S27 N55:P57 Z48:AB50 AL55:AN57 AH62:AJ64 N62:P64 R41:T43 AL71:AN72 R83:T90 AH22:AI27 R55:T57 N48:P50 N41:P43 Z88:AA96 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 R71:T72 R95:T96 AD77:AF78 N101:P102 AD34:AF36 V89:X90 AL34:AN36 Z71:AB72 N83:P90 AD48:AF50 V22:W27 N95:P96 AD62:AF64 AH71:AJ72 AH101:AJ102 Z34:AB36 AL77:AN78 Z22:AA27 Z8:AB10 AL41:AN43 AL8:AN10 R62:T64 N8:P10 AD55:AF57 R101:T102 AL95:AN96 V101:X102 F14:H16 J101:L102 B71:D72 J62:L64 B83:D84 J71:L72 B41:D43 F41:H43 J22:K27 B8:D10 J89:L90 F83:H84 F48:H50 F55:H57 J14:L16 F95:H96 B77:D78 J77:L78 B14:D16 F101:H102 B89:D90 F22:G27 J34:L36 J55:L57 F62:H64 F89:H90 B22:C27 F34:H36 F8:H10 F77:H78 B95:D102 B34:D36 J83:L84 B48:D50 F71:H72 J95:L96 J48:L50 J8:L10 B55:D57 B62:D64 V71:X72">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="Z55:AB57 AH14:AJ16 AH83:AJ84 V95:X96 J41:L43 AL22:AM27 AD88:AE96 J132:L133 Z83:AB84 N22:O27 B62:D64 AL62:AN64 AL83:AN84 AH77:AJ78 AD71:AF72 AD41:AF43 V48:X50 AH41:AJ43 AL101:AN102 V77:X78 V8:X10 Z62:AB64 AL48:AN50 J114:L115 AD8:AF10 AL89:AN90 AD83:AF84 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 AH48:AJ50 R14:T16 AH55:AJ57 AL14:AN16 N71:P72 Z77:AB78 V41:X43 AH34:AJ36 V62:X64 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X36 Z101:AB102 V55:X57 Z41:AB43 R77:T78 AD22:AE27 V14:X16 AH88:AI96 F108:H109 N77:P78 R22:S27 N55:P57 Z48:AB50 AL55:AN57 AH62:AJ64 N62:P64 R41:T43 AL71:AN72 R83:T90 AH22:AI27 R55:T57 N48:P50 N41:P43 Z88:AA96 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 R71:T72 R95:T96 AD77:AF78 N101:P102 AD34:AF36 V71:X72 AL34:AN36 Z71:AB72 N83:P90 AD48:AF50 V22:W27 N95:P96 AD62:AF64 AH71:AJ72 AH101:AJ102 Z34:AB36 AL77:AN78 Z22:AA27 Z8:AB10 AL41:AN43 AL8:AN10 R62:T64 N8:P10 AD55:AF57 R101:T102 AL95:AN96 V101:X102 F14:H16 J101:L102 B71:D72 J62:L64 B83:D84 J71:L72 B41:D43 F41:H43 J22:K27 B8:D10 J89:L90 F83:H84 F48:H50 F55:H57 J14:L16 F95:H96 B77:D78 J77:L78 B14:D16 F101:H102 B89:D90 F22:G27 J34:L36 J55:L57 F62:H64 F89:H90 B22:C27 F34:H36 F8:H10 F77:H78 B95:D102 B34:D36 J83:L84 B48:D50 F71:H72 J95:L96 J48:L50 J8:L10 B55:D57 V83:X90">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="91">
   <si>
     <t>CUMA</t>
   </si>
@@ -1569,6 +1569,24 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1578,15 +1596,6 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1596,18 +1605,18 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1648,15 +1657,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2103,7 +2103,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="180" row="3" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="181" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2379,23 +2379,23 @@
       <c r="K4" s="118"/>
       <c r="L4" s="118"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="105" t="s">
+      <c r="N4" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="105"/>
-      <c r="R4" s="105"/>
-      <c r="S4" s="105"/>
-      <c r="T4" s="105"/>
-      <c r="U4" s="105"/>
-      <c r="V4" s="105"/>
-      <c r="W4" s="105"/>
-      <c r="X4" s="105"/>
-      <c r="Y4" s="105"/>
-      <c r="Z4" s="105"/>
-      <c r="AA4" s="105"/>
-      <c r="AB4" s="105"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
+      <c r="X4" s="108"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="108"/>
+      <c r="AA4" s="108"/>
+      <c r="AB4" s="108"/>
       <c r="AC4" s="33"/>
       <c r="AD4" s="118"/>
       <c r="AE4" s="118"/>
@@ -2427,21 +2427,21 @@
       <c r="K5" s="118"/>
       <c r="L5" s="118"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="105"/>
-      <c r="S5" s="105"/>
-      <c r="T5" s="105"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105"/>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
-      <c r="AA5" s="105"/>
-      <c r="AB5" s="105"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="108"/>
       <c r="AC5" s="33"/>
       <c r="AD5" s="118"/>
       <c r="AE5" s="118"/>
@@ -2562,47 +2562,47 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="84"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="84"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="90"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="84"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="90"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="84"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="89"/>
+      <c r="P8" s="90"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="82"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="84"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="89"/>
+      <c r="T8" s="90"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="82"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="84"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="89"/>
+      <c r="X8" s="90"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="82"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="84"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="89"/>
+      <c r="AB8" s="90"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="83"/>
-      <c r="AF8" s="84"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="89"/>
+      <c r="AF8" s="90"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="82"/>
-      <c r="AI8" s="83"/>
-      <c r="AJ8" s="84"/>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="89"/>
+      <c r="AJ8" s="90"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="82"/>
-      <c r="AM8" s="83"/>
-      <c r="AN8" s="84"/>
+      <c r="AL8" s="88"/>
+      <c r="AM8" s="89"/>
+      <c r="AN8" s="90"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2613,45 +2613,45 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="93"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="87"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="93"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="87"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="93"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="87"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="93"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="87"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="91"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="93"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="87"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="91"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="93"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="87"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="92"/>
-      <c r="AB9" s="93"/>
+      <c r="Z9" s="85"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="87"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="92"/>
-      <c r="AF9" s="93"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="87"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="91"/>
-      <c r="AI9" s="92"/>
-      <c r="AJ9" s="93"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
+      <c r="AJ9" s="87"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="91"/>
-      <c r="AM9" s="92"/>
-      <c r="AN9" s="93"/>
+      <c r="AL9" s="85"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="87"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2662,45 +2662,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="100"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="102"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="102"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="105"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="101"/>
-      <c r="L10" s="102"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="105"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="100"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="102"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="105"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="100"/>
-      <c r="S10" s="101"/>
-      <c r="T10" s="102"/>
+      <c r="R10" s="103"/>
+      <c r="S10" s="104"/>
+      <c r="T10" s="105"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="100"/>
-      <c r="W10" s="101"/>
-      <c r="X10" s="102"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="104"/>
+      <c r="X10" s="105"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="100"/>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="102"/>
+      <c r="Z10" s="103"/>
+      <c r="AA10" s="104"/>
+      <c r="AB10" s="105"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="100"/>
-      <c r="AE10" s="101"/>
-      <c r="AF10" s="102"/>
+      <c r="AD10" s="103"/>
+      <c r="AE10" s="104"/>
+      <c r="AF10" s="105"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="100"/>
-      <c r="AI10" s="101"/>
-      <c r="AJ10" s="102"/>
+      <c r="AH10" s="103"/>
+      <c r="AI10" s="104"/>
+      <c r="AJ10" s="105"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="100"/>
-      <c r="AM10" s="101"/>
-      <c r="AN10" s="102"/>
+      <c r="AL10" s="103"/>
+      <c r="AM10" s="104"/>
+      <c r="AN10" s="105"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2813,13 +2813,13 @@
       <c r="C13" s="69"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="90"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="93"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="90"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="93"/>
       <c r="M13" s="5"/>
       <c r="N13" s="76"/>
       <c r="O13" s="77"/>
@@ -2858,45 +2858,45 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="82"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="84"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="90"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="84"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="90"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="84"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="84"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="89"/>
+      <c r="P14" s="90"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="82"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="84"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="90"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="82"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="84"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="89"/>
+      <c r="X14" s="90"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="82"/>
-      <c r="AA14" s="83"/>
-      <c r="AB14" s="84"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="89"/>
+      <c r="AB14" s="90"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="82"/>
-      <c r="AE14" s="83"/>
-      <c r="AF14" s="84"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="89"/>
+      <c r="AF14" s="90"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="82"/>
-      <c r="AI14" s="83"/>
-      <c r="AJ14" s="84"/>
+      <c r="AH14" s="88"/>
+      <c r="AI14" s="89"/>
+      <c r="AJ14" s="90"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="82"/>
-      <c r="AM14" s="83"/>
-      <c r="AN14" s="84"/>
+      <c r="AL14" s="88"/>
+      <c r="AM14" s="89"/>
+      <c r="AN14" s="90"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2907,45 +2907,45 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="91"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="93"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="93"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="87"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="93"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="87"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="92"/>
-      <c r="P15" s="93"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="87"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="92"/>
-      <c r="T15" s="93"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="86"/>
+      <c r="T15" s="87"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="91"/>
-      <c r="W15" s="92"/>
-      <c r="X15" s="93"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="86"/>
+      <c r="X15" s="87"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="91"/>
-      <c r="AA15" s="92"/>
-      <c r="AB15" s="93"/>
+      <c r="Z15" s="85"/>
+      <c r="AA15" s="86"/>
+      <c r="AB15" s="87"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="91"/>
-      <c r="AE15" s="92"/>
-      <c r="AF15" s="93"/>
+      <c r="AD15" s="85"/>
+      <c r="AE15" s="86"/>
+      <c r="AF15" s="87"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="91"/>
-      <c r="AI15" s="92"/>
-      <c r="AJ15" s="93"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="86"/>
+      <c r="AJ15" s="87"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="91"/>
-      <c r="AM15" s="92"/>
-      <c r="AN15" s="93"/>
+      <c r="AL15" s="85"/>
+      <c r="AM15" s="86"/>
+      <c r="AN15" s="87"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2956,45 +2956,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="100"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="105"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="105"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="101"/>
-      <c r="L16" s="102"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="105"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="100"/>
-      <c r="O16" s="101"/>
-      <c r="P16" s="102"/>
+      <c r="N16" s="103"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="105"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="100"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="102"/>
+      <c r="R16" s="103"/>
+      <c r="S16" s="104"/>
+      <c r="T16" s="105"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="100"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="102"/>
+      <c r="V16" s="103"/>
+      <c r="W16" s="104"/>
+      <c r="X16" s="105"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="100"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="102"/>
+      <c r="Z16" s="103"/>
+      <c r="AA16" s="104"/>
+      <c r="AB16" s="105"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="100"/>
-      <c r="AE16" s="101"/>
-      <c r="AF16" s="102"/>
+      <c r="AD16" s="103"/>
+      <c r="AE16" s="104"/>
+      <c r="AF16" s="105"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="100"/>
-      <c r="AI16" s="101"/>
-      <c r="AJ16" s="102"/>
+      <c r="AH16" s="103"/>
+      <c r="AI16" s="104"/>
+      <c r="AJ16" s="105"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="100"/>
-      <c r="AM16" s="101"/>
-      <c r="AN16" s="102"/>
+      <c r="AL16" s="103"/>
+      <c r="AM16" s="104"/>
+      <c r="AN16" s="105"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3066,23 +3066,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="105" t="s">
+      <c r="N18" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="105"/>
-      <c r="R18" s="105"/>
-      <c r="S18" s="105"/>
-      <c r="T18" s="105"/>
-      <c r="U18" s="105"/>
-      <c r="V18" s="105"/>
-      <c r="W18" s="105"/>
-      <c r="X18" s="105"/>
-      <c r="Y18" s="105"/>
-      <c r="Z18" s="105"/>
-      <c r="AA18" s="105"/>
-      <c r="AB18" s="105"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+      <c r="R18" s="108"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+      <c r="U18" s="108"/>
+      <c r="V18" s="108"/>
+      <c r="W18" s="108"/>
+      <c r="X18" s="108"/>
+      <c r="Y18" s="108"/>
+      <c r="Z18" s="108"/>
+      <c r="AA18" s="108"/>
+      <c r="AB18" s="108"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3117,21 +3117,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="105"/>
-      <c r="R19" s="105"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="105"/>
-      <c r="U19" s="105"/>
-      <c r="V19" s="105"/>
-      <c r="W19" s="105"/>
-      <c r="X19" s="105"/>
-      <c r="Y19" s="105"/>
-      <c r="Z19" s="105"/>
-      <c r="AA19" s="105"/>
-      <c r="AB19" s="105"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+      <c r="U19" s="108"/>
+      <c r="V19" s="108"/>
+      <c r="W19" s="108"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="108"/>
+      <c r="Z19" s="108"/>
+      <c r="AA19" s="108"/>
+      <c r="AB19" s="108"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3186,26 +3186,26 @@
         <v>47</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="103" t="s">
+      <c r="R20" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="S20" s="104"/>
+      <c r="S20" s="107"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="103" t="s">
+      <c r="V20" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="W20" s="104"/>
+      <c r="W20" s="107"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="103" t="s">
+      <c r="Z20" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="AA20" s="104"/>
+      <c r="AA20" s="107"/>
       <c r="AB20" s="56" t="s">
         <v>43</v>
       </c>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AQ22" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR22" s="30"/>
     </row>
@@ -3803,23 +3803,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="105" t="s">
+      <c r="N29" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="105"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="105"/>
-      <c r="R29" s="105"/>
-      <c r="S29" s="105"/>
-      <c r="T29" s="105"/>
-      <c r="U29" s="105"/>
-      <c r="V29" s="105"/>
-      <c r="W29" s="105"/>
-      <c r="X29" s="105"/>
-      <c r="Y29" s="105"/>
-      <c r="Z29" s="105"/>
-      <c r="AA29" s="105"/>
-      <c r="AB29" s="105"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="108"/>
+      <c r="U29" s="108"/>
+      <c r="V29" s="108"/>
+      <c r="W29" s="108"/>
+      <c r="X29" s="108"/>
+      <c r="Y29" s="108"/>
+      <c r="Z29" s="108"/>
+      <c r="AA29" s="108"/>
+      <c r="AB29" s="108"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3854,21 +3854,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="105"/>
-      <c r="O30" s="105"/>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="105"/>
-      <c r="R30" s="105"/>
-      <c r="S30" s="105"/>
-      <c r="T30" s="105"/>
-      <c r="U30" s="105"/>
-      <c r="V30" s="105"/>
-      <c r="W30" s="105"/>
-      <c r="X30" s="105"/>
-      <c r="Y30" s="105"/>
-      <c r="Z30" s="105"/>
-      <c r="AA30" s="105"/>
-      <c r="AB30" s="105"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="108"/>
+      <c r="U30" s="108"/>
+      <c r="V30" s="108"/>
+      <c r="W30" s="108"/>
+      <c r="X30" s="108"/>
+      <c r="Y30" s="108"/>
+      <c r="Z30" s="108"/>
+      <c r="AA30" s="108"/>
+      <c r="AB30" s="108"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AQ30" s="47">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR30" s="30"/>
     </row>
@@ -3953,23 +3953,23 @@
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="89"/>
-      <c r="D32" s="90"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="93"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="88" t="s">
+      <c r="F32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="89"/>
-      <c r="H32" s="90"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="93"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="88" t="s">
+      <c r="J32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="89"/>
-      <c r="L32" s="90"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="93"/>
       <c r="M32" s="5"/>
       <c r="N32" s="76" t="s">
         <v>70</v>
@@ -4068,63 +4068,63 @@
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="93"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="87"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="91" t="s">
+      <c r="F34" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="92"/>
-      <c r="H34" s="93"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="87"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="91" t="s">
+      <c r="J34" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="87"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="82" t="s">
+      <c r="N34" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="83"/>
-      <c r="P34" s="84"/>
+      <c r="O34" s="89"/>
+      <c r="P34" s="90"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="84"/>
+      <c r="R34" s="88"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="90"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="82" t="s">
+      <c r="V34" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="83"/>
-      <c r="X34" s="84"/>
+      <c r="W34" s="89"/>
+      <c r="X34" s="90"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="82" t="s">
+      <c r="Z34" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="83"/>
-      <c r="AB34" s="84"/>
+      <c r="AA34" s="89"/>
+      <c r="AB34" s="90"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="82" t="s">
+      <c r="AD34" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="AE34" s="83"/>
-      <c r="AF34" s="84"/>
+      <c r="AE34" s="89"/>
+      <c r="AF34" s="90"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="82" t="s">
+      <c r="AH34" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="AI34" s="83"/>
-      <c r="AJ34" s="84"/>
+      <c r="AI34" s="89"/>
+      <c r="AJ34" s="90"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="82" t="s">
+      <c r="AL34" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="AM34" s="83"/>
-      <c r="AN34" s="84"/>
+      <c r="AM34" s="89"/>
+      <c r="AN34" s="90"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -4132,90 +4132,90 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
-      <c r="B35" s="91" t="s">
+      <c r="B35" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="93"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="87"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="91" t="s">
+      <c r="F35" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="92"/>
-      <c r="H35" s="93"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="87"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="91" t="s">
+      <c r="J35" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="92"/>
-      <c r="L35" s="93"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="87"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="91" t="s">
+      <c r="N35" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="O35" s="92"/>
-      <c r="P35" s="93"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="87"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="91"/>
-      <c r="S35" s="92"/>
-      <c r="T35" s="93"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="86"/>
+      <c r="T35" s="87"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="85" t="s">
+      <c r="V35" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="86"/>
-      <c r="X35" s="87"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="84"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="85" t="s">
+      <c r="Z35" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="86"/>
-      <c r="AB35" s="87"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="84"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="85" t="s">
+      <c r="AD35" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="86"/>
-      <c r="AF35" s="87"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="84"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="85" t="s">
+      <c r="AH35" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="AI35" s="86"/>
-      <c r="AJ35" s="87"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="84"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="85" t="s">
+      <c r="AL35" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="AM35" s="86"/>
-      <c r="AN35" s="87"/>
+      <c r="AM35" s="83"/>
+      <c r="AN35" s="84"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="87"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="84"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="87"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="84"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="87"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="84"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="85" t="s">
+      <c r="N36" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="O36" s="86"/>
-      <c r="P36" s="87"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="84"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="85"/>
-      <c r="S36" s="86"/>
-      <c r="T36" s="87"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="83"/>
+      <c r="T36" s="84"/>
       <c r="U36" s="40"/>
       <c r="V36" s="35"/>
       <c r="W36" s="35"/>
@@ -4303,10 +4303,10 @@
       <c r="C38" s="67"/>
       <c r="D38" s="60"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="98" t="s">
+      <c r="F38" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="99"/>
+      <c r="G38" s="102"/>
       <c r="H38" s="55" t="s">
         <v>52</v>
       </c>
@@ -4363,21 +4363,21 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="88"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="90"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="93"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="88" t="s">
+      <c r="F39" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="89"/>
-      <c r="H39" s="90"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="88" t="s">
+      <c r="J39" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="K39" s="89"/>
-      <c r="L39" s="90"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="93"/>
       <c r="M39" s="5"/>
       <c r="N39" s="129" t="s">
         <v>66</v>
@@ -4437,45 +4437,45 @@
       <c r="K40" s="69"/>
       <c r="L40" s="94"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="106" t="s">
+      <c r="N40" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="O40" s="107"/>
-      <c r="P40" s="108"/>
+      <c r="O40" s="110"/>
+      <c r="P40" s="111"/>
       <c r="Q40" s="37"/>
       <c r="R40" s="79"/>
       <c r="S40" s="80"/>
       <c r="T40" s="81"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="82" t="s">
+      <c r="V40" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="83"/>
-      <c r="X40" s="84"/>
+      <c r="W40" s="89"/>
+      <c r="X40" s="90"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="82" t="s">
+      <c r="Z40" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="83"/>
-      <c r="AB40" s="84"/>
+      <c r="AA40" s="89"/>
+      <c r="AB40" s="90"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="82" t="s">
+      <c r="AD40" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="AE40" s="83"/>
-      <c r="AF40" s="84"/>
+      <c r="AE40" s="89"/>
+      <c r="AF40" s="90"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="82" t="s">
+      <c r="AH40" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="AI40" s="83"/>
-      <c r="AJ40" s="84"/>
+      <c r="AI40" s="89"/>
+      <c r="AJ40" s="90"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="82" t="s">
+      <c r="AL40" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="AM40" s="83"/>
-      <c r="AN40" s="84"/>
+      <c r="AM40" s="89"/>
+      <c r="AN40" s="90"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4483,61 +4483,61 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="93"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="87"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="82" t="s">
+      <c r="F41" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="83"/>
-      <c r="H41" s="84"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="90"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="109" t="s">
+      <c r="J41" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="K41" s="110"/>
-      <c r="L41" s="111"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="97"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="82" t="s">
+      <c r="N41" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="O41" s="83"/>
-      <c r="P41" s="84"/>
+      <c r="O41" s="89"/>
+      <c r="P41" s="90"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="82"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="84"/>
+      <c r="R41" s="88"/>
+      <c r="S41" s="89"/>
+      <c r="T41" s="90"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="85" t="s">
+      <c r="V41" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="86"/>
-      <c r="X41" s="87"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="84"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="85" t="s">
+      <c r="Z41" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="86"/>
-      <c r="AB41" s="87"/>
+      <c r="AA41" s="83"/>
+      <c r="AB41" s="84"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="85" t="s">
+      <c r="AD41" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="AE41" s="86"/>
-      <c r="AF41" s="87"/>
+      <c r="AE41" s="83"/>
+      <c r="AF41" s="84"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="85" t="s">
+      <c r="AH41" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="AI41" s="86"/>
-      <c r="AJ41" s="87"/>
+      <c r="AI41" s="83"/>
+      <c r="AJ41" s="84"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="85" t="s">
+      <c r="AL41" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="AM41" s="86"/>
-      <c r="AN41" s="87"/>
+      <c r="AM41" s="83"/>
+      <c r="AN41" s="84"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4545,31 +4545,31 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="93"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="87"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="91" t="s">
+      <c r="F42" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="92"/>
-      <c r="H42" s="93"/>
+      <c r="G42" s="86"/>
+      <c r="H42" s="87"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="91" t="s">
+      <c r="J42" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="92"/>
-      <c r="L42" s="93"/>
+      <c r="K42" s="86"/>
+      <c r="L42" s="87"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="91" t="s">
+      <c r="N42" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="O42" s="92"/>
-      <c r="P42" s="93"/>
+      <c r="O42" s="86"/>
+      <c r="P42" s="87"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="91"/>
-      <c r="S42" s="92"/>
-      <c r="T42" s="93"/>
+      <c r="R42" s="85"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="87"/>
       <c r="U42" s="44"/>
       <c r="V42" s="35"/>
       <c r="W42" s="35"/>
@@ -4597,27 +4597,27 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="87"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="84"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="87"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="84"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="95" t="s">
+      <c r="J43" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="K43" s="96"/>
-      <c r="L43" s="97"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="100"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="87"/>
+      <c r="N43" s="82"/>
+      <c r="O43" s="83"/>
+      <c r="P43" s="84"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="86"/>
-      <c r="T43" s="87"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
+      <c r="T43" s="84"/>
       <c r="U43" s="50"/>
       <c r="V43" s="74" t="s">
         <v>71</v>
@@ -4719,10 +4719,10 @@
       <c r="G45" s="67"/>
       <c r="H45" s="60"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="98" t="s">
+      <c r="J45" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="K45" s="99"/>
+      <c r="K45" s="102"/>
       <c r="L45" s="55"/>
       <c r="M45" s="14"/>
       <c r="N45" s="74"/>
@@ -4769,19 +4769,19 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="88"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="90"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="93"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="92"/>
+      <c r="H46" s="93"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="88" t="s">
+      <c r="J46" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="90"/>
+      <c r="K46" s="92"/>
+      <c r="L46" s="93"/>
       <c r="M46" s="4"/>
       <c r="N46" s="76"/>
       <c r="O46" s="77"/>
@@ -4791,35 +4791,35 @@
       <c r="S46" s="77"/>
       <c r="T46" s="78"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="91" t="s">
+      <c r="V46" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="92"/>
-      <c r="X46" s="93"/>
+      <c r="W46" s="86"/>
+      <c r="X46" s="87"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="91" t="s">
+      <c r="Z46" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="92"/>
-      <c r="AB46" s="93"/>
+      <c r="AA46" s="86"/>
+      <c r="AB46" s="87"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="91" t="s">
+      <c r="AD46" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="AE46" s="92"/>
-      <c r="AF46" s="93"/>
+      <c r="AE46" s="86"/>
+      <c r="AF46" s="87"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="91" t="s">
+      <c r="AH46" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="AI46" s="92"/>
-      <c r="AJ46" s="93"/>
+      <c r="AI46" s="86"/>
+      <c r="AJ46" s="87"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="91" t="s">
+      <c r="AL46" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="AM46" s="92"/>
-      <c r="AN46" s="93"/>
+      <c r="AM46" s="86"/>
+      <c r="AN46" s="87"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4849,35 +4849,35 @@
       <c r="S47" s="80"/>
       <c r="T47" s="81"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="91" t="s">
+      <c r="V47" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="92"/>
-      <c r="X47" s="93"/>
+      <c r="W47" s="86"/>
+      <c r="X47" s="87"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="91" t="s">
+      <c r="Z47" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="92"/>
-      <c r="AB47" s="93"/>
+      <c r="AA47" s="86"/>
+      <c r="AB47" s="87"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="91" t="s">
+      <c r="AD47" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="AE47" s="92"/>
-      <c r="AF47" s="93"/>
+      <c r="AE47" s="86"/>
+      <c r="AF47" s="87"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="91" t="s">
+      <c r="AH47" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="AI47" s="92"/>
-      <c r="AJ47" s="93"/>
+      <c r="AI47" s="86"/>
+      <c r="AJ47" s="87"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="91" t="s">
+      <c r="AL47" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="AM47" s="92"/>
-      <c r="AN47" s="93"/>
+      <c r="AM47" s="86"/>
+      <c r="AN47" s="87"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4885,139 +4885,139 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="84"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="90"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="91"/>
-      <c r="G48" s="92"/>
-      <c r="H48" s="93"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="87"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="91" t="s">
+      <c r="J48" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="92"/>
-      <c r="L48" s="93"/>
+      <c r="K48" s="86"/>
+      <c r="L48" s="87"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="91"/>
-      <c r="O48" s="92"/>
-      <c r="P48" s="93"/>
+      <c r="N48" s="85"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="87"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="91"/>
-      <c r="S48" s="92"/>
-      <c r="T48" s="93"/>
+      <c r="R48" s="85"/>
+      <c r="S48" s="86"/>
+      <c r="T48" s="87"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="91" t="s">
+      <c r="V48" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="92"/>
-      <c r="X48" s="93"/>
+      <c r="W48" s="86"/>
+      <c r="X48" s="87"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="91" t="s">
+      <c r="Z48" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="92"/>
-      <c r="AB48" s="93"/>
+      <c r="AA48" s="86"/>
+      <c r="AB48" s="87"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="91" t="s">
+      <c r="AD48" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="AE48" s="92"/>
-      <c r="AF48" s="93"/>
+      <c r="AE48" s="86"/>
+      <c r="AF48" s="87"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="91" t="s">
+      <c r="AH48" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="AI48" s="92"/>
-      <c r="AJ48" s="93"/>
+      <c r="AI48" s="86"/>
+      <c r="AJ48" s="87"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="91" t="s">
+      <c r="AL48" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="AM48" s="92"/>
-      <c r="AN48" s="93"/>
+      <c r="AM48" s="86"/>
+      <c r="AN48" s="87"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="91"/>
-      <c r="C49" s="92"/>
-      <c r="D49" s="93"/>
+      <c r="B49" s="85"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="87"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="91"/>
-      <c r="G49" s="92"/>
-      <c r="H49" s="93"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="87"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="91" t="s">
+      <c r="J49" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="K49" s="92"/>
-      <c r="L49" s="93"/>
+      <c r="K49" s="86"/>
+      <c r="L49" s="87"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="92"/>
-      <c r="P49" s="93"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="87"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="91"/>
-      <c r="S49" s="92"/>
-      <c r="T49" s="93"/>
+      <c r="R49" s="85"/>
+      <c r="S49" s="86"/>
+      <c r="T49" s="87"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="85" t="s">
+      <c r="V49" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="86"/>
-      <c r="X49" s="87"/>
+      <c r="W49" s="83"/>
+      <c r="X49" s="84"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="85" t="s">
+      <c r="Z49" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="86"/>
-      <c r="AB49" s="87"/>
+      <c r="AA49" s="83"/>
+      <c r="AB49" s="84"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="85" t="s">
+      <c r="AD49" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AE49" s="86"/>
-      <c r="AF49" s="87"/>
+      <c r="AE49" s="83"/>
+      <c r="AF49" s="84"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="85" t="s">
+      <c r="AH49" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AI49" s="86"/>
-      <c r="AJ49" s="87"/>
+      <c r="AI49" s="83"/>
+      <c r="AJ49" s="84"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="85" t="s">
+      <c r="AL49" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="86"/>
-      <c r="AN49" s="87"/>
+      <c r="AM49" s="83"/>
+      <c r="AN49" s="84"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="85"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="87"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="87"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="84"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="87"/>
+      <c r="J50" s="82"/>
+      <c r="K50" s="83"/>
+      <c r="L50" s="84"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="87"/>
+      <c r="N50" s="82"/>
+      <c r="O50" s="83"/>
+      <c r="P50" s="84"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="85"/>
-      <c r="S50" s="86"/>
-      <c r="T50" s="87"/>
+      <c r="R50" s="82"/>
+      <c r="S50" s="83"/>
+      <c r="T50" s="84"/>
       <c r="U50" s="35"/>
       <c r="V50" s="35"/>
       <c r="W50" s="35"/>
@@ -5103,12 +5103,12 @@
       <c r="G52" s="67"/>
       <c r="H52" s="60"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="98" t="s">
+      <c r="J52" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="K52" s="99"/>
+      <c r="K52" s="102"/>
       <c r="L52" s="55" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M52" s="14"/>
       <c r="N52" s="74"/>
@@ -5147,19 +5147,19 @@
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="88"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="90"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="93"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="88"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="90"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="92"/>
+      <c r="H53" s="93"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="88" t="s">
+      <c r="J53" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="89"/>
-      <c r="L53" s="90"/>
+      <c r="K53" s="92"/>
+      <c r="L53" s="93"/>
       <c r="M53" s="4"/>
       <c r="N53" s="76"/>
       <c r="O53" s="77"/>
@@ -5217,153 +5217,153 @@
       <c r="S54" s="80"/>
       <c r="T54" s="81"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="82"/>
-      <c r="W54" s="83"/>
-      <c r="X54" s="84"/>
+      <c r="V54" s="88"/>
+      <c r="W54" s="89"/>
+      <c r="X54" s="90"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="82"/>
-      <c r="AA54" s="83"/>
-      <c r="AB54" s="84"/>
+      <c r="Z54" s="88"/>
+      <c r="AA54" s="89"/>
+      <c r="AB54" s="90"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="82" t="s">
+      <c r="AD54" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="AE54" s="83"/>
-      <c r="AF54" s="84"/>
+      <c r="AE54" s="89"/>
+      <c r="AF54" s="90"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="82" t="s">
+      <c r="AH54" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="AI54" s="83"/>
-      <c r="AJ54" s="84"/>
+      <c r="AI54" s="89"/>
+      <c r="AJ54" s="90"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="82" t="s">
+      <c r="AL54" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="AM54" s="83"/>
-      <c r="AN54" s="84"/>
+      <c r="AM54" s="89"/>
+      <c r="AN54" s="90"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="82"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="84"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="90"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="84"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="90"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="91" t="s">
+      <c r="J55" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="92"/>
-      <c r="L55" s="93"/>
+      <c r="K55" s="86"/>
+      <c r="L55" s="87"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="84"/>
+      <c r="N55" s="88"/>
+      <c r="O55" s="89"/>
+      <c r="P55" s="90"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="83"/>
-      <c r="T55" s="84"/>
+      <c r="R55" s="88"/>
+      <c r="S55" s="89"/>
+      <c r="T55" s="90"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="91"/>
-      <c r="W55" s="92"/>
-      <c r="X55" s="93"/>
+      <c r="V55" s="85"/>
+      <c r="W55" s="86"/>
+      <c r="X55" s="87"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="91"/>
-      <c r="AA55" s="92"/>
-      <c r="AB55" s="93"/>
+      <c r="Z55" s="85"/>
+      <c r="AA55" s="86"/>
+      <c r="AB55" s="87"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="91" t="s">
+      <c r="AD55" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="AE55" s="92"/>
-      <c r="AF55" s="93"/>
+      <c r="AE55" s="86"/>
+      <c r="AF55" s="87"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="91" t="s">
+      <c r="AH55" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="92"/>
-      <c r="AJ55" s="93"/>
+      <c r="AI55" s="86"/>
+      <c r="AJ55" s="87"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="91" t="s">
+      <c r="AL55" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="AM55" s="92"/>
-      <c r="AN55" s="93"/>
+      <c r="AM55" s="86"/>
+      <c r="AN55" s="87"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="91"/>
-      <c r="C56" s="92"/>
-      <c r="D56" s="93"/>
+      <c r="B56" s="85"/>
+      <c r="C56" s="86"/>
+      <c r="D56" s="87"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="91"/>
-      <c r="G56" s="92"/>
-      <c r="H56" s="93"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="86"/>
+      <c r="H56" s="87"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="91" t="s">
+      <c r="J56" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="K56" s="92"/>
-      <c r="L56" s="93"/>
+      <c r="K56" s="86"/>
+      <c r="L56" s="87"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="91"/>
-      <c r="O56" s="92"/>
-      <c r="P56" s="93"/>
+      <c r="N56" s="85"/>
+      <c r="O56" s="86"/>
+      <c r="P56" s="87"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="91"/>
-      <c r="S56" s="92"/>
-      <c r="T56" s="93"/>
+      <c r="R56" s="85"/>
+      <c r="S56" s="86"/>
+      <c r="T56" s="87"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="85"/>
-      <c r="W56" s="86"/>
-      <c r="X56" s="87"/>
+      <c r="V56" s="82"/>
+      <c r="W56" s="83"/>
+      <c r="X56" s="84"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="85"/>
-      <c r="AA56" s="86"/>
-      <c r="AB56" s="87"/>
+      <c r="Z56" s="82"/>
+      <c r="AA56" s="83"/>
+      <c r="AB56" s="84"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="85" t="s">
+      <c r="AD56" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="AE56" s="86"/>
-      <c r="AF56" s="87"/>
+      <c r="AE56" s="83"/>
+      <c r="AF56" s="84"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="85" t="s">
+      <c r="AH56" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="AI56" s="86"/>
-      <c r="AJ56" s="87"/>
+      <c r="AI56" s="83"/>
+      <c r="AJ56" s="84"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="85" t="s">
+      <c r="AL56" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="AM56" s="86"/>
-      <c r="AN56" s="87"/>
+      <c r="AM56" s="83"/>
+      <c r="AN56" s="84"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="85"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="87"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="84"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="87"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="84"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="87"/>
+      <c r="J57" s="82"/>
+      <c r="K57" s="83"/>
+      <c r="L57" s="84"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="87"/>
+      <c r="N57" s="82"/>
+      <c r="O57" s="83"/>
+      <c r="P57" s="84"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="85"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="87"/>
+      <c r="R57" s="82"/>
+      <c r="S57" s="83"/>
+      <c r="T57" s="84"/>
       <c r="U57" s="50"/>
       <c r="V57" s="35"/>
       <c r="W57" s="35"/>
@@ -5477,17 +5477,17 @@
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="88"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="90"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="93"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="90"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="92"/>
+      <c r="H60" s="93"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="88"/>
-      <c r="K60" s="89"/>
-      <c r="L60" s="90"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="92"/>
+      <c r="L60" s="93"/>
       <c r="M60" s="4"/>
       <c r="N60" s="76"/>
       <c r="O60" s="77"/>
@@ -5543,157 +5543,157 @@
       <c r="S61" s="80"/>
       <c r="T61" s="81"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="82"/>
-      <c r="W61" s="83"/>
-      <c r="X61" s="84"/>
+      <c r="V61" s="88"/>
+      <c r="W61" s="89"/>
+      <c r="X61" s="90"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="82"/>
-      <c r="AA61" s="83"/>
-      <c r="AB61" s="84"/>
+      <c r="Z61" s="88"/>
+      <c r="AA61" s="89"/>
+      <c r="AB61" s="90"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="82"/>
-      <c r="AE61" s="83"/>
-      <c r="AF61" s="84"/>
+      <c r="AD61" s="88"/>
+      <c r="AE61" s="89"/>
+      <c r="AF61" s="90"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="82"/>
-      <c r="AI61" s="83"/>
-      <c r="AJ61" s="84"/>
+      <c r="AH61" s="88"/>
+      <c r="AI61" s="89"/>
+      <c r="AJ61" s="90"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="82" t="s">
+      <c r="AL61" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="AM61" s="83"/>
-      <c r="AN61" s="84"/>
+      <c r="AM61" s="89"/>
+      <c r="AN61" s="90"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="82"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="84"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="90"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="82"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="84"/>
+      <c r="F62" s="88"/>
+      <c r="G62" s="89"/>
+      <c r="H62" s="90"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="82"/>
-      <c r="K62" s="83"/>
-      <c r="L62" s="84"/>
+      <c r="J62" s="88"/>
+      <c r="K62" s="89"/>
+      <c r="L62" s="90"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="91"/>
-      <c r="O62" s="92"/>
-      <c r="P62" s="93"/>
+      <c r="N62" s="85"/>
+      <c r="O62" s="86"/>
+      <c r="P62" s="87"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="91" t="s">
+      <c r="R62" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="S62" s="92"/>
-      <c r="T62" s="93"/>
+      <c r="S62" s="86"/>
+      <c r="T62" s="87"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="91"/>
-      <c r="W62" s="92"/>
-      <c r="X62" s="93"/>
+      <c r="V62" s="85"/>
+      <c r="W62" s="86"/>
+      <c r="X62" s="87"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="91"/>
-      <c r="AA62" s="92"/>
-      <c r="AB62" s="93"/>
+      <c r="Z62" s="85"/>
+      <c r="AA62" s="86"/>
+      <c r="AB62" s="87"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="91"/>
-      <c r="AE62" s="92"/>
-      <c r="AF62" s="93"/>
+      <c r="AD62" s="85"/>
+      <c r="AE62" s="86"/>
+      <c r="AF62" s="87"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="91"/>
-      <c r="AI62" s="92"/>
-      <c r="AJ62" s="93"/>
+      <c r="AH62" s="85"/>
+      <c r="AI62" s="86"/>
+      <c r="AJ62" s="87"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="91" t="s">
+      <c r="AL62" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="AM62" s="92"/>
-      <c r="AN62" s="93"/>
+      <c r="AM62" s="86"/>
+      <c r="AN62" s="87"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="91"/>
-      <c r="C63" s="92"/>
-      <c r="D63" s="93"/>
+      <c r="B63" s="85"/>
+      <c r="C63" s="86"/>
+      <c r="D63" s="87"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="91"/>
-      <c r="G63" s="92"/>
-      <c r="H63" s="93"/>
+      <c r="F63" s="85"/>
+      <c r="G63" s="86"/>
+      <c r="H63" s="87"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="91"/>
-      <c r="K63" s="92"/>
-      <c r="L63" s="93"/>
+      <c r="J63" s="85"/>
+      <c r="K63" s="86"/>
+      <c r="L63" s="87"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="91"/>
-      <c r="O63" s="92"/>
-      <c r="P63" s="93"/>
+      <c r="N63" s="85"/>
+      <c r="O63" s="86"/>
+      <c r="P63" s="87"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="91"/>
-      <c r="S63" s="92"/>
-      <c r="T63" s="93"/>
+      <c r="R63" s="85"/>
+      <c r="S63" s="86"/>
+      <c r="T63" s="87"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="91"/>
-      <c r="W63" s="92"/>
-      <c r="X63" s="93"/>
+      <c r="V63" s="85"/>
+      <c r="W63" s="86"/>
+      <c r="X63" s="87"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="91"/>
-      <c r="AA63" s="92"/>
-      <c r="AB63" s="93"/>
+      <c r="Z63" s="85"/>
+      <c r="AA63" s="86"/>
+      <c r="AB63" s="87"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="91"/>
-      <c r="AE63" s="92"/>
-      <c r="AF63" s="93"/>
+      <c r="AD63" s="85"/>
+      <c r="AE63" s="86"/>
+      <c r="AF63" s="87"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="91"/>
-      <c r="AI63" s="92"/>
-      <c r="AJ63" s="93"/>
+      <c r="AH63" s="85"/>
+      <c r="AI63" s="86"/>
+      <c r="AJ63" s="87"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="91"/>
-      <c r="AM63" s="92"/>
-      <c r="AN63" s="93"/>
+      <c r="AL63" s="85"/>
+      <c r="AM63" s="86"/>
+      <c r="AN63" s="87"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="85"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="87"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="83"/>
+      <c r="D64" s="84"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="86"/>
-      <c r="H64" s="87"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="83"/>
+      <c r="H64" s="84"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="86"/>
-      <c r="L64" s="87"/>
+      <c r="J64" s="82"/>
+      <c r="K64" s="83"/>
+      <c r="L64" s="84"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="85"/>
-      <c r="O64" s="86"/>
-      <c r="P64" s="87"/>
+      <c r="N64" s="82"/>
+      <c r="O64" s="83"/>
+      <c r="P64" s="84"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="85"/>
-      <c r="S64" s="86"/>
-      <c r="T64" s="87"/>
+      <c r="R64" s="82"/>
+      <c r="S64" s="83"/>
+      <c r="T64" s="84"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="85"/>
-      <c r="W64" s="86"/>
-      <c r="X64" s="87"/>
+      <c r="V64" s="82"/>
+      <c r="W64" s="83"/>
+      <c r="X64" s="84"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="85"/>
-      <c r="AA64" s="86"/>
-      <c r="AB64" s="87"/>
+      <c r="Z64" s="82"/>
+      <c r="AA64" s="83"/>
+      <c r="AB64" s="84"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="85"/>
-      <c r="AE64" s="86"/>
-      <c r="AF64" s="87"/>
+      <c r="AD64" s="82"/>
+      <c r="AE64" s="83"/>
+      <c r="AF64" s="84"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="85"/>
-      <c r="AI64" s="86"/>
-      <c r="AJ64" s="87"/>
+      <c r="AH64" s="82"/>
+      <c r="AI64" s="83"/>
+      <c r="AJ64" s="84"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="85"/>
-      <c r="AM64" s="86"/>
-      <c r="AN64" s="87"/>
+      <c r="AL64" s="82"/>
+      <c r="AM64" s="83"/>
+      <c r="AN64" s="84"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5756,23 +5756,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="105" t="s">
+      <c r="N66" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="105"/>
-      <c r="P66" s="105"/>
-      <c r="Q66" s="105"/>
-      <c r="R66" s="105"/>
-      <c r="S66" s="105"/>
-      <c r="T66" s="105"/>
-      <c r="U66" s="105"/>
-      <c r="V66" s="105"/>
-      <c r="W66" s="105"/>
-      <c r="X66" s="105"/>
-      <c r="Y66" s="105"/>
-      <c r="Z66" s="105"/>
-      <c r="AA66" s="105"/>
-      <c r="AB66" s="105"/>
+      <c r="O66" s="108"/>
+      <c r="P66" s="108"/>
+      <c r="Q66" s="108"/>
+      <c r="R66" s="108"/>
+      <c r="S66" s="108"/>
+      <c r="T66" s="108"/>
+      <c r="U66" s="108"/>
+      <c r="V66" s="108"/>
+      <c r="W66" s="108"/>
+      <c r="X66" s="108"/>
+      <c r="Y66" s="108"/>
+      <c r="Z66" s="108"/>
+      <c r="AA66" s="108"/>
+      <c r="AB66" s="108"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5803,21 +5803,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="105"/>
-      <c r="O67" s="105"/>
-      <c r="P67" s="105"/>
-      <c r="Q67" s="105"/>
-      <c r="R67" s="105"/>
-      <c r="S67" s="105"/>
-      <c r="T67" s="105"/>
-      <c r="U67" s="105"/>
-      <c r="V67" s="105"/>
-      <c r="W67" s="105"/>
-      <c r="X67" s="105"/>
-      <c r="Y67" s="105"/>
-      <c r="Z67" s="105"/>
-      <c r="AA67" s="105"/>
-      <c r="AB67" s="105"/>
+      <c r="N67" s="108"/>
+      <c r="O67" s="108"/>
+      <c r="P67" s="108"/>
+      <c r="Q67" s="108"/>
+      <c r="R67" s="108"/>
+      <c r="S67" s="108"/>
+      <c r="T67" s="108"/>
+      <c r="U67" s="108"/>
+      <c r="V67" s="108"/>
+      <c r="W67" s="108"/>
+      <c r="X67" s="108"/>
+      <c r="Y67" s="108"/>
+      <c r="Z67" s="108"/>
+      <c r="AA67" s="108"/>
+      <c r="AB67" s="108"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5897,23 +5897,23 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="88" t="s">
+      <c r="B69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="89"/>
-      <c r="D69" s="90"/>
+      <c r="C69" s="92"/>
+      <c r="D69" s="93"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="88" t="s">
+      <c r="F69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="G69" s="89"/>
-      <c r="H69" s="90"/>
+      <c r="G69" s="92"/>
+      <c r="H69" s="93"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="88" t="s">
+      <c r="J69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="K69" s="89"/>
-      <c r="L69" s="90"/>
+      <c r="K69" s="92"/>
+      <c r="L69" s="93"/>
       <c r="M69" s="4"/>
       <c r="N69" s="76" t="s">
         <v>60</v>
@@ -6017,57 +6017,57 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="82" t="s">
+      <c r="B71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="83"/>
-      <c r="D71" s="84"/>
+      <c r="C71" s="89"/>
+      <c r="D71" s="90"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="82" t="s">
+      <c r="F71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="83"/>
-      <c r="H71" s="84"/>
+      <c r="G71" s="89"/>
+      <c r="H71" s="90"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="82" t="s">
+      <c r="J71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="K71" s="83"/>
-      <c r="L71" s="84"/>
+      <c r="K71" s="89"/>
+      <c r="L71" s="90"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="82" t="s">
+      <c r="N71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="O71" s="83"/>
-      <c r="P71" s="84"/>
+      <c r="O71" s="89"/>
+      <c r="P71" s="90"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="82" t="s">
+      <c r="R71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="S71" s="83"/>
-      <c r="T71" s="84"/>
+      <c r="S71" s="89"/>
+      <c r="T71" s="90"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="82"/>
-      <c r="W71" s="83"/>
-      <c r="X71" s="84"/>
+      <c r="V71" s="88"/>
+      <c r="W71" s="89"/>
+      <c r="X71" s="90"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="82"/>
-      <c r="AA71" s="83"/>
-      <c r="AB71" s="84"/>
+      <c r="Z71" s="88"/>
+      <c r="AA71" s="89"/>
+      <c r="AB71" s="90"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="82"/>
-      <c r="AE71" s="83"/>
-      <c r="AF71" s="84"/>
+      <c r="AD71" s="88"/>
+      <c r="AE71" s="89"/>
+      <c r="AF71" s="90"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="82"/>
-      <c r="AI71" s="83"/>
-      <c r="AJ71" s="84"/>
+      <c r="AH71" s="88"/>
+      <c r="AI71" s="89"/>
+      <c r="AJ71" s="90"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="82" t="s">
+      <c r="AL71" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="AM71" s="83"/>
-      <c r="AN71" s="84"/>
+      <c r="AM71" s="89"/>
+      <c r="AN71" s="90"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6077,47 +6077,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="87"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="83"/>
+      <c r="D72" s="84"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="87"/>
+      <c r="F72" s="82"/>
+      <c r="G72" s="83"/>
+      <c r="H72" s="84"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="85"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="87"/>
+      <c r="J72" s="82"/>
+      <c r="K72" s="83"/>
+      <c r="L72" s="84"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="85"/>
-      <c r="O72" s="86"/>
-      <c r="P72" s="87"/>
+      <c r="N72" s="82"/>
+      <c r="O72" s="83"/>
+      <c r="P72" s="84"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="86"/>
-      <c r="T72" s="87"/>
+      <c r="R72" s="82"/>
+      <c r="S72" s="83"/>
+      <c r="T72" s="84"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="85"/>
-      <c r="W72" s="86"/>
-      <c r="X72" s="87"/>
+      <c r="V72" s="82"/>
+      <c r="W72" s="83"/>
+      <c r="X72" s="84"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="85"/>
-      <c r="AA72" s="86"/>
-      <c r="AB72" s="87"/>
+      <c r="Z72" s="82"/>
+      <c r="AA72" s="83"/>
+      <c r="AB72" s="84"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="85"/>
-      <c r="AE72" s="86"/>
-      <c r="AF72" s="87"/>
+      <c r="AD72" s="82"/>
+      <c r="AE72" s="83"/>
+      <c r="AF72" s="84"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="85"/>
-      <c r="AI72" s="86"/>
-      <c r="AJ72" s="87"/>
+      <c r="AH72" s="82"/>
+      <c r="AI72" s="83"/>
+      <c r="AJ72" s="84"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="85" t="s">
+      <c r="AL72" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="AM72" s="86"/>
-      <c r="AN72" s="87"/>
+      <c r="AM72" s="83"/>
+      <c r="AN72" s="84"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6231,21 +6231,21 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
-      <c r="B75" s="88" t="s">
+      <c r="B75" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="89"/>
-      <c r="D75" s="90"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="93"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="88" t="s">
+      <c r="F75" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="89"/>
-      <c r="H75" s="90"/>
+      <c r="G75" s="92"/>
+      <c r="H75" s="93"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="88"/>
-      <c r="K75" s="89"/>
-      <c r="L75" s="90"/>
+      <c r="J75" s="91"/>
+      <c r="K75" s="92"/>
+      <c r="L75" s="93"/>
       <c r="M75" s="14"/>
       <c r="N75" s="76"/>
       <c r="O75" s="77"/>
@@ -6341,59 +6341,59 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="82" t="s">
+      <c r="B77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="83"/>
-      <c r="D77" s="84"/>
+      <c r="C77" s="89"/>
+      <c r="D77" s="90"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="82" t="s">
+      <c r="F77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="83"/>
-      <c r="H77" s="84"/>
+      <c r="G77" s="89"/>
+      <c r="H77" s="90"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="83"/>
-      <c r="L77" s="84"/>
+      <c r="J77" s="88"/>
+      <c r="K77" s="89"/>
+      <c r="L77" s="90"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="O77" s="83"/>
-      <c r="P77" s="84"/>
+      <c r="N77" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="O77" s="96"/>
+      <c r="P77" s="97"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="82" t="s">
+      <c r="R77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="83"/>
-      <c r="T77" s="84"/>
+      <c r="S77" s="89"/>
+      <c r="T77" s="90"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="82"/>
-      <c r="W77" s="83"/>
-      <c r="X77" s="84"/>
+      <c r="V77" s="88"/>
+      <c r="W77" s="89"/>
+      <c r="X77" s="90"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="82" t="s">
+      <c r="Z77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="83"/>
-      <c r="AB77" s="84"/>
+      <c r="AA77" s="89"/>
+      <c r="AB77" s="90"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="82" t="s">
+      <c r="AD77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="83"/>
-      <c r="AF77" s="84"/>
+      <c r="AE77" s="89"/>
+      <c r="AF77" s="90"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="82" t="s">
+      <c r="AH77" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="83"/>
-      <c r="AJ77" s="84"/>
+      <c r="AI77" s="89"/>
+      <c r="AJ77" s="90"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="82"/>
-      <c r="AM77" s="83"/>
-      <c r="AN77" s="84"/>
+      <c r="AL77" s="88"/>
+      <c r="AM77" s="89"/>
+      <c r="AN77" s="90"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6401,45 +6401,47 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
-      <c r="B78" s="85"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="87"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="83"/>
+      <c r="D78" s="84"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="85"/>
-      <c r="G78" s="86"/>
-      <c r="H78" s="87"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="83"/>
+      <c r="H78" s="84"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="85"/>
-      <c r="K78" s="86"/>
-      <c r="L78" s="87"/>
+      <c r="J78" s="82"/>
+      <c r="K78" s="83"/>
+      <c r="L78" s="84"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="85"/>
-      <c r="O78" s="86"/>
-      <c r="P78" s="87"/>
+      <c r="N78" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="O78" s="99"/>
+      <c r="P78" s="100"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="85"/>
-      <c r="S78" s="86"/>
-      <c r="T78" s="87"/>
+      <c r="R78" s="82"/>
+      <c r="S78" s="83"/>
+      <c r="T78" s="84"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="85"/>
-      <c r="W78" s="86"/>
-      <c r="X78" s="87"/>
+      <c r="V78" s="82"/>
+      <c r="W78" s="83"/>
+      <c r="X78" s="84"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="85"/>
-      <c r="AA78" s="86"/>
-      <c r="AB78" s="87"/>
+      <c r="Z78" s="82"/>
+      <c r="AA78" s="83"/>
+      <c r="AB78" s="84"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="85"/>
-      <c r="AE78" s="86"/>
-      <c r="AF78" s="87"/>
+      <c r="AD78" s="82"/>
+      <c r="AE78" s="83"/>
+      <c r="AF78" s="84"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="85"/>
-      <c r="AI78" s="86"/>
-      <c r="AJ78" s="87"/>
+      <c r="AH78" s="82"/>
+      <c r="AI78" s="83"/>
+      <c r="AJ78" s="84"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="85"/>
-      <c r="AM78" s="86"/>
-      <c r="AN78" s="87"/>
+      <c r="AL78" s="82"/>
+      <c r="AM78" s="83"/>
+      <c r="AN78" s="84"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6551,17 +6553,17 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
-      <c r="B81" s="88"/>
-      <c r="C81" s="89"/>
-      <c r="D81" s="90"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="93"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="88"/>
-      <c r="G81" s="89"/>
-      <c r="H81" s="90"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="93"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="88"/>
-      <c r="K81" s="89"/>
-      <c r="L81" s="90"/>
+      <c r="J81" s="91"/>
+      <c r="K81" s="92"/>
+      <c r="L81" s="93"/>
       <c r="M81" s="5"/>
       <c r="N81" s="76"/>
       <c r="O81" s="77"/>
@@ -6655,57 +6657,57 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
-      <c r="B83" s="82"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="84"/>
+      <c r="B83" s="88"/>
+      <c r="C83" s="89"/>
+      <c r="D83" s="90"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="109" t="s">
+      <c r="F83" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="G83" s="110"/>
-      <c r="H83" s="111"/>
+      <c r="G83" s="96"/>
+      <c r="H83" s="97"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="82" t="s">
+      <c r="J83" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="83"/>
-      <c r="L83" s="84"/>
+      <c r="K83" s="89"/>
+      <c r="L83" s="90"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="82" t="s">
+      <c r="N83" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="O83" s="83"/>
-      <c r="P83" s="84"/>
+      <c r="O83" s="89"/>
+      <c r="P83" s="90"/>
       <c r="Q83" s="44"/>
-      <c r="R83" s="82" t="s">
+      <c r="R83" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="83"/>
-      <c r="T83" s="84"/>
+      <c r="S83" s="89"/>
+      <c r="T83" s="90"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="82"/>
-      <c r="W83" s="83"/>
-      <c r="X83" s="84"/>
+      <c r="V83" s="88"/>
+      <c r="W83" s="89"/>
+      <c r="X83" s="90"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="82" t="s">
+      <c r="Z83" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="83"/>
-      <c r="AB83" s="84"/>
+      <c r="AA83" s="89"/>
+      <c r="AB83" s="90"/>
       <c r="AC83" s="43"/>
-      <c r="AD83" s="82" t="s">
+      <c r="AD83" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="AE83" s="83"/>
-      <c r="AF83" s="84"/>
+      <c r="AE83" s="89"/>
+      <c r="AF83" s="90"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="82"/>
-      <c r="AI83" s="83"/>
-      <c r="AJ83" s="84"/>
+      <c r="AH83" s="88"/>
+      <c r="AI83" s="89"/>
+      <c r="AJ83" s="90"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="82"/>
-      <c r="AM83" s="83"/>
-      <c r="AN83" s="84"/>
+      <c r="AL83" s="88"/>
+      <c r="AM83" s="89"/>
+      <c r="AN83" s="90"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6713,49 +6715,49 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12"/>
-      <c r="B84" s="85"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="87"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="84"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="95" t="s">
+      <c r="F84" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="G84" s="96"/>
-      <c r="H84" s="97"/>
+      <c r="G84" s="99"/>
+      <c r="H84" s="100"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="95" t="s">
+      <c r="J84" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="96"/>
-      <c r="L84" s="97"/>
+      <c r="K84" s="99"/>
+      <c r="L84" s="100"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="85"/>
-      <c r="O84" s="86"/>
-      <c r="P84" s="87"/>
+      <c r="N84" s="82"/>
+      <c r="O84" s="83"/>
+      <c r="P84" s="84"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="85"/>
-      <c r="S84" s="86"/>
-      <c r="T84" s="87"/>
+      <c r="R84" s="82"/>
+      <c r="S84" s="83"/>
+      <c r="T84" s="84"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="85"/>
-      <c r="W84" s="86"/>
-      <c r="X84" s="87"/>
+      <c r="V84" s="82"/>
+      <c r="W84" s="83"/>
+      <c r="X84" s="84"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="85"/>
-      <c r="AA84" s="86"/>
-      <c r="AB84" s="87"/>
+      <c r="Z84" s="82"/>
+      <c r="AA84" s="83"/>
+      <c r="AB84" s="84"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="85"/>
-      <c r="AE84" s="86"/>
-      <c r="AF84" s="87"/>
+      <c r="AD84" s="82"/>
+      <c r="AE84" s="83"/>
+      <c r="AF84" s="84"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="85"/>
-      <c r="AI84" s="86"/>
-      <c r="AJ84" s="87"/>
+      <c r="AH84" s="82"/>
+      <c r="AI84" s="83"/>
+      <c r="AJ84" s="84"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="85"/>
-      <c r="AM84" s="86"/>
-      <c r="AN84" s="87"/>
+      <c r="AL84" s="82"/>
+      <c r="AM84" s="83"/>
+      <c r="AN84" s="84"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6875,9 +6877,9 @@
       <c r="G87" s="69"/>
       <c r="H87" s="61"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="88"/>
-      <c r="K87" s="89"/>
-      <c r="L87" s="90"/>
+      <c r="J87" s="91"/>
+      <c r="K87" s="92"/>
+      <c r="L87" s="93"/>
       <c r="M87" s="6"/>
       <c r="N87" s="76"/>
       <c r="O87" s="77"/>
@@ -6987,41 +6989,41 @@
         <v>33</v>
       </c>
       <c r="I89" s="31"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="83"/>
-      <c r="L89" s="84"/>
+      <c r="J89" s="88"/>
+      <c r="K89" s="89"/>
+      <c r="L89" s="90"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="82" t="s">
+      <c r="N89" s="95" t="s">
+        <v>14</v>
+      </c>
+      <c r="O89" s="96"/>
+      <c r="P89" s="97"/>
+      <c r="Q89" s="44"/>
+      <c r="R89" s="88"/>
+      <c r="S89" s="89"/>
+      <c r="T89" s="90"/>
+      <c r="U89" s="32"/>
+      <c r="V89" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="O89" s="83"/>
-      <c r="P89" s="84"/>
-      <c r="Q89" s="44"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="83"/>
-      <c r="T89" s="84"/>
-      <c r="U89" s="32"/>
-      <c r="V89" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="W89" s="83"/>
-      <c r="X89" s="84"/>
+      <c r="W89" s="89"/>
+      <c r="X89" s="90"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="82"/>
-      <c r="AA89" s="83"/>
-      <c r="AB89" s="84"/>
+      <c r="Z89" s="88"/>
+      <c r="AA89" s="89"/>
+      <c r="AB89" s="90"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="82"/>
-      <c r="AE89" s="83"/>
-      <c r="AF89" s="84"/>
+      <c r="AD89" s="88"/>
+      <c r="AE89" s="89"/>
+      <c r="AF89" s="90"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="82"/>
-      <c r="AI89" s="83"/>
-      <c r="AJ89" s="84"/>
+      <c r="AH89" s="88"/>
+      <c r="AI89" s="89"/>
+      <c r="AJ89" s="90"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="82"/>
-      <c r="AM89" s="83"/>
-      <c r="AN89" s="84"/>
+      <c r="AL89" s="88"/>
+      <c r="AM89" s="89"/>
+      <c r="AN89" s="90"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7045,37 +7047,39 @@
         <v>34</v>
       </c>
       <c r="I90" s="32"/>
-      <c r="J90" s="85"/>
-      <c r="K90" s="86"/>
-      <c r="L90" s="87"/>
+      <c r="J90" s="82"/>
+      <c r="K90" s="83"/>
+      <c r="L90" s="84"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="85"/>
-      <c r="O90" s="86"/>
-      <c r="P90" s="87"/>
+      <c r="N90" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="O90" s="99"/>
+      <c r="P90" s="100"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="85"/>
-      <c r="S90" s="86"/>
-      <c r="T90" s="87"/>
+      <c r="R90" s="82"/>
+      <c r="S90" s="83"/>
+      <c r="T90" s="84"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="85"/>
-      <c r="W90" s="86"/>
-      <c r="X90" s="87"/>
+      <c r="V90" s="82"/>
+      <c r="W90" s="83"/>
+      <c r="X90" s="84"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="85"/>
-      <c r="AA90" s="86"/>
-      <c r="AB90" s="87"/>
+      <c r="Z90" s="82"/>
+      <c r="AA90" s="83"/>
+      <c r="AB90" s="84"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="85"/>
-      <c r="AE90" s="86"/>
-      <c r="AF90" s="87"/>
+      <c r="AD90" s="82"/>
+      <c r="AE90" s="83"/>
+      <c r="AF90" s="84"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="85"/>
-      <c r="AI90" s="86"/>
-      <c r="AJ90" s="87"/>
+      <c r="AH90" s="82"/>
+      <c r="AI90" s="83"/>
+      <c r="AJ90" s="84"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="85"/>
-      <c r="AM90" s="86"/>
-      <c r="AN90" s="87"/>
+      <c r="AL90" s="82"/>
+      <c r="AM90" s="83"/>
+      <c r="AN90" s="84"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7199,9 +7203,9 @@
       <c r="G93" s="63"/>
       <c r="H93" s="45"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="88"/>
-      <c r="K93" s="89"/>
-      <c r="L93" s="90"/>
+      <c r="J93" s="91"/>
+      <c r="K93" s="92"/>
+      <c r="L93" s="93"/>
       <c r="M93" s="6"/>
       <c r="N93" s="76"/>
       <c r="O93" s="77"/>
@@ -7291,37 +7295,37 @@
       <c r="G95" s="63"/>
       <c r="H95" s="45"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="82"/>
-      <c r="K95" s="83"/>
-      <c r="L95" s="84"/>
+      <c r="J95" s="88"/>
+      <c r="K95" s="89"/>
+      <c r="L95" s="90"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="82"/>
-      <c r="O95" s="83"/>
-      <c r="P95" s="84"/>
+      <c r="N95" s="88"/>
+      <c r="O95" s="89"/>
+      <c r="P95" s="90"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="82"/>
-      <c r="S95" s="83"/>
-      <c r="T95" s="84"/>
+      <c r="R95" s="88"/>
+      <c r="S95" s="89"/>
+      <c r="T95" s="90"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="82"/>
-      <c r="W95" s="83"/>
-      <c r="X95" s="84"/>
+      <c r="V95" s="88"/>
+      <c r="W95" s="89"/>
+      <c r="X95" s="90"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="82"/>
-      <c r="AA95" s="83"/>
-      <c r="AB95" s="84"/>
+      <c r="Z95" s="88"/>
+      <c r="AA95" s="89"/>
+      <c r="AB95" s="90"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="82"/>
-      <c r="AE95" s="83"/>
-      <c r="AF95" s="84"/>
+      <c r="AD95" s="88"/>
+      <c r="AE95" s="89"/>
+      <c r="AF95" s="90"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="82"/>
-      <c r="AI95" s="83"/>
-      <c r="AJ95" s="84"/>
+      <c r="AH95" s="88"/>
+      <c r="AI95" s="89"/>
+      <c r="AJ95" s="90"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="82"/>
-      <c r="AM95" s="83"/>
-      <c r="AN95" s="84"/>
+      <c r="AL95" s="88"/>
+      <c r="AM95" s="89"/>
+      <c r="AN95" s="90"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7337,37 +7341,37 @@
       <c r="G96" s="65"/>
       <c r="H96" s="42"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="85"/>
-      <c r="K96" s="86"/>
-      <c r="L96" s="87"/>
+      <c r="J96" s="82"/>
+      <c r="K96" s="83"/>
+      <c r="L96" s="84"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="85"/>
-      <c r="O96" s="86"/>
-      <c r="P96" s="87"/>
+      <c r="N96" s="82"/>
+      <c r="O96" s="83"/>
+      <c r="P96" s="84"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="85"/>
-      <c r="S96" s="86"/>
-      <c r="T96" s="87"/>
+      <c r="R96" s="82"/>
+      <c r="S96" s="83"/>
+      <c r="T96" s="84"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="85"/>
-      <c r="W96" s="86"/>
-      <c r="X96" s="87"/>
+      <c r="V96" s="82"/>
+      <c r="W96" s="83"/>
+      <c r="X96" s="84"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="85"/>
-      <c r="AA96" s="86"/>
-      <c r="AB96" s="87"/>
+      <c r="Z96" s="82"/>
+      <c r="AA96" s="83"/>
+      <c r="AB96" s="84"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="85"/>
-      <c r="AE96" s="86"/>
-      <c r="AF96" s="87"/>
+      <c r="AD96" s="82"/>
+      <c r="AE96" s="83"/>
+      <c r="AF96" s="84"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="85"/>
-      <c r="AI96" s="86"/>
-      <c r="AJ96" s="87"/>
+      <c r="AH96" s="82"/>
+      <c r="AI96" s="83"/>
+      <c r="AJ96" s="84"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="85"/>
-      <c r="AM96" s="86"/>
-      <c r="AN96" s="87"/>
+      <c r="AL96" s="82"/>
+      <c r="AM96" s="83"/>
+      <c r="AN96" s="84"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7469,19 +7473,19 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
-      <c r="B99" s="88" t="s">
+      <c r="B99" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C99" s="89"/>
-      <c r="D99" s="90"/>
+      <c r="C99" s="92"/>
+      <c r="D99" s="93"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="88"/>
-      <c r="G99" s="89"/>
-      <c r="H99" s="90"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="92"/>
+      <c r="H99" s="93"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="88"/>
-      <c r="K99" s="89"/>
-      <c r="L99" s="90"/>
+      <c r="J99" s="91"/>
+      <c r="K99" s="92"/>
+      <c r="L99" s="93"/>
       <c r="M99" s="26"/>
       <c r="N99" s="76"/>
       <c r="O99" s="77"/>
@@ -7563,47 +7567,47 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
-      <c r="B101" s="82" t="s">
+      <c r="B101" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="83"/>
-      <c r="D101" s="84"/>
+      <c r="C101" s="89"/>
+      <c r="D101" s="90"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="82"/>
-      <c r="G101" s="83"/>
-      <c r="H101" s="84"/>
+      <c r="F101" s="88"/>
+      <c r="G101" s="89"/>
+      <c r="H101" s="90"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="82"/>
-      <c r="K101" s="83"/>
-      <c r="L101" s="84"/>
+      <c r="J101" s="88"/>
+      <c r="K101" s="89"/>
+      <c r="L101" s="90"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="82"/>
-      <c r="O101" s="83"/>
-      <c r="P101" s="84"/>
+      <c r="N101" s="88"/>
+      <c r="O101" s="89"/>
+      <c r="P101" s="90"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="82"/>
-      <c r="S101" s="83"/>
-      <c r="T101" s="84"/>
+      <c r="R101" s="88"/>
+      <c r="S101" s="89"/>
+      <c r="T101" s="90"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="82"/>
-      <c r="W101" s="83"/>
-      <c r="X101" s="84"/>
+      <c r="V101" s="88"/>
+      <c r="W101" s="89"/>
+      <c r="X101" s="90"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="82"/>
-      <c r="AA101" s="83"/>
-      <c r="AB101" s="84"/>
+      <c r="Z101" s="88"/>
+      <c r="AA101" s="89"/>
+      <c r="AB101" s="90"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="82"/>
-      <c r="AE101" s="83"/>
-      <c r="AF101" s="84"/>
+      <c r="AD101" s="88"/>
+      <c r="AE101" s="89"/>
+      <c r="AF101" s="90"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="82"/>
-      <c r="AI101" s="83"/>
-      <c r="AJ101" s="84"/>
+      <c r="AH101" s="88"/>
+      <c r="AI101" s="89"/>
+      <c r="AJ101" s="90"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="82"/>
-      <c r="AM101" s="83"/>
-      <c r="AN101" s="84"/>
+      <c r="AL101" s="88"/>
+      <c r="AM101" s="89"/>
+      <c r="AN101" s="90"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7611,45 +7615,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
-      <c r="B102" s="85"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="87"/>
+      <c r="B102" s="82"/>
+      <c r="C102" s="83"/>
+      <c r="D102" s="84"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="86"/>
-      <c r="H102" s="87"/>
+      <c r="F102" s="82"/>
+      <c r="G102" s="83"/>
+      <c r="H102" s="84"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="85"/>
-      <c r="K102" s="86"/>
-      <c r="L102" s="87"/>
+      <c r="J102" s="82"/>
+      <c r="K102" s="83"/>
+      <c r="L102" s="84"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="85"/>
-      <c r="O102" s="86"/>
-      <c r="P102" s="87"/>
+      <c r="N102" s="82"/>
+      <c r="O102" s="83"/>
+      <c r="P102" s="84"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="85"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="87"/>
+      <c r="R102" s="82"/>
+      <c r="S102" s="83"/>
+      <c r="T102" s="84"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="85"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="87"/>
+      <c r="V102" s="82"/>
+      <c r="W102" s="83"/>
+      <c r="X102" s="84"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="85"/>
-      <c r="AA102" s="86"/>
-      <c r="AB102" s="87"/>
+      <c r="Z102" s="82"/>
+      <c r="AA102" s="83"/>
+      <c r="AB102" s="84"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="85"/>
-      <c r="AE102" s="86"/>
-      <c r="AF102" s="87"/>
+      <c r="AD102" s="82"/>
+      <c r="AE102" s="83"/>
+      <c r="AF102" s="84"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="85"/>
-      <c r="AI102" s="86"/>
-      <c r="AJ102" s="87"/>
+      <c r="AH102" s="82"/>
+      <c r="AI102" s="83"/>
+      <c r="AJ102" s="84"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="85"/>
-      <c r="AM102" s="86"/>
-      <c r="AN102" s="87"/>
+      <c r="AL102" s="82"/>
+      <c r="AM102" s="83"/>
+      <c r="AN102" s="84"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7759,30 +7763,30 @@
       <c r="L107" s="81"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="82"/>
-      <c r="C108" s="83"/>
-      <c r="D108" s="84"/>
+      <c r="B108" s="88"/>
+      <c r="C108" s="89"/>
+      <c r="D108" s="90"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="83"/>
-      <c r="H108" s="84"/>
+      <c r="F108" s="88"/>
+      <c r="G108" s="89"/>
+      <c r="H108" s="90"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="82"/>
-      <c r="K108" s="83"/>
-      <c r="L108" s="84"/>
+      <c r="J108" s="88"/>
+      <c r="K108" s="89"/>
+      <c r="L108" s="90"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="85"/>
-      <c r="C109" s="86"/>
-      <c r="D109" s="87"/>
+      <c r="B109" s="82"/>
+      <c r="C109" s="83"/>
+      <c r="D109" s="84"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="85"/>
-      <c r="G109" s="86"/>
-      <c r="H109" s="87"/>
+      <c r="F109" s="82"/>
+      <c r="G109" s="83"/>
+      <c r="H109" s="84"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="85"/>
-      <c r="K109" s="86"/>
-      <c r="L109" s="87"/>
+      <c r="J109" s="82"/>
+      <c r="K109" s="83"/>
+      <c r="L109" s="84"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="35"/>
@@ -7837,30 +7841,30 @@
       <c r="L113" s="81"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="82"/>
-      <c r="C114" s="83"/>
-      <c r="D114" s="84"/>
+      <c r="B114" s="88"/>
+      <c r="C114" s="89"/>
+      <c r="D114" s="90"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="82"/>
-      <c r="G114" s="83"/>
-      <c r="H114" s="84"/>
+      <c r="F114" s="88"/>
+      <c r="G114" s="89"/>
+      <c r="H114" s="90"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="82"/>
-      <c r="K114" s="83"/>
-      <c r="L114" s="84"/>
+      <c r="J114" s="88"/>
+      <c r="K114" s="89"/>
+      <c r="L114" s="90"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="85"/>
-      <c r="C115" s="86"/>
-      <c r="D115" s="87"/>
+      <c r="B115" s="82"/>
+      <c r="C115" s="83"/>
+      <c r="D115" s="84"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="85"/>
-      <c r="G115" s="86"/>
-      <c r="H115" s="87"/>
+      <c r="F115" s="82"/>
+      <c r="G115" s="83"/>
+      <c r="H115" s="84"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="85"/>
-      <c r="K115" s="86"/>
-      <c r="L115" s="87"/>
+      <c r="J115" s="82"/>
+      <c r="K115" s="83"/>
+      <c r="L115" s="84"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="35"/>
@@ -7915,30 +7919,30 @@
       <c r="L119" s="81"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="82"/>
-      <c r="C120" s="83"/>
-      <c r="D120" s="84"/>
+      <c r="B120" s="88"/>
+      <c r="C120" s="89"/>
+      <c r="D120" s="90"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="82"/>
-      <c r="G120" s="83"/>
-      <c r="H120" s="84"/>
+      <c r="F120" s="88"/>
+      <c r="G120" s="89"/>
+      <c r="H120" s="90"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="82"/>
-      <c r="K120" s="83"/>
-      <c r="L120" s="84"/>
+      <c r="J120" s="88"/>
+      <c r="K120" s="89"/>
+      <c r="L120" s="90"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="85"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="87"/>
+      <c r="B121" s="82"/>
+      <c r="C121" s="83"/>
+      <c r="D121" s="84"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="85"/>
-      <c r="G121" s="86"/>
-      <c r="H121" s="87"/>
+      <c r="F121" s="82"/>
+      <c r="G121" s="83"/>
+      <c r="H121" s="84"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="85"/>
-      <c r="K121" s="86"/>
-      <c r="L121" s="87"/>
+      <c r="J121" s="82"/>
+      <c r="K121" s="83"/>
+      <c r="L121" s="84"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="35"/>
@@ -7993,30 +7997,30 @@
       <c r="L125" s="81"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="82"/>
-      <c r="C126" s="83"/>
-      <c r="D126" s="84"/>
+      <c r="B126" s="88"/>
+      <c r="C126" s="89"/>
+      <c r="D126" s="90"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="82"/>
-      <c r="G126" s="83"/>
-      <c r="H126" s="84"/>
+      <c r="F126" s="88"/>
+      <c r="G126" s="89"/>
+      <c r="H126" s="90"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="82"/>
-      <c r="K126" s="83"/>
-      <c r="L126" s="84"/>
+      <c r="J126" s="88"/>
+      <c r="K126" s="89"/>
+      <c r="L126" s="90"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="85"/>
-      <c r="C127" s="86"/>
-      <c r="D127" s="87"/>
+      <c r="B127" s="82"/>
+      <c r="C127" s="83"/>
+      <c r="D127" s="84"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="85"/>
-      <c r="G127" s="86"/>
-      <c r="H127" s="87"/>
+      <c r="F127" s="82"/>
+      <c r="G127" s="83"/>
+      <c r="H127" s="84"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="85"/>
-      <c r="K127" s="86"/>
-      <c r="L127" s="87"/>
+      <c r="J127" s="82"/>
+      <c r="K127" s="83"/>
+      <c r="L127" s="84"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="35"/>
@@ -8071,30 +8075,30 @@
       <c r="L131" s="81"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="82"/>
-      <c r="C132" s="83"/>
-      <c r="D132" s="84"/>
+      <c r="B132" s="88"/>
+      <c r="C132" s="89"/>
+      <c r="D132" s="90"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="82"/>
-      <c r="G132" s="83"/>
-      <c r="H132" s="84"/>
+      <c r="F132" s="88"/>
+      <c r="G132" s="89"/>
+      <c r="H132" s="90"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="82"/>
-      <c r="K132" s="83"/>
-      <c r="L132" s="84"/>
+      <c r="J132" s="88"/>
+      <c r="K132" s="89"/>
+      <c r="L132" s="90"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="85"/>
-      <c r="C133" s="86"/>
-      <c r="D133" s="87"/>
+      <c r="B133" s="82"/>
+      <c r="C133" s="83"/>
+      <c r="D133" s="84"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="85"/>
-      <c r="G133" s="86"/>
-      <c r="H133" s="87"/>
+      <c r="F133" s="82"/>
+      <c r="G133" s="83"/>
+      <c r="H133" s="84"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="85"/>
-      <c r="K133" s="86"/>
-      <c r="L133" s="87"/>
+      <c r="J133" s="82"/>
+      <c r="K133" s="83"/>
+      <c r="L133" s="84"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
@@ -8124,6 +8128,12 @@
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F21:G21"/>
@@ -8136,20 +8146,6 @@
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B23:C23"/>
@@ -8170,8 +8166,10 @@
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="N29:AB30"/>
     <mergeCell ref="N32:P32"/>
     <mergeCell ref="Z26:AA26"/>
@@ -8180,6 +8178,10 @@
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="V31:W31"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="AL13:AN13"/>
     <mergeCell ref="Z39:AB39"/>
     <mergeCell ref="AL31:AM31"/>
@@ -8204,8 +8206,6 @@
     <mergeCell ref="AH27:AI27"/>
     <mergeCell ref="AD26:AE26"/>
     <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
     <mergeCell ref="N34:P34"/>
     <mergeCell ref="AD33:AF33"/>
     <mergeCell ref="AH33:AJ33"/>
@@ -8219,15 +8219,7 @@
     <mergeCell ref="N38:O38"/>
     <mergeCell ref="R35:T35"/>
     <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="V33:X33"/>
     <mergeCell ref="R77:T77"/>
     <mergeCell ref="Z54:AB54"/>
     <mergeCell ref="V55:X55"/>
@@ -8242,17 +8234,9 @@
     <mergeCell ref="Z72:AB72"/>
     <mergeCell ref="Z71:AB71"/>
     <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
     <mergeCell ref="Z61:AB61"/>
     <mergeCell ref="R70:T70"/>
     <mergeCell ref="R64:T64"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="Z62:AB62"/>
     <mergeCell ref="V53:X53"/>
     <mergeCell ref="V61:X61"/>
     <mergeCell ref="N66:AB67"/>
@@ -8260,6 +8244,13 @@
     <mergeCell ref="R68:S68"/>
     <mergeCell ref="V56:X56"/>
     <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
     <mergeCell ref="Z49:AB49"/>
     <mergeCell ref="V49:X49"/>
     <mergeCell ref="N86:O86"/>
@@ -8269,6 +8260,21 @@
     <mergeCell ref="R93:T93"/>
     <mergeCell ref="N81:P81"/>
     <mergeCell ref="N83:P83"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
     <mergeCell ref="J87:L87"/>
     <mergeCell ref="Z83:AB83"/>
     <mergeCell ref="V84:X84"/>
@@ -8282,19 +8288,15 @@
     <mergeCell ref="N87:P87"/>
     <mergeCell ref="Z89:AB89"/>
     <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z93:AB93"/>
     <mergeCell ref="N88:P88"/>
     <mergeCell ref="V90:X90"/>
     <mergeCell ref="V87:X87"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
     <mergeCell ref="V88:X88"/>
     <mergeCell ref="V89:X89"/>
     <mergeCell ref="R90:T90"/>
     <mergeCell ref="R87:T87"/>
     <mergeCell ref="R89:T89"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="Z84:AB84"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="V60:X60"/>
     <mergeCell ref="R72:T72"/>
@@ -8313,6 +8315,11 @@
     <mergeCell ref="N61:P61"/>
     <mergeCell ref="N69:P69"/>
     <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
     <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="AD84:AF84"/>
     <mergeCell ref="AH84:AJ84"/>
@@ -8392,8 +8399,6 @@
     <mergeCell ref="AL55:AN55"/>
     <mergeCell ref="AL75:AN75"/>
     <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
     <mergeCell ref="AL64:AN64"/>
     <mergeCell ref="AL61:AN61"/>
     <mergeCell ref="AD64:AF64"/>
@@ -8402,6 +8407,8 @@
     <mergeCell ref="AD71:AF71"/>
     <mergeCell ref="AH68:AI68"/>
     <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
     <mergeCell ref="R14:T14"/>
     <mergeCell ref="AD76:AF76"/>
     <mergeCell ref="AH74:AI74"/>
@@ -8435,6 +8442,8 @@
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="N9:P9"/>
     <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="V1:X1"/>
     <mergeCell ref="V14:X14"/>
@@ -8501,7 +8510,9 @@
     <mergeCell ref="B86:C86"/>
     <mergeCell ref="F78:H78"/>
     <mergeCell ref="F77:H77"/>
-    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
     <mergeCell ref="AD27:AE27"/>
     <mergeCell ref="AH26:AI26"/>
     <mergeCell ref="AD21:AE21"/>
@@ -8516,10 +8527,16 @@
     <mergeCell ref="V32:X32"/>
     <mergeCell ref="Z32:AB32"/>
     <mergeCell ref="AD45:AF45"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AH37:AI37"/>
+    <mergeCell ref="AH38:AJ38"/>
+    <mergeCell ref="AH43:AI43"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AH45:AJ45"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="V24:W24"/>
     <mergeCell ref="F92:G92"/>
     <mergeCell ref="AH34:AJ34"/>
     <mergeCell ref="AH41:AJ41"/>
@@ -8542,6 +8559,8 @@
     <mergeCell ref="F84:H84"/>
     <mergeCell ref="F86:G86"/>
     <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD61:AF61"/>
     <mergeCell ref="AD49:AF49"/>
     <mergeCell ref="AH53:AJ53"/>
     <mergeCell ref="B21:C21"/>
@@ -8590,8 +8609,6 @@
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="R13:T13"/>
     <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="N10:P10"/>
@@ -8689,10 +8706,6 @@
     <mergeCell ref="J115:L115"/>
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="F112:H112"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
     <mergeCell ref="N96:P96"/>
     <mergeCell ref="R96:T96"/>
     <mergeCell ref="J99:L99"/>
@@ -8704,10 +8717,6 @@
     <mergeCell ref="N98:O98"/>
     <mergeCell ref="R98:S98"/>
     <mergeCell ref="V98:W98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="J94:L94"/>
     <mergeCell ref="J95:L95"/>
     <mergeCell ref="J102:L102"/>
     <mergeCell ref="Z99:AB99"/>
@@ -8729,10 +8738,9 @@
     <mergeCell ref="J90:L90"/>
     <mergeCell ref="V86:W86"/>
     <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
     <mergeCell ref="V54:X54"/>
     <mergeCell ref="J106:L106"/>
     <mergeCell ref="Z100:AB100"/>
@@ -8754,25 +8762,9 @@
     <mergeCell ref="J62:L62"/>
     <mergeCell ref="V77:X77"/>
     <mergeCell ref="R57:T57"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="J94:L94"/>
     <mergeCell ref="R42:T42"/>
     <mergeCell ref="R36:T36"/>
     <mergeCell ref="R38:S38"/>
@@ -8782,6 +8774,9 @@
     <mergeCell ref="R54:T54"/>
     <mergeCell ref="R49:T49"/>
     <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="R31:S31"/>
@@ -8830,9 +8825,6 @@
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="J49:L49"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V80:W80"/>
     <mergeCell ref="AH80:AI80"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="F72:H72"/>
@@ -8854,7 +8846,9 @@
     <mergeCell ref="N71:P71"/>
     <mergeCell ref="J76:L76"/>
     <mergeCell ref="N74:O74"/>
-    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="V75:X75"/>
     <mergeCell ref="AH60:AJ60"/>
     <mergeCell ref="AD53:AF53"/>
     <mergeCell ref="Z75:AB75"/>
@@ -8869,15 +8863,13 @@
     <mergeCell ref="Z68:AA68"/>
     <mergeCell ref="AH54:AJ54"/>
     <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
     <mergeCell ref="AH76:AJ76"/>
     <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="Z62:AB62"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F47:H47"/>
@@ -8893,6 +8885,15 @@
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
     <mergeCell ref="J77:L77"/>
     <mergeCell ref="J72:L72"/>
     <mergeCell ref="J74:K74"/>
@@ -8902,8 +8903,18 @@
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="F43:H43"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J75:L75"/>
     <mergeCell ref="Z94:AB94"/>
     <mergeCell ref="Z95:AB95"/>
     <mergeCell ref="Z96:AB96"/>
@@ -8915,13 +8926,6 @@
     <mergeCell ref="AD94:AF94"/>
     <mergeCell ref="AD95:AF95"/>
     <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="AH37:AI37"/>
-    <mergeCell ref="AH38:AJ38"/>
-    <mergeCell ref="AH43:AI43"/>
-    <mergeCell ref="AH44:AJ44"/>
-    <mergeCell ref="AH45:AJ45"/>
     <mergeCell ref="AH51:AI51"/>
     <mergeCell ref="AH52:AJ52"/>
     <mergeCell ref="AH58:AI58"/>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="94">
   <si>
     <t>CUMA</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>Ç.TAŞ.</t>
+  </si>
+  <si>
+    <t>TOPLANTI</t>
   </si>
 </sst>
 </file>
@@ -854,7 +857,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1293,6 +1296,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1356,7 +1370,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1515,6 +1529,42 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1530,6 +1580,42 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1539,86 +1625,143 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1626,133 +1769,7 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2204,65 +2221,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="116" t="s">
+      <c r="F1" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="116" t="s">
+      <c r="J1" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="116"/>
-      <c r="L1" s="117"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="127"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="120" t="s">
+      <c r="N1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="114" t="s">
+      <c r="R1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="114" t="s">
+      <c r="V1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="114" t="s">
+      <c r="Z1" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="114" t="s">
+      <c r="AD1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="114" t="s">
+      <c r="AH1" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="114"/>
-      <c r="AJ1" s="114"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="114" t="s">
+      <c r="AL1" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="114"/>
-      <c r="AN1" s="127"/>
+      <c r="AM1" s="120"/>
+      <c r="AN1" s="121"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2270,74 +2287,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="118">
+      <c r="B2" s="128">
         <f>N2-3</f>
         <v>46199</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="119">
+      <c r="F2" s="129">
         <f>N2-2</f>
         <v>46200</v>
       </c>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="119">
+      <c r="J2" s="129">
         <f>N2-1</f>
         <v>46201</v>
       </c>
-      <c r="K2" s="119"/>
-      <c r="L2" s="122"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="132"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="121">
+      <c r="N2" s="131">
         <v>46202</v>
       </c>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="113">
+      <c r="R2" s="122">
         <f>N2+1</f>
         <v>46203</v>
       </c>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="113">
+      <c r="V2" s="122">
         <f>N2+2</f>
         <v>46204</v>
       </c>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="113">
+      <c r="Z2" s="122">
         <f>N2+3</f>
         <v>46205</v>
       </c>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
+      <c r="AA2" s="122"/>
+      <c r="AB2" s="122"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="113">
+      <c r="AD2" s="122">
         <f>N2+4</f>
         <v>46206</v>
       </c>
-      <c r="AE2" s="113"/>
-      <c r="AF2" s="113"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="113">
+      <c r="AH2" s="122">
         <f>N2+5</f>
         <v>46207</v>
       </c>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="113"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="113">
+      <c r="AL2" s="122">
         <f>N2+6</f>
         <v>46208</v>
       </c>
-      <c r="AM2" s="113"/>
-      <c r="AN2" s="128"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="123"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2391,47 +2408,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="104" t="s">
+      <c r="N4" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="104"/>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="104"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="123"/>
-      <c r="AE4" s="123"/>
-      <c r="AF4" s="123"/>
-      <c r="AG4" s="123"/>
-      <c r="AH4" s="123"/>
-      <c r="AI4" s="123"/>
-      <c r="AJ4" s="123"/>
-      <c r="AK4" s="123"/>
-      <c r="AL4" s="123"/>
-      <c r="AM4" s="123"/>
-      <c r="AN4" s="123"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2439,93 +2456,93 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="104"/>
-      <c r="S5" s="104"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="104"/>
-      <c r="V5" s="104"/>
-      <c r="W5" s="104"/>
-      <c r="X5" s="104"/>
-      <c r="Y5" s="104"/>
-      <c r="Z5" s="104"/>
-      <c r="AA5" s="104"/>
-      <c r="AB5" s="104"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="114"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="114"/>
+      <c r="W5" s="114"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="123"/>
-      <c r="AE5" s="123"/>
-      <c r="AF5" s="123"/>
-      <c r="AG5" s="123"/>
-      <c r="AH5" s="123"/>
-      <c r="AI5" s="123"/>
-      <c r="AJ5" s="123"/>
-      <c r="AK5" s="123"/>
-      <c r="AL5" s="123"/>
-      <c r="AM5" s="123"/>
-      <c r="AN5" s="123"/>
+      <c r="AD5" s="124"/>
+      <c r="AE5" s="124"/>
+      <c r="AF5" s="124"/>
+      <c r="AG5" s="124"/>
+      <c r="AH5" s="124"/>
+      <c r="AI5" s="124"/>
+      <c r="AJ5" s="124"/>
+      <c r="AK5" s="124"/>
+      <c r="AL5" s="124"/>
+      <c r="AM5" s="124"/>
+      <c r="AN5" s="124"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="93" t="s">
+      <c r="B6" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="94"/>
+      <c r="C6" s="67"/>
       <c r="D6" s="60" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="39"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="94"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="67"/>
       <c r="H6" s="60"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="94"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="67"/>
       <c r="L6" s="60"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="63"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="75"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="63"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="75"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="63"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="75"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
+      <c r="Z6" s="74"/>
+      <c r="AA6" s="75"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="63"/>
+      <c r="AD6" s="74"/>
+      <c r="AE6" s="75"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="63"/>
+      <c r="AH6" s="74"/>
+      <c r="AI6" s="75"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="63"/>
+      <c r="AL6" s="74"/>
+      <c r="AM6" s="75"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2537,44 +2554,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="87"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="87"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="78"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="80"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="78"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="80"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="78"/>
+      <c r="V7" s="79"/>
+      <c r="W7" s="80"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="77"/>
-      <c r="AA7" s="78"/>
+      <c r="Z7" s="79"/>
+      <c r="AA7" s="80"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="77"/>
-      <c r="AE7" s="78"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="80"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="77"/>
-      <c r="AI7" s="78"/>
+      <c r="AH7" s="79"/>
+      <c r="AI7" s="80"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="77"/>
-      <c r="AM7" s="78"/>
+      <c r="AL7" s="79"/>
+      <c r="AM7" s="80"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2586,47 +2603,47 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="82"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="84"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="84"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="82"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="84"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="80"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="84"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="84"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="80"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="84"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="80"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="84"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="81"/>
-      <c r="AJ8" s="82"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="83"/>
+      <c r="AJ8" s="84"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="80"/>
-      <c r="AM8" s="81"/>
-      <c r="AN8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="83"/>
+      <c r="AN8" s="84"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2637,45 +2654,45 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="83"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="85"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="85"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="90"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="85"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="85"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="90"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="85"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="90"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="84"/>
-      <c r="X9" s="85"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="89"/>
+      <c r="X9" s="90"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="85"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="89"/>
+      <c r="AB9" s="90"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="83"/>
-      <c r="AE9" s="84"/>
-      <c r="AF9" s="85"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="90"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="83"/>
-      <c r="AI9" s="84"/>
-      <c r="AJ9" s="85"/>
+      <c r="AH9" s="88"/>
+      <c r="AI9" s="89"/>
+      <c r="AJ9" s="90"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="83"/>
-      <c r="AM9" s="84"/>
-      <c r="AN9" s="85"/>
+      <c r="AL9" s="88"/>
+      <c r="AM9" s="89"/>
+      <c r="AN9" s="90"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2686,45 +2703,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="124"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="126"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="126"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="111"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="125"/>
-      <c r="L10" s="126"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="111"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="125"/>
-      <c r="P10" s="126"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="125"/>
-      <c r="T10" s="126"/>
+      <c r="R10" s="109"/>
+      <c r="S10" s="110"/>
+      <c r="T10" s="111"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="125"/>
-      <c r="X10" s="126"/>
+      <c r="V10" s="109"/>
+      <c r="W10" s="110"/>
+      <c r="X10" s="111"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="124"/>
-      <c r="AA10" s="125"/>
-      <c r="AB10" s="126"/>
+      <c r="Z10" s="109"/>
+      <c r="AA10" s="110"/>
+      <c r="AB10" s="111"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="124"/>
-      <c r="AE10" s="125"/>
-      <c r="AF10" s="126"/>
+      <c r="AD10" s="109"/>
+      <c r="AE10" s="110"/>
+      <c r="AF10" s="111"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="125"/>
-      <c r="AJ10" s="126"/>
+      <c r="AH10" s="109"/>
+      <c r="AI10" s="110"/>
+      <c r="AJ10" s="111"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="124"/>
-      <c r="AM10" s="125"/>
-      <c r="AN10" s="126"/>
+      <c r="AL10" s="109"/>
+      <c r="AM10" s="110"/>
+      <c r="AN10" s="111"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2784,44 +2801,44 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="93"/>
-      <c r="C12" s="94"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
       <c r="D12" s="60"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="94"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="60"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="94"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="67"/>
       <c r="L12" s="60"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="63"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="75"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="62"/>
-      <c r="S12" s="63"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="75"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="62"/>
-      <c r="W12" s="63"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="75"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="63"/>
+      <c r="Z12" s="74"/>
+      <c r="AA12" s="75"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="62"/>
-      <c r="AE12" s="63"/>
+      <c r="AD12" s="74"/>
+      <c r="AE12" s="75"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="63"/>
+      <c r="AH12" s="74"/>
+      <c r="AI12" s="75"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="62"/>
-      <c r="AM12" s="63"/>
+      <c r="AL12" s="74"/>
+      <c r="AM12" s="75"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2833,45 +2850,45 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="69"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="93"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="69"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="93"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="66"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="77"/>
+      <c r="P13" s="78"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="66"/>
+      <c r="R13" s="76"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="78"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="64"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="66"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="77"/>
+      <c r="X13" s="78"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="78"/>
+      <c r="Z13" s="79"/>
+      <c r="AA13" s="80"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="77"/>
-      <c r="AE13" s="78"/>
+      <c r="AD13" s="79"/>
+      <c r="AE13" s="80"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="64"/>
-      <c r="AI13" s="65"/>
-      <c r="AJ13" s="66"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
+      <c r="AJ13" s="78"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="64"/>
-      <c r="AM13" s="65"/>
-      <c r="AN13" s="66"/>
+      <c r="AL13" s="76"/>
+      <c r="AM13" s="77"/>
+      <c r="AN13" s="78"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2882,45 +2899,45 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="80"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="82"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="84"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="82"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="84"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="80"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="84"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="80"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="84"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="80"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="84"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="80"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="83"/>
+      <c r="AF14" s="84"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="80"/>
-      <c r="AI14" s="81"/>
-      <c r="AJ14" s="82"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="84"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="80"/>
-      <c r="AM14" s="81"/>
-      <c r="AN14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="83"/>
+      <c r="AN14" s="84"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2931,94 +2948,94 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="83"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="85"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="90"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="85"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="85"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="90"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="85"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="90"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="83"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="85"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="90"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="83"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="85"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="89"/>
+      <c r="X15" s="90"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="83"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="85"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="89"/>
+      <c r="AB15" s="90"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="83"/>
-      <c r="AE15" s="84"/>
-      <c r="AF15" s="85"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="90"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="83"/>
-      <c r="AI15" s="84"/>
-      <c r="AJ15" s="85"/>
+      <c r="AH15" s="88"/>
+      <c r="AI15" s="89"/>
+      <c r="AJ15" s="90"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="83"/>
-      <c r="AM15" s="84"/>
-      <c r="AN15" s="85"/>
+      <c r="AL15" s="88"/>
+      <c r="AM15" s="89"/>
+      <c r="AN15" s="90"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="124"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="126"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="126"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="111"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="125"/>
-      <c r="L16" s="126"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="111"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="125"/>
-      <c r="P16" s="126"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="111"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="125"/>
-      <c r="T16" s="126"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="110"/>
+      <c r="T16" s="111"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="124"/>
-      <c r="W16" s="125"/>
-      <c r="X16" s="126"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="110"/>
+      <c r="X16" s="111"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="124"/>
-      <c r="AA16" s="125"/>
-      <c r="AB16" s="126"/>
+      <c r="Z16" s="109"/>
+      <c r="AA16" s="110"/>
+      <c r="AB16" s="111"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="124"/>
-      <c r="AE16" s="125"/>
-      <c r="AF16" s="126"/>
+      <c r="AD16" s="109"/>
+      <c r="AE16" s="110"/>
+      <c r="AF16" s="111"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="125"/>
-      <c r="AJ16" s="126"/>
+      <c r="AH16" s="109"/>
+      <c r="AI16" s="110"/>
+      <c r="AJ16" s="111"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="124"/>
-      <c r="AM16" s="125"/>
-      <c r="AN16" s="126"/>
+      <c r="AL16" s="109"/>
+      <c r="AM16" s="110"/>
+      <c r="AN16" s="111"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3090,23 +3107,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="104" t="s">
+      <c r="N18" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="104"/>
-      <c r="R18" s="104"/>
-      <c r="S18" s="104"/>
-      <c r="T18" s="104"/>
-      <c r="U18" s="104"/>
-      <c r="V18" s="104"/>
-      <c r="W18" s="104"/>
-      <c r="X18" s="104"/>
-      <c r="Y18" s="104"/>
-      <c r="Z18" s="104"/>
-      <c r="AA18" s="104"/>
-      <c r="AB18" s="104"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="114"/>
+      <c r="Y18" s="114"/>
+      <c r="Z18" s="114"/>
+      <c r="AA18" s="114"/>
+      <c r="AB18" s="114"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3141,21 +3158,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="104"/>
-      <c r="Q19" s="104"/>
-      <c r="R19" s="104"/>
-      <c r="S19" s="104"/>
-      <c r="T19" s="104"/>
-      <c r="U19" s="104"/>
-      <c r="V19" s="104"/>
-      <c r="W19" s="104"/>
-      <c r="X19" s="104"/>
-      <c r="Y19" s="104"/>
-      <c r="Z19" s="104"/>
-      <c r="AA19" s="104"/>
-      <c r="AB19" s="104"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="114"/>
+      <c r="Y19" s="114"/>
+      <c r="Z19" s="114"/>
+      <c r="AA19" s="114"/>
+      <c r="AB19" s="114"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3178,74 +3195,74 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="94"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="60" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="36"/>
-      <c r="F20" s="93" t="s">
+      <c r="F20" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="94"/>
+      <c r="G20" s="67"/>
       <c r="H20" s="60" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="93" t="s">
+      <c r="J20" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="K20" s="94"/>
+      <c r="K20" s="67"/>
       <c r="L20" s="60" t="s">
         <v>63</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="62" t="s">
+      <c r="N20" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="O20" s="63"/>
+      <c r="O20" s="75"/>
       <c r="P20" s="34" t="s">
         <v>47</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="134" t="s">
+      <c r="R20" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="S20" s="135"/>
+      <c r="S20" s="113"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="134" t="s">
+      <c r="V20" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="W20" s="135"/>
+      <c r="W20" s="113"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="134" t="s">
+      <c r="Z20" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="AA20" s="135"/>
+      <c r="AA20" s="113"/>
       <c r="AB20" s="56" t="s">
         <v>43</v>
       </c>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="63"/>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="75"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="63"/>
+      <c r="AH20" s="74"/>
+      <c r="AI20" s="75"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="62" t="s">
+      <c r="AL20" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="AM20" s="63"/>
+      <c r="AM20" s="75"/>
       <c r="AN20" s="34" t="s">
         <v>63</v>
       </c>
@@ -3259,48 +3276,48 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="87"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="86" t="s">
+      <c r="F21" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="87"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="87"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="78"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="80"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="78"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="80"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="129"/>
-      <c r="W21" s="130"/>
+      <c r="V21" s="118"/>
+      <c r="W21" s="119"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="129"/>
-      <c r="AA21" s="130"/>
+      <c r="Z21" s="118"/>
+      <c r="AA21" s="119"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="77"/>
-      <c r="AE21" s="78"/>
+      <c r="AD21" s="79"/>
+      <c r="AE21" s="80"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="77"/>
-      <c r="AI21" s="78"/>
+      <c r="AH21" s="79"/>
+      <c r="AI21" s="80"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="77"/>
-      <c r="AM21" s="78"/>
+      <c r="AL21" s="79"/>
+      <c r="AM21" s="80"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3312,74 +3329,74 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="99" t="s">
+      <c r="B22" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="100"/>
+      <c r="C22" s="71"/>
       <c r="D22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="37"/>
-      <c r="F22" s="99" t="s">
+      <c r="F22" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="100"/>
+      <c r="G22" s="71"/>
       <c r="H22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="35"/>
-      <c r="J22" s="99" t="s">
+      <c r="J22" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="100"/>
+      <c r="K22" s="71"/>
       <c r="L22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="89" t="s">
+      <c r="N22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="90"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="89" t="s">
+      <c r="R22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="S22" s="90"/>
+      <c r="S22" s="134"/>
       <c r="T22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="37"/>
-      <c r="V22" s="89" t="s">
+      <c r="V22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="90"/>
+      <c r="W22" s="134"/>
       <c r="X22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="89" t="s">
+      <c r="Z22" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="AA22" s="90"/>
+      <c r="AA22" s="134"/>
       <c r="AB22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="99"/>
-      <c r="AE22" s="100"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="71"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="99"/>
-      <c r="AI22" s="100"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="71"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="89" t="s">
+      <c r="AL22" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="AM22" s="90"/>
+      <c r="AM22" s="134"/>
       <c r="AN22" s="41" t="s">
         <v>32</v>
       </c>
@@ -3388,79 +3405,79 @@
       </c>
       <c r="AQ22" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="73"/>
       <c r="D23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="95" t="s">
+      <c r="F23" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="96"/>
+      <c r="G23" s="73"/>
       <c r="H23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="43"/>
-      <c r="J23" s="95" t="s">
+      <c r="J23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="96"/>
+      <c r="K23" s="73"/>
       <c r="L23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="95" t="s">
+      <c r="N23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="96"/>
+      <c r="O23" s="73"/>
       <c r="P23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q23" s="43"/>
-      <c r="R23" s="95" t="s">
+      <c r="R23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="96"/>
+      <c r="S23" s="73"/>
       <c r="T23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U23" s="43"/>
-      <c r="V23" s="95" t="s">
+      <c r="V23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="96"/>
+      <c r="W23" s="73"/>
       <c r="X23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="95" t="s">
+      <c r="Z23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AA23" s="96"/>
+      <c r="AA23" s="73"/>
       <c r="AB23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="95"/>
-      <c r="AE23" s="96"/>
+      <c r="AD23" s="72"/>
+      <c r="AE23" s="73"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="95"/>
-      <c r="AI23" s="96"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="73"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="95" t="s">
+      <c r="AL23" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AM23" s="96"/>
+      <c r="AM23" s="73"/>
       <c r="AN23" s="45" t="s">
         <v>33</v>
       </c>
@@ -3474,74 +3491,74 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="63"/>
       <c r="D24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="70" t="s">
+      <c r="F24" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="71"/>
+      <c r="G24" s="63"/>
       <c r="H24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I24" s="44"/>
-      <c r="J24" s="70" t="s">
+      <c r="J24" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="71"/>
+      <c r="K24" s="63"/>
       <c r="L24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="70" t="s">
+      <c r="N24" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="O24" s="71"/>
+      <c r="O24" s="63"/>
       <c r="P24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q24" s="43"/>
-      <c r="R24" s="70" t="s">
+      <c r="R24" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="S24" s="71"/>
+      <c r="S24" s="63"/>
       <c r="T24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="44"/>
-      <c r="V24" s="70" t="s">
+      <c r="V24" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="W24" s="71"/>
+      <c r="W24" s="63"/>
       <c r="X24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="70" t="s">
+      <c r="Z24" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="AA24" s="71"/>
+      <c r="AA24" s="63"/>
       <c r="AB24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="70"/>
-      <c r="AE24" s="71"/>
+      <c r="AD24" s="62"/>
+      <c r="AE24" s="63"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="70"/>
-      <c r="AI24" s="71"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="63"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="70" t="s">
+      <c r="AL24" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="AM24" s="71"/>
+      <c r="AM24" s="63"/>
       <c r="AN24" s="45" t="s">
         <v>34</v>
       </c>
@@ -3555,74 +3572,74 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="63"/>
       <c r="D25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="97" t="s">
+      <c r="F25" s="140" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="98"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="44"/>
-      <c r="J25" s="70" t="s">
+      <c r="J25" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="71"/>
+      <c r="K25" s="63"/>
       <c r="L25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="70" t="s">
+      <c r="N25" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="O25" s="71"/>
+      <c r="O25" s="63"/>
       <c r="P25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q25" s="44"/>
-      <c r="R25" s="70" t="s">
+      <c r="R25" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="S25" s="71"/>
+      <c r="S25" s="63"/>
       <c r="T25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="44"/>
-      <c r="V25" s="70" t="s">
+      <c r="V25" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="W25" s="71"/>
+      <c r="W25" s="63"/>
       <c r="X25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="70" t="s">
+      <c r="Z25" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="AA25" s="71"/>
+      <c r="AA25" s="63"/>
       <c r="AB25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="70"/>
-      <c r="AE25" s="71"/>
+      <c r="AD25" s="62"/>
+      <c r="AE25" s="63"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="70"/>
-      <c r="AI25" s="71"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="63"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="70" t="s">
+      <c r="AL25" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="AM25" s="71"/>
+      <c r="AM25" s="63"/>
       <c r="AN25" s="45" t="s">
         <v>35</v>
       </c>
@@ -3636,74 +3653,74 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="63"/>
       <c r="D26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="70" t="s">
+      <c r="F26" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="71"/>
+      <c r="G26" s="63"/>
       <c r="H26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I26" s="44"/>
-      <c r="J26" s="70" t="s">
+      <c r="J26" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="71"/>
+      <c r="K26" s="63"/>
       <c r="L26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="70" t="s">
+      <c r="N26" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="71"/>
+      <c r="O26" s="63"/>
       <c r="P26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q26" s="44"/>
-      <c r="R26" s="70" t="s">
+      <c r="R26" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="S26" s="71"/>
+      <c r="S26" s="63"/>
       <c r="T26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="44"/>
-      <c r="V26" s="70" t="s">
+      <c r="V26" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W26" s="71"/>
+      <c r="W26" s="63"/>
       <c r="X26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="70" t="s">
+      <c r="Z26" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="AA26" s="71"/>
+      <c r="AA26" s="63"/>
       <c r="AB26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="70"/>
-      <c r="AE26" s="71"/>
+      <c r="AD26" s="62"/>
+      <c r="AE26" s="63"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="70"/>
-      <c r="AI26" s="71"/>
+      <c r="AH26" s="62"/>
+      <c r="AI26" s="63"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="70" t="s">
+      <c r="AL26" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="AM26" s="71"/>
+      <c r="AM26" s="63"/>
       <c r="AN26" s="45" t="s">
         <v>35</v>
       </c>
@@ -3717,44 +3734,44 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="72"/>
-      <c r="C27" s="73"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="73"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="65"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="73"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="65"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="73"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="65"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="73"/>
+      <c r="R27" s="64"/>
+      <c r="S27" s="65"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="72"/>
-      <c r="W27" s="73"/>
+      <c r="V27" s="64"/>
+      <c r="W27" s="65"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="72"/>
-      <c r="AA27" s="73"/>
+      <c r="Z27" s="64"/>
+      <c r="AA27" s="65"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="72"/>
-      <c r="AE27" s="73"/>
+      <c r="AD27" s="64"/>
+      <c r="AE27" s="65"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="72"/>
-      <c r="AI27" s="73"/>
+      <c r="AH27" s="64"/>
+      <c r="AI27" s="65"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="72"/>
-      <c r="AM27" s="73"/>
+      <c r="AL27" s="64"/>
+      <c r="AM27" s="65"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3827,23 +3844,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="104" t="s">
+      <c r="N29" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="104"/>
-      <c r="P29" s="104"/>
-      <c r="Q29" s="104"/>
-      <c r="R29" s="104"/>
-      <c r="S29" s="104"/>
-      <c r="T29" s="104"/>
-      <c r="U29" s="104"/>
-      <c r="V29" s="104"/>
-      <c r="W29" s="104"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="104"/>
-      <c r="Z29" s="104"/>
-      <c r="AA29" s="104"/>
-      <c r="AB29" s="104"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
+      <c r="U29" s="114"/>
+      <c r="V29" s="114"/>
+      <c r="W29" s="114"/>
+      <c r="X29" s="114"/>
+      <c r="Y29" s="114"/>
+      <c r="Z29" s="114"/>
+      <c r="AA29" s="114"/>
+      <c r="AB29" s="114"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3878,21 +3895,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="104"/>
-      <c r="Q30" s="104"/>
-      <c r="R30" s="104"/>
-      <c r="S30" s="104"/>
-      <c r="T30" s="104"/>
-      <c r="U30" s="104"/>
-      <c r="V30" s="104"/>
-      <c r="W30" s="104"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="104"/>
-      <c r="Z30" s="104"/>
-      <c r="AA30" s="104"/>
-      <c r="AB30" s="104"/>
+      <c r="N30" s="114"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
+      <c r="U30" s="114"/>
+      <c r="V30" s="114"/>
+      <c r="W30" s="114"/>
+      <c r="X30" s="114"/>
+      <c r="Y30" s="114"/>
+      <c r="Z30" s="114"/>
+      <c r="AA30" s="114"/>
+      <c r="AB30" s="114"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3915,240 +3932,240 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="94"/>
+      <c r="C31" s="67"/>
       <c r="D31" s="60"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="94"/>
+      <c r="G31" s="67"/>
       <c r="H31" s="60"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="93" t="s">
+      <c r="J31" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="94"/>
+      <c r="K31" s="67"/>
       <c r="L31" s="60"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="62" t="s">
+      <c r="N31" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="O31" s="63"/>
+      <c r="O31" s="75"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="63"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="75"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="62" t="s">
+      <c r="V31" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="W31" s="63"/>
+      <c r="W31" s="75"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="62" t="s">
+      <c r="Z31" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AA31" s="63"/>
+      <c r="AA31" s="75"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="62" t="s">
+      <c r="AD31" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AE31" s="63"/>
+      <c r="AE31" s="75"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="62" t="s">
+      <c r="AH31" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AI31" s="63"/>
+      <c r="AI31" s="75"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="62" t="s">
+      <c r="AL31" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM31" s="63"/>
+      <c r="AM31" s="75"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="68"/>
-      <c r="D32" s="69"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="93"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="67" t="s">
+      <c r="F32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="69"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="93"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="67" t="s">
+      <c r="J32" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="68"/>
-      <c r="L32" s="69"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="93"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="64" t="s">
+      <c r="N32" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="O32" s="65"/>
-      <c r="P32" s="66"/>
+      <c r="O32" s="77"/>
+      <c r="P32" s="78"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="64"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="66"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="78"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="64" t="s">
+      <c r="V32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="W32" s="65"/>
-      <c r="X32" s="66"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="78"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="64" t="s">
+      <c r="Z32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AA32" s="65"/>
-      <c r="AB32" s="66"/>
+      <c r="AA32" s="77"/>
+      <c r="AB32" s="78"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="64" t="s">
+      <c r="AD32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AE32" s="65"/>
-      <c r="AF32" s="66"/>
+      <c r="AE32" s="77"/>
+      <c r="AF32" s="78"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="64" t="s">
+      <c r="AH32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AI32" s="65"/>
-      <c r="AJ32" s="66"/>
+      <c r="AI32" s="77"/>
+      <c r="AJ32" s="78"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="64" t="s">
+      <c r="AL32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM32" s="65"/>
-      <c r="AN32" s="66"/>
+      <c r="AM32" s="77"/>
+      <c r="AN32" s="78"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="86"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="88"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="94"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="88"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="94"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="88"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="94"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="77"/>
-      <c r="O33" s="78"/>
-      <c r="P33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="81"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="77"/>
-      <c r="S33" s="78"/>
-      <c r="T33" s="79"/>
+      <c r="R33" s="79"/>
+      <c r="S33" s="80"/>
+      <c r="T33" s="81"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="77" t="s">
+      <c r="V33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="W33" s="78"/>
-      <c r="X33" s="79"/>
+      <c r="W33" s="80"/>
+      <c r="X33" s="81"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="77" t="s">
+      <c r="Z33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AA33" s="78"/>
-      <c r="AB33" s="79"/>
+      <c r="AA33" s="80"/>
+      <c r="AB33" s="81"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="77" t="s">
+      <c r="AD33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AE33" s="78"/>
-      <c r="AF33" s="79"/>
+      <c r="AE33" s="80"/>
+      <c r="AF33" s="81"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="77" t="s">
+      <c r="AH33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AI33" s="78"/>
-      <c r="AJ33" s="79"/>
+      <c r="AI33" s="80"/>
+      <c r="AJ33" s="81"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="77" t="s">
+      <c r="AL33" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AM33" s="78"/>
-      <c r="AN33" s="79"/>
+      <c r="AM33" s="80"/>
+      <c r="AN33" s="81"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="83" t="s">
+      <c r="B34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="84"/>
-      <c r="D34" s="85"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="90"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="84"/>
-      <c r="H34" s="85"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="84"/>
-      <c r="L34" s="85"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="80" t="s">
+      <c r="N34" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="81"/>
-      <c r="P34" s="82"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="84"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="80"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="84"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="80" t="s">
+      <c r="V34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="81"/>
-      <c r="X34" s="82"/>
+      <c r="W34" s="83"/>
+      <c r="X34" s="84"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="80" t="s">
+      <c r="Z34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="82"/>
+      <c r="AA34" s="83"/>
+      <c r="AB34" s="84"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="80" t="s">
+      <c r="AD34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="82"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="84"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="80" t="s">
+      <c r="AH34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="82"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="84"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="80" t="s">
+      <c r="AL34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="82"/>
+      <c r="AM34" s="83"/>
+      <c r="AN34" s="84"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -4156,90 +4173,90 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="83" t="s">
+      <c r="B35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="84"/>
-      <c r="D35" s="85"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="90"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="83" t="s">
+      <c r="F35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="84"/>
-      <c r="H35" s="85"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="90"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="83" t="s">
+      <c r="J35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="84"/>
-      <c r="L35" s="85"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="90"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="83" t="s">
+      <c r="N35" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="O35" s="84"/>
-      <c r="P35" s="85"/>
+      <c r="O35" s="89"/>
+      <c r="P35" s="90"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="84"/>
-      <c r="T35" s="85"/>
+      <c r="R35" s="88"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="90"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="74" t="s">
+      <c r="V35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="75"/>
-      <c r="X35" s="76"/>
+      <c r="W35" s="86"/>
+      <c r="X35" s="87"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="74" t="s">
+      <c r="Z35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="75"/>
-      <c r="AB35" s="76"/>
+      <c r="AA35" s="86"/>
+      <c r="AB35" s="87"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="74" t="s">
+      <c r="AD35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="75"/>
-      <c r="AF35" s="76"/>
+      <c r="AE35" s="86"/>
+      <c r="AF35" s="87"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="74" t="s">
+      <c r="AH35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AI35" s="75"/>
-      <c r="AJ35" s="76"/>
+      <c r="AI35" s="86"/>
+      <c r="AJ35" s="87"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="74" t="s">
+      <c r="AL35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AM35" s="75"/>
-      <c r="AN35" s="76"/>
+      <c r="AM35" s="86"/>
+      <c r="AN35" s="87"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="74"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="76"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="87"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="76"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="76"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="87"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="74" t="s">
+      <c r="N36" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="O36" s="75"/>
-      <c r="P36" s="76"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="87"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="75"/>
-      <c r="T36" s="76"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="86"/>
+      <c r="T36" s="87"/>
       <c r="U36" s="40"/>
       <c r="V36" s="35"/>
       <c r="W36" s="35"/>
@@ -4287,34 +4304,34 @@
       <c r="S37" s="35"/>
       <c r="T37" s="35"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="62" t="s">
+      <c r="V37" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="W37" s="63"/>
+      <c r="W37" s="75"/>
       <c r="X37" s="34"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="62" t="s">
+      <c r="Z37" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AA37" s="63"/>
+      <c r="AA37" s="75"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="36"/>
-      <c r="AD37" s="62" t="s">
+      <c r="AD37" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AE37" s="63"/>
+      <c r="AE37" s="75"/>
       <c r="AF37" s="34"/>
       <c r="AG37" s="50"/>
-      <c r="AH37" s="62" t="s">
+      <c r="AH37" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AI37" s="63"/>
+      <c r="AI37" s="75"/>
       <c r="AJ37" s="34"/>
       <c r="AK37" s="50"/>
-      <c r="AL37" s="62" t="s">
+      <c r="AL37" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM37" s="63"/>
+      <c r="AM37" s="75"/>
       <c r="AN37" s="34"/>
       <c r="AO37" s="31"/>
       <c r="AP37" s="22"/>
@@ -4323,63 +4340,63 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="93"/>
-      <c r="C38" s="94"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="67"/>
       <c r="D38" s="60"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="91" t="s">
+      <c r="F38" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="92"/>
+      <c r="G38" s="102"/>
       <c r="H38" s="55" t="s">
         <v>52</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="93" t="s">
+      <c r="J38" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="K38" s="94"/>
+      <c r="K38" s="67"/>
       <c r="L38" s="60"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="108" t="s">
+      <c r="N38" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="O38" s="109"/>
+      <c r="O38" s="139"/>
       <c r="P38" s="59"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="63"/>
+      <c r="R38" s="74"/>
+      <c r="S38" s="75"/>
       <c r="T38" s="34"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="64" t="s">
+      <c r="V38" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="W38" s="65"/>
-      <c r="X38" s="66"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="78"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="64" t="s">
+      <c r="Z38" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AA38" s="65"/>
-      <c r="AB38" s="66"/>
+      <c r="AA38" s="77"/>
+      <c r="AB38" s="78"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="64" t="s">
+      <c r="AD38" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AE38" s="65"/>
-      <c r="AF38" s="66"/>
+      <c r="AE38" s="77"/>
+      <c r="AF38" s="78"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="64" t="s">
+      <c r="AH38" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AI38" s="65"/>
-      <c r="AJ38" s="66"/>
+      <c r="AI38" s="77"/>
+      <c r="AJ38" s="78"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="64" t="s">
+      <c r="AL38" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="65"/>
-      <c r="AN38" s="66"/>
+      <c r="AM38" s="77"/>
+      <c r="AN38" s="78"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
       <c r="AQ38" s="31"/>
@@ -4387,61 +4404,61 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="69"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="93"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="67" t="s">
+      <c r="F39" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="68"/>
-      <c r="H39" s="69"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="67" t="s">
+      <c r="J39" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="K39" s="68"/>
-      <c r="L39" s="69"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="93"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="105" t="s">
+      <c r="N39" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="O39" s="106"/>
-      <c r="P39" s="107"/>
+      <c r="O39" s="136"/>
+      <c r="P39" s="137"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="66"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="78"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="77" t="s">
+      <c r="V39" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="W39" s="78"/>
-      <c r="X39" s="79"/>
+      <c r="W39" s="80"/>
+      <c r="X39" s="81"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="77" t="s">
+      <c r="Z39" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AA39" s="78"/>
-      <c r="AB39" s="79"/>
+      <c r="AA39" s="80"/>
+      <c r="AB39" s="81"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="77" t="s">
+      <c r="AD39" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AE39" s="78"/>
-      <c r="AF39" s="79"/>
+      <c r="AE39" s="80"/>
+      <c r="AF39" s="81"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="77" t="s">
+      <c r="AH39" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AI39" s="78"/>
-      <c r="AJ39" s="79"/>
+      <c r="AI39" s="80"/>
+      <c r="AJ39" s="81"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="77" t="s">
+      <c r="AL39" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AM39" s="78"/>
-      <c r="AN39" s="79"/>
+      <c r="AM39" s="80"/>
+      <c r="AN39" s="81"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4449,57 +4466,57 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="86"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="88"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="94"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="88"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="94"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="87"/>
-      <c r="L40" s="88"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="94"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="131" t="s">
+      <c r="N40" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="O40" s="132"/>
-      <c r="P40" s="133"/>
+      <c r="O40" s="116"/>
+      <c r="P40" s="117"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="78"/>
-      <c r="T40" s="79"/>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="81"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="80" t="s">
+      <c r="V40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="81"/>
-      <c r="X40" s="82"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="84"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="80" t="s">
+      <c r="Z40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="81"/>
-      <c r="AB40" s="82"/>
+      <c r="AA40" s="83"/>
+      <c r="AB40" s="84"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="80" t="s">
+      <c r="AD40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AE40" s="81"/>
-      <c r="AF40" s="82"/>
+      <c r="AE40" s="83"/>
+      <c r="AF40" s="84"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="80" t="s">
+      <c r="AH40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AI40" s="81"/>
-      <c r="AJ40" s="82"/>
+      <c r="AI40" s="83"/>
+      <c r="AJ40" s="84"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="80" t="s">
+      <c r="AL40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AM40" s="81"/>
-      <c r="AN40" s="82"/>
+      <c r="AM40" s="83"/>
+      <c r="AN40" s="84"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4507,61 +4524,61 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="85"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="90"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="80" t="s">
+      <c r="F41" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="81"/>
-      <c r="H41" s="82"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="84"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="101" t="s">
+      <c r="J41" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="K41" s="102"/>
-      <c r="L41" s="103"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="97"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="136" t="s">
+      <c r="N41" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="O41" s="137"/>
-      <c r="P41" s="138"/>
+      <c r="O41" s="107"/>
+      <c r="P41" s="108"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="80"/>
-      <c r="S41" s="81"/>
-      <c r="T41" s="82"/>
+      <c r="R41" s="82"/>
+      <c r="S41" s="83"/>
+      <c r="T41" s="84"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="74" t="s">
+      <c r="V41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="75"/>
-      <c r="X41" s="76"/>
+      <c r="W41" s="86"/>
+      <c r="X41" s="87"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="74" t="s">
+      <c r="Z41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="75"/>
-      <c r="AB41" s="76"/>
+      <c r="AA41" s="86"/>
+      <c r="AB41" s="87"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="74" t="s">
+      <c r="AD41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AE41" s="75"/>
-      <c r="AF41" s="76"/>
+      <c r="AE41" s="86"/>
+      <c r="AF41" s="87"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="74" t="s">
+      <c r="AH41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AI41" s="75"/>
-      <c r="AJ41" s="76"/>
+      <c r="AI41" s="86"/>
+      <c r="AJ41" s="87"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="74" t="s">
+      <c r="AL41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AM41" s="75"/>
-      <c r="AN41" s="76"/>
+      <c r="AM41" s="86"/>
+      <c r="AN41" s="87"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4569,31 +4586,31 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="85"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="90"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="83" t="s">
+      <c r="F42" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="84"/>
-      <c r="H42" s="85"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="90"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="83" t="s">
+      <c r="J42" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="84"/>
-      <c r="L42" s="85"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="90"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="139" t="s">
+      <c r="N42" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="O42" s="140"/>
-      <c r="P42" s="141"/>
+      <c r="O42" s="104"/>
+      <c r="P42" s="105"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="84"/>
-      <c r="T42" s="85"/>
+      <c r="R42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="90"/>
       <c r="U42" s="44"/>
       <c r="V42" s="35"/>
       <c r="W42" s="35"/>
@@ -4621,56 +4638,56 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="87"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="76"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="87"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="110" t="s">
+      <c r="J43" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="K43" s="111"/>
-      <c r="L43" s="112"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="100"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="110"/>
-      <c r="O43" s="111"/>
-      <c r="P43" s="112"/>
+      <c r="N43" s="98"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="100"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="75"/>
-      <c r="T43" s="76"/>
+      <c r="R43" s="85"/>
+      <c r="S43" s="86"/>
+      <c r="T43" s="87"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="62" t="s">
+      <c r="V43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="W43" s="63"/>
+      <c r="W43" s="75"/>
       <c r="X43" s="34"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="62" t="s">
+      <c r="Z43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AA43" s="63"/>
+      <c r="AA43" s="75"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="62" t="s">
+      <c r="AD43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AE43" s="63"/>
+      <c r="AE43" s="75"/>
       <c r="AF43" s="34"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="62" t="s">
+      <c r="AH43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AI43" s="63"/>
+      <c r="AI43" s="75"/>
       <c r="AJ43" s="34"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="62" t="s">
+      <c r="AL43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM43" s="63"/>
+      <c r="AM43" s="75"/>
       <c r="AN43" s="34"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
@@ -4699,35 +4716,35 @@
       <c r="S44" s="35"/>
       <c r="T44" s="35"/>
       <c r="U44" s="36"/>
-      <c r="V44" s="64" t="s">
+      <c r="V44" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="W44" s="65"/>
-      <c r="X44" s="66"/>
+      <c r="W44" s="77"/>
+      <c r="X44" s="78"/>
       <c r="Y44" s="36"/>
-      <c r="Z44" s="64" t="s">
+      <c r="Z44" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AA44" s="65"/>
-      <c r="AB44" s="66"/>
+      <c r="AA44" s="77"/>
+      <c r="AB44" s="78"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="64" t="s">
+      <c r="AD44" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AE44" s="65"/>
-      <c r="AF44" s="66"/>
+      <c r="AE44" s="77"/>
+      <c r="AF44" s="78"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="64" t="s">
+      <c r="AH44" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AI44" s="65"/>
-      <c r="AJ44" s="66"/>
+      <c r="AI44" s="77"/>
+      <c r="AJ44" s="78"/>
       <c r="AK44" s="50"/>
-      <c r="AL44" s="64" t="s">
+      <c r="AL44" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM44" s="65"/>
-      <c r="AN44" s="66"/>
+      <c r="AM44" s="77"/>
+      <c r="AN44" s="78"/>
       <c r="AO44" s="31"/>
       <c r="AP44" s="31"/>
       <c r="AQ44" s="31"/>
@@ -4735,57 +4752,57 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="93"/>
-      <c r="C45" s="94"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="67"/>
       <c r="D45" s="60"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="93"/>
-      <c r="G45" s="94"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="67"/>
       <c r="H45" s="60"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="91" t="s">
+      <c r="J45" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="K45" s="92"/>
+      <c r="K45" s="102"/>
       <c r="L45" s="55"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="62"/>
-      <c r="O45" s="63"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="75"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="62"/>
-      <c r="S45" s="63"/>
+      <c r="R45" s="74"/>
+      <c r="S45" s="75"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="77" t="s">
+      <c r="V45" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="W45" s="78"/>
-      <c r="X45" s="79"/>
+      <c r="W45" s="80"/>
+      <c r="X45" s="81"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="77" t="s">
+      <c r="Z45" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AA45" s="78"/>
-      <c r="AB45" s="79"/>
+      <c r="AA45" s="80"/>
+      <c r="AB45" s="81"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="77" t="s">
+      <c r="AD45" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AE45" s="78"/>
-      <c r="AF45" s="79"/>
+      <c r="AE45" s="80"/>
+      <c r="AF45" s="81"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="77" t="s">
+      <c r="AH45" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AI45" s="78"/>
-      <c r="AJ45" s="79"/>
+      <c r="AI45" s="80"/>
+      <c r="AJ45" s="81"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="77" t="s">
+      <c r="AL45" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AM45" s="78"/>
-      <c r="AN45" s="79"/>
+      <c r="AM45" s="80"/>
+      <c r="AN45" s="81"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
@@ -4793,57 +4810,57 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="69"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="93"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="69"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="92"/>
+      <c r="H46" s="93"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="67" t="s">
+      <c r="J46" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="K46" s="68"/>
-      <c r="L46" s="69"/>
+      <c r="K46" s="92"/>
+      <c r="L46" s="93"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="66"/>
+      <c r="N46" s="76"/>
+      <c r="O46" s="77"/>
+      <c r="P46" s="78"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="64"/>
-      <c r="S46" s="65"/>
-      <c r="T46" s="66"/>
+      <c r="R46" s="76"/>
+      <c r="S46" s="77"/>
+      <c r="T46" s="78"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="83" t="s">
+      <c r="V46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="84"/>
-      <c r="X46" s="85"/>
+      <c r="W46" s="89"/>
+      <c r="X46" s="90"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="83" t="s">
+      <c r="Z46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="84"/>
-      <c r="AB46" s="85"/>
+      <c r="AA46" s="89"/>
+      <c r="AB46" s="90"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="83" t="s">
+      <c r="AD46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AE46" s="84"/>
-      <c r="AF46" s="85"/>
+      <c r="AE46" s="89"/>
+      <c r="AF46" s="90"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="83" t="s">
+      <c r="AH46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AI46" s="84"/>
-      <c r="AJ46" s="85"/>
+      <c r="AI46" s="89"/>
+      <c r="AJ46" s="90"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="83" t="s">
+      <c r="AL46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AM46" s="84"/>
-      <c r="AN46" s="85"/>
+      <c r="AM46" s="89"/>
+      <c r="AN46" s="90"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4851,57 +4868,57 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="86"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="88"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="94"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="86"/>
-      <c r="G47" s="87"/>
-      <c r="H47" s="88"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="94"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="86" t="s">
+      <c r="J47" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="K47" s="87"/>
-      <c r="L47" s="88"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="94"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="78"/>
-      <c r="P47" s="79"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="80"/>
+      <c r="P47" s="81"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="77"/>
-      <c r="S47" s="78"/>
-      <c r="T47" s="79"/>
+      <c r="R47" s="79"/>
+      <c r="S47" s="80"/>
+      <c r="T47" s="81"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="83" t="s">
+      <c r="V47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="84"/>
-      <c r="X47" s="85"/>
+      <c r="W47" s="89"/>
+      <c r="X47" s="90"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="83" t="s">
+      <c r="Z47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="84"/>
-      <c r="AB47" s="85"/>
+      <c r="AA47" s="89"/>
+      <c r="AB47" s="90"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="83" t="s">
+      <c r="AD47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AE47" s="84"/>
-      <c r="AF47" s="85"/>
+      <c r="AE47" s="89"/>
+      <c r="AF47" s="90"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="83" t="s">
+      <c r="AH47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AI47" s="84"/>
-      <c r="AJ47" s="85"/>
+      <c r="AI47" s="89"/>
+      <c r="AJ47" s="90"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="83" t="s">
+      <c r="AL47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AM47" s="84"/>
-      <c r="AN47" s="85"/>
+      <c r="AM47" s="89"/>
+      <c r="AN47" s="90"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4909,139 +4926,139 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="82"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="85"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="90"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="83" t="s">
+      <c r="J48" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="84"/>
-      <c r="L48" s="85"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="90"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="84"/>
-      <c r="P48" s="85"/>
+      <c r="N48" s="88"/>
+      <c r="O48" s="89"/>
+      <c r="P48" s="90"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="83"/>
-      <c r="S48" s="84"/>
-      <c r="T48" s="85"/>
+      <c r="R48" s="88"/>
+      <c r="S48" s="89"/>
+      <c r="T48" s="90"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="83" t="s">
+      <c r="V48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="84"/>
-      <c r="X48" s="85"/>
+      <c r="W48" s="89"/>
+      <c r="X48" s="90"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="83" t="s">
+      <c r="Z48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="84"/>
-      <c r="AB48" s="85"/>
+      <c r="AA48" s="89"/>
+      <c r="AB48" s="90"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="83" t="s">
+      <c r="AD48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AE48" s="84"/>
-      <c r="AF48" s="85"/>
+      <c r="AE48" s="89"/>
+      <c r="AF48" s="90"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="83" t="s">
+      <c r="AH48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AI48" s="84"/>
-      <c r="AJ48" s="85"/>
+      <c r="AI48" s="89"/>
+      <c r="AJ48" s="90"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="83" t="s">
+      <c r="AL48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AM48" s="84"/>
-      <c r="AN48" s="85"/>
+      <c r="AM48" s="89"/>
+      <c r="AN48" s="90"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="83"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="85"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="90"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="84"/>
-      <c r="H49" s="85"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="90"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="83" t="s">
+      <c r="J49" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="K49" s="84"/>
-      <c r="L49" s="85"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="90"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="84"/>
-      <c r="P49" s="85"/>
+      <c r="N49" s="88"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="90"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="83"/>
-      <c r="S49" s="84"/>
-      <c r="T49" s="85"/>
+      <c r="R49" s="88"/>
+      <c r="S49" s="89"/>
+      <c r="T49" s="90"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="74" t="s">
+      <c r="V49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="75"/>
-      <c r="X49" s="76"/>
+      <c r="W49" s="86"/>
+      <c r="X49" s="87"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="74" t="s">
+      <c r="Z49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="75"/>
-      <c r="AB49" s="76"/>
+      <c r="AA49" s="86"/>
+      <c r="AB49" s="87"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="74" t="s">
+      <c r="AD49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AE49" s="75"/>
-      <c r="AF49" s="76"/>
+      <c r="AE49" s="86"/>
+      <c r="AF49" s="87"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="74" t="s">
+      <c r="AH49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AI49" s="75"/>
-      <c r="AJ49" s="76"/>
+      <c r="AI49" s="86"/>
+      <c r="AJ49" s="87"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="74" t="s">
+      <c r="AL49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="75"/>
-      <c r="AN49" s="76"/>
+      <c r="AM49" s="86"/>
+      <c r="AN49" s="87"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="74"/>
-      <c r="C50" s="75"/>
-      <c r="D50" s="76"/>
+      <c r="B50" s="85"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="87"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="76"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="87"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="74"/>
-      <c r="K50" s="75"/>
-      <c r="L50" s="76"/>
+      <c r="J50" s="85"/>
+      <c r="K50" s="86"/>
+      <c r="L50" s="87"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="74"/>
-      <c r="O50" s="75"/>
-      <c r="P50" s="76"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="87"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="74"/>
-      <c r="S50" s="75"/>
-      <c r="T50" s="76"/>
+      <c r="R50" s="85"/>
+      <c r="S50" s="86"/>
+      <c r="T50" s="87"/>
       <c r="U50" s="35"/>
       <c r="V50" s="35"/>
       <c r="W50" s="35"/>
@@ -5088,30 +5105,30 @@
       <c r="S51" s="35"/>
       <c r="T51" s="35"/>
       <c r="U51" s="40"/>
-      <c r="V51" s="62"/>
-      <c r="W51" s="63"/>
+      <c r="V51" s="74"/>
+      <c r="W51" s="75"/>
       <c r="X51" s="34"/>
       <c r="Y51" s="32"/>
-      <c r="Z51" s="62"/>
-      <c r="AA51" s="63"/>
+      <c r="Z51" s="74"/>
+      <c r="AA51" s="75"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="40"/>
-      <c r="AD51" s="62" t="s">
+      <c r="AD51" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AE51" s="63"/>
+      <c r="AE51" s="75"/>
       <c r="AF51" s="34"/>
       <c r="AG51" s="50"/>
-      <c r="AH51" s="62" t="s">
+      <c r="AH51" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AI51" s="63"/>
+      <c r="AI51" s="75"/>
       <c r="AJ51" s="34"/>
       <c r="AK51" s="50"/>
-      <c r="AL51" s="62" t="s">
+      <c r="AL51" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM51" s="63"/>
+      <c r="AM51" s="75"/>
       <c r="AN51" s="34"/>
       <c r="AO51" s="31"/>
       <c r="AP51" s="31"/>
@@ -5119,275 +5136,275 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="93"/>
-      <c r="C52" s="94"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="67"/>
       <c r="D52" s="60"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="94"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="67"/>
       <c r="H52" s="60"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="91" t="s">
+      <c r="J52" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="K52" s="92"/>
+      <c r="K52" s="102"/>
       <c r="L52" s="55" t="s">
         <v>47</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="62"/>
-      <c r="O52" s="63"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="75"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="62"/>
-      <c r="S52" s="63"/>
+      <c r="R52" s="74"/>
+      <c r="S52" s="75"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="64"/>
-      <c r="W52" s="65"/>
-      <c r="X52" s="66"/>
+      <c r="V52" s="76"/>
+      <c r="W52" s="77"/>
+      <c r="X52" s="78"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="64"/>
-      <c r="AA52" s="65"/>
-      <c r="AB52" s="66"/>
+      <c r="Z52" s="76"/>
+      <c r="AA52" s="77"/>
+      <c r="AB52" s="78"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="64" t="s">
+      <c r="AD52" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AE52" s="65"/>
-      <c r="AF52" s="66"/>
+      <c r="AE52" s="77"/>
+      <c r="AF52" s="78"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="64" t="s">
+      <c r="AH52" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AI52" s="65"/>
-      <c r="AJ52" s="66"/>
+      <c r="AI52" s="77"/>
+      <c r="AJ52" s="78"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="64" t="s">
+      <c r="AL52" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM52" s="65"/>
-      <c r="AN52" s="66"/>
+      <c r="AM52" s="77"/>
+      <c r="AN52" s="78"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="67"/>
-      <c r="C53" s="68"/>
-      <c r="D53" s="69"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="93"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="68"/>
-      <c r="H53" s="69"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="92"/>
+      <c r="H53" s="93"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="67" t="s">
+      <c r="J53" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="68"/>
-      <c r="L53" s="69"/>
+      <c r="K53" s="92"/>
+      <c r="L53" s="93"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="64"/>
-      <c r="O53" s="65"/>
-      <c r="P53" s="66"/>
+      <c r="N53" s="76"/>
+      <c r="O53" s="77"/>
+      <c r="P53" s="78"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="64"/>
-      <c r="S53" s="65"/>
-      <c r="T53" s="66"/>
+      <c r="R53" s="76"/>
+      <c r="S53" s="77"/>
+      <c r="T53" s="78"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="77"/>
-      <c r="W53" s="78"/>
-      <c r="X53" s="79"/>
+      <c r="V53" s="79"/>
+      <c r="W53" s="80"/>
+      <c r="X53" s="81"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="77"/>
-      <c r="AA53" s="78"/>
-      <c r="AB53" s="79"/>
+      <c r="Z53" s="79"/>
+      <c r="AA53" s="80"/>
+      <c r="AB53" s="81"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="77" t="s">
+      <c r="AD53" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AE53" s="78"/>
-      <c r="AF53" s="79"/>
+      <c r="AE53" s="80"/>
+      <c r="AF53" s="81"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="77" t="s">
+      <c r="AH53" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AI53" s="78"/>
-      <c r="AJ53" s="79"/>
+      <c r="AI53" s="80"/>
+      <c r="AJ53" s="81"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="77" t="s">
+      <c r="AL53" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AM53" s="78"/>
-      <c r="AN53" s="79"/>
+      <c r="AM53" s="80"/>
+      <c r="AN53" s="81"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="86"/>
-      <c r="C54" s="87"/>
-      <c r="D54" s="88"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="94"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="88"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="94"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="86"/>
-      <c r="K54" s="87"/>
-      <c r="L54" s="88"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="94"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="77"/>
-      <c r="O54" s="78"/>
-      <c r="P54" s="79"/>
+      <c r="N54" s="79"/>
+      <c r="O54" s="80"/>
+      <c r="P54" s="81"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="77"/>
-      <c r="S54" s="78"/>
-      <c r="T54" s="79"/>
+      <c r="R54" s="79"/>
+      <c r="S54" s="80"/>
+      <c r="T54" s="81"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="80"/>
-      <c r="W54" s="81"/>
-      <c r="X54" s="82"/>
+      <c r="V54" s="82"/>
+      <c r="W54" s="83"/>
+      <c r="X54" s="84"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="80"/>
-      <c r="AA54" s="81"/>
-      <c r="AB54" s="82"/>
+      <c r="Z54" s="82"/>
+      <c r="AA54" s="83"/>
+      <c r="AB54" s="84"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="80" t="s">
+      <c r="AD54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AE54" s="81"/>
-      <c r="AF54" s="82"/>
+      <c r="AE54" s="83"/>
+      <c r="AF54" s="84"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="80" t="s">
+      <c r="AH54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AI54" s="81"/>
-      <c r="AJ54" s="82"/>
+      <c r="AI54" s="83"/>
+      <c r="AJ54" s="84"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="80" t="s">
+      <c r="AL54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AM54" s="81"/>
-      <c r="AN54" s="82"/>
+      <c r="AM54" s="83"/>
+      <c r="AN54" s="84"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="80"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="82"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="84"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="84"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="83" t="s">
+      <c r="J55" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="84"/>
-      <c r="L55" s="85"/>
+      <c r="K55" s="89"/>
+      <c r="L55" s="90"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="80"/>
-      <c r="O55" s="81"/>
-      <c r="P55" s="82"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="83"/>
+      <c r="P55" s="84"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="80"/>
-      <c r="S55" s="81"/>
-      <c r="T55" s="82"/>
+      <c r="R55" s="82"/>
+      <c r="S55" s="83"/>
+      <c r="T55" s="84"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="83"/>
-      <c r="W55" s="84"/>
-      <c r="X55" s="85"/>
+      <c r="V55" s="88"/>
+      <c r="W55" s="89"/>
+      <c r="X55" s="90"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="83"/>
-      <c r="AA55" s="84"/>
-      <c r="AB55" s="85"/>
+      <c r="Z55" s="88"/>
+      <c r="AA55" s="89"/>
+      <c r="AB55" s="90"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="83" t="s">
+      <c r="AD55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AE55" s="84"/>
-      <c r="AF55" s="85"/>
+      <c r="AE55" s="89"/>
+      <c r="AF55" s="90"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="83" t="s">
+      <c r="AH55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="84"/>
-      <c r="AJ55" s="85"/>
+      <c r="AI55" s="89"/>
+      <c r="AJ55" s="90"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="83" t="s">
+      <c r="AL55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AM55" s="84"/>
-      <c r="AN55" s="85"/>
+      <c r="AM55" s="89"/>
+      <c r="AN55" s="90"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="83"/>
-      <c r="C56" s="84"/>
-      <c r="D56" s="85"/>
+      <c r="B56" s="88"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="90"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="84"/>
-      <c r="H56" s="85"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="89"/>
+      <c r="H56" s="90"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="83" t="s">
+      <c r="J56" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="K56" s="84"/>
-      <c r="L56" s="85"/>
+      <c r="K56" s="89"/>
+      <c r="L56" s="90"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="83"/>
-      <c r="O56" s="84"/>
-      <c r="P56" s="85"/>
+      <c r="N56" s="88"/>
+      <c r="O56" s="89"/>
+      <c r="P56" s="90"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="83"/>
-      <c r="S56" s="84"/>
-      <c r="T56" s="85"/>
+      <c r="R56" s="88"/>
+      <c r="S56" s="89"/>
+      <c r="T56" s="90"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="74"/>
-      <c r="W56" s="75"/>
-      <c r="X56" s="76"/>
+      <c r="V56" s="85"/>
+      <c r="W56" s="86"/>
+      <c r="X56" s="87"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="74"/>
-      <c r="AA56" s="75"/>
-      <c r="AB56" s="76"/>
+      <c r="Z56" s="85"/>
+      <c r="AA56" s="86"/>
+      <c r="AB56" s="87"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="74" t="s">
+      <c r="AD56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AE56" s="75"/>
-      <c r="AF56" s="76"/>
+      <c r="AE56" s="86"/>
+      <c r="AF56" s="87"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="74" t="s">
+      <c r="AH56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AI56" s="75"/>
-      <c r="AJ56" s="76"/>
+      <c r="AI56" s="86"/>
+      <c r="AJ56" s="87"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="74" t="s">
+      <c r="AL56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AM56" s="75"/>
-      <c r="AN56" s="76"/>
+      <c r="AM56" s="86"/>
+      <c r="AN56" s="87"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="74"/>
-      <c r="C57" s="75"/>
-      <c r="D57" s="76"/>
+      <c r="B57" s="85"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="87"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="76"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="87"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="74"/>
-      <c r="K57" s="75"/>
-      <c r="L57" s="76"/>
+      <c r="J57" s="85"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="87"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="74"/>
-      <c r="O57" s="75"/>
-      <c r="P57" s="76"/>
+      <c r="N57" s="85"/>
+      <c r="O57" s="86"/>
+      <c r="P57" s="87"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="74"/>
-      <c r="S57" s="75"/>
-      <c r="T57" s="76"/>
+      <c r="R57" s="85"/>
+      <c r="S57" s="86"/>
+      <c r="T57" s="87"/>
       <c r="U57" s="50"/>
       <c r="V57" s="35"/>
       <c r="W57" s="35"/>
@@ -5431,293 +5448,303 @@
       <c r="S58" s="35"/>
       <c r="T58" s="35"/>
       <c r="U58" s="50"/>
-      <c r="V58" s="62"/>
-      <c r="W58" s="63"/>
+      <c r="V58" s="74"/>
+      <c r="W58" s="75"/>
       <c r="X58" s="34"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="62"/>
-      <c r="AA58" s="63"/>
+      <c r="Z58" s="74"/>
+      <c r="AA58" s="75"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
-      <c r="AD58" s="62"/>
-      <c r="AE58" s="63"/>
-      <c r="AF58" s="34"/>
+      <c r="AD58" s="101" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE58" s="102"/>
+      <c r="AF58" s="55"/>
       <c r="AG58" s="50"/>
-      <c r="AH58" s="62"/>
-      <c r="AI58" s="63"/>
+      <c r="AH58" s="74"/>
+      <c r="AI58" s="75"/>
       <c r="AJ58" s="34"/>
       <c r="AK58" s="50"/>
-      <c r="AL58" s="62" t="s">
+      <c r="AL58" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM58" s="63"/>
+      <c r="AM58" s="75"/>
       <c r="AN58" s="34"/>
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="93"/>
-      <c r="C59" s="94"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="67"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="94"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="67"/>
       <c r="H59" s="60"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="93"/>
-      <c r="K59" s="94"/>
+      <c r="J59" s="66"/>
+      <c r="K59" s="67"/>
       <c r="L59" s="60"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="62"/>
-      <c r="O59" s="63"/>
+      <c r="N59" s="74"/>
+      <c r="O59" s="75"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="62" t="s">
+      <c r="R59" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="S59" s="63"/>
+      <c r="S59" s="75"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="65"/>
-      <c r="X59" s="66"/>
+      <c r="V59" s="76"/>
+      <c r="W59" s="77"/>
+      <c r="X59" s="78"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="64"/>
-      <c r="AA59" s="65"/>
-      <c r="AB59" s="66"/>
+      <c r="Z59" s="76"/>
+      <c r="AA59" s="77"/>
+      <c r="AB59" s="78"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="64"/>
-      <c r="AE59" s="65"/>
-      <c r="AF59" s="66"/>
+      <c r="AD59" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE59" s="77"/>
+      <c r="AF59" s="78"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="64"/>
-      <c r="AI59" s="65"/>
-      <c r="AJ59" s="66"/>
+      <c r="AH59" s="76"/>
+      <c r="AI59" s="77"/>
+      <c r="AJ59" s="78"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="64" t="s">
+      <c r="AL59" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM59" s="65"/>
-      <c r="AN59" s="66"/>
+      <c r="AM59" s="77"/>
+      <c r="AN59" s="78"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="67"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="69"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="93"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="69"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="92"/>
+      <c r="H60" s="93"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="68"/>
-      <c r="L60" s="69"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="92"/>
+      <c r="L60" s="93"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="64"/>
-      <c r="O60" s="65"/>
-      <c r="P60" s="66"/>
+      <c r="N60" s="76"/>
+      <c r="O60" s="77"/>
+      <c r="P60" s="78"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="64" t="s">
+      <c r="R60" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="S60" s="65"/>
-      <c r="T60" s="66"/>
+      <c r="S60" s="77"/>
+      <c r="T60" s="78"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="77"/>
-      <c r="W60" s="78"/>
-      <c r="X60" s="79"/>
+      <c r="V60" s="79"/>
+      <c r="W60" s="80"/>
+      <c r="X60" s="81"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="77"/>
-      <c r="AA60" s="78"/>
-      <c r="AB60" s="79"/>
+      <c r="Z60" s="79"/>
+      <c r="AA60" s="80"/>
+      <c r="AB60" s="81"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="77"/>
-      <c r="AE60" s="78"/>
-      <c r="AF60" s="79"/>
+      <c r="AD60" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE60" s="80"/>
+      <c r="AF60" s="81"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="77"/>
-      <c r="AI60" s="78"/>
-      <c r="AJ60" s="79"/>
+      <c r="AH60" s="79"/>
+      <c r="AI60" s="80"/>
+      <c r="AJ60" s="81"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="77" t="s">
+      <c r="AL60" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="AM60" s="78"/>
-      <c r="AN60" s="79"/>
+      <c r="AM60" s="80"/>
+      <c r="AN60" s="81"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="86"/>
-      <c r="C61" s="87"/>
-      <c r="D61" s="88"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="94"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="88"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="94"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="86"/>
-      <c r="K61" s="87"/>
-      <c r="L61" s="88"/>
+      <c r="J61" s="68"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="94"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="77"/>
-      <c r="O61" s="78"/>
-      <c r="P61" s="79"/>
+      <c r="N61" s="79"/>
+      <c r="O61" s="80"/>
+      <c r="P61" s="81"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="77"/>
-      <c r="S61" s="78"/>
-      <c r="T61" s="79"/>
+      <c r="R61" s="79"/>
+      <c r="S61" s="80"/>
+      <c r="T61" s="81"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="80"/>
-      <c r="W61" s="81"/>
-      <c r="X61" s="82"/>
+      <c r="V61" s="82"/>
+      <c r="W61" s="83"/>
+      <c r="X61" s="84"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="80"/>
-      <c r="AA61" s="81"/>
-      <c r="AB61" s="82"/>
+      <c r="Z61" s="82"/>
+      <c r="AA61" s="83"/>
+      <c r="AB61" s="84"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="80"/>
-      <c r="AE61" s="81"/>
-      <c r="AF61" s="82"/>
+      <c r="AD61" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE61" s="83"/>
+      <c r="AF61" s="84"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="80"/>
-      <c r="AI61" s="81"/>
-      <c r="AJ61" s="82"/>
+      <c r="AH61" s="82"/>
+      <c r="AI61" s="83"/>
+      <c r="AJ61" s="84"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="80" t="s">
+      <c r="AL61" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="AM61" s="81"/>
-      <c r="AN61" s="82"/>
+      <c r="AM61" s="83"/>
+      <c r="AN61" s="84"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="80"/>
-      <c r="C62" s="81"/>
-      <c r="D62" s="82"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="84"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="81"/>
-      <c r="H62" s="82"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="84"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="80"/>
-      <c r="K62" s="81"/>
-      <c r="L62" s="82"/>
+      <c r="J62" s="82"/>
+      <c r="K62" s="83"/>
+      <c r="L62" s="84"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="83"/>
-      <c r="O62" s="84"/>
-      <c r="P62" s="85"/>
+      <c r="N62" s="88"/>
+      <c r="O62" s="89"/>
+      <c r="P62" s="90"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="83" t="s">
+      <c r="R62" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="S62" s="84"/>
-      <c r="T62" s="85"/>
+      <c r="S62" s="89"/>
+      <c r="T62" s="90"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="83"/>
-      <c r="W62" s="84"/>
-      <c r="X62" s="85"/>
+      <c r="V62" s="88"/>
+      <c r="W62" s="89"/>
+      <c r="X62" s="90"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="83"/>
-      <c r="AA62" s="84"/>
-      <c r="AB62" s="85"/>
+      <c r="Z62" s="88"/>
+      <c r="AA62" s="89"/>
+      <c r="AB62" s="90"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="83"/>
-      <c r="AE62" s="84"/>
-      <c r="AF62" s="85"/>
+      <c r="AD62" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE62" s="89"/>
+      <c r="AF62" s="90"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="83"/>
-      <c r="AI62" s="84"/>
-      <c r="AJ62" s="85"/>
+      <c r="AH62" s="88"/>
+      <c r="AI62" s="89"/>
+      <c r="AJ62" s="90"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="83" t="s">
+      <c r="AL62" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="AM62" s="84"/>
-      <c r="AN62" s="85"/>
+      <c r="AM62" s="89"/>
+      <c r="AN62" s="90"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="83"/>
-      <c r="C63" s="84"/>
-      <c r="D63" s="85"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="90"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="83"/>
-      <c r="G63" s="84"/>
-      <c r="H63" s="85"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="89"/>
+      <c r="H63" s="90"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="83"/>
-      <c r="K63" s="84"/>
-      <c r="L63" s="85"/>
+      <c r="J63" s="88"/>
+      <c r="K63" s="89"/>
+      <c r="L63" s="90"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="83"/>
-      <c r="O63" s="84"/>
-      <c r="P63" s="85"/>
+      <c r="N63" s="88"/>
+      <c r="O63" s="89"/>
+      <c r="P63" s="90"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="83"/>
-      <c r="S63" s="84"/>
-      <c r="T63" s="85"/>
+      <c r="R63" s="88"/>
+      <c r="S63" s="89"/>
+      <c r="T63" s="90"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="83"/>
-      <c r="W63" s="84"/>
-      <c r="X63" s="85"/>
+      <c r="V63" s="88"/>
+      <c r="W63" s="89"/>
+      <c r="X63" s="90"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="83"/>
-      <c r="AA63" s="84"/>
-      <c r="AB63" s="85"/>
+      <c r="Z63" s="88"/>
+      <c r="AA63" s="89"/>
+      <c r="AB63" s="90"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="83"/>
-      <c r="AE63" s="84"/>
-      <c r="AF63" s="85"/>
+      <c r="AD63" s="88"/>
+      <c r="AE63" s="89"/>
+      <c r="AF63" s="90"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="83"/>
-      <c r="AI63" s="84"/>
-      <c r="AJ63" s="85"/>
+      <c r="AH63" s="88"/>
+      <c r="AI63" s="89"/>
+      <c r="AJ63" s="90"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="83"/>
-      <c r="AM63" s="84"/>
-      <c r="AN63" s="85"/>
+      <c r="AL63" s="88"/>
+      <c r="AM63" s="89"/>
+      <c r="AN63" s="90"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="74"/>
-      <c r="C64" s="75"/>
-      <c r="D64" s="76"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="86"/>
+      <c r="D64" s="87"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="75"/>
-      <c r="H64" s="76"/>
+      <c r="F64" s="85"/>
+      <c r="G64" s="86"/>
+      <c r="H64" s="87"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="74"/>
-      <c r="K64" s="75"/>
-      <c r="L64" s="76"/>
+      <c r="J64" s="85"/>
+      <c r="K64" s="86"/>
+      <c r="L64" s="87"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="74"/>
-      <c r="O64" s="75"/>
-      <c r="P64" s="76"/>
+      <c r="N64" s="85"/>
+      <c r="O64" s="86"/>
+      <c r="P64" s="87"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="74"/>
-      <c r="S64" s="75"/>
-      <c r="T64" s="76"/>
+      <c r="R64" s="85"/>
+      <c r="S64" s="86"/>
+      <c r="T64" s="87"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="74"/>
-      <c r="W64" s="75"/>
-      <c r="X64" s="76"/>
+      <c r="V64" s="85"/>
+      <c r="W64" s="86"/>
+      <c r="X64" s="87"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="74"/>
-      <c r="AA64" s="75"/>
-      <c r="AB64" s="76"/>
+      <c r="Z64" s="85"/>
+      <c r="AA64" s="86"/>
+      <c r="AB64" s="87"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="74"/>
-      <c r="AE64" s="75"/>
-      <c r="AF64" s="76"/>
+      <c r="AD64" s="85"/>
+      <c r="AE64" s="86"/>
+      <c r="AF64" s="87"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="74"/>
-      <c r="AI64" s="75"/>
-      <c r="AJ64" s="76"/>
+      <c r="AH64" s="85"/>
+      <c r="AI64" s="86"/>
+      <c r="AJ64" s="87"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="74"/>
-      <c r="AM64" s="75"/>
-      <c r="AN64" s="76"/>
+      <c r="AL64" s="85"/>
+      <c r="AM64" s="86"/>
+      <c r="AN64" s="87"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5780,23 +5807,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="104" t="s">
+      <c r="N66" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="104"/>
-      <c r="P66" s="104"/>
-      <c r="Q66" s="104"/>
-      <c r="R66" s="104"/>
-      <c r="S66" s="104"/>
-      <c r="T66" s="104"/>
-      <c r="U66" s="104"/>
-      <c r="V66" s="104"/>
-      <c r="W66" s="104"/>
-      <c r="X66" s="104"/>
-      <c r="Y66" s="104"/>
-      <c r="Z66" s="104"/>
-      <c r="AA66" s="104"/>
-      <c r="AB66" s="104"/>
+      <c r="O66" s="114"/>
+      <c r="P66" s="114"/>
+      <c r="Q66" s="114"/>
+      <c r="R66" s="114"/>
+      <c r="S66" s="114"/>
+      <c r="T66" s="114"/>
+      <c r="U66" s="114"/>
+      <c r="V66" s="114"/>
+      <c r="W66" s="114"/>
+      <c r="X66" s="114"/>
+      <c r="Y66" s="114"/>
+      <c r="Z66" s="114"/>
+      <c r="AA66" s="114"/>
+      <c r="AB66" s="114"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5827,21 +5854,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="104"/>
-      <c r="O67" s="104"/>
-      <c r="P67" s="104"/>
-      <c r="Q67" s="104"/>
-      <c r="R67" s="104"/>
-      <c r="S67" s="104"/>
-      <c r="T67" s="104"/>
-      <c r="U67" s="104"/>
-      <c r="V67" s="104"/>
-      <c r="W67" s="104"/>
-      <c r="X67" s="104"/>
-      <c r="Y67" s="104"/>
-      <c r="Z67" s="104"/>
-      <c r="AA67" s="104"/>
-      <c r="AB67" s="104"/>
+      <c r="N67" s="114"/>
+      <c r="O67" s="114"/>
+      <c r="P67" s="114"/>
+      <c r="Q67" s="114"/>
+      <c r="R67" s="114"/>
+      <c r="S67" s="114"/>
+      <c r="T67" s="114"/>
+      <c r="U67" s="114"/>
+      <c r="V67" s="114"/>
+      <c r="W67" s="114"/>
+      <c r="X67" s="114"/>
+      <c r="Y67" s="114"/>
+      <c r="Z67" s="114"/>
+      <c r="AA67" s="114"/>
+      <c r="AB67" s="114"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5861,56 +5888,56 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="93" t="s">
+      <c r="B68" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C68" s="94"/>
+      <c r="C68" s="67"/>
       <c r="D68" s="60"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="93" t="s">
+      <c r="F68" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="G68" s="94"/>
+      <c r="G68" s="67"/>
       <c r="H68" s="60"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="93" t="s">
+      <c r="J68" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="K68" s="94"/>
+      <c r="K68" s="67"/>
       <c r="L68" s="60"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="62" t="s">
+      <c r="N68" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="O68" s="63"/>
+      <c r="O68" s="75"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="32"/>
-      <c r="R68" s="62" t="s">
+      <c r="R68" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="S68" s="63"/>
+      <c r="S68" s="75"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="62"/>
-      <c r="W68" s="63"/>
+      <c r="V68" s="74"/>
+      <c r="W68" s="75"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="62"/>
-      <c r="AA68" s="63"/>
+      <c r="Z68" s="74"/>
+      <c r="AA68" s="75"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="62"/>
-      <c r="AE68" s="63"/>
+      <c r="AD68" s="74"/>
+      <c r="AE68" s="75"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="62"/>
-      <c r="AI68" s="63"/>
+      <c r="AH68" s="74"/>
+      <c r="AI68" s="75"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="62" t="s">
+      <c r="AL68" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="AM68" s="63"/>
+      <c r="AM68" s="75"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5921,57 +5948,57 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="69"/>
+      <c r="C69" s="92"/>
+      <c r="D69" s="93"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="67" t="s">
+      <c r="F69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="G69" s="68"/>
-      <c r="H69" s="69"/>
+      <c r="G69" s="92"/>
+      <c r="H69" s="93"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="67" t="s">
+      <c r="J69" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="K69" s="68"/>
-      <c r="L69" s="69"/>
+      <c r="K69" s="92"/>
+      <c r="L69" s="93"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="64" t="s">
+      <c r="N69" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="O69" s="65"/>
-      <c r="P69" s="66"/>
+      <c r="O69" s="77"/>
+      <c r="P69" s="78"/>
       <c r="Q69" s="35"/>
-      <c r="R69" s="64" t="s">
+      <c r="R69" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="S69" s="65"/>
-      <c r="T69" s="66"/>
+      <c r="S69" s="77"/>
+      <c r="T69" s="78"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="64"/>
-      <c r="W69" s="65"/>
-      <c r="X69" s="66"/>
+      <c r="V69" s="76"/>
+      <c r="W69" s="77"/>
+      <c r="X69" s="78"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="64"/>
-      <c r="AA69" s="65"/>
-      <c r="AB69" s="66"/>
+      <c r="Z69" s="76"/>
+      <c r="AA69" s="77"/>
+      <c r="AB69" s="78"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="64"/>
-      <c r="AE69" s="65"/>
-      <c r="AF69" s="66"/>
+      <c r="AD69" s="76"/>
+      <c r="AE69" s="77"/>
+      <c r="AF69" s="78"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="64"/>
-      <c r="AI69" s="65"/>
-      <c r="AJ69" s="66"/>
+      <c r="AH69" s="76"/>
+      <c r="AI69" s="77"/>
+      <c r="AJ69" s="78"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="64" t="s">
+      <c r="AL69" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="AM69" s="65"/>
-      <c r="AN69" s="66"/>
+      <c r="AM69" s="77"/>
+      <c r="AN69" s="78"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5981,57 +6008,57 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="86" t="s">
+      <c r="B70" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="87"/>
-      <c r="D70" s="88"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="94"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="86" t="s">
+      <c r="F70" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="G70" s="87"/>
-      <c r="H70" s="88"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="94"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="86" t="s">
+      <c r="J70" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="K70" s="87"/>
-      <c r="L70" s="88"/>
+      <c r="K70" s="69"/>
+      <c r="L70" s="94"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="77" t="s">
+      <c r="N70" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="78"/>
-      <c r="P70" s="79"/>
+      <c r="O70" s="80"/>
+      <c r="P70" s="81"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="77" t="s">
+      <c r="R70" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="S70" s="78"/>
-      <c r="T70" s="79"/>
+      <c r="S70" s="80"/>
+      <c r="T70" s="81"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="77"/>
-      <c r="W70" s="78"/>
-      <c r="X70" s="79"/>
+      <c r="V70" s="79"/>
+      <c r="W70" s="80"/>
+      <c r="X70" s="81"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="77"/>
-      <c r="AA70" s="78"/>
-      <c r="AB70" s="79"/>
+      <c r="Z70" s="79"/>
+      <c r="AA70" s="80"/>
+      <c r="AB70" s="81"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="77"/>
-      <c r="AE70" s="78"/>
-      <c r="AF70" s="79"/>
+      <c r="AD70" s="79"/>
+      <c r="AE70" s="80"/>
+      <c r="AF70" s="81"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="77"/>
-      <c r="AI70" s="78"/>
-      <c r="AJ70" s="79"/>
+      <c r="AH70" s="79"/>
+      <c r="AI70" s="80"/>
+      <c r="AJ70" s="81"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="77" t="s">
+      <c r="AL70" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AM70" s="78"/>
-      <c r="AN70" s="79"/>
+      <c r="AM70" s="80"/>
+      <c r="AN70" s="81"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6041,57 +6068,57 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="80" t="s">
+      <c r="B71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="81"/>
-      <c r="D71" s="82"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="84"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="80" t="s">
+      <c r="F71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="81"/>
-      <c r="H71" s="82"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="84"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="80" t="s">
+      <c r="J71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="K71" s="81"/>
-      <c r="L71" s="82"/>
+      <c r="K71" s="83"/>
+      <c r="L71" s="84"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="80" t="s">
+      <c r="N71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="O71" s="81"/>
-      <c r="P71" s="82"/>
+      <c r="O71" s="83"/>
+      <c r="P71" s="84"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="80" t="s">
+      <c r="R71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="S71" s="81"/>
-      <c r="T71" s="82"/>
+      <c r="S71" s="83"/>
+      <c r="T71" s="84"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="80"/>
-      <c r="W71" s="81"/>
-      <c r="X71" s="82"/>
+      <c r="V71" s="82"/>
+      <c r="W71" s="83"/>
+      <c r="X71" s="84"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="80"/>
-      <c r="AA71" s="81"/>
-      <c r="AB71" s="82"/>
+      <c r="Z71" s="82"/>
+      <c r="AA71" s="83"/>
+      <c r="AB71" s="84"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="80"/>
-      <c r="AE71" s="81"/>
-      <c r="AF71" s="82"/>
+      <c r="AD71" s="82"/>
+      <c r="AE71" s="83"/>
+      <c r="AF71" s="84"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="80"/>
-      <c r="AI71" s="81"/>
-      <c r="AJ71" s="82"/>
+      <c r="AH71" s="82"/>
+      <c r="AI71" s="83"/>
+      <c r="AJ71" s="84"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="80" t="s">
+      <c r="AL71" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="AM71" s="81"/>
-      <c r="AN71" s="82"/>
+      <c r="AM71" s="83"/>
+      <c r="AN71" s="84"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6101,47 +6128,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="75"/>
-      <c r="D72" s="76"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="87"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
-      <c r="H72" s="76"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="87"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="74"/>
-      <c r="K72" s="75"/>
-      <c r="L72" s="76"/>
+      <c r="J72" s="85"/>
+      <c r="K72" s="86"/>
+      <c r="L72" s="87"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="74"/>
-      <c r="O72" s="75"/>
-      <c r="P72" s="76"/>
+      <c r="N72" s="85"/>
+      <c r="O72" s="86"/>
+      <c r="P72" s="87"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="74"/>
-      <c r="S72" s="75"/>
-      <c r="T72" s="76"/>
+      <c r="R72" s="85"/>
+      <c r="S72" s="86"/>
+      <c r="T72" s="87"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="74"/>
-      <c r="W72" s="75"/>
-      <c r="X72" s="76"/>
+      <c r="V72" s="85"/>
+      <c r="W72" s="86"/>
+      <c r="X72" s="87"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="74"/>
-      <c r="AA72" s="75"/>
-      <c r="AB72" s="76"/>
+      <c r="Z72" s="85"/>
+      <c r="AA72" s="86"/>
+      <c r="AB72" s="87"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="74"/>
-      <c r="AE72" s="75"/>
-      <c r="AF72" s="76"/>
+      <c r="AD72" s="85"/>
+      <c r="AE72" s="86"/>
+      <c r="AF72" s="87"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="74"/>
-      <c r="AI72" s="75"/>
-      <c r="AJ72" s="76"/>
+      <c r="AH72" s="85"/>
+      <c r="AI72" s="86"/>
+      <c r="AJ72" s="87"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="74" t="s">
+      <c r="AL72" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="AM72" s="75"/>
-      <c r="AN72" s="76"/>
+      <c r="AM72" s="86"/>
+      <c r="AN72" s="87"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6195,58 +6222,58 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="93" t="s">
+      <c r="B74" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C74" s="94"/>
+      <c r="C74" s="67"/>
       <c r="D74" s="60"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="93" t="s">
+      <c r="F74" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="G74" s="94"/>
+      <c r="G74" s="67"/>
       <c r="H74" s="60"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="93"/>
-      <c r="K74" s="94"/>
+      <c r="J74" s="66"/>
+      <c r="K74" s="67"/>
       <c r="L74" s="60"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="62" t="s">
+      <c r="N74" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="O74" s="63"/>
+      <c r="O74" s="75"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="36"/>
-      <c r="R74" s="62" t="s">
+      <c r="R74" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="S74" s="63"/>
+      <c r="S74" s="75"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="62"/>
-      <c r="W74" s="63"/>
+      <c r="V74" s="74"/>
+      <c r="W74" s="75"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="62" t="s">
+      <c r="Z74" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="AA74" s="63"/>
+      <c r="AA74" s="75"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="32"/>
-      <c r="AD74" s="62" t="s">
+      <c r="AD74" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="AE74" s="63"/>
+      <c r="AE74" s="75"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="62" t="s">
+      <c r="AH74" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="AI74" s="63"/>
+      <c r="AI74" s="75"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="62"/>
-      <c r="AM74" s="63"/>
+      <c r="AL74" s="74"/>
+      <c r="AM74" s="75"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6255,49 +6282,49 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="67" t="s">
+      <c r="B75" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="68"/>
-      <c r="D75" s="69"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="93"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="67" t="s">
+      <c r="F75" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="68"/>
-      <c r="H75" s="69"/>
+      <c r="G75" s="92"/>
+      <c r="H75" s="93"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="67"/>
-      <c r="K75" s="68"/>
-      <c r="L75" s="69"/>
+      <c r="J75" s="91"/>
+      <c r="K75" s="92"/>
+      <c r="L75" s="93"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="64"/>
-      <c r="O75" s="65"/>
-      <c r="P75" s="66"/>
+      <c r="N75" s="76"/>
+      <c r="O75" s="77"/>
+      <c r="P75" s="78"/>
       <c r="Q75" s="32"/>
-      <c r="R75" s="64"/>
-      <c r="S75" s="65"/>
-      <c r="T75" s="66"/>
+      <c r="R75" s="76"/>
+      <c r="S75" s="77"/>
+      <c r="T75" s="78"/>
       <c r="U75" s="36"/>
-      <c r="V75" s="64"/>
-      <c r="W75" s="65"/>
-      <c r="X75" s="66"/>
+      <c r="V75" s="76"/>
+      <c r="W75" s="77"/>
+      <c r="X75" s="78"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="64"/>
-      <c r="AA75" s="65"/>
-      <c r="AB75" s="66"/>
+      <c r="Z75" s="76"/>
+      <c r="AA75" s="77"/>
+      <c r="AB75" s="78"/>
       <c r="AC75" s="35"/>
-      <c r="AD75" s="64"/>
-      <c r="AE75" s="65"/>
-      <c r="AF75" s="66"/>
+      <c r="AD75" s="76"/>
+      <c r="AE75" s="77"/>
+      <c r="AF75" s="78"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="64"/>
-      <c r="AI75" s="65"/>
-      <c r="AJ75" s="66"/>
+      <c r="AH75" s="76"/>
+      <c r="AI75" s="77"/>
+      <c r="AJ75" s="78"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="64"/>
-      <c r="AM75" s="65"/>
-      <c r="AN75" s="66"/>
+      <c r="AL75" s="76"/>
+      <c r="AM75" s="77"/>
+      <c r="AN75" s="78"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6305,59 +6332,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="86" t="s">
+      <c r="B76" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="87"/>
-      <c r="D76" s="88"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="94"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="86" t="s">
+      <c r="F76" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="87"/>
-      <c r="H76" s="88"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="94"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="86"/>
-      <c r="K76" s="87"/>
-      <c r="L76" s="88"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="69"/>
+      <c r="L76" s="94"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="77" t="s">
+      <c r="N76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="78"/>
-      <c r="P76" s="79"/>
+      <c r="O76" s="80"/>
+      <c r="P76" s="81"/>
       <c r="Q76" s="31"/>
-      <c r="R76" s="77" t="s">
+      <c r="R76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="78"/>
-      <c r="T76" s="79"/>
+      <c r="S76" s="80"/>
+      <c r="T76" s="81"/>
       <c r="U76" s="36"/>
-      <c r="V76" s="77"/>
-      <c r="W76" s="78"/>
-      <c r="X76" s="79"/>
+      <c r="V76" s="79"/>
+      <c r="W76" s="80"/>
+      <c r="X76" s="81"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="77" t="s">
+      <c r="Z76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="78"/>
-      <c r="AB76" s="79"/>
+      <c r="AA76" s="80"/>
+      <c r="AB76" s="81"/>
       <c r="AC76" s="31"/>
-      <c r="AD76" s="77" t="s">
+      <c r="AD76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AE76" s="78"/>
-      <c r="AF76" s="79"/>
+      <c r="AE76" s="80"/>
+      <c r="AF76" s="81"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="77" t="s">
+      <c r="AH76" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AI76" s="78"/>
-      <c r="AJ76" s="79"/>
+      <c r="AI76" s="80"/>
+      <c r="AJ76" s="81"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="77"/>
-      <c r="AM76" s="78"/>
-      <c r="AN76" s="79"/>
+      <c r="AL76" s="79"/>
+      <c r="AM76" s="80"/>
+      <c r="AN76" s="81"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6365,59 +6392,59 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="80" t="s">
+      <c r="B77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="81"/>
-      <c r="D77" s="82"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="80" t="s">
+      <c r="F77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="81"/>
-      <c r="H77" s="82"/>
+      <c r="G77" s="83"/>
+      <c r="H77" s="84"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="81"/>
-      <c r="L77" s="82"/>
+      <c r="J77" s="82"/>
+      <c r="K77" s="83"/>
+      <c r="L77" s="84"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="101" t="s">
+      <c r="N77" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="O77" s="102"/>
-      <c r="P77" s="103"/>
+      <c r="O77" s="96"/>
+      <c r="P77" s="97"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="80" t="s">
+      <c r="R77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="81"/>
-      <c r="T77" s="82"/>
+      <c r="S77" s="83"/>
+      <c r="T77" s="84"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="80"/>
-      <c r="W77" s="81"/>
-      <c r="X77" s="82"/>
+      <c r="V77" s="82"/>
+      <c r="W77" s="83"/>
+      <c r="X77" s="84"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="80" t="s">
+      <c r="Z77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="81"/>
-      <c r="AB77" s="82"/>
+      <c r="AA77" s="83"/>
+      <c r="AB77" s="84"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="80" t="s">
+      <c r="AD77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="81"/>
-      <c r="AF77" s="82"/>
+      <c r="AE77" s="83"/>
+      <c r="AF77" s="84"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="80" t="s">
+      <c r="AH77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="81"/>
-      <c r="AJ77" s="82"/>
+      <c r="AI77" s="83"/>
+      <c r="AJ77" s="84"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="80"/>
-      <c r="AM77" s="81"/>
-      <c r="AN77" s="82"/>
+      <c r="AL77" s="82"/>
+      <c r="AM77" s="83"/>
+      <c r="AN77" s="84"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6425,47 +6452,47 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="74"/>
-      <c r="C78" s="75"/>
-      <c r="D78" s="76"/>
+      <c r="B78" s="85"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="87"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="75"/>
-      <c r="H78" s="76"/>
+      <c r="F78" s="85"/>
+      <c r="G78" s="86"/>
+      <c r="H78" s="87"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="74"/>
-      <c r="K78" s="75"/>
-      <c r="L78" s="76"/>
+      <c r="J78" s="85"/>
+      <c r="K78" s="86"/>
+      <c r="L78" s="87"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="110" t="s">
+      <c r="N78" s="98" t="s">
         <v>81</v>
       </c>
-      <c r="O78" s="111"/>
-      <c r="P78" s="112"/>
+      <c r="O78" s="99"/>
+      <c r="P78" s="100"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="74"/>
-      <c r="S78" s="75"/>
-      <c r="T78" s="76"/>
+      <c r="R78" s="85"/>
+      <c r="S78" s="86"/>
+      <c r="T78" s="87"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="74"/>
-      <c r="W78" s="75"/>
-      <c r="X78" s="76"/>
+      <c r="V78" s="85"/>
+      <c r="W78" s="86"/>
+      <c r="X78" s="87"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="74"/>
-      <c r="AA78" s="75"/>
-      <c r="AB78" s="76"/>
+      <c r="Z78" s="85"/>
+      <c r="AA78" s="86"/>
+      <c r="AB78" s="87"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="74"/>
-      <c r="AE78" s="75"/>
-      <c r="AF78" s="76"/>
+      <c r="AD78" s="85"/>
+      <c r="AE78" s="86"/>
+      <c r="AF78" s="87"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="74"/>
-      <c r="AI78" s="75"/>
-      <c r="AJ78" s="76"/>
+      <c r="AH78" s="85"/>
+      <c r="AI78" s="86"/>
+      <c r="AJ78" s="87"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="74"/>
-      <c r="AM78" s="75"/>
-      <c r="AN78" s="76"/>
+      <c r="AL78" s="85"/>
+      <c r="AM78" s="86"/>
+      <c r="AN78" s="87"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6519,56 +6546,56 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="93"/>
-      <c r="C80" s="94"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="67"/>
       <c r="D80" s="60"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="93" t="s">
+      <c r="F80" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="G80" s="94"/>
+      <c r="G80" s="67"/>
       <c r="H80" s="60"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="K80" s="94"/>
+      <c r="K80" s="67"/>
       <c r="L80" s="60"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="62" t="s">
+      <c r="N80" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="O80" s="63"/>
+      <c r="O80" s="75"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="62" t="s">
+      <c r="R80" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="S80" s="63"/>
+      <c r="S80" s="75"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="62"/>
-      <c r="W80" s="63"/>
+      <c r="V80" s="74"/>
+      <c r="W80" s="75"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="62" t="s">
+      <c r="Z80" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="AA80" s="63"/>
+      <c r="AA80" s="75"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="62" t="s">
+      <c r="AD80" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="AE80" s="63"/>
+      <c r="AE80" s="75"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="62"/>
-      <c r="AI80" s="63"/>
+      <c r="AH80" s="74"/>
+      <c r="AI80" s="75"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="62"/>
-      <c r="AM80" s="63"/>
+      <c r="AL80" s="74"/>
+      <c r="AM80" s="75"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6577,45 +6604,45 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="67"/>
-      <c r="C81" s="68"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="91"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="93"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="68"/>
-      <c r="H81" s="69"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="93"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="67"/>
-      <c r="K81" s="68"/>
-      <c r="L81" s="69"/>
+      <c r="J81" s="91"/>
+      <c r="K81" s="92"/>
+      <c r="L81" s="93"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="64"/>
-      <c r="O81" s="65"/>
-      <c r="P81" s="66"/>
+      <c r="N81" s="76"/>
+      <c r="O81" s="77"/>
+      <c r="P81" s="78"/>
       <c r="Q81" s="44"/>
-      <c r="R81" s="64"/>
-      <c r="S81" s="65"/>
-      <c r="T81" s="66"/>
+      <c r="R81" s="76"/>
+      <c r="S81" s="77"/>
+      <c r="T81" s="78"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="64"/>
-      <c r="W81" s="65"/>
-      <c r="X81" s="66"/>
+      <c r="V81" s="76"/>
+      <c r="W81" s="77"/>
+      <c r="X81" s="78"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="64"/>
-      <c r="AA81" s="65"/>
-      <c r="AB81" s="66"/>
+      <c r="Z81" s="76"/>
+      <c r="AA81" s="77"/>
+      <c r="AB81" s="78"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="64"/>
-      <c r="AE81" s="65"/>
-      <c r="AF81" s="66"/>
+      <c r="AD81" s="76"/>
+      <c r="AE81" s="77"/>
+      <c r="AF81" s="78"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="64"/>
-      <c r="AI81" s="65"/>
-      <c r="AJ81" s="66"/>
+      <c r="AH81" s="76"/>
+      <c r="AI81" s="77"/>
+      <c r="AJ81" s="78"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="64"/>
-      <c r="AM81" s="65"/>
-      <c r="AN81" s="66"/>
+      <c r="AL81" s="76"/>
+      <c r="AM81" s="77"/>
+      <c r="AN81" s="78"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6623,57 +6650,57 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="86"/>
-      <c r="C82" s="87"/>
-      <c r="D82" s="88"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="94"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="86" t="s">
+      <c r="F82" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="87"/>
-      <c r="H82" s="88"/>
+      <c r="G82" s="69"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="86" t="s">
+      <c r="J82" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="K82" s="87"/>
-      <c r="L82" s="88"/>
+      <c r="K82" s="69"/>
+      <c r="L82" s="94"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="77" t="s">
+      <c r="N82" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="78"/>
-      <c r="P82" s="79"/>
+      <c r="O82" s="80"/>
+      <c r="P82" s="81"/>
       <c r="Q82" s="44"/>
-      <c r="R82" s="77" t="s">
+      <c r="R82" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="S82" s="78"/>
-      <c r="T82" s="79"/>
+      <c r="S82" s="80"/>
+      <c r="T82" s="81"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="77"/>
-      <c r="W82" s="78"/>
-      <c r="X82" s="79"/>
+      <c r="V82" s="79"/>
+      <c r="W82" s="80"/>
+      <c r="X82" s="81"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="77" t="s">
+      <c r="Z82" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AA82" s="78"/>
-      <c r="AB82" s="79"/>
+      <c r="AA82" s="80"/>
+      <c r="AB82" s="81"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="77" t="s">
+      <c r="AD82" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="AE82" s="78"/>
-      <c r="AF82" s="79"/>
+      <c r="AE82" s="80"/>
+      <c r="AF82" s="81"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="77"/>
-      <c r="AI82" s="78"/>
-      <c r="AJ82" s="79"/>
+      <c r="AH82" s="79"/>
+      <c r="AI82" s="80"/>
+      <c r="AJ82" s="81"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="77"/>
-      <c r="AM82" s="78"/>
-      <c r="AN82" s="79"/>
+      <c r="AL82" s="79"/>
+      <c r="AM82" s="80"/>
+      <c r="AN82" s="81"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6681,57 +6708,57 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="80"/>
-      <c r="C83" s="81"/>
-      <c r="D83" s="82"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="84"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="101" t="s">
+      <c r="F83" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103"/>
+      <c r="G83" s="96"/>
+      <c r="H83" s="97"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="80" t="s">
+      <c r="J83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="81"/>
-      <c r="L83" s="82"/>
+      <c r="K83" s="83"/>
+      <c r="L83" s="84"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="80" t="s">
+      <c r="N83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="O83" s="81"/>
-      <c r="P83" s="82"/>
+      <c r="O83" s="83"/>
+      <c r="P83" s="84"/>
       <c r="Q83" s="44"/>
-      <c r="R83" s="80" t="s">
+      <c r="R83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="81"/>
-      <c r="T83" s="82"/>
+      <c r="S83" s="83"/>
+      <c r="T83" s="84"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="80"/>
-      <c r="W83" s="81"/>
-      <c r="X83" s="82"/>
+      <c r="V83" s="82"/>
+      <c r="W83" s="83"/>
+      <c r="X83" s="84"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="80" t="s">
+      <c r="Z83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="81"/>
-      <c r="AB83" s="82"/>
+      <c r="AA83" s="83"/>
+      <c r="AB83" s="84"/>
       <c r="AC83" s="43"/>
-      <c r="AD83" s="80" t="s">
+      <c r="AD83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AE83" s="81"/>
-      <c r="AF83" s="82"/>
+      <c r="AE83" s="83"/>
+      <c r="AF83" s="84"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="80"/>
-      <c r="AI83" s="81"/>
-      <c r="AJ83" s="82"/>
+      <c r="AH83" s="82"/>
+      <c r="AI83" s="83"/>
+      <c r="AJ83" s="84"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="80"/>
-      <c r="AM83" s="81"/>
-      <c r="AN83" s="82"/>
+      <c r="AL83" s="82"/>
+      <c r="AM83" s="83"/>
+      <c r="AN83" s="84"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6739,49 +6766,49 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="74"/>
-      <c r="C84" s="75"/>
-      <c r="D84" s="76"/>
+      <c r="B84" s="85"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="87"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="110" t="s">
+      <c r="F84" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="G84" s="111"/>
-      <c r="H84" s="112"/>
+      <c r="G84" s="99"/>
+      <c r="H84" s="100"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="110" t="s">
+      <c r="J84" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="111"/>
-      <c r="L84" s="112"/>
+      <c r="K84" s="99"/>
+      <c r="L84" s="100"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="74"/>
-      <c r="O84" s="75"/>
-      <c r="P84" s="76"/>
+      <c r="N84" s="85"/>
+      <c r="O84" s="86"/>
+      <c r="P84" s="87"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="74"/>
-      <c r="S84" s="75"/>
-      <c r="T84" s="76"/>
+      <c r="R84" s="85"/>
+      <c r="S84" s="86"/>
+      <c r="T84" s="87"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="74"/>
-      <c r="W84" s="75"/>
-      <c r="X84" s="76"/>
+      <c r="V84" s="85"/>
+      <c r="W84" s="86"/>
+      <c r="X84" s="87"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="74"/>
-      <c r="AA84" s="75"/>
-      <c r="AB84" s="76"/>
+      <c r="Z84" s="85"/>
+      <c r="AA84" s="86"/>
+      <c r="AB84" s="87"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="74"/>
-      <c r="AE84" s="75"/>
-      <c r="AF84" s="76"/>
+      <c r="AD84" s="85"/>
+      <c r="AE84" s="86"/>
+      <c r="AF84" s="87"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="74"/>
-      <c r="AI84" s="75"/>
-      <c r="AJ84" s="76"/>
+      <c r="AH84" s="85"/>
+      <c r="AI84" s="86"/>
+      <c r="AJ84" s="87"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="74"/>
-      <c r="AM84" s="75"/>
-      <c r="AN84" s="76"/>
+      <c r="AL84" s="85"/>
+      <c r="AM84" s="86"/>
+      <c r="AN84" s="87"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6835,52 +6862,52 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="93" t="s">
+      <c r="B86" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C86" s="94"/>
+      <c r="C86" s="67"/>
       <c r="D86" s="60"/>
       <c r="E86" s="36"/>
-      <c r="F86" s="93" t="s">
+      <c r="F86" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="G86" s="94"/>
+      <c r="G86" s="67"/>
       <c r="H86" s="60"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="93"/>
-      <c r="K86" s="94"/>
+      <c r="J86" s="66"/>
+      <c r="K86" s="67"/>
       <c r="L86" s="60"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="62" t="s">
+      <c r="N86" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="O86" s="63"/>
+      <c r="O86" s="75"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="62"/>
-      <c r="S86" s="63"/>
+      <c r="R86" s="74"/>
+      <c r="S86" s="75"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="62" t="s">
+      <c r="V86" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="W86" s="63"/>
+      <c r="W86" s="75"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="62"/>
-      <c r="AA86" s="63"/>
+      <c r="Z86" s="74"/>
+      <c r="AA86" s="75"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="62"/>
-      <c r="AE86" s="63"/>
+      <c r="AD86" s="74"/>
+      <c r="AE86" s="75"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="62"/>
-      <c r="AI86" s="63"/>
+      <c r="AH86" s="74"/>
+      <c r="AI86" s="75"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="62"/>
-      <c r="AM86" s="63"/>
+      <c r="AL86" s="74"/>
+      <c r="AM86" s="75"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6889,49 +6916,49 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="86" t="s">
+      <c r="B87" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="87"/>
+      <c r="C87" s="69"/>
       <c r="D87" s="61"/>
       <c r="E87" s="38"/>
-      <c r="F87" s="86" t="s">
+      <c r="F87" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="G87" s="87"/>
+      <c r="G87" s="69"/>
       <c r="H87" s="61"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="67"/>
-      <c r="K87" s="68"/>
-      <c r="L87" s="69"/>
+      <c r="J87" s="91"/>
+      <c r="K87" s="92"/>
+      <c r="L87" s="93"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="64"/>
-      <c r="O87" s="65"/>
-      <c r="P87" s="66"/>
+      <c r="N87" s="76"/>
+      <c r="O87" s="77"/>
+      <c r="P87" s="78"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="64"/>
-      <c r="S87" s="65"/>
-      <c r="T87" s="66"/>
+      <c r="R87" s="76"/>
+      <c r="S87" s="77"/>
+      <c r="T87" s="78"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="64"/>
-      <c r="W87" s="65"/>
-      <c r="X87" s="66"/>
+      <c r="V87" s="76"/>
+      <c r="W87" s="77"/>
+      <c r="X87" s="78"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="64"/>
-      <c r="AA87" s="65"/>
-      <c r="AB87" s="66"/>
+      <c r="Z87" s="76"/>
+      <c r="AA87" s="77"/>
+      <c r="AB87" s="78"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="64"/>
-      <c r="AE87" s="65"/>
-      <c r="AF87" s="66"/>
+      <c r="AD87" s="76"/>
+      <c r="AE87" s="77"/>
+      <c r="AF87" s="78"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="64"/>
-      <c r="AI87" s="65"/>
-      <c r="AJ87" s="66"/>
+      <c r="AH87" s="76"/>
+      <c r="AI87" s="77"/>
+      <c r="AJ87" s="78"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="64"/>
-      <c r="AM87" s="65"/>
-      <c r="AN87" s="66"/>
+      <c r="AL87" s="76"/>
+      <c r="AM87" s="77"/>
+      <c r="AN87" s="78"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6939,57 +6966,57 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="99" t="s">
+      <c r="B88" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="100"/>
+      <c r="C88" s="71"/>
       <c r="D88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E88" s="37"/>
-      <c r="F88" s="99" t="s">
+      <c r="F88" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="100"/>
+      <c r="G88" s="71"/>
       <c r="H88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I88" s="31"/>
-      <c r="J88" s="86"/>
-      <c r="K88" s="87"/>
-      <c r="L88" s="88"/>
+      <c r="J88" s="68"/>
+      <c r="K88" s="69"/>
+      <c r="L88" s="94"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="77" t="s">
+      <c r="N88" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="O88" s="78"/>
-      <c r="P88" s="79"/>
+      <c r="O88" s="80"/>
+      <c r="P88" s="81"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="77"/>
-      <c r="S88" s="78"/>
-      <c r="T88" s="79"/>
+      <c r="R88" s="79"/>
+      <c r="S88" s="80"/>
+      <c r="T88" s="81"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="77" t="s">
+      <c r="V88" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="W88" s="78"/>
-      <c r="X88" s="79"/>
+      <c r="W88" s="80"/>
+      <c r="X88" s="81"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="77"/>
-      <c r="AA88" s="78"/>
-      <c r="AB88" s="79"/>
+      <c r="Z88" s="79"/>
+      <c r="AA88" s="80"/>
+      <c r="AB88" s="81"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="77"/>
-      <c r="AE88" s="78"/>
-      <c r="AF88" s="79"/>
+      <c r="AD88" s="79"/>
+      <c r="AE88" s="80"/>
+      <c r="AF88" s="81"/>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="77"/>
-      <c r="AI88" s="78"/>
-      <c r="AJ88" s="79"/>
+      <c r="AH88" s="79"/>
+      <c r="AI88" s="80"/>
+      <c r="AJ88" s="81"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="77"/>
-      <c r="AM88" s="78"/>
-      <c r="AN88" s="79"/>
+      <c r="AL88" s="79"/>
+      <c r="AM88" s="80"/>
+      <c r="AN88" s="81"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6997,57 +7024,57 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="95" t="s">
+      <c r="B89" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="96"/>
+      <c r="C89" s="73"/>
       <c r="D89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="43"/>
-      <c r="F89" s="95" t="s">
+      <c r="F89" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="G89" s="96"/>
+      <c r="G89" s="73"/>
       <c r="H89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I89" s="31"/>
-      <c r="J89" s="80"/>
-      <c r="K89" s="81"/>
-      <c r="L89" s="82"/>
+      <c r="J89" s="82"/>
+      <c r="K89" s="83"/>
+      <c r="L89" s="84"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="101" t="s">
+      <c r="N89" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="O89" s="102"/>
-      <c r="P89" s="103"/>
+      <c r="O89" s="96"/>
+      <c r="P89" s="97"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="80"/>
-      <c r="S89" s="81"/>
-      <c r="T89" s="82"/>
+      <c r="R89" s="82"/>
+      <c r="S89" s="83"/>
+      <c r="T89" s="84"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="80" t="s">
+      <c r="V89" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="W89" s="81"/>
-      <c r="X89" s="82"/>
+      <c r="W89" s="83"/>
+      <c r="X89" s="84"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="80"/>
-      <c r="AA89" s="81"/>
-      <c r="AB89" s="82"/>
+      <c r="Z89" s="82"/>
+      <c r="AA89" s="83"/>
+      <c r="AB89" s="84"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="80"/>
-      <c r="AE89" s="81"/>
-      <c r="AF89" s="82"/>
+      <c r="AD89" s="82"/>
+      <c r="AE89" s="83"/>
+      <c r="AF89" s="84"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="80"/>
-      <c r="AI89" s="81"/>
-      <c r="AJ89" s="82"/>
+      <c r="AH89" s="82"/>
+      <c r="AI89" s="83"/>
+      <c r="AJ89" s="84"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="80"/>
-      <c r="AM89" s="81"/>
-      <c r="AN89" s="82"/>
+      <c r="AL89" s="82"/>
+      <c r="AM89" s="83"/>
+      <c r="AN89" s="84"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7055,55 +7082,55 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="70" t="s">
+      <c r="B90" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="71"/>
+      <c r="C90" s="63"/>
       <c r="D90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E90" s="43"/>
-      <c r="F90" s="70" t="s">
+      <c r="F90" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="G90" s="71"/>
+      <c r="G90" s="63"/>
       <c r="H90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I90" s="32"/>
-      <c r="J90" s="74"/>
-      <c r="K90" s="75"/>
-      <c r="L90" s="76"/>
+      <c r="J90" s="85"/>
+      <c r="K90" s="86"/>
+      <c r="L90" s="87"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="110" t="s">
+      <c r="N90" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="O90" s="111"/>
-      <c r="P90" s="112"/>
+      <c r="O90" s="99"/>
+      <c r="P90" s="100"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="74"/>
-      <c r="S90" s="75"/>
-      <c r="T90" s="76"/>
+      <c r="R90" s="85"/>
+      <c r="S90" s="86"/>
+      <c r="T90" s="87"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="74"/>
-      <c r="W90" s="75"/>
-      <c r="X90" s="76"/>
+      <c r="V90" s="85"/>
+      <c r="W90" s="86"/>
+      <c r="X90" s="87"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="74"/>
-      <c r="AA90" s="75"/>
-      <c r="AB90" s="76"/>
+      <c r="Z90" s="85"/>
+      <c r="AA90" s="86"/>
+      <c r="AB90" s="87"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="74"/>
-      <c r="AE90" s="75"/>
-      <c r="AF90" s="76"/>
+      <c r="AD90" s="85"/>
+      <c r="AE90" s="86"/>
+      <c r="AF90" s="87"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="74"/>
-      <c r="AI90" s="75"/>
-      <c r="AJ90" s="76"/>
+      <c r="AH90" s="85"/>
+      <c r="AI90" s="86"/>
+      <c r="AJ90" s="87"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="74"/>
-      <c r="AM90" s="75"/>
-      <c r="AN90" s="76"/>
+      <c r="AL90" s="85"/>
+      <c r="AM90" s="86"/>
+      <c r="AN90" s="87"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7111,18 +7138,18 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
-      <c r="B91" s="70" t="s">
+      <c r="B91" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="71"/>
+      <c r="C91" s="63"/>
       <c r="D91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="44"/>
-      <c r="F91" s="70" t="s">
+      <c r="F91" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="G91" s="71"/>
+      <c r="G91" s="63"/>
       <c r="H91" s="45" t="s">
         <v>35</v>
       </c>
@@ -7145,12 +7172,12 @@
       <c r="Y91" s="35"/>
       <c r="Z91" s="35"/>
       <c r="AA91" s="35"/>
-      <c r="AB91" s="35"/>
-      <c r="AC91" s="44"/>
+      <c r="AB91" s="142"/>
+      <c r="AC91" s="50"/>
       <c r="AD91" s="35"/>
       <c r="AE91" s="35"/>
-      <c r="AF91" s="35"/>
-      <c r="AG91" s="44"/>
+      <c r="AF91" s="142"/>
+      <c r="AG91" s="50"/>
       <c r="AH91" s="35"/>
       <c r="AI91" s="35"/>
       <c r="AJ91" s="35"/>
@@ -7165,52 +7192,52 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="70" t="s">
+      <c r="B92" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="71"/>
+      <c r="C92" s="63"/>
       <c r="D92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="44"/>
-      <c r="F92" s="70" t="s">
+      <c r="F92" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="G92" s="71"/>
+      <c r="G92" s="63"/>
       <c r="H92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I92" s="32"/>
-      <c r="J92" s="93"/>
-      <c r="K92" s="94"/>
+      <c r="J92" s="66"/>
+      <c r="K92" s="67"/>
       <c r="L92" s="60"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="62"/>
-      <c r="O92" s="63"/>
+      <c r="N92" s="74"/>
+      <c r="O92" s="75"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="36"/>
-      <c r="R92" s="62"/>
-      <c r="S92" s="63"/>
+      <c r="R92" s="74"/>
+      <c r="S92" s="75"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="62"/>
-      <c r="W92" s="63"/>
+      <c r="V92" s="74"/>
+      <c r="W92" s="75"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="62"/>
-      <c r="AA92" s="63"/>
+      <c r="Z92" s="74"/>
+      <c r="AA92" s="75"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="62"/>
-      <c r="AE92" s="63"/>
+      <c r="AD92" s="74"/>
+      <c r="AE92" s="75"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="62"/>
-      <c r="AI92" s="63"/>
+      <c r="AH92" s="74"/>
+      <c r="AI92" s="75"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="62"/>
-      <c r="AM92" s="63"/>
+      <c r="AL92" s="74"/>
+      <c r="AM92" s="75"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -7219,45 +7246,45 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="70"/>
-      <c r="C93" s="71"/>
+      <c r="B93" s="62"/>
+      <c r="C93" s="63"/>
       <c r="D93" s="45"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="70"/>
-      <c r="G93" s="71"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="45"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="67"/>
-      <c r="K93" s="68"/>
-      <c r="L93" s="69"/>
+      <c r="J93" s="91"/>
+      <c r="K93" s="92"/>
+      <c r="L93" s="93"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="64"/>
-      <c r="O93" s="65"/>
-      <c r="P93" s="66"/>
+      <c r="N93" s="76"/>
+      <c r="O93" s="77"/>
+      <c r="P93" s="78"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="64"/>
-      <c r="S93" s="65"/>
-      <c r="T93" s="66"/>
+      <c r="R93" s="76"/>
+      <c r="S93" s="77"/>
+      <c r="T93" s="78"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="64"/>
-      <c r="W93" s="65"/>
-      <c r="X93" s="66"/>
+      <c r="V93" s="76"/>
+      <c r="W93" s="77"/>
+      <c r="X93" s="78"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="64"/>
-      <c r="AA93" s="65"/>
-      <c r="AB93" s="66"/>
+      <c r="Z93" s="76"/>
+      <c r="AA93" s="77"/>
+      <c r="AB93" s="78"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="64"/>
-      <c r="AE93" s="65"/>
-      <c r="AF93" s="66"/>
+      <c r="AD93" s="76"/>
+      <c r="AE93" s="77"/>
+      <c r="AF93" s="78"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="64"/>
-      <c r="AI93" s="65"/>
-      <c r="AJ93" s="66"/>
+      <c r="AH93" s="76"/>
+      <c r="AI93" s="77"/>
+      <c r="AJ93" s="78"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="64"/>
-      <c r="AM93" s="65"/>
-      <c r="AN93" s="66"/>
+      <c r="AL93" s="76"/>
+      <c r="AM93" s="77"/>
+      <c r="AN93" s="78"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -7265,45 +7292,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="70"/>
-      <c r="C94" s="71"/>
+      <c r="B94" s="62"/>
+      <c r="C94" s="63"/>
       <c r="D94" s="45"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="70"/>
-      <c r="G94" s="71"/>
+      <c r="F94" s="62"/>
+      <c r="G94" s="63"/>
       <c r="H94" s="45"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="86"/>
-      <c r="K94" s="87"/>
-      <c r="L94" s="88"/>
+      <c r="J94" s="68"/>
+      <c r="K94" s="69"/>
+      <c r="L94" s="94"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="77"/>
-      <c r="O94" s="78"/>
-      <c r="P94" s="79"/>
+      <c r="N94" s="79"/>
+      <c r="O94" s="80"/>
+      <c r="P94" s="81"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="77"/>
-      <c r="S94" s="78"/>
-      <c r="T94" s="79"/>
+      <c r="R94" s="79"/>
+      <c r="S94" s="80"/>
+      <c r="T94" s="81"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="77"/>
-      <c r="W94" s="78"/>
-      <c r="X94" s="79"/>
+      <c r="V94" s="79"/>
+      <c r="W94" s="80"/>
+      <c r="X94" s="81"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="77"/>
-      <c r="AA94" s="78"/>
-      <c r="AB94" s="79"/>
+      <c r="Z94" s="79"/>
+      <c r="AA94" s="80"/>
+      <c r="AB94" s="81"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="77"/>
-      <c r="AE94" s="78"/>
-      <c r="AF94" s="79"/>
+      <c r="AD94" s="79"/>
+      <c r="AE94" s="80"/>
+      <c r="AF94" s="81"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="77"/>
-      <c r="AI94" s="78"/>
-      <c r="AJ94" s="79"/>
+      <c r="AH94" s="79"/>
+      <c r="AI94" s="80"/>
+      <c r="AJ94" s="81"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="77"/>
-      <c r="AM94" s="78"/>
-      <c r="AN94" s="79"/>
+      <c r="AL94" s="79"/>
+      <c r="AM94" s="80"/>
+      <c r="AN94" s="81"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7311,45 +7338,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="70"/>
-      <c r="C95" s="71"/>
+      <c r="B95" s="62"/>
+      <c r="C95" s="63"/>
       <c r="D95" s="45"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="70"/>
-      <c r="G95" s="71"/>
+      <c r="F95" s="62"/>
+      <c r="G95" s="63"/>
       <c r="H95" s="45"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="80"/>
-      <c r="K95" s="81"/>
-      <c r="L95" s="82"/>
+      <c r="J95" s="82"/>
+      <c r="K95" s="83"/>
+      <c r="L95" s="84"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="80"/>
-      <c r="O95" s="81"/>
-      <c r="P95" s="82"/>
+      <c r="N95" s="82"/>
+      <c r="O95" s="83"/>
+      <c r="P95" s="84"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="80"/>
-      <c r="S95" s="81"/>
-      <c r="T95" s="82"/>
+      <c r="R95" s="82"/>
+      <c r="S95" s="83"/>
+      <c r="T95" s="84"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="80"/>
-      <c r="W95" s="81"/>
-      <c r="X95" s="82"/>
+      <c r="V95" s="82"/>
+      <c r="W95" s="83"/>
+      <c r="X95" s="84"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="80"/>
-      <c r="AA95" s="81"/>
-      <c r="AB95" s="82"/>
+      <c r="Z95" s="82"/>
+      <c r="AA95" s="83"/>
+      <c r="AB95" s="84"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="80"/>
-      <c r="AE95" s="81"/>
-      <c r="AF95" s="82"/>
+      <c r="AD95" s="82"/>
+      <c r="AE95" s="83"/>
+      <c r="AF95" s="84"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="80"/>
-      <c r="AI95" s="81"/>
-      <c r="AJ95" s="82"/>
+      <c r="AH95" s="82"/>
+      <c r="AI95" s="83"/>
+      <c r="AJ95" s="84"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="80"/>
-      <c r="AM95" s="81"/>
-      <c r="AN95" s="82"/>
+      <c r="AL95" s="82"/>
+      <c r="AM95" s="83"/>
+      <c r="AN95" s="84"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7357,45 +7384,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="72"/>
-      <c r="C96" s="73"/>
+      <c r="B96" s="64"/>
+      <c r="C96" s="65"/>
       <c r="D96" s="42"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="72"/>
-      <c r="G96" s="73"/>
+      <c r="F96" s="64"/>
+      <c r="G96" s="65"/>
       <c r="H96" s="42"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="74"/>
-      <c r="K96" s="75"/>
-      <c r="L96" s="76"/>
+      <c r="J96" s="85"/>
+      <c r="K96" s="86"/>
+      <c r="L96" s="87"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="74"/>
-      <c r="O96" s="75"/>
-      <c r="P96" s="76"/>
+      <c r="N96" s="85"/>
+      <c r="O96" s="86"/>
+      <c r="P96" s="87"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="74"/>
-      <c r="S96" s="75"/>
-      <c r="T96" s="76"/>
+      <c r="R96" s="85"/>
+      <c r="S96" s="86"/>
+      <c r="T96" s="87"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="74"/>
-      <c r="W96" s="75"/>
-      <c r="X96" s="76"/>
+      <c r="V96" s="85"/>
+      <c r="W96" s="86"/>
+      <c r="X96" s="87"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="74"/>
-      <c r="AA96" s="75"/>
-      <c r="AB96" s="76"/>
+      <c r="Z96" s="85"/>
+      <c r="AA96" s="86"/>
+      <c r="AB96" s="87"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="74"/>
-      <c r="AE96" s="75"/>
-      <c r="AF96" s="76"/>
+      <c r="AD96" s="85"/>
+      <c r="AE96" s="86"/>
+      <c r="AF96" s="87"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="74"/>
-      <c r="AI96" s="75"/>
-      <c r="AJ96" s="76"/>
+      <c r="AH96" s="85"/>
+      <c r="AI96" s="86"/>
+      <c r="AJ96" s="87"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="74"/>
-      <c r="AM96" s="75"/>
-      <c r="AN96" s="76"/>
+      <c r="AL96" s="85"/>
+      <c r="AM96" s="86"/>
+      <c r="AN96" s="87"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7449,46 +7476,46 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="93" t="s">
+      <c r="B98" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C98" s="94"/>
+      <c r="C98" s="67"/>
       <c r="D98" s="60"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="93"/>
-      <c r="G98" s="94"/>
+      <c r="F98" s="66"/>
+      <c r="G98" s="67"/>
       <c r="H98" s="60"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="93"/>
-      <c r="K98" s="94"/>
+      <c r="J98" s="66"/>
+      <c r="K98" s="67"/>
       <c r="L98" s="60"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="62"/>
-      <c r="O98" s="63"/>
+      <c r="N98" s="74"/>
+      <c r="O98" s="75"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="62"/>
-      <c r="S98" s="63"/>
+      <c r="R98" s="74"/>
+      <c r="S98" s="75"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="62"/>
-      <c r="W98" s="63"/>
+      <c r="V98" s="74"/>
+      <c r="W98" s="75"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="62"/>
-      <c r="AA98" s="63"/>
+      <c r="Z98" s="74"/>
+      <c r="AA98" s="75"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="62"/>
-      <c r="AE98" s="63"/>
+      <c r="AD98" s="74"/>
+      <c r="AE98" s="75"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="62"/>
-      <c r="AI98" s="63"/>
+      <c r="AH98" s="74"/>
+      <c r="AI98" s="75"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="62"/>
-      <c r="AM98" s="63"/>
+      <c r="AL98" s="74"/>
+      <c r="AM98" s="75"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7497,47 +7524,47 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="67" t="s">
+      <c r="B99" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C99" s="68"/>
-      <c r="D99" s="69"/>
+      <c r="C99" s="92"/>
+      <c r="D99" s="93"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="68"/>
-      <c r="H99" s="69"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="92"/>
+      <c r="H99" s="93"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="67"/>
-      <c r="K99" s="68"/>
-      <c r="L99" s="69"/>
+      <c r="J99" s="91"/>
+      <c r="K99" s="92"/>
+      <c r="L99" s="93"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="64"/>
-      <c r="O99" s="65"/>
-      <c r="P99" s="66"/>
+      <c r="N99" s="76"/>
+      <c r="O99" s="77"/>
+      <c r="P99" s="78"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="64"/>
-      <c r="S99" s="65"/>
-      <c r="T99" s="66"/>
+      <c r="R99" s="76"/>
+      <c r="S99" s="77"/>
+      <c r="T99" s="78"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="64"/>
-      <c r="W99" s="65"/>
-      <c r="X99" s="66"/>
+      <c r="V99" s="76"/>
+      <c r="W99" s="77"/>
+      <c r="X99" s="78"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="64"/>
-      <c r="AA99" s="65"/>
-      <c r="AB99" s="66"/>
+      <c r="Z99" s="76"/>
+      <c r="AA99" s="77"/>
+      <c r="AB99" s="78"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="64"/>
-      <c r="AE99" s="65"/>
-      <c r="AF99" s="66"/>
+      <c r="AD99" s="76"/>
+      <c r="AE99" s="77"/>
+      <c r="AF99" s="78"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="64"/>
-      <c r="AI99" s="65"/>
-      <c r="AJ99" s="66"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
+      <c r="AJ99" s="78"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="64"/>
-      <c r="AM99" s="65"/>
-      <c r="AN99" s="66"/>
+      <c r="AL99" s="76"/>
+      <c r="AM99" s="77"/>
+      <c r="AN99" s="78"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7545,45 +7572,45 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="86"/>
-      <c r="C100" s="87"/>
-      <c r="D100" s="88"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="69"/>
+      <c r="D100" s="94"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="86"/>
-      <c r="G100" s="87"/>
-      <c r="H100" s="88"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="94"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="86"/>
-      <c r="K100" s="87"/>
-      <c r="L100" s="88"/>
+      <c r="J100" s="68"/>
+      <c r="K100" s="69"/>
+      <c r="L100" s="94"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="77"/>
-      <c r="O100" s="78"/>
-      <c r="P100" s="79"/>
+      <c r="N100" s="79"/>
+      <c r="O100" s="80"/>
+      <c r="P100" s="81"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="77"/>
-      <c r="S100" s="78"/>
-      <c r="T100" s="79"/>
+      <c r="R100" s="79"/>
+      <c r="S100" s="80"/>
+      <c r="T100" s="81"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="77"/>
-      <c r="W100" s="78"/>
-      <c r="X100" s="79"/>
+      <c r="V100" s="79"/>
+      <c r="W100" s="80"/>
+      <c r="X100" s="81"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="77"/>
-      <c r="AA100" s="78"/>
-      <c r="AB100" s="79"/>
+      <c r="Z100" s="79"/>
+      <c r="AA100" s="80"/>
+      <c r="AB100" s="81"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="77"/>
-      <c r="AE100" s="78"/>
-      <c r="AF100" s="79"/>
+      <c r="AD100" s="79"/>
+      <c r="AE100" s="80"/>
+      <c r="AF100" s="81"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="77"/>
-      <c r="AI100" s="78"/>
-      <c r="AJ100" s="79"/>
+      <c r="AH100" s="79"/>
+      <c r="AI100" s="80"/>
+      <c r="AJ100" s="81"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="77"/>
-      <c r="AM100" s="78"/>
-      <c r="AN100" s="79"/>
+      <c r="AL100" s="79"/>
+      <c r="AM100" s="80"/>
+      <c r="AN100" s="81"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7591,47 +7618,47 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="80" t="s">
+      <c r="B101" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="81"/>
-      <c r="D101" s="82"/>
+      <c r="C101" s="83"/>
+      <c r="D101" s="84"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="80"/>
-      <c r="G101" s="81"/>
-      <c r="H101" s="82"/>
+      <c r="F101" s="82"/>
+      <c r="G101" s="83"/>
+      <c r="H101" s="84"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="80"/>
-      <c r="K101" s="81"/>
-      <c r="L101" s="82"/>
+      <c r="J101" s="82"/>
+      <c r="K101" s="83"/>
+      <c r="L101" s="84"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="80"/>
-      <c r="O101" s="81"/>
-      <c r="P101" s="82"/>
+      <c r="N101" s="82"/>
+      <c r="O101" s="83"/>
+      <c r="P101" s="84"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="80"/>
-      <c r="S101" s="81"/>
-      <c r="T101" s="82"/>
+      <c r="R101" s="82"/>
+      <c r="S101" s="83"/>
+      <c r="T101" s="84"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="80"/>
-      <c r="W101" s="81"/>
-      <c r="X101" s="82"/>
+      <c r="V101" s="82"/>
+      <c r="W101" s="83"/>
+      <c r="X101" s="84"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="80"/>
-      <c r="AA101" s="81"/>
-      <c r="AB101" s="82"/>
+      <c r="Z101" s="82"/>
+      <c r="AA101" s="83"/>
+      <c r="AB101" s="84"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="80"/>
-      <c r="AE101" s="81"/>
-      <c r="AF101" s="82"/>
+      <c r="AD101" s="82"/>
+      <c r="AE101" s="83"/>
+      <c r="AF101" s="84"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="80"/>
-      <c r="AI101" s="81"/>
-      <c r="AJ101" s="82"/>
+      <c r="AH101" s="82"/>
+      <c r="AI101" s="83"/>
+      <c r="AJ101" s="84"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="80"/>
-      <c r="AM101" s="81"/>
-      <c r="AN101" s="82"/>
+      <c r="AL101" s="82"/>
+      <c r="AM101" s="83"/>
+      <c r="AN101" s="84"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7639,45 +7666,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="74"/>
-      <c r="C102" s="75"/>
-      <c r="D102" s="76"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="86"/>
+      <c r="D102" s="87"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="74"/>
-      <c r="G102" s="75"/>
-      <c r="H102" s="76"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="87"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="74"/>
-      <c r="K102" s="75"/>
-      <c r="L102" s="76"/>
+      <c r="J102" s="85"/>
+      <c r="K102" s="86"/>
+      <c r="L102" s="87"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="74"/>
-      <c r="O102" s="75"/>
-      <c r="P102" s="76"/>
+      <c r="N102" s="85"/>
+      <c r="O102" s="86"/>
+      <c r="P102" s="87"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="74"/>
-      <c r="S102" s="75"/>
-      <c r="T102" s="76"/>
+      <c r="R102" s="85"/>
+      <c r="S102" s="86"/>
+      <c r="T102" s="87"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="74"/>
-      <c r="W102" s="75"/>
-      <c r="X102" s="76"/>
+      <c r="V102" s="85"/>
+      <c r="W102" s="86"/>
+      <c r="X102" s="87"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="74"/>
-      <c r="AA102" s="75"/>
-      <c r="AB102" s="76"/>
+      <c r="Z102" s="85"/>
+      <c r="AA102" s="86"/>
+      <c r="AB102" s="87"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="74"/>
-      <c r="AE102" s="75"/>
-      <c r="AF102" s="76"/>
+      <c r="AD102" s="85"/>
+      <c r="AE102" s="86"/>
+      <c r="AF102" s="87"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="74"/>
-      <c r="AI102" s="75"/>
-      <c r="AJ102" s="76"/>
+      <c r="AH102" s="85"/>
+      <c r="AI102" s="86"/>
+      <c r="AJ102" s="87"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="74"/>
-      <c r="AM102" s="75"/>
-      <c r="AN102" s="76"/>
+      <c r="AL102" s="85"/>
+      <c r="AM102" s="86"/>
+      <c r="AN102" s="87"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7747,70 +7774,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="62"/>
-      <c r="C105" s="63"/>
+      <c r="B105" s="74"/>
+      <c r="C105" s="75"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="62"/>
-      <c r="G105" s="63"/>
+      <c r="F105" s="74"/>
+      <c r="G105" s="75"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="62"/>
-      <c r="K105" s="63"/>
+      <c r="J105" s="74"/>
+      <c r="K105" s="75"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="64"/>
-      <c r="C106" s="65"/>
-      <c r="D106" s="66"/>
+      <c r="B106" s="76"/>
+      <c r="C106" s="77"/>
+      <c r="D106" s="78"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="64"/>
-      <c r="G106" s="65"/>
-      <c r="H106" s="66"/>
+      <c r="F106" s="76"/>
+      <c r="G106" s="77"/>
+      <c r="H106" s="78"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="64"/>
-      <c r="K106" s="65"/>
-      <c r="L106" s="66"/>
+      <c r="J106" s="76"/>
+      <c r="K106" s="77"/>
+      <c r="L106" s="78"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="77"/>
-      <c r="C107" s="78"/>
-      <c r="D107" s="79"/>
+      <c r="B107" s="79"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="81"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="77"/>
-      <c r="G107" s="78"/>
-      <c r="H107" s="79"/>
+      <c r="F107" s="79"/>
+      <c r="G107" s="80"/>
+      <c r="H107" s="81"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="77"/>
-      <c r="K107" s="78"/>
-      <c r="L107" s="79"/>
+      <c r="J107" s="79"/>
+      <c r="K107" s="80"/>
+      <c r="L107" s="81"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="80"/>
-      <c r="C108" s="81"/>
-      <c r="D108" s="82"/>
+      <c r="B108" s="82"/>
+      <c r="C108" s="83"/>
+      <c r="D108" s="84"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="80"/>
-      <c r="G108" s="81"/>
-      <c r="H108" s="82"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="83"/>
+      <c r="H108" s="84"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="80"/>
-      <c r="K108" s="81"/>
-      <c r="L108" s="82"/>
+      <c r="J108" s="82"/>
+      <c r="K108" s="83"/>
+      <c r="L108" s="84"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="74"/>
-      <c r="C109" s="75"/>
-      <c r="D109" s="76"/>
+      <c r="B109" s="85"/>
+      <c r="C109" s="86"/>
+      <c r="D109" s="87"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="74"/>
-      <c r="G109" s="75"/>
-      <c r="H109" s="76"/>
+      <c r="F109" s="85"/>
+      <c r="G109" s="86"/>
+      <c r="H109" s="87"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="74"/>
-      <c r="K109" s="75"/>
-      <c r="L109" s="76"/>
+      <c r="J109" s="85"/>
+      <c r="K109" s="86"/>
+      <c r="L109" s="87"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7826,69 +7853,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="62"/>
-      <c r="C111" s="63"/>
+      <c r="B111" s="74"/>
+      <c r="C111" s="75"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="62"/>
-      <c r="G111" s="63"/>
+      <c r="F111" s="74"/>
+      <c r="G111" s="75"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="62"/>
-      <c r="K111" s="63"/>
+      <c r="J111" s="74"/>
+      <c r="K111" s="75"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="64"/>
-      <c r="C112" s="65"/>
-      <c r="D112" s="66"/>
+      <c r="B112" s="76"/>
+      <c r="C112" s="77"/>
+      <c r="D112" s="78"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="65"/>
-      <c r="H112" s="66"/>
+      <c r="F112" s="76"/>
+      <c r="G112" s="77"/>
+      <c r="H112" s="78"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="64"/>
-      <c r="K112" s="65"/>
-      <c r="L112" s="66"/>
+      <c r="J112" s="76"/>
+      <c r="K112" s="77"/>
+      <c r="L112" s="78"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="77"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="79"/>
+      <c r="B113" s="79"/>
+      <c r="C113" s="80"/>
+      <c r="D113" s="81"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="77"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="79"/>
+      <c r="F113" s="79"/>
+      <c r="G113" s="80"/>
+      <c r="H113" s="81"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="77"/>
-      <c r="K113" s="78"/>
-      <c r="L113" s="79"/>
+      <c r="J113" s="79"/>
+      <c r="K113" s="80"/>
+      <c r="L113" s="81"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="80"/>
-      <c r="C114" s="81"/>
-      <c r="D114" s="82"/>
+      <c r="B114" s="82"/>
+      <c r="C114" s="83"/>
+      <c r="D114" s="84"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="80"/>
-      <c r="G114" s="81"/>
-      <c r="H114" s="82"/>
+      <c r="F114" s="82"/>
+      <c r="G114" s="83"/>
+      <c r="H114" s="84"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="80"/>
-      <c r="K114" s="81"/>
-      <c r="L114" s="82"/>
+      <c r="J114" s="82"/>
+      <c r="K114" s="83"/>
+      <c r="L114" s="84"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="74"/>
-      <c r="C115" s="75"/>
-      <c r="D115" s="76"/>
+      <c r="B115" s="85"/>
+      <c r="C115" s="86"/>
+      <c r="D115" s="87"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="74"/>
-      <c r="G115" s="75"/>
-      <c r="H115" s="76"/>
+      <c r="F115" s="85"/>
+      <c r="G115" s="86"/>
+      <c r="H115" s="87"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="74"/>
-      <c r="K115" s="75"/>
-      <c r="L115" s="76"/>
+      <c r="J115" s="85"/>
+      <c r="K115" s="86"/>
+      <c r="L115" s="87"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7904,69 +7931,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="62"/>
-      <c r="C117" s="63"/>
+      <c r="B117" s="74"/>
+      <c r="C117" s="75"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="62"/>
-      <c r="G117" s="63"/>
+      <c r="F117" s="74"/>
+      <c r="G117" s="75"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="62"/>
-      <c r="K117" s="63"/>
+      <c r="J117" s="74"/>
+      <c r="K117" s="75"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="64"/>
-      <c r="C118" s="65"/>
-      <c r="D118" s="66"/>
+      <c r="B118" s="76"/>
+      <c r="C118" s="77"/>
+      <c r="D118" s="78"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="64"/>
-      <c r="G118" s="65"/>
-      <c r="H118" s="66"/>
+      <c r="F118" s="76"/>
+      <c r="G118" s="77"/>
+      <c r="H118" s="78"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="64"/>
-      <c r="K118" s="65"/>
-      <c r="L118" s="66"/>
+      <c r="J118" s="76"/>
+      <c r="K118" s="77"/>
+      <c r="L118" s="78"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="77"/>
-      <c r="C119" s="78"/>
-      <c r="D119" s="79"/>
+      <c r="B119" s="79"/>
+      <c r="C119" s="80"/>
+      <c r="D119" s="81"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="77"/>
-      <c r="G119" s="78"/>
-      <c r="H119" s="79"/>
+      <c r="F119" s="79"/>
+      <c r="G119" s="80"/>
+      <c r="H119" s="81"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="77"/>
-      <c r="K119" s="78"/>
-      <c r="L119" s="79"/>
+      <c r="J119" s="79"/>
+      <c r="K119" s="80"/>
+      <c r="L119" s="81"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="80"/>
-      <c r="C120" s="81"/>
-      <c r="D120" s="82"/>
+      <c r="B120" s="82"/>
+      <c r="C120" s="83"/>
+      <c r="D120" s="84"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="80"/>
-      <c r="G120" s="81"/>
-      <c r="H120" s="82"/>
+      <c r="F120" s="82"/>
+      <c r="G120" s="83"/>
+      <c r="H120" s="84"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="80"/>
-      <c r="K120" s="81"/>
-      <c r="L120" s="82"/>
+      <c r="J120" s="82"/>
+      <c r="K120" s="83"/>
+      <c r="L120" s="84"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="74"/>
-      <c r="C121" s="75"/>
-      <c r="D121" s="76"/>
+      <c r="B121" s="85"/>
+      <c r="C121" s="86"/>
+      <c r="D121" s="87"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="74"/>
-      <c r="G121" s="75"/>
-      <c r="H121" s="76"/>
+      <c r="F121" s="85"/>
+      <c r="G121" s="86"/>
+      <c r="H121" s="87"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="74"/>
-      <c r="K121" s="75"/>
-      <c r="L121" s="76"/>
+      <c r="J121" s="85"/>
+      <c r="K121" s="86"/>
+      <c r="L121" s="87"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -7982,69 +8009,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="62"/>
-      <c r="C123" s="63"/>
+      <c r="B123" s="74"/>
+      <c r="C123" s="75"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="62"/>
-      <c r="G123" s="63"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="75"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="62"/>
-      <c r="K123" s="63"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="75"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="64"/>
-      <c r="C124" s="65"/>
-      <c r="D124" s="66"/>
+      <c r="B124" s="76"/>
+      <c r="C124" s="77"/>
+      <c r="D124" s="78"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="64"/>
-      <c r="G124" s="65"/>
-      <c r="H124" s="66"/>
+      <c r="F124" s="76"/>
+      <c r="G124" s="77"/>
+      <c r="H124" s="78"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="64"/>
-      <c r="K124" s="65"/>
-      <c r="L124" s="66"/>
+      <c r="J124" s="76"/>
+      <c r="K124" s="77"/>
+      <c r="L124" s="78"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="77"/>
-      <c r="C125" s="78"/>
-      <c r="D125" s="79"/>
+      <c r="B125" s="79"/>
+      <c r="C125" s="80"/>
+      <c r="D125" s="81"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="77"/>
-      <c r="G125" s="78"/>
-      <c r="H125" s="79"/>
+      <c r="F125" s="79"/>
+      <c r="G125" s="80"/>
+      <c r="H125" s="81"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="77"/>
-      <c r="K125" s="78"/>
-      <c r="L125" s="79"/>
+      <c r="J125" s="79"/>
+      <c r="K125" s="80"/>
+      <c r="L125" s="81"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="80"/>
-      <c r="C126" s="81"/>
-      <c r="D126" s="82"/>
+      <c r="B126" s="82"/>
+      <c r="C126" s="83"/>
+      <c r="D126" s="84"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="80"/>
-      <c r="G126" s="81"/>
-      <c r="H126" s="82"/>
+      <c r="F126" s="82"/>
+      <c r="G126" s="83"/>
+      <c r="H126" s="84"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="80"/>
-      <c r="K126" s="81"/>
-      <c r="L126" s="82"/>
+      <c r="J126" s="82"/>
+      <c r="K126" s="83"/>
+      <c r="L126" s="84"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="74"/>
-      <c r="C127" s="75"/>
-      <c r="D127" s="76"/>
+      <c r="B127" s="85"/>
+      <c r="C127" s="86"/>
+      <c r="D127" s="87"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="74"/>
-      <c r="G127" s="75"/>
-      <c r="H127" s="76"/>
+      <c r="F127" s="85"/>
+      <c r="G127" s="86"/>
+      <c r="H127" s="87"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="74"/>
-      <c r="K127" s="75"/>
-      <c r="L127" s="76"/>
+      <c r="J127" s="85"/>
+      <c r="K127" s="86"/>
+      <c r="L127" s="87"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8060,108 +8087,898 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="62"/>
-      <c r="C129" s="63"/>
+      <c r="B129" s="74"/>
+      <c r="C129" s="75"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="62"/>
-      <c r="G129" s="63"/>
+      <c r="F129" s="74"/>
+      <c r="G129" s="75"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="62"/>
-      <c r="K129" s="63"/>
+      <c r="J129" s="74"/>
+      <c r="K129" s="75"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="64"/>
-      <c r="C130" s="65"/>
-      <c r="D130" s="66"/>
+      <c r="B130" s="76"/>
+      <c r="C130" s="77"/>
+      <c r="D130" s="78"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="64"/>
-      <c r="G130" s="65"/>
-      <c r="H130" s="66"/>
+      <c r="F130" s="76"/>
+      <c r="G130" s="77"/>
+      <c r="H130" s="78"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="64"/>
-      <c r="K130" s="65"/>
-      <c r="L130" s="66"/>
+      <c r="J130" s="76"/>
+      <c r="K130" s="77"/>
+      <c r="L130" s="78"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="77"/>
-      <c r="C131" s="78"/>
-      <c r="D131" s="79"/>
+      <c r="B131" s="79"/>
+      <c r="C131" s="80"/>
+      <c r="D131" s="81"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="77"/>
-      <c r="G131" s="78"/>
-      <c r="H131" s="79"/>
+      <c r="F131" s="79"/>
+      <c r="G131" s="80"/>
+      <c r="H131" s="81"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="77"/>
-      <c r="K131" s="78"/>
-      <c r="L131" s="79"/>
+      <c r="J131" s="79"/>
+      <c r="K131" s="80"/>
+      <c r="L131" s="81"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="80"/>
-      <c r="C132" s="81"/>
-      <c r="D132" s="82"/>
+      <c r="B132" s="82"/>
+      <c r="C132" s="83"/>
+      <c r="D132" s="84"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="80"/>
-      <c r="G132" s="81"/>
-      <c r="H132" s="82"/>
+      <c r="F132" s="82"/>
+      <c r="G132" s="83"/>
+      <c r="H132" s="84"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="80"/>
-      <c r="K132" s="81"/>
-      <c r="L132" s="82"/>
+      <c r="J132" s="82"/>
+      <c r="K132" s="83"/>
+      <c r="L132" s="84"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="74"/>
-      <c r="C133" s="75"/>
-      <c r="D133" s="76"/>
+      <c r="B133" s="85"/>
+      <c r="C133" s="86"/>
+      <c r="D133" s="87"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="74"/>
-      <c r="G133" s="75"/>
-      <c r="H133" s="76"/>
+      <c r="F133" s="85"/>
+      <c r="G133" s="86"/>
+      <c r="H133" s="87"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="74"/>
-      <c r="K133" s="75"/>
-      <c r="L133" s="76"/>
+      <c r="J133" s="85"/>
+      <c r="K133" s="86"/>
+      <c r="L133" s="87"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="883">
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="V52:X52"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="V59:X59"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="Z59:AB59"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AD38:AF38"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AD45:AF45"/>
+    <mergeCell ref="AH37:AI37"/>
+    <mergeCell ref="AH38:AJ38"/>
+    <mergeCell ref="AH43:AI43"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AH45:AJ45"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="V38:X38"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="V44:X44"/>
+    <mergeCell ref="V45:X45"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AD95:AF95"/>
     <mergeCell ref="AD96:AF96"/>
     <mergeCell ref="AH51:AI51"/>
@@ -8186,837 +9003,47 @@
     <mergeCell ref="AD52:AF52"/>
     <mergeCell ref="AD58:AE58"/>
     <mergeCell ref="AD59:AF59"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="V52:X52"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="V59:X59"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="Z59:AB59"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="AD38:AF38"/>
+    <mergeCell ref="AD43:AE43"/>
+    <mergeCell ref="AD44:AF44"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
     <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AD45:AF45"/>
-    <mergeCell ref="AH37:AI37"/>
-    <mergeCell ref="AH38:AJ38"/>
-    <mergeCell ref="AH43:AI43"/>
-    <mergeCell ref="AH44:AJ44"/>
-    <mergeCell ref="AH45:AJ45"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="V38:X38"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="V44:X44"/>
-    <mergeCell ref="V45:X45"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="Z52:AB52"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="B98:C98"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 H88:H96 H22:H27 D22:D27 D88:D96 L22:L27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V40:X41 AH14:AJ16 AL22:AM27 V95:X96 Z77:AB78 R22:S27 V77:X78 J132:L133 AL71:AN72 AL46:AN49 N77:P78 Z95:AB96 V71:X72 R95:T96 AD71:AF72 AD40:AF41 V22:W27 AH40:AJ41 AL101:AN102 N95:P96 V8:X10 Z54:AB56 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 V61:X64 R14:T16 AH34:AJ35 AL14:AN16 AL83:AN84 V46:X49 Z40:AB41 AH46:AJ49 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 Z34:AB35 Z101:AB102 Z46:AB49 AL54:AN56 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 N55:P57 AL34:AN35 V54:X56 AL61:AN64 N62:P64 R41:T43 AD54:AF56 AD77:AF78 AH22:AI27 R55:T57 N48:P50 N41:P43 R89:T90 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 V34:X35 V83:X84 AL40:AN41 N101:P102 AH54:AJ56 AH77:AJ78 R71:T72 Z71:AB72 Z83:AB84 AD34:AF35 Z22:AA27 AH83:AJ84 AD46:AF49 AH71:AJ72 AH101:AJ102 AD61:AF64 AL77:AN78 N71:P72 Z8:AB10 Z61:AB64 AL8:AN10 R62:T64 N8:P10 AH61:AJ64 R101:T102 AL95:AN96 V101:X102 R83:T84 N83:P84 V89:X90 R77:T78 AD83:AF84 F14:H16 F83:H84 J22:K27 B88:C96 J62:L64 J83:L84 F77:H78 B71:D72 B41:D43 J101:L102 B55:D57 B8:D10 J89:L90 B83:D84 F48:H50 F55:H57 J14:L16 F34:H36 B14:D16 B22:C27 F88:G96 F41:H43 F62:H64 J71:L72 F22:G27 B101:D102 F8:H10 B77:D78 B34:D36 J34:L36 B48:D50 B62:D64 F71:H72 F101:H102 J77:L78 J95:L96 J8:L10 J48:L50 J41:L43 J55:L57">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V40:X41 AH14:AJ16 AL22:AM27 V95:X96 Z77:AB78 R22:S27 V77:X78 J132:L133 AL71:AN72 AL46:AN49 N77:P78 Z95:AB96 V71:X72 R95:T96 AD71:AF72 AD40:AF41 V22:W27 AH40:AJ41 AL101:AN102 N95:P96 V8:X10 Z54:AB56 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 V61:X64 R14:T16 AH34:AJ35 AL14:AN16 AL83:AN84 V46:X49 Z40:AB41 AH46:AJ49 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 Z34:AB35 Z101:AB102 Z46:AB49 AL54:AN56 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 N55:P57 AL34:AN35 V54:X56 AL61:AN64 N62:P64 R41:T43 AD54:AF56 AD77:AF78 AH22:AI27 R55:T57 N48:P50 N41:P43 R89:T90 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 V34:X35 V83:X84 AL40:AN41 N101:P102 AH54:AJ56 AH77:AJ78 R71:T72 Z71:AB72 Z83:AB84 AD34:AF35 Z22:AA27 AH83:AJ84 AD46:AF49 AH71:AJ72 AH101:AJ102 J55:L57 AL77:AN78 N71:P72 Z8:AB10 Z61:AB64 AL8:AN10 R62:T64 N8:P10 AH61:AJ64 R101:T102 AL95:AN96 V101:X102 R83:T84 N83:P84 V89:X90 R77:T78 AD83:AF84 F14:H16 F83:H84 J22:K27 B88:C96 J62:L64 J83:L84 F77:H78 B71:D72 B41:D43 J101:L102 B55:D57 B8:D10 J89:L90 B83:D84 F48:H50 F55:H57 J14:L16 F34:H36 B14:D16 B22:C27 F88:G96 F41:H43 F62:H64 J71:L72 F22:G27 B101:D102 F8:H10 B77:D78 B34:D36 J34:L36 B48:D50 B62:D64 F71:H72 F101:H102 J77:L78 J95:L96 J8:L10 J48:L50 J41:L43 AD61:AF64">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="98">
   <si>
     <t>CUMA</t>
   </si>
@@ -306,6 +306,18 @@
   </si>
   <si>
     <t>TOPLANTI</t>
+  </si>
+  <si>
+    <t>İPTAL</t>
+  </si>
+  <si>
+    <t>E.DÖNMEZ.</t>
+  </si>
+  <si>
+    <t>Ö.KARAKUŞ.</t>
+  </si>
+  <si>
+    <t>D.A.SALTIK.</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1382,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1529,6 +1541,9 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1565,6 +1580,24 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1589,24 +1622,6 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1616,6 +1631,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1646,12 +1667,6 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1670,6 +1685,33 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1688,14 +1730,50 @@
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1703,58 +1781,22 @@
     <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1769,8 +1811,35 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="32" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="33" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2144,7 +2213,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="2" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2221,65 +2290,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="126" t="s">
+      <c r="F1" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="126" t="s">
+      <c r="J1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="126"/>
-      <c r="L1" s="127"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="132"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="130" t="s">
+      <c r="N1" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="120" t="s">
+      <c r="R1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="120" t="s">
+      <c r="V1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="120" t="s">
+      <c r="Z1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="120" t="s">
+      <c r="AD1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="120" t="s">
+      <c r="AH1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="120" t="s">
+      <c r="AL1" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="120"/>
-      <c r="AN1" s="121"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="126"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2287,74 +2356,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="128">
+      <c r="B2" s="133">
         <f>N2-3</f>
         <v>46199</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="129">
+      <c r="F2" s="134">
         <f>N2-2</f>
         <v>46200</v>
       </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="129">
+      <c r="J2" s="134">
         <f>N2-1</f>
         <v>46201</v>
       </c>
-      <c r="K2" s="129"/>
-      <c r="L2" s="132"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="137"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="131">
+      <c r="N2" s="136">
         <v>46202</v>
       </c>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="122">
+      <c r="R2" s="127">
         <f>N2+1</f>
         <v>46203</v>
       </c>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="122">
+      <c r="V2" s="127">
         <f>N2+2</f>
         <v>46204</v>
       </c>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="122">
+      <c r="Z2" s="127">
         <f>N2+3</f>
         <v>46205</v>
       </c>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="122">
+      <c r="AD2" s="127">
         <f>N2+4</f>
         <v>46206</v>
       </c>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="122">
+      <c r="AH2" s="127">
         <f>N2+5</f>
         <v>46207</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
+      <c r="AI2" s="127"/>
+      <c r="AJ2" s="127"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="122">
+      <c r="AL2" s="127">
         <f>N2+6</f>
         <v>46208</v>
       </c>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="123"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="128"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2408,47 +2477,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="114" t="s">
+      <c r="N4" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="124"/>
-      <c r="AE4" s="124"/>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="124"/>
-      <c r="AK4" s="124"/>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124"/>
+      <c r="AD4" s="129"/>
+      <c r="AE4" s="129"/>
+      <c r="AF4" s="129"/>
+      <c r="AG4" s="129"/>
+      <c r="AH4" s="129"/>
+      <c r="AI4" s="129"/>
+      <c r="AJ4" s="129"/>
+      <c r="AK4" s="129"/>
+      <c r="AL4" s="129"/>
+      <c r="AM4" s="129"/>
+      <c r="AN4" s="129"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2456,93 +2525,93 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="129"/>
+      <c r="L5" s="129"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="114"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
-      <c r="S5" s="114"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="114"/>
-      <c r="W5" s="114"/>
-      <c r="X5" s="114"/>
-      <c r="Y5" s="114"/>
-      <c r="Z5" s="114"/>
-      <c r="AA5" s="114"/>
-      <c r="AB5" s="114"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="124"/>
+      <c r="X5" s="124"/>
+      <c r="Y5" s="124"/>
+      <c r="Z5" s="124"/>
+      <c r="AA5" s="124"/>
+      <c r="AB5" s="124"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="124"/>
-      <c r="AE5" s="124"/>
-      <c r="AF5" s="124"/>
-      <c r="AG5" s="124"/>
-      <c r="AH5" s="124"/>
-      <c r="AI5" s="124"/>
-      <c r="AJ5" s="124"/>
-      <c r="AK5" s="124"/>
-      <c r="AL5" s="124"/>
-      <c r="AM5" s="124"/>
-      <c r="AN5" s="124"/>
+      <c r="AD5" s="129"/>
+      <c r="AE5" s="129"/>
+      <c r="AF5" s="129"/>
+      <c r="AG5" s="129"/>
+      <c r="AH5" s="129"/>
+      <c r="AI5" s="129"/>
+      <c r="AJ5" s="129"/>
+      <c r="AK5" s="129"/>
+      <c r="AL5" s="129"/>
+      <c r="AM5" s="129"/>
+      <c r="AN5" s="129"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="67"/>
+      <c r="C6" s="68"/>
       <c r="D6" s="60" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="39"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="68"/>
       <c r="H6" s="60"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="68"/>
       <c r="L6" s="60"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="75"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="82"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="75"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="82"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="74"/>
-      <c r="W6" s="75"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="82"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="74"/>
-      <c r="AA6" s="75"/>
+      <c r="Z6" s="81"/>
+      <c r="AA6" s="82"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="74"/>
-      <c r="AE6" s="75"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="82"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="74"/>
-      <c r="AI6" s="75"/>
+      <c r="AH6" s="81"/>
+      <c r="AI6" s="82"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="74"/>
-      <c r="AM6" s="75"/>
+      <c r="AL6" s="81"/>
+      <c r="AM6" s="82"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2554,44 +2623,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="70"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="80"/>
+      <c r="N7" s="86"/>
+      <c r="O7" s="87"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="79"/>
-      <c r="S7" s="80"/>
+      <c r="R7" s="86"/>
+      <c r="S7" s="87"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="79"/>
-      <c r="W7" s="80"/>
+      <c r="V7" s="86"/>
+      <c r="W7" s="87"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="79"/>
-      <c r="AA7" s="80"/>
+      <c r="Z7" s="86"/>
+      <c r="AA7" s="87"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="79"/>
-      <c r="AE7" s="80"/>
+      <c r="AD7" s="86"/>
+      <c r="AE7" s="87"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="79"/>
-      <c r="AI7" s="80"/>
+      <c r="AH7" s="86"/>
+      <c r="AI7" s="87"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="79"/>
-      <c r="AM7" s="80"/>
+      <c r="AL7" s="86"/>
+      <c r="AM7" s="87"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2603,47 +2672,47 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="84"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="77"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="84"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="77"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="84"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="84"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="77"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="82"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="84"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="77"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="82"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="84"/>
+      <c r="V8" s="75"/>
+      <c r="W8" s="76"/>
+      <c r="X8" s="77"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="82"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="84"/>
+      <c r="Z8" s="75"/>
+      <c r="AA8" s="76"/>
+      <c r="AB8" s="77"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="82"/>
-      <c r="AE8" s="83"/>
-      <c r="AF8" s="84"/>
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="77"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="82"/>
-      <c r="AI8" s="83"/>
-      <c r="AJ8" s="84"/>
+      <c r="AH8" s="75"/>
+      <c r="AI8" s="76"/>
+      <c r="AJ8" s="77"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="82"/>
-      <c r="AM8" s="83"/>
-      <c r="AN8" s="84"/>
+      <c r="AL8" s="75"/>
+      <c r="AM8" s="76"/>
+      <c r="AN8" s="77"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2654,94 +2723,94 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="90"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="91"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="90"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="91"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="88"/>
-      <c r="O9" s="89"/>
-      <c r="P9" s="90"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="91"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="89"/>
-      <c r="T9" s="90"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="91"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="90"/>
+      <c r="V9" s="89"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="91"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="90"/>
+      <c r="Z9" s="89"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="91"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="90"/>
+      <c r="AD9" s="89"/>
+      <c r="AE9" s="90"/>
+      <c r="AF9" s="91"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="88"/>
-      <c r="AI9" s="89"/>
-      <c r="AJ9" s="90"/>
+      <c r="AH9" s="89"/>
+      <c r="AI9" s="90"/>
+      <c r="AJ9" s="91"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="88"/>
-      <c r="AM9" s="89"/>
-      <c r="AN9" s="90"/>
+      <c r="AL9" s="89"/>
+      <c r="AM9" s="90"/>
+      <c r="AN9" s="91"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
       <c r="AQ9" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="109"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="111"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="121"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="111"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="121"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="111"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="121"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="111"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="120"/>
+      <c r="P10" s="121"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="109"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="111"/>
+      <c r="R10" s="119"/>
+      <c r="S10" s="120"/>
+      <c r="T10" s="121"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="109"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="111"/>
+      <c r="V10" s="119"/>
+      <c r="W10" s="120"/>
+      <c r="X10" s="121"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="109"/>
-      <c r="AA10" s="110"/>
-      <c r="AB10" s="111"/>
+      <c r="Z10" s="119"/>
+      <c r="AA10" s="120"/>
+      <c r="AB10" s="121"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="109"/>
-      <c r="AE10" s="110"/>
-      <c r="AF10" s="111"/>
+      <c r="AD10" s="119"/>
+      <c r="AE10" s="120"/>
+      <c r="AF10" s="121"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="109"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="111"/>
+      <c r="AH10" s="119"/>
+      <c r="AI10" s="120"/>
+      <c r="AJ10" s="121"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="109"/>
-      <c r="AM10" s="110"/>
-      <c r="AN10" s="111"/>
+      <c r="AL10" s="119"/>
+      <c r="AM10" s="120"/>
+      <c r="AN10" s="121"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2801,44 +2870,44 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="60"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="60"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="68"/>
       <c r="L12" s="60"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="75"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="82"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="75"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="82"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="75"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="82"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="75"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="82"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="74"/>
-      <c r="AE12" s="75"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="82"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="74"/>
-      <c r="AI12" s="75"/>
+      <c r="AH12" s="81"/>
+      <c r="AI12" s="82"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="74"/>
-      <c r="AM12" s="75"/>
+      <c r="AL12" s="81"/>
+      <c r="AM12" s="82"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2850,45 +2919,45 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="96"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="93"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="96"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="77"/>
-      <c r="P13" s="78"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="85"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="76"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="78"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="85"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="76"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="78"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="84"/>
+      <c r="X13" s="85"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="79"/>
-      <c r="AA13" s="80"/>
+      <c r="Z13" s="86"/>
+      <c r="AA13" s="87"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="79"/>
-      <c r="AE13" s="80"/>
+      <c r="AD13" s="86"/>
+      <c r="AE13" s="87"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="77"/>
-      <c r="AJ13" s="78"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="84"/>
+      <c r="AJ13" s="85"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="76"/>
-      <c r="AM13" s="77"/>
-      <c r="AN13" s="78"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="84"/>
+      <c r="AN13" s="85"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2899,45 +2968,45 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="82"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="84"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="77"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="84"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="77"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="84"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="77"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="84"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="77"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="82"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="84"/>
+      <c r="R14" s="75"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="77"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="82"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="84"/>
+      <c r="V14" s="75"/>
+      <c r="W14" s="76"/>
+      <c r="X14" s="77"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="82"/>
-      <c r="AA14" s="83"/>
-      <c r="AB14" s="84"/>
+      <c r="Z14" s="75"/>
+      <c r="AA14" s="76"/>
+      <c r="AB14" s="77"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="82"/>
-      <c r="AE14" s="83"/>
-      <c r="AF14" s="84"/>
+      <c r="AD14" s="75"/>
+      <c r="AE14" s="76"/>
+      <c r="AF14" s="77"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="82"/>
-      <c r="AI14" s="83"/>
-      <c r="AJ14" s="84"/>
+      <c r="AH14" s="75"/>
+      <c r="AI14" s="76"/>
+      <c r="AJ14" s="77"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="82"/>
-      <c r="AM14" s="83"/>
-      <c r="AN14" s="84"/>
+      <c r="AL14" s="75"/>
+      <c r="AM14" s="76"/>
+      <c r="AN14" s="77"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2948,45 +3017,45 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="91"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="90"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="91"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="91"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="90"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="90"/>
+      <c r="P15" s="91"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="90"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="91"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="89"/>
-      <c r="X15" s="90"/>
+      <c r="V15" s="89"/>
+      <c r="W15" s="90"/>
+      <c r="X15" s="91"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="90"/>
+      <c r="Z15" s="89"/>
+      <c r="AA15" s="90"/>
+      <c r="AB15" s="91"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="90"/>
+      <c r="AD15" s="89"/>
+      <c r="AE15" s="90"/>
+      <c r="AF15" s="91"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="88"/>
-      <c r="AI15" s="89"/>
-      <c r="AJ15" s="90"/>
+      <c r="AH15" s="89"/>
+      <c r="AI15" s="90"/>
+      <c r="AJ15" s="91"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="88"/>
-      <c r="AM15" s="89"/>
-      <c r="AN15" s="90"/>
+      <c r="AL15" s="89"/>
+      <c r="AM15" s="90"/>
+      <c r="AN15" s="91"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2997,45 +3066,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="109"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="111"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="111"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="121"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="111"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="121"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="111"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="121"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="109"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="111"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="121"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="109"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="111"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="120"/>
+      <c r="X16" s="121"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="109"/>
-      <c r="AA16" s="110"/>
-      <c r="AB16" s="111"/>
+      <c r="Z16" s="119"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="121"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="109"/>
-      <c r="AE16" s="110"/>
-      <c r="AF16" s="111"/>
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="120"/>
+      <c r="AF16" s="121"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="109"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="111"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="120"/>
+      <c r="AJ16" s="121"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="109"/>
-      <c r="AM16" s="110"/>
-      <c r="AN16" s="111"/>
+      <c r="AL16" s="119"/>
+      <c r="AM16" s="120"/>
+      <c r="AN16" s="121"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3107,23 +3176,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="114" t="s">
+      <c r="N18" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="114"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="114"/>
-      <c r="R18" s="114"/>
-      <c r="S18" s="114"/>
-      <c r="T18" s="114"/>
-      <c r="U18" s="114"/>
-      <c r="V18" s="114"/>
-      <c r="W18" s="114"/>
-      <c r="X18" s="114"/>
-      <c r="Y18" s="114"/>
-      <c r="Z18" s="114"/>
-      <c r="AA18" s="114"/>
-      <c r="AB18" s="114"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="124"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="124"/>
+      <c r="W18" s="124"/>
+      <c r="X18" s="124"/>
+      <c r="Y18" s="124"/>
+      <c r="Z18" s="124"/>
+      <c r="AA18" s="124"/>
+      <c r="AB18" s="124"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3158,21 +3227,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="114"/>
-      <c r="T19" s="114"/>
-      <c r="U19" s="114"/>
-      <c r="V19" s="114"/>
-      <c r="W19" s="114"/>
-      <c r="X19" s="114"/>
-      <c r="Y19" s="114"/>
-      <c r="Z19" s="114"/>
-      <c r="AA19" s="114"/>
-      <c r="AB19" s="114"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+      <c r="T19" s="124"/>
+      <c r="U19" s="124"/>
+      <c r="V19" s="124"/>
+      <c r="W19" s="124"/>
+      <c r="X19" s="124"/>
+      <c r="Y19" s="124"/>
+      <c r="Z19" s="124"/>
+      <c r="AA19" s="124"/>
+      <c r="AB19" s="124"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3195,75 +3264,75 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="67"/>
+      <c r="C20" s="68"/>
       <c r="D20" s="60" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="36"/>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="67"/>
+      <c r="G20" s="68"/>
       <c r="H20" s="60" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="66" t="s">
+      <c r="J20" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="K20" s="67"/>
+      <c r="K20" s="68"/>
       <c r="L20" s="60" t="s">
         <v>63</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="74" t="s">
+      <c r="N20" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="O20" s="75"/>
+      <c r="O20" s="82"/>
       <c r="P20" s="34" t="s">
         <v>47</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="112" t="s">
+      <c r="R20" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="S20" s="113"/>
+      <c r="S20" s="123"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="112" t="s">
+      <c r="V20" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="W20" s="113"/>
+      <c r="W20" s="123"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="112" t="s">
+      <c r="Z20" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="AA20" s="113"/>
+      <c r="AA20" s="123"/>
       <c r="AB20" s="56" t="s">
         <v>43</v>
       </c>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="74"/>
-      <c r="AE20" s="75"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="82"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="74"/>
-      <c r="AI20" s="75"/>
+      <c r="AH20" s="81"/>
+      <c r="AI20" s="82"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="74" t="s">
+      <c r="AL20" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="AM20" s="75"/>
-      <c r="AN20" s="34" t="s">
+      <c r="AM20" s="149"/>
+      <c r="AN20" s="59" t="s">
         <v>63</v>
       </c>
       <c r="AP20" s="46" t="s">
@@ -3276,128 +3345,128 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="69"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="68" t="s">
+      <c r="F21" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="69"/>
+      <c r="G21" s="70"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="70"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="80"/>
+      <c r="N21" s="86"/>
+      <c r="O21" s="87"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="79"/>
-      <c r="S21" s="80"/>
+      <c r="R21" s="86"/>
+      <c r="S21" s="87"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="118"/>
-      <c r="W21" s="119"/>
+      <c r="V21" s="140"/>
+      <c r="W21" s="141"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="118"/>
-      <c r="AA21" s="119"/>
+      <c r="Z21" s="140"/>
+      <c r="AA21" s="141"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="79"/>
-      <c r="AE21" s="80"/>
+      <c r="AD21" s="86"/>
+      <c r="AE21" s="87"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="79"/>
-      <c r="AI21" s="80"/>
+      <c r="AH21" s="86"/>
+      <c r="AI21" s="87"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="79"/>
-      <c r="AM21" s="80"/>
-      <c r="AN21" s="18"/>
+      <c r="AL21" s="113"/>
+      <c r="AM21" s="114"/>
+      <c r="AN21" s="156"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
       </c>
       <c r="AQ21" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="72"/>
       <c r="D22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="37"/>
-      <c r="F22" s="70" t="s">
+      <c r="F22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="71"/>
+      <c r="G22" s="72"/>
       <c r="H22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="35"/>
-      <c r="J22" s="70" t="s">
+      <c r="J22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="71"/>
+      <c r="K22" s="72"/>
       <c r="L22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="133" t="s">
+      <c r="N22" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="134"/>
+      <c r="O22" s="139"/>
       <c r="P22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="133" t="s">
+      <c r="R22" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="S22" s="134"/>
+      <c r="S22" s="139"/>
       <c r="T22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="37"/>
-      <c r="V22" s="133" t="s">
+      <c r="V22" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="134"/>
+      <c r="W22" s="139"/>
       <c r="X22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="133" t="s">
+      <c r="Z22" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="AA22" s="134"/>
+      <c r="AA22" s="139"/>
       <c r="AB22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="70"/>
-      <c r="AE22" s="71"/>
+      <c r="AD22" s="71"/>
+      <c r="AE22" s="72"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="70"/>
-      <c r="AI22" s="71"/>
+      <c r="AH22" s="71"/>
+      <c r="AI22" s="72"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="AM22" s="134"/>
-      <c r="AN22" s="41" t="s">
+      <c r="AL22" s="152" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM22" s="153"/>
+      <c r="AN22" s="160" t="s">
         <v>32</v>
       </c>
       <c r="AP22" s="46" t="s">
@@ -3410,75 +3479,75 @@
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="73"/>
+      <c r="G23" s="74"/>
       <c r="H23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="43"/>
-      <c r="J23" s="72" t="s">
+      <c r="J23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="73"/>
+      <c r="K23" s="74"/>
       <c r="L23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="72" t="s">
+      <c r="N23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="73"/>
+      <c r="O23" s="74"/>
       <c r="P23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q23" s="43"/>
-      <c r="R23" s="72" t="s">
+      <c r="R23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="73"/>
+      <c r="S23" s="74"/>
       <c r="T23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U23" s="43"/>
-      <c r="V23" s="72" t="s">
+      <c r="V23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="73"/>
+      <c r="W23" s="74"/>
       <c r="X23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="72" t="s">
+      <c r="Z23" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AA23" s="73"/>
+      <c r="AA23" s="74"/>
       <c r="AB23" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="73"/>
+      <c r="AD23" s="73"/>
+      <c r="AE23" s="74"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="73"/>
+      <c r="AH23" s="73"/>
+      <c r="AI23" s="74"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM23" s="73"/>
-      <c r="AN23" s="45" t="s">
+      <c r="AL23" s="154" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM23" s="155"/>
+      <c r="AN23" s="161" t="s">
         <v>33</v>
       </c>
       <c r="AP23" s="46" t="s">
@@ -3491,75 +3560,75 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="63"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="63"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I24" s="44"/>
-      <c r="J24" s="62" t="s">
+      <c r="J24" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="63"/>
+      <c r="K24" s="64"/>
       <c r="L24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="62" t="s">
+      <c r="N24" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="O24" s="63"/>
+      <c r="O24" s="64"/>
       <c r="P24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q24" s="43"/>
-      <c r="R24" s="62" t="s">
+      <c r="R24" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="S24" s="63"/>
+      <c r="S24" s="64"/>
       <c r="T24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="44"/>
-      <c r="V24" s="62" t="s">
+      <c r="V24" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="W24" s="63"/>
+      <c r="W24" s="64"/>
       <c r="X24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="62" t="s">
+      <c r="Z24" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="AA24" s="63"/>
+      <c r="AA24" s="64"/>
       <c r="AB24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="62"/>
-      <c r="AE24" s="63"/>
+      <c r="AD24" s="63"/>
+      <c r="AE24" s="64"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="63"/>
+      <c r="AH24" s="63"/>
+      <c r="AI24" s="64"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="62" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM24" s="63"/>
-      <c r="AN24" s="45" t="s">
+      <c r="AL24" s="150" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM24" s="151"/>
+      <c r="AN24" s="161" t="s">
         <v>34</v>
       </c>
       <c r="AP24" s="46" t="s">
@@ -3567,80 +3636,80 @@
       </c>
       <c r="AQ24" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="63"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="140" t="s">
+      <c r="F25" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="141"/>
+      <c r="G25" s="151"/>
       <c r="H25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="44"/>
-      <c r="J25" s="62" t="s">
+      <c r="J25" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="63"/>
+      <c r="K25" s="64"/>
       <c r="L25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="62" t="s">
+      <c r="N25" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="O25" s="63"/>
+      <c r="O25" s="64"/>
       <c r="P25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q25" s="44"/>
-      <c r="R25" s="62" t="s">
+      <c r="R25" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="S25" s="63"/>
+      <c r="S25" s="64"/>
       <c r="T25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="44"/>
-      <c r="V25" s="62" t="s">
+      <c r="V25" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="W25" s="63"/>
+      <c r="W25" s="64"/>
       <c r="X25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="62" t="s">
+      <c r="Z25" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="AA25" s="63"/>
+      <c r="AA25" s="64"/>
       <c r="AB25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="62"/>
-      <c r="AE25" s="63"/>
+      <c r="AD25" s="63"/>
+      <c r="AE25" s="64"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="63"/>
+      <c r="AH25" s="63"/>
+      <c r="AI25" s="64"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM25" s="63"/>
-      <c r="AN25" s="45" t="s">
+      <c r="AL25" s="150" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM25" s="151"/>
+      <c r="AN25" s="161" t="s">
         <v>35</v>
       </c>
       <c r="AP25" s="46" t="s">
@@ -3653,75 +3722,75 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="63"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="63"/>
+      <c r="G26" s="64"/>
       <c r="H26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I26" s="44"/>
-      <c r="J26" s="62" t="s">
+      <c r="J26" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="63"/>
+      <c r="K26" s="64"/>
       <c r="L26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="62" t="s">
+      <c r="N26" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="63"/>
+      <c r="O26" s="64"/>
       <c r="P26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q26" s="44"/>
-      <c r="R26" s="62" t="s">
+      <c r="R26" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="S26" s="63"/>
+      <c r="S26" s="64"/>
       <c r="T26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="44"/>
-      <c r="V26" s="62" t="s">
+      <c r="V26" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="W26" s="63"/>
+      <c r="W26" s="64"/>
       <c r="X26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="62" t="s">
+      <c r="Z26" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="AA26" s="63"/>
+      <c r="AA26" s="64"/>
       <c r="AB26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="62"/>
-      <c r="AE26" s="63"/>
+      <c r="AD26" s="63"/>
+      <c r="AE26" s="64"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="63"/>
+      <c r="AH26" s="63"/>
+      <c r="AI26" s="64"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM26" s="63"/>
-      <c r="AN26" s="45" t="s">
+      <c r="AL26" s="150" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM26" s="151"/>
+      <c r="AN26" s="161" t="s">
         <v>35</v>
       </c>
       <c r="AP26" s="46" t="s">
@@ -3734,51 +3803,51 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="64"/>
-      <c r="C27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="66"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="66"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="66"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="64"/>
-      <c r="S27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="66"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="64"/>
-      <c r="W27" s="65"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="66"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="64"/>
-      <c r="AA27" s="65"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="66"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="64"/>
-      <c r="AE27" s="65"/>
+      <c r="AD27" s="65"/>
+      <c r="AE27" s="66"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="64"/>
-      <c r="AI27" s="65"/>
+      <c r="AH27" s="65"/>
+      <c r="AI27" s="66"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="64"/>
-      <c r="AM27" s="65"/>
-      <c r="AN27" s="42"/>
+      <c r="AL27" s="157"/>
+      <c r="AM27" s="158"/>
+      <c r="AN27" s="159"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
       </c>
       <c r="AQ27" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR27" s="30"/>
     </row>
@@ -3827,7 +3896,7 @@
       </c>
       <c r="AQ28" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR28" s="30"/>
     </row>
@@ -3844,23 +3913,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="114" t="s">
+      <c r="N29" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="114"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="114"/>
-      <c r="R29" s="114"/>
-      <c r="S29" s="114"/>
-      <c r="T29" s="114"/>
-      <c r="U29" s="114"/>
-      <c r="V29" s="114"/>
-      <c r="W29" s="114"/>
-      <c r="X29" s="114"/>
-      <c r="Y29" s="114"/>
-      <c r="Z29" s="114"/>
-      <c r="AA29" s="114"/>
-      <c r="AB29" s="114"/>
+      <c r="O29" s="124"/>
+      <c r="P29" s="124"/>
+      <c r="Q29" s="124"/>
+      <c r="R29" s="124"/>
+      <c r="S29" s="124"/>
+      <c r="T29" s="124"/>
+      <c r="U29" s="124"/>
+      <c r="V29" s="124"/>
+      <c r="W29" s="124"/>
+      <c r="X29" s="124"/>
+      <c r="Y29" s="124"/>
+      <c r="Z29" s="124"/>
+      <c r="AA29" s="124"/>
+      <c r="AB29" s="124"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3878,7 +3947,7 @@
       </c>
       <c r="AQ29" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR29" s="30"/>
     </row>
@@ -3895,21 +3964,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="114"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="114"/>
-      <c r="Q30" s="114"/>
-      <c r="R30" s="114"/>
-      <c r="S30" s="114"/>
-      <c r="T30" s="114"/>
-      <c r="U30" s="114"/>
-      <c r="V30" s="114"/>
-      <c r="W30" s="114"/>
-      <c r="X30" s="114"/>
-      <c r="Y30" s="114"/>
-      <c r="Z30" s="114"/>
-      <c r="AA30" s="114"/>
-      <c r="AB30" s="114"/>
+      <c r="N30" s="124"/>
+      <c r="O30" s="124"/>
+      <c r="P30" s="124"/>
+      <c r="Q30" s="124"/>
+      <c r="R30" s="124"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="124"/>
+      <c r="U30" s="124"/>
+      <c r="V30" s="124"/>
+      <c r="W30" s="124"/>
+      <c r="X30" s="124"/>
+      <c r="Y30" s="124"/>
+      <c r="Z30" s="124"/>
+      <c r="AA30" s="124"/>
+      <c r="AB30" s="124"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3932,240 +4001,240 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="67"/>
+      <c r="C31" s="68"/>
       <c r="D31" s="60"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="66" t="s">
+      <c r="F31" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="67"/>
+      <c r="G31" s="68"/>
       <c r="H31" s="60"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="66" t="s">
+      <c r="J31" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="67"/>
+      <c r="K31" s="68"/>
       <c r="L31" s="60"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="74" t="s">
+      <c r="N31" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="O31" s="75"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="75"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="82"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="74" t="s">
+      <c r="V31" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="W31" s="75"/>
+      <c r="W31" s="82"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="74" t="s">
+      <c r="Z31" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AA31" s="75"/>
+      <c r="AA31" s="82"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="74" t="s">
+      <c r="AD31" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE31" s="75"/>
+      <c r="AE31" s="82"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="74" t="s">
+      <c r="AH31" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI31" s="75"/>
+      <c r="AI31" s="82"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="74" t="s">
+      <c r="AL31" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM31" s="75"/>
+      <c r="AM31" s="82"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="92"/>
-      <c r="D32" s="93"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="91" t="s">
+      <c r="F32" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="92"/>
-      <c r="H32" s="93"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="96"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="91" t="s">
+      <c r="J32" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="92"/>
-      <c r="L32" s="93"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="96"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="76" t="s">
+      <c r="N32" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="O32" s="77"/>
-      <c r="P32" s="78"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="85"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="76"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="78"/>
+      <c r="R32" s="83"/>
+      <c r="S32" s="84"/>
+      <c r="T32" s="85"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="76" t="s">
+      <c r="V32" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="W32" s="77"/>
-      <c r="X32" s="78"/>
+      <c r="W32" s="84"/>
+      <c r="X32" s="85"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="76" t="s">
+      <c r="Z32" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AA32" s="77"/>
-      <c r="AB32" s="78"/>
+      <c r="AA32" s="84"/>
+      <c r="AB32" s="85"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="76" t="s">
+      <c r="AD32" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AE32" s="77"/>
-      <c r="AF32" s="78"/>
+      <c r="AE32" s="84"/>
+      <c r="AF32" s="85"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="76" t="s">
+      <c r="AH32" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AI32" s="77"/>
-      <c r="AJ32" s="78"/>
+      <c r="AI32" s="84"/>
+      <c r="AJ32" s="85"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="76" t="s">
+      <c r="AL32" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM32" s="77"/>
-      <c r="AN32" s="78"/>
+      <c r="AM32" s="84"/>
+      <c r="AN32" s="85"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="68"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="94"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="97"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="94"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="97"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="94"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="97"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="81"/>
+      <c r="N33" s="86"/>
+      <c r="O33" s="87"/>
+      <c r="P33" s="88"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="79"/>
-      <c r="S33" s="80"/>
-      <c r="T33" s="81"/>
+      <c r="R33" s="86"/>
+      <c r="S33" s="87"/>
+      <c r="T33" s="88"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="79" t="s">
+      <c r="V33" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="W33" s="80"/>
-      <c r="X33" s="81"/>
+      <c r="W33" s="87"/>
+      <c r="X33" s="88"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="79" t="s">
+      <c r="Z33" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="AA33" s="80"/>
-      <c r="AB33" s="81"/>
+      <c r="AA33" s="87"/>
+      <c r="AB33" s="88"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="79" t="s">
+      <c r="AD33" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="AE33" s="80"/>
-      <c r="AF33" s="81"/>
+      <c r="AE33" s="87"/>
+      <c r="AF33" s="88"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="79" t="s">
+      <c r="AH33" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="AI33" s="80"/>
-      <c r="AJ33" s="81"/>
+      <c r="AI33" s="87"/>
+      <c r="AJ33" s="88"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="79" t="s">
+      <c r="AL33" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="AM33" s="80"/>
-      <c r="AN33" s="81"/>
+      <c r="AM33" s="87"/>
+      <c r="AN33" s="88"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="89"/>
-      <c r="D34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="91"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="88" t="s">
+      <c r="F34" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="91"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="88" t="s">
+      <c r="J34" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="91"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="82" t="s">
+      <c r="N34" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="83"/>
-      <c r="P34" s="84"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="77"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="84"/>
+      <c r="R34" s="75"/>
+      <c r="S34" s="76"/>
+      <c r="T34" s="77"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="82" t="s">
+      <c r="V34" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="83"/>
-      <c r="X34" s="84"/>
+      <c r="W34" s="76"/>
+      <c r="X34" s="77"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="82" t="s">
+      <c r="Z34" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="83"/>
-      <c r="AB34" s="84"/>
+      <c r="AA34" s="76"/>
+      <c r="AB34" s="77"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="82" t="s">
+      <c r="AD34" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="AE34" s="83"/>
-      <c r="AF34" s="84"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="77"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="82" t="s">
+      <c r="AH34" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="AI34" s="83"/>
-      <c r="AJ34" s="84"/>
+      <c r="AI34" s="76"/>
+      <c r="AJ34" s="77"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="82" t="s">
+      <c r="AL34" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="AM34" s="83"/>
-      <c r="AN34" s="84"/>
+      <c r="AM34" s="76"/>
+      <c r="AN34" s="77"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -4173,90 +4242,90 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="88" t="s">
+      <c r="B35" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="89"/>
-      <c r="D35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="91"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="88" t="s">
+      <c r="F35" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="89"/>
-      <c r="H35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="91"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="88" t="s">
+      <c r="J35" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="89"/>
-      <c r="L35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="91"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="88" t="s">
+      <c r="N35" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="O35" s="89"/>
-      <c r="P35" s="90"/>
+      <c r="O35" s="90"/>
+      <c r="P35" s="91"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="88"/>
-      <c r="S35" s="89"/>
-      <c r="T35" s="90"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="91"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="85" t="s">
+      <c r="V35" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="86"/>
-      <c r="X35" s="87"/>
+      <c r="W35" s="79"/>
+      <c r="X35" s="80"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="85" t="s">
+      <c r="Z35" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="86"/>
-      <c r="AB35" s="87"/>
+      <c r="AA35" s="79"/>
+      <c r="AB35" s="80"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="85" t="s">
+      <c r="AD35" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="86"/>
-      <c r="AF35" s="87"/>
+      <c r="AE35" s="79"/>
+      <c r="AF35" s="80"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="85" t="s">
+      <c r="AH35" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AI35" s="86"/>
-      <c r="AJ35" s="87"/>
+      <c r="AI35" s="79"/>
+      <c r="AJ35" s="80"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="85" t="s">
+      <c r="AL35" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AM35" s="86"/>
-      <c r="AN35" s="87"/>
+      <c r="AM35" s="79"/>
+      <c r="AN35" s="80"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="87"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="80"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="87"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="80"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="87"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="80"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="85" t="s">
+      <c r="N36" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="O36" s="86"/>
-      <c r="P36" s="87"/>
+      <c r="O36" s="79"/>
+      <c r="P36" s="80"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="85"/>
-      <c r="S36" s="86"/>
-      <c r="T36" s="87"/>
+      <c r="R36" s="78"/>
+      <c r="S36" s="79"/>
+      <c r="T36" s="80"/>
       <c r="U36" s="40"/>
       <c r="V36" s="35"/>
       <c r="W36" s="35"/>
@@ -4304,34 +4373,34 @@
       <c r="S37" s="35"/>
       <c r="T37" s="35"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="74" t="s">
+      <c r="V37" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="W37" s="75"/>
+      <c r="W37" s="82"/>
       <c r="X37" s="34"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="74" t="s">
+      <c r="Z37" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AA37" s="75"/>
+      <c r="AA37" s="82"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="36"/>
-      <c r="AD37" s="74" t="s">
+      <c r="AD37" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE37" s="75"/>
+      <c r="AE37" s="82"/>
       <c r="AF37" s="34"/>
       <c r="AG37" s="50"/>
-      <c r="AH37" s="74" t="s">
+      <c r="AH37" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI37" s="75"/>
+      <c r="AI37" s="82"/>
       <c r="AJ37" s="34"/>
       <c r="AK37" s="50"/>
-      <c r="AL37" s="74" t="s">
+      <c r="AL37" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM37" s="75"/>
+      <c r="AM37" s="82"/>
       <c r="AN37" s="34"/>
       <c r="AO37" s="31"/>
       <c r="AP37" s="22"/>
@@ -4340,63 +4409,63 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="67"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="68"/>
       <c r="D38" s="60"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="101" t="s">
+      <c r="F38" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="102"/>
+      <c r="G38" s="93"/>
       <c r="H38" s="55" t="s">
         <v>52</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="66" t="s">
+      <c r="J38" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="K38" s="67"/>
+      <c r="K38" s="68"/>
       <c r="L38" s="60"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="138" t="s">
+      <c r="N38" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="O38" s="139"/>
+      <c r="O38" s="149"/>
       <c r="P38" s="59"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="74"/>
-      <c r="S38" s="75"/>
+      <c r="R38" s="81"/>
+      <c r="S38" s="82"/>
       <c r="T38" s="34"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="76" t="s">
+      <c r="V38" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="W38" s="77"/>
-      <c r="X38" s="78"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="85"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="76" t="s">
+      <c r="Z38" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="78"/>
+      <c r="AA38" s="84"/>
+      <c r="AB38" s="85"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="76" t="s">
+      <c r="AD38" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AE38" s="77"/>
-      <c r="AF38" s="78"/>
+      <c r="AE38" s="84"/>
+      <c r="AF38" s="85"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="76" t="s">
+      <c r="AH38" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AI38" s="77"/>
-      <c r="AJ38" s="78"/>
+      <c r="AI38" s="84"/>
+      <c r="AJ38" s="85"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="76" t="s">
+      <c r="AL38" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="77"/>
-      <c r="AN38" s="78"/>
+      <c r="AM38" s="84"/>
+      <c r="AN38" s="85"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
       <c r="AQ38" s="31"/>
@@ -4404,61 +4473,61 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="91"/>
-      <c r="C39" s="92"/>
-      <c r="D39" s="93"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="96"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="91" t="s">
+      <c r="F39" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="92"/>
-      <c r="H39" s="93"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="96"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="91" t="s">
+      <c r="J39" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="K39" s="92"/>
-      <c r="L39" s="93"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="96"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="135" t="s">
+      <c r="N39" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="O39" s="136"/>
-      <c r="P39" s="137"/>
+      <c r="O39" s="111"/>
+      <c r="P39" s="112"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="78"/>
+      <c r="R39" s="83"/>
+      <c r="S39" s="84"/>
+      <c r="T39" s="85"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="79" t="s">
+      <c r="V39" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="W39" s="80"/>
-      <c r="X39" s="81"/>
+      <c r="W39" s="87"/>
+      <c r="X39" s="88"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="79" t="s">
+      <c r="Z39" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AA39" s="80"/>
-      <c r="AB39" s="81"/>
+      <c r="AA39" s="87"/>
+      <c r="AB39" s="88"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="79" t="s">
+      <c r="AD39" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AE39" s="80"/>
-      <c r="AF39" s="81"/>
+      <c r="AE39" s="87"/>
+      <c r="AF39" s="88"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="79" t="s">
+      <c r="AH39" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AI39" s="80"/>
-      <c r="AJ39" s="81"/>
+      <c r="AI39" s="87"/>
+      <c r="AJ39" s="88"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="79" t="s">
+      <c r="AL39" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AM39" s="80"/>
-      <c r="AN39" s="81"/>
+      <c r="AM39" s="87"/>
+      <c r="AN39" s="88"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4466,57 +4535,57 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="94"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="94"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="97"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="94"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="97"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="115" t="s">
+      <c r="N40" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="O40" s="116"/>
-      <c r="P40" s="117"/>
+      <c r="O40" s="114"/>
+      <c r="P40" s="115"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="81"/>
+      <c r="R40" s="86"/>
+      <c r="S40" s="87"/>
+      <c r="T40" s="88"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="82" t="s">
+      <c r="V40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="83"/>
-      <c r="X40" s="84"/>
+      <c r="W40" s="76"/>
+      <c r="X40" s="77"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="82" t="s">
+      <c r="Z40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="83"/>
-      <c r="AB40" s="84"/>
+      <c r="AA40" s="76"/>
+      <c r="AB40" s="77"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="82" t="s">
+      <c r="AD40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="AE40" s="83"/>
-      <c r="AF40" s="84"/>
+      <c r="AE40" s="76"/>
+      <c r="AF40" s="77"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="82" t="s">
+      <c r="AH40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="AI40" s="83"/>
-      <c r="AJ40" s="84"/>
+      <c r="AI40" s="76"/>
+      <c r="AJ40" s="77"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="82" t="s">
+      <c r="AL40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="AM40" s="83"/>
-      <c r="AN40" s="84"/>
+      <c r="AM40" s="76"/>
+      <c r="AN40" s="77"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4524,61 +4593,61 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="88"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="90"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="91"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="82" t="s">
+      <c r="F41" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="83"/>
-      <c r="H41" s="84"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="77"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="95" t="s">
+      <c r="J41" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="K41" s="96"/>
-      <c r="L41" s="97"/>
+      <c r="K41" s="99"/>
+      <c r="L41" s="100"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="106" t="s">
+      <c r="N41" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="O41" s="107"/>
-      <c r="P41" s="108"/>
+      <c r="O41" s="108"/>
+      <c r="P41" s="109"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="82"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="84"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="76"/>
+      <c r="T41" s="77"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="85" t="s">
+      <c r="V41" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="86"/>
-      <c r="X41" s="87"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="80"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="85" t="s">
+      <c r="Z41" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="86"/>
-      <c r="AB41" s="87"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="80"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="85" t="s">
+      <c r="AD41" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="AE41" s="86"/>
-      <c r="AF41" s="87"/>
+      <c r="AE41" s="79"/>
+      <c r="AF41" s="80"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="85" t="s">
+      <c r="AH41" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="AI41" s="86"/>
-      <c r="AJ41" s="87"/>
+      <c r="AI41" s="79"/>
+      <c r="AJ41" s="80"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="85" t="s">
+      <c r="AL41" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="AM41" s="86"/>
-      <c r="AN41" s="87"/>
+      <c r="AM41" s="79"/>
+      <c r="AN41" s="80"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4586,31 +4655,31 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="88"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="90"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="91"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="88" t="s">
+      <c r="F42" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="89"/>
-      <c r="H42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="91"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="88" t="s">
+      <c r="J42" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="89"/>
-      <c r="L42" s="90"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="91"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="103" t="s">
+      <c r="N42" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="O42" s="104"/>
-      <c r="P42" s="105"/>
+      <c r="O42" s="105"/>
+      <c r="P42" s="106"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="88"/>
-      <c r="S42" s="89"/>
-      <c r="T42" s="90"/>
+      <c r="R42" s="89"/>
+      <c r="S42" s="90"/>
+      <c r="T42" s="91"/>
       <c r="U42" s="44"/>
       <c r="V42" s="35"/>
       <c r="W42" s="35"/>
@@ -4638,56 +4707,56 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="87"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="80"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="87"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="80"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="98" t="s">
+      <c r="J43" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="K43" s="99"/>
-      <c r="L43" s="100"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="103"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="98"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="100"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="102"/>
+      <c r="P43" s="103"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="86"/>
-      <c r="T43" s="87"/>
+      <c r="R43" s="78"/>
+      <c r="S43" s="79"/>
+      <c r="T43" s="80"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="74" t="s">
+      <c r="V43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="W43" s="75"/>
+      <c r="W43" s="82"/>
       <c r="X43" s="34"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="74" t="s">
+      <c r="Z43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AA43" s="75"/>
+      <c r="AA43" s="82"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="74" t="s">
+      <c r="AD43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE43" s="75"/>
+      <c r="AE43" s="82"/>
       <c r="AF43" s="34"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="74" t="s">
+      <c r="AH43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI43" s="75"/>
+      <c r="AI43" s="82"/>
       <c r="AJ43" s="34"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="74" t="s">
+      <c r="AL43" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM43" s="75"/>
+      <c r="AM43" s="82"/>
       <c r="AN43" s="34"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
@@ -4716,35 +4785,35 @@
       <c r="S44" s="35"/>
       <c r="T44" s="35"/>
       <c r="U44" s="36"/>
-      <c r="V44" s="76" t="s">
+      <c r="V44" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="W44" s="77"/>
-      <c r="X44" s="78"/>
+      <c r="W44" s="84"/>
+      <c r="X44" s="85"/>
       <c r="Y44" s="36"/>
-      <c r="Z44" s="76" t="s">
+      <c r="Z44" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AA44" s="77"/>
-      <c r="AB44" s="78"/>
+      <c r="AA44" s="84"/>
+      <c r="AB44" s="85"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="76" t="s">
+      <c r="AD44" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AE44" s="77"/>
-      <c r="AF44" s="78"/>
+      <c r="AE44" s="84"/>
+      <c r="AF44" s="85"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="76" t="s">
+      <c r="AH44" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AI44" s="77"/>
-      <c r="AJ44" s="78"/>
+      <c r="AI44" s="84"/>
+      <c r="AJ44" s="85"/>
       <c r="AK44" s="50"/>
-      <c r="AL44" s="76" t="s">
+      <c r="AL44" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM44" s="77"/>
-      <c r="AN44" s="78"/>
+      <c r="AM44" s="84"/>
+      <c r="AN44" s="85"/>
       <c r="AO44" s="31"/>
       <c r="AP44" s="31"/>
       <c r="AQ44" s="31"/>
@@ -4752,57 +4821,57 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="67"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="68"/>
       <c r="D45" s="60"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="68"/>
       <c r="H45" s="60"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="101" t="s">
+      <c r="J45" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="K45" s="102"/>
+      <c r="K45" s="93"/>
       <c r="L45" s="55"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="75"/>
+      <c r="N45" s="81"/>
+      <c r="O45" s="82"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="74"/>
-      <c r="S45" s="75"/>
+      <c r="R45" s="81"/>
+      <c r="S45" s="82"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="79" t="s">
+      <c r="V45" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="W45" s="80"/>
-      <c r="X45" s="81"/>
+      <c r="W45" s="87"/>
+      <c r="X45" s="88"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="79" t="s">
+      <c r="Z45" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AA45" s="80"/>
-      <c r="AB45" s="81"/>
+      <c r="AA45" s="87"/>
+      <c r="AB45" s="88"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="79" t="s">
+      <c r="AD45" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AE45" s="80"/>
-      <c r="AF45" s="81"/>
+      <c r="AE45" s="87"/>
+      <c r="AF45" s="88"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="79" t="s">
+      <c r="AH45" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AI45" s="80"/>
-      <c r="AJ45" s="81"/>
+      <c r="AI45" s="87"/>
+      <c r="AJ45" s="88"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="79" t="s">
+      <c r="AL45" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AM45" s="80"/>
-      <c r="AN45" s="81"/>
+      <c r="AM45" s="87"/>
+      <c r="AN45" s="88"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
@@ -4810,57 +4879,57 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="93"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="96"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="91"/>
-      <c r="G46" s="92"/>
-      <c r="H46" s="93"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="96"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="91" t="s">
+      <c r="J46" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="K46" s="92"/>
-      <c r="L46" s="93"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="96"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="76"/>
-      <c r="O46" s="77"/>
-      <c r="P46" s="78"/>
+      <c r="N46" s="83"/>
+      <c r="O46" s="84"/>
+      <c r="P46" s="85"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="76"/>
-      <c r="S46" s="77"/>
-      <c r="T46" s="78"/>
+      <c r="R46" s="83"/>
+      <c r="S46" s="84"/>
+      <c r="T46" s="85"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="88" t="s">
+      <c r="V46" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="89"/>
-      <c r="X46" s="90"/>
+      <c r="W46" s="90"/>
+      <c r="X46" s="91"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="88" t="s">
+      <c r="Z46" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="89"/>
-      <c r="AB46" s="90"/>
+      <c r="AA46" s="90"/>
+      <c r="AB46" s="91"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="88" t="s">
+      <c r="AD46" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="AE46" s="89"/>
-      <c r="AF46" s="90"/>
+      <c r="AE46" s="90"/>
+      <c r="AF46" s="91"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="88" t="s">
+      <c r="AH46" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="AI46" s="89"/>
-      <c r="AJ46" s="90"/>
+      <c r="AI46" s="90"/>
+      <c r="AJ46" s="91"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="88" t="s">
+      <c r="AL46" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="AM46" s="89"/>
-      <c r="AN46" s="90"/>
+      <c r="AM46" s="90"/>
+      <c r="AN46" s="91"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4868,57 +4937,57 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="94"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="97"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="94"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="97"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="68" t="s">
+      <c r="J47" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="K47" s="69"/>
-      <c r="L47" s="94"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="97"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="80"/>
-      <c r="P47" s="81"/>
+      <c r="N47" s="86"/>
+      <c r="O47" s="87"/>
+      <c r="P47" s="88"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="79"/>
-      <c r="S47" s="80"/>
-      <c r="T47" s="81"/>
+      <c r="R47" s="86"/>
+      <c r="S47" s="87"/>
+      <c r="T47" s="88"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="88" t="s">
+      <c r="V47" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="89"/>
-      <c r="X47" s="90"/>
+      <c r="W47" s="90"/>
+      <c r="X47" s="91"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="88" t="s">
+      <c r="Z47" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="89"/>
-      <c r="AB47" s="90"/>
+      <c r="AA47" s="90"/>
+      <c r="AB47" s="91"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="88" t="s">
+      <c r="AD47" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="AE47" s="89"/>
-      <c r="AF47" s="90"/>
+      <c r="AE47" s="90"/>
+      <c r="AF47" s="91"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="88" t="s">
+      <c r="AH47" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="AI47" s="89"/>
-      <c r="AJ47" s="90"/>
+      <c r="AI47" s="90"/>
+      <c r="AJ47" s="91"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="88" t="s">
+      <c r="AL47" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="AM47" s="89"/>
-      <c r="AN47" s="90"/>
+      <c r="AM47" s="90"/>
+      <c r="AN47" s="91"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4926,139 +4995,139 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="84"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="77"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="90"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="91"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="88" t="s">
+      <c r="J48" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="89"/>
-      <c r="L48" s="90"/>
+      <c r="K48" s="90"/>
+      <c r="L48" s="91"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="88"/>
-      <c r="O48" s="89"/>
-      <c r="P48" s="90"/>
+      <c r="N48" s="89"/>
+      <c r="O48" s="90"/>
+      <c r="P48" s="91"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="88"/>
-      <c r="S48" s="89"/>
-      <c r="T48" s="90"/>
+      <c r="R48" s="89"/>
+      <c r="S48" s="90"/>
+      <c r="T48" s="91"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="88" t="s">
+      <c r="V48" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="89"/>
-      <c r="X48" s="90"/>
+      <c r="W48" s="90"/>
+      <c r="X48" s="91"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="88" t="s">
+      <c r="Z48" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="89"/>
-      <c r="AB48" s="90"/>
+      <c r="AA48" s="90"/>
+      <c r="AB48" s="91"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="88" t="s">
+      <c r="AD48" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="AE48" s="89"/>
-      <c r="AF48" s="90"/>
+      <c r="AE48" s="90"/>
+      <c r="AF48" s="91"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="88" t="s">
+      <c r="AH48" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="AI48" s="89"/>
-      <c r="AJ48" s="90"/>
+      <c r="AI48" s="90"/>
+      <c r="AJ48" s="91"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="88" t="s">
+      <c r="AL48" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="AM48" s="89"/>
-      <c r="AN48" s="90"/>
+      <c r="AM48" s="90"/>
+      <c r="AN48" s="91"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="88"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="90"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="91"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="90"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="91"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="88" t="s">
+      <c r="J49" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="K49" s="89"/>
-      <c r="L49" s="90"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="91"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="88"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="90"/>
+      <c r="N49" s="89"/>
+      <c r="O49" s="90"/>
+      <c r="P49" s="91"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="88"/>
-      <c r="S49" s="89"/>
-      <c r="T49" s="90"/>
+      <c r="R49" s="89"/>
+      <c r="S49" s="90"/>
+      <c r="T49" s="91"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="85" t="s">
+      <c r="V49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="86"/>
-      <c r="X49" s="87"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="80"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="85" t="s">
+      <c r="Z49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="86"/>
-      <c r="AB49" s="87"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="80"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="85" t="s">
+      <c r="AD49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AE49" s="86"/>
-      <c r="AF49" s="87"/>
+      <c r="AE49" s="79"/>
+      <c r="AF49" s="80"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="85" t="s">
+      <c r="AH49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AI49" s="86"/>
-      <c r="AJ49" s="87"/>
+      <c r="AI49" s="79"/>
+      <c r="AJ49" s="80"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="85" t="s">
+      <c r="AL49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="86"/>
-      <c r="AN49" s="87"/>
+      <c r="AM49" s="79"/>
+      <c r="AN49" s="80"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="85"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="79"/>
+      <c r="D50" s="80"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="87"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="80"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="87"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="79"/>
+      <c r="L50" s="80"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="87"/>
+      <c r="N50" s="78"/>
+      <c r="O50" s="79"/>
+      <c r="P50" s="80"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="85"/>
-      <c r="S50" s="86"/>
-      <c r="T50" s="87"/>
+      <c r="R50" s="78"/>
+      <c r="S50" s="79"/>
+      <c r="T50" s="80"/>
       <c r="U50" s="35"/>
       <c r="V50" s="35"/>
       <c r="W50" s="35"/>
@@ -5105,30 +5174,30 @@
       <c r="S51" s="35"/>
       <c r="T51" s="35"/>
       <c r="U51" s="40"/>
-      <c r="V51" s="74"/>
-      <c r="W51" s="75"/>
+      <c r="V51" s="81"/>
+      <c r="W51" s="82"/>
       <c r="X51" s="34"/>
       <c r="Y51" s="32"/>
-      <c r="Z51" s="74"/>
-      <c r="AA51" s="75"/>
+      <c r="Z51" s="81"/>
+      <c r="AA51" s="82"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="40"/>
-      <c r="AD51" s="74" t="s">
+      <c r="AD51" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE51" s="75"/>
+      <c r="AE51" s="82"/>
       <c r="AF51" s="34"/>
       <c r="AG51" s="50"/>
-      <c r="AH51" s="74" t="s">
+      <c r="AH51" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI51" s="75"/>
+      <c r="AI51" s="82"/>
       <c r="AJ51" s="34"/>
       <c r="AK51" s="50"/>
-      <c r="AL51" s="74" t="s">
+      <c r="AL51" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM51" s="75"/>
+      <c r="AM51" s="82"/>
       <c r="AN51" s="34"/>
       <c r="AO51" s="31"/>
       <c r="AP51" s="31"/>
@@ -5136,275 +5205,275 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="66"/>
-      <c r="C52" s="67"/>
+      <c r="B52" s="67"/>
+      <c r="C52" s="68"/>
       <c r="D52" s="60"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="68"/>
       <c r="H52" s="60"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="101" t="s">
+      <c r="J52" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="K52" s="102"/>
+      <c r="K52" s="93"/>
       <c r="L52" s="55" t="s">
         <v>47</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="74"/>
-      <c r="O52" s="75"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="82"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="74"/>
-      <c r="S52" s="75"/>
+      <c r="R52" s="81"/>
+      <c r="S52" s="82"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="76"/>
-      <c r="W52" s="77"/>
-      <c r="X52" s="78"/>
+      <c r="V52" s="83"/>
+      <c r="W52" s="84"/>
+      <c r="X52" s="85"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="76"/>
-      <c r="AA52" s="77"/>
-      <c r="AB52" s="78"/>
+      <c r="Z52" s="83"/>
+      <c r="AA52" s="84"/>
+      <c r="AB52" s="85"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="76" t="s">
+      <c r="AD52" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AE52" s="77"/>
-      <c r="AF52" s="78"/>
+      <c r="AE52" s="84"/>
+      <c r="AF52" s="85"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="76" t="s">
+      <c r="AH52" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AI52" s="77"/>
-      <c r="AJ52" s="78"/>
+      <c r="AI52" s="84"/>
+      <c r="AJ52" s="85"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="76" t="s">
+      <c r="AL52" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM52" s="77"/>
-      <c r="AN52" s="78"/>
+      <c r="AM52" s="84"/>
+      <c r="AN52" s="85"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="91"/>
-      <c r="C53" s="92"/>
-      <c r="D53" s="93"/>
+      <c r="B53" s="94"/>
+      <c r="C53" s="95"/>
+      <c r="D53" s="96"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="91"/>
-      <c r="G53" s="92"/>
-      <c r="H53" s="93"/>
+      <c r="F53" s="94"/>
+      <c r="G53" s="95"/>
+      <c r="H53" s="96"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="91" t="s">
+      <c r="J53" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="92"/>
-      <c r="L53" s="93"/>
+      <c r="K53" s="95"/>
+      <c r="L53" s="96"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="76"/>
-      <c r="O53" s="77"/>
-      <c r="P53" s="78"/>
+      <c r="N53" s="83"/>
+      <c r="O53" s="84"/>
+      <c r="P53" s="85"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="76"/>
-      <c r="S53" s="77"/>
-      <c r="T53" s="78"/>
+      <c r="R53" s="83"/>
+      <c r="S53" s="84"/>
+      <c r="T53" s="85"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="79"/>
-      <c r="W53" s="80"/>
-      <c r="X53" s="81"/>
+      <c r="V53" s="86"/>
+      <c r="W53" s="87"/>
+      <c r="X53" s="88"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="79"/>
-      <c r="AA53" s="80"/>
-      <c r="AB53" s="81"/>
+      <c r="Z53" s="86"/>
+      <c r="AA53" s="87"/>
+      <c r="AB53" s="88"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="79" t="s">
+      <c r="AD53" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="AE53" s="80"/>
-      <c r="AF53" s="81"/>
+      <c r="AE53" s="87"/>
+      <c r="AF53" s="88"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="79" t="s">
+      <c r="AH53" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="AI53" s="80"/>
-      <c r="AJ53" s="81"/>
+      <c r="AI53" s="87"/>
+      <c r="AJ53" s="88"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="79" t="s">
+      <c r="AL53" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="AM53" s="80"/>
-      <c r="AN53" s="81"/>
+      <c r="AM53" s="87"/>
+      <c r="AN53" s="88"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="68"/>
-      <c r="C54" s="69"/>
-      <c r="D54" s="94"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="97"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="69"/>
-      <c r="H54" s="94"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="97"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="69"/>
-      <c r="L54" s="94"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="97"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="79"/>
-      <c r="O54" s="80"/>
-      <c r="P54" s="81"/>
+      <c r="N54" s="86"/>
+      <c r="O54" s="87"/>
+      <c r="P54" s="88"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="79"/>
-      <c r="S54" s="80"/>
-      <c r="T54" s="81"/>
+      <c r="R54" s="86"/>
+      <c r="S54" s="87"/>
+      <c r="T54" s="88"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="82"/>
-      <c r="W54" s="83"/>
-      <c r="X54" s="84"/>
+      <c r="V54" s="75"/>
+      <c r="W54" s="76"/>
+      <c r="X54" s="77"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="82"/>
-      <c r="AA54" s="83"/>
-      <c r="AB54" s="84"/>
+      <c r="Z54" s="75"/>
+      <c r="AA54" s="76"/>
+      <c r="AB54" s="77"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="82" t="s">
+      <c r="AD54" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="AE54" s="83"/>
-      <c r="AF54" s="84"/>
+      <c r="AE54" s="76"/>
+      <c r="AF54" s="77"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="82" t="s">
+      <c r="AH54" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="AI54" s="83"/>
-      <c r="AJ54" s="84"/>
+      <c r="AI54" s="76"/>
+      <c r="AJ54" s="77"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="82" t="s">
+      <c r="AL54" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="AM54" s="83"/>
-      <c r="AN54" s="84"/>
+      <c r="AM54" s="76"/>
+      <c r="AN54" s="77"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="82"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="84"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="77"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="84"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="77"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="88" t="s">
+      <c r="J55" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="90"/>
+      <c r="K55" s="90"/>
+      <c r="L55" s="91"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="84"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="76"/>
+      <c r="P55" s="77"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="83"/>
-      <c r="T55" s="84"/>
+      <c r="R55" s="75"/>
+      <c r="S55" s="76"/>
+      <c r="T55" s="77"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="88"/>
-      <c r="W55" s="89"/>
-      <c r="X55" s="90"/>
+      <c r="V55" s="89"/>
+      <c r="W55" s="90"/>
+      <c r="X55" s="91"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="88"/>
-      <c r="AA55" s="89"/>
-      <c r="AB55" s="90"/>
+      <c r="Z55" s="89"/>
+      <c r="AA55" s="90"/>
+      <c r="AB55" s="91"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="88" t="s">
+      <c r="AD55" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="AE55" s="89"/>
-      <c r="AF55" s="90"/>
+      <c r="AE55" s="90"/>
+      <c r="AF55" s="91"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="88" t="s">
+      <c r="AH55" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="89"/>
-      <c r="AJ55" s="90"/>
+      <c r="AI55" s="90"/>
+      <c r="AJ55" s="91"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="88" t="s">
+      <c r="AL55" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="AM55" s="89"/>
-      <c r="AN55" s="90"/>
+      <c r="AM55" s="90"/>
+      <c r="AN55" s="91"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="88"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="90"/>
+      <c r="B56" s="89"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="91"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="90"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="90"/>
+      <c r="H56" s="91"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="88" t="s">
+      <c r="J56" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="K56" s="89"/>
-      <c r="L56" s="90"/>
+      <c r="K56" s="90"/>
+      <c r="L56" s="91"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="88"/>
-      <c r="O56" s="89"/>
-      <c r="P56" s="90"/>
+      <c r="N56" s="89"/>
+      <c r="O56" s="90"/>
+      <c r="P56" s="91"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="88"/>
-      <c r="S56" s="89"/>
-      <c r="T56" s="90"/>
+      <c r="R56" s="89"/>
+      <c r="S56" s="90"/>
+      <c r="T56" s="91"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="85"/>
-      <c r="W56" s="86"/>
-      <c r="X56" s="87"/>
+      <c r="V56" s="78"/>
+      <c r="W56" s="79"/>
+      <c r="X56" s="80"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="85"/>
-      <c r="AA56" s="86"/>
-      <c r="AB56" s="87"/>
+      <c r="Z56" s="78"/>
+      <c r="AA56" s="79"/>
+      <c r="AB56" s="80"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="85" t="s">
+      <c r="AD56" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="AE56" s="86"/>
-      <c r="AF56" s="87"/>
+      <c r="AE56" s="79"/>
+      <c r="AF56" s="80"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="85" t="s">
+      <c r="AH56" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="AI56" s="86"/>
-      <c r="AJ56" s="87"/>
+      <c r="AI56" s="79"/>
+      <c r="AJ56" s="80"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="85" t="s">
+      <c r="AL56" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="AM56" s="86"/>
-      <c r="AN56" s="87"/>
+      <c r="AM56" s="79"/>
+      <c r="AN56" s="80"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="85"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="87"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="80"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="87"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="80"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="87"/>
+      <c r="J57" s="78"/>
+      <c r="K57" s="79"/>
+      <c r="L57" s="80"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="87"/>
+      <c r="N57" s="78"/>
+      <c r="O57" s="79"/>
+      <c r="P57" s="80"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="85"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="87"/>
+      <c r="R57" s="78"/>
+      <c r="S57" s="79"/>
+      <c r="T57" s="80"/>
       <c r="U57" s="50"/>
       <c r="V57" s="35"/>
       <c r="W57" s="35"/>
@@ -5448,303 +5517,303 @@
       <c r="S58" s="35"/>
       <c r="T58" s="35"/>
       <c r="U58" s="50"/>
-      <c r="V58" s="74"/>
-      <c r="W58" s="75"/>
+      <c r="V58" s="81"/>
+      <c r="W58" s="82"/>
       <c r="X58" s="34"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="74"/>
-      <c r="AA58" s="75"/>
+      <c r="Z58" s="81"/>
+      <c r="AA58" s="82"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
-      <c r="AD58" s="101" t="s">
+      <c r="AD58" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="AE58" s="102"/>
+      <c r="AE58" s="93"/>
       <c r="AF58" s="55"/>
       <c r="AG58" s="50"/>
-      <c r="AH58" s="74"/>
-      <c r="AI58" s="75"/>
+      <c r="AH58" s="81"/>
+      <c r="AI58" s="82"/>
       <c r="AJ58" s="34"/>
       <c r="AK58" s="50"/>
-      <c r="AL58" s="74" t="s">
+      <c r="AL58" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM58" s="75"/>
+      <c r="AM58" s="82"/>
       <c r="AN58" s="34"/>
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="66"/>
-      <c r="C59" s="67"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="68"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="67"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="68"/>
       <c r="H59" s="60"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="67"/>
+      <c r="J59" s="67"/>
+      <c r="K59" s="68"/>
       <c r="L59" s="60"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="74"/>
-      <c r="O59" s="75"/>
+      <c r="N59" s="81"/>
+      <c r="O59" s="82"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="74" t="s">
+      <c r="R59" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="S59" s="75"/>
+      <c r="S59" s="82"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="76"/>
-      <c r="W59" s="77"/>
-      <c r="X59" s="78"/>
+      <c r="V59" s="83"/>
+      <c r="W59" s="84"/>
+      <c r="X59" s="85"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="76"/>
-      <c r="AA59" s="77"/>
-      <c r="AB59" s="78"/>
+      <c r="Z59" s="83"/>
+      <c r="AA59" s="84"/>
+      <c r="AB59" s="85"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="76" t="s">
+      <c r="AD59" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AE59" s="77"/>
-      <c r="AF59" s="78"/>
+      <c r="AE59" s="84"/>
+      <c r="AF59" s="85"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="76"/>
-      <c r="AI59" s="77"/>
-      <c r="AJ59" s="78"/>
+      <c r="AH59" s="83"/>
+      <c r="AI59" s="84"/>
+      <c r="AJ59" s="85"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="76" t="s">
+      <c r="AL59" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM59" s="77"/>
-      <c r="AN59" s="78"/>
+      <c r="AM59" s="84"/>
+      <c r="AN59" s="85"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="91"/>
-      <c r="C60" s="92"/>
-      <c r="D60" s="93"/>
+      <c r="B60" s="94"/>
+      <c r="C60" s="95"/>
+      <c r="D60" s="96"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="92"/>
-      <c r="H60" s="93"/>
+      <c r="F60" s="94"/>
+      <c r="G60" s="95"/>
+      <c r="H60" s="96"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="91"/>
-      <c r="K60" s="92"/>
-      <c r="L60" s="93"/>
+      <c r="J60" s="94"/>
+      <c r="K60" s="95"/>
+      <c r="L60" s="96"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="76"/>
-      <c r="O60" s="77"/>
-      <c r="P60" s="78"/>
+      <c r="N60" s="83"/>
+      <c r="O60" s="84"/>
+      <c r="P60" s="85"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="76" t="s">
+      <c r="R60" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="S60" s="77"/>
-      <c r="T60" s="78"/>
+      <c r="S60" s="84"/>
+      <c r="T60" s="85"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="79"/>
-      <c r="W60" s="80"/>
-      <c r="X60" s="81"/>
+      <c r="V60" s="86"/>
+      <c r="W60" s="87"/>
+      <c r="X60" s="88"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="79"/>
-      <c r="AA60" s="80"/>
-      <c r="AB60" s="81"/>
+      <c r="Z60" s="86"/>
+      <c r="AA60" s="87"/>
+      <c r="AB60" s="88"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="79" t="s">
+      <c r="AD60" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="AE60" s="80"/>
-      <c r="AF60" s="81"/>
+      <c r="AE60" s="87"/>
+      <c r="AF60" s="88"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="79"/>
-      <c r="AI60" s="80"/>
-      <c r="AJ60" s="81"/>
+      <c r="AH60" s="86"/>
+      <c r="AI60" s="87"/>
+      <c r="AJ60" s="88"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="79" t="s">
+      <c r="AL60" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="AM60" s="80"/>
-      <c r="AN60" s="81"/>
+      <c r="AM60" s="87"/>
+      <c r="AN60" s="88"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="68"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="94"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="97"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="94"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="97"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="69"/>
-      <c r="L61" s="94"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="97"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="80"/>
-      <c r="P61" s="81"/>
+      <c r="N61" s="86"/>
+      <c r="O61" s="87"/>
+      <c r="P61" s="88"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="79"/>
-      <c r="S61" s="80"/>
-      <c r="T61" s="81"/>
+      <c r="R61" s="86"/>
+      <c r="S61" s="87"/>
+      <c r="T61" s="88"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="82"/>
-      <c r="W61" s="83"/>
-      <c r="X61" s="84"/>
+      <c r="V61" s="75"/>
+      <c r="W61" s="76"/>
+      <c r="X61" s="77"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="82"/>
-      <c r="AA61" s="83"/>
-      <c r="AB61" s="84"/>
+      <c r="Z61" s="75"/>
+      <c r="AA61" s="76"/>
+      <c r="AB61" s="77"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="82" t="s">
+      <c r="AD61" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="AE61" s="83"/>
-      <c r="AF61" s="84"/>
+      <c r="AE61" s="76"/>
+      <c r="AF61" s="77"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="82"/>
-      <c r="AI61" s="83"/>
-      <c r="AJ61" s="84"/>
+      <c r="AH61" s="75"/>
+      <c r="AI61" s="76"/>
+      <c r="AJ61" s="77"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="82" t="s">
+      <c r="AL61" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="AM61" s="83"/>
-      <c r="AN61" s="84"/>
+      <c r="AM61" s="76"/>
+      <c r="AN61" s="77"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="82"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="84"/>
+      <c r="B62" s="75"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="77"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="82"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="84"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="76"/>
+      <c r="H62" s="77"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="82"/>
-      <c r="K62" s="83"/>
-      <c r="L62" s="84"/>
+      <c r="J62" s="75"/>
+      <c r="K62" s="76"/>
+      <c r="L62" s="77"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="88"/>
-      <c r="O62" s="89"/>
-      <c r="P62" s="90"/>
+      <c r="N62" s="89"/>
+      <c r="O62" s="90"/>
+      <c r="P62" s="91"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="88" t="s">
+      <c r="R62" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="S62" s="89"/>
-      <c r="T62" s="90"/>
+      <c r="S62" s="90"/>
+      <c r="T62" s="91"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="88"/>
-      <c r="W62" s="89"/>
-      <c r="X62" s="90"/>
+      <c r="V62" s="89"/>
+      <c r="W62" s="90"/>
+      <c r="X62" s="91"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="88"/>
-      <c r="AA62" s="89"/>
-      <c r="AB62" s="90"/>
+      <c r="Z62" s="89"/>
+      <c r="AA62" s="90"/>
+      <c r="AB62" s="91"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="88" t="s">
+      <c r="AD62" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="AE62" s="89"/>
-      <c r="AF62" s="90"/>
+      <c r="AE62" s="90"/>
+      <c r="AF62" s="91"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="88"/>
-      <c r="AI62" s="89"/>
-      <c r="AJ62" s="90"/>
+      <c r="AH62" s="89"/>
+      <c r="AI62" s="90"/>
+      <c r="AJ62" s="91"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="88" t="s">
+      <c r="AL62" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="AM62" s="89"/>
-      <c r="AN62" s="90"/>
+      <c r="AM62" s="90"/>
+      <c r="AN62" s="91"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="88"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="90"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="91"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="90"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="90"/>
+      <c r="H63" s="91"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="88"/>
-      <c r="K63" s="89"/>
-      <c r="L63" s="90"/>
+      <c r="J63" s="89"/>
+      <c r="K63" s="90"/>
+      <c r="L63" s="91"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="88"/>
-      <c r="O63" s="89"/>
-      <c r="P63" s="90"/>
+      <c r="N63" s="89"/>
+      <c r="O63" s="90"/>
+      <c r="P63" s="91"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="88"/>
-      <c r="S63" s="89"/>
-      <c r="T63" s="90"/>
+      <c r="R63" s="89"/>
+      <c r="S63" s="90"/>
+      <c r="T63" s="91"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="88"/>
-      <c r="W63" s="89"/>
-      <c r="X63" s="90"/>
+      <c r="V63" s="89"/>
+      <c r="W63" s="90"/>
+      <c r="X63" s="91"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="88"/>
-      <c r="AA63" s="89"/>
-      <c r="AB63" s="90"/>
+      <c r="Z63" s="89"/>
+      <c r="AA63" s="90"/>
+      <c r="AB63" s="91"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="88"/>
-      <c r="AE63" s="89"/>
-      <c r="AF63" s="90"/>
+      <c r="AD63" s="89"/>
+      <c r="AE63" s="90"/>
+      <c r="AF63" s="91"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="88"/>
-      <c r="AI63" s="89"/>
-      <c r="AJ63" s="90"/>
+      <c r="AH63" s="89"/>
+      <c r="AI63" s="90"/>
+      <c r="AJ63" s="91"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="88"/>
-      <c r="AM63" s="89"/>
-      <c r="AN63" s="90"/>
+      <c r="AL63" s="89"/>
+      <c r="AM63" s="90"/>
+      <c r="AN63" s="91"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="85"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="87"/>
+      <c r="B64" s="78"/>
+      <c r="C64" s="79"/>
+      <c r="D64" s="80"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="86"/>
-      <c r="H64" s="87"/>
+      <c r="F64" s="78"/>
+      <c r="G64" s="79"/>
+      <c r="H64" s="80"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="86"/>
-      <c r="L64" s="87"/>
+      <c r="J64" s="78"/>
+      <c r="K64" s="79"/>
+      <c r="L64" s="80"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="85"/>
-      <c r="O64" s="86"/>
-      <c r="P64" s="87"/>
+      <c r="N64" s="78"/>
+      <c r="O64" s="79"/>
+      <c r="P64" s="80"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="85"/>
-      <c r="S64" s="86"/>
-      <c r="T64" s="87"/>
+      <c r="R64" s="78"/>
+      <c r="S64" s="79"/>
+      <c r="T64" s="80"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="85"/>
-      <c r="W64" s="86"/>
-      <c r="X64" s="87"/>
+      <c r="V64" s="78"/>
+      <c r="W64" s="79"/>
+      <c r="X64" s="80"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="85"/>
-      <c r="AA64" s="86"/>
-      <c r="AB64" s="87"/>
+      <c r="Z64" s="78"/>
+      <c r="AA64" s="79"/>
+      <c r="AB64" s="80"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="85"/>
-      <c r="AE64" s="86"/>
-      <c r="AF64" s="87"/>
+      <c r="AD64" s="78"/>
+      <c r="AE64" s="79"/>
+      <c r="AF64" s="80"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="85"/>
-      <c r="AI64" s="86"/>
-      <c r="AJ64" s="87"/>
+      <c r="AH64" s="78"/>
+      <c r="AI64" s="79"/>
+      <c r="AJ64" s="80"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="85"/>
-      <c r="AM64" s="86"/>
-      <c r="AN64" s="87"/>
+      <c r="AL64" s="78"/>
+      <c r="AM64" s="79"/>
+      <c r="AN64" s="80"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5807,23 +5876,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="114" t="s">
+      <c r="N66" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="114"/>
-      <c r="P66" s="114"/>
-      <c r="Q66" s="114"/>
-      <c r="R66" s="114"/>
-      <c r="S66" s="114"/>
-      <c r="T66" s="114"/>
-      <c r="U66" s="114"/>
-      <c r="V66" s="114"/>
-      <c r="W66" s="114"/>
-      <c r="X66" s="114"/>
-      <c r="Y66" s="114"/>
-      <c r="Z66" s="114"/>
-      <c r="AA66" s="114"/>
-      <c r="AB66" s="114"/>
+      <c r="O66" s="124"/>
+      <c r="P66" s="124"/>
+      <c r="Q66" s="124"/>
+      <c r="R66" s="124"/>
+      <c r="S66" s="124"/>
+      <c r="T66" s="124"/>
+      <c r="U66" s="124"/>
+      <c r="V66" s="124"/>
+      <c r="W66" s="124"/>
+      <c r="X66" s="124"/>
+      <c r="Y66" s="124"/>
+      <c r="Z66" s="124"/>
+      <c r="AA66" s="124"/>
+      <c r="AB66" s="124"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5854,21 +5923,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="114"/>
-      <c r="O67" s="114"/>
-      <c r="P67" s="114"/>
-      <c r="Q67" s="114"/>
-      <c r="R67" s="114"/>
-      <c r="S67" s="114"/>
-      <c r="T67" s="114"/>
-      <c r="U67" s="114"/>
-      <c r="V67" s="114"/>
-      <c r="W67" s="114"/>
-      <c r="X67" s="114"/>
-      <c r="Y67" s="114"/>
-      <c r="Z67" s="114"/>
-      <c r="AA67" s="114"/>
-      <c r="AB67" s="114"/>
+      <c r="N67" s="124"/>
+      <c r="O67" s="124"/>
+      <c r="P67" s="124"/>
+      <c r="Q67" s="124"/>
+      <c r="R67" s="124"/>
+      <c r="S67" s="124"/>
+      <c r="T67" s="124"/>
+      <c r="U67" s="124"/>
+      <c r="V67" s="124"/>
+      <c r="W67" s="124"/>
+      <c r="X67" s="124"/>
+      <c r="Y67" s="124"/>
+      <c r="Z67" s="124"/>
+      <c r="AA67" s="124"/>
+      <c r="AB67" s="124"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5888,56 +5957,56 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="66" t="s">
+      <c r="B68" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C68" s="67"/>
+      <c r="C68" s="68"/>
       <c r="D68" s="60"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="66" t="s">
+      <c r="F68" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="G68" s="67"/>
+      <c r="G68" s="68"/>
       <c r="H68" s="60"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="66" t="s">
+      <c r="J68" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="K68" s="67"/>
+      <c r="K68" s="68"/>
       <c r="L68" s="60"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="74" t="s">
+      <c r="N68" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="O68" s="75"/>
+      <c r="O68" s="82"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="32"/>
-      <c r="R68" s="74" t="s">
+      <c r="R68" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S68" s="75"/>
+      <c r="S68" s="82"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="74"/>
-      <c r="W68" s="75"/>
+      <c r="V68" s="81"/>
+      <c r="W68" s="82"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="74"/>
-      <c r="AA68" s="75"/>
+      <c r="Z68" s="81"/>
+      <c r="AA68" s="82"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="74"/>
-      <c r="AE68" s="75"/>
+      <c r="AD68" s="81"/>
+      <c r="AE68" s="82"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="74"/>
-      <c r="AI68" s="75"/>
+      <c r="AH68" s="81"/>
+      <c r="AI68" s="82"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="74" t="s">
+      <c r="AL68" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AM68" s="75"/>
+      <c r="AM68" s="82"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5948,57 +6017,57 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="91" t="s">
+      <c r="B69" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="92"/>
-      <c r="D69" s="93"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="96"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="91" t="s">
+      <c r="F69" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="G69" s="92"/>
-      <c r="H69" s="93"/>
+      <c r="G69" s="95"/>
+      <c r="H69" s="96"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="91" t="s">
+      <c r="J69" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="K69" s="92"/>
-      <c r="L69" s="93"/>
+      <c r="K69" s="95"/>
+      <c r="L69" s="96"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="76" t="s">
+      <c r="N69" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="O69" s="77"/>
-      <c r="P69" s="78"/>
+      <c r="O69" s="84"/>
+      <c r="P69" s="85"/>
       <c r="Q69" s="35"/>
-      <c r="R69" s="76" t="s">
+      <c r="R69" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="S69" s="77"/>
-      <c r="T69" s="78"/>
+      <c r="S69" s="84"/>
+      <c r="T69" s="85"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="76"/>
-      <c r="W69" s="77"/>
-      <c r="X69" s="78"/>
+      <c r="V69" s="83"/>
+      <c r="W69" s="84"/>
+      <c r="X69" s="85"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="76"/>
-      <c r="AA69" s="77"/>
-      <c r="AB69" s="78"/>
+      <c r="Z69" s="83"/>
+      <c r="AA69" s="84"/>
+      <c r="AB69" s="85"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="76"/>
-      <c r="AE69" s="77"/>
-      <c r="AF69" s="78"/>
+      <c r="AD69" s="83"/>
+      <c r="AE69" s="84"/>
+      <c r="AF69" s="85"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="76"/>
-      <c r="AI69" s="77"/>
-      <c r="AJ69" s="78"/>
+      <c r="AH69" s="83"/>
+      <c r="AI69" s="84"/>
+      <c r="AJ69" s="85"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="76" t="s">
+      <c r="AL69" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="AM69" s="77"/>
-      <c r="AN69" s="78"/>
+      <c r="AM69" s="84"/>
+      <c r="AN69" s="85"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -6008,57 +6077,57 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="69"/>
-      <c r="D70" s="94"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="97"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="68" t="s">
+      <c r="F70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="G70" s="69"/>
-      <c r="H70" s="94"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="97"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="68" t="s">
+      <c r="J70" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="K70" s="69"/>
-      <c r="L70" s="94"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="97"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="79" t="s">
+      <c r="N70" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="80"/>
-      <c r="P70" s="81"/>
+      <c r="O70" s="87"/>
+      <c r="P70" s="88"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="79" t="s">
+      <c r="R70" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="S70" s="80"/>
-      <c r="T70" s="81"/>
+      <c r="S70" s="87"/>
+      <c r="T70" s="88"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="79"/>
-      <c r="W70" s="80"/>
-      <c r="X70" s="81"/>
+      <c r="V70" s="86"/>
+      <c r="W70" s="87"/>
+      <c r="X70" s="88"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="79"/>
-      <c r="AA70" s="80"/>
-      <c r="AB70" s="81"/>
+      <c r="Z70" s="86"/>
+      <c r="AA70" s="87"/>
+      <c r="AB70" s="88"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="79"/>
-      <c r="AE70" s="80"/>
-      <c r="AF70" s="81"/>
+      <c r="AD70" s="86"/>
+      <c r="AE70" s="87"/>
+      <c r="AF70" s="88"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="79"/>
-      <c r="AI70" s="80"/>
-      <c r="AJ70" s="81"/>
+      <c r="AH70" s="86"/>
+      <c r="AI70" s="87"/>
+      <c r="AJ70" s="88"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="79" t="s">
+      <c r="AL70" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="AM70" s="80"/>
-      <c r="AN70" s="81"/>
+      <c r="AM70" s="87"/>
+      <c r="AN70" s="88"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6068,57 +6137,57 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="82" t="s">
+      <c r="B71" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="83"/>
-      <c r="D71" s="84"/>
+      <c r="C71" s="76"/>
+      <c r="D71" s="77"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="82" t="s">
+      <c r="F71" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="83"/>
-      <c r="H71" s="84"/>
+      <c r="G71" s="76"/>
+      <c r="H71" s="77"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="82" t="s">
+      <c r="J71" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="K71" s="83"/>
-      <c r="L71" s="84"/>
+      <c r="K71" s="76"/>
+      <c r="L71" s="77"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="82" t="s">
+      <c r="N71" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="O71" s="83"/>
-      <c r="P71" s="84"/>
+      <c r="O71" s="76"/>
+      <c r="P71" s="77"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="82" t="s">
+      <c r="R71" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="S71" s="83"/>
-      <c r="T71" s="84"/>
+      <c r="S71" s="76"/>
+      <c r="T71" s="77"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="82"/>
-      <c r="W71" s="83"/>
-      <c r="X71" s="84"/>
+      <c r="V71" s="75"/>
+      <c r="W71" s="76"/>
+      <c r="X71" s="77"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="82"/>
-      <c r="AA71" s="83"/>
-      <c r="AB71" s="84"/>
+      <c r="Z71" s="75"/>
+      <c r="AA71" s="76"/>
+      <c r="AB71" s="77"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="82"/>
-      <c r="AE71" s="83"/>
-      <c r="AF71" s="84"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="77"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="82"/>
-      <c r="AI71" s="83"/>
-      <c r="AJ71" s="84"/>
+      <c r="AH71" s="75"/>
+      <c r="AI71" s="76"/>
+      <c r="AJ71" s="77"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="82" t="s">
+      <c r="AL71" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="AM71" s="83"/>
-      <c r="AN71" s="84"/>
+      <c r="AM71" s="76"/>
+      <c r="AN71" s="77"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6128,47 +6197,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="87"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="79"/>
+      <c r="D72" s="80"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="87"/>
+      <c r="F72" s="78"/>
+      <c r="G72" s="79"/>
+      <c r="H72" s="80"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="85"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="87"/>
+      <c r="J72" s="78"/>
+      <c r="K72" s="79"/>
+      <c r="L72" s="80"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="85"/>
-      <c r="O72" s="86"/>
-      <c r="P72" s="87"/>
+      <c r="N72" s="78"/>
+      <c r="O72" s="79"/>
+      <c r="P72" s="80"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="86"/>
-      <c r="T72" s="87"/>
+      <c r="R72" s="78"/>
+      <c r="S72" s="79"/>
+      <c r="T72" s="80"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="85"/>
-      <c r="W72" s="86"/>
-      <c r="X72" s="87"/>
+      <c r="V72" s="78"/>
+      <c r="W72" s="79"/>
+      <c r="X72" s="80"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="85"/>
-      <c r="AA72" s="86"/>
-      <c r="AB72" s="87"/>
+      <c r="Z72" s="78"/>
+      <c r="AA72" s="79"/>
+      <c r="AB72" s="80"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="85"/>
-      <c r="AE72" s="86"/>
-      <c r="AF72" s="87"/>
+      <c r="AD72" s="78"/>
+      <c r="AE72" s="79"/>
+      <c r="AF72" s="80"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="85"/>
-      <c r="AI72" s="86"/>
-      <c r="AJ72" s="87"/>
+      <c r="AH72" s="78"/>
+      <c r="AI72" s="79"/>
+      <c r="AJ72" s="80"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="85" t="s">
+      <c r="AL72" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AM72" s="86"/>
-      <c r="AN72" s="87"/>
+      <c r="AM72" s="79"/>
+      <c r="AN72" s="80"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6222,58 +6291,58 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="66" t="s">
+      <c r="B74" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="C74" s="67"/>
+      <c r="C74" s="68"/>
       <c r="D74" s="60"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="66" t="s">
+      <c r="F74" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="G74" s="67"/>
+      <c r="G74" s="68"/>
       <c r="H74" s="60"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="66"/>
-      <c r="K74" s="67"/>
+      <c r="J74" s="67"/>
+      <c r="K74" s="68"/>
       <c r="L74" s="60"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="74" t="s">
+      <c r="N74" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="O74" s="75"/>
+      <c r="O74" s="82"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="36"/>
-      <c r="R74" s="74" t="s">
+      <c r="R74" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="S74" s="75"/>
+      <c r="S74" s="82"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="74"/>
-      <c r="W74" s="75"/>
+      <c r="V74" s="81"/>
+      <c r="W74" s="82"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="74" t="s">
+      <c r="Z74" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AA74" s="75"/>
+      <c r="AA74" s="82"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="32"/>
-      <c r="AD74" s="74" t="s">
+      <c r="AD74" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AE74" s="75"/>
+      <c r="AE74" s="82"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="74" t="s">
+      <c r="AH74" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AI74" s="75"/>
+      <c r="AI74" s="82"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="74"/>
-      <c r="AM74" s="75"/>
+      <c r="AL74" s="81"/>
+      <c r="AM74" s="82"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6282,49 +6351,49 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="91" t="s">
+      <c r="B75" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="92"/>
-      <c r="D75" s="93"/>
+      <c r="C75" s="95"/>
+      <c r="D75" s="96"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="91" t="s">
+      <c r="F75" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="92"/>
-      <c r="H75" s="93"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="96"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="91"/>
-      <c r="K75" s="92"/>
-      <c r="L75" s="93"/>
+      <c r="J75" s="94"/>
+      <c r="K75" s="95"/>
+      <c r="L75" s="96"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="76"/>
-      <c r="O75" s="77"/>
-      <c r="P75" s="78"/>
+      <c r="N75" s="83"/>
+      <c r="O75" s="84"/>
+      <c r="P75" s="85"/>
       <c r="Q75" s="32"/>
-      <c r="R75" s="76"/>
-      <c r="S75" s="77"/>
-      <c r="T75" s="78"/>
+      <c r="R75" s="83"/>
+      <c r="S75" s="84"/>
+      <c r="T75" s="85"/>
       <c r="U75" s="36"/>
-      <c r="V75" s="76"/>
-      <c r="W75" s="77"/>
-      <c r="X75" s="78"/>
+      <c r="V75" s="83"/>
+      <c r="W75" s="84"/>
+      <c r="X75" s="85"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="76"/>
-      <c r="AA75" s="77"/>
-      <c r="AB75" s="78"/>
+      <c r="Z75" s="83"/>
+      <c r="AA75" s="84"/>
+      <c r="AB75" s="85"/>
       <c r="AC75" s="35"/>
-      <c r="AD75" s="76"/>
-      <c r="AE75" s="77"/>
-      <c r="AF75" s="78"/>
+      <c r="AD75" s="83"/>
+      <c r="AE75" s="84"/>
+      <c r="AF75" s="85"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="76"/>
-      <c r="AI75" s="77"/>
-      <c r="AJ75" s="78"/>
+      <c r="AH75" s="83"/>
+      <c r="AI75" s="84"/>
+      <c r="AJ75" s="85"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="76"/>
-      <c r="AM75" s="77"/>
-      <c r="AN75" s="78"/>
+      <c r="AL75" s="83"/>
+      <c r="AM75" s="84"/>
+      <c r="AN75" s="85"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6332,59 +6401,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="68" t="s">
+      <c r="B76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="69"/>
-      <c r="D76" s="94"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="97"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="68" t="s">
+      <c r="F76" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="69"/>
-      <c r="H76" s="94"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="97"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="68"/>
-      <c r="K76" s="69"/>
-      <c r="L76" s="94"/>
+      <c r="J76" s="69"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="97"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="79" t="s">
+      <c r="N76" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="80"/>
-      <c r="P76" s="81"/>
+      <c r="O76" s="87"/>
+      <c r="P76" s="88"/>
       <c r="Q76" s="31"/>
-      <c r="R76" s="79" t="s">
+      <c r="R76" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="80"/>
-      <c r="T76" s="81"/>
+      <c r="S76" s="87"/>
+      <c r="T76" s="88"/>
       <c r="U76" s="36"/>
-      <c r="V76" s="79"/>
-      <c r="W76" s="80"/>
-      <c r="X76" s="81"/>
+      <c r="V76" s="86"/>
+      <c r="W76" s="87"/>
+      <c r="X76" s="88"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="79" t="s">
+      <c r="Z76" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="80"/>
-      <c r="AB76" s="81"/>
+      <c r="AA76" s="87"/>
+      <c r="AB76" s="88"/>
       <c r="AC76" s="31"/>
-      <c r="AD76" s="79" t="s">
+      <c r="AD76" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AE76" s="80"/>
-      <c r="AF76" s="81"/>
+      <c r="AE76" s="87"/>
+      <c r="AF76" s="88"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="79" t="s">
+      <c r="AH76" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AI76" s="80"/>
-      <c r="AJ76" s="81"/>
+      <c r="AI76" s="87"/>
+      <c r="AJ76" s="88"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="79"/>
-      <c r="AM76" s="80"/>
-      <c r="AN76" s="81"/>
+      <c r="AL76" s="86"/>
+      <c r="AM76" s="87"/>
+      <c r="AN76" s="88"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6392,59 +6461,59 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="82" t="s">
+      <c r="B77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="83"/>
-      <c r="D77" s="84"/>
+      <c r="C77" s="76"/>
+      <c r="D77" s="77"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="82" t="s">
+      <c r="F77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="83"/>
-      <c r="H77" s="84"/>
+      <c r="G77" s="76"/>
+      <c r="H77" s="77"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="83"/>
-      <c r="L77" s="84"/>
+      <c r="J77" s="75"/>
+      <c r="K77" s="76"/>
+      <c r="L77" s="77"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="95" t="s">
+      <c r="N77" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="O77" s="96"/>
-      <c r="P77" s="97"/>
+      <c r="O77" s="99"/>
+      <c r="P77" s="100"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="82" t="s">
+      <c r="R77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="83"/>
-      <c r="T77" s="84"/>
+      <c r="S77" s="76"/>
+      <c r="T77" s="77"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="82"/>
-      <c r="W77" s="83"/>
-      <c r="X77" s="84"/>
+      <c r="V77" s="75"/>
+      <c r="W77" s="76"/>
+      <c r="X77" s="77"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="82" t="s">
+      <c r="Z77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="83"/>
-      <c r="AB77" s="84"/>
+      <c r="AA77" s="76"/>
+      <c r="AB77" s="77"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="82" t="s">
+      <c r="AD77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="83"/>
-      <c r="AF77" s="84"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="77"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="82" t="s">
+      <c r="AH77" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="83"/>
-      <c r="AJ77" s="84"/>
+      <c r="AI77" s="76"/>
+      <c r="AJ77" s="77"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="82"/>
-      <c r="AM77" s="83"/>
-      <c r="AN77" s="84"/>
+      <c r="AL77" s="75"/>
+      <c r="AM77" s="76"/>
+      <c r="AN77" s="77"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6452,47 +6521,47 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="85"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="87"/>
+      <c r="B78" s="78"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="80"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="85"/>
-      <c r="G78" s="86"/>
-      <c r="H78" s="87"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="79"/>
+      <c r="H78" s="80"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="85"/>
-      <c r="K78" s="86"/>
-      <c r="L78" s="87"/>
+      <c r="J78" s="78"/>
+      <c r="K78" s="79"/>
+      <c r="L78" s="80"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="98" t="s">
+      <c r="N78" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="O78" s="99"/>
-      <c r="P78" s="100"/>
+      <c r="O78" s="102"/>
+      <c r="P78" s="103"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="85"/>
-      <c r="S78" s="86"/>
-      <c r="T78" s="87"/>
+      <c r="R78" s="78"/>
+      <c r="S78" s="79"/>
+      <c r="T78" s="80"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="85"/>
-      <c r="W78" s="86"/>
-      <c r="X78" s="87"/>
+      <c r="V78" s="78"/>
+      <c r="W78" s="79"/>
+      <c r="X78" s="80"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="85"/>
-      <c r="AA78" s="86"/>
-      <c r="AB78" s="87"/>
+      <c r="Z78" s="78"/>
+      <c r="AA78" s="79"/>
+      <c r="AB78" s="80"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="85"/>
-      <c r="AE78" s="86"/>
-      <c r="AF78" s="87"/>
+      <c r="AD78" s="78"/>
+      <c r="AE78" s="79"/>
+      <c r="AF78" s="80"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="85"/>
-      <c r="AI78" s="86"/>
-      <c r="AJ78" s="87"/>
+      <c r="AH78" s="78"/>
+      <c r="AI78" s="79"/>
+      <c r="AJ78" s="80"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="85"/>
-      <c r="AM78" s="86"/>
-      <c r="AN78" s="87"/>
+      <c r="AL78" s="78"/>
+      <c r="AM78" s="79"/>
+      <c r="AN78" s="80"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6546,56 +6615,56 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="67"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="68"/>
       <c r="D80" s="60"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="66" t="s">
+      <c r="F80" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="G80" s="67"/>
+      <c r="G80" s="68"/>
       <c r="H80" s="60"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="66" t="s">
+      <c r="J80" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="K80" s="67"/>
+      <c r="K80" s="68"/>
       <c r="L80" s="60"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="74" t="s">
+      <c r="N80" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="O80" s="75"/>
-      <c r="P80" s="34"/>
+      <c r="O80" s="149"/>
+      <c r="P80" s="59"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="74" t="s">
+      <c r="R80" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="S80" s="75"/>
+      <c r="S80" s="82"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="74"/>
-      <c r="W80" s="75"/>
+      <c r="V80" s="81"/>
+      <c r="W80" s="82"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="74" t="s">
+      <c r="Z80" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="AA80" s="75"/>
+      <c r="AA80" s="82"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="74" t="s">
+      <c r="AD80" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="AE80" s="75"/>
+      <c r="AE80" s="82"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="74"/>
-      <c r="AI80" s="75"/>
+      <c r="AH80" s="81"/>
+      <c r="AI80" s="82"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="74"/>
-      <c r="AM80" s="75"/>
+      <c r="AL80" s="81"/>
+      <c r="AM80" s="82"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6604,45 +6673,47 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="91"/>
-      <c r="C81" s="92"/>
-      <c r="D81" s="93"/>
+      <c r="B81" s="94"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="96"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="93"/>
+      <c r="F81" s="94"/>
+      <c r="G81" s="95"/>
+      <c r="H81" s="96"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="91"/>
-      <c r="K81" s="92"/>
-      <c r="L81" s="93"/>
+      <c r="J81" s="94"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="96"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="76"/>
-      <c r="O81" s="77"/>
-      <c r="P81" s="78"/>
+      <c r="N81" s="142" t="s">
+        <v>94</v>
+      </c>
+      <c r="O81" s="143"/>
+      <c r="P81" s="144"/>
       <c r="Q81" s="44"/>
-      <c r="R81" s="76"/>
-      <c r="S81" s="77"/>
-      <c r="T81" s="78"/>
+      <c r="R81" s="83"/>
+      <c r="S81" s="84"/>
+      <c r="T81" s="85"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="76"/>
-      <c r="W81" s="77"/>
-      <c r="X81" s="78"/>
+      <c r="V81" s="83"/>
+      <c r="W81" s="84"/>
+      <c r="X81" s="85"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="76"/>
-      <c r="AA81" s="77"/>
-      <c r="AB81" s="78"/>
+      <c r="Z81" s="83"/>
+      <c r="AA81" s="84"/>
+      <c r="AB81" s="85"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="76"/>
-      <c r="AE81" s="77"/>
-      <c r="AF81" s="78"/>
+      <c r="AD81" s="83"/>
+      <c r="AE81" s="84"/>
+      <c r="AF81" s="85"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="76"/>
-      <c r="AI81" s="77"/>
-      <c r="AJ81" s="78"/>
+      <c r="AH81" s="83"/>
+      <c r="AI81" s="84"/>
+      <c r="AJ81" s="85"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="76"/>
-      <c r="AM81" s="77"/>
-      <c r="AN81" s="78"/>
+      <c r="AL81" s="83"/>
+      <c r="AM81" s="84"/>
+      <c r="AN81" s="85"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6650,57 +6721,57 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="94"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="68" t="s">
+      <c r="F82" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="69"/>
-      <c r="H82" s="94"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="97"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="68" t="s">
+      <c r="J82" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="K82" s="69"/>
-      <c r="L82" s="94"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="97"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="79" t="s">
+      <c r="N82" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="80"/>
-      <c r="P82" s="81"/>
+      <c r="O82" s="114"/>
+      <c r="P82" s="115"/>
       <c r="Q82" s="44"/>
-      <c r="R82" s="79" t="s">
+      <c r="R82" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="S82" s="80"/>
-      <c r="T82" s="81"/>
+      <c r="S82" s="87"/>
+      <c r="T82" s="88"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="79"/>
-      <c r="W82" s="80"/>
-      <c r="X82" s="81"/>
+      <c r="V82" s="86"/>
+      <c r="W82" s="87"/>
+      <c r="X82" s="88"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="79" t="s">
+      <c r="Z82" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AA82" s="80"/>
-      <c r="AB82" s="81"/>
+      <c r="AA82" s="87"/>
+      <c r="AB82" s="88"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="79" t="s">
+      <c r="AD82" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AE82" s="80"/>
-      <c r="AF82" s="81"/>
+      <c r="AE82" s="87"/>
+      <c r="AF82" s="88"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="79"/>
-      <c r="AI82" s="80"/>
-      <c r="AJ82" s="81"/>
+      <c r="AH82" s="86"/>
+      <c r="AI82" s="87"/>
+      <c r="AJ82" s="88"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="79"/>
-      <c r="AM82" s="80"/>
-      <c r="AN82" s="81"/>
+      <c r="AL82" s="86"/>
+      <c r="AM82" s="87"/>
+      <c r="AN82" s="88"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6708,57 +6779,57 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="82"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="84"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="77"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="95" t="s">
+      <c r="F83" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="G83" s="96"/>
-      <c r="H83" s="97"/>
+      <c r="G83" s="99"/>
+      <c r="H83" s="100"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="82" t="s">
+      <c r="J83" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="83"/>
-      <c r="L83" s="84"/>
+      <c r="K83" s="76"/>
+      <c r="L83" s="77"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="82" t="s">
+      <c r="N83" s="145" t="s">
+        <v>85</v>
+      </c>
+      <c r="O83" s="146"/>
+      <c r="P83" s="147"/>
+      <c r="Q83" s="44"/>
+      <c r="R83" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="O83" s="83"/>
-      <c r="P83" s="84"/>
-      <c r="Q83" s="44"/>
-      <c r="R83" s="82" t="s">
+      <c r="S83" s="76"/>
+      <c r="T83" s="77"/>
+      <c r="U83" s="32"/>
+      <c r="V83" s="75"/>
+      <c r="W83" s="76"/>
+      <c r="X83" s="77"/>
+      <c r="Y83" s="32"/>
+      <c r="Z83" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="83"/>
-      <c r="T83" s="84"/>
-      <c r="U83" s="32"/>
-      <c r="V83" s="82"/>
-      <c r="W83" s="83"/>
-      <c r="X83" s="84"/>
-      <c r="Y83" s="32"/>
-      <c r="Z83" s="82" t="s">
+      <c r="AA83" s="76"/>
+      <c r="AB83" s="77"/>
+      <c r="AC83" s="43"/>
+      <c r="AD83" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="83"/>
-      <c r="AB83" s="84"/>
-      <c r="AC83" s="43"/>
-      <c r="AD83" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE83" s="83"/>
-      <c r="AF83" s="84"/>
+      <c r="AE83" s="76"/>
+      <c r="AF83" s="77"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="82"/>
-      <c r="AI83" s="83"/>
-      <c r="AJ83" s="84"/>
+      <c r="AH83" s="75"/>
+      <c r="AI83" s="76"/>
+      <c r="AJ83" s="77"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="82"/>
-      <c r="AM83" s="83"/>
-      <c r="AN83" s="84"/>
+      <c r="AL83" s="75"/>
+      <c r="AM83" s="76"/>
+      <c r="AN83" s="77"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6766,49 +6837,49 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="85"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="87"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="98" t="s">
+      <c r="F84" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="G84" s="99"/>
-      <c r="H84" s="100"/>
+      <c r="G84" s="102"/>
+      <c r="H84" s="103"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="98" t="s">
+      <c r="J84" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="K84" s="99"/>
-      <c r="L84" s="100"/>
+      <c r="K84" s="102"/>
+      <c r="L84" s="103"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="85"/>
-      <c r="O84" s="86"/>
-      <c r="P84" s="87"/>
+      <c r="N84" s="116"/>
+      <c r="O84" s="117"/>
+      <c r="P84" s="118"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="85"/>
-      <c r="S84" s="86"/>
-      <c r="T84" s="87"/>
+      <c r="R84" s="78"/>
+      <c r="S84" s="79"/>
+      <c r="T84" s="80"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="85"/>
-      <c r="W84" s="86"/>
-      <c r="X84" s="87"/>
+      <c r="V84" s="78"/>
+      <c r="W84" s="79"/>
+      <c r="X84" s="80"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="85"/>
-      <c r="AA84" s="86"/>
-      <c r="AB84" s="87"/>
+      <c r="Z84" s="78"/>
+      <c r="AA84" s="79"/>
+      <c r="AB84" s="80"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="85"/>
-      <c r="AE84" s="86"/>
-      <c r="AF84" s="87"/>
+      <c r="AD84" s="78"/>
+      <c r="AE84" s="79"/>
+      <c r="AF84" s="80"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="85"/>
-      <c r="AI84" s="86"/>
-      <c r="AJ84" s="87"/>
+      <c r="AH84" s="78"/>
+      <c r="AI84" s="79"/>
+      <c r="AJ84" s="80"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="85"/>
-      <c r="AM84" s="86"/>
-      <c r="AN84" s="87"/>
+      <c r="AL84" s="78"/>
+      <c r="AM84" s="79"/>
+      <c r="AN84" s="80"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6862,52 +6933,52 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="66" t="s">
+      <c r="B86" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C86" s="67"/>
+      <c r="C86" s="68"/>
       <c r="D86" s="60"/>
       <c r="E86" s="36"/>
-      <c r="F86" s="66" t="s">
+      <c r="F86" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="G86" s="67"/>
+      <c r="G86" s="68"/>
       <c r="H86" s="60"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="66"/>
-      <c r="K86" s="67"/>
+      <c r="J86" s="67"/>
+      <c r="K86" s="68"/>
       <c r="L86" s="60"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="74" t="s">
+      <c r="N86" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="O86" s="75"/>
+      <c r="O86" s="82"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="74"/>
-      <c r="S86" s="75"/>
+      <c r="R86" s="81"/>
+      <c r="S86" s="82"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="74" t="s">
+      <c r="V86" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="W86" s="75"/>
+      <c r="W86" s="82"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="74"/>
-      <c r="AA86" s="75"/>
+      <c r="Z86" s="81"/>
+      <c r="AA86" s="82"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="74"/>
-      <c r="AE86" s="75"/>
+      <c r="AD86" s="81"/>
+      <c r="AE86" s="82"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="74"/>
-      <c r="AI86" s="75"/>
+      <c r="AH86" s="81"/>
+      <c r="AI86" s="82"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="74"/>
-      <c r="AM86" s="75"/>
+      <c r="AL86" s="81"/>
+      <c r="AM86" s="82"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6916,49 +6987,49 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="68" t="s">
+      <c r="B87" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="69"/>
+      <c r="C87" s="70"/>
       <c r="D87" s="61"/>
       <c r="E87" s="38"/>
-      <c r="F87" s="68" t="s">
+      <c r="F87" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="G87" s="69"/>
+      <c r="G87" s="70"/>
       <c r="H87" s="61"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="91"/>
-      <c r="K87" s="92"/>
-      <c r="L87" s="93"/>
+      <c r="J87" s="94"/>
+      <c r="K87" s="95"/>
+      <c r="L87" s="96"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="76"/>
-      <c r="O87" s="77"/>
-      <c r="P87" s="78"/>
+      <c r="N87" s="83"/>
+      <c r="O87" s="84"/>
+      <c r="P87" s="85"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="76"/>
-      <c r="S87" s="77"/>
-      <c r="T87" s="78"/>
+      <c r="R87" s="83"/>
+      <c r="S87" s="84"/>
+      <c r="T87" s="85"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="76"/>
-      <c r="W87" s="77"/>
-      <c r="X87" s="78"/>
+      <c r="V87" s="83"/>
+      <c r="W87" s="84"/>
+      <c r="X87" s="85"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="76"/>
-      <c r="AA87" s="77"/>
-      <c r="AB87" s="78"/>
+      <c r="Z87" s="83"/>
+      <c r="AA87" s="84"/>
+      <c r="AB87" s="85"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="76"/>
-      <c r="AE87" s="77"/>
-      <c r="AF87" s="78"/>
+      <c r="AD87" s="83"/>
+      <c r="AE87" s="84"/>
+      <c r="AF87" s="85"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="76"/>
-      <c r="AI87" s="77"/>
-      <c r="AJ87" s="78"/>
+      <c r="AH87" s="83"/>
+      <c r="AI87" s="84"/>
+      <c r="AJ87" s="85"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="76"/>
-      <c r="AM87" s="77"/>
-      <c r="AN87" s="78"/>
+      <c r="AL87" s="83"/>
+      <c r="AM87" s="84"/>
+      <c r="AN87" s="85"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6966,57 +7037,57 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="70" t="s">
+      <c r="B88" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="71"/>
+      <c r="C88" s="72"/>
       <c r="D88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E88" s="37"/>
-      <c r="F88" s="70" t="s">
+      <c r="F88" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="71"/>
+      <c r="G88" s="72"/>
       <c r="H88" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I88" s="31"/>
-      <c r="J88" s="68"/>
-      <c r="K88" s="69"/>
-      <c r="L88" s="94"/>
+      <c r="J88" s="69"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="97"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="79" t="s">
+      <c r="N88" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="O88" s="80"/>
-      <c r="P88" s="81"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="88"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="79"/>
-      <c r="S88" s="80"/>
-      <c r="T88" s="81"/>
+      <c r="R88" s="86"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="88"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="79" t="s">
+      <c r="V88" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="W88" s="80"/>
-      <c r="X88" s="81"/>
+      <c r="W88" s="87"/>
+      <c r="X88" s="88"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="79"/>
-      <c r="AA88" s="80"/>
-      <c r="AB88" s="81"/>
+      <c r="Z88" s="86"/>
+      <c r="AA88" s="87"/>
+      <c r="AB88" s="88"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="79"/>
-      <c r="AE88" s="80"/>
-      <c r="AF88" s="81"/>
+      <c r="AD88" s="86"/>
+      <c r="AE88" s="87"/>
+      <c r="AF88" s="88"/>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="79"/>
-      <c r="AI88" s="80"/>
-      <c r="AJ88" s="81"/>
+      <c r="AH88" s="86"/>
+      <c r="AI88" s="87"/>
+      <c r="AJ88" s="88"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="79"/>
-      <c r="AM88" s="80"/>
-      <c r="AN88" s="81"/>
+      <c r="AL88" s="86"/>
+      <c r="AM88" s="87"/>
+      <c r="AN88" s="88"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -7024,57 +7095,57 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="72" t="s">
+      <c r="B89" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="73"/>
+      <c r="C89" s="74"/>
       <c r="D89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="43"/>
-      <c r="F89" s="72" t="s">
+      <c r="F89" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="G89" s="73"/>
+      <c r="G89" s="74"/>
       <c r="H89" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I89" s="31"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="83"/>
-      <c r="L89" s="84"/>
+      <c r="J89" s="75"/>
+      <c r="K89" s="76"/>
+      <c r="L89" s="77"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="95" t="s">
+      <c r="N89" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="O89" s="96"/>
-      <c r="P89" s="97"/>
+      <c r="O89" s="99"/>
+      <c r="P89" s="100"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="83"/>
-      <c r="T89" s="84"/>
+      <c r="R89" s="75"/>
+      <c r="S89" s="76"/>
+      <c r="T89" s="77"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="82" t="s">
+      <c r="V89" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="W89" s="83"/>
-      <c r="X89" s="84"/>
+      <c r="W89" s="76"/>
+      <c r="X89" s="77"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="82"/>
-      <c r="AA89" s="83"/>
-      <c r="AB89" s="84"/>
+      <c r="Z89" s="75"/>
+      <c r="AA89" s="76"/>
+      <c r="AB89" s="77"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="82"/>
-      <c r="AE89" s="83"/>
-      <c r="AF89" s="84"/>
+      <c r="AD89" s="75"/>
+      <c r="AE89" s="76"/>
+      <c r="AF89" s="77"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="82"/>
-      <c r="AI89" s="83"/>
-      <c r="AJ89" s="84"/>
+      <c r="AH89" s="75"/>
+      <c r="AI89" s="76"/>
+      <c r="AJ89" s="77"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="82"/>
-      <c r="AM89" s="83"/>
-      <c r="AN89" s="84"/>
+      <c r="AL89" s="75"/>
+      <c r="AM89" s="76"/>
+      <c r="AN89" s="77"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7082,55 +7153,55 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="62" t="s">
+      <c r="B90" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="63"/>
+      <c r="C90" s="64"/>
       <c r="D90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E90" s="43"/>
-      <c r="F90" s="62" t="s">
+      <c r="F90" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G90" s="63"/>
+      <c r="G90" s="64"/>
       <c r="H90" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I90" s="32"/>
-      <c r="J90" s="85"/>
-      <c r="K90" s="86"/>
-      <c r="L90" s="87"/>
+      <c r="J90" s="78"/>
+      <c r="K90" s="79"/>
+      <c r="L90" s="80"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="98" t="s">
+      <c r="N90" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="O90" s="99"/>
-      <c r="P90" s="100"/>
+      <c r="O90" s="102"/>
+      <c r="P90" s="103"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="85"/>
-      <c r="S90" s="86"/>
-      <c r="T90" s="87"/>
+      <c r="R90" s="78"/>
+      <c r="S90" s="79"/>
+      <c r="T90" s="80"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="85"/>
-      <c r="W90" s="86"/>
-      <c r="X90" s="87"/>
+      <c r="V90" s="78"/>
+      <c r="W90" s="79"/>
+      <c r="X90" s="80"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="85"/>
-      <c r="AA90" s="86"/>
-      <c r="AB90" s="87"/>
+      <c r="Z90" s="78"/>
+      <c r="AA90" s="79"/>
+      <c r="AB90" s="80"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="85"/>
-      <c r="AE90" s="86"/>
-      <c r="AF90" s="87"/>
+      <c r="AD90" s="78"/>
+      <c r="AE90" s="79"/>
+      <c r="AF90" s="80"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="85"/>
-      <c r="AI90" s="86"/>
-      <c r="AJ90" s="87"/>
+      <c r="AH90" s="78"/>
+      <c r="AI90" s="79"/>
+      <c r="AJ90" s="80"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="85"/>
-      <c r="AM90" s="86"/>
-      <c r="AN90" s="87"/>
+      <c r="AL90" s="78"/>
+      <c r="AM90" s="79"/>
+      <c r="AN90" s="80"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7138,18 +7209,18 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
-      <c r="B91" s="62" t="s">
+      <c r="B91" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="63"/>
+      <c r="C91" s="64"/>
       <c r="D91" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="44"/>
-      <c r="F91" s="62" t="s">
+      <c r="F91" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="G91" s="63"/>
+      <c r="G91" s="64"/>
       <c r="H91" s="45" t="s">
         <v>35</v>
       </c>
@@ -7172,11 +7243,11 @@
       <c r="Y91" s="35"/>
       <c r="Z91" s="35"/>
       <c r="AA91" s="35"/>
-      <c r="AB91" s="142"/>
+      <c r="AB91" s="62"/>
       <c r="AC91" s="50"/>
       <c r="AD91" s="35"/>
       <c r="AE91" s="35"/>
-      <c r="AF91" s="142"/>
+      <c r="AF91" s="62"/>
       <c r="AG91" s="50"/>
       <c r="AH91" s="35"/>
       <c r="AI91" s="35"/>
@@ -7192,52 +7263,52 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="62" t="s">
+      <c r="B92" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="63"/>
+      <c r="C92" s="64"/>
       <c r="D92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="44"/>
-      <c r="F92" s="62" t="s">
+      <c r="F92" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="G92" s="63"/>
+      <c r="G92" s="64"/>
       <c r="H92" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I92" s="32"/>
-      <c r="J92" s="66"/>
-      <c r="K92" s="67"/>
+      <c r="J92" s="67"/>
+      <c r="K92" s="68"/>
       <c r="L92" s="60"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="74"/>
-      <c r="O92" s="75"/>
+      <c r="N92" s="81"/>
+      <c r="O92" s="82"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="36"/>
-      <c r="R92" s="74"/>
-      <c r="S92" s="75"/>
+      <c r="R92" s="81"/>
+      <c r="S92" s="82"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="74"/>
-      <c r="W92" s="75"/>
+      <c r="V92" s="81"/>
+      <c r="W92" s="82"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="74"/>
-      <c r="AA92" s="75"/>
+      <c r="Z92" s="81"/>
+      <c r="AA92" s="82"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="74"/>
-      <c r="AE92" s="75"/>
+      <c r="AD92" s="81"/>
+      <c r="AE92" s="82"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="74"/>
-      <c r="AI92" s="75"/>
+      <c r="AH92" s="81"/>
+      <c r="AI92" s="82"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="74"/>
-      <c r="AM92" s="75"/>
+      <c r="AL92" s="81"/>
+      <c r="AM92" s="82"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -7246,45 +7317,45 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="62"/>
-      <c r="C93" s="63"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="64"/>
       <c r="D93" s="45"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="62"/>
-      <c r="G93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="64"/>
       <c r="H93" s="45"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="91"/>
-      <c r="K93" s="92"/>
-      <c r="L93" s="93"/>
+      <c r="J93" s="94"/>
+      <c r="K93" s="95"/>
+      <c r="L93" s="96"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="76"/>
-      <c r="O93" s="77"/>
-      <c r="P93" s="78"/>
+      <c r="N93" s="83"/>
+      <c r="O93" s="84"/>
+      <c r="P93" s="85"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="76"/>
-      <c r="S93" s="77"/>
-      <c r="T93" s="78"/>
+      <c r="R93" s="83"/>
+      <c r="S93" s="84"/>
+      <c r="T93" s="85"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="76"/>
-      <c r="W93" s="77"/>
-      <c r="X93" s="78"/>
+      <c r="V93" s="83"/>
+      <c r="W93" s="84"/>
+      <c r="X93" s="85"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="76"/>
-      <c r="AA93" s="77"/>
-      <c r="AB93" s="78"/>
+      <c r="Z93" s="83"/>
+      <c r="AA93" s="84"/>
+      <c r="AB93" s="85"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="76"/>
-      <c r="AE93" s="77"/>
-      <c r="AF93" s="78"/>
+      <c r="AD93" s="83"/>
+      <c r="AE93" s="84"/>
+      <c r="AF93" s="85"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="76"/>
-      <c r="AI93" s="77"/>
-      <c r="AJ93" s="78"/>
+      <c r="AH93" s="83"/>
+      <c r="AI93" s="84"/>
+      <c r="AJ93" s="85"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="76"/>
-      <c r="AM93" s="77"/>
-      <c r="AN93" s="78"/>
+      <c r="AL93" s="83"/>
+      <c r="AM93" s="84"/>
+      <c r="AN93" s="85"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -7292,45 +7363,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="62"/>
-      <c r="C94" s="63"/>
+      <c r="B94" s="63"/>
+      <c r="C94" s="64"/>
       <c r="D94" s="45"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="62"/>
-      <c r="G94" s="63"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="64"/>
       <c r="H94" s="45"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="68"/>
-      <c r="K94" s="69"/>
-      <c r="L94" s="94"/>
+      <c r="J94" s="69"/>
+      <c r="K94" s="70"/>
+      <c r="L94" s="97"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="79"/>
-      <c r="O94" s="80"/>
-      <c r="P94" s="81"/>
+      <c r="N94" s="86"/>
+      <c r="O94" s="87"/>
+      <c r="P94" s="88"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="79"/>
-      <c r="S94" s="80"/>
-      <c r="T94" s="81"/>
+      <c r="R94" s="86"/>
+      <c r="S94" s="87"/>
+      <c r="T94" s="88"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="79"/>
-      <c r="W94" s="80"/>
-      <c r="X94" s="81"/>
+      <c r="V94" s="86"/>
+      <c r="W94" s="87"/>
+      <c r="X94" s="88"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="79"/>
-      <c r="AA94" s="80"/>
-      <c r="AB94" s="81"/>
+      <c r="Z94" s="86"/>
+      <c r="AA94" s="87"/>
+      <c r="AB94" s="88"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="79"/>
-      <c r="AE94" s="80"/>
-      <c r="AF94" s="81"/>
+      <c r="AD94" s="86"/>
+      <c r="AE94" s="87"/>
+      <c r="AF94" s="88"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="79"/>
-      <c r="AI94" s="80"/>
-      <c r="AJ94" s="81"/>
+      <c r="AH94" s="86"/>
+      <c r="AI94" s="87"/>
+      <c r="AJ94" s="88"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="79"/>
-      <c r="AM94" s="80"/>
-      <c r="AN94" s="81"/>
+      <c r="AL94" s="86"/>
+      <c r="AM94" s="87"/>
+      <c r="AN94" s="88"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7338,45 +7409,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="62"/>
-      <c r="C95" s="63"/>
+      <c r="B95" s="63"/>
+      <c r="C95" s="64"/>
       <c r="D95" s="45"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="62"/>
-      <c r="G95" s="63"/>
+      <c r="F95" s="63"/>
+      <c r="G95" s="64"/>
       <c r="H95" s="45"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="82"/>
-      <c r="K95" s="83"/>
-      <c r="L95" s="84"/>
+      <c r="J95" s="75"/>
+      <c r="K95" s="76"/>
+      <c r="L95" s="77"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="82"/>
-      <c r="O95" s="83"/>
-      <c r="P95" s="84"/>
+      <c r="N95" s="75"/>
+      <c r="O95" s="76"/>
+      <c r="P95" s="77"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="82"/>
-      <c r="S95" s="83"/>
-      <c r="T95" s="84"/>
+      <c r="R95" s="75"/>
+      <c r="S95" s="76"/>
+      <c r="T95" s="77"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="82"/>
-      <c r="W95" s="83"/>
-      <c r="X95" s="84"/>
+      <c r="V95" s="75"/>
+      <c r="W95" s="76"/>
+      <c r="X95" s="77"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="82"/>
-      <c r="AA95" s="83"/>
-      <c r="AB95" s="84"/>
+      <c r="Z95" s="75"/>
+      <c r="AA95" s="76"/>
+      <c r="AB95" s="77"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="82"/>
-      <c r="AE95" s="83"/>
-      <c r="AF95" s="84"/>
+      <c r="AD95" s="75"/>
+      <c r="AE95" s="76"/>
+      <c r="AF95" s="77"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="82"/>
-      <c r="AI95" s="83"/>
-      <c r="AJ95" s="84"/>
+      <c r="AH95" s="75"/>
+      <c r="AI95" s="76"/>
+      <c r="AJ95" s="77"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="82"/>
-      <c r="AM95" s="83"/>
-      <c r="AN95" s="84"/>
+      <c r="AL95" s="75"/>
+      <c r="AM95" s="76"/>
+      <c r="AN95" s="77"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7384,45 +7455,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="64"/>
-      <c r="C96" s="65"/>
+      <c r="B96" s="65"/>
+      <c r="C96" s="66"/>
       <c r="D96" s="42"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="64"/>
-      <c r="G96" s="65"/>
+      <c r="F96" s="65"/>
+      <c r="G96" s="66"/>
       <c r="H96" s="42"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="85"/>
-      <c r="K96" s="86"/>
-      <c r="L96" s="87"/>
+      <c r="J96" s="78"/>
+      <c r="K96" s="79"/>
+      <c r="L96" s="80"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="85"/>
-      <c r="O96" s="86"/>
-      <c r="P96" s="87"/>
+      <c r="N96" s="78"/>
+      <c r="O96" s="79"/>
+      <c r="P96" s="80"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="85"/>
-      <c r="S96" s="86"/>
-      <c r="T96" s="87"/>
+      <c r="R96" s="78"/>
+      <c r="S96" s="79"/>
+      <c r="T96" s="80"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="85"/>
-      <c r="W96" s="86"/>
-      <c r="X96" s="87"/>
+      <c r="V96" s="78"/>
+      <c r="W96" s="79"/>
+      <c r="X96" s="80"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="85"/>
-      <c r="AA96" s="86"/>
-      <c r="AB96" s="87"/>
+      <c r="Z96" s="78"/>
+      <c r="AA96" s="79"/>
+      <c r="AB96" s="80"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="85"/>
-      <c r="AE96" s="86"/>
-      <c r="AF96" s="87"/>
+      <c r="AD96" s="78"/>
+      <c r="AE96" s="79"/>
+      <c r="AF96" s="80"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="85"/>
-      <c r="AI96" s="86"/>
-      <c r="AJ96" s="87"/>
+      <c r="AH96" s="78"/>
+      <c r="AI96" s="79"/>
+      <c r="AJ96" s="80"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="85"/>
-      <c r="AM96" s="86"/>
-      <c r="AN96" s="87"/>
+      <c r="AL96" s="78"/>
+      <c r="AM96" s="79"/>
+      <c r="AN96" s="80"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7476,46 +7547,46 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="66" t="s">
+      <c r="B98" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C98" s="67"/>
+      <c r="C98" s="68"/>
       <c r="D98" s="60"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="66"/>
-      <c r="G98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="68"/>
       <c r="H98" s="60"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="66"/>
-      <c r="K98" s="67"/>
+      <c r="J98" s="67"/>
+      <c r="K98" s="68"/>
       <c r="L98" s="60"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="74"/>
-      <c r="O98" s="75"/>
+      <c r="N98" s="81"/>
+      <c r="O98" s="82"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="74"/>
-      <c r="S98" s="75"/>
+      <c r="R98" s="81"/>
+      <c r="S98" s="82"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="74"/>
-      <c r="W98" s="75"/>
+      <c r="V98" s="81"/>
+      <c r="W98" s="82"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="74"/>
-      <c r="AA98" s="75"/>
+      <c r="Z98" s="81"/>
+      <c r="AA98" s="82"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="74"/>
-      <c r="AE98" s="75"/>
+      <c r="AD98" s="81"/>
+      <c r="AE98" s="82"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="74"/>
-      <c r="AI98" s="75"/>
+      <c r="AH98" s="81"/>
+      <c r="AI98" s="82"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="74"/>
-      <c r="AM98" s="75"/>
+      <c r="AL98" s="81"/>
+      <c r="AM98" s="82"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7524,47 +7595,47 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="91" t="s">
+      <c r="B99" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="C99" s="92"/>
-      <c r="D99" s="93"/>
+      <c r="C99" s="95"/>
+      <c r="D99" s="96"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="91"/>
-      <c r="G99" s="92"/>
-      <c r="H99" s="93"/>
+      <c r="F99" s="94"/>
+      <c r="G99" s="95"/>
+      <c r="H99" s="96"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="91"/>
-      <c r="K99" s="92"/>
-      <c r="L99" s="93"/>
+      <c r="J99" s="94"/>
+      <c r="K99" s="95"/>
+      <c r="L99" s="96"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="76"/>
-      <c r="O99" s="77"/>
-      <c r="P99" s="78"/>
+      <c r="N99" s="83"/>
+      <c r="O99" s="84"/>
+      <c r="P99" s="85"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="76"/>
-      <c r="S99" s="77"/>
-      <c r="T99" s="78"/>
+      <c r="R99" s="83"/>
+      <c r="S99" s="84"/>
+      <c r="T99" s="85"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="76"/>
-      <c r="W99" s="77"/>
-      <c r="X99" s="78"/>
+      <c r="V99" s="83"/>
+      <c r="W99" s="84"/>
+      <c r="X99" s="85"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="76"/>
-      <c r="AA99" s="77"/>
-      <c r="AB99" s="78"/>
+      <c r="Z99" s="83"/>
+      <c r="AA99" s="84"/>
+      <c r="AB99" s="85"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="76"/>
-      <c r="AE99" s="77"/>
-      <c r="AF99" s="78"/>
+      <c r="AD99" s="83"/>
+      <c r="AE99" s="84"/>
+      <c r="AF99" s="85"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="76"/>
-      <c r="AI99" s="77"/>
-      <c r="AJ99" s="78"/>
+      <c r="AH99" s="83"/>
+      <c r="AI99" s="84"/>
+      <c r="AJ99" s="85"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="76"/>
-      <c r="AM99" s="77"/>
-      <c r="AN99" s="78"/>
+      <c r="AL99" s="83"/>
+      <c r="AM99" s="84"/>
+      <c r="AN99" s="85"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7572,45 +7643,45 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="69"/>
-      <c r="D100" s="94"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="70"/>
+      <c r="D100" s="97"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="69"/>
-      <c r="H100" s="94"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="70"/>
+      <c r="H100" s="97"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="68"/>
-      <c r="K100" s="69"/>
-      <c r="L100" s="94"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="70"/>
+      <c r="L100" s="97"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="79"/>
-      <c r="O100" s="80"/>
-      <c r="P100" s="81"/>
+      <c r="N100" s="86"/>
+      <c r="O100" s="87"/>
+      <c r="P100" s="88"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="79"/>
-      <c r="S100" s="80"/>
-      <c r="T100" s="81"/>
+      <c r="R100" s="86"/>
+      <c r="S100" s="87"/>
+      <c r="T100" s="88"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="79"/>
-      <c r="W100" s="80"/>
-      <c r="X100" s="81"/>
+      <c r="V100" s="86"/>
+      <c r="W100" s="87"/>
+      <c r="X100" s="88"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="79"/>
-      <c r="AA100" s="80"/>
-      <c r="AB100" s="81"/>
+      <c r="Z100" s="86"/>
+      <c r="AA100" s="87"/>
+      <c r="AB100" s="88"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="79"/>
-      <c r="AE100" s="80"/>
-      <c r="AF100" s="81"/>
+      <c r="AD100" s="86"/>
+      <c r="AE100" s="87"/>
+      <c r="AF100" s="88"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="79"/>
-      <c r="AI100" s="80"/>
-      <c r="AJ100" s="81"/>
+      <c r="AH100" s="86"/>
+      <c r="AI100" s="87"/>
+      <c r="AJ100" s="88"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="79"/>
-      <c r="AM100" s="80"/>
-      <c r="AN100" s="81"/>
+      <c r="AL100" s="86"/>
+      <c r="AM100" s="87"/>
+      <c r="AN100" s="88"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7618,47 +7689,47 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="82" t="s">
+      <c r="B101" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="83"/>
-      <c r="D101" s="84"/>
+      <c r="C101" s="76"/>
+      <c r="D101" s="77"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="82"/>
-      <c r="G101" s="83"/>
-      <c r="H101" s="84"/>
+      <c r="F101" s="75"/>
+      <c r="G101" s="76"/>
+      <c r="H101" s="77"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="82"/>
-      <c r="K101" s="83"/>
-      <c r="L101" s="84"/>
+      <c r="J101" s="75"/>
+      <c r="K101" s="76"/>
+      <c r="L101" s="77"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="82"/>
-      <c r="O101" s="83"/>
-      <c r="P101" s="84"/>
+      <c r="N101" s="75"/>
+      <c r="O101" s="76"/>
+      <c r="P101" s="77"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="82"/>
-      <c r="S101" s="83"/>
-      <c r="T101" s="84"/>
+      <c r="R101" s="75"/>
+      <c r="S101" s="76"/>
+      <c r="T101" s="77"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="82"/>
-      <c r="W101" s="83"/>
-      <c r="X101" s="84"/>
+      <c r="V101" s="75"/>
+      <c r="W101" s="76"/>
+      <c r="X101" s="77"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="82"/>
-      <c r="AA101" s="83"/>
-      <c r="AB101" s="84"/>
+      <c r="Z101" s="75"/>
+      <c r="AA101" s="76"/>
+      <c r="AB101" s="77"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="82"/>
-      <c r="AE101" s="83"/>
-      <c r="AF101" s="84"/>
+      <c r="AD101" s="75"/>
+      <c r="AE101" s="76"/>
+      <c r="AF101" s="77"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="82"/>
-      <c r="AI101" s="83"/>
-      <c r="AJ101" s="84"/>
+      <c r="AH101" s="75"/>
+      <c r="AI101" s="76"/>
+      <c r="AJ101" s="77"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="82"/>
-      <c r="AM101" s="83"/>
-      <c r="AN101" s="84"/>
+      <c r="AL101" s="75"/>
+      <c r="AM101" s="76"/>
+      <c r="AN101" s="77"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7666,45 +7737,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="85"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="87"/>
+      <c r="B102" s="78"/>
+      <c r="C102" s="79"/>
+      <c r="D102" s="80"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="86"/>
-      <c r="H102" s="87"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="79"/>
+      <c r="H102" s="80"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="85"/>
-      <c r="K102" s="86"/>
-      <c r="L102" s="87"/>
+      <c r="J102" s="78"/>
+      <c r="K102" s="79"/>
+      <c r="L102" s="80"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="85"/>
-      <c r="O102" s="86"/>
-      <c r="P102" s="87"/>
+      <c r="N102" s="78"/>
+      <c r="O102" s="79"/>
+      <c r="P102" s="80"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="85"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="87"/>
+      <c r="R102" s="78"/>
+      <c r="S102" s="79"/>
+      <c r="T102" s="80"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="85"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="87"/>
+      <c r="V102" s="78"/>
+      <c r="W102" s="79"/>
+      <c r="X102" s="80"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="85"/>
-      <c r="AA102" s="86"/>
-      <c r="AB102" s="87"/>
+      <c r="Z102" s="78"/>
+      <c r="AA102" s="79"/>
+      <c r="AB102" s="80"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="85"/>
-      <c r="AE102" s="86"/>
-      <c r="AF102" s="87"/>
+      <c r="AD102" s="78"/>
+      <c r="AE102" s="79"/>
+      <c r="AF102" s="80"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="85"/>
-      <c r="AI102" s="86"/>
-      <c r="AJ102" s="87"/>
+      <c r="AH102" s="78"/>
+      <c r="AI102" s="79"/>
+      <c r="AJ102" s="80"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="85"/>
-      <c r="AM102" s="86"/>
-      <c r="AN102" s="87"/>
+      <c r="AL102" s="78"/>
+      <c r="AM102" s="79"/>
+      <c r="AN102" s="80"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7774,70 +7845,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="74"/>
-      <c r="C105" s="75"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="82"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="75"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="82"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="74"/>
-      <c r="K105" s="75"/>
+      <c r="J105" s="81"/>
+      <c r="K105" s="82"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="76"/>
-      <c r="C106" s="77"/>
-      <c r="D106" s="78"/>
+      <c r="B106" s="83"/>
+      <c r="C106" s="84"/>
+      <c r="D106" s="85"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="76"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="78"/>
+      <c r="F106" s="83"/>
+      <c r="G106" s="84"/>
+      <c r="H106" s="85"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="76"/>
-      <c r="K106" s="77"/>
-      <c r="L106" s="78"/>
+      <c r="J106" s="83"/>
+      <c r="K106" s="84"/>
+      <c r="L106" s="85"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="79"/>
-      <c r="C107" s="80"/>
-      <c r="D107" s="81"/>
+      <c r="B107" s="86"/>
+      <c r="C107" s="87"/>
+      <c r="D107" s="88"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="79"/>
-      <c r="G107" s="80"/>
-      <c r="H107" s="81"/>
+      <c r="F107" s="86"/>
+      <c r="G107" s="87"/>
+      <c r="H107" s="88"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="79"/>
-      <c r="K107" s="80"/>
-      <c r="L107" s="81"/>
+      <c r="J107" s="86"/>
+      <c r="K107" s="87"/>
+      <c r="L107" s="88"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="82"/>
-      <c r="C108" s="83"/>
-      <c r="D108" s="84"/>
+      <c r="B108" s="75"/>
+      <c r="C108" s="76"/>
+      <c r="D108" s="77"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="83"/>
-      <c r="H108" s="84"/>
+      <c r="F108" s="75"/>
+      <c r="G108" s="76"/>
+      <c r="H108" s="77"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="82"/>
-      <c r="K108" s="83"/>
-      <c r="L108" s="84"/>
+      <c r="J108" s="75"/>
+      <c r="K108" s="76"/>
+      <c r="L108" s="77"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="85"/>
-      <c r="C109" s="86"/>
-      <c r="D109" s="87"/>
+      <c r="B109" s="78"/>
+      <c r="C109" s="79"/>
+      <c r="D109" s="80"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="85"/>
-      <c r="G109" s="86"/>
-      <c r="H109" s="87"/>
+      <c r="F109" s="78"/>
+      <c r="G109" s="79"/>
+      <c r="H109" s="80"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="85"/>
-      <c r="K109" s="86"/>
-      <c r="L109" s="87"/>
+      <c r="J109" s="78"/>
+      <c r="K109" s="79"/>
+      <c r="L109" s="80"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7853,69 +7924,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="74"/>
-      <c r="C111" s="75"/>
+      <c r="B111" s="81"/>
+      <c r="C111" s="82"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="74"/>
-      <c r="G111" s="75"/>
+      <c r="F111" s="81"/>
+      <c r="G111" s="82"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="74"/>
-      <c r="K111" s="75"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="82"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="76"/>
-      <c r="C112" s="77"/>
-      <c r="D112" s="78"/>
+      <c r="B112" s="83"/>
+      <c r="C112" s="84"/>
+      <c r="D112" s="85"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="76"/>
-      <c r="G112" s="77"/>
-      <c r="H112" s="78"/>
+      <c r="F112" s="83"/>
+      <c r="G112" s="84"/>
+      <c r="H112" s="85"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="76"/>
-      <c r="K112" s="77"/>
-      <c r="L112" s="78"/>
+      <c r="J112" s="83"/>
+      <c r="K112" s="84"/>
+      <c r="L112" s="85"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="79"/>
-      <c r="C113" s="80"/>
-      <c r="D113" s="81"/>
+      <c r="B113" s="86"/>
+      <c r="C113" s="87"/>
+      <c r="D113" s="88"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="79"/>
-      <c r="G113" s="80"/>
-      <c r="H113" s="81"/>
+      <c r="F113" s="86"/>
+      <c r="G113" s="87"/>
+      <c r="H113" s="88"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="79"/>
-      <c r="K113" s="80"/>
-      <c r="L113" s="81"/>
+      <c r="J113" s="86"/>
+      <c r="K113" s="87"/>
+      <c r="L113" s="88"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="82"/>
-      <c r="C114" s="83"/>
-      <c r="D114" s="84"/>
+      <c r="B114" s="75"/>
+      <c r="C114" s="76"/>
+      <c r="D114" s="77"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="82"/>
-      <c r="G114" s="83"/>
-      <c r="H114" s="84"/>
+      <c r="F114" s="75"/>
+      <c r="G114" s="76"/>
+      <c r="H114" s="77"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="82"/>
-      <c r="K114" s="83"/>
-      <c r="L114" s="84"/>
+      <c r="J114" s="75"/>
+      <c r="K114" s="76"/>
+      <c r="L114" s="77"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="85"/>
-      <c r="C115" s="86"/>
-      <c r="D115" s="87"/>
+      <c r="B115" s="78"/>
+      <c r="C115" s="79"/>
+      <c r="D115" s="80"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="85"/>
-      <c r="G115" s="86"/>
-      <c r="H115" s="87"/>
+      <c r="F115" s="78"/>
+      <c r="G115" s="79"/>
+      <c r="H115" s="80"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="85"/>
-      <c r="K115" s="86"/>
-      <c r="L115" s="87"/>
+      <c r="J115" s="78"/>
+      <c r="K115" s="79"/>
+      <c r="L115" s="80"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7931,69 +8002,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="74"/>
-      <c r="C117" s="75"/>
+      <c r="B117" s="81"/>
+      <c r="C117" s="82"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="74"/>
-      <c r="G117" s="75"/>
+      <c r="F117" s="81"/>
+      <c r="G117" s="82"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="74"/>
-      <c r="K117" s="75"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="82"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="76"/>
-      <c r="C118" s="77"/>
-      <c r="D118" s="78"/>
+      <c r="B118" s="83"/>
+      <c r="C118" s="84"/>
+      <c r="D118" s="85"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="76"/>
-      <c r="G118" s="77"/>
-      <c r="H118" s="78"/>
+      <c r="F118" s="83"/>
+      <c r="G118" s="84"/>
+      <c r="H118" s="85"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="76"/>
-      <c r="K118" s="77"/>
-      <c r="L118" s="78"/>
+      <c r="J118" s="83"/>
+      <c r="K118" s="84"/>
+      <c r="L118" s="85"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="79"/>
-      <c r="C119" s="80"/>
-      <c r="D119" s="81"/>
+      <c r="B119" s="86"/>
+      <c r="C119" s="87"/>
+      <c r="D119" s="88"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="79"/>
-      <c r="G119" s="80"/>
-      <c r="H119" s="81"/>
+      <c r="F119" s="86"/>
+      <c r="G119" s="87"/>
+      <c r="H119" s="88"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="79"/>
-      <c r="K119" s="80"/>
-      <c r="L119" s="81"/>
+      <c r="J119" s="86"/>
+      <c r="K119" s="87"/>
+      <c r="L119" s="88"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="82"/>
-      <c r="C120" s="83"/>
-      <c r="D120" s="84"/>
+      <c r="B120" s="75"/>
+      <c r="C120" s="76"/>
+      <c r="D120" s="77"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="82"/>
-      <c r="G120" s="83"/>
-      <c r="H120" s="84"/>
+      <c r="F120" s="75"/>
+      <c r="G120" s="76"/>
+      <c r="H120" s="77"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="82"/>
-      <c r="K120" s="83"/>
-      <c r="L120" s="84"/>
+      <c r="J120" s="75"/>
+      <c r="K120" s="76"/>
+      <c r="L120" s="77"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="85"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="87"/>
+      <c r="B121" s="78"/>
+      <c r="C121" s="79"/>
+      <c r="D121" s="80"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="85"/>
-      <c r="G121" s="86"/>
-      <c r="H121" s="87"/>
+      <c r="F121" s="78"/>
+      <c r="G121" s="79"/>
+      <c r="H121" s="80"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="85"/>
-      <c r="K121" s="86"/>
-      <c r="L121" s="87"/>
+      <c r="J121" s="78"/>
+      <c r="K121" s="79"/>
+      <c r="L121" s="80"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -8009,69 +8080,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="74"/>
-      <c r="C123" s="75"/>
+      <c r="B123" s="81"/>
+      <c r="C123" s="82"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="74"/>
-      <c r="G123" s="75"/>
+      <c r="F123" s="81"/>
+      <c r="G123" s="82"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="74"/>
-      <c r="K123" s="75"/>
+      <c r="J123" s="81"/>
+      <c r="K123" s="82"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="76"/>
-      <c r="C124" s="77"/>
-      <c r="D124" s="78"/>
+      <c r="B124" s="83"/>
+      <c r="C124" s="84"/>
+      <c r="D124" s="85"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="76"/>
-      <c r="G124" s="77"/>
-      <c r="H124" s="78"/>
+      <c r="F124" s="83"/>
+      <c r="G124" s="84"/>
+      <c r="H124" s="85"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="76"/>
-      <c r="K124" s="77"/>
-      <c r="L124" s="78"/>
+      <c r="J124" s="83"/>
+      <c r="K124" s="84"/>
+      <c r="L124" s="85"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="79"/>
-      <c r="C125" s="80"/>
-      <c r="D125" s="81"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="87"/>
+      <c r="D125" s="88"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="79"/>
-      <c r="G125" s="80"/>
-      <c r="H125" s="81"/>
+      <c r="F125" s="86"/>
+      <c r="G125" s="87"/>
+      <c r="H125" s="88"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="79"/>
-      <c r="K125" s="80"/>
-      <c r="L125" s="81"/>
+      <c r="J125" s="86"/>
+      <c r="K125" s="87"/>
+      <c r="L125" s="88"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="82"/>
-      <c r="C126" s="83"/>
-      <c r="D126" s="84"/>
+      <c r="B126" s="75"/>
+      <c r="C126" s="76"/>
+      <c r="D126" s="77"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="82"/>
-      <c r="G126" s="83"/>
-      <c r="H126" s="84"/>
+      <c r="F126" s="75"/>
+      <c r="G126" s="76"/>
+      <c r="H126" s="77"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="82"/>
-      <c r="K126" s="83"/>
-      <c r="L126" s="84"/>
+      <c r="J126" s="75"/>
+      <c r="K126" s="76"/>
+      <c r="L126" s="77"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="85"/>
-      <c r="C127" s="86"/>
-      <c r="D127" s="87"/>
+      <c r="B127" s="78"/>
+      <c r="C127" s="79"/>
+      <c r="D127" s="80"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="85"/>
-      <c r="G127" s="86"/>
-      <c r="H127" s="87"/>
+      <c r="F127" s="78"/>
+      <c r="G127" s="79"/>
+      <c r="H127" s="80"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="85"/>
-      <c r="K127" s="86"/>
-      <c r="L127" s="87"/>
+      <c r="J127" s="78"/>
+      <c r="K127" s="79"/>
+      <c r="L127" s="80"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8087,69 +8158,69 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="74"/>
-      <c r="C129" s="75"/>
+      <c r="B129" s="81"/>
+      <c r="C129" s="82"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="74"/>
-      <c r="G129" s="75"/>
+      <c r="F129" s="81"/>
+      <c r="G129" s="82"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="74"/>
-      <c r="K129" s="75"/>
+      <c r="J129" s="81"/>
+      <c r="K129" s="82"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="76"/>
-      <c r="C130" s="77"/>
-      <c r="D130" s="78"/>
+      <c r="B130" s="83"/>
+      <c r="C130" s="84"/>
+      <c r="D130" s="85"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="77"/>
-      <c r="H130" s="78"/>
+      <c r="F130" s="83"/>
+      <c r="G130" s="84"/>
+      <c r="H130" s="85"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="76"/>
-      <c r="K130" s="77"/>
-      <c r="L130" s="78"/>
+      <c r="J130" s="83"/>
+      <c r="K130" s="84"/>
+      <c r="L130" s="85"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="79"/>
-      <c r="C131" s="80"/>
-      <c r="D131" s="81"/>
+      <c r="B131" s="86"/>
+      <c r="C131" s="87"/>
+      <c r="D131" s="88"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="79"/>
-      <c r="G131" s="80"/>
-      <c r="H131" s="81"/>
+      <c r="F131" s="86"/>
+      <c r="G131" s="87"/>
+      <c r="H131" s="88"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="79"/>
-      <c r="K131" s="80"/>
-      <c r="L131" s="81"/>
+      <c r="J131" s="86"/>
+      <c r="K131" s="87"/>
+      <c r="L131" s="88"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="82"/>
-      <c r="C132" s="83"/>
-      <c r="D132" s="84"/>
+      <c r="B132" s="75"/>
+      <c r="C132" s="76"/>
+      <c r="D132" s="77"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="82"/>
-      <c r="G132" s="83"/>
-      <c r="H132" s="84"/>
+      <c r="F132" s="75"/>
+      <c r="G132" s="76"/>
+      <c r="H132" s="77"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="82"/>
-      <c r="K132" s="83"/>
-      <c r="L132" s="84"/>
+      <c r="J132" s="75"/>
+      <c r="K132" s="76"/>
+      <c r="L132" s="77"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="85"/>
-      <c r="C133" s="86"/>
-      <c r="D133" s="87"/>
+      <c r="B133" s="78"/>
+      <c r="C133" s="79"/>
+      <c r="D133" s="80"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="85"/>
-      <c r="G133" s="86"/>
-      <c r="H133" s="87"/>
+      <c r="F133" s="78"/>
+      <c r="G133" s="79"/>
+      <c r="H133" s="80"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="85"/>
-      <c r="K133" s="86"/>
-      <c r="L133" s="87"/>
+      <c r="J133" s="78"/>
+      <c r="K133" s="79"/>
+      <c r="L133" s="80"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
@@ -8193,6 +8264,7 @@
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:C27"/>
@@ -8251,9 +8323,12 @@
     <mergeCell ref="AL31:AM31"/>
     <mergeCell ref="AL22:AM22"/>
     <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
     <mergeCell ref="AL32:AN32"/>
     <mergeCell ref="Z31:AA31"/>
     <mergeCell ref="Z35:AB35"/>
@@ -8272,7 +8347,12 @@
     <mergeCell ref="AL47:AN47"/>
     <mergeCell ref="AH47:AJ47"/>
     <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AD43:AE43"/>
+    <mergeCell ref="AD44:AF44"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
     <mergeCell ref="Z48:AB48"/>
     <mergeCell ref="Z53:AB53"/>
     <mergeCell ref="Z49:AB49"/>
@@ -8289,6 +8369,10 @@
     <mergeCell ref="Z64:AB64"/>
     <mergeCell ref="Z60:AB60"/>
     <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="V52:X52"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="V59:X59"/>
     <mergeCell ref="Z93:AB93"/>
     <mergeCell ref="Z92:AA92"/>
     <mergeCell ref="V92:W92"/>
@@ -8313,7 +8397,6 @@
     <mergeCell ref="R64:T64"/>
     <mergeCell ref="Z76:AB76"/>
     <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="N76:P76"/>
     <mergeCell ref="N55:P55"/>
     <mergeCell ref="N57:P57"/>
     <mergeCell ref="R56:T56"/>
@@ -8332,6 +8415,11 @@
     <mergeCell ref="V77:X77"/>
     <mergeCell ref="R57:T57"/>
     <mergeCell ref="R55:T55"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V74:W74"/>
     <mergeCell ref="Z75:AB75"/>
     <mergeCell ref="Z77:AB77"/>
     <mergeCell ref="N81:P81"/>
@@ -8348,11 +8436,12 @@
     <mergeCell ref="R89:T89"/>
     <mergeCell ref="Z87:AB87"/>
     <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="N76:P76"/>
     <mergeCell ref="R61:T61"/>
     <mergeCell ref="N72:P72"/>
     <mergeCell ref="J61:L61"/>
@@ -8366,6 +8455,11 @@
     <mergeCell ref="R69:T69"/>
     <mergeCell ref="N70:P70"/>
     <mergeCell ref="N63:P63"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J63:L63"/>
     <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="AD84:AF84"/>
     <mergeCell ref="AH84:AJ84"/>
@@ -8414,6 +8508,12 @@
     <mergeCell ref="AH88:AJ88"/>
     <mergeCell ref="AH89:AJ89"/>
     <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="V32:X32"/>
     <mergeCell ref="AL82:AN82"/>
     <mergeCell ref="V62:X62"/>
     <mergeCell ref="V63:X63"/>
@@ -8432,15 +8532,6 @@
     <mergeCell ref="AL63:AN63"/>
     <mergeCell ref="AH64:AJ64"/>
     <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
     <mergeCell ref="AH31:AI31"/>
     <mergeCell ref="AD32:AF32"/>
     <mergeCell ref="AL81:AN81"/>
@@ -8458,15 +8549,13 @@
     <mergeCell ref="AL60:AN60"/>
     <mergeCell ref="AL64:AN64"/>
     <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="Z52:AB52"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AD60:AF60"/>
     <mergeCell ref="AH23:AI23"/>
     <mergeCell ref="AD22:AE22"/>
     <mergeCell ref="AH22:AI22"/>
@@ -8476,6 +8565,21 @@
     <mergeCell ref="AD33:AF33"/>
     <mergeCell ref="AH33:AJ33"/>
     <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AD45:AF45"/>
+    <mergeCell ref="AH37:AI37"/>
+    <mergeCell ref="AH38:AJ38"/>
+    <mergeCell ref="AH43:AI43"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AH45:AJ45"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z59:AB59"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="AD38:AF38"/>
     <mergeCell ref="V22:W22"/>
     <mergeCell ref="Z22:AA22"/>
     <mergeCell ref="N23:O23"/>
@@ -8493,6 +8597,9 @@
     <mergeCell ref="R12:S12"/>
     <mergeCell ref="V12:W12"/>
     <mergeCell ref="R9:T9"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="Z9:AB9"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="V1:X1"/>
     <mergeCell ref="V14:X14"/>
@@ -8505,6 +8612,8 @@
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="V13:X13"/>
     <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="J1:L1"/>
@@ -8572,21 +8681,6 @@
     <mergeCell ref="F101:H101"/>
     <mergeCell ref="F99:H99"/>
     <mergeCell ref="B92:C92"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AD45:AF45"/>
-    <mergeCell ref="AH37:AI37"/>
-    <mergeCell ref="AH38:AJ38"/>
-    <mergeCell ref="AH43:AI43"/>
-    <mergeCell ref="AH44:AJ44"/>
-    <mergeCell ref="AH45:AJ45"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
     <mergeCell ref="V24:W24"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="Z23:AA23"/>
@@ -8596,6 +8690,12 @@
     <mergeCell ref="V44:X44"/>
     <mergeCell ref="V45:X45"/>
     <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="V26:W26"/>
     <mergeCell ref="F92:G92"/>
     <mergeCell ref="AH34:AJ34"/>
     <mergeCell ref="AH41:AJ41"/>
@@ -8638,9 +8738,6 @@
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="AH15:AJ15"/>
     <mergeCell ref="J10:L10"/>
@@ -8754,8 +8851,6 @@
     <mergeCell ref="J115:L115"/>
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="F112:H112"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
     <mergeCell ref="J92:K92"/>
     <mergeCell ref="J90:L90"/>
     <mergeCell ref="V86:W86"/>
@@ -8776,10 +8871,10 @@
     <mergeCell ref="V98:W98"/>
     <mergeCell ref="J95:L95"/>
     <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
     <mergeCell ref="J100:L100"/>
-    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
     <mergeCell ref="J80:K80"/>
     <mergeCell ref="N82:P82"/>
     <mergeCell ref="R83:T83"/>
@@ -8792,9 +8887,6 @@
     <mergeCell ref="R80:S80"/>
     <mergeCell ref="R81:T81"/>
     <mergeCell ref="R82:T82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
     <mergeCell ref="J88:L88"/>
     <mergeCell ref="J89:L89"/>
     <mergeCell ref="N87:P87"/>
@@ -8838,6 +8930,11 @@
     <mergeCell ref="R40:T40"/>
     <mergeCell ref="N53:P53"/>
     <mergeCell ref="N39:P39"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="J77:L77"/>
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="R31:S31"/>
     <mergeCell ref="R32:T32"/>
@@ -8862,20 +8959,10 @@
     <mergeCell ref="N50:P50"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="R42:T42"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="F62:H62"/>
     <mergeCell ref="F61:H61"/>
     <mergeCell ref="F42:H42"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="N47:P47"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="F50:H50"/>
     <mergeCell ref="J50:L50"/>
@@ -8883,6 +8970,12 @@
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="J49:L49"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
     <mergeCell ref="AH80:AI80"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="F72:H72"/>
@@ -8907,7 +9000,6 @@
     <mergeCell ref="AH82:AJ82"/>
     <mergeCell ref="AH81:AJ81"/>
     <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z78:AB78"/>
     <mergeCell ref="AD75:AF75"/>
     <mergeCell ref="Z74:AA74"/>
     <mergeCell ref="AH78:AJ78"/>
@@ -8931,9 +9023,7 @@
     <mergeCell ref="AD70:AF70"/>
     <mergeCell ref="AD76:AF76"/>
     <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="Z58:AA58"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="B81:D81"/>
     <mergeCell ref="F76:H76"/>
@@ -8943,7 +9033,6 @@
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F45:G45"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="B56:D56"/>
@@ -8955,18 +9044,10 @@
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="F63:H63"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:K74"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="J56:L56"/>
     <mergeCell ref="J59:K59"/>
     <mergeCell ref="B60:D60"/>
@@ -8977,8 +9058,14 @@
     <mergeCell ref="F57:H57"/>
     <mergeCell ref="J75:L75"/>
     <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="AD95:AF95"/>
     <mergeCell ref="AD96:AF96"/>
     <mergeCell ref="AH51:AI51"/>
@@ -9003,22 +9090,6 @@
     <mergeCell ref="AD52:AF52"/>
     <mergeCell ref="AD58:AE58"/>
     <mergeCell ref="AD59:AF59"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="V52:X52"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="V59:X59"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="Z59:AB59"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AD38:AF38"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="AD46:AF46"/>
     <mergeCell ref="B87:C87"/>
     <mergeCell ref="F87:G87"/>
     <mergeCell ref="B88:C88"/>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -1452,6 +1452,57 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1461,6 +1512,36 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1470,194 +1551,113 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2031,7 +2031,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="175" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2057,197 +2057,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="112" t="s">
+      <c r="J1" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="112"/>
-      <c r="L1" s="113"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="122"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="116" t="s">
+      <c r="N1" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="117" t="s">
+      <c r="R1" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="117" t="s">
+      <c r="V1" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
+      <c r="W1" s="115"/>
+      <c r="X1" s="115"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="117" t="s">
+      <c r="Z1" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="AA1" s="115"/>
+      <c r="AB1" s="115"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="117" t="s">
+      <c r="AD1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="117"/>
-      <c r="AF1" s="117"/>
+      <c r="AE1" s="115"/>
+      <c r="AF1" s="115"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="117" t="s">
+      <c r="AH1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="117"/>
-      <c r="AJ1" s="117"/>
+      <c r="AI1" s="115"/>
+      <c r="AJ1" s="115"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="117" t="s">
+      <c r="AL1" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="117"/>
-      <c r="AN1" s="121"/>
+      <c r="AM1" s="115"/>
+      <c r="AN1" s="116"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="114">
+      <c r="B2" s="123">
         <f>N2-3</f>
         <v>46206</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="115">
+      <c r="F2" s="124">
         <f>N2-2</f>
         <v>46207</v>
       </c>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="115">
+      <c r="J2" s="124">
         <f>N2-1</f>
         <v>46208</v>
       </c>
-      <c r="K2" s="115"/>
-      <c r="L2" s="119"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="127"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="118">
+      <c r="N2" s="126">
         <v>46209</v>
       </c>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="110">
+      <c r="R2" s="117">
         <f>N2+1</f>
         <v>46210</v>
       </c>
-      <c r="S2" s="110"/>
-      <c r="T2" s="110"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="110">
+      <c r="V2" s="117">
         <f>N2+2</f>
         <v>46211</v>
       </c>
-      <c r="W2" s="110"/>
-      <c r="X2" s="110"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="110">
+      <c r="Z2" s="117">
         <f>N2+3</f>
         <v>46212</v>
       </c>
-      <c r="AA2" s="110"/>
-      <c r="AB2" s="110"/>
+      <c r="AA2" s="117"/>
+      <c r="AB2" s="117"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="110">
+      <c r="AD2" s="117">
         <f>N2+4</f>
         <v>46213</v>
       </c>
-      <c r="AE2" s="110"/>
-      <c r="AF2" s="110"/>
+      <c r="AE2" s="117"/>
+      <c r="AF2" s="117"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="110">
+      <c r="AH2" s="117">
         <f>N2+5</f>
         <v>46214</v>
       </c>
-      <c r="AI2" s="110"/>
-      <c r="AJ2" s="110"/>
+      <c r="AI2" s="117"/>
+      <c r="AJ2" s="117"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="110">
+      <c r="AL2" s="117">
         <f>N2+6</f>
         <v>46215</v>
       </c>
-      <c r="AM2" s="110"/>
-      <c r="AN2" s="122"/>
+      <c r="AM2" s="117"/>
+      <c r="AN2" s="118"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2293,139 +2293,139 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="106" t="s">
+      <c r="N4" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="106"/>
-      <c r="T4" s="106"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="106"/>
-      <c r="W4" s="106"/>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="106"/>
-      <c r="Z4" s="106"/>
-      <c r="AA4" s="106"/>
-      <c r="AB4" s="106"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
+      <c r="X4" s="108"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="108"/>
+      <c r="AA4" s="108"/>
+      <c r="AB4" s="108"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="120"/>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AD4" s="119"/>
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="106"/>
-      <c r="O5" s="106"/>
-      <c r="P5" s="106"/>
-      <c r="Q5" s="106"/>
-      <c r="R5" s="106"/>
-      <c r="S5" s="106"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="106"/>
-      <c r="W5" s="106"/>
-      <c r="X5" s="106"/>
-      <c r="Y5" s="106"/>
-      <c r="Z5" s="106"/>
-      <c r="AA5" s="106"/>
-      <c r="AB5" s="106"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="108"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
+      <c r="AD5" s="119"/>
+      <c r="AE5" s="119"/>
+      <c r="AF5" s="119"/>
+      <c r="AG5" s="119"/>
+      <c r="AH5" s="119"/>
+      <c r="AI5" s="119"/>
+      <c r="AJ5" s="119"/>
+      <c r="AK5" s="119"/>
+      <c r="AL5" s="119"/>
+      <c r="AM5" s="119"/>
+      <c r="AN5" s="119"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="75"/>
-      <c r="C6" s="76"/>
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="89"/>
+      <c r="C6" s="90"/>
       <c r="D6" s="59"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="76"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="90"/>
       <c r="H6" s="59"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="76"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="90"/>
       <c r="L6" s="59"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="84"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="84"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="70"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="84"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="70"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="84"/>
+      <c r="Z6" s="69"/>
+      <c r="AA6" s="70"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="83"/>
-      <c r="AE6" s="84"/>
+      <c r="AD6" s="69"/>
+      <c r="AE6" s="70"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="83"/>
-      <c r="AI6" s="84"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="70"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="83"/>
-      <c r="AM6" s="84"/>
+      <c r="AL6" s="69"/>
+      <c r="AM6" s="70"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2436,45 +2436,45 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="93"/>
+      <c r="C7" s="94"/>
       <c r="D7" s="60"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="67"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="94"/>
       <c r="H7" s="60"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="67"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="94"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="92"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="75"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="92"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="75"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="92"/>
+      <c r="V7" s="74"/>
+      <c r="W7" s="75"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="92"/>
+      <c r="Z7" s="74"/>
+      <c r="AA7" s="75"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="92"/>
+      <c r="AD7" s="74"/>
+      <c r="AE7" s="75"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="92"/>
+      <c r="AH7" s="74"/>
+      <c r="AI7" s="75"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="92"/>
+      <c r="AL7" s="74"/>
+      <c r="AM7" s="75"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2485,46 +2485,46 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="69"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71"/>
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="71"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="71"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="79"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="71"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="79"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="70"/>
-      <c r="T8" s="71"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="78"/>
+      <c r="T8" s="79"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="70"/>
-      <c r="X8" s="71"/>
+      <c r="V8" s="77"/>
+      <c r="W8" s="78"/>
+      <c r="X8" s="79"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="70"/>
-      <c r="AB8" s="71"/>
+      <c r="Z8" s="77"/>
+      <c r="AA8" s="78"/>
+      <c r="AB8" s="79"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="70"/>
-      <c r="AF8" s="71"/>
+      <c r="AD8" s="77"/>
+      <c r="AE8" s="78"/>
+      <c r="AF8" s="79"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="69"/>
-      <c r="AI8" s="70"/>
-      <c r="AJ8" s="71"/>
+      <c r="AH8" s="77"/>
+      <c r="AI8" s="78"/>
+      <c r="AJ8" s="79"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="69"/>
-      <c r="AM8" s="70"/>
-      <c r="AN8" s="71"/>
+      <c r="AL8" s="77"/>
+      <c r="AM8" s="78"/>
+      <c r="AN8" s="79"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2534,46 +2534,46 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="90"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="63"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="90"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="65"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="65"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="88"/>
-      <c r="O9" s="89"/>
-      <c r="P9" s="90"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="65"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="89"/>
-      <c r="T9" s="90"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="65"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="90"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="65"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="90"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="65"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="90"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="64"/>
+      <c r="AF9" s="65"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="88"/>
-      <c r="AI9" s="89"/>
-      <c r="AJ9" s="90"/>
+      <c r="AH9" s="63"/>
+      <c r="AI9" s="64"/>
+      <c r="AJ9" s="65"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="88"/>
-      <c r="AM9" s="89"/>
-      <c r="AN9" s="90"/>
+      <c r="AL9" s="63"/>
+      <c r="AM9" s="64"/>
+      <c r="AN9" s="65"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2583,46 +2583,46 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="109"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="101"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="109"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="103"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="109"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="103"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="109"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="103"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="107"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="109"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="103"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="107"/>
-      <c r="W10" s="108"/>
-      <c r="X10" s="109"/>
+      <c r="V10" s="101"/>
+      <c r="W10" s="102"/>
+      <c r="X10" s="103"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="107"/>
-      <c r="AA10" s="108"/>
-      <c r="AB10" s="109"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="102"/>
+      <c r="AB10" s="103"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="107"/>
-      <c r="AE10" s="108"/>
-      <c r="AF10" s="109"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="102"/>
+      <c r="AF10" s="103"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="107"/>
-      <c r="AI10" s="108"/>
-      <c r="AJ10" s="109"/>
+      <c r="AH10" s="101"/>
+      <c r="AI10" s="102"/>
+      <c r="AJ10" s="103"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="107"/>
-      <c r="AM10" s="108"/>
-      <c r="AN10" s="109"/>
+      <c r="AL10" s="101"/>
+      <c r="AM10" s="102"/>
+      <c r="AN10" s="103"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2681,45 +2681,45 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
       <c r="D12" s="59"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="76"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="90"/>
       <c r="H12" s="59"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="76"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="90"/>
       <c r="L12" s="59"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="84"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="70"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="84"/>
+      <c r="V12" s="69"/>
+      <c r="W12" s="70"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="83"/>
-      <c r="AA12" s="84"/>
+      <c r="Z12" s="69"/>
+      <c r="AA12" s="70"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="83"/>
-      <c r="AE12" s="84"/>
+      <c r="AD12" s="69"/>
+      <c r="AE12" s="70"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="83"/>
-      <c r="AI12" s="84"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="70"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="83"/>
-      <c r="AM12" s="84"/>
+      <c r="AL12" s="69"/>
+      <c r="AM12" s="70"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2730,46 +2730,46 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="93"/>
+      <c r="C13" s="94"/>
       <c r="D13" s="60"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="65"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="65"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="82"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="87"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="73"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="85"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="87"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="73"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="85"/>
-      <c r="W13" s="86"/>
-      <c r="X13" s="87"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="73"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="91"/>
-      <c r="AA13" s="92"/>
+      <c r="Z13" s="74"/>
+      <c r="AA13" s="75"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="91"/>
-      <c r="AE13" s="92"/>
+      <c r="AD13" s="74"/>
+      <c r="AE13" s="75"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="86"/>
-      <c r="AJ13" s="87"/>
+      <c r="AH13" s="71"/>
+      <c r="AI13" s="72"/>
+      <c r="AJ13" s="73"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="85"/>
-      <c r="AM13" s="86"/>
-      <c r="AN13" s="87"/>
+      <c r="AL13" s="71"/>
+      <c r="AM13" s="72"/>
+      <c r="AN13" s="73"/>
       <c r="AP13" s="61" t="s">
         <v>22</v>
       </c>
@@ -2781,46 +2781,46 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="69"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="71"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="79"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="71"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="79"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="71"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="71"/>
+      <c r="V14" s="77"/>
+      <c r="W14" s="78"/>
+      <c r="X14" s="79"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="71"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="78"/>
+      <c r="AB14" s="79"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="69"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="71"/>
+      <c r="AD14" s="77"/>
+      <c r="AE14" s="78"/>
+      <c r="AF14" s="79"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="70"/>
-      <c r="AJ14" s="71"/>
+      <c r="AH14" s="77"/>
+      <c r="AI14" s="78"/>
+      <c r="AJ14" s="79"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="69"/>
-      <c r="AM14" s="70"/>
-      <c r="AN14" s="71"/>
+      <c r="AL14" s="77"/>
+      <c r="AM14" s="78"/>
+      <c r="AN14" s="79"/>
       <c r="AP14" s="61" t="s">
         <v>23</v>
       </c>
@@ -2832,46 +2832,46 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="63"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="65"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="90"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="65"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="90"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="65"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="90"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="65"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="89"/>
-      <c r="X15" s="90"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="65"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="90"/>
+      <c r="Z15" s="63"/>
+      <c r="AA15" s="64"/>
+      <c r="AB15" s="65"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="90"/>
+      <c r="AD15" s="63"/>
+      <c r="AE15" s="64"/>
+      <c r="AF15" s="65"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="88"/>
-      <c r="AI15" s="89"/>
-      <c r="AJ15" s="90"/>
+      <c r="AH15" s="63"/>
+      <c r="AI15" s="64"/>
+      <c r="AJ15" s="65"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="88"/>
-      <c r="AM15" s="89"/>
-      <c r="AN15" s="90"/>
+      <c r="AL15" s="63"/>
+      <c r="AM15" s="64"/>
+      <c r="AN15" s="65"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2881,46 +2881,46 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="107"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="109"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="101"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="103"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="109"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="103"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="109"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="103"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="109"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="103"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
-      <c r="T16" s="109"/>
+      <c r="R16" s="101"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="103"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="107"/>
-      <c r="W16" s="108"/>
-      <c r="X16" s="109"/>
+      <c r="V16" s="101"/>
+      <c r="W16" s="102"/>
+      <c r="X16" s="103"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="107"/>
-      <c r="AA16" s="108"/>
-      <c r="AB16" s="109"/>
+      <c r="Z16" s="101"/>
+      <c r="AA16" s="102"/>
+      <c r="AB16" s="103"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="107"/>
-      <c r="AE16" s="108"/>
-      <c r="AF16" s="109"/>
+      <c r="AD16" s="101"/>
+      <c r="AE16" s="102"/>
+      <c r="AF16" s="103"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="107"/>
-      <c r="AI16" s="108"/>
-      <c r="AJ16" s="109"/>
+      <c r="AH16" s="101"/>
+      <c r="AI16" s="102"/>
+      <c r="AJ16" s="103"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="107"/>
-      <c r="AM16" s="108"/>
-      <c r="AN16" s="109"/>
+      <c r="AL16" s="101"/>
+      <c r="AM16" s="102"/>
+      <c r="AN16" s="103"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -2992,23 +2992,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="106" t="s">
+      <c r="N18" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="106"/>
-      <c r="R18" s="106"/>
-      <c r="S18" s="106"/>
-      <c r="T18" s="106"/>
-      <c r="U18" s="106"/>
-      <c r="V18" s="106"/>
-      <c r="W18" s="106"/>
-      <c r="X18" s="106"/>
-      <c r="Y18" s="106"/>
-      <c r="Z18" s="106"/>
-      <c r="AA18" s="106"/>
-      <c r="AB18" s="106"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+      <c r="R18" s="108"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+      <c r="U18" s="108"/>
+      <c r="V18" s="108"/>
+      <c r="W18" s="108"/>
+      <c r="X18" s="108"/>
+      <c r="Y18" s="108"/>
+      <c r="Z18" s="108"/>
+      <c r="AA18" s="108"/>
+      <c r="AB18" s="108"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3043,21 +3043,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="106"/>
-      <c r="T19" s="106"/>
-      <c r="U19" s="106"/>
-      <c r="V19" s="106"/>
-      <c r="W19" s="106"/>
-      <c r="X19" s="106"/>
-      <c r="Y19" s="106"/>
-      <c r="Z19" s="106"/>
-      <c r="AA19" s="106"/>
-      <c r="AB19" s="106"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+      <c r="U19" s="108"/>
+      <c r="V19" s="108"/>
+      <c r="W19" s="108"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="108"/>
+      <c r="Z19" s="108"/>
+      <c r="AA19" s="108"/>
+      <c r="AB19" s="108"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3079,45 +3079,45 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="89"/>
+      <c r="C20" s="90"/>
       <c r="D20" s="59"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="76"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="90"/>
       <c r="H20" s="59"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="76"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="90"/>
       <c r="L20" s="59"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="84"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="126"/>
+      <c r="R20" s="106"/>
+      <c r="S20" s="107"/>
       <c r="T20" s="56"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="125"/>
-      <c r="W20" s="126"/>
+      <c r="V20" s="106"/>
+      <c r="W20" s="107"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="125"/>
-      <c r="AA20" s="126"/>
+      <c r="Z20" s="106"/>
+      <c r="AA20" s="107"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="83"/>
-      <c r="AE20" s="84"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="70"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="83"/>
-      <c r="AI20" s="84"/>
+      <c r="AH20" s="69"/>
+      <c r="AI20" s="70"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="83"/>
-      <c r="AM20" s="84"/>
+      <c r="AL20" s="69"/>
+      <c r="AM20" s="70"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3128,45 +3128,45 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="93"/>
+      <c r="C21" s="94"/>
       <c r="D21" s="60"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="67"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="94"/>
       <c r="H21" s="60"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="67"/>
+      <c r="J21" s="93"/>
+      <c r="K21" s="94"/>
       <c r="L21" s="60"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="92"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="75"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="92"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="75"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="124"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="114"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="123"/>
-      <c r="AA21" s="124"/>
+      <c r="Z21" s="113"/>
+      <c r="AA21" s="114"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="91"/>
-      <c r="AE21" s="92"/>
+      <c r="AD21" s="74"/>
+      <c r="AE21" s="75"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="91"/>
-      <c r="AI21" s="92"/>
+      <c r="AH21" s="74"/>
+      <c r="AI21" s="75"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="91"/>
-      <c r="AM21" s="92"/>
+      <c r="AL21" s="74"/>
+      <c r="AM21" s="75"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3177,45 +3177,45 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="130"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="78"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="131"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="78"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="131"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="95"/>
+      <c r="N22" s="128"/>
+      <c r="O22" s="129"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="95"/>
+      <c r="R22" s="128"/>
+      <c r="S22" s="129"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="95"/>
+      <c r="V22" s="128"/>
+      <c r="W22" s="129"/>
       <c r="X22" s="58"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="95"/>
+      <c r="Z22" s="128"/>
+      <c r="AA22" s="129"/>
       <c r="AB22" s="58"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="78"/>
+      <c r="AD22" s="130"/>
+      <c r="AE22" s="131"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="77"/>
-      <c r="AI22" s="78"/>
+      <c r="AH22" s="130"/>
+      <c r="AI22" s="131"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="94"/>
-      <c r="AM22" s="95"/>
+      <c r="AL22" s="128"/>
+      <c r="AM22" s="129"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
@@ -3226,45 +3226,45 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="96"/>
-      <c r="C23" s="97"/>
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="109"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="97"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="110"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="97"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="110"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="97"/>
+      <c r="N23" s="109"/>
+      <c r="O23" s="110"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="96"/>
-      <c r="S23" s="97"/>
+      <c r="R23" s="109"/>
+      <c r="S23" s="110"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="96"/>
-      <c r="W23" s="97"/>
+      <c r="V23" s="109"/>
+      <c r="W23" s="110"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="96"/>
-      <c r="AA23" s="97"/>
+      <c r="Z23" s="109"/>
+      <c r="AA23" s="110"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="96"/>
-      <c r="AE23" s="97"/>
+      <c r="AD23" s="109"/>
+      <c r="AE23" s="110"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="96"/>
-      <c r="AI23" s="97"/>
+      <c r="AH23" s="109"/>
+      <c r="AI23" s="110"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="96"/>
-      <c r="AM23" s="97"/>
+      <c r="AL23" s="109"/>
+      <c r="AM23" s="110"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3275,45 +3275,45 @@
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="111"/>
+      <c r="C24" s="112"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="82"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="112"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="112"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="82"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="112"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="82"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="112"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="82"/>
+      <c r="V24" s="111"/>
+      <c r="W24" s="112"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="82"/>
+      <c r="Z24" s="111"/>
+      <c r="AA24" s="112"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="82"/>
+      <c r="AD24" s="111"/>
+      <c r="AE24" s="112"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="82"/>
+      <c r="AH24" s="111"/>
+      <c r="AI24" s="112"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="82"/>
+      <c r="AL24" s="111"/>
+      <c r="AM24" s="112"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3324,45 +3324,45 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="81"/>
-      <c r="C25" s="82"/>
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="111"/>
+      <c r="C25" s="112"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="82"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="82"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="112"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="82"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="112"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="82"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="112"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="82"/>
+      <c r="V25" s="111"/>
+      <c r="W25" s="112"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="82"/>
+      <c r="Z25" s="111"/>
+      <c r="AA25" s="112"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="82"/>
+      <c r="AD25" s="111"/>
+      <c r="AE25" s="112"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="82"/>
+      <c r="AH25" s="111"/>
+      <c r="AI25" s="112"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="82"/>
+      <c r="AL25" s="111"/>
+      <c r="AM25" s="112"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="46" t="s">
         <v>21</v>
@@ -3373,45 +3373,45 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="81"/>
-      <c r="C26" s="82"/>
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="111"/>
+      <c r="C26" s="112"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="82"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="112"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="82"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="112"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="82"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="112"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="82"/>
+      <c r="R26" s="111"/>
+      <c r="S26" s="112"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="82"/>
+      <c r="V26" s="111"/>
+      <c r="W26" s="112"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="82"/>
+      <c r="Z26" s="111"/>
+      <c r="AA26" s="112"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="82"/>
+      <c r="AD26" s="111"/>
+      <c r="AE26" s="112"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="82"/>
+      <c r="AH26" s="111"/>
+      <c r="AI26" s="112"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="82"/>
+      <c r="AL26" s="111"/>
+      <c r="AM26" s="112"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
@@ -3422,45 +3422,45 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="79"/>
-      <c r="C27" s="80"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="104"/>
+      <c r="C27" s="105"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="80"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="105"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="80"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="105"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="80"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="105"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="79"/>
-      <c r="S27" s="80"/>
+      <c r="R27" s="104"/>
+      <c r="S27" s="105"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="79"/>
-      <c r="W27" s="80"/>
+      <c r="V27" s="104"/>
+      <c r="W27" s="105"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="79"/>
-      <c r="AA27" s="80"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="105"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="79"/>
-      <c r="AE27" s="80"/>
+      <c r="AD27" s="104"/>
+      <c r="AE27" s="105"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="79"/>
-      <c r="AI27" s="80"/>
+      <c r="AH27" s="104"/>
+      <c r="AI27" s="105"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="79"/>
-      <c r="AM27" s="80"/>
+      <c r="AL27" s="104"/>
+      <c r="AM27" s="105"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -3533,23 +3533,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="106" t="s">
+      <c r="N29" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="106"/>
-      <c r="P29" s="106"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="106"/>
-      <c r="S29" s="106"/>
-      <c r="T29" s="106"/>
-      <c r="U29" s="106"/>
-      <c r="V29" s="106"/>
-      <c r="W29" s="106"/>
-      <c r="X29" s="106"/>
-      <c r="Y29" s="106"/>
-      <c r="Z29" s="106"/>
-      <c r="AA29" s="106"/>
-      <c r="AB29" s="106"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="108"/>
+      <c r="U29" s="108"/>
+      <c r="V29" s="108"/>
+      <c r="W29" s="108"/>
+      <c r="X29" s="108"/>
+      <c r="Y29" s="108"/>
+      <c r="Z29" s="108"/>
+      <c r="AA29" s="108"/>
+      <c r="AB29" s="108"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -3584,21 +3584,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="106"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="106"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="106"/>
-      <c r="S30" s="106"/>
-      <c r="T30" s="106"/>
-      <c r="U30" s="106"/>
-      <c r="V30" s="106"/>
-      <c r="W30" s="106"/>
-      <c r="X30" s="106"/>
-      <c r="Y30" s="106"/>
-      <c r="Z30" s="106"/>
-      <c r="AA30" s="106"/>
-      <c r="AB30" s="106"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="108"/>
+      <c r="Q30" s="108"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="108"/>
+      <c r="T30" s="108"/>
+      <c r="U30" s="108"/>
+      <c r="V30" s="108"/>
+      <c r="W30" s="108"/>
+      <c r="X30" s="108"/>
+      <c r="Y30" s="108"/>
+      <c r="Z30" s="108"/>
+      <c r="AA30" s="108"/>
+      <c r="AB30" s="108"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3620,326 +3620,318 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="75" t="s">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="76"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="59"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="75" t="s">
+      <c r="F31" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="76"/>
+      <c r="G31" s="90"/>
       <c r="H31" s="59"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="75" t="s">
+      <c r="J31" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="76"/>
+      <c r="K31" s="90"/>
       <c r="L31" s="59"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="83" t="s">
+      <c r="N31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="84"/>
+      <c r="O31" s="70"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="83" t="s">
+      <c r="R31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="84"/>
+      <c r="S31" s="70"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="83" t="s">
+      <c r="V31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="84"/>
+      <c r="W31" s="70"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="83" t="s">
+      <c r="Z31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="84"/>
+      <c r="AA31" s="70"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="101" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE31" s="102"/>
-      <c r="AF31" s="62"/>
+      <c r="AD31" s="69"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="83" t="s">
+      <c r="AH31" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="AI31" s="84"/>
-      <c r="AJ31" s="34"/>
+      <c r="AI31" s="97"/>
+      <c r="AJ31" s="62"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="83" t="s">
+      <c r="AL31" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="AM31" s="84"/>
+      <c r="AM31" s="70"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="63" t="s">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="65"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="82"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="63" t="s">
+      <c r="F32" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="65"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="82"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="63" t="s">
+      <c r="J32" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="64"/>
-      <c r="L32" s="65"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="82"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="85" t="s">
+      <c r="N32" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="O32" s="86"/>
-      <c r="P32" s="87"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="73"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="85" t="s">
+      <c r="R32" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S32" s="86"/>
-      <c r="T32" s="87"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="73"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="85" t="s">
+      <c r="V32" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="86"/>
-      <c r="X32" s="87"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="73"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="85" t="s">
+      <c r="Z32" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AA32" s="86"/>
-      <c r="AB32" s="87"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="73"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE32" s="99"/>
-      <c r="AF32" s="100"/>
+      <c r="AD32" s="71"/>
+      <c r="AE32" s="72"/>
+      <c r="AF32" s="73"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="85" t="s">
+      <c r="AH32" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="AI32" s="86"/>
-      <c r="AJ32" s="87"/>
+      <c r="AI32" s="84"/>
+      <c r="AJ32" s="85"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="85" t="s">
+      <c r="AL32" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="AM32" s="86"/>
-      <c r="AN32" s="87"/>
+      <c r="AM32" s="72"/>
+      <c r="AN32" s="73"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="67"/>
-      <c r="D33" s="68"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="95"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="66" t="s">
+      <c r="F33" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="67"/>
-      <c r="H33" s="68"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="95"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="66" t="s">
+      <c r="J33" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="67"/>
-      <c r="L33" s="68"/>
+      <c r="K33" s="94"/>
+      <c r="L33" s="95"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="91" t="s">
+      <c r="N33" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="92"/>
-      <c r="P33" s="93"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="76"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="91" t="s">
+      <c r="R33" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="92"/>
-      <c r="T33" s="93"/>
+      <c r="S33" s="75"/>
+      <c r="T33" s="76"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="91" t="s">
+      <c r="V33" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="W33" s="92"/>
-      <c r="X33" s="93"/>
+      <c r="W33" s="75"/>
+      <c r="X33" s="76"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="91" t="s">
+      <c r="Z33" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="AA33" s="92"/>
-      <c r="AB33" s="93"/>
+      <c r="AA33" s="75"/>
+      <c r="AB33" s="76"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="103"/>
-      <c r="AE33" s="104"/>
-      <c r="AF33" s="105"/>
+      <c r="AD33" s="74"/>
+      <c r="AE33" s="75"/>
+      <c r="AF33" s="76"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="91" t="s">
+      <c r="AH33" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="AI33" s="92"/>
-      <c r="AJ33" s="93"/>
+      <c r="AI33" s="87"/>
+      <c r="AJ33" s="88"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="91" t="s">
+      <c r="AL33" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="AM33" s="92"/>
-      <c r="AN33" s="93"/>
+      <c r="AM33" s="75"/>
+      <c r="AN33" s="76"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="71"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="79"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="70"/>
-      <c r="H34" s="71"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="79"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="69" t="s">
+      <c r="J34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="K34" s="70"/>
-      <c r="L34" s="71"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="79"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="69" t="s">
+      <c r="N34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="O34" s="70"/>
-      <c r="P34" s="71"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="79"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="69" t="s">
+      <c r="R34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="S34" s="70"/>
-      <c r="T34" s="71"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="79"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="69" t="s">
+      <c r="V34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="70"/>
-      <c r="X34" s="71"/>
+      <c r="W34" s="78"/>
+      <c r="X34" s="79"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="69" t="s">
+      <c r="Z34" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="71"/>
+      <c r="AA34" s="78"/>
+      <c r="AB34" s="79"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="71"/>
+      <c r="AD34" s="77"/>
+      <c r="AE34" s="78"/>
+      <c r="AF34" s="79"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="69" t="s">
+      <c r="AH34" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="AI34" s="70"/>
-      <c r="AJ34" s="71"/>
+      <c r="AI34" s="78"/>
+      <c r="AJ34" s="79"/>
       <c r="AK34" s="35"/>
-      <c r="AL34" s="69" t="s">
+      <c r="AL34" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="AM34" s="70"/>
-      <c r="AN34" s="71"/>
+      <c r="AM34" s="78"/>
+      <c r="AN34" s="79"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="74"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="73"/>
-      <c r="H35" s="74"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="68"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="72" t="s">
+      <c r="J35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="K35" s="73"/>
-      <c r="L35" s="74"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="68"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="72" t="s">
+      <c r="N35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="O35" s="73"/>
-      <c r="P35" s="74"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="68"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="72" t="s">
+      <c r="R35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="S35" s="73"/>
-      <c r="T35" s="74"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="68"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="72" t="s">
+      <c r="V35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="73"/>
-      <c r="X35" s="74"/>
+      <c r="W35" s="67"/>
+      <c r="X35" s="68"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="72" t="s">
+      <c r="Z35" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="74"/>
+      <c r="AA35" s="67"/>
+      <c r="AB35" s="68"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE35" s="89"/>
-      <c r="AF35" s="90"/>
+      <c r="AD35" s="63"/>
+      <c r="AE35" s="64"/>
+      <c r="AF35" s="65"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="88" t="s">
+      <c r="AH35" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="AI35" s="89"/>
-      <c r="AJ35" s="90"/>
+      <c r="AI35" s="64"/>
+      <c r="AJ35" s="65"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="88" t="s">
+      <c r="AL35" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="AM35" s="89"/>
-      <c r="AN35" s="90"/>
+      <c r="AM35" s="64"/>
+      <c r="AN35" s="65"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="35"/>
       <c r="C36" s="35"/>
@@ -3969,68 +3961,68 @@
       <c r="AA36" s="35"/>
       <c r="AB36" s="35"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="72"/>
-      <c r="AE36" s="73"/>
-      <c r="AF36" s="74"/>
+      <c r="AD36" s="66"/>
+      <c r="AE36" s="67"/>
+      <c r="AF36" s="68"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="72" t="s">
+      <c r="AH36" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="AI36" s="73"/>
-      <c r="AJ36" s="74"/>
+      <c r="AI36" s="67"/>
+      <c r="AJ36" s="68"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="72" t="s">
+      <c r="AL36" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="AM36" s="73"/>
-      <c r="AN36" s="74"/>
+      <c r="AM36" s="67"/>
+      <c r="AN36" s="68"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="76"/>
+      <c r="C37" s="90"/>
       <c r="D37" s="59"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="75" t="s">
+      <c r="F37" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="G37" s="76"/>
+      <c r="G37" s="90"/>
       <c r="H37" s="59"/>
       <c r="I37" s="50"/>
-      <c r="J37" s="75" t="s">
+      <c r="J37" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="K37" s="76"/>
+      <c r="K37" s="90"/>
       <c r="L37" s="59"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="83" t="s">
+      <c r="N37" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O37" s="84"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="34"/>
       <c r="Q37" s="36"/>
-      <c r="R37" s="83" t="s">
+      <c r="R37" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S37" s="84"/>
+      <c r="S37" s="70"/>
       <c r="T37" s="34"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="83" t="s">
+      <c r="V37" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="W37" s="84"/>
+      <c r="W37" s="70"/>
       <c r="X37" s="34"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="83" t="s">
+      <c r="Z37" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA37" s="84"/>
+      <c r="AA37" s="70"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="36"/>
       <c r="AD37" s="35"/>
@@ -4049,261 +4041,261 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="82"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="63" t="s">
+      <c r="F38" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="G38" s="64"/>
-      <c r="H38" s="65"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="82"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="63" t="s">
+      <c r="J38" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="64"/>
-      <c r="L38" s="65"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="82"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="85" t="s">
+      <c r="N38" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="O38" s="86"/>
-      <c r="P38" s="87"/>
+      <c r="O38" s="72"/>
+      <c r="P38" s="73"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="85" t="s">
+      <c r="R38" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S38" s="86"/>
-      <c r="T38" s="87"/>
+      <c r="S38" s="72"/>
+      <c r="T38" s="73"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="85" t="s">
+      <c r="V38" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="W38" s="86"/>
-      <c r="X38" s="87"/>
+      <c r="W38" s="72"/>
+      <c r="X38" s="73"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="85" t="s">
+      <c r="Z38" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AA38" s="86"/>
-      <c r="AB38" s="87"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="83"/>
-      <c r="AE38" s="84"/>
+      <c r="AD38" s="69"/>
+      <c r="AE38" s="70"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="101" t="s">
+      <c r="AH38" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="AI38" s="102"/>
+      <c r="AI38" s="97"/>
       <c r="AJ38" s="62"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="83" t="s">
+      <c r="AL38" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="AM38" s="84"/>
+      <c r="AM38" s="70"/>
       <c r="AN38" s="34"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="67"/>
-      <c r="D39" s="68"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="95"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="66" t="s">
+      <c r="F39" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="67"/>
-      <c r="H39" s="68"/>
+      <c r="G39" s="94"/>
+      <c r="H39" s="95"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="66" t="s">
+      <c r="J39" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="K39" s="67"/>
-      <c r="L39" s="68"/>
+      <c r="K39" s="94"/>
+      <c r="L39" s="95"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="91" t="s">
+      <c r="N39" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="O39" s="92"/>
-      <c r="P39" s="93"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="76"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="91" t="s">
+      <c r="R39" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="S39" s="92"/>
-      <c r="T39" s="93"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="76"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="91" t="s">
+      <c r="V39" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="W39" s="92"/>
-      <c r="X39" s="93"/>
+      <c r="W39" s="75"/>
+      <c r="X39" s="76"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="91" t="s">
+      <c r="Z39" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="AA39" s="92"/>
-      <c r="AB39" s="93"/>
+      <c r="AA39" s="75"/>
+      <c r="AB39" s="76"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="85"/>
-      <c r="AE39" s="86"/>
-      <c r="AF39" s="87"/>
+      <c r="AD39" s="71"/>
+      <c r="AE39" s="72"/>
+      <c r="AF39" s="73"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="98" t="s">
+      <c r="AH39" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="AI39" s="99"/>
-      <c r="AJ39" s="100"/>
+      <c r="AI39" s="84"/>
+      <c r="AJ39" s="85"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="85" t="s">
+      <c r="AL39" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="AM39" s="86"/>
-      <c r="AN39" s="87"/>
+      <c r="AM39" s="72"/>
+      <c r="AN39" s="73"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="71"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="79"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="69" t="s">
+      <c r="F40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="70"/>
-      <c r="H40" s="71"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="79"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="69" t="s">
+      <c r="J40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="70"/>
-      <c r="L40" s="71"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="79"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="69" t="s">
+      <c r="N40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="O40" s="70"/>
-      <c r="P40" s="71"/>
+      <c r="O40" s="78"/>
+      <c r="P40" s="79"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="69" t="s">
+      <c r="R40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="S40" s="70"/>
-      <c r="T40" s="71"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="79"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="69" t="s">
+      <c r="V40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="70"/>
-      <c r="X40" s="71"/>
+      <c r="W40" s="78"/>
+      <c r="X40" s="79"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="69" t="s">
+      <c r="Z40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="70"/>
-      <c r="AB40" s="71"/>
+      <c r="AA40" s="78"/>
+      <c r="AB40" s="79"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="91"/>
-      <c r="AE40" s="92"/>
-      <c r="AF40" s="93"/>
+      <c r="AD40" s="74"/>
+      <c r="AE40" s="75"/>
+      <c r="AF40" s="76"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="103" t="s">
+      <c r="AH40" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="AI40" s="104"/>
-      <c r="AJ40" s="105"/>
+      <c r="AI40" s="87"/>
+      <c r="AJ40" s="88"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="91"/>
-      <c r="AM40" s="92"/>
-      <c r="AN40" s="93"/>
+      <c r="AL40" s="74"/>
+      <c r="AM40" s="75"/>
+      <c r="AN40" s="76"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="72" t="s">
+      <c r="B41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="73"/>
-      <c r="D41" s="74"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="G41" s="73"/>
-      <c r="H41" s="74"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="68"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="72" t="s">
+      <c r="J41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="K41" s="73"/>
-      <c r="L41" s="74"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="68"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="72" t="s">
+      <c r="N41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="O41" s="73"/>
-      <c r="P41" s="74"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="68"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="72" t="s">
+      <c r="R41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="73"/>
-      <c r="T41" s="74"/>
+      <c r="S41" s="67"/>
+      <c r="T41" s="68"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="72" t="s">
+      <c r="V41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="73"/>
-      <c r="X41" s="74"/>
+      <c r="W41" s="67"/>
+      <c r="X41" s="68"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="72" t="s">
+      <c r="Z41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="73"/>
-      <c r="AB41" s="74"/>
+      <c r="AA41" s="67"/>
+      <c r="AB41" s="68"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="69"/>
-      <c r="AE41" s="70"/>
-      <c r="AF41" s="71"/>
+      <c r="AD41" s="77"/>
+      <c r="AE41" s="78"/>
+      <c r="AF41" s="79"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="69" t="s">
+      <c r="AH41" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="AI41" s="70"/>
-      <c r="AJ41" s="71"/>
+      <c r="AI41" s="78"/>
+      <c r="AJ41" s="79"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="69" t="s">
+      <c r="AL41" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="AM41" s="70"/>
-      <c r="AN41" s="71"/>
+      <c r="AM41" s="78"/>
+      <c r="AN41" s="79"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -4333,133 +4325,133 @@
       <c r="AA42" s="35"/>
       <c r="AB42" s="35"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="88"/>
-      <c r="AE42" s="89"/>
-      <c r="AF42" s="90"/>
+      <c r="AD42" s="63"/>
+      <c r="AE42" s="64"/>
+      <c r="AF42" s="65"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="88" t="s">
+      <c r="AH42" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="AI42" s="89"/>
-      <c r="AJ42" s="90"/>
+      <c r="AI42" s="64"/>
+      <c r="AJ42" s="65"/>
       <c r="AK42" s="35"/>
-      <c r="AL42" s="88" t="s">
+      <c r="AL42" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="AM42" s="89"/>
-      <c r="AN42" s="90"/>
+      <c r="AM42" s="64"/>
+      <c r="AN42" s="65"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="75" t="s">
+      <c r="B43" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="76"/>
+      <c r="C43" s="90"/>
       <c r="D43" s="59"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="75" t="s">
+      <c r="F43" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="G43" s="76"/>
+      <c r="G43" s="90"/>
       <c r="H43" s="59"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="75" t="s">
+      <c r="J43" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="K43" s="76"/>
+      <c r="K43" s="90"/>
       <c r="L43" s="59"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="83" t="s">
+      <c r="N43" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O43" s="84"/>
+      <c r="O43" s="70"/>
       <c r="P43" s="34"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="83" t="s">
+      <c r="R43" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S43" s="84"/>
+      <c r="S43" s="70"/>
       <c r="T43" s="34"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="83" t="s">
+      <c r="V43" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="W43" s="84"/>
+      <c r="W43" s="70"/>
       <c r="X43" s="34"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="83" t="s">
+      <c r="Z43" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA43" s="84"/>
+      <c r="AA43" s="70"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="72"/>
-      <c r="AE43" s="73"/>
-      <c r="AF43" s="74"/>
+      <c r="AD43" s="66"/>
+      <c r="AE43" s="67"/>
+      <c r="AF43" s="68"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="72" t="s">
+      <c r="AH43" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="AI43" s="73"/>
-      <c r="AJ43" s="74"/>
+      <c r="AI43" s="67"/>
+      <c r="AJ43" s="68"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="72" t="s">
+      <c r="AL43" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="AM43" s="73"/>
-      <c r="AN43" s="74"/>
+      <c r="AM43" s="67"/>
+      <c r="AN43" s="68"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="82"/>
       <c r="E44" s="50"/>
-      <c r="F44" s="63" t="s">
+      <c r="F44" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="G44" s="64"/>
-      <c r="H44" s="65"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="82"/>
       <c r="I44" s="50"/>
-      <c r="J44" s="63" t="s">
+      <c r="J44" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="K44" s="64"/>
-      <c r="L44" s="65"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="82"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="85" t="s">
+      <c r="N44" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="O44" s="86"/>
-      <c r="P44" s="87"/>
+      <c r="O44" s="72"/>
+      <c r="P44" s="73"/>
       <c r="Q44" s="35"/>
-      <c r="R44" s="85" t="s">
+      <c r="R44" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S44" s="86"/>
-      <c r="T44" s="87"/>
+      <c r="S44" s="72"/>
+      <c r="T44" s="73"/>
       <c r="U44" s="36"/>
-      <c r="V44" s="85" t="s">
+      <c r="V44" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="W44" s="86"/>
-      <c r="X44" s="87"/>
+      <c r="W44" s="72"/>
+      <c r="X44" s="73"/>
       <c r="Y44" s="36"/>
-      <c r="Z44" s="85" t="s">
+      <c r="Z44" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AA44" s="86"/>
-      <c r="AB44" s="87"/>
+      <c r="AA44" s="72"/>
+      <c r="AB44" s="73"/>
       <c r="AC44" s="36"/>
       <c r="AD44" s="35"/>
       <c r="AE44" s="35"/>
@@ -4477,62 +4469,64 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="67"/>
-      <c r="D45" s="68"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="95"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="67"/>
-      <c r="H45" s="68"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="95"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="66" t="s">
+      <c r="J45" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="K45" s="67"/>
-      <c r="L45" s="68"/>
+      <c r="K45" s="94"/>
+      <c r="L45" s="95"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="91" t="s">
+      <c r="N45" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="O45" s="92"/>
-      <c r="P45" s="93"/>
+      <c r="O45" s="75"/>
+      <c r="P45" s="76"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="91" t="s">
+      <c r="R45" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="S45" s="92"/>
-      <c r="T45" s="93"/>
+      <c r="S45" s="75"/>
+      <c r="T45" s="76"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="91" t="s">
+      <c r="V45" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="W45" s="92"/>
-      <c r="X45" s="93"/>
+      <c r="W45" s="75"/>
+      <c r="X45" s="76"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="91" t="s">
+      <c r="Z45" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="AA45" s="92"/>
-      <c r="AB45" s="93"/>
+      <c r="AA45" s="75"/>
+      <c r="AB45" s="76"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="83"/>
-      <c r="AE45" s="84"/>
+      <c r="AD45" s="69"/>
+      <c r="AE45" s="70"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="83"/>
-      <c r="AI45" s="84"/>
-      <c r="AJ45" s="34"/>
+      <c r="AH45" s="96" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI45" s="97"/>
+      <c r="AJ45" s="62"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="83" t="s">
+      <c r="AL45" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="AM45" s="84"/>
+      <c r="AM45" s="70"/>
       <c r="AN45" s="34" t="s">
         <v>43</v>
       </c>
@@ -4541,252 +4535,258 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="89"/>
-      <c r="D46" s="90"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="65"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="65"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="88" t="s">
+      <c r="J46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="90"/>
+      <c r="K46" s="64"/>
+      <c r="L46" s="65"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="88" t="s">
+      <c r="N46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="O46" s="89"/>
-      <c r="P46" s="90"/>
+      <c r="O46" s="64"/>
+      <c r="P46" s="65"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="88" t="s">
+      <c r="R46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="S46" s="89"/>
-      <c r="T46" s="90"/>
+      <c r="S46" s="64"/>
+      <c r="T46" s="65"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="88" t="s">
+      <c r="V46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="89"/>
-      <c r="X46" s="90"/>
+      <c r="W46" s="64"/>
+      <c r="X46" s="65"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="88" t="s">
+      <c r="Z46" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="89"/>
-      <c r="AB46" s="90"/>
+      <c r="AA46" s="64"/>
+      <c r="AB46" s="65"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="85"/>
-      <c r="AE46" s="86"/>
-      <c r="AF46" s="87"/>
+      <c r="AD46" s="71"/>
+      <c r="AE46" s="72"/>
+      <c r="AF46" s="73"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="85"/>
-      <c r="AI46" s="86"/>
-      <c r="AJ46" s="87"/>
+      <c r="AH46" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI46" s="84"/>
+      <c r="AJ46" s="85"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="85" t="s">
+      <c r="AL46" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="AM46" s="86"/>
-      <c r="AN46" s="87"/>
+      <c r="AM46" s="72"/>
+      <c r="AN46" s="73"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="89"/>
-      <c r="D47" s="90"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="88" t="s">
+      <c r="F47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="89"/>
-      <c r="H47" s="90"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="65"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="88" t="s">
+      <c r="J47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="89"/>
-      <c r="L47" s="90"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="65"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="88" t="s">
+      <c r="N47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="O47" s="89"/>
-      <c r="P47" s="90"/>
+      <c r="O47" s="64"/>
+      <c r="P47" s="65"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="88" t="s">
+      <c r="R47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="S47" s="89"/>
-      <c r="T47" s="90"/>
+      <c r="S47" s="64"/>
+      <c r="T47" s="65"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="88" t="s">
+      <c r="V47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="89"/>
-      <c r="X47" s="90"/>
+      <c r="W47" s="64"/>
+      <c r="X47" s="65"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="88" t="s">
+      <c r="Z47" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="89"/>
-      <c r="AB47" s="90"/>
+      <c r="AA47" s="64"/>
+      <c r="AB47" s="65"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="91"/>
-      <c r="AE47" s="92"/>
-      <c r="AF47" s="93"/>
+      <c r="AD47" s="74"/>
+      <c r="AE47" s="75"/>
+      <c r="AF47" s="76"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="91"/>
-      <c r="AI47" s="92"/>
-      <c r="AJ47" s="93"/>
+      <c r="AH47" s="86"/>
+      <c r="AI47" s="87"/>
+      <c r="AJ47" s="88"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="91"/>
-      <c r="AM47" s="92"/>
-      <c r="AN47" s="93"/>
+      <c r="AL47" s="74"/>
+      <c r="AM47" s="75"/>
+      <c r="AN47" s="76"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="89"/>
-      <c r="D48" s="90"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="89"/>
-      <c r="H48" s="90"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="65"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="88" t="s">
+      <c r="J48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K48" s="89"/>
-      <c r="L48" s="90"/>
+      <c r="K48" s="64"/>
+      <c r="L48" s="65"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="88" t="s">
+      <c r="N48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="89"/>
-      <c r="P48" s="90"/>
+      <c r="O48" s="64"/>
+      <c r="P48" s="65"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="88" t="s">
+      <c r="R48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S48" s="89"/>
-      <c r="T48" s="90"/>
+      <c r="S48" s="64"/>
+      <c r="T48" s="65"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="88" t="s">
+      <c r="V48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="89"/>
-      <c r="X48" s="90"/>
+      <c r="W48" s="64"/>
+      <c r="X48" s="65"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="88" t="s">
+      <c r="Z48" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="89"/>
-      <c r="AB48" s="90"/>
+      <c r="AA48" s="64"/>
+      <c r="AB48" s="65"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="88"/>
-      <c r="AE48" s="89"/>
-      <c r="AF48" s="90"/>
+      <c r="AD48" s="63"/>
+      <c r="AE48" s="64"/>
+      <c r="AF48" s="65"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="88"/>
-      <c r="AI48" s="89"/>
-      <c r="AJ48" s="90"/>
+      <c r="AH48" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI48" s="78"/>
+      <c r="AJ48" s="79"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="69" t="s">
+      <c r="AL48" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="AM48" s="70"/>
-      <c r="AN48" s="71"/>
+      <c r="AM48" s="78"/>
+      <c r="AN48" s="79"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="72" t="s">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="74"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="68"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="73"/>
-      <c r="H49" s="74"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="68"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="72" t="s">
+      <c r="J49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="73"/>
-      <c r="L49" s="74"/>
+      <c r="K49" s="67"/>
+      <c r="L49" s="68"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="72" t="s">
+      <c r="N49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="O49" s="73"/>
-      <c r="P49" s="74"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="68"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="72" t="s">
+      <c r="R49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="S49" s="73"/>
-      <c r="T49" s="74"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="68"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="72" t="s">
+      <c r="V49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="73"/>
-      <c r="X49" s="74"/>
+      <c r="W49" s="67"/>
+      <c r="X49" s="68"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="72" t="s">
+      <c r="Z49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="73"/>
-      <c r="AB49" s="74"/>
+      <c r="AA49" s="67"/>
+      <c r="AB49" s="68"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="88"/>
-      <c r="AE49" s="89"/>
-      <c r="AF49" s="90"/>
+      <c r="AD49" s="63"/>
+      <c r="AE49" s="64"/>
+      <c r="AF49" s="65"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="88"/>
-      <c r="AI49" s="89"/>
-      <c r="AJ49" s="90"/>
+      <c r="AH49" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI49" s="64"/>
+      <c r="AJ49" s="65"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="88" t="s">
+      <c r="AL49" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="AM49" s="89"/>
-      <c r="AN49" s="90"/>
+      <c r="AM49" s="64"/>
+      <c r="AN49" s="65"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="35"/>
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
@@ -4815,63 +4815,63 @@
       <c r="AA50" s="35"/>
       <c r="AB50" s="35"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="72"/>
-      <c r="AE50" s="73"/>
-      <c r="AF50" s="74"/>
+      <c r="AD50" s="66"/>
+      <c r="AE50" s="67"/>
+      <c r="AF50" s="68"/>
       <c r="AG50" s="35"/>
-      <c r="AH50" s="72"/>
-      <c r="AI50" s="73"/>
-      <c r="AJ50" s="74"/>
+      <c r="AH50" s="66"/>
+      <c r="AI50" s="67"/>
+      <c r="AJ50" s="68"/>
       <c r="AK50" s="35"/>
-      <c r="AL50" s="72"/>
-      <c r="AM50" s="73"/>
-      <c r="AN50" s="74"/>
+      <c r="AL50" s="66"/>
+      <c r="AM50" s="67"/>
+      <c r="AN50" s="68"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="75" t="s">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="76"/>
+      <c r="C51" s="90"/>
       <c r="D51" s="59"/>
       <c r="E51" s="50"/>
-      <c r="F51" s="75" t="s">
+      <c r="F51" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="76"/>
+      <c r="G51" s="90"/>
       <c r="H51" s="59"/>
       <c r="I51" s="50"/>
-      <c r="J51" s="75" t="s">
+      <c r="J51" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="K51" s="76"/>
+      <c r="K51" s="90"/>
       <c r="L51" s="59"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="83" t="s">
+      <c r="N51" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O51" s="84"/>
+      <c r="O51" s="70"/>
       <c r="P51" s="34"/>
       <c r="Q51" s="40"/>
-      <c r="R51" s="83" t="s">
+      <c r="R51" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S51" s="84"/>
+      <c r="S51" s="70"/>
       <c r="T51" s="34"/>
       <c r="U51" s="40"/>
-      <c r="V51" s="83" t="s">
+      <c r="V51" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="W51" s="84"/>
+      <c r="W51" s="70"/>
       <c r="X51" s="34"/>
       <c r="Y51" s="32"/>
-      <c r="Z51" s="83" t="s">
+      <c r="Z51" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA51" s="84"/>
+      <c r="AA51" s="70"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="40"/>
       <c r="AD51" s="35"/>
@@ -4890,287 +4890,287 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="63" t="s">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="82"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="63" t="s">
+      <c r="F52" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="64"/>
-      <c r="H52" s="65"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="82"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="63" t="s">
+      <c r="J52" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="K52" s="64"/>
-      <c r="L52" s="65"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="82"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="85" t="s">
+      <c r="N52" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="86"/>
-      <c r="P52" s="87"/>
+      <c r="O52" s="72"/>
+      <c r="P52" s="73"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="85" t="s">
+      <c r="R52" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S52" s="86"/>
-      <c r="T52" s="87"/>
+      <c r="S52" s="72"/>
+      <c r="T52" s="73"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="85" t="s">
+      <c r="V52" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="W52" s="86"/>
-      <c r="X52" s="87"/>
+      <c r="W52" s="72"/>
+      <c r="X52" s="73"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="85" t="s">
+      <c r="Z52" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AA52" s="86"/>
-      <c r="AB52" s="87"/>
+      <c r="AA52" s="72"/>
+      <c r="AB52" s="73"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="83"/>
-      <c r="AE52" s="84"/>
+      <c r="AD52" s="69"/>
+      <c r="AE52" s="70"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="83"/>
-      <c r="AI52" s="84"/>
+      <c r="AH52" s="69"/>
+      <c r="AI52" s="70"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="83"/>
-      <c r="AM52" s="84"/>
+      <c r="AL52" s="69"/>
+      <c r="AM52" s="70"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="66" t="s">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="67"/>
-      <c r="D53" s="68"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="95"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="66" t="s">
+      <c r="F53" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="67"/>
-      <c r="H53" s="68"/>
+      <c r="G53" s="94"/>
+      <c r="H53" s="95"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="66" t="s">
+      <c r="J53" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="K53" s="67"/>
-      <c r="L53" s="68"/>
+      <c r="K53" s="94"/>
+      <c r="L53" s="95"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="91" t="s">
+      <c r="N53" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="O53" s="92"/>
-      <c r="P53" s="93"/>
+      <c r="O53" s="75"/>
+      <c r="P53" s="76"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="91" t="s">
+      <c r="R53" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="S53" s="92"/>
-      <c r="T53" s="93"/>
+      <c r="S53" s="75"/>
+      <c r="T53" s="76"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="91" t="s">
+      <c r="V53" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="W53" s="92"/>
-      <c r="X53" s="93"/>
+      <c r="W53" s="75"/>
+      <c r="X53" s="76"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="91" t="s">
+      <c r="Z53" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="AA53" s="92"/>
-      <c r="AB53" s="93"/>
+      <c r="AA53" s="75"/>
+      <c r="AB53" s="76"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="85"/>
-      <c r="AE53" s="86"/>
-      <c r="AF53" s="87"/>
+      <c r="AD53" s="71"/>
+      <c r="AE53" s="72"/>
+      <c r="AF53" s="73"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="85"/>
-      <c r="AI53" s="86"/>
-      <c r="AJ53" s="87"/>
+      <c r="AH53" s="71"/>
+      <c r="AI53" s="72"/>
+      <c r="AJ53" s="73"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="85"/>
-      <c r="AM53" s="86"/>
-      <c r="AN53" s="87"/>
+      <c r="AL53" s="71"/>
+      <c r="AM53" s="72"/>
+      <c r="AN53" s="73"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="69" t="s">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="70"/>
-      <c r="D54" s="71"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="79"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="69" t="s">
+      <c r="F54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G54" s="70"/>
-      <c r="H54" s="71"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="69" t="s">
+      <c r="J54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="70"/>
-      <c r="L54" s="71"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="79"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="69" t="s">
+      <c r="N54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="O54" s="70"/>
-      <c r="P54" s="71"/>
+      <c r="O54" s="78"/>
+      <c r="P54" s="79"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="69" t="s">
+      <c r="R54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="S54" s="70"/>
-      <c r="T54" s="71"/>
+      <c r="S54" s="78"/>
+      <c r="T54" s="79"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="69" t="s">
+      <c r="V54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="W54" s="70"/>
-      <c r="X54" s="71"/>
+      <c r="W54" s="78"/>
+      <c r="X54" s="79"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="69" t="s">
+      <c r="Z54" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="71"/>
+      <c r="AA54" s="78"/>
+      <c r="AB54" s="79"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="91"/>
-      <c r="AE54" s="92"/>
-      <c r="AF54" s="93"/>
+      <c r="AD54" s="74"/>
+      <c r="AE54" s="75"/>
+      <c r="AF54" s="76"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="91"/>
-      <c r="AI54" s="92"/>
-      <c r="AJ54" s="93"/>
+      <c r="AH54" s="74"/>
+      <c r="AI54" s="75"/>
+      <c r="AJ54" s="76"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="91"/>
-      <c r="AM54" s="92"/>
-      <c r="AN54" s="93"/>
+      <c r="AL54" s="74"/>
+      <c r="AM54" s="75"/>
+      <c r="AN54" s="76"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="88" t="s">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="89"/>
-      <c r="D55" s="90"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="65"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="88" t="s">
+      <c r="F55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="89"/>
-      <c r="H55" s="90"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="65"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="88" t="s">
+      <c r="J55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="90"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="65"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="88" t="s">
+      <c r="N55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="O55" s="89"/>
-      <c r="P55" s="90"/>
+      <c r="O55" s="64"/>
+      <c r="P55" s="65"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="88" t="s">
+      <c r="R55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="89"/>
-      <c r="T55" s="90"/>
+      <c r="S55" s="64"/>
+      <c r="T55" s="65"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="88" t="s">
+      <c r="V55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="89"/>
-      <c r="X55" s="90"/>
+      <c r="W55" s="64"/>
+      <c r="X55" s="65"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="88" t="s">
+      <c r="Z55" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="AA55" s="89"/>
-      <c r="AB55" s="90"/>
+      <c r="AA55" s="64"/>
+      <c r="AB55" s="65"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="69"/>
-      <c r="AE55" s="70"/>
-      <c r="AF55" s="71"/>
+      <c r="AD55" s="77"/>
+      <c r="AE55" s="78"/>
+      <c r="AF55" s="79"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="69"/>
-      <c r="AI55" s="70"/>
-      <c r="AJ55" s="71"/>
+      <c r="AH55" s="77"/>
+      <c r="AI55" s="78"/>
+      <c r="AJ55" s="79"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="69"/>
-      <c r="AM55" s="70"/>
-      <c r="AN55" s="71"/>
+      <c r="AL55" s="77"/>
+      <c r="AM55" s="78"/>
+      <c r="AN55" s="79"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="72" t="s">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="73"/>
-      <c r="D56" s="74"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="68"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="73"/>
-      <c r="H56" s="74"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="68"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="72" t="s">
+      <c r="J56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="K56" s="73"/>
-      <c r="L56" s="74"/>
+      <c r="K56" s="67"/>
+      <c r="L56" s="68"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="72" t="s">
+      <c r="N56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="O56" s="73"/>
-      <c r="P56" s="74"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="68"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="72" t="s">
+      <c r="R56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="S56" s="73"/>
-      <c r="T56" s="74"/>
+      <c r="S56" s="67"/>
+      <c r="T56" s="68"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="72" t="s">
+      <c r="V56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="W56" s="73"/>
-      <c r="X56" s="74"/>
+      <c r="W56" s="67"/>
+      <c r="X56" s="68"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="72" t="s">
+      <c r="Z56" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="AA56" s="73"/>
-      <c r="AB56" s="74"/>
+      <c r="AA56" s="67"/>
+      <c r="AB56" s="68"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="88"/>
-      <c r="AE56" s="89"/>
-      <c r="AF56" s="90"/>
+      <c r="AD56" s="63"/>
+      <c r="AE56" s="64"/>
+      <c r="AF56" s="65"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="88"/>
-      <c r="AI56" s="89"/>
-      <c r="AJ56" s="90"/>
+      <c r="AH56" s="63"/>
+      <c r="AI56" s="64"/>
+      <c r="AJ56" s="65"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="88"/>
-      <c r="AM56" s="89"/>
-      <c r="AN56" s="90"/>
+      <c r="AL56" s="63"/>
+      <c r="AM56" s="64"/>
+      <c r="AN56" s="65"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
       <c r="D57" s="35"/>
@@ -5199,58 +5199,58 @@
       <c r="AA57" s="35"/>
       <c r="AB57" s="35"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="72"/>
-      <c r="AE57" s="73"/>
-      <c r="AF57" s="74"/>
+      <c r="AD57" s="66"/>
+      <c r="AE57" s="67"/>
+      <c r="AF57" s="68"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="72"/>
-      <c r="AI57" s="73"/>
-      <c r="AJ57" s="74"/>
+      <c r="AH57" s="66"/>
+      <c r="AI57" s="67"/>
+      <c r="AJ57" s="68"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="72"/>
-      <c r="AM57" s="73"/>
-      <c r="AN57" s="74"/>
+      <c r="AL57" s="66"/>
+      <c r="AM57" s="67"/>
+      <c r="AN57" s="68"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="127" t="s">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="128"/>
+      <c r="C58" s="92"/>
       <c r="D58" s="55"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="75"/>
-      <c r="G58" s="76"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="90"/>
       <c r="H58" s="59"/>
       <c r="I58" s="50"/>
-      <c r="J58" s="75" t="s">
+      <c r="J58" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="K58" s="76"/>
+      <c r="K58" s="90"/>
       <c r="L58" s="59"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="83" t="s">
+      <c r="N58" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="O58" s="84"/>
+      <c r="O58" s="70"/>
       <c r="P58" s="34"/>
       <c r="Q58" s="31"/>
-      <c r="R58" s="83" t="s">
+      <c r="R58" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S58" s="84"/>
+      <c r="S58" s="70"/>
       <c r="T58" s="34"/>
       <c r="U58" s="50"/>
-      <c r="V58" s="83" t="s">
+      <c r="V58" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="W58" s="84"/>
+      <c r="W58" s="70"/>
       <c r="X58" s="34"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="83" t="s">
+      <c r="Z58" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA58" s="84"/>
+      <c r="AA58" s="70"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
       <c r="AD58" s="35"/>
@@ -5266,307 +5266,307 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="63" t="s">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="65"/>
+      <c r="C59" s="81"/>
+      <c r="D59" s="82"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="63"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="65"/>
+      <c r="F59" s="80"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="82"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="63" t="s">
+      <c r="J59" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="K59" s="64"/>
-      <c r="L59" s="65"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="82"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="85" t="s">
+      <c r="N59" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="86"/>
-      <c r="P59" s="87"/>
+      <c r="O59" s="72"/>
+      <c r="P59" s="73"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="85" t="s">
+      <c r="R59" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S59" s="86"/>
-      <c r="T59" s="87"/>
+      <c r="S59" s="72"/>
+      <c r="T59" s="73"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="85" t="s">
+      <c r="V59" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="W59" s="86"/>
-      <c r="X59" s="87"/>
+      <c r="W59" s="72"/>
+      <c r="X59" s="73"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="85" t="s">
+      <c r="Z59" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="AA59" s="86"/>
-      <c r="AB59" s="87"/>
+      <c r="AA59" s="72"/>
+      <c r="AB59" s="73"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="83"/>
-      <c r="AE59" s="84"/>
+      <c r="AD59" s="69"/>
+      <c r="AE59" s="70"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="83"/>
-      <c r="AI59" s="84"/>
+      <c r="AH59" s="69"/>
+      <c r="AI59" s="70"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="83"/>
-      <c r="AM59" s="84"/>
+      <c r="AL59" s="69"/>
+      <c r="AM59" s="70"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="66" t="s">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="67"/>
-      <c r="D60" s="68"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="95"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="68"/>
+      <c r="F60" s="93"/>
+      <c r="G60" s="94"/>
+      <c r="H60" s="95"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="66" t="s">
+      <c r="J60" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="K60" s="67"/>
-      <c r="L60" s="68"/>
+      <c r="K60" s="94"/>
+      <c r="L60" s="95"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="91" t="s">
+      <c r="N60" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="O60" s="92"/>
-      <c r="P60" s="93"/>
+      <c r="O60" s="75"/>
+      <c r="P60" s="76"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="91" t="s">
+      <c r="R60" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="S60" s="92"/>
-      <c r="T60" s="93"/>
+      <c r="S60" s="75"/>
+      <c r="T60" s="76"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="91" t="s">
+      <c r="V60" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="W60" s="92"/>
-      <c r="X60" s="93"/>
+      <c r="W60" s="75"/>
+      <c r="X60" s="76"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="91" t="s">
+      <c r="Z60" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="AA60" s="92"/>
-      <c r="AB60" s="93"/>
+      <c r="AA60" s="75"/>
+      <c r="AB60" s="76"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="85"/>
-      <c r="AE60" s="86"/>
-      <c r="AF60" s="87"/>
+      <c r="AD60" s="71"/>
+      <c r="AE60" s="72"/>
+      <c r="AF60" s="73"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="85"/>
-      <c r="AI60" s="86"/>
-      <c r="AJ60" s="87"/>
+      <c r="AH60" s="71"/>
+      <c r="AI60" s="72"/>
+      <c r="AJ60" s="73"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="85"/>
-      <c r="AM60" s="86"/>
-      <c r="AN60" s="87"/>
+      <c r="AL60" s="71"/>
+      <c r="AM60" s="72"/>
+      <c r="AN60" s="73"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="69" t="s">
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="70"/>
-      <c r="D61" s="71"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="79"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="71"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="78"/>
+      <c r="H61" s="79"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="69" t="s">
+      <c r="J61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="K61" s="70"/>
-      <c r="L61" s="71"/>
+      <c r="K61" s="78"/>
+      <c r="L61" s="79"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="69" t="s">
+      <c r="N61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="O61" s="70"/>
-      <c r="P61" s="71"/>
+      <c r="O61" s="78"/>
+      <c r="P61" s="79"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="69" t="s">
+      <c r="R61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="S61" s="70"/>
-      <c r="T61" s="71"/>
+      <c r="S61" s="78"/>
+      <c r="T61" s="79"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="69" t="s">
+      <c r="V61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="W61" s="70"/>
-      <c r="X61" s="71"/>
+      <c r="W61" s="78"/>
+      <c r="X61" s="79"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="69" t="s">
+      <c r="Z61" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="71"/>
+      <c r="AA61" s="78"/>
+      <c r="AB61" s="79"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="91"/>
-      <c r="AE61" s="92"/>
-      <c r="AF61" s="93"/>
+      <c r="AD61" s="74"/>
+      <c r="AE61" s="75"/>
+      <c r="AF61" s="76"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="91"/>
-      <c r="AI61" s="92"/>
-      <c r="AJ61" s="93"/>
+      <c r="AH61" s="74"/>
+      <c r="AI61" s="75"/>
+      <c r="AJ61" s="76"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="91"/>
-      <c r="AM61" s="92"/>
-      <c r="AN61" s="93"/>
+      <c r="AL61" s="74"/>
+      <c r="AM61" s="75"/>
+      <c r="AN61" s="76"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="88" t="s">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="89"/>
-      <c r="D62" s="90"/>
+      <c r="C62" s="64"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="90"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="65"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="88" t="s">
+      <c r="J62" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="K62" s="89"/>
-      <c r="L62" s="90"/>
+      <c r="K62" s="64"/>
+      <c r="L62" s="65"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="88" t="s">
+      <c r="N62" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="O62" s="89"/>
-      <c r="P62" s="90"/>
+      <c r="O62" s="64"/>
+      <c r="P62" s="65"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="88" t="s">
+      <c r="R62" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="S62" s="89"/>
-      <c r="T62" s="90"/>
+      <c r="S62" s="64"/>
+      <c r="T62" s="65"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="88" t="s">
+      <c r="V62" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="W62" s="89"/>
-      <c r="X62" s="90"/>
+      <c r="W62" s="64"/>
+      <c r="X62" s="65"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="88" t="s">
+      <c r="Z62" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AA62" s="89"/>
-      <c r="AB62" s="90"/>
+      <c r="AA62" s="64"/>
+      <c r="AB62" s="65"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="88"/>
-      <c r="AE62" s="89"/>
-      <c r="AF62" s="90"/>
+      <c r="AD62" s="63"/>
+      <c r="AE62" s="64"/>
+      <c r="AF62" s="65"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="88"/>
-      <c r="AI62" s="89"/>
-      <c r="AJ62" s="90"/>
+      <c r="AH62" s="63"/>
+      <c r="AI62" s="64"/>
+      <c r="AJ62" s="65"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="88"/>
-      <c r="AM62" s="89"/>
-      <c r="AN62" s="90"/>
+      <c r="AL62" s="63"/>
+      <c r="AM62" s="64"/>
+      <c r="AN62" s="65"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="88"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="90"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="63"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="65"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="90"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="65"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="88"/>
-      <c r="K63" s="89"/>
-      <c r="L63" s="90"/>
+      <c r="J63" s="63"/>
+      <c r="K63" s="64"/>
+      <c r="L63" s="65"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="88"/>
-      <c r="O63" s="89"/>
-      <c r="P63" s="90"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="64"/>
+      <c r="P63" s="65"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="88"/>
-      <c r="S63" s="89"/>
-      <c r="T63" s="90"/>
+      <c r="R63" s="63"/>
+      <c r="S63" s="64"/>
+      <c r="T63" s="65"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="88"/>
-      <c r="W63" s="89"/>
-      <c r="X63" s="90"/>
+      <c r="V63" s="63"/>
+      <c r="W63" s="64"/>
+      <c r="X63" s="65"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="88"/>
-      <c r="AA63" s="89"/>
-      <c r="AB63" s="90"/>
+      <c r="Z63" s="63"/>
+      <c r="AA63" s="64"/>
+      <c r="AB63" s="65"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="88"/>
-      <c r="AE63" s="89"/>
-      <c r="AF63" s="90"/>
+      <c r="AD63" s="63"/>
+      <c r="AE63" s="64"/>
+      <c r="AF63" s="65"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="88"/>
-      <c r="AI63" s="89"/>
-      <c r="AJ63" s="90"/>
+      <c r="AH63" s="63"/>
+      <c r="AI63" s="64"/>
+      <c r="AJ63" s="65"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="88"/>
-      <c r="AM63" s="89"/>
-      <c r="AN63" s="90"/>
+      <c r="AL63" s="63"/>
+      <c r="AM63" s="64"/>
+      <c r="AN63" s="65"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="72"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="74"/>
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="66"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="68"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="72"/>
-      <c r="G64" s="73"/>
-      <c r="H64" s="74"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="68"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="72"/>
-      <c r="K64" s="73"/>
-      <c r="L64" s="74"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="67"/>
+      <c r="L64" s="68"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="72"/>
-      <c r="O64" s="73"/>
-      <c r="P64" s="74"/>
+      <c r="N64" s="66"/>
+      <c r="O64" s="67"/>
+      <c r="P64" s="68"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="72"/>
-      <c r="S64" s="73"/>
-      <c r="T64" s="74"/>
+      <c r="R64" s="66"/>
+      <c r="S64" s="67"/>
+      <c r="T64" s="68"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="72"/>
-      <c r="W64" s="73"/>
-      <c r="X64" s="74"/>
+      <c r="V64" s="66"/>
+      <c r="W64" s="67"/>
+      <c r="X64" s="68"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="72"/>
-      <c r="AA64" s="73"/>
-      <c r="AB64" s="74"/>
+      <c r="Z64" s="66"/>
+      <c r="AA64" s="67"/>
+      <c r="AB64" s="68"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="72"/>
-      <c r="AE64" s="73"/>
-      <c r="AF64" s="74"/>
+      <c r="AD64" s="66"/>
+      <c r="AE64" s="67"/>
+      <c r="AF64" s="68"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="72"/>
-      <c r="AI64" s="73"/>
-      <c r="AJ64" s="74"/>
+      <c r="AH64" s="66"/>
+      <c r="AI64" s="67"/>
+      <c r="AJ64" s="68"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="72"/>
-      <c r="AM64" s="73"/>
-      <c r="AN64" s="74"/>
+      <c r="AL64" s="66"/>
+      <c r="AM64" s="67"/>
+      <c r="AN64" s="68"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -5612,7 +5612,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -5626,23 +5626,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="106" t="s">
+      <c r="N66" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="106"/>
-      <c r="P66" s="106"/>
-      <c r="Q66" s="106"/>
-      <c r="R66" s="106"/>
-      <c r="S66" s="106"/>
-      <c r="T66" s="106"/>
-      <c r="U66" s="106"/>
-      <c r="V66" s="106"/>
-      <c r="W66" s="106"/>
-      <c r="X66" s="106"/>
-      <c r="Y66" s="106"/>
-      <c r="Z66" s="106"/>
-      <c r="AA66" s="106"/>
-      <c r="AB66" s="106"/>
+      <c r="O66" s="108"/>
+      <c r="P66" s="108"/>
+      <c r="Q66" s="108"/>
+      <c r="R66" s="108"/>
+      <c r="S66" s="108"/>
+      <c r="T66" s="108"/>
+      <c r="U66" s="108"/>
+      <c r="V66" s="108"/>
+      <c r="W66" s="108"/>
+      <c r="X66" s="108"/>
+      <c r="Y66" s="108"/>
+      <c r="Z66" s="108"/>
+      <c r="AA66" s="108"/>
+      <c r="AB66" s="108"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5659,7 +5659,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -5673,21 +5673,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="106"/>
-      <c r="O67" s="106"/>
-      <c r="P67" s="106"/>
-      <c r="Q67" s="106"/>
-      <c r="R67" s="106"/>
-      <c r="S67" s="106"/>
-      <c r="T67" s="106"/>
-      <c r="U67" s="106"/>
-      <c r="V67" s="106"/>
-      <c r="W67" s="106"/>
-      <c r="X67" s="106"/>
-      <c r="Y67" s="106"/>
-      <c r="Z67" s="106"/>
-      <c r="AA67" s="106"/>
-      <c r="AB67" s="106"/>
+      <c r="N67" s="108"/>
+      <c r="O67" s="108"/>
+      <c r="P67" s="108"/>
+      <c r="Q67" s="108"/>
+      <c r="R67" s="108"/>
+      <c r="S67" s="108"/>
+      <c r="T67" s="108"/>
+      <c r="U67" s="108"/>
+      <c r="V67" s="108"/>
+      <c r="W67" s="108"/>
+      <c r="X67" s="108"/>
+      <c r="Y67" s="108"/>
+      <c r="Z67" s="108"/>
+      <c r="AA67" s="108"/>
+      <c r="AB67" s="108"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5705,54 +5705,54 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="127" t="s">
+      <c r="B68" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="128"/>
+      <c r="C68" s="92"/>
       <c r="D68" s="55"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="101" t="s">
+      <c r="F68" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="G68" s="102"/>
+      <c r="G68" s="97"/>
       <c r="H68" s="62"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="101" t="s">
+      <c r="J68" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="K68" s="102"/>
+      <c r="K68" s="97"/>
       <c r="L68" s="62"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="83"/>
-      <c r="O68" s="84"/>
+      <c r="N68" s="69"/>
+      <c r="O68" s="70"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="32"/>
-      <c r="R68" s="83" t="s">
+      <c r="R68" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="S68" s="84"/>
+      <c r="S68" s="70"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="83"/>
-      <c r="W68" s="84"/>
+      <c r="V68" s="69"/>
+      <c r="W68" s="70"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="83"/>
-      <c r="AA68" s="84"/>
+      <c r="Z68" s="69"/>
+      <c r="AA68" s="70"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="83"/>
-      <c r="AE68" s="84"/>
+      <c r="AD68" s="69"/>
+      <c r="AE68" s="70"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="83"/>
-      <c r="AI68" s="84"/>
+      <c r="AH68" s="69"/>
+      <c r="AI68" s="70"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="83"/>
-      <c r="AM68" s="84"/>
+      <c r="AL68" s="69"/>
+      <c r="AM68" s="70"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5761,55 +5761,55 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="63" t="s">
+      <c r="B69" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="64"/>
-      <c r="D69" s="65"/>
+      <c r="C69" s="81"/>
+      <c r="D69" s="82"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="98" t="s">
+      <c r="F69" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="G69" s="99"/>
-      <c r="H69" s="100"/>
+      <c r="G69" s="84"/>
+      <c r="H69" s="85"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="98" t="s">
+      <c r="J69" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="K69" s="99"/>
-      <c r="L69" s="100"/>
+      <c r="K69" s="84"/>
+      <c r="L69" s="85"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="85"/>
-      <c r="O69" s="86"/>
-      <c r="P69" s="87"/>
+      <c r="N69" s="71"/>
+      <c r="O69" s="72"/>
+      <c r="P69" s="73"/>
       <c r="Q69" s="35"/>
-      <c r="R69" s="85" t="s">
+      <c r="R69" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="S69" s="86"/>
-      <c r="T69" s="87"/>
+      <c r="S69" s="72"/>
+      <c r="T69" s="73"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="85"/>
-      <c r="W69" s="86"/>
-      <c r="X69" s="87"/>
+      <c r="V69" s="71"/>
+      <c r="W69" s="72"/>
+      <c r="X69" s="73"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="85"/>
-      <c r="AA69" s="86"/>
-      <c r="AB69" s="87"/>
+      <c r="Z69" s="71"/>
+      <c r="AA69" s="72"/>
+      <c r="AB69" s="73"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="85"/>
-      <c r="AE69" s="86"/>
-      <c r="AF69" s="87"/>
+      <c r="AD69" s="71"/>
+      <c r="AE69" s="72"/>
+      <c r="AF69" s="73"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="85"/>
-      <c r="AI69" s="86"/>
-      <c r="AJ69" s="87"/>
+      <c r="AH69" s="71"/>
+      <c r="AI69" s="72"/>
+      <c r="AJ69" s="73"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="85"/>
-      <c r="AM69" s="86"/>
-      <c r="AN69" s="87"/>
+      <c r="AL69" s="71"/>
+      <c r="AM69" s="72"/>
+      <c r="AN69" s="73"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5817,53 +5817,53 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="66" t="s">
+      <c r="B70" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="67"/>
-      <c r="D70" s="68"/>
+      <c r="C70" s="94"/>
+      <c r="D70" s="95"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="103"/>
-      <c r="G70" s="104"/>
-      <c r="H70" s="105"/>
+      <c r="F70" s="86"/>
+      <c r="G70" s="87"/>
+      <c r="H70" s="88"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="103" t="s">
+      <c r="J70" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="K70" s="104"/>
-      <c r="L70" s="105"/>
+      <c r="K70" s="87"/>
+      <c r="L70" s="88"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="91"/>
-      <c r="O70" s="92"/>
-      <c r="P70" s="93"/>
+      <c r="N70" s="74"/>
+      <c r="O70" s="75"/>
+      <c r="P70" s="76"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="91" t="s">
+      <c r="R70" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="S70" s="92"/>
-      <c r="T70" s="93"/>
+      <c r="S70" s="75"/>
+      <c r="T70" s="76"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="91"/>
-      <c r="W70" s="92"/>
-      <c r="X70" s="93"/>
+      <c r="V70" s="74"/>
+      <c r="W70" s="75"/>
+      <c r="X70" s="76"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="91"/>
-      <c r="AA70" s="92"/>
-      <c r="AB70" s="93"/>
+      <c r="Z70" s="74"/>
+      <c r="AA70" s="75"/>
+      <c r="AB70" s="76"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="91"/>
-      <c r="AE70" s="92"/>
-      <c r="AF70" s="93"/>
+      <c r="AD70" s="74"/>
+      <c r="AE70" s="75"/>
+      <c r="AF70" s="76"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="91"/>
-      <c r="AI70" s="92"/>
-      <c r="AJ70" s="93"/>
+      <c r="AH70" s="74"/>
+      <c r="AI70" s="75"/>
+      <c r="AJ70" s="76"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="91"/>
-      <c r="AM70" s="92"/>
-      <c r="AN70" s="93"/>
+      <c r="AL70" s="74"/>
+      <c r="AM70" s="75"/>
+      <c r="AN70" s="76"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5871,55 +5871,55 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="69" t="s">
+      <c r="B71" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="70"/>
-      <c r="D71" s="71"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="79"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="69" t="s">
+      <c r="F71" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="G71" s="70"/>
-      <c r="H71" s="71"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="79"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="129" t="s">
+      <c r="J71" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="K71" s="130"/>
-      <c r="L71" s="131"/>
+      <c r="K71" s="99"/>
+      <c r="L71" s="100"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="69"/>
-      <c r="O71" s="70"/>
-      <c r="P71" s="71"/>
+      <c r="N71" s="77"/>
+      <c r="O71" s="78"/>
+      <c r="P71" s="79"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="69" t="s">
+      <c r="R71" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="S71" s="70"/>
-      <c r="T71" s="71"/>
+      <c r="S71" s="78"/>
+      <c r="T71" s="79"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="69"/>
-      <c r="W71" s="70"/>
-      <c r="X71" s="71"/>
+      <c r="V71" s="77"/>
+      <c r="W71" s="78"/>
+      <c r="X71" s="79"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="69"/>
-      <c r="AA71" s="70"/>
-      <c r="AB71" s="71"/>
+      <c r="Z71" s="77"/>
+      <c r="AA71" s="78"/>
+      <c r="AB71" s="79"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="69"/>
-      <c r="AE71" s="70"/>
-      <c r="AF71" s="71"/>
+      <c r="AD71" s="77"/>
+      <c r="AE71" s="78"/>
+      <c r="AF71" s="79"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="69"/>
-      <c r="AI71" s="70"/>
-      <c r="AJ71" s="71"/>
+      <c r="AH71" s="77"/>
+      <c r="AI71" s="78"/>
+      <c r="AJ71" s="79"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="69"/>
-      <c r="AM71" s="70"/>
-      <c r="AN71" s="71"/>
+      <c r="AL71" s="77"/>
+      <c r="AM71" s="78"/>
+      <c r="AN71" s="79"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5927,59 +5927,59 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="72" t="s">
+      <c r="B72" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="73"/>
-      <c r="D72" s="74"/>
+      <c r="C72" s="67"/>
+      <c r="D72" s="68"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="72"/>
-      <c r="G72" s="73"/>
-      <c r="H72" s="74"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="67"/>
+      <c r="H72" s="68"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="72" t="s">
+      <c r="J72" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="K72" s="73"/>
-      <c r="L72" s="74"/>
+      <c r="K72" s="67"/>
+      <c r="L72" s="68"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="72"/>
-      <c r="O72" s="73"/>
-      <c r="P72" s="74"/>
+      <c r="N72" s="66"/>
+      <c r="O72" s="67"/>
+      <c r="P72" s="68"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="72" t="s">
+      <c r="R72" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="S72" s="73"/>
-      <c r="T72" s="74"/>
+      <c r="S72" s="67"/>
+      <c r="T72" s="68"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="72"/>
-      <c r="W72" s="73"/>
-      <c r="X72" s="74"/>
+      <c r="V72" s="66"/>
+      <c r="W72" s="67"/>
+      <c r="X72" s="68"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="72"/>
-      <c r="AA72" s="73"/>
-      <c r="AB72" s="74"/>
+      <c r="Z72" s="66"/>
+      <c r="AA72" s="67"/>
+      <c r="AB72" s="68"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="72"/>
-      <c r="AE72" s="73"/>
-      <c r="AF72" s="74"/>
+      <c r="AD72" s="66"/>
+      <c r="AE72" s="67"/>
+      <c r="AF72" s="68"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="72"/>
-      <c r="AI72" s="73"/>
-      <c r="AJ72" s="74"/>
+      <c r="AH72" s="66"/>
+      <c r="AI72" s="67"/>
+      <c r="AJ72" s="68"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="72"/>
-      <c r="AM72" s="73"/>
-      <c r="AN72" s="74"/>
+      <c r="AL72" s="66"/>
+      <c r="AM72" s="67"/>
+      <c r="AN72" s="68"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6025,273 +6025,273 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="75" t="s">
+      <c r="B74" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="C74" s="76"/>
+      <c r="C74" s="90"/>
       <c r="D74" s="59"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="75" t="s">
+      <c r="F74" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="G74" s="76"/>
+      <c r="G74" s="90"/>
       <c r="H74" s="59"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="127" t="s">
+      <c r="J74" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="K74" s="128"/>
+      <c r="K74" s="92"/>
       <c r="L74" s="55"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="83"/>
-      <c r="O74" s="84"/>
+      <c r="N74" s="69"/>
+      <c r="O74" s="70"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="44"/>
-      <c r="R74" s="83" t="s">
+      <c r="R74" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="S74" s="84"/>
+      <c r="S74" s="70"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="83"/>
-      <c r="W74" s="84"/>
+      <c r="V74" s="69"/>
+      <c r="W74" s="70"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="83" t="s">
+      <c r="Z74" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="AA74" s="84"/>
+      <c r="AA74" s="70"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="83"/>
-      <c r="AE74" s="84"/>
+      <c r="AD74" s="69"/>
+      <c r="AE74" s="70"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="83" t="s">
+      <c r="AH74" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="AI74" s="84"/>
+      <c r="AI74" s="70"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="83"/>
-      <c r="AM74" s="84"/>
+      <c r="AL74" s="69"/>
+      <c r="AM74" s="70"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="63"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="65"/>
+      <c r="B75" s="80"/>
+      <c r="C75" s="81"/>
+      <c r="D75" s="82"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="63"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="65"/>
+      <c r="F75" s="80"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="82"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="63"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="65"/>
+      <c r="J75" s="80"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="82"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="86"/>
-      <c r="P75" s="87"/>
+      <c r="N75" s="71"/>
+      <c r="O75" s="72"/>
+      <c r="P75" s="73"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="85"/>
-      <c r="S75" s="86"/>
-      <c r="T75" s="87"/>
+      <c r="R75" s="71"/>
+      <c r="S75" s="72"/>
+      <c r="T75" s="73"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="85"/>
-      <c r="W75" s="86"/>
-      <c r="X75" s="87"/>
+      <c r="V75" s="71"/>
+      <c r="W75" s="72"/>
+      <c r="X75" s="73"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="85"/>
-      <c r="AA75" s="86"/>
-      <c r="AB75" s="87"/>
+      <c r="Z75" s="71"/>
+      <c r="AA75" s="72"/>
+      <c r="AB75" s="73"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="85"/>
-      <c r="AE75" s="86"/>
-      <c r="AF75" s="87"/>
+      <c r="AD75" s="71"/>
+      <c r="AE75" s="72"/>
+      <c r="AF75" s="73"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="85"/>
-      <c r="AI75" s="86"/>
-      <c r="AJ75" s="87"/>
+      <c r="AH75" s="71"/>
+      <c r="AI75" s="72"/>
+      <c r="AJ75" s="73"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="85"/>
-      <c r="AM75" s="86"/>
-      <c r="AN75" s="87"/>
+      <c r="AL75" s="71"/>
+      <c r="AM75" s="72"/>
+      <c r="AN75" s="73"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="66" t="s">
+      <c r="B76" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="67"/>
-      <c r="D76" s="68"/>
+      <c r="C76" s="94"/>
+      <c r="D76" s="95"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="66" t="s">
+      <c r="F76" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="67"/>
-      <c r="H76" s="68"/>
+      <c r="G76" s="94"/>
+      <c r="H76" s="95"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="66" t="s">
+      <c r="J76" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="K76" s="67"/>
-      <c r="L76" s="68"/>
+      <c r="K76" s="94"/>
+      <c r="L76" s="95"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="91"/>
-      <c r="O76" s="92"/>
-      <c r="P76" s="93"/>
+      <c r="N76" s="74"/>
+      <c r="O76" s="75"/>
+      <c r="P76" s="76"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="91" t="s">
+      <c r="R76" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="92"/>
-      <c r="T76" s="93"/>
+      <c r="S76" s="75"/>
+      <c r="T76" s="76"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="91"/>
-      <c r="W76" s="92"/>
-      <c r="X76" s="93"/>
+      <c r="V76" s="74"/>
+      <c r="W76" s="75"/>
+      <c r="X76" s="76"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="91" t="s">
+      <c r="Z76" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="92"/>
-      <c r="AB76" s="93"/>
+      <c r="AA76" s="75"/>
+      <c r="AB76" s="76"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="91"/>
-      <c r="AE76" s="92"/>
-      <c r="AF76" s="93"/>
+      <c r="AD76" s="74"/>
+      <c r="AE76" s="75"/>
+      <c r="AF76" s="76"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="91" t="s">
+      <c r="AH76" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="AI76" s="92"/>
-      <c r="AJ76" s="93"/>
+      <c r="AI76" s="75"/>
+      <c r="AJ76" s="76"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="91"/>
-      <c r="AM76" s="92"/>
-      <c r="AN76" s="93"/>
+      <c r="AL76" s="74"/>
+      <c r="AM76" s="75"/>
+      <c r="AN76" s="76"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="69" t="s">
+      <c r="B77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="70"/>
-      <c r="D77" s="71"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="79"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="69" t="s">
+      <c r="F77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="70"/>
-      <c r="H77" s="71"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="79"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="69" t="s">
+      <c r="J77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="K77" s="70"/>
-      <c r="L77" s="71"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="79"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="69"/>
-      <c r="O77" s="70"/>
-      <c r="P77" s="71"/>
+      <c r="N77" s="77"/>
+      <c r="O77" s="78"/>
+      <c r="P77" s="79"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="69" t="s">
+      <c r="R77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="70"/>
-      <c r="T77" s="71"/>
+      <c r="S77" s="78"/>
+      <c r="T77" s="79"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="69"/>
-      <c r="W77" s="70"/>
-      <c r="X77" s="71"/>
+      <c r="V77" s="77"/>
+      <c r="W77" s="78"/>
+      <c r="X77" s="79"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="69" t="s">
+      <c r="Z77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="70"/>
-      <c r="AB77" s="71"/>
+      <c r="AA77" s="78"/>
+      <c r="AB77" s="79"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="69"/>
-      <c r="AE77" s="70"/>
-      <c r="AF77" s="71"/>
+      <c r="AD77" s="77"/>
+      <c r="AE77" s="78"/>
+      <c r="AF77" s="79"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="69" t="s">
+      <c r="AH77" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="70"/>
-      <c r="AJ77" s="71"/>
+      <c r="AI77" s="78"/>
+      <c r="AJ77" s="79"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="69"/>
-      <c r="AM77" s="70"/>
-      <c r="AN77" s="71"/>
+      <c r="AL77" s="77"/>
+      <c r="AM77" s="78"/>
+      <c r="AN77" s="79"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="73"/>
-      <c r="D78" s="74"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="68"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="72"/>
-      <c r="G78" s="73"/>
-      <c r="H78" s="74"/>
+      <c r="F78" s="66"/>
+      <c r="G78" s="67"/>
+      <c r="H78" s="68"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="72"/>
-      <c r="K78" s="73"/>
-      <c r="L78" s="74"/>
+      <c r="J78" s="66"/>
+      <c r="K78" s="67"/>
+      <c r="L78" s="68"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="72"/>
-      <c r="O78" s="73"/>
-      <c r="P78" s="74"/>
+      <c r="N78" s="66"/>
+      <c r="O78" s="67"/>
+      <c r="P78" s="68"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="72"/>
-      <c r="S78" s="73"/>
-      <c r="T78" s="74"/>
+      <c r="R78" s="66"/>
+      <c r="S78" s="67"/>
+      <c r="T78" s="68"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="72"/>
-      <c r="W78" s="73"/>
-      <c r="X78" s="74"/>
+      <c r="V78" s="66"/>
+      <c r="W78" s="67"/>
+      <c r="X78" s="68"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="72"/>
-      <c r="AA78" s="73"/>
-      <c r="AB78" s="74"/>
+      <c r="Z78" s="66"/>
+      <c r="AA78" s="67"/>
+      <c r="AB78" s="68"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="72"/>
-      <c r="AE78" s="73"/>
-      <c r="AF78" s="74"/>
+      <c r="AD78" s="66"/>
+      <c r="AE78" s="67"/>
+      <c r="AF78" s="68"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="72"/>
-      <c r="AI78" s="73"/>
-      <c r="AJ78" s="74"/>
+      <c r="AH78" s="66"/>
+      <c r="AI78" s="67"/>
+      <c r="AJ78" s="68"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="72"/>
-      <c r="AM78" s="73"/>
-      <c r="AN78" s="74"/>
+      <c r="AL78" s="66"/>
+      <c r="AM78" s="67"/>
+      <c r="AN78" s="68"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6337,267 +6337,267 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="75" t="s">
+      <c r="B80" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="C80" s="76"/>
+      <c r="C80" s="90"/>
       <c r="D80" s="59"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="76"/>
+      <c r="F80" s="89"/>
+      <c r="G80" s="90"/>
       <c r="H80" s="59"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="75"/>
-      <c r="K80" s="76"/>
+      <c r="J80" s="89"/>
+      <c r="K80" s="90"/>
       <c r="L80" s="59"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="83" t="s">
+      <c r="N80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="O80" s="84"/>
+      <c r="O80" s="70"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="83" t="s">
+      <c r="R80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="S80" s="84"/>
+      <c r="S80" s="70"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="83"/>
-      <c r="W80" s="84"/>
+      <c r="V80" s="69"/>
+      <c r="W80" s="70"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="83" t="s">
+      <c r="Z80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="AA80" s="84"/>
+      <c r="AA80" s="70"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="83" t="s">
+      <c r="AD80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="AE80" s="84"/>
+      <c r="AE80" s="70"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="83"/>
-      <c r="AI80" s="84"/>
+      <c r="AH80" s="69"/>
+      <c r="AI80" s="70"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="83"/>
-      <c r="AM80" s="84"/>
+      <c r="AL80" s="69"/>
+      <c r="AM80" s="70"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="63"/>
-      <c r="C81" s="64"/>
-      <c r="D81" s="65"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="81"/>
+      <c r="D81" s="82"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="63"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="65"/>
+      <c r="F81" s="80"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="82"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="63"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="65"/>
+      <c r="J81" s="80"/>
+      <c r="K81" s="81"/>
+      <c r="L81" s="82"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="85"/>
-      <c r="O81" s="86"/>
-      <c r="P81" s="87"/>
+      <c r="N81" s="71"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="73"/>
       <c r="Q81" s="44"/>
-      <c r="R81" s="85"/>
-      <c r="S81" s="86"/>
-      <c r="T81" s="87"/>
+      <c r="R81" s="71"/>
+      <c r="S81" s="72"/>
+      <c r="T81" s="73"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="85"/>
-      <c r="W81" s="86"/>
-      <c r="X81" s="87"/>
+      <c r="V81" s="71"/>
+      <c r="W81" s="72"/>
+      <c r="X81" s="73"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="85"/>
-      <c r="AA81" s="86"/>
-      <c r="AB81" s="87"/>
+      <c r="Z81" s="71"/>
+      <c r="AA81" s="72"/>
+      <c r="AB81" s="73"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="85"/>
-      <c r="AE81" s="86"/>
-      <c r="AF81" s="87"/>
+      <c r="AD81" s="71"/>
+      <c r="AE81" s="72"/>
+      <c r="AF81" s="73"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="85"/>
-      <c r="AI81" s="86"/>
-      <c r="AJ81" s="87"/>
+      <c r="AH81" s="71"/>
+      <c r="AI81" s="72"/>
+      <c r="AJ81" s="73"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="85"/>
-      <c r="AM81" s="86"/>
-      <c r="AN81" s="87"/>
+      <c r="AL81" s="71"/>
+      <c r="AM81" s="72"/>
+      <c r="AN81" s="73"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="C82" s="67"/>
-      <c r="D82" s="68"/>
+      <c r="C82" s="94"/>
+      <c r="D82" s="95"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="68"/>
+      <c r="F82" s="93"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="95"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="66"/>
-      <c r="K82" s="67"/>
-      <c r="L82" s="68"/>
+      <c r="J82" s="93"/>
+      <c r="K82" s="94"/>
+      <c r="L82" s="95"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="91" t="s">
+      <c r="N82" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="92"/>
-      <c r="P82" s="93"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="76"/>
       <c r="Q82" s="44"/>
-      <c r="R82" s="91" t="s">
+      <c r="R82" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="S82" s="92"/>
-      <c r="T82" s="93"/>
+      <c r="S82" s="75"/>
+      <c r="T82" s="76"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="91"/>
-      <c r="W82" s="92"/>
-      <c r="X82" s="93"/>
+      <c r="V82" s="74"/>
+      <c r="W82" s="75"/>
+      <c r="X82" s="76"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="91" t="s">
+      <c r="Z82" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="AA82" s="92"/>
-      <c r="AB82" s="93"/>
+      <c r="AA82" s="75"/>
+      <c r="AB82" s="76"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="91" t="s">
+      <c r="AD82" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="AE82" s="92"/>
-      <c r="AF82" s="93"/>
+      <c r="AE82" s="75"/>
+      <c r="AF82" s="76"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="91"/>
-      <c r="AI82" s="92"/>
-      <c r="AJ82" s="93"/>
+      <c r="AH82" s="74"/>
+      <c r="AI82" s="75"/>
+      <c r="AJ82" s="76"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="91"/>
-      <c r="AM82" s="92"/>
-      <c r="AN82" s="93"/>
+      <c r="AL82" s="74"/>
+      <c r="AM82" s="75"/>
+      <c r="AN82" s="76"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="69" t="s">
+      <c r="B83" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C83" s="70"/>
-      <c r="D83" s="71"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="69"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="71"/>
+      <c r="F83" s="77"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="79"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="69"/>
-      <c r="K83" s="70"/>
-      <c r="L83" s="71"/>
+      <c r="J83" s="77"/>
+      <c r="K83" s="78"/>
+      <c r="L83" s="79"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="69" t="s">
+      <c r="N83" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="O83" s="70"/>
-      <c r="P83" s="71"/>
+      <c r="O83" s="78"/>
+      <c r="P83" s="79"/>
       <c r="Q83" s="37"/>
-      <c r="R83" s="69" t="s">
+      <c r="R83" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="70"/>
-      <c r="T83" s="71"/>
+      <c r="S83" s="78"/>
+      <c r="T83" s="79"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="69"/>
-      <c r="W83" s="70"/>
-      <c r="X83" s="71"/>
+      <c r="V83" s="77"/>
+      <c r="W83" s="78"/>
+      <c r="X83" s="79"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="69" t="s">
+      <c r="Z83" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="AA83" s="70"/>
-      <c r="AB83" s="71"/>
+      <c r="AA83" s="78"/>
+      <c r="AB83" s="79"/>
       <c r="AC83" s="44"/>
-      <c r="AD83" s="69" t="s">
+      <c r="AD83" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AE83" s="70"/>
-      <c r="AF83" s="71"/>
+      <c r="AE83" s="78"/>
+      <c r="AF83" s="79"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="69"/>
-      <c r="AI83" s="70"/>
-      <c r="AJ83" s="71"/>
+      <c r="AH83" s="77"/>
+      <c r="AI83" s="78"/>
+      <c r="AJ83" s="79"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="69"/>
-      <c r="AM83" s="70"/>
-      <c r="AN83" s="71"/>
+      <c r="AL83" s="77"/>
+      <c r="AM83" s="78"/>
+      <c r="AN83" s="79"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="72"/>
-      <c r="C84" s="73"/>
-      <c r="D84" s="74"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="68"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="73"/>
-      <c r="H84" s="74"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="67"/>
+      <c r="H84" s="68"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="73"/>
-      <c r="L84" s="74"/>
+      <c r="J84" s="66"/>
+      <c r="K84" s="67"/>
+      <c r="L84" s="68"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="72"/>
-      <c r="O84" s="73"/>
-      <c r="P84" s="74"/>
+      <c r="N84" s="66"/>
+      <c r="O84" s="67"/>
+      <c r="P84" s="68"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="73"/>
-      <c r="T84" s="74"/>
+      <c r="R84" s="66"/>
+      <c r="S84" s="67"/>
+      <c r="T84" s="68"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="72"/>
-      <c r="W84" s="73"/>
-      <c r="X84" s="74"/>
+      <c r="V84" s="66"/>
+      <c r="W84" s="67"/>
+      <c r="X84" s="68"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="72"/>
-      <c r="AA84" s="73"/>
-      <c r="AB84" s="74"/>
+      <c r="Z84" s="66"/>
+      <c r="AA84" s="67"/>
+      <c r="AB84" s="68"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="72"/>
-      <c r="AE84" s="73"/>
-      <c r="AF84" s="74"/>
+      <c r="AD84" s="66"/>
+      <c r="AE84" s="67"/>
+      <c r="AF84" s="68"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="72"/>
-      <c r="AI84" s="73"/>
-      <c r="AJ84" s="74"/>
+      <c r="AH84" s="66"/>
+      <c r="AI84" s="67"/>
+      <c r="AJ84" s="68"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="72"/>
-      <c r="AM84" s="73"/>
-      <c r="AN84" s="74"/>
+      <c r="AL84" s="66"/>
+      <c r="AM84" s="67"/>
+      <c r="AN84" s="68"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -6643,249 +6643,249 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="75"/>
-      <c r="C86" s="76"/>
+      <c r="B86" s="89"/>
+      <c r="C86" s="90"/>
       <c r="D86" s="59"/>
       <c r="E86" s="36"/>
-      <c r="F86" s="75"/>
-      <c r="G86" s="76"/>
+      <c r="F86" s="89"/>
+      <c r="G86" s="90"/>
       <c r="H86" s="59"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="75"/>
-      <c r="K86" s="76"/>
+      <c r="J86" s="89"/>
+      <c r="K86" s="90"/>
       <c r="L86" s="59"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="83" t="s">
+      <c r="N86" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="O86" s="84"/>
+      <c r="O86" s="70"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="83" t="s">
+      <c r="R86" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="S86" s="84"/>
+      <c r="S86" s="70"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="83"/>
-      <c r="W86" s="84"/>
+      <c r="V86" s="69"/>
+      <c r="W86" s="70"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="83"/>
-      <c r="AA86" s="84"/>
+      <c r="Z86" s="69"/>
+      <c r="AA86" s="70"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="83"/>
-      <c r="AE86" s="84"/>
+      <c r="AD86" s="69"/>
+      <c r="AE86" s="70"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="83"/>
-      <c r="AI86" s="84"/>
+      <c r="AH86" s="69"/>
+      <c r="AI86" s="70"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="83"/>
-      <c r="AM86" s="84"/>
+      <c r="AL86" s="69"/>
+      <c r="AM86" s="70"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="63"/>
-      <c r="C87" s="64"/>
-      <c r="D87" s="65"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="81"/>
+      <c r="D87" s="82"/>
       <c r="E87" s="38"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="65"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="81"/>
+      <c r="H87" s="82"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="64"/>
-      <c r="L87" s="65"/>
+      <c r="J87" s="80"/>
+      <c r="K87" s="81"/>
+      <c r="L87" s="82"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="85"/>
-      <c r="O87" s="86"/>
-      <c r="P87" s="87"/>
+      <c r="N87" s="71"/>
+      <c r="O87" s="72"/>
+      <c r="P87" s="73"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="85"/>
-      <c r="S87" s="86"/>
-      <c r="T87" s="87"/>
+      <c r="R87" s="71"/>
+      <c r="S87" s="72"/>
+      <c r="T87" s="73"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="85"/>
-      <c r="W87" s="86"/>
-      <c r="X87" s="87"/>
+      <c r="V87" s="71"/>
+      <c r="W87" s="72"/>
+      <c r="X87" s="73"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="85"/>
-      <c r="AA87" s="86"/>
-      <c r="AB87" s="87"/>
+      <c r="Z87" s="71"/>
+      <c r="AA87" s="72"/>
+      <c r="AB87" s="73"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="85"/>
-      <c r="AE87" s="86"/>
-      <c r="AF87" s="87"/>
+      <c r="AD87" s="71"/>
+      <c r="AE87" s="72"/>
+      <c r="AF87" s="73"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="85"/>
-      <c r="AI87" s="86"/>
-      <c r="AJ87" s="87"/>
+      <c r="AH87" s="71"/>
+      <c r="AI87" s="72"/>
+      <c r="AJ87" s="73"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="85"/>
-      <c r="AM87" s="86"/>
-      <c r="AN87" s="87"/>
+      <c r="AL87" s="71"/>
+      <c r="AM87" s="72"/>
+      <c r="AN87" s="73"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="66"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="68"/>
+      <c r="B88" s="93"/>
+      <c r="C88" s="94"/>
+      <c r="D88" s="95"/>
       <c r="E88" s="37"/>
-      <c r="F88" s="66"/>
-      <c r="G88" s="67"/>
-      <c r="H88" s="68"/>
+      <c r="F88" s="93"/>
+      <c r="G88" s="94"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="31"/>
-      <c r="J88" s="66"/>
-      <c r="K88" s="67"/>
-      <c r="L88" s="68"/>
+      <c r="J88" s="93"/>
+      <c r="K88" s="94"/>
+      <c r="L88" s="95"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="91" t="s">
+      <c r="N88" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="O88" s="92"/>
-      <c r="P88" s="93"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="76"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="91" t="s">
+      <c r="R88" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="S88" s="92"/>
-      <c r="T88" s="93"/>
+      <c r="S88" s="75"/>
+      <c r="T88" s="76"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="91"/>
-      <c r="W88" s="92"/>
-      <c r="X88" s="93"/>
+      <c r="V88" s="74"/>
+      <c r="W88" s="75"/>
+      <c r="X88" s="76"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="91"/>
-      <c r="AA88" s="92"/>
-      <c r="AB88" s="93"/>
+      <c r="Z88" s="74"/>
+      <c r="AA88" s="75"/>
+      <c r="AB88" s="76"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="91"/>
-      <c r="AE88" s="92"/>
-      <c r="AF88" s="93"/>
+      <c r="AD88" s="74"/>
+      <c r="AE88" s="75"/>
+      <c r="AF88" s="76"/>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="91"/>
-      <c r="AI88" s="92"/>
-      <c r="AJ88" s="93"/>
+      <c r="AH88" s="74"/>
+      <c r="AI88" s="75"/>
+      <c r="AJ88" s="76"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="91"/>
-      <c r="AM88" s="92"/>
-      <c r="AN88" s="93"/>
+      <c r="AL88" s="74"/>
+      <c r="AM88" s="75"/>
+      <c r="AN88" s="76"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="69"/>
-      <c r="C89" s="70"/>
-      <c r="D89" s="71"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
       <c r="E89" s="43"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
-      <c r="H89" s="71"/>
+      <c r="F89" s="77"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="79"/>
       <c r="I89" s="31"/>
-      <c r="J89" s="69"/>
-      <c r="K89" s="70"/>
-      <c r="L89" s="71"/>
+      <c r="J89" s="77"/>
+      <c r="K89" s="78"/>
+      <c r="L89" s="79"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="69" t="s">
+      <c r="N89" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="O89" s="70"/>
-      <c r="P89" s="71"/>
+      <c r="O89" s="78"/>
+      <c r="P89" s="79"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="69" t="s">
+      <c r="R89" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="S89" s="70"/>
-      <c r="T89" s="71"/>
+      <c r="S89" s="78"/>
+      <c r="T89" s="79"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="69"/>
-      <c r="W89" s="70"/>
-      <c r="X89" s="71"/>
+      <c r="V89" s="77"/>
+      <c r="W89" s="78"/>
+      <c r="X89" s="79"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="69"/>
-      <c r="AA89" s="70"/>
-      <c r="AB89" s="71"/>
+      <c r="Z89" s="77"/>
+      <c r="AA89" s="78"/>
+      <c r="AB89" s="79"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="69"/>
-      <c r="AE89" s="70"/>
-      <c r="AF89" s="71"/>
+      <c r="AD89" s="77"/>
+      <c r="AE89" s="78"/>
+      <c r="AF89" s="79"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="69"/>
-      <c r="AI89" s="70"/>
-      <c r="AJ89" s="71"/>
+      <c r="AH89" s="77"/>
+      <c r="AI89" s="78"/>
+      <c r="AJ89" s="79"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="69"/>
-      <c r="AM89" s="70"/>
-      <c r="AN89" s="71"/>
+      <c r="AL89" s="77"/>
+      <c r="AM89" s="78"/>
+      <c r="AN89" s="79"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="72"/>
-      <c r="C90" s="73"/>
-      <c r="D90" s="74"/>
+      <c r="B90" s="66"/>
+      <c r="C90" s="67"/>
+      <c r="D90" s="68"/>
       <c r="E90" s="43"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="73"/>
-      <c r="H90" s="74"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="67"/>
+      <c r="H90" s="68"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="73"/>
-      <c r="L90" s="74"/>
+      <c r="J90" s="66"/>
+      <c r="K90" s="67"/>
+      <c r="L90" s="68"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="72"/>
-      <c r="O90" s="73"/>
-      <c r="P90" s="74"/>
+      <c r="N90" s="66"/>
+      <c r="O90" s="67"/>
+      <c r="P90" s="68"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="72"/>
-      <c r="S90" s="73"/>
-      <c r="T90" s="74"/>
+      <c r="R90" s="66"/>
+      <c r="S90" s="67"/>
+      <c r="T90" s="68"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="72"/>
-      <c r="W90" s="73"/>
-      <c r="X90" s="74"/>
+      <c r="V90" s="66"/>
+      <c r="W90" s="67"/>
+      <c r="X90" s="68"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="72"/>
-      <c r="AA90" s="73"/>
-      <c r="AB90" s="74"/>
+      <c r="Z90" s="66"/>
+      <c r="AA90" s="67"/>
+      <c r="AB90" s="68"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="72"/>
-      <c r="AE90" s="73"/>
-      <c r="AF90" s="74"/>
+      <c r="AD90" s="66"/>
+      <c r="AE90" s="67"/>
+      <c r="AF90" s="68"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="72"/>
-      <c r="AI90" s="73"/>
-      <c r="AJ90" s="74"/>
+      <c r="AH90" s="66"/>
+      <c r="AI90" s="67"/>
+      <c r="AJ90" s="68"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="72"/>
-      <c r="AM90" s="73"/>
-      <c r="AN90" s="74"/>
+      <c r="AL90" s="66"/>
+      <c r="AM90" s="67"/>
+      <c r="AN90" s="68"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -6931,237 +6931,237 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="75"/>
-      <c r="C92" s="76"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="90"/>
       <c r="D92" s="59"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="75"/>
-      <c r="G92" s="76"/>
+      <c r="F92" s="89"/>
+      <c r="G92" s="90"/>
       <c r="H92" s="59"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="75"/>
-      <c r="K92" s="76"/>
+      <c r="J92" s="89"/>
+      <c r="K92" s="90"/>
       <c r="L92" s="59"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="83"/>
-      <c r="O92" s="84"/>
+      <c r="N92" s="69"/>
+      <c r="O92" s="70"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="83"/>
-      <c r="S92" s="84"/>
+      <c r="R92" s="69"/>
+      <c r="S92" s="70"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="83"/>
-      <c r="W92" s="84"/>
+      <c r="V92" s="69"/>
+      <c r="W92" s="70"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="83"/>
-      <c r="AA92" s="84"/>
+      <c r="Z92" s="69"/>
+      <c r="AA92" s="70"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="83"/>
-      <c r="AE92" s="84"/>
+      <c r="AD92" s="69"/>
+      <c r="AE92" s="70"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="83"/>
-      <c r="AI92" s="84"/>
+      <c r="AH92" s="69"/>
+      <c r="AI92" s="70"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="83"/>
-      <c r="AM92" s="84"/>
+      <c r="AL92" s="69"/>
+      <c r="AM92" s="70"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="64"/>
-      <c r="D93" s="65"/>
+      <c r="B93" s="80"/>
+      <c r="C93" s="81"/>
+      <c r="D93" s="82"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="63"/>
-      <c r="G93" s="64"/>
-      <c r="H93" s="65"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="81"/>
+      <c r="H93" s="82"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="63"/>
-      <c r="K93" s="64"/>
-      <c r="L93" s="65"/>
+      <c r="J93" s="80"/>
+      <c r="K93" s="81"/>
+      <c r="L93" s="82"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="85"/>
-      <c r="O93" s="86"/>
-      <c r="P93" s="87"/>
+      <c r="N93" s="71"/>
+      <c r="O93" s="72"/>
+      <c r="P93" s="73"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="85"/>
-      <c r="S93" s="86"/>
-      <c r="T93" s="87"/>
+      <c r="R93" s="71"/>
+      <c r="S93" s="72"/>
+      <c r="T93" s="73"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="85"/>
-      <c r="W93" s="86"/>
-      <c r="X93" s="87"/>
+      <c r="V93" s="71"/>
+      <c r="W93" s="72"/>
+      <c r="X93" s="73"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="85"/>
-      <c r="AA93" s="86"/>
-      <c r="AB93" s="87"/>
+      <c r="Z93" s="71"/>
+      <c r="AA93" s="72"/>
+      <c r="AB93" s="73"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="85"/>
-      <c r="AE93" s="86"/>
-      <c r="AF93" s="87"/>
+      <c r="AD93" s="71"/>
+      <c r="AE93" s="72"/>
+      <c r="AF93" s="73"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="85"/>
-      <c r="AI93" s="86"/>
-      <c r="AJ93" s="87"/>
+      <c r="AH93" s="71"/>
+      <c r="AI93" s="72"/>
+      <c r="AJ93" s="73"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="85"/>
-      <c r="AM93" s="86"/>
-      <c r="AN93" s="87"/>
+      <c r="AL93" s="71"/>
+      <c r="AM93" s="72"/>
+      <c r="AN93" s="73"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="66"/>
-      <c r="C94" s="67"/>
-      <c r="D94" s="68"/>
+      <c r="B94" s="93"/>
+      <c r="C94" s="94"/>
+      <c r="D94" s="95"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="67"/>
-      <c r="H94" s="68"/>
+      <c r="F94" s="93"/>
+      <c r="G94" s="94"/>
+      <c r="H94" s="95"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="66"/>
-      <c r="K94" s="67"/>
-      <c r="L94" s="68"/>
+      <c r="J94" s="93"/>
+      <c r="K94" s="94"/>
+      <c r="L94" s="95"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="91"/>
-      <c r="O94" s="92"/>
-      <c r="P94" s="93"/>
+      <c r="N94" s="74"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="76"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="91"/>
-      <c r="S94" s="92"/>
-      <c r="T94" s="93"/>
+      <c r="R94" s="74"/>
+      <c r="S94" s="75"/>
+      <c r="T94" s="76"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="91"/>
-      <c r="W94" s="92"/>
-      <c r="X94" s="93"/>
+      <c r="V94" s="74"/>
+      <c r="W94" s="75"/>
+      <c r="X94" s="76"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="91"/>
-      <c r="AA94" s="92"/>
-      <c r="AB94" s="93"/>
+      <c r="Z94" s="74"/>
+      <c r="AA94" s="75"/>
+      <c r="AB94" s="76"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="91"/>
-      <c r="AE94" s="92"/>
-      <c r="AF94" s="93"/>
+      <c r="AD94" s="74"/>
+      <c r="AE94" s="75"/>
+      <c r="AF94" s="76"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="91"/>
-      <c r="AI94" s="92"/>
-      <c r="AJ94" s="93"/>
+      <c r="AH94" s="74"/>
+      <c r="AI94" s="75"/>
+      <c r="AJ94" s="76"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="91"/>
-      <c r="AM94" s="92"/>
-      <c r="AN94" s="93"/>
+      <c r="AL94" s="74"/>
+      <c r="AM94" s="75"/>
+      <c r="AN94" s="76"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="69"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="71"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="79"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="69"/>
-      <c r="G95" s="70"/>
-      <c r="H95" s="71"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="78"/>
+      <c r="H95" s="79"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="69"/>
-      <c r="K95" s="70"/>
-      <c r="L95" s="71"/>
+      <c r="J95" s="77"/>
+      <c r="K95" s="78"/>
+      <c r="L95" s="79"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="69"/>
-      <c r="O95" s="70"/>
-      <c r="P95" s="71"/>
+      <c r="N95" s="77"/>
+      <c r="O95" s="78"/>
+      <c r="P95" s="79"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="69"/>
-      <c r="S95" s="70"/>
-      <c r="T95" s="71"/>
+      <c r="R95" s="77"/>
+      <c r="S95" s="78"/>
+      <c r="T95" s="79"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="69"/>
-      <c r="W95" s="70"/>
-      <c r="X95" s="71"/>
+      <c r="V95" s="77"/>
+      <c r="W95" s="78"/>
+      <c r="X95" s="79"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="69"/>
-      <c r="AA95" s="70"/>
-      <c r="AB95" s="71"/>
+      <c r="Z95" s="77"/>
+      <c r="AA95" s="78"/>
+      <c r="AB95" s="79"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="69"/>
-      <c r="AE95" s="70"/>
-      <c r="AF95" s="71"/>
+      <c r="AD95" s="77"/>
+      <c r="AE95" s="78"/>
+      <c r="AF95" s="79"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="69"/>
-      <c r="AI95" s="70"/>
-      <c r="AJ95" s="71"/>
+      <c r="AH95" s="77"/>
+      <c r="AI95" s="78"/>
+      <c r="AJ95" s="79"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="69"/>
-      <c r="AM95" s="70"/>
-      <c r="AN95" s="71"/>
+      <c r="AL95" s="77"/>
+      <c r="AM95" s="78"/>
+      <c r="AN95" s="79"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="72"/>
-      <c r="C96" s="73"/>
-      <c r="D96" s="74"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="67"/>
+      <c r="D96" s="68"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="72"/>
-      <c r="G96" s="73"/>
-      <c r="H96" s="74"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="67"/>
+      <c r="H96" s="68"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="72"/>
-      <c r="K96" s="73"/>
-      <c r="L96" s="74"/>
+      <c r="J96" s="66"/>
+      <c r="K96" s="67"/>
+      <c r="L96" s="68"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="72"/>
-      <c r="O96" s="73"/>
-      <c r="P96" s="74"/>
+      <c r="N96" s="66"/>
+      <c r="O96" s="67"/>
+      <c r="P96" s="68"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="72"/>
-      <c r="S96" s="73"/>
-      <c r="T96" s="74"/>
+      <c r="R96" s="66"/>
+      <c r="S96" s="67"/>
+      <c r="T96" s="68"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="72"/>
-      <c r="W96" s="73"/>
-      <c r="X96" s="74"/>
+      <c r="V96" s="66"/>
+      <c r="W96" s="67"/>
+      <c r="X96" s="68"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="72"/>
-      <c r="AA96" s="73"/>
-      <c r="AB96" s="74"/>
+      <c r="Z96" s="66"/>
+      <c r="AA96" s="67"/>
+      <c r="AB96" s="68"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="72"/>
-      <c r="AE96" s="73"/>
-      <c r="AF96" s="74"/>
+      <c r="AD96" s="66"/>
+      <c r="AE96" s="67"/>
+      <c r="AF96" s="68"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="72"/>
-      <c r="AI96" s="73"/>
-      <c r="AJ96" s="74"/>
+      <c r="AH96" s="66"/>
+      <c r="AI96" s="67"/>
+      <c r="AJ96" s="68"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="72"/>
-      <c r="AM96" s="73"/>
-      <c r="AN96" s="74"/>
+      <c r="AL96" s="66"/>
+      <c r="AM96" s="67"/>
+      <c r="AN96" s="68"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7207,261 +7207,261 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="75"/>
-      <c r="C98" s="76"/>
+      <c r="B98" s="89"/>
+      <c r="C98" s="90"/>
       <c r="D98" s="59"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="75"/>
-      <c r="G98" s="76"/>
+      <c r="F98" s="89"/>
+      <c r="G98" s="90"/>
       <c r="H98" s="59"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="75"/>
-      <c r="K98" s="76"/>
+      <c r="J98" s="89"/>
+      <c r="K98" s="90"/>
       <c r="L98" s="59"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="101" t="s">
+      <c r="N98" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="O98" s="102"/>
+      <c r="O98" s="97"/>
       <c r="P98" s="62"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="101" t="s">
+      <c r="R98" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="S98" s="102"/>
+      <c r="S98" s="97"/>
       <c r="T98" s="62"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="101" t="s">
+      <c r="V98" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="W98" s="102"/>
+      <c r="W98" s="97"/>
       <c r="X98" s="62"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="101" t="s">
+      <c r="Z98" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="AA98" s="102"/>
+      <c r="AA98" s="97"/>
       <c r="AB98" s="62"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="83"/>
-      <c r="AE98" s="84"/>
+      <c r="AD98" s="69"/>
+      <c r="AE98" s="70"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="83"/>
-      <c r="AI98" s="84"/>
+      <c r="AH98" s="69"/>
+      <c r="AI98" s="70"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="83"/>
-      <c r="AM98" s="84"/>
+      <c r="AL98" s="69"/>
+      <c r="AM98" s="70"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="63"/>
-      <c r="C99" s="64"/>
-      <c r="D99" s="65"/>
+      <c r="B99" s="80"/>
+      <c r="C99" s="81"/>
+      <c r="D99" s="82"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="63"/>
-      <c r="G99" s="64"/>
-      <c r="H99" s="65"/>
+      <c r="F99" s="80"/>
+      <c r="G99" s="81"/>
+      <c r="H99" s="82"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="63"/>
-      <c r="K99" s="64"/>
-      <c r="L99" s="65"/>
+      <c r="J99" s="80"/>
+      <c r="K99" s="81"/>
+      <c r="L99" s="82"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="98" t="s">
+      <c r="N99" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="O99" s="99"/>
-      <c r="P99" s="100"/>
+      <c r="O99" s="84"/>
+      <c r="P99" s="85"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="98" t="s">
+      <c r="R99" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="S99" s="99"/>
-      <c r="T99" s="100"/>
+      <c r="S99" s="84"/>
+      <c r="T99" s="85"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="98" t="s">
+      <c r="V99" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="W99" s="99"/>
-      <c r="X99" s="100"/>
+      <c r="W99" s="84"/>
+      <c r="X99" s="85"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="98" t="s">
+      <c r="Z99" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="AA99" s="99"/>
-      <c r="AB99" s="100"/>
+      <c r="AA99" s="84"/>
+      <c r="AB99" s="85"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="85"/>
-      <c r="AE99" s="86"/>
-      <c r="AF99" s="87"/>
+      <c r="AD99" s="71"/>
+      <c r="AE99" s="72"/>
+      <c r="AF99" s="73"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="85"/>
-      <c r="AI99" s="86"/>
-      <c r="AJ99" s="87"/>
+      <c r="AH99" s="71"/>
+      <c r="AI99" s="72"/>
+      <c r="AJ99" s="73"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="85"/>
-      <c r="AM99" s="86"/>
-      <c r="AN99" s="87"/>
+      <c r="AL99" s="71"/>
+      <c r="AM99" s="72"/>
+      <c r="AN99" s="73"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="66"/>
-      <c r="C100" s="67"/>
-      <c r="D100" s="68"/>
+      <c r="B100" s="93"/>
+      <c r="C100" s="94"/>
+      <c r="D100" s="95"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="66"/>
-      <c r="G100" s="67"/>
-      <c r="H100" s="68"/>
+      <c r="F100" s="93"/>
+      <c r="G100" s="94"/>
+      <c r="H100" s="95"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="66"/>
-      <c r="K100" s="67"/>
-      <c r="L100" s="68"/>
+      <c r="J100" s="93"/>
+      <c r="K100" s="94"/>
+      <c r="L100" s="95"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="103"/>
-      <c r="O100" s="104"/>
-      <c r="P100" s="105"/>
+      <c r="N100" s="86"/>
+      <c r="O100" s="87"/>
+      <c r="P100" s="88"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="103"/>
-      <c r="S100" s="104"/>
-      <c r="T100" s="105"/>
+      <c r="R100" s="86"/>
+      <c r="S100" s="87"/>
+      <c r="T100" s="88"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="103"/>
-      <c r="W100" s="104"/>
-      <c r="X100" s="105"/>
+      <c r="V100" s="86"/>
+      <c r="W100" s="87"/>
+      <c r="X100" s="88"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="103"/>
-      <c r="AA100" s="104"/>
-      <c r="AB100" s="105"/>
+      <c r="Z100" s="86"/>
+      <c r="AA100" s="87"/>
+      <c r="AB100" s="88"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="91"/>
-      <c r="AE100" s="92"/>
-      <c r="AF100" s="93"/>
+      <c r="AD100" s="74"/>
+      <c r="AE100" s="75"/>
+      <c r="AF100" s="76"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="91"/>
-      <c r="AI100" s="92"/>
-      <c r="AJ100" s="93"/>
+      <c r="AH100" s="74"/>
+      <c r="AI100" s="75"/>
+      <c r="AJ100" s="76"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="91"/>
-      <c r="AM100" s="92"/>
-      <c r="AN100" s="93"/>
+      <c r="AL100" s="74"/>
+      <c r="AM100" s="75"/>
+      <c r="AN100" s="76"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="69"/>
-      <c r="C101" s="70"/>
-      <c r="D101" s="71"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="78"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="69"/>
-      <c r="G101" s="70"/>
-      <c r="H101" s="71"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="78"/>
+      <c r="H101" s="79"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="69"/>
-      <c r="K101" s="70"/>
-      <c r="L101" s="71"/>
+      <c r="J101" s="77"/>
+      <c r="K101" s="78"/>
+      <c r="L101" s="79"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="69" t="s">
+      <c r="N101" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="O101" s="70"/>
-      <c r="P101" s="71"/>
+      <c r="O101" s="78"/>
+      <c r="P101" s="79"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="69" t="s">
+      <c r="R101" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="S101" s="70"/>
-      <c r="T101" s="71"/>
+      <c r="S101" s="78"/>
+      <c r="T101" s="79"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="69" t="s">
+      <c r="V101" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="W101" s="70"/>
-      <c r="X101" s="71"/>
+      <c r="W101" s="78"/>
+      <c r="X101" s="79"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="69" t="s">
+      <c r="Z101" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="AA101" s="70"/>
-      <c r="AB101" s="71"/>
+      <c r="AA101" s="78"/>
+      <c r="AB101" s="79"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="69"/>
-      <c r="AE101" s="70"/>
-      <c r="AF101" s="71"/>
+      <c r="AD101" s="77"/>
+      <c r="AE101" s="78"/>
+      <c r="AF101" s="79"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="69"/>
-      <c r="AI101" s="70"/>
-      <c r="AJ101" s="71"/>
+      <c r="AH101" s="77"/>
+      <c r="AI101" s="78"/>
+      <c r="AJ101" s="79"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="69"/>
-      <c r="AM101" s="70"/>
-      <c r="AN101" s="71"/>
+      <c r="AL101" s="77"/>
+      <c r="AM101" s="78"/>
+      <c r="AN101" s="79"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="72"/>
-      <c r="C102" s="73"/>
-      <c r="D102" s="74"/>
+      <c r="B102" s="66"/>
+      <c r="C102" s="67"/>
+      <c r="D102" s="68"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="72"/>
-      <c r="G102" s="73"/>
-      <c r="H102" s="74"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="67"/>
+      <c r="H102" s="68"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="72"/>
-      <c r="K102" s="73"/>
-      <c r="L102" s="74"/>
+      <c r="J102" s="66"/>
+      <c r="K102" s="67"/>
+      <c r="L102" s="68"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="72"/>
-      <c r="O102" s="73"/>
-      <c r="P102" s="74"/>
+      <c r="N102" s="66"/>
+      <c r="O102" s="67"/>
+      <c r="P102" s="68"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="72"/>
-      <c r="S102" s="73"/>
-      <c r="T102" s="74"/>
+      <c r="R102" s="66"/>
+      <c r="S102" s="67"/>
+      <c r="T102" s="68"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="72"/>
-      <c r="W102" s="73"/>
-      <c r="X102" s="74"/>
+      <c r="V102" s="66"/>
+      <c r="W102" s="67"/>
+      <c r="X102" s="68"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="72"/>
-      <c r="AA102" s="73"/>
-      <c r="AB102" s="74"/>
+      <c r="Z102" s="66"/>
+      <c r="AA102" s="67"/>
+      <c r="AB102" s="68"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="72"/>
-      <c r="AE102" s="73"/>
-      <c r="AF102" s="74"/>
+      <c r="AD102" s="66"/>
+      <c r="AE102" s="67"/>
+      <c r="AF102" s="68"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="72"/>
-      <c r="AI102" s="73"/>
-      <c r="AJ102" s="74"/>
+      <c r="AH102" s="66"/>
+      <c r="AI102" s="67"/>
+      <c r="AJ102" s="68"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="72"/>
-      <c r="AM102" s="73"/>
-      <c r="AN102" s="74"/>
+      <c r="AL102" s="66"/>
+      <c r="AM102" s="67"/>
+      <c r="AN102" s="68"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7507,7 +7507,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7524,73 +7524,73 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="83"/>
-      <c r="C105" s="84"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="69"/>
+      <c r="C105" s="70"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="83"/>
-      <c r="G105" s="84"/>
+      <c r="F105" s="69"/>
+      <c r="G105" s="70"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="83"/>
-      <c r="K105" s="84"/>
+      <c r="J105" s="69"/>
+      <c r="K105" s="70"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="85"/>
-      <c r="C106" s="86"/>
-      <c r="D106" s="87"/>
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="71"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="73"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="85"/>
-      <c r="G106" s="86"/>
-      <c r="H106" s="87"/>
+      <c r="F106" s="71"/>
+      <c r="G106" s="72"/>
+      <c r="H106" s="73"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="85"/>
-      <c r="K106" s="86"/>
-      <c r="L106" s="87"/>
-    </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="91"/>
-      <c r="C107" s="92"/>
-      <c r="D107" s="93"/>
+      <c r="J106" s="71"/>
+      <c r="K106" s="72"/>
+      <c r="L106" s="73"/>
+    </row>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="74"/>
+      <c r="C107" s="75"/>
+      <c r="D107" s="76"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="91"/>
-      <c r="G107" s="92"/>
-      <c r="H107" s="93"/>
+      <c r="F107" s="74"/>
+      <c r="G107" s="75"/>
+      <c r="H107" s="76"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="91"/>
-      <c r="K107" s="92"/>
-      <c r="L107" s="93"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="69"/>
-      <c r="C108" s="70"/>
-      <c r="D108" s="71"/>
+      <c r="J107" s="74"/>
+      <c r="K107" s="75"/>
+      <c r="L107" s="76"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="77"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="79"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="69"/>
-      <c r="G108" s="70"/>
-      <c r="H108" s="71"/>
+      <c r="F108" s="77"/>
+      <c r="G108" s="78"/>
+      <c r="H108" s="79"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="69"/>
-      <c r="K108" s="70"/>
-      <c r="L108" s="71"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="72"/>
-      <c r="C109" s="73"/>
-      <c r="D109" s="74"/>
+      <c r="J108" s="77"/>
+      <c r="K108" s="78"/>
+      <c r="L108" s="79"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="66"/>
+      <c r="C109" s="67"/>
+      <c r="D109" s="68"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="72"/>
-      <c r="G109" s="73"/>
-      <c r="H109" s="74"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="67"/>
+      <c r="H109" s="68"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="72"/>
-      <c r="K109" s="73"/>
-      <c r="L109" s="74"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J109" s="66"/>
+      <c r="K109" s="67"/>
+      <c r="L109" s="68"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7603,72 +7603,72 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="83"/>
-      <c r="C111" s="84"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="69"/>
+      <c r="C111" s="70"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="83"/>
-      <c r="G111" s="84"/>
+      <c r="F111" s="69"/>
+      <c r="G111" s="70"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="83"/>
-      <c r="K111" s="84"/>
+      <c r="J111" s="69"/>
+      <c r="K111" s="70"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="85"/>
-      <c r="C112" s="86"/>
-      <c r="D112" s="87"/>
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="71"/>
+      <c r="C112" s="72"/>
+      <c r="D112" s="73"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="85"/>
-      <c r="G112" s="86"/>
-      <c r="H112" s="87"/>
+      <c r="F112" s="71"/>
+      <c r="G112" s="72"/>
+      <c r="H112" s="73"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="85"/>
-      <c r="K112" s="86"/>
-      <c r="L112" s="87"/>
-    </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="91"/>
-      <c r="C113" s="92"/>
-      <c r="D113" s="93"/>
+      <c r="J112" s="71"/>
+      <c r="K112" s="72"/>
+      <c r="L112" s="73"/>
+    </row>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="74"/>
+      <c r="C113" s="75"/>
+      <c r="D113" s="76"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="91"/>
-      <c r="G113" s="92"/>
-      <c r="H113" s="93"/>
+      <c r="F113" s="74"/>
+      <c r="G113" s="75"/>
+      <c r="H113" s="76"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="91"/>
-      <c r="K113" s="92"/>
-      <c r="L113" s="93"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="69"/>
-      <c r="C114" s="70"/>
-      <c r="D114" s="71"/>
+      <c r="J113" s="74"/>
+      <c r="K113" s="75"/>
+      <c r="L113" s="76"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="77"/>
+      <c r="C114" s="78"/>
+      <c r="D114" s="79"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="69"/>
-      <c r="G114" s="70"/>
-      <c r="H114" s="71"/>
+      <c r="F114" s="77"/>
+      <c r="G114" s="78"/>
+      <c r="H114" s="79"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="69"/>
-      <c r="K114" s="70"/>
-      <c r="L114" s="71"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="72"/>
-      <c r="C115" s="73"/>
-      <c r="D115" s="74"/>
+      <c r="J114" s="77"/>
+      <c r="K114" s="78"/>
+      <c r="L114" s="79"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="66"/>
+      <c r="C115" s="67"/>
+      <c r="D115" s="68"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="72"/>
-      <c r="G115" s="73"/>
-      <c r="H115" s="74"/>
+      <c r="F115" s="66"/>
+      <c r="G115" s="67"/>
+      <c r="H115" s="68"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="72"/>
-      <c r="K115" s="73"/>
-      <c r="L115" s="74"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J115" s="66"/>
+      <c r="K115" s="67"/>
+      <c r="L115" s="68"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7681,72 +7681,72 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="83"/>
-      <c r="C117" s="84"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="69"/>
+      <c r="C117" s="70"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="83"/>
-      <c r="G117" s="84"/>
+      <c r="F117" s="69"/>
+      <c r="G117" s="70"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="83"/>
-      <c r="K117" s="84"/>
+      <c r="J117" s="69"/>
+      <c r="K117" s="70"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="85"/>
-      <c r="C118" s="86"/>
-      <c r="D118" s="87"/>
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="71"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="73"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="85"/>
-      <c r="G118" s="86"/>
-      <c r="H118" s="87"/>
+      <c r="F118" s="71"/>
+      <c r="G118" s="72"/>
+      <c r="H118" s="73"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="85"/>
-      <c r="K118" s="86"/>
-      <c r="L118" s="87"/>
-    </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="91"/>
-      <c r="C119" s="92"/>
-      <c r="D119" s="93"/>
+      <c r="J118" s="71"/>
+      <c r="K118" s="72"/>
+      <c r="L118" s="73"/>
+    </row>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="74"/>
+      <c r="C119" s="75"/>
+      <c r="D119" s="76"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="91"/>
-      <c r="G119" s="92"/>
-      <c r="H119" s="93"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="75"/>
+      <c r="H119" s="76"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="91"/>
-      <c r="K119" s="92"/>
-      <c r="L119" s="93"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="69"/>
-      <c r="C120" s="70"/>
-      <c r="D120" s="71"/>
+      <c r="J119" s="74"/>
+      <c r="K119" s="75"/>
+      <c r="L119" s="76"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="77"/>
+      <c r="C120" s="78"/>
+      <c r="D120" s="79"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="69"/>
-      <c r="G120" s="70"/>
-      <c r="H120" s="71"/>
+      <c r="F120" s="77"/>
+      <c r="G120" s="78"/>
+      <c r="H120" s="79"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="69"/>
-      <c r="K120" s="70"/>
-      <c r="L120" s="71"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="72"/>
-      <c r="C121" s="73"/>
-      <c r="D121" s="74"/>
+      <c r="J120" s="77"/>
+      <c r="K120" s="78"/>
+      <c r="L120" s="79"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="66"/>
+      <c r="C121" s="67"/>
+      <c r="D121" s="68"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="72"/>
-      <c r="G121" s="73"/>
-      <c r="H121" s="74"/>
+      <c r="F121" s="66"/>
+      <c r="G121" s="67"/>
+      <c r="H121" s="68"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="72"/>
-      <c r="K121" s="73"/>
-      <c r="L121" s="74"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J121" s="66"/>
+      <c r="K121" s="67"/>
+      <c r="L121" s="68"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7759,72 +7759,72 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="83"/>
-      <c r="C123" s="84"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="69"/>
+      <c r="C123" s="70"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="83"/>
-      <c r="G123" s="84"/>
+      <c r="F123" s="69"/>
+      <c r="G123" s="70"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="83"/>
-      <c r="K123" s="84"/>
+      <c r="J123" s="69"/>
+      <c r="K123" s="70"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="85"/>
-      <c r="C124" s="86"/>
-      <c r="D124" s="87"/>
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="71"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="73"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="85"/>
-      <c r="G124" s="86"/>
-      <c r="H124" s="87"/>
+      <c r="F124" s="71"/>
+      <c r="G124" s="72"/>
+      <c r="H124" s="73"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="85"/>
-      <c r="K124" s="86"/>
-      <c r="L124" s="87"/>
-    </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="91"/>
-      <c r="C125" s="92"/>
-      <c r="D125" s="93"/>
+      <c r="J124" s="71"/>
+      <c r="K124" s="72"/>
+      <c r="L124" s="73"/>
+    </row>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="74"/>
+      <c r="C125" s="75"/>
+      <c r="D125" s="76"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="91"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="93"/>
+      <c r="F125" s="74"/>
+      <c r="G125" s="75"/>
+      <c r="H125" s="76"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="91"/>
-      <c r="K125" s="92"/>
-      <c r="L125" s="93"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="69"/>
-      <c r="C126" s="70"/>
-      <c r="D126" s="71"/>
+      <c r="J125" s="74"/>
+      <c r="K125" s="75"/>
+      <c r="L125" s="76"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="77"/>
+      <c r="C126" s="78"/>
+      <c r="D126" s="79"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="69"/>
-      <c r="G126" s="70"/>
-      <c r="H126" s="71"/>
+      <c r="F126" s="77"/>
+      <c r="G126" s="78"/>
+      <c r="H126" s="79"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="69"/>
-      <c r="K126" s="70"/>
-      <c r="L126" s="71"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="72"/>
-      <c r="C127" s="73"/>
-      <c r="D127" s="74"/>
+      <c r="J126" s="77"/>
+      <c r="K126" s="78"/>
+      <c r="L126" s="79"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="66"/>
+      <c r="C127" s="67"/>
+      <c r="D127" s="68"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="72"/>
-      <c r="G127" s="73"/>
-      <c r="H127" s="74"/>
+      <c r="F127" s="66"/>
+      <c r="G127" s="67"/>
+      <c r="H127" s="68"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="72"/>
-      <c r="K127" s="73"/>
-      <c r="L127" s="74"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J127" s="66"/>
+      <c r="K127" s="67"/>
+      <c r="L127" s="68"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -7837,96 +7837,909 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="83"/>
-      <c r="C129" s="84"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="69"/>
+      <c r="C129" s="70"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="83"/>
-      <c r="G129" s="84"/>
+      <c r="F129" s="69"/>
+      <c r="G129" s="70"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="83"/>
-      <c r="K129" s="84"/>
+      <c r="J129" s="69"/>
+      <c r="K129" s="70"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="85"/>
-      <c r="C130" s="86"/>
-      <c r="D130" s="87"/>
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="71"/>
+      <c r="C130" s="72"/>
+      <c r="D130" s="73"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="85"/>
-      <c r="G130" s="86"/>
-      <c r="H130" s="87"/>
+      <c r="F130" s="71"/>
+      <c r="G130" s="72"/>
+      <c r="H130" s="73"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="85"/>
-      <c r="K130" s="86"/>
-      <c r="L130" s="87"/>
-    </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="91"/>
-      <c r="C131" s="92"/>
-      <c r="D131" s="93"/>
+      <c r="J130" s="71"/>
+      <c r="K130" s="72"/>
+      <c r="L130" s="73"/>
+    </row>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="74"/>
+      <c r="C131" s="75"/>
+      <c r="D131" s="76"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="91"/>
-      <c r="G131" s="92"/>
-      <c r="H131" s="93"/>
+      <c r="F131" s="74"/>
+      <c r="G131" s="75"/>
+      <c r="H131" s="76"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="91"/>
-      <c r="K131" s="92"/>
-      <c r="L131" s="93"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="69"/>
-      <c r="C132" s="70"/>
-      <c r="D132" s="71"/>
+      <c r="J131" s="74"/>
+      <c r="K131" s="75"/>
+      <c r="L131" s="76"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="77"/>
+      <c r="C132" s="78"/>
+      <c r="D132" s="79"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="69"/>
-      <c r="G132" s="70"/>
-      <c r="H132" s="71"/>
+      <c r="F132" s="77"/>
+      <c r="G132" s="78"/>
+      <c r="H132" s="79"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="69"/>
-      <c r="K132" s="70"/>
-      <c r="L132" s="71"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="72"/>
-      <c r="C133" s="73"/>
-      <c r="D133" s="74"/>
+      <c r="J132" s="77"/>
+      <c r="K132" s="78"/>
+      <c r="L132" s="79"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="66"/>
+      <c r="C133" s="67"/>
+      <c r="D133" s="68"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="72"/>
-      <c r="G133" s="73"/>
-      <c r="H133" s="74"/>
+      <c r="F133" s="66"/>
+      <c r="G133" s="67"/>
+      <c r="H133" s="68"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="72"/>
-      <c r="K133" s="73"/>
-      <c r="L133" s="74"/>
+      <c r="J133" s="66"/>
+      <c r="K133" s="67"/>
+      <c r="L133" s="68"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="881">
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="V38:X38"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="N59:P59"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V59:X59"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V52:X52"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:T52"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="R59:T59"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="Z59:AB59"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AD83:AF83"/>
     <mergeCell ref="AD50:AF50"/>
     <mergeCell ref="AD52:AE52"/>
     <mergeCell ref="V47:X47"/>
@@ -7951,848 +8764,35 @@
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="J69:L69"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="F52:H52"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="Z59:AB59"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V52:X52"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:T52"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="R59:T59"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V59:X59"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="N59:P59"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="V38:X38"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="Z52:AB52"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 L22:L27 H22:H27 D22:D27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R46:T49 AH14:AJ16 AL22:AM27 V95:X96 AD77:AF78 R22:S27 V77:X78 J132:L133 AL71:AN72 AH48:AJ50 N77:P78 Z95:AB96 R71:T72 N95:P96 AD71:AF72 Z46:AB49 V22:W27 AD48:AF50 AL101:AN102 J14:L16 V8:X10 V46:X49 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 N46:P49 B108:D109 N54:P56 Z14:AB16 R54:T56 R14:T16 R101:T102 AL14:AN16 AH83:AJ84 R34:T35 V54:X56 AD41:AF43 R89:T90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X35 V101:X102 V61:X64 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J95:L96 AL48:AN50 R61:T64 AH55:AJ57 J8:L10 N34:P35 Z54:AB56 R77:T78 AH22:AI27 N61:P64 AL41:AN43 B14:D16 J77:L78 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 R40:T41 AH34:AJ36 AH62:AJ64 Z101:AB102 AD55:AF57 Z77:AB78 Z83:AB84 N71:P72 V83:X84 Z34:AB35 Z22:AA27 AD83:AF84 Z61:AB64 AH71:AJ72 AH101:AJ102 Z40:AB41 AL77:AN78 AL62:AN64 Z8:AB10 V40:X41 AL8:AN10 N40:P41 N8:P10 AD62:AF64 Z71:AB72 AL95:AN96 AD34:AF36 F22:G27 R83:T84 V89:X90 AL34:AN36 N83:P84 F14:H16 B22:C27 J22:K27 F89:H90 F95:H96 V71:X72 AH41:AJ43 AL55:AN57 B89:D90 J101:L102 B95:D96 B8:D10 J89:L90 F8:H10 F101:H102 AH77:AJ78 B101:D102 N89:P90 J71:L72 J46:L49 B71:D72 B40:D41 F40:H41 F34:H35 J83:L84 F46:H49 J54:L56 J34:L35 J61:L64 B54:D56 B77:D78 J40:L41 F54:H56 F77:H78 B34:D35 F83:H84 B46:D49 F71:H72 B61:D64 F61:H64 B83:D84 N101:P102">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R46:T49 AH14:AJ16 AL22:AM27 V95:X96 AD77:AF78 R22:S27 V77:X78 J132:L133 AL71:AN72 N101:P102 N77:P78 Z95:AB96 R71:T72 N95:P96 AD71:AF72 Z46:AB49 V22:W27 AD48:AF50 AL101:AN102 J14:L16 V8:X10 V46:X49 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 N46:P49 B108:D109 N54:P56 Z14:AB16 R54:T56 R14:T16 R101:T102 AL14:AN16 AH83:AJ84 R34:T35 V54:X56 AD41:AF43 R89:T90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X35 V101:X102 V61:X64 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J95:L96 AL48:AN50 R61:T64 AH55:AJ57 J8:L10 N34:P35 Z54:AB56 R77:T78 AH22:AI27 N61:P64 AL41:AN43 B14:D16 J77:L78 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 R40:T41 AH34:AJ36 AH62:AJ64 Z101:AB102 AD55:AF57 Z77:AB78 Z83:AB84 N71:P72 V83:X84 Z34:AB35 Z22:AA27 AD83:AF84 Z61:AB64 AH71:AJ72 AH101:AJ102 Z40:AB41 AL77:AN78 AL62:AN64 Z8:AB10 V40:X41 AL8:AN10 N40:P41 N8:P10 AD62:AF64 Z71:AB72 AL95:AN96 AH48:AJ50 F22:G27 R83:T84 V89:X90 AL34:AN36 N83:P84 F14:H16 B22:C27 J22:K27 F89:H90 F95:H96 V71:X72 AH41:AJ43 AL55:AN57 B89:D90 J101:L102 B95:D96 B8:D10 J89:L90 F8:H10 F101:H102 AH77:AJ78 B101:D102 N89:P90 J71:L72 J46:L49 B71:D72 B40:D41 F40:H41 F34:H35 J83:L84 F46:H49 J54:L56 J34:L35 J61:L64 B54:D56 B77:D78 J40:L41 F54:H56 F77:H78 B34:D35 F83:H84 B46:D49 F71:H72 B61:D64 F61:H64 B83:D84 AD34:AF36">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="73">
   <si>
     <t>CUMA</t>
   </si>
@@ -224,9 +224,6 @@
     <t>A.C.PEHLİVAN.</t>
   </si>
   <si>
-    <t>PROVA</t>
-  </si>
-  <si>
     <t>CB Külliye   KURULUM</t>
   </si>
   <si>
@@ -237,6 +234,15 @@
   </si>
   <si>
     <t>???</t>
+  </si>
+  <si>
+    <t>HAZIRLIK</t>
+  </si>
+  <si>
+    <t>Çekmeköy Depo</t>
+  </si>
+  <si>
+    <t>KURULUM + PROVA</t>
   </si>
 </sst>
 </file>
@@ -1452,6 +1458,48 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1461,14 +1509,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1494,23 +1551,17 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1530,10 +1581,73 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1542,21 +1656,6 @@
     <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1565,99 +1664,6 @@
     </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2108,65 +2114,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="121" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="121" t="s">
+      <c r="J1" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="121"/>
-      <c r="L1" s="122"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="113"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="125" t="s">
+      <c r="N1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="115" t="s">
+      <c r="R1" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="115" t="s">
+      <c r="V1" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="115" t="s">
+      <c r="Z1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="115"/>
-      <c r="AB1" s="115"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="115" t="s">
+      <c r="AD1" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="115"/>
-      <c r="AF1" s="115"/>
+      <c r="AE1" s="117"/>
+      <c r="AF1" s="117"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="115" t="s">
+      <c r="AH1" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="115"/>
-      <c r="AJ1" s="115"/>
+      <c r="AI1" s="117"/>
+      <c r="AJ1" s="117"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="115" t="s">
+      <c r="AL1" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="115"/>
-      <c r="AN1" s="116"/>
+      <c r="AM1" s="117"/>
+      <c r="AN1" s="121"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2174,74 +2180,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="123">
+      <c r="B2" s="114">
         <f>N2-3</f>
         <v>46206</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="124">
+      <c r="F2" s="115">
         <f>N2-2</f>
         <v>46207</v>
       </c>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="124">
+      <c r="J2" s="115">
         <f>N2-1</f>
         <v>46208</v>
       </c>
-      <c r="K2" s="124"/>
-      <c r="L2" s="127"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="119"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="126">
+      <c r="N2" s="118">
         <v>46209</v>
       </c>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="117">
+      <c r="R2" s="110">
         <f>N2+1</f>
         <v>46210</v>
       </c>
-      <c r="S2" s="117"/>
-      <c r="T2" s="117"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="117">
+      <c r="V2" s="110">
         <f>N2+2</f>
         <v>46211</v>
       </c>
-      <c r="W2" s="117"/>
-      <c r="X2" s="117"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="117">
+      <c r="Z2" s="110">
         <f>N2+3</f>
         <v>46212</v>
       </c>
-      <c r="AA2" s="117"/>
-      <c r="AB2" s="117"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="110"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="117">
+      <c r="AD2" s="110">
         <f>N2+4</f>
         <v>46213</v>
       </c>
-      <c r="AE2" s="117"/>
-      <c r="AF2" s="117"/>
+      <c r="AE2" s="110"/>
+      <c r="AF2" s="110"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="117">
+      <c r="AH2" s="110">
         <f>N2+5</f>
         <v>46214</v>
       </c>
-      <c r="AI2" s="117"/>
-      <c r="AJ2" s="117"/>
+      <c r="AI2" s="110"/>
+      <c r="AJ2" s="110"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="117">
+      <c r="AL2" s="110">
         <f>N2+6</f>
         <v>46215</v>
       </c>
-      <c r="AM2" s="117"/>
-      <c r="AN2" s="118"/>
+      <c r="AM2" s="110"/>
+      <c r="AN2" s="122"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2295,47 +2301,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="108" t="s">
+      <c r="N4" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="108"/>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108"/>
-      <c r="AA4" s="108"/>
-      <c r="AB4" s="108"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106"/>
+      <c r="W4" s="106"/>
+      <c r="X4" s="106"/>
+      <c r="Y4" s="106"/>
+      <c r="Z4" s="106"/>
+      <c r="AA4" s="106"/>
+      <c r="AB4" s="106"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="119"/>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
+      <c r="AD4" s="120"/>
+      <c r="AE4" s="120"/>
+      <c r="AF4" s="120"/>
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120"/>
+      <c r="AL4" s="120"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="120"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2343,89 +2349,89 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108"/>
-      <c r="AA5" s="108"/>
-      <c r="AB5" s="108"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="106"/>
+      <c r="T5" s="106"/>
+      <c r="U5" s="106"/>
+      <c r="V5" s="106"/>
+      <c r="W5" s="106"/>
+      <c r="X5" s="106"/>
+      <c r="Y5" s="106"/>
+      <c r="Z5" s="106"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="106"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="119"/>
-      <c r="AE5" s="119"/>
-      <c r="AF5" s="119"/>
-      <c r="AG5" s="119"/>
-      <c r="AH5" s="119"/>
-      <c r="AI5" s="119"/>
-      <c r="AJ5" s="119"/>
-      <c r="AK5" s="119"/>
-      <c r="AL5" s="119"/>
-      <c r="AM5" s="119"/>
-      <c r="AN5" s="119"/>
+      <c r="AD5" s="120"/>
+      <c r="AE5" s="120"/>
+      <c r="AF5" s="120"/>
+      <c r="AG5" s="120"/>
+      <c r="AH5" s="120"/>
+      <c r="AI5" s="120"/>
+      <c r="AJ5" s="120"/>
+      <c r="AK5" s="120"/>
+      <c r="AL5" s="120"/>
+      <c r="AM5" s="120"/>
+      <c r="AN5" s="120"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="89"/>
-      <c r="C6" s="90"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
       <c r="D6" s="59"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="90"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="76"/>
       <c r="H6" s="59"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="90"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="76"/>
       <c r="L6" s="59"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="70"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="87"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="70"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="87"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="70"/>
+      <c r="V6" s="86"/>
+      <c r="W6" s="87"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="69"/>
-      <c r="AA6" s="70"/>
+      <c r="Z6" s="86"/>
+      <c r="AA6" s="87"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="69"/>
-      <c r="AE6" s="70"/>
+      <c r="AD6" s="86"/>
+      <c r="AE6" s="87"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="70"/>
+      <c r="AH6" s="86"/>
+      <c r="AI6" s="87"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="69"/>
-      <c r="AM6" s="70"/>
+      <c r="AL6" s="86"/>
+      <c r="AM6" s="87"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2437,44 +2443,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="93"/>
-      <c r="C7" s="94"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="60"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="94"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="67"/>
       <c r="H7" s="60"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="94"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="67"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="75"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="92"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="75"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="92"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="75"/>
+      <c r="V7" s="91"/>
+      <c r="W7" s="92"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="75"/>
+      <c r="Z7" s="91"/>
+      <c r="AA7" s="92"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="75"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="92"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="74"/>
-      <c r="AI7" s="75"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="92"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="74"/>
-      <c r="AM7" s="75"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="92"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2486,45 +2492,45 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="79"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="71"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="78"/>
-      <c r="L8" s="79"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="79"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="71"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="78"/>
-      <c r="T8" s="79"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="70"/>
+      <c r="T8" s="71"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="77"/>
-      <c r="W8" s="78"/>
-      <c r="X8" s="79"/>
+      <c r="V8" s="69"/>
+      <c r="W8" s="70"/>
+      <c r="X8" s="71"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="77"/>
-      <c r="AA8" s="78"/>
-      <c r="AB8" s="79"/>
+      <c r="Z8" s="69"/>
+      <c r="AA8" s="70"/>
+      <c r="AB8" s="71"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="77"/>
-      <c r="AE8" s="78"/>
-      <c r="AF8" s="79"/>
+      <c r="AD8" s="69"/>
+      <c r="AE8" s="70"/>
+      <c r="AF8" s="71"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="77"/>
-      <c r="AI8" s="78"/>
-      <c r="AJ8" s="79"/>
+      <c r="AH8" s="69"/>
+      <c r="AI8" s="70"/>
+      <c r="AJ8" s="71"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="77"/>
-      <c r="AM8" s="78"/>
-      <c r="AN8" s="79"/>
+      <c r="AL8" s="69"/>
+      <c r="AM8" s="70"/>
+      <c r="AN8" s="71"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2535,45 +2541,45 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="63"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="65"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="79"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="65"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="65"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="79"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="65"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="79"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="65"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="79"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="65"/>
+      <c r="V9" s="77"/>
+      <c r="W9" s="78"/>
+      <c r="X9" s="79"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="65"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="79"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="64"/>
-      <c r="AF9" s="65"/>
+      <c r="AD9" s="77"/>
+      <c r="AE9" s="78"/>
+      <c r="AF9" s="79"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="63"/>
-      <c r="AI9" s="64"/>
-      <c r="AJ9" s="65"/>
+      <c r="AH9" s="77"/>
+      <c r="AI9" s="78"/>
+      <c r="AJ9" s="79"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="63"/>
-      <c r="AM9" s="64"/>
-      <c r="AN9" s="65"/>
+      <c r="AL9" s="77"/>
+      <c r="AM9" s="78"/>
+      <c r="AN9" s="79"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2584,45 +2590,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="101"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="103"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="109"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="103"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="109"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="101"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="103"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="109"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="103"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="109"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="101"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="103"/>
+      <c r="R10" s="107"/>
+      <c r="S10" s="108"/>
+      <c r="T10" s="109"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="101"/>
-      <c r="W10" s="102"/>
-      <c r="X10" s="103"/>
+      <c r="V10" s="107"/>
+      <c r="W10" s="108"/>
+      <c r="X10" s="109"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="101"/>
-      <c r="AA10" s="102"/>
-      <c r="AB10" s="103"/>
+      <c r="Z10" s="107"/>
+      <c r="AA10" s="108"/>
+      <c r="AB10" s="109"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="101"/>
-      <c r="AE10" s="102"/>
-      <c r="AF10" s="103"/>
+      <c r="AD10" s="107"/>
+      <c r="AE10" s="108"/>
+      <c r="AF10" s="109"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="101"/>
-      <c r="AI10" s="102"/>
-      <c r="AJ10" s="103"/>
+      <c r="AH10" s="107"/>
+      <c r="AI10" s="108"/>
+      <c r="AJ10" s="109"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="101"/>
-      <c r="AM10" s="102"/>
-      <c r="AN10" s="103"/>
+      <c r="AL10" s="107"/>
+      <c r="AM10" s="108"/>
+      <c r="AN10" s="109"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2682,94 +2688,94 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="89"/>
-      <c r="C12" s="90"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="59"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="90"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="76"/>
       <c r="H12" s="59"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="90"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="76"/>
       <c r="L12" s="59"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="70"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="87"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="70"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="87"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="70"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="87"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="69"/>
-      <c r="AA12" s="70"/>
+      <c r="Z12" s="86"/>
+      <c r="AA12" s="87"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="69"/>
-      <c r="AE12" s="70"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="87"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="70"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="87"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="69"/>
-      <c r="AM12" s="70"/>
+      <c r="AL12" s="86"/>
+      <c r="AM12" s="87"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
       </c>
       <c r="AQ12" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="60"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="65"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="82"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="65"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="73"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="90"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="73"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="90"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="72"/>
-      <c r="X13" s="73"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="89"/>
+      <c r="X13" s="90"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="75"/>
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="92"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="75"/>
+      <c r="AD13" s="91"/>
+      <c r="AE13" s="92"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="71"/>
-      <c r="AI13" s="72"/>
-      <c r="AJ13" s="73"/>
+      <c r="AH13" s="88"/>
+      <c r="AI13" s="89"/>
+      <c r="AJ13" s="90"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="72"/>
-      <c r="AN13" s="73"/>
+      <c r="AL13" s="88"/>
+      <c r="AM13" s="89"/>
+      <c r="AN13" s="90"/>
       <c r="AP13" s="61" t="s">
         <v>22</v>
       </c>
@@ -2782,45 +2788,45 @@
       </c>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="77"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="79"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="71"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="71"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="79"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="79"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="71"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="79"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="71"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="78"/>
-      <c r="AB14" s="79"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="71"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="77"/>
-      <c r="AE14" s="78"/>
-      <c r="AF14" s="79"/>
+      <c r="AD14" s="69"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="71"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="77"/>
-      <c r="AI14" s="78"/>
-      <c r="AJ14" s="79"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="70"/>
+      <c r="AJ14" s="71"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="77"/>
-      <c r="AM14" s="78"/>
-      <c r="AN14" s="79"/>
+      <c r="AL14" s="69"/>
+      <c r="AM14" s="70"/>
+      <c r="AN14" s="71"/>
       <c r="AP14" s="61" t="s">
         <v>23</v>
       </c>
@@ -2833,45 +2839,45 @@
       </c>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="63"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="65"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="65"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="79"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="65"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="79"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="63"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="65"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="79"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="63"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="65"/>
+      <c r="V15" s="77"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="79"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="64"/>
-      <c r="AB15" s="65"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="79"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="63"/>
-      <c r="AE15" s="64"/>
-      <c r="AF15" s="65"/>
+      <c r="AD15" s="77"/>
+      <c r="AE15" s="78"/>
+      <c r="AF15" s="79"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="63"/>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="65"/>
+      <c r="AH15" s="77"/>
+      <c r="AI15" s="78"/>
+      <c r="AJ15" s="79"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="63"/>
-      <c r="AM15" s="64"/>
-      <c r="AN15" s="65"/>
+      <c r="AL15" s="77"/>
+      <c r="AM15" s="78"/>
+      <c r="AN15" s="79"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2882,51 +2888,51 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="101"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="103"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="109"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="103"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="109"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="103"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="109"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="101"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="103"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="103"/>
+      <c r="R16" s="107"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="109"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="101"/>
-      <c r="W16" s="102"/>
-      <c r="X16" s="103"/>
+      <c r="V16" s="107"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="109"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="101"/>
-      <c r="AA16" s="102"/>
-      <c r="AB16" s="103"/>
+      <c r="Z16" s="107"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="109"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="101"/>
-      <c r="AE16" s="102"/>
-      <c r="AF16" s="103"/>
+      <c r="AD16" s="107"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="109"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="101"/>
-      <c r="AI16" s="102"/>
-      <c r="AJ16" s="103"/>
+      <c r="AH16" s="107"/>
+      <c r="AI16" s="108"/>
+      <c r="AJ16" s="109"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="101"/>
-      <c r="AM16" s="102"/>
-      <c r="AN16" s="103"/>
+      <c r="AL16" s="107"/>
+      <c r="AM16" s="108"/>
+      <c r="AN16" s="109"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
       <c r="AQ16" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" s="30"/>
     </row>
@@ -2992,23 +2998,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="108" t="s">
+      <c r="N18" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="108"/>
-      <c r="P18" s="108"/>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="108"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="108"/>
-      <c r="V18" s="108"/>
-      <c r="W18" s="108"/>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="108"/>
-      <c r="Z18" s="108"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="108"/>
+      <c r="O18" s="106"/>
+      <c r="P18" s="106"/>
+      <c r="Q18" s="106"/>
+      <c r="R18" s="106"/>
+      <c r="S18" s="106"/>
+      <c r="T18" s="106"/>
+      <c r="U18" s="106"/>
+      <c r="V18" s="106"/>
+      <c r="W18" s="106"/>
+      <c r="X18" s="106"/>
+      <c r="Y18" s="106"/>
+      <c r="Z18" s="106"/>
+      <c r="AA18" s="106"/>
+      <c r="AB18" s="106"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3043,21 +3049,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="108"/>
-      <c r="U19" s="108"/>
-      <c r="V19" s="108"/>
-      <c r="W19" s="108"/>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="108"/>
-      <c r="Z19" s="108"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="108"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="106"/>
+      <c r="T19" s="106"/>
+      <c r="U19" s="106"/>
+      <c r="V19" s="106"/>
+      <c r="W19" s="106"/>
+      <c r="X19" s="106"/>
+      <c r="Y19" s="106"/>
+      <c r="Z19" s="106"/>
+      <c r="AA19" s="106"/>
+      <c r="AB19" s="106"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3080,44 +3086,44 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="89"/>
-      <c r="C20" s="90"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="59"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="90"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="76"/>
       <c r="H20" s="59"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="90"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="76"/>
       <c r="L20" s="59"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="70"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="87"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="106"/>
-      <c r="S20" s="107"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="126"/>
       <c r="T20" s="56"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="106"/>
-      <c r="W20" s="107"/>
+      <c r="V20" s="125"/>
+      <c r="W20" s="126"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="106"/>
-      <c r="AA20" s="107"/>
+      <c r="Z20" s="125"/>
+      <c r="AA20" s="126"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="69"/>
-      <c r="AE20" s="70"/>
+      <c r="AD20" s="86"/>
+      <c r="AE20" s="87"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="69"/>
-      <c r="AI20" s="70"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="87"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="69"/>
-      <c r="AM20" s="70"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="87"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3129,44 +3135,44 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="93"/>
-      <c r="C21" s="94"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="60"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="94"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="67"/>
       <c r="H21" s="60"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="94"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="67"/>
       <c r="L21" s="60"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="75"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="92"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="74"/>
-      <c r="S21" s="75"/>
+      <c r="R21" s="91"/>
+      <c r="S21" s="92"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="114"/>
+      <c r="V21" s="123"/>
+      <c r="W21" s="124"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="113"/>
-      <c r="AA21" s="114"/>
+      <c r="Z21" s="123"/>
+      <c r="AA21" s="124"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="74"/>
-      <c r="AE21" s="75"/>
+      <c r="AD21" s="91"/>
+      <c r="AE21" s="92"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="74"/>
-      <c r="AI21" s="75"/>
+      <c r="AH21" s="91"/>
+      <c r="AI21" s="92"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="74"/>
-      <c r="AM21" s="75"/>
+      <c r="AL21" s="91"/>
+      <c r="AM21" s="92"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3178,44 +3184,44 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="130"/>
-      <c r="C22" s="131"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="81"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="131"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="81"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="131"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="81"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="128"/>
-      <c r="O22" s="129"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="95"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="128"/>
-      <c r="S22" s="129"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="95"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="128"/>
-      <c r="W22" s="129"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="95"/>
       <c r="X22" s="58"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="128"/>
-      <c r="AA22" s="129"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="95"/>
       <c r="AB22" s="58"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="130"/>
-      <c r="AE22" s="131"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="81"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="130"/>
-      <c r="AI22" s="131"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="81"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="128"/>
-      <c r="AM22" s="129"/>
+      <c r="AL22" s="94"/>
+      <c r="AM22" s="95"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
@@ -3227,142 +3233,142 @@
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="109"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="97"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="110"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="97"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="110"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="97"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="109"/>
-      <c r="O23" s="110"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="97"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="109"/>
-      <c r="S23" s="110"/>
+      <c r="R23" s="96"/>
+      <c r="S23" s="97"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="109"/>
-      <c r="W23" s="110"/>
+      <c r="V23" s="96"/>
+      <c r="W23" s="97"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="109"/>
-      <c r="AA23" s="110"/>
+      <c r="Z23" s="96"/>
+      <c r="AA23" s="97"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="109"/>
-      <c r="AE23" s="110"/>
+      <c r="AD23" s="96"/>
+      <c r="AE23" s="97"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="109"/>
-      <c r="AI23" s="110"/>
+      <c r="AH23" s="96"/>
+      <c r="AI23" s="97"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="109"/>
-      <c r="AM23" s="110"/>
+      <c r="AL23" s="96"/>
+      <c r="AM23" s="97"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
       </c>
       <c r="AQ23" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="111"/>
-      <c r="C24" s="112"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="112"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="85"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="112"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="112"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="85"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="112"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="85"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="112"/>
+      <c r="V24" s="84"/>
+      <c r="W24" s="85"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="112"/>
+      <c r="Z24" s="84"/>
+      <c r="AA24" s="85"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="111"/>
-      <c r="AE24" s="112"/>
+      <c r="AD24" s="84"/>
+      <c r="AE24" s="85"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="111"/>
-      <c r="AI24" s="112"/>
+      <c r="AH24" s="84"/>
+      <c r="AI24" s="85"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="111"/>
-      <c r="AM24" s="112"/>
+      <c r="AL24" s="84"/>
+      <c r="AM24" s="85"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
       </c>
       <c r="AQ24" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="111"/>
-      <c r="C25" s="112"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="112"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="85"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="112"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="112"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="85"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="112"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="85"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="112"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="85"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="111"/>
-      <c r="AA25" s="112"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="85"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="111"/>
-      <c r="AE25" s="112"/>
+      <c r="AD25" s="84"/>
+      <c r="AE25" s="85"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="111"/>
-      <c r="AI25" s="112"/>
+      <c r="AH25" s="84"/>
+      <c r="AI25" s="85"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="111"/>
-      <c r="AM25" s="112"/>
+      <c r="AL25" s="84"/>
+      <c r="AM25" s="85"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="46" t="s">
         <v>21</v>
@@ -3374,93 +3380,93 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="111"/>
-      <c r="C26" s="112"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="112"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="85"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="112"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="112"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="85"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="112"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="85"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="111"/>
-      <c r="W26" s="112"/>
+      <c r="V26" s="84"/>
+      <c r="W26" s="85"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="111"/>
-      <c r="AA26" s="112"/>
+      <c r="Z26" s="84"/>
+      <c r="AA26" s="85"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="111"/>
-      <c r="AE26" s="112"/>
+      <c r="AD26" s="84"/>
+      <c r="AE26" s="85"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="111"/>
-      <c r="AI26" s="112"/>
+      <c r="AH26" s="84"/>
+      <c r="AI26" s="85"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="111"/>
-      <c r="AM26" s="112"/>
+      <c r="AL26" s="84"/>
+      <c r="AM26" s="85"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
       </c>
       <c r="AQ26" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="104"/>
-      <c r="C27" s="105"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="105"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="105"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="83"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="105"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="83"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="104"/>
-      <c r="S27" s="105"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="83"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="104"/>
-      <c r="W27" s="105"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="83"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="104"/>
-      <c r="AA27" s="105"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="83"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="104"/>
-      <c r="AE27" s="105"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="83"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="104"/>
-      <c r="AI27" s="105"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="83"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="104"/>
-      <c r="AM27" s="105"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="83"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3533,23 +3539,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="108" t="s">
+      <c r="N29" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="108"/>
-      <c r="U29" s="108"/>
-      <c r="V29" s="108"/>
-      <c r="W29" s="108"/>
-      <c r="X29" s="108"/>
-      <c r="Y29" s="108"/>
-      <c r="Z29" s="108"/>
-      <c r="AA29" s="108"/>
-      <c r="AB29" s="108"/>
+      <c r="O29" s="106"/>
+      <c r="P29" s="106"/>
+      <c r="Q29" s="106"/>
+      <c r="R29" s="106"/>
+      <c r="S29" s="106"/>
+      <c r="T29" s="106"/>
+      <c r="U29" s="106"/>
+      <c r="V29" s="106"/>
+      <c r="W29" s="106"/>
+      <c r="X29" s="106"/>
+      <c r="Y29" s="106"/>
+      <c r="Z29" s="106"/>
+      <c r="AA29" s="106"/>
+      <c r="AB29" s="106"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3584,21 +3590,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="108"/>
-      <c r="U30" s="108"/>
-      <c r="V30" s="108"/>
-      <c r="W30" s="108"/>
-      <c r="X30" s="108"/>
-      <c r="Y30" s="108"/>
-      <c r="Z30" s="108"/>
-      <c r="AA30" s="108"/>
-      <c r="AB30" s="108"/>
+      <c r="N30" s="106"/>
+      <c r="O30" s="106"/>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="106"/>
+      <c r="S30" s="106"/>
+      <c r="T30" s="106"/>
+      <c r="U30" s="106"/>
+      <c r="V30" s="106"/>
+      <c r="W30" s="106"/>
+      <c r="X30" s="106"/>
+      <c r="Y30" s="106"/>
+      <c r="Z30" s="106"/>
+      <c r="AA30" s="106"/>
+      <c r="AB30" s="106"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3621,248 +3627,248 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="90"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="59"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="89" t="s">
+      <c r="F31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="90"/>
+      <c r="G31" s="76"/>
       <c r="H31" s="59"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="89" t="s">
+      <c r="J31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="90"/>
+      <c r="K31" s="76"/>
       <c r="L31" s="59"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="69" t="s">
+      <c r="N31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="70"/>
+      <c r="O31" s="87"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="69" t="s">
+      <c r="R31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="70"/>
+      <c r="S31" s="87"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="69" t="s">
+      <c r="V31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="70"/>
+      <c r="W31" s="87"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="69" t="s">
+      <c r="Z31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="70"/>
+      <c r="AA31" s="87"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="69"/>
-      <c r="AE31" s="70"/>
-      <c r="AF31" s="34"/>
+      <c r="AD31" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE31" s="105"/>
+      <c r="AF31" s="62"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="96" t="s">
+      <c r="AH31" s="86"/>
+      <c r="AI31" s="87"/>
+      <c r="AJ31" s="34"/>
+      <c r="AK31" s="36"/>
+      <c r="AL31" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="AI31" s="97"/>
-      <c r="AJ31" s="62"/>
-      <c r="AK31" s="36"/>
-      <c r="AL31" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM31" s="70"/>
+      <c r="AM31" s="87"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="82"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="65"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="80" t="s">
+      <c r="F32" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="82"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="65"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="80" t="s">
+      <c r="J32" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="81"/>
-      <c r="L32" s="82"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="65"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="71" t="s">
+      <c r="N32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O32" s="72"/>
-      <c r="P32" s="73"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="90"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="71" t="s">
+      <c r="R32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S32" s="72"/>
-      <c r="T32" s="73"/>
+      <c r="S32" s="89"/>
+      <c r="T32" s="90"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="71" t="s">
+      <c r="V32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="72"/>
-      <c r="X32" s="73"/>
+      <c r="W32" s="89"/>
+      <c r="X32" s="90"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="71" t="s">
+      <c r="Z32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA32" s="72"/>
-      <c r="AB32" s="73"/>
+      <c r="AA32" s="89"/>
+      <c r="AB32" s="90"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="71"/>
-      <c r="AE32" s="72"/>
-      <c r="AF32" s="73"/>
+      <c r="AD32" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE32" s="99"/>
+      <c r="AF32" s="100"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="83" t="s">
+      <c r="AH32" s="88"/>
+      <c r="AI32" s="89"/>
+      <c r="AJ32" s="90"/>
+      <c r="AK32" s="36"/>
+      <c r="AL32" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="AI32" s="84"/>
-      <c r="AJ32" s="85"/>
-      <c r="AK32" s="36"/>
-      <c r="AL32" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM32" s="72"/>
-      <c r="AN32" s="73"/>
+      <c r="AM32" s="89"/>
+      <c r="AN32" s="90"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="93" t="s">
+      <c r="B33" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="68"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="93" t="s">
+      <c r="F33" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="95"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="68"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="93" t="s">
+      <c r="J33" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="94"/>
-      <c r="L33" s="95"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="68"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="74" t="s">
+      <c r="N33" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="75"/>
-      <c r="P33" s="76"/>
+      <c r="O33" s="92"/>
+      <c r="P33" s="93"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="74" t="s">
+      <c r="R33" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="75"/>
-      <c r="T33" s="76"/>
+      <c r="S33" s="92"/>
+      <c r="T33" s="93"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="74" t="s">
+      <c r="V33" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="W33" s="75"/>
-      <c r="X33" s="76"/>
+      <c r="W33" s="92"/>
+      <c r="X33" s="93"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="74" t="s">
+      <c r="Z33" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="AA33" s="75"/>
-      <c r="AB33" s="76"/>
+      <c r="AA33" s="92"/>
+      <c r="AB33" s="93"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="74"/>
-      <c r="AE33" s="75"/>
-      <c r="AF33" s="76"/>
+      <c r="AD33" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE33" s="102"/>
+      <c r="AF33" s="103"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI33" s="87"/>
-      <c r="AJ33" s="88"/>
+      <c r="AH33" s="91"/>
+      <c r="AI33" s="92"/>
+      <c r="AJ33" s="93"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM33" s="75"/>
-      <c r="AN33" s="76"/>
+      <c r="AL33" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM33" s="92"/>
+      <c r="AN33" s="93"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="79"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="71"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="77" t="s">
+      <c r="F34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="78"/>
-      <c r="H34" s="79"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="71"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="77" t="s">
+      <c r="J34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="K34" s="78"/>
-      <c r="L34" s="79"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="71"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="77" t="s">
+      <c r="N34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="O34" s="78"/>
-      <c r="P34" s="79"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="71"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="77" t="s">
+      <c r="R34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="S34" s="78"/>
-      <c r="T34" s="79"/>
+      <c r="S34" s="70"/>
+      <c r="T34" s="71"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="77" t="s">
+      <c r="V34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="78"/>
-      <c r="X34" s="79"/>
+      <c r="W34" s="70"/>
+      <c r="X34" s="71"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="77" t="s">
+      <c r="Z34" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="78"/>
-      <c r="AB34" s="79"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="71"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="77"/>
-      <c r="AE34" s="78"/>
-      <c r="AF34" s="79"/>
+      <c r="AD34" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE34" s="70"/>
+      <c r="AF34" s="71"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="77" t="s">
+      <c r="AH34" s="69"/>
+      <c r="AI34" s="70"/>
+      <c r="AJ34" s="71"/>
+      <c r="AK34" s="35"/>
+      <c r="AL34" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="AI34" s="78"/>
-      <c r="AJ34" s="79"/>
-      <c r="AK34" s="35"/>
-      <c r="AL34" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="AM34" s="78"/>
-      <c r="AN34" s="79"/>
+      <c r="AM34" s="70"/>
+      <c r="AN34" s="71"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -3870,63 +3876,63 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="67"/>
-      <c r="D35" s="68"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="74"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="67"/>
-      <c r="H35" s="68"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="66" t="s">
+      <c r="J35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="K35" s="67"/>
-      <c r="L35" s="68"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="74"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="66" t="s">
+      <c r="N35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="O35" s="67"/>
-      <c r="P35" s="68"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="74"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="66" t="s">
+      <c r="R35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="S35" s="67"/>
-      <c r="T35" s="68"/>
+      <c r="S35" s="73"/>
+      <c r="T35" s="74"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="66" t="s">
+      <c r="V35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="67"/>
-      <c r="X35" s="68"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="74"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="66" t="s">
+      <c r="Z35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="68"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="74"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="63"/>
-      <c r="AE35" s="64"/>
-      <c r="AF35" s="65"/>
+      <c r="AD35" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE35" s="78"/>
+      <c r="AF35" s="79"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="63" t="s">
+      <c r="AH35" s="77"/>
+      <c r="AI35" s="78"/>
+      <c r="AJ35" s="79"/>
+      <c r="AK35" s="44"/>
+      <c r="AL35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AI35" s="64"/>
-      <c r="AJ35" s="65"/>
-      <c r="AK35" s="44"/>
-      <c r="AL35" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM35" s="64"/>
-      <c r="AN35" s="65"/>
+      <c r="AM35" s="78"/>
+      <c r="AN35" s="79"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
@@ -3961,21 +3967,19 @@
       <c r="AA36" s="35"/>
       <c r="AB36" s="35"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="66"/>
-      <c r="AE36" s="67"/>
-      <c r="AF36" s="68"/>
+      <c r="AD36" s="72"/>
+      <c r="AE36" s="73"/>
+      <c r="AF36" s="74"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="66" t="s">
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="73"/>
+      <c r="AJ36" s="74"/>
+      <c r="AK36" s="35"/>
+      <c r="AL36" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="AI36" s="67"/>
-      <c r="AJ36" s="68"/>
-      <c r="AK36" s="35"/>
-      <c r="AL36" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM36" s="67"/>
-      <c r="AN36" s="68"/>
+      <c r="AM36" s="73"/>
+      <c r="AN36" s="74"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -3983,46 +3987,46 @@
     </row>
     <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
-      <c r="B37" s="89" t="s">
+      <c r="B37" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="90"/>
+      <c r="C37" s="76"/>
       <c r="D37" s="59"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="89" t="s">
+      <c r="F37" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="G37" s="90"/>
+      <c r="G37" s="76"/>
       <c r="H37" s="59"/>
       <c r="I37" s="50"/>
-      <c r="J37" s="89" t="s">
+      <c r="J37" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="K37" s="90"/>
+      <c r="K37" s="76"/>
       <c r="L37" s="59"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="69" t="s">
+      <c r="N37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O37" s="70"/>
+      <c r="O37" s="87"/>
       <c r="P37" s="34"/>
       <c r="Q37" s="36"/>
-      <c r="R37" s="69" t="s">
+      <c r="R37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S37" s="70"/>
+      <c r="S37" s="87"/>
       <c r="T37" s="34"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="69" t="s">
+      <c r="V37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W37" s="70"/>
+      <c r="W37" s="87"/>
       <c r="X37" s="34"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="69" t="s">
+      <c r="Z37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA37" s="70"/>
+      <c r="AA37" s="87"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="36"/>
       <c r="AD37" s="35"/>
@@ -4043,62 +4047,62 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="82"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="80" t="s">
+      <c r="F38" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="G38" s="81"/>
-      <c r="H38" s="82"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="65"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="80" t="s">
+      <c r="J38" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="81"/>
-      <c r="L38" s="82"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="65"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="71" t="s">
+      <c r="N38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O38" s="72"/>
-      <c r="P38" s="73"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="90"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="71" t="s">
+      <c r="R38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S38" s="72"/>
-      <c r="T38" s="73"/>
+      <c r="S38" s="89"/>
+      <c r="T38" s="90"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="71" t="s">
+      <c r="V38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W38" s="72"/>
-      <c r="X38" s="73"/>
+      <c r="W38" s="89"/>
+      <c r="X38" s="90"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="71" t="s">
+      <c r="Z38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA38" s="72"/>
-      <c r="AB38" s="73"/>
+      <c r="AA38" s="89"/>
+      <c r="AB38" s="90"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="69"/>
-      <c r="AE38" s="70"/>
+      <c r="AD38" s="86"/>
+      <c r="AE38" s="87"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="96" t="s">
+      <c r="AH38" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="AI38" s="97"/>
+      <c r="AI38" s="105"/>
       <c r="AJ38" s="62"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="69" t="s">
+      <c r="AL38" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="AM38" s="70"/>
+      <c r="AM38" s="87"/>
       <c r="AN38" s="34"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
@@ -4107,63 +4111,63 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="93" t="s">
+      <c r="B39" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="95"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="68"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="93" t="s">
+      <c r="F39" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="94"/>
-      <c r="H39" s="95"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="68"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="93" t="s">
+      <c r="J39" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="K39" s="94"/>
-      <c r="L39" s="95"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="68"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="74" t="s">
+      <c r="N39" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="O39" s="75"/>
-      <c r="P39" s="76"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="93"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="74" t="s">
+      <c r="R39" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="S39" s="75"/>
-      <c r="T39" s="76"/>
+      <c r="S39" s="92"/>
+      <c r="T39" s="93"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="74" t="s">
+      <c r="V39" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="W39" s="75"/>
-      <c r="X39" s="76"/>
+      <c r="W39" s="92"/>
+      <c r="X39" s="93"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="74" t="s">
+      <c r="Z39" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="AA39" s="75"/>
-      <c r="AB39" s="76"/>
+      <c r="AA39" s="92"/>
+      <c r="AB39" s="93"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="71"/>
-      <c r="AE39" s="72"/>
-      <c r="AF39" s="73"/>
+      <c r="AD39" s="88"/>
+      <c r="AE39" s="89"/>
+      <c r="AF39" s="90"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="83" t="s">
+      <c r="AH39" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="AI39" s="84"/>
-      <c r="AJ39" s="85"/>
+      <c r="AI39" s="99"/>
+      <c r="AJ39" s="100"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="71" t="s">
+      <c r="AL39" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="AM39" s="72"/>
-      <c r="AN39" s="73"/>
+      <c r="AM39" s="89"/>
+      <c r="AN39" s="90"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4171,61 +4175,61 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="79"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="71"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="77" t="s">
+      <c r="F40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="78"/>
-      <c r="H40" s="79"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="71"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="77" t="s">
+      <c r="J40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="78"/>
-      <c r="L40" s="79"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="71"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="79"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="71"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="77" t="s">
+      <c r="R40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="S40" s="78"/>
-      <c r="T40" s="79"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="71"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="77" t="s">
+      <c r="V40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="78"/>
-      <c r="X40" s="79"/>
+      <c r="W40" s="70"/>
+      <c r="X40" s="71"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="77" t="s">
+      <c r="Z40" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="78"/>
-      <c r="AB40" s="79"/>
+      <c r="AA40" s="70"/>
+      <c r="AB40" s="71"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="74"/>
-      <c r="AE40" s="75"/>
-      <c r="AF40" s="76"/>
+      <c r="AD40" s="91"/>
+      <c r="AE40" s="92"/>
+      <c r="AF40" s="93"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="86" t="s">
+      <c r="AH40" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AI40" s="87"/>
-      <c r="AJ40" s="88"/>
+      <c r="AI40" s="102"/>
+      <c r="AJ40" s="103"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="74"/>
-      <c r="AM40" s="75"/>
-      <c r="AN40" s="76"/>
+      <c r="AL40" s="91"/>
+      <c r="AM40" s="92"/>
+      <c r="AN40" s="93"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4233,63 +4237,63 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="66" t="s">
+      <c r="B41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="67"/>
-      <c r="D41" s="68"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="74"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G41" s="67"/>
-      <c r="H41" s="68"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="74"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="66" t="s">
+      <c r="J41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="K41" s="67"/>
-      <c r="L41" s="68"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="74"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="66" t="s">
+      <c r="N41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="74"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="66" t="s">
+      <c r="R41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="67"/>
-      <c r="T41" s="68"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="74"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="66" t="s">
+      <c r="V41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="67"/>
-      <c r="X41" s="68"/>
+      <c r="W41" s="73"/>
+      <c r="X41" s="74"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="66" t="s">
+      <c r="Z41" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="68"/>
+      <c r="AA41" s="73"/>
+      <c r="AB41" s="74"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="77"/>
-      <c r="AE41" s="78"/>
-      <c r="AF41" s="79"/>
+      <c r="AD41" s="69"/>
+      <c r="AE41" s="70"/>
+      <c r="AF41" s="71"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="77" t="s">
+      <c r="AH41" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="AI41" s="78"/>
-      <c r="AJ41" s="79"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="71"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="77" t="s">
+      <c r="AL41" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="AM41" s="78"/>
-      <c r="AN41" s="79"/>
+      <c r="AM41" s="70"/>
+      <c r="AN41" s="71"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4325,21 +4329,21 @@
       <c r="AA42" s="35"/>
       <c r="AB42" s="35"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="63"/>
-      <c r="AE42" s="64"/>
-      <c r="AF42" s="65"/>
+      <c r="AD42" s="77"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="79"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="63" t="s">
+      <c r="AH42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="AI42" s="64"/>
-      <c r="AJ42" s="65"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="79"/>
       <c r="AK42" s="35"/>
-      <c r="AL42" s="63" t="s">
+      <c r="AL42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="AM42" s="64"/>
-      <c r="AN42" s="65"/>
+      <c r="AM42" s="78"/>
+      <c r="AN42" s="79"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4347,63 +4351,63 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="89" t="s">
+      <c r="B43" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="90"/>
+      <c r="C43" s="76"/>
       <c r="D43" s="59"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="89" t="s">
+      <c r="F43" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="G43" s="90"/>
+      <c r="G43" s="76"/>
       <c r="H43" s="59"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="89" t="s">
+      <c r="J43" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="K43" s="90"/>
+      <c r="K43" s="76"/>
       <c r="L43" s="59"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="69" t="s">
+      <c r="N43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O43" s="70"/>
+      <c r="O43" s="87"/>
       <c r="P43" s="34"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="69" t="s">
+      <c r="R43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S43" s="70"/>
+      <c r="S43" s="87"/>
       <c r="T43" s="34"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="69" t="s">
+      <c r="V43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W43" s="70"/>
+      <c r="W43" s="87"/>
       <c r="X43" s="34"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="69" t="s">
+      <c r="Z43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA43" s="70"/>
+      <c r="AA43" s="87"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="66"/>
-      <c r="AE43" s="67"/>
-      <c r="AF43" s="68"/>
+      <c r="AD43" s="72"/>
+      <c r="AE43" s="73"/>
+      <c r="AF43" s="74"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="66" t="s">
+      <c r="AH43" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="AI43" s="67"/>
-      <c r="AJ43" s="68"/>
+      <c r="AI43" s="73"/>
+      <c r="AJ43" s="74"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="66" t="s">
+      <c r="AL43" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="AM43" s="67"/>
-      <c r="AN43" s="68"/>
+      <c r="AM43" s="73"/>
+      <c r="AN43" s="74"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4411,47 +4415,47 @@
     </row>
     <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
-      <c r="B44" s="80" t="s">
+      <c r="B44" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="81"/>
-      <c r="D44" s="82"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
       <c r="E44" s="50"/>
-      <c r="F44" s="80" t="s">
+      <c r="F44" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="G44" s="81"/>
-      <c r="H44" s="82"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="65"/>
       <c r="I44" s="50"/>
-      <c r="J44" s="80" t="s">
+      <c r="J44" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K44" s="81"/>
-      <c r="L44" s="82"/>
+      <c r="K44" s="64"/>
+      <c r="L44" s="65"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="71" t="s">
+      <c r="N44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O44" s="72"/>
-      <c r="P44" s="73"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="90"/>
       <c r="Q44" s="35"/>
-      <c r="R44" s="71" t="s">
+      <c r="R44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S44" s="72"/>
-      <c r="T44" s="73"/>
+      <c r="S44" s="89"/>
+      <c r="T44" s="90"/>
       <c r="U44" s="36"/>
-      <c r="V44" s="71" t="s">
+      <c r="V44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W44" s="72"/>
-      <c r="X44" s="73"/>
+      <c r="W44" s="89"/>
+      <c r="X44" s="90"/>
       <c r="Y44" s="36"/>
-      <c r="Z44" s="71" t="s">
+      <c r="Z44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA44" s="72"/>
-      <c r="AB44" s="73"/>
+      <c r="AA44" s="89"/>
+      <c r="AB44" s="90"/>
       <c r="AC44" s="36"/>
       <c r="AD44" s="35"/>
       <c r="AE44" s="35"/>
@@ -4471,62 +4475,62 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="93" t="s">
+      <c r="B45" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="95"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="68"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="93" t="s">
+      <c r="F45" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="94"/>
-      <c r="H45" s="95"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="68"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="93" t="s">
+      <c r="J45" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="K45" s="94"/>
-      <c r="L45" s="95"/>
+      <c r="K45" s="67"/>
+      <c r="L45" s="68"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="74" t="s">
+      <c r="N45" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="O45" s="75"/>
-      <c r="P45" s="76"/>
+      <c r="O45" s="92"/>
+      <c r="P45" s="93"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="74" t="s">
+      <c r="R45" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="S45" s="75"/>
-      <c r="T45" s="76"/>
+      <c r="S45" s="92"/>
+      <c r="T45" s="93"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="74" t="s">
+      <c r="V45" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="W45" s="75"/>
-      <c r="X45" s="76"/>
+      <c r="W45" s="92"/>
+      <c r="X45" s="93"/>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="74" t="s">
+      <c r="Z45" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="AA45" s="75"/>
-      <c r="AB45" s="76"/>
+      <c r="AA45" s="92"/>
+      <c r="AB45" s="93"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="69"/>
-      <c r="AE45" s="70"/>
+      <c r="AD45" s="86"/>
+      <c r="AE45" s="87"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="96" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI45" s="97"/>
+      <c r="AH45" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI45" s="105"/>
       <c r="AJ45" s="62"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="69" t="s">
+      <c r="AL45" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="AM45" s="70"/>
+      <c r="AM45" s="87"/>
       <c r="AN45" s="34" t="s">
         <v>43</v>
       </c>
@@ -4537,63 +4541,63 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="65"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="79"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="63" t="s">
+      <c r="F46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="G46" s="64"/>
-      <c r="H46" s="65"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="79"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="63" t="s">
+      <c r="J46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="64"/>
-      <c r="L46" s="65"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="79"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="63" t="s">
+      <c r="N46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="O46" s="64"/>
-      <c r="P46" s="65"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="79"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="63" t="s">
+      <c r="R46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="S46" s="64"/>
-      <c r="T46" s="65"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="79"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="63" t="s">
+      <c r="V46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="64"/>
-      <c r="X46" s="65"/>
+      <c r="W46" s="78"/>
+      <c r="X46" s="79"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="63" t="s">
+      <c r="Z46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="64"/>
-      <c r="AB46" s="65"/>
+      <c r="AA46" s="78"/>
+      <c r="AB46" s="79"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="71"/>
-      <c r="AE46" s="72"/>
-      <c r="AF46" s="73"/>
+      <c r="AD46" s="88"/>
+      <c r="AE46" s="89"/>
+      <c r="AF46" s="90"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI46" s="84"/>
-      <c r="AJ46" s="85"/>
+      <c r="AH46" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI46" s="99"/>
+      <c r="AJ46" s="100"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="71" t="s">
+      <c r="AL46" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="AM46" s="72"/>
-      <c r="AN46" s="73"/>
+      <c r="AM46" s="89"/>
+      <c r="AN46" s="90"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4601,59 +4605,59 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="79"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="63" t="s">
+      <c r="F47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="64"/>
-      <c r="H47" s="65"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="63" t="s">
+      <c r="J47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="64"/>
-      <c r="L47" s="65"/>
+      <c r="K47" s="78"/>
+      <c r="L47" s="79"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="63" t="s">
+      <c r="N47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="O47" s="64"/>
-      <c r="P47" s="65"/>
+      <c r="O47" s="78"/>
+      <c r="P47" s="79"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="63" t="s">
+      <c r="R47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="S47" s="64"/>
-      <c r="T47" s="65"/>
+      <c r="S47" s="78"/>
+      <c r="T47" s="79"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="63" t="s">
+      <c r="V47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="64"/>
-      <c r="X47" s="65"/>
+      <c r="W47" s="78"/>
+      <c r="X47" s="79"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="63" t="s">
+      <c r="Z47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="64"/>
-      <c r="AB47" s="65"/>
+      <c r="AA47" s="78"/>
+      <c r="AB47" s="79"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="74"/>
-      <c r="AE47" s="75"/>
-      <c r="AF47" s="76"/>
+      <c r="AD47" s="91"/>
+      <c r="AE47" s="92"/>
+      <c r="AF47" s="93"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="86"/>
-      <c r="AI47" s="87"/>
-      <c r="AJ47" s="88"/>
+      <c r="AH47" s="101"/>
+      <c r="AI47" s="102"/>
+      <c r="AJ47" s="103"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="74"/>
-      <c r="AM47" s="75"/>
-      <c r="AN47" s="76"/>
+      <c r="AL47" s="91"/>
+      <c r="AM47" s="92"/>
+      <c r="AN47" s="93"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4661,126 +4665,126 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="63" t="s">
+      <c r="F48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="64"/>
-      <c r="H48" s="65"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="79"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="63" t="s">
+      <c r="J48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K48" s="64"/>
-      <c r="L48" s="65"/>
+      <c r="K48" s="78"/>
+      <c r="L48" s="79"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="63" t="s">
+      <c r="N48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="64"/>
-      <c r="P48" s="65"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="79"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="63" t="s">
+      <c r="R48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="S48" s="64"/>
-      <c r="T48" s="65"/>
+      <c r="S48" s="78"/>
+      <c r="T48" s="79"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="63" t="s">
+      <c r="V48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="64"/>
-      <c r="X48" s="65"/>
+      <c r="W48" s="78"/>
+      <c r="X48" s="79"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="63" t="s">
+      <c r="Z48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="64"/>
-      <c r="AB48" s="65"/>
+      <c r="AA48" s="78"/>
+      <c r="AB48" s="79"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="63"/>
-      <c r="AE48" s="64"/>
-      <c r="AF48" s="65"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="78"/>
+      <c r="AF48" s="79"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="77" t="s">
+      <c r="AH48" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="AI48" s="78"/>
-      <c r="AJ48" s="79"/>
+      <c r="AI48" s="70"/>
+      <c r="AJ48" s="71"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="77" t="s">
+      <c r="AL48" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="AM48" s="78"/>
-      <c r="AN48" s="79"/>
+      <c r="AM48" s="70"/>
+      <c r="AN48" s="71"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="66" t="s">
+      <c r="B49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="67"/>
-      <c r="D49" s="68"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="74"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="66" t="s">
+      <c r="F49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="67"/>
-      <c r="H49" s="68"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="74"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="66" t="s">
+      <c r="J49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="67"/>
-      <c r="L49" s="68"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="66" t="s">
+      <c r="N49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="74"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="66" t="s">
+      <c r="R49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="S49" s="67"/>
-      <c r="T49" s="68"/>
+      <c r="S49" s="73"/>
+      <c r="T49" s="74"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="66" t="s">
+      <c r="V49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="67"/>
-      <c r="X49" s="68"/>
+      <c r="W49" s="73"/>
+      <c r="X49" s="74"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="66" t="s">
+      <c r="Z49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
+      <c r="AA49" s="73"/>
+      <c r="AB49" s="74"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="63"/>
-      <c r="AE49" s="64"/>
-      <c r="AF49" s="65"/>
+      <c r="AD49" s="77"/>
+      <c r="AE49" s="78"/>
+      <c r="AF49" s="79"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="63" t="s">
+      <c r="AH49" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="AI49" s="64"/>
-      <c r="AJ49" s="65"/>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="79"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="63" t="s">
+      <c r="AL49" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="AM49" s="64"/>
-      <c r="AN49" s="65"/>
+      <c r="AM49" s="78"/>
+      <c r="AN49" s="79"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
@@ -4815,63 +4819,63 @@
       <c r="AA50" s="35"/>
       <c r="AB50" s="35"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="66"/>
-      <c r="AE50" s="67"/>
-      <c r="AF50" s="68"/>
+      <c r="AD50" s="72"/>
+      <c r="AE50" s="73"/>
+      <c r="AF50" s="74"/>
       <c r="AG50" s="35"/>
-      <c r="AH50" s="66"/>
-      <c r="AI50" s="67"/>
-      <c r="AJ50" s="68"/>
+      <c r="AH50" s="72"/>
+      <c r="AI50" s="73"/>
+      <c r="AJ50" s="74"/>
       <c r="AK50" s="35"/>
-      <c r="AL50" s="66"/>
-      <c r="AM50" s="67"/>
-      <c r="AN50" s="68"/>
+      <c r="AL50" s="72"/>
+      <c r="AM50" s="73"/>
+      <c r="AN50" s="74"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
     <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="89" t="s">
+      <c r="B51" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="90"/>
+      <c r="C51" s="76"/>
       <c r="D51" s="59"/>
       <c r="E51" s="50"/>
-      <c r="F51" s="89" t="s">
+      <c r="F51" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="90"/>
+      <c r="G51" s="76"/>
       <c r="H51" s="59"/>
       <c r="I51" s="50"/>
-      <c r="J51" s="89" t="s">
+      <c r="J51" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="K51" s="90"/>
+      <c r="K51" s="76"/>
       <c r="L51" s="59"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="69" t="s">
+      <c r="N51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O51" s="70"/>
+      <c r="O51" s="87"/>
       <c r="P51" s="34"/>
       <c r="Q51" s="40"/>
-      <c r="R51" s="69" t="s">
+      <c r="R51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S51" s="70"/>
+      <c r="S51" s="87"/>
       <c r="T51" s="34"/>
       <c r="U51" s="40"/>
-      <c r="V51" s="69" t="s">
+      <c r="V51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W51" s="70"/>
+      <c r="W51" s="87"/>
       <c r="X51" s="34"/>
       <c r="Y51" s="32"/>
-      <c r="Z51" s="69" t="s">
+      <c r="Z51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA51" s="70"/>
+      <c r="AA51" s="87"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="40"/>
       <c r="AD51" s="35"/>
@@ -4891,283 +4895,283 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="80" t="s">
+      <c r="B52" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="82"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="80" t="s">
+      <c r="F52" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="81"/>
-      <c r="H52" s="82"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="65"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="80" t="s">
+      <c r="J52" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K52" s="81"/>
-      <c r="L52" s="82"/>
+      <c r="K52" s="64"/>
+      <c r="L52" s="65"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="71" t="s">
+      <c r="N52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="72"/>
-      <c r="P52" s="73"/>
+      <c r="O52" s="89"/>
+      <c r="P52" s="90"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="71" t="s">
+      <c r="R52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S52" s="72"/>
-      <c r="T52" s="73"/>
+      <c r="S52" s="89"/>
+      <c r="T52" s="90"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="71" t="s">
+      <c r="V52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W52" s="72"/>
-      <c r="X52" s="73"/>
+      <c r="W52" s="89"/>
+      <c r="X52" s="90"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="71" t="s">
+      <c r="Z52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA52" s="72"/>
-      <c r="AB52" s="73"/>
+      <c r="AA52" s="89"/>
+      <c r="AB52" s="90"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="69"/>
-      <c r="AE52" s="70"/>
+      <c r="AD52" s="86"/>
+      <c r="AE52" s="87"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="69"/>
-      <c r="AI52" s="70"/>
+      <c r="AH52" s="86"/>
+      <c r="AI52" s="87"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="69"/>
-      <c r="AM52" s="70"/>
+      <c r="AL52" s="86"/>
+      <c r="AM52" s="87"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="93" t="s">
+      <c r="B53" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="94"/>
-      <c r="D53" s="95"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="68"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="93" t="s">
+      <c r="F53" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="94"/>
-      <c r="H53" s="95"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="68"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="93" t="s">
+      <c r="J53" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="K53" s="94"/>
-      <c r="L53" s="95"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="68"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="74" t="s">
+      <c r="N53" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="O53" s="75"/>
-      <c r="P53" s="76"/>
+      <c r="O53" s="92"/>
+      <c r="P53" s="93"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="74" t="s">
+      <c r="R53" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="S53" s="75"/>
-      <c r="T53" s="76"/>
+      <c r="S53" s="92"/>
+      <c r="T53" s="93"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="74" t="s">
+      <c r="V53" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="W53" s="75"/>
-      <c r="X53" s="76"/>
+      <c r="W53" s="92"/>
+      <c r="X53" s="93"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="74" t="s">
+      <c r="Z53" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="AA53" s="75"/>
-      <c r="AB53" s="76"/>
+      <c r="AA53" s="92"/>
+      <c r="AB53" s="93"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="71"/>
-      <c r="AE53" s="72"/>
-      <c r="AF53" s="73"/>
+      <c r="AD53" s="88"/>
+      <c r="AE53" s="89"/>
+      <c r="AF53" s="90"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="71"/>
-      <c r="AI53" s="72"/>
-      <c r="AJ53" s="73"/>
+      <c r="AH53" s="88"/>
+      <c r="AI53" s="89"/>
+      <c r="AJ53" s="90"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="71"/>
-      <c r="AM53" s="72"/>
-      <c r="AN53" s="73"/>
+      <c r="AL53" s="88"/>
+      <c r="AM53" s="89"/>
+      <c r="AN53" s="90"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="77" t="s">
+      <c r="B54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="78"/>
-      <c r="D54" s="79"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="71"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="77" t="s">
+      <c r="F54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="G54" s="78"/>
-      <c r="H54" s="79"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="71"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="77" t="s">
+      <c r="J54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="78"/>
-      <c r="L54" s="79"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="71"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="77" t="s">
+      <c r="N54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="O54" s="78"/>
-      <c r="P54" s="79"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="77" t="s">
+      <c r="R54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="S54" s="78"/>
-      <c r="T54" s="79"/>
+      <c r="S54" s="70"/>
+      <c r="T54" s="71"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="77" t="s">
+      <c r="V54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="W54" s="78"/>
-      <c r="X54" s="79"/>
+      <c r="W54" s="70"/>
+      <c r="X54" s="71"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="77" t="s">
+      <c r="Z54" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="AA54" s="78"/>
-      <c r="AB54" s="79"/>
+      <c r="AA54" s="70"/>
+      <c r="AB54" s="71"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="74"/>
-      <c r="AE54" s="75"/>
-      <c r="AF54" s="76"/>
+      <c r="AD54" s="91"/>
+      <c r="AE54" s="92"/>
+      <c r="AF54" s="93"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="74"/>
-      <c r="AI54" s="75"/>
-      <c r="AJ54" s="76"/>
+      <c r="AH54" s="91"/>
+      <c r="AI54" s="92"/>
+      <c r="AJ54" s="93"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="74"/>
-      <c r="AM54" s="75"/>
-      <c r="AN54" s="76"/>
+      <c r="AL54" s="91"/>
+      <c r="AM54" s="92"/>
+      <c r="AN54" s="93"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="64"/>
-      <c r="D55" s="65"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="79"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="63" t="s">
+      <c r="F55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="64"/>
-      <c r="H55" s="65"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="79"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="63" t="s">
+      <c r="J55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="64"/>
-      <c r="L55" s="65"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="79"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="63" t="s">
+      <c r="N55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="O55" s="64"/>
-      <c r="P55" s="65"/>
+      <c r="O55" s="78"/>
+      <c r="P55" s="79"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="63" t="s">
+      <c r="R55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="64"/>
-      <c r="T55" s="65"/>
+      <c r="S55" s="78"/>
+      <c r="T55" s="79"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="63" t="s">
+      <c r="V55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="64"/>
-      <c r="X55" s="65"/>
+      <c r="W55" s="78"/>
+      <c r="X55" s="79"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="63" t="s">
+      <c r="Z55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AA55" s="64"/>
-      <c r="AB55" s="65"/>
+      <c r="AA55" s="78"/>
+      <c r="AB55" s="79"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="77"/>
-      <c r="AE55" s="78"/>
-      <c r="AF55" s="79"/>
+      <c r="AD55" s="69"/>
+      <c r="AE55" s="70"/>
+      <c r="AF55" s="71"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="77"/>
-      <c r="AI55" s="78"/>
-      <c r="AJ55" s="79"/>
+      <c r="AH55" s="69"/>
+      <c r="AI55" s="70"/>
+      <c r="AJ55" s="71"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="77"/>
-      <c r="AM55" s="78"/>
-      <c r="AN55" s="79"/>
+      <c r="AL55" s="69"/>
+      <c r="AM55" s="70"/>
+      <c r="AN55" s="71"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="66" t="s">
+      <c r="B56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="67"/>
-      <c r="D56" s="68"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="66" t="s">
+      <c r="F56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="67"/>
-      <c r="H56" s="68"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="74"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="66" t="s">
+      <c r="J56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="K56" s="67"/>
-      <c r="L56" s="68"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="74"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="66" t="s">
+      <c r="N56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="O56" s="67"/>
-      <c r="P56" s="68"/>
+      <c r="O56" s="73"/>
+      <c r="P56" s="74"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="66" t="s">
+      <c r="R56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="S56" s="67"/>
-      <c r="T56" s="68"/>
+      <c r="S56" s="73"/>
+      <c r="T56" s="74"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="66" t="s">
+      <c r="V56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="W56" s="67"/>
-      <c r="X56" s="68"/>
+      <c r="W56" s="73"/>
+      <c r="X56" s="74"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="66" t="s">
+      <c r="Z56" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AA56" s="67"/>
-      <c r="AB56" s="68"/>
+      <c r="AA56" s="73"/>
+      <c r="AB56" s="74"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="63"/>
-      <c r="AE56" s="64"/>
-      <c r="AF56" s="65"/>
+      <c r="AD56" s="77"/>
+      <c r="AE56" s="78"/>
+      <c r="AF56" s="79"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="63"/>
-      <c r="AI56" s="64"/>
-      <c r="AJ56" s="65"/>
+      <c r="AH56" s="77"/>
+      <c r="AI56" s="78"/>
+      <c r="AJ56" s="79"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="63"/>
-      <c r="AM56" s="64"/>
-      <c r="AN56" s="65"/>
+      <c r="AL56" s="77"/>
+      <c r="AM56" s="78"/>
+      <c r="AN56" s="79"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5199,58 +5203,58 @@
       <c r="AA57" s="35"/>
       <c r="AB57" s="35"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="66"/>
-      <c r="AE57" s="67"/>
-      <c r="AF57" s="68"/>
+      <c r="AD57" s="72"/>
+      <c r="AE57" s="73"/>
+      <c r="AF57" s="74"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="66"/>
-      <c r="AI57" s="67"/>
-      <c r="AJ57" s="68"/>
+      <c r="AH57" s="72"/>
+      <c r="AI57" s="73"/>
+      <c r="AJ57" s="74"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="66"/>
-      <c r="AM57" s="67"/>
-      <c r="AN57" s="68"/>
+      <c r="AL57" s="72"/>
+      <c r="AM57" s="73"/>
+      <c r="AN57" s="74"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="91" t="s">
+      <c r="B58" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="92"/>
+      <c r="C58" s="128"/>
       <c r="D58" s="55"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="89"/>
-      <c r="G58" s="90"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="76"/>
       <c r="H58" s="59"/>
       <c r="I58" s="50"/>
-      <c r="J58" s="89" t="s">
+      <c r="J58" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="K58" s="90"/>
+      <c r="K58" s="76"/>
       <c r="L58" s="59"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="69" t="s">
+      <c r="N58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O58" s="70"/>
+      <c r="O58" s="87"/>
       <c r="P58" s="34"/>
       <c r="Q58" s="31"/>
-      <c r="R58" s="69" t="s">
+      <c r="R58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S58" s="70"/>
+      <c r="S58" s="87"/>
       <c r="T58" s="34"/>
       <c r="U58" s="50"/>
-      <c r="V58" s="69" t="s">
+      <c r="V58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W58" s="70"/>
+      <c r="W58" s="87"/>
       <c r="X58" s="34"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="69" t="s">
+      <c r="Z58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA58" s="70"/>
+      <c r="AA58" s="87"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
       <c r="AD58" s="35"/>
@@ -5267,303 +5271,303 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="81"/>
-      <c r="D59" s="82"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="65"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="82"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="65"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="80" t="s">
+      <c r="J59" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="K59" s="81"/>
-      <c r="L59" s="82"/>
+      <c r="K59" s="64"/>
+      <c r="L59" s="65"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="71" t="s">
+      <c r="N59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="72"/>
-      <c r="P59" s="73"/>
+      <c r="O59" s="89"/>
+      <c r="P59" s="90"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="71" t="s">
+      <c r="R59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S59" s="72"/>
-      <c r="T59" s="73"/>
+      <c r="S59" s="89"/>
+      <c r="T59" s="90"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="71" t="s">
+      <c r="V59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W59" s="72"/>
-      <c r="X59" s="73"/>
+      <c r="W59" s="89"/>
+      <c r="X59" s="90"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="71" t="s">
+      <c r="Z59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA59" s="72"/>
-      <c r="AB59" s="73"/>
+      <c r="AA59" s="89"/>
+      <c r="AB59" s="90"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="69"/>
-      <c r="AE59" s="70"/>
+      <c r="AD59" s="86"/>
+      <c r="AE59" s="87"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="69"/>
-      <c r="AI59" s="70"/>
+      <c r="AH59" s="86"/>
+      <c r="AI59" s="87"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="69"/>
-      <c r="AM59" s="70"/>
+      <c r="AL59" s="86"/>
+      <c r="AM59" s="87"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="94"/>
-      <c r="D60" s="95"/>
+      <c r="C60" s="67"/>
+      <c r="D60" s="68"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="93"/>
-      <c r="G60" s="94"/>
-      <c r="H60" s="95"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="68"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="K60" s="94"/>
-      <c r="L60" s="95"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="68"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="74" t="s">
+      <c r="N60" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="O60" s="75"/>
-      <c r="P60" s="76"/>
+      <c r="O60" s="92"/>
+      <c r="P60" s="93"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="74" t="s">
+      <c r="R60" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="S60" s="75"/>
-      <c r="T60" s="76"/>
+      <c r="S60" s="92"/>
+      <c r="T60" s="93"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="74" t="s">
+      <c r="V60" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="W60" s="75"/>
-      <c r="X60" s="76"/>
+      <c r="W60" s="92"/>
+      <c r="X60" s="93"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="74" t="s">
+      <c r="Z60" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="AA60" s="75"/>
-      <c r="AB60" s="76"/>
+      <c r="AA60" s="92"/>
+      <c r="AB60" s="93"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="71"/>
-      <c r="AE60" s="72"/>
-      <c r="AF60" s="73"/>
+      <c r="AD60" s="88"/>
+      <c r="AE60" s="89"/>
+      <c r="AF60" s="90"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="71"/>
-      <c r="AI60" s="72"/>
-      <c r="AJ60" s="73"/>
+      <c r="AH60" s="88"/>
+      <c r="AI60" s="89"/>
+      <c r="AJ60" s="90"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="71"/>
-      <c r="AM60" s="72"/>
-      <c r="AN60" s="73"/>
+      <c r="AL60" s="88"/>
+      <c r="AM60" s="89"/>
+      <c r="AN60" s="90"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="77" t="s">
+      <c r="B61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="78"/>
-      <c r="D61" s="79"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="71"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="79"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="71"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="77" t="s">
+      <c r="J61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="K61" s="78"/>
-      <c r="L61" s="79"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="71"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="77" t="s">
+      <c r="N61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="O61" s="78"/>
-      <c r="P61" s="79"/>
+      <c r="O61" s="70"/>
+      <c r="P61" s="71"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="77" t="s">
+      <c r="R61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="S61" s="78"/>
-      <c r="T61" s="79"/>
+      <c r="S61" s="70"/>
+      <c r="T61" s="71"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="77" t="s">
+      <c r="V61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="W61" s="78"/>
-      <c r="X61" s="79"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="71"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="77" t="s">
+      <c r="Z61" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="AA61" s="78"/>
-      <c r="AB61" s="79"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="71"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="74"/>
-      <c r="AE61" s="75"/>
-      <c r="AF61" s="76"/>
+      <c r="AD61" s="91"/>
+      <c r="AE61" s="92"/>
+      <c r="AF61" s="93"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="74"/>
-      <c r="AI61" s="75"/>
-      <c r="AJ61" s="76"/>
+      <c r="AH61" s="91"/>
+      <c r="AI61" s="92"/>
+      <c r="AJ61" s="93"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="74"/>
-      <c r="AM61" s="75"/>
-      <c r="AN61" s="76"/>
+      <c r="AL61" s="91"/>
+      <c r="AM61" s="92"/>
+      <c r="AN61" s="93"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="64"/>
-      <c r="D62" s="65"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="79"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="65"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="78"/>
+      <c r="H62" s="79"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="63" t="s">
+      <c r="J62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="K62" s="64"/>
-      <c r="L62" s="65"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="79"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="63" t="s">
+      <c r="N62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="O62" s="64"/>
-      <c r="P62" s="65"/>
+      <c r="O62" s="78"/>
+      <c r="P62" s="79"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="63" t="s">
+      <c r="R62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="S62" s="64"/>
-      <c r="T62" s="65"/>
+      <c r="S62" s="78"/>
+      <c r="T62" s="79"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="63" t="s">
+      <c r="V62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="W62" s="64"/>
-      <c r="X62" s="65"/>
+      <c r="W62" s="78"/>
+      <c r="X62" s="79"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="63" t="s">
+      <c r="Z62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AA62" s="64"/>
-      <c r="AB62" s="65"/>
+      <c r="AA62" s="78"/>
+      <c r="AB62" s="79"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="63"/>
-      <c r="AE62" s="64"/>
-      <c r="AF62" s="65"/>
+      <c r="AD62" s="77"/>
+      <c r="AE62" s="78"/>
+      <c r="AF62" s="79"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="63"/>
-      <c r="AI62" s="64"/>
-      <c r="AJ62" s="65"/>
+      <c r="AH62" s="77"/>
+      <c r="AI62" s="78"/>
+      <c r="AJ62" s="79"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="63"/>
-      <c r="AM62" s="64"/>
-      <c r="AN62" s="65"/>
+      <c r="AL62" s="77"/>
+      <c r="AM62" s="78"/>
+      <c r="AN62" s="79"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="63"/>
-      <c r="C63" s="64"/>
-      <c r="D63" s="65"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="78"/>
+      <c r="D63" s="79"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="65"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="78"/>
+      <c r="H63" s="79"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="64"/>
-      <c r="L63" s="65"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="79"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="63"/>
-      <c r="O63" s="64"/>
-      <c r="P63" s="65"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="78"/>
+      <c r="P63" s="79"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="63"/>
-      <c r="S63" s="64"/>
-      <c r="T63" s="65"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="78"/>
+      <c r="T63" s="79"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="63"/>
-      <c r="W63" s="64"/>
-      <c r="X63" s="65"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="78"/>
+      <c r="X63" s="79"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="63"/>
-      <c r="AA63" s="64"/>
-      <c r="AB63" s="65"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="78"/>
+      <c r="AB63" s="79"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="63"/>
-      <c r="AE63" s="64"/>
-      <c r="AF63" s="65"/>
+      <c r="AD63" s="77"/>
+      <c r="AE63" s="78"/>
+      <c r="AF63" s="79"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="63"/>
-      <c r="AI63" s="64"/>
-      <c r="AJ63" s="65"/>
+      <c r="AH63" s="77"/>
+      <c r="AI63" s="78"/>
+      <c r="AJ63" s="79"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="63"/>
-      <c r="AM63" s="64"/>
-      <c r="AN63" s="65"/>
+      <c r="AL63" s="77"/>
+      <c r="AM63" s="78"/>
+      <c r="AN63" s="79"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="66"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="68"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="74"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="68"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="73"/>
+      <c r="H64" s="74"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="66"/>
-      <c r="K64" s="67"/>
-      <c r="L64" s="68"/>
+      <c r="J64" s="72"/>
+      <c r="K64" s="73"/>
+      <c r="L64" s="74"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="66"/>
-      <c r="O64" s="67"/>
-      <c r="P64" s="68"/>
+      <c r="N64" s="72"/>
+      <c r="O64" s="73"/>
+      <c r="P64" s="74"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="66"/>
-      <c r="S64" s="67"/>
-      <c r="T64" s="68"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="73"/>
+      <c r="T64" s="74"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="66"/>
-      <c r="W64" s="67"/>
-      <c r="X64" s="68"/>
+      <c r="V64" s="72"/>
+      <c r="W64" s="73"/>
+      <c r="X64" s="74"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="66"/>
-      <c r="AA64" s="67"/>
-      <c r="AB64" s="68"/>
+      <c r="Z64" s="72"/>
+      <c r="AA64" s="73"/>
+      <c r="AB64" s="74"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="66"/>
-      <c r="AE64" s="67"/>
-      <c r="AF64" s="68"/>
+      <c r="AD64" s="72"/>
+      <c r="AE64" s="73"/>
+      <c r="AF64" s="74"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="66"/>
-      <c r="AI64" s="67"/>
-      <c r="AJ64" s="68"/>
+      <c r="AH64" s="72"/>
+      <c r="AI64" s="73"/>
+      <c r="AJ64" s="74"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="66"/>
-      <c r="AM64" s="67"/>
-      <c r="AN64" s="68"/>
+      <c r="AL64" s="72"/>
+      <c r="AM64" s="73"/>
+      <c r="AN64" s="74"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5626,23 +5630,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="108" t="s">
+      <c r="N66" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="108"/>
-      <c r="P66" s="108"/>
-      <c r="Q66" s="108"/>
-      <c r="R66" s="108"/>
-      <c r="S66" s="108"/>
-      <c r="T66" s="108"/>
-      <c r="U66" s="108"/>
-      <c r="V66" s="108"/>
-      <c r="W66" s="108"/>
-      <c r="X66" s="108"/>
-      <c r="Y66" s="108"/>
-      <c r="Z66" s="108"/>
-      <c r="AA66" s="108"/>
-      <c r="AB66" s="108"/>
+      <c r="O66" s="106"/>
+      <c r="P66" s="106"/>
+      <c r="Q66" s="106"/>
+      <c r="R66" s="106"/>
+      <c r="S66" s="106"/>
+      <c r="T66" s="106"/>
+      <c r="U66" s="106"/>
+      <c r="V66" s="106"/>
+      <c r="W66" s="106"/>
+      <c r="X66" s="106"/>
+      <c r="Y66" s="106"/>
+      <c r="Z66" s="106"/>
+      <c r="AA66" s="106"/>
+      <c r="AB66" s="106"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5673,21 +5677,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="108"/>
-      <c r="O67" s="108"/>
-      <c r="P67" s="108"/>
-      <c r="Q67" s="108"/>
-      <c r="R67" s="108"/>
-      <c r="S67" s="108"/>
-      <c r="T67" s="108"/>
-      <c r="U67" s="108"/>
-      <c r="V67" s="108"/>
-      <c r="W67" s="108"/>
-      <c r="X67" s="108"/>
-      <c r="Y67" s="108"/>
-      <c r="Z67" s="108"/>
-      <c r="AA67" s="108"/>
-      <c r="AB67" s="108"/>
+      <c r="N67" s="106"/>
+      <c r="O67" s="106"/>
+      <c r="P67" s="106"/>
+      <c r="Q67" s="106"/>
+      <c r="R67" s="106"/>
+      <c r="S67" s="106"/>
+      <c r="T67" s="106"/>
+      <c r="U67" s="106"/>
+      <c r="V67" s="106"/>
+      <c r="W67" s="106"/>
+      <c r="X67" s="106"/>
+      <c r="Y67" s="106"/>
+      <c r="Z67" s="106"/>
+      <c r="AA67" s="106"/>
+      <c r="AB67" s="106"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5707,52 +5711,52 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="91" t="s">
+      <c r="B68" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="92"/>
+      <c r="C68" s="128"/>
       <c r="D68" s="55"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="96" t="s">
+      <c r="F68" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="G68" s="97"/>
+      <c r="G68" s="105"/>
       <c r="H68" s="62"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="96" t="s">
+      <c r="J68" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="K68" s="97"/>
+      <c r="K68" s="105"/>
       <c r="L68" s="62"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="69"/>
-      <c r="O68" s="70"/>
+      <c r="N68" s="86"/>
+      <c r="O68" s="87"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="32"/>
-      <c r="R68" s="69" t="s">
+      <c r="R68" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S68" s="70"/>
+      <c r="S68" s="87"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="69"/>
-      <c r="W68" s="70"/>
+      <c r="V68" s="86"/>
+      <c r="W68" s="87"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="69"/>
-      <c r="AA68" s="70"/>
+      <c r="Z68" s="86"/>
+      <c r="AA68" s="87"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="69"/>
-      <c r="AE68" s="70"/>
+      <c r="AD68" s="86"/>
+      <c r="AE68" s="87"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="69"/>
-      <c r="AI68" s="70"/>
+      <c r="AH68" s="86"/>
+      <c r="AI68" s="87"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="69"/>
-      <c r="AM68" s="70"/>
+      <c r="AL68" s="86"/>
+      <c r="AM68" s="87"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5763,53 +5767,53 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="80" t="s">
+      <c r="B69" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="81"/>
-      <c r="D69" s="82"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="65"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="83" t="s">
+      <c r="F69" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="G69" s="84"/>
-      <c r="H69" s="85"/>
+      <c r="G69" s="99"/>
+      <c r="H69" s="100"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="83" t="s">
+      <c r="J69" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="K69" s="84"/>
-      <c r="L69" s="85"/>
+      <c r="K69" s="99"/>
+      <c r="L69" s="100"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="71"/>
-      <c r="O69" s="72"/>
-      <c r="P69" s="73"/>
+      <c r="N69" s="88"/>
+      <c r="O69" s="89"/>
+      <c r="P69" s="90"/>
       <c r="Q69" s="35"/>
-      <c r="R69" s="71" t="s">
+      <c r="R69" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S69" s="72"/>
-      <c r="T69" s="73"/>
+      <c r="S69" s="89"/>
+      <c r="T69" s="90"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="71"/>
-      <c r="W69" s="72"/>
-      <c r="X69" s="73"/>
+      <c r="V69" s="88"/>
+      <c r="W69" s="89"/>
+      <c r="X69" s="90"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="71"/>
-      <c r="AA69" s="72"/>
-      <c r="AB69" s="73"/>
+      <c r="Z69" s="88"/>
+      <c r="AA69" s="89"/>
+      <c r="AB69" s="90"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="71"/>
-      <c r="AE69" s="72"/>
-      <c r="AF69" s="73"/>
+      <c r="AD69" s="88"/>
+      <c r="AE69" s="89"/>
+      <c r="AF69" s="90"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="71"/>
-      <c r="AI69" s="72"/>
-      <c r="AJ69" s="73"/>
+      <c r="AH69" s="88"/>
+      <c r="AI69" s="89"/>
+      <c r="AJ69" s="90"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="71"/>
-      <c r="AM69" s="72"/>
-      <c r="AN69" s="73"/>
+      <c r="AL69" s="88"/>
+      <c r="AM69" s="89"/>
+      <c r="AN69" s="90"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5819,51 +5823,51 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="93" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70" s="94"/>
-      <c r="D70" s="95"/>
+      <c r="B70" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" s="67"/>
+      <c r="D70" s="68"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="86"/>
-      <c r="G70" s="87"/>
-      <c r="H70" s="88"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="102"/>
+      <c r="H70" s="103"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="86" t="s">
+      <c r="J70" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="K70" s="87"/>
-      <c r="L70" s="88"/>
+      <c r="K70" s="102"/>
+      <c r="L70" s="103"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="74"/>
-      <c r="O70" s="75"/>
-      <c r="P70" s="76"/>
+      <c r="N70" s="91"/>
+      <c r="O70" s="92"/>
+      <c r="P70" s="93"/>
       <c r="Q70" s="31"/>
-      <c r="R70" s="74" t="s">
+      <c r="R70" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="S70" s="75"/>
-      <c r="T70" s="76"/>
+      <c r="S70" s="92"/>
+      <c r="T70" s="93"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="74"/>
-      <c r="W70" s="75"/>
-      <c r="X70" s="76"/>
+      <c r="V70" s="91"/>
+      <c r="W70" s="92"/>
+      <c r="X70" s="93"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="74"/>
-      <c r="AA70" s="75"/>
-      <c r="AB70" s="76"/>
+      <c r="Z70" s="91"/>
+      <c r="AA70" s="92"/>
+      <c r="AB70" s="93"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="74"/>
-      <c r="AE70" s="75"/>
-      <c r="AF70" s="76"/>
+      <c r="AD70" s="91"/>
+      <c r="AE70" s="92"/>
+      <c r="AF70" s="93"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="74"/>
-      <c r="AI70" s="75"/>
-      <c r="AJ70" s="76"/>
+      <c r="AH70" s="91"/>
+      <c r="AI70" s="92"/>
+      <c r="AJ70" s="93"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="74"/>
-      <c r="AM70" s="75"/>
-      <c r="AN70" s="76"/>
+      <c r="AL70" s="91"/>
+      <c r="AM70" s="92"/>
+      <c r="AN70" s="93"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5873,53 +5877,53 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="77" t="s">
+      <c r="B71" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="78"/>
-      <c r="D71" s="79"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="71"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="77" t="s">
+      <c r="F71" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="G71" s="78"/>
-      <c r="H71" s="79"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="71"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="98" t="s">
-        <v>68</v>
-      </c>
-      <c r="K71" s="99"/>
-      <c r="L71" s="100"/>
+      <c r="J71" s="129" t="s">
+        <v>67</v>
+      </c>
+      <c r="K71" s="130"/>
+      <c r="L71" s="131"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="77"/>
-      <c r="O71" s="78"/>
-      <c r="P71" s="79"/>
+      <c r="N71" s="69"/>
+      <c r="O71" s="70"/>
+      <c r="P71" s="71"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="77" t="s">
+      <c r="R71" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="S71" s="78"/>
-      <c r="T71" s="79"/>
+      <c r="S71" s="70"/>
+      <c r="T71" s="71"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="77"/>
-      <c r="W71" s="78"/>
-      <c r="X71" s="79"/>
+      <c r="V71" s="69"/>
+      <c r="W71" s="70"/>
+      <c r="X71" s="71"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="77"/>
-      <c r="AA71" s="78"/>
-      <c r="AB71" s="79"/>
+      <c r="Z71" s="69"/>
+      <c r="AA71" s="70"/>
+      <c r="AB71" s="71"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="77"/>
-      <c r="AE71" s="78"/>
-      <c r="AF71" s="79"/>
+      <c r="AD71" s="69"/>
+      <c r="AE71" s="70"/>
+      <c r="AF71" s="71"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="77"/>
-      <c r="AI71" s="78"/>
-      <c r="AJ71" s="79"/>
+      <c r="AH71" s="69"/>
+      <c r="AI71" s="70"/>
+      <c r="AJ71" s="71"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="77"/>
-      <c r="AM71" s="78"/>
-      <c r="AN71" s="79"/>
+      <c r="AL71" s="69"/>
+      <c r="AM71" s="70"/>
+      <c r="AN71" s="71"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5929,51 +5933,51 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="66" t="s">
+      <c r="B72" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="67"/>
-      <c r="D72" s="68"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="74"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="68"/>
+      <c r="F72" s="72"/>
+      <c r="G72" s="73"/>
+      <c r="H72" s="74"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="66" t="s">
+      <c r="J72" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="K72" s="67"/>
-      <c r="L72" s="68"/>
+      <c r="K72" s="73"/>
+      <c r="L72" s="74"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="66"/>
-      <c r="O72" s="67"/>
-      <c r="P72" s="68"/>
+      <c r="N72" s="72"/>
+      <c r="O72" s="73"/>
+      <c r="P72" s="74"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="66" t="s">
+      <c r="R72" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="S72" s="67"/>
-      <c r="T72" s="68"/>
+      <c r="S72" s="73"/>
+      <c r="T72" s="74"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="66"/>
-      <c r="W72" s="67"/>
-      <c r="X72" s="68"/>
+      <c r="V72" s="72"/>
+      <c r="W72" s="73"/>
+      <c r="X72" s="74"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="66"/>
-      <c r="AA72" s="67"/>
-      <c r="AB72" s="68"/>
+      <c r="Z72" s="72"/>
+      <c r="AA72" s="73"/>
+      <c r="AB72" s="74"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="66"/>
-      <c r="AE72" s="67"/>
-      <c r="AF72" s="68"/>
+      <c r="AD72" s="72"/>
+      <c r="AE72" s="73"/>
+      <c r="AF72" s="74"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="66"/>
-      <c r="AI72" s="67"/>
-      <c r="AJ72" s="68"/>
+      <c r="AH72" s="72"/>
+      <c r="AI72" s="73"/>
+      <c r="AJ72" s="74"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="66"/>
-      <c r="AM72" s="67"/>
-      <c r="AN72" s="68"/>
+      <c r="AL72" s="72"/>
+      <c r="AM72" s="73"/>
+      <c r="AN72" s="74"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6027,56 +6031,56 @@
     </row>
     <row r=